--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="243">
   <si>
     <t>DELL</t>
   </si>
@@ -579,7 +579,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-12 19:58 UTC · данные на 2026-09-11 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-15 00:43 UTC · данные на 2026-09-11 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -660,7 +660,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-12 19:58 UTC</t>
+    <t>2026-09-15 00:43 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -693,7 +693,7 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
-    <t>4</t>
+    <t>2</t>
   </si>
   <si>
     <t>Источник цен</t>
@@ -709,9 +709,6 @@
   </si>
   <si>
     <t>Версия состояния</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Регламент данных</t>
@@ -3689,7 +3686,7 @@
         <v>390.4200134277344</v>
       </c>
       <c r="F5" s="17">
-        <v>1.047108316388112</v>
+        <v>1.047108330916111</v>
       </c>
       <c r="G5" s="20">
         <v>0.7163099250210818</v>
@@ -3701,16 +3698,16 @@
         <v>2.885035079678366</v>
       </c>
       <c r="J5" s="20">
-        <v>2.304642575666302</v>
+        <v>2.304642624456685</v>
       </c>
       <c r="K5" s="20">
         <v>0.602059804282177</v>
       </c>
       <c r="L5" s="20">
-        <v>0.2191623325268342</v>
+        <v>0.2191623314588784</v>
       </c>
       <c r="M5" s="20">
-        <v>-0.4773117363922201</v>
+        <v>-0.4773117369551982</v>
       </c>
       <c r="N5" s="20">
         <v>15.453106</v>
@@ -3728,7 +3725,7 @@
         <v>0.6699501897759226</v>
       </c>
       <c r="S5" s="11">
-        <v>78.66166951516148</v>
+        <v>78.66166944743316</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>89</v>
@@ -3751,7 +3748,7 @@
         <v>975.260009765625</v>
       </c>
       <c r="F6" s="17">
-        <v>1.037399728061543</v>
+        <v>1.037399736457067</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5381709417593455</v>
@@ -3763,16 +3760,16 @@
         <v>3.983916492932042</v>
       </c>
       <c r="J6" s="20">
-        <v>1.896417243282169</v>
+        <v>1.896417271006613</v>
       </c>
       <c r="K6" s="20">
         <v>0.4757611069296119</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.28307080405615</v>
+        <v>-3.28307080283564</v>
       </c>
       <c r="M6" s="20">
-        <v>0.2074618263134788</v>
+        <v>0.2074618263754775</v>
       </c>
       <c r="N6" s="20">
         <v>22.98937</v>
@@ -3790,7 +3787,7 @@
         <v>1.407351202710621</v>
       </c>
       <c r="S6" s="11">
-        <v>52.99519951104043</v>
+        <v>52.99519951119411</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>89</v>
@@ -3813,7 +3810,7 @@
         <v>1633.349975585938</v>
       </c>
       <c r="F7" s="17">
-        <v>1.009624300029146</v>
+        <v>1.009624307650897</v>
       </c>
       <c r="G7" s="20">
         <v>-0.5564495730839067</v>
@@ -3825,16 +3822,16 @@
         <v>4.120745224686987</v>
       </c>
       <c r="J7" s="20">
-        <v>1.689006656738524</v>
+        <v>1.689006681877619</v>
       </c>
       <c r="K7" s="20">
         <v>0.08036885848301029</v>
       </c>
       <c r="L7" s="20">
-        <v>-3.28307080405615</v>
+        <v>-3.28307080283564</v>
       </c>
       <c r="M7" s="20">
-        <v>0.6131855492623729</v>
+        <v>0.6131855493472688</v>
       </c>
       <c r="N7" s="20">
         <v>23.583628</v>
@@ -3875,7 +3872,7 @@
         <v>395.9299926757812</v>
       </c>
       <c r="F8" s="17">
-        <v>1.008651060724112</v>
+        <v>1.008651076085922</v>
       </c>
       <c r="G8" s="20">
         <v>0.704035078477925</v>
@@ -3887,16 +3884,16 @@
         <v>2.454207309239585</v>
       </c>
       <c r="J8" s="20">
-        <v>2.269552311330991</v>
+        <v>2.269552362960187</v>
       </c>
       <c r="K8" s="20">
         <v>0.7690833877198547</v>
       </c>
       <c r="L8" s="20">
-        <v>0.2642901010011683</v>
+        <v>0.2642900999037246</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.7575872668324671</v>
+        <v>-0.7575872675962474</v>
       </c>
       <c r="N8" s="20">
         <v>13.475398</v>
@@ -3911,10 +3908,10 @@
         <v>0.537</v>
       </c>
       <c r="R8" s="12">
-        <v>0.732208882978006</v>
+        <v>0.7322089986164448</v>
       </c>
       <c r="S8" s="11">
-        <v>74.73609878024585</v>
+        <v>74.73609888428106</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>89</v>
@@ -3937,7 +3934,7 @@
         <v>567.2899780273438</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9904076940040809</v>
+        <v>0.9904077039269833</v>
       </c>
       <c r="G9" s="20">
         <v>-0.2096896716004668</v>
@@ -3949,16 +3946,16 @@
         <v>2.195812652927404</v>
       </c>
       <c r="J9" s="20">
-        <v>3.05700407465007</v>
+        <v>3.057004107730039</v>
       </c>
       <c r="K9" s="20">
         <v>1.596984236488098</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.87914761694003</v>
+        <v>-2.879147615983456</v>
       </c>
       <c r="M9" s="20">
-        <v>0.09923566324962096</v>
+        <v>0.09923566251858906</v>
       </c>
       <c r="N9" s="20">
         <v>30.490984</v>
@@ -3976,7 +3973,7 @@
         <v>2.802185284799948</v>
       </c>
       <c r="S9" s="11">
-        <v>66.57472266074001</v>
+        <v>66.57472265866397</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>89</v>
@@ -3999,7 +3996,7 @@
         <v>62.09000015258789</v>
       </c>
       <c r="F10" s="17">
-        <v>0.9392451438436592</v>
+        <v>0.939245154268785</v>
       </c>
       <c r="G10" s="20">
         <v>0.5218225520995097</v>
@@ -4011,16 +4008,16 @@
         <v>2.225163086097977</v>
       </c>
       <c r="J10" s="20">
-        <v>2.611442955153402</v>
+        <v>2.61144298994151</v>
       </c>
       <c r="K10" s="20">
         <v>0.3221406505579205</v>
       </c>
       <c r="L10" s="20">
-        <v>-1.730503073782279</v>
+        <v>-1.730503073576264</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.1267380333326295</v>
+        <v>-0.126738033628476</v>
       </c>
       <c r="N10" s="20">
         <v>26.804123</v>
@@ -4038,7 +4035,7 @@
         <v>1.904225712994388</v>
       </c>
       <c r="S10" s="11">
-        <v>64.11120072873764</v>
+        <v>64.11120072894144</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>89</v>
@@ -4061,7 +4058,7 @@
         <v>259.4700012207031</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8588013948738856</v>
+        <v>0.8588014094590573</v>
       </c>
       <c r="G11" s="20">
         <v>0.4937473502003348</v>
@@ -4073,16 +4070,16 @@
         <v>2.423226908404409</v>
       </c>
       <c r="J11" s="20">
-        <v>2.035052488785592</v>
+        <v>2.035052537658677</v>
       </c>
       <c r="K11" s="20">
         <v>0.6850560911138626</v>
       </c>
       <c r="L11" s="20">
-        <v>0.4590621609727876</v>
+        <v>0.4590621597480739</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.8326244203771638</v>
+        <v>-0.8326244204180518</v>
       </c>
       <c r="N11" s="20">
         <v>14.559931</v>
@@ -4100,7 +4097,7 @@
         <v>0.5092246674773435</v>
       </c>
       <c r="S11" s="11">
-        <v>74.6143160244973</v>
+        <v>74.6143159237013</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>89</v>
@@ -4123,7 +4120,7 @@
         <v>375.2000122070312</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8511590155219225</v>
+        <v>0.8511590141827708</v>
       </c>
       <c r="G12" s="20">
         <v>1.215230467965422</v>
@@ -4135,16 +4132,16 @@
         <v>-0.3758707799348074</v>
       </c>
       <c r="J12" s="20">
-        <v>0.759023885475421</v>
+        <v>0.759023881299384</v>
       </c>
       <c r="K12" s="20">
         <v>3.812624241473097</v>
       </c>
       <c r="L12" s="20">
-        <v>0.5726267272838349</v>
+        <v>0.5726267259849146</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.3767976404345989</v>
+        <v>-0.3767976405396661</v>
       </c>
       <c r="N12" s="20">
         <v>9.931433999999999</v>
@@ -4162,7 +4159,7 @@
         <v>0.2518020698297732</v>
       </c>
       <c r="S12" s="11">
-        <v>58.68437519657845</v>
+        <v>58.68437519657044</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>89</v>
@@ -4185,7 +4182,7 @@
         <v>66.41999816894531</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8362185268379707</v>
+        <v>0.8362185200337082</v>
       </c>
       <c r="G13" s="20">
         <v>1.296202382232963</v>
@@ -4197,16 +4194,16 @@
         <v>-0.5780959126470824</v>
       </c>
       <c r="J13" s="20">
-        <v>1.269140525007449</v>
+        <v>1.269140502497847</v>
       </c>
       <c r="K13" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L13" s="20">
-        <v>0.02559509975794783</v>
+        <v>0.02559509881647475</v>
       </c>
       <c r="M13" s="20">
-        <v>-0.1083452608262806</v>
+        <v>-0.1083452607624456</v>
       </c>
       <c r="N13" s="20">
         <v>12.6192465</v>
@@ -4247,7 +4244,7 @@
         <v>338.5</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7901120610988167</v>
+        <v>0.7901120390773569</v>
       </c>
       <c r="G14" s="20">
         <v>-0.3753606373785415</v>
@@ -4259,16 +4256,16 @@
         <v>1.40880022334584</v>
       </c>
       <c r="J14" s="20">
-        <v>-0.1284957776473247</v>
+        <v>-0.1284958515787564</v>
       </c>
       <c r="K14" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L14" s="20">
-        <v>0.05388730734830557</v>
+        <v>0.05388730638834549</v>
       </c>
       <c r="M14" s="20">
-        <v>0.1786956586269247</v>
+        <v>0.1786956613215165</v>
       </c>
       <c r="N14" s="20">
         <v>16.97392</v>
@@ -4283,10 +4280,10 @@
         <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>0.1165209541550665</v>
+        <v>0.1165208417657306</v>
       </c>
       <c r="S14" s="11">
-        <v>46.91265082065971</v>
+        <v>46.91265079040681</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>89</v>
@@ -4309,7 +4306,7 @@
         <v>335.4500122070312</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7897842254659772</v>
+        <v>0.7897842317984384</v>
       </c>
       <c r="G15" s="20">
         <v>-0.3654991602347105</v>
@@ -4321,16 +4318,16 @@
         <v>1.40880022334584</v>
       </c>
       <c r="J15" s="20">
-        <v>-0.1561099253257341</v>
+        <v>-0.1561099043153476</v>
       </c>
       <c r="K15" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L15" s="20">
-        <v>0.07778047350152564</v>
+        <v>0.07778047252595303</v>
       </c>
       <c r="M15" s="20">
-        <v>0.2380425688219295</v>
+        <v>0.2380425699204254</v>
       </c>
       <c r="N15" s="20">
         <v>16.83283</v>
@@ -4348,7 +4345,7 @@
         <v>0.1077134950968779</v>
       </c>
       <c r="S15" s="11">
-        <v>46.26375764089853</v>
+        <v>46.26375761869606</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>89</v>
@@ -4371,7 +4368,7 @@
         <v>247.7200012207031</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7866722245329362</v>
+        <v>0.7866722272056267</v>
       </c>
       <c r="G16" s="20">
         <v>0.313884107527872</v>
@@ -4383,16 +4380,16 @@
         <v>0.202940183485447</v>
       </c>
       <c r="J16" s="20">
-        <v>1.238107958642042</v>
+        <v>1.238107967545342</v>
       </c>
       <c r="K16" s="20">
         <v>3.515693426472779</v>
       </c>
       <c r="L16" s="20">
-        <v>-1.611896356077898</v>
+        <v>-1.611896355949384</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.9099416986817039</v>
+        <v>-0.9099416987568313</v>
       </c>
       <c r="N16" s="20">
         <v>23.76077</v>
@@ -4410,7 +4407,7 @@
         <v>0.2494004299711519</v>
       </c>
       <c r="S16" s="11">
-        <v>64.8923482211983</v>
+        <v>64.89234821607687</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>89</v>
@@ -4433,7 +4430,7 @@
         <v>61.45999908447266</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7481695366145695</v>
+        <v>0.7481695457661486</v>
       </c>
       <c r="G17" s="20">
         <v>0.6321397772136792</v>
@@ -4445,16 +4442,16 @@
         <v>2.930171312463986</v>
       </c>
       <c r="J17" s="20">
-        <v>0.5613260254512988</v>
+        <v>0.5613260562665766</v>
       </c>
       <c r="K17" s="20">
         <v>0.8675448211661402</v>
       </c>
       <c r="L17" s="20">
-        <v>0.341750242859634</v>
+        <v>0.3417502417115755</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.6265932572509491</v>
+        <v>-0.6265932575524594</v>
       </c>
       <c r="N17" s="20">
         <v>17.710915</v>
@@ -4472,7 +4469,7 @@
         <v>0.06192779992740483</v>
       </c>
       <c r="S17" s="11">
-        <v>63.75161075439093</v>
+        <v>63.75161075517163</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>89</v>
@@ -4495,7 +4492,7 @@
         <v>199.2799987792969</v>
       </c>
       <c r="F18" s="17">
-        <v>0.7307640803651428</v>
+        <v>0.7307640765324444</v>
       </c>
       <c r="G18" s="20">
         <v>-0.3904668641526476</v>
@@ -4507,16 +4504,16 @@
         <v>0.4411015820383316</v>
       </c>
       <c r="J18" s="20">
-        <v>1.866696494227026</v>
+        <v>1.866696481641062</v>
       </c>
       <c r="K18" s="20">
         <v>0.4834936802369117</v>
       </c>
       <c r="L18" s="20">
-        <v>-0.3872192614912924</v>
+        <v>-0.38721926216302</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.6915728158848526</v>
+        <v>-0.6915728160924274</v>
       </c>
       <c r="N18" s="20">
         <v>26.250353</v>
@@ -4534,7 +4531,7 @@
         <v>1.072723636880157</v>
       </c>
       <c r="S18" s="11">
-        <v>61.61763607405091</v>
+        <v>61.61763607406569</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>89</v>
@@ -4557,7 +4554,7 @@
         <v>40.09999847412109</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6640922651628306</v>
+        <v>0.6640922650584004</v>
       </c>
       <c r="G19" s="20">
         <v>0.09785741135882757</v>
@@ -4569,16 +4566,16 @@
         <v>3.920900829953943</v>
       </c>
       <c r="J19" s="20">
-        <v>0.7484635783314193</v>
+        <v>0.7484635777842236</v>
       </c>
       <c r="K19" s="20">
         <v>3.370836553182694</v>
       </c>
       <c r="L19" s="20">
-        <v>-3.28307080405615</v>
+        <v>-3.28307080283564</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.5964576431351394</v>
+        <v>-0.5964576433039166</v>
       </c>
       <c r="N19" s="20">
         <v>12.144172</v>
@@ -4619,7 +4616,7 @@
         <v>155.8300018310547</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6514352203361898</v>
+        <v>0.6514352314021793</v>
       </c>
       <c r="G20" s="20">
         <v>0.4941985872113094</v>
@@ -4631,16 +4628,16 @@
         <v>-0.03241763381358259</v>
       </c>
       <c r="J20" s="20">
-        <v>0.9791290750999503</v>
+        <v>0.9791291122804968</v>
       </c>
       <c r="K20" s="20">
         <v>3.282169712592323</v>
       </c>
       <c r="L20" s="20">
-        <v>0.2185710605219728</v>
+        <v>0.2185710594544033</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.5711024418782924</v>
+        <v>-0.5711024421797948</v>
       </c>
       <c r="N20" s="20">
         <v>17.05809</v>
@@ -4658,7 +4655,7 @@
         <v>0.369413942364327</v>
       </c>
       <c r="S20" s="11">
-        <v>48.25302802891057</v>
+        <v>48.25302803577884</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>89</v>
@@ -4681,7 +4678,7 @@
         <v>256.7799987792969</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6494692721130143</v>
+        <v>0.6494692717513246</v>
       </c>
       <c r="G21" s="20">
         <v>-0.04482148267622166</v>
@@ -4693,16 +4690,16 @@
         <v>1.035672297744961</v>
       </c>
       <c r="J21" s="20">
-        <v>0.212280936555171</v>
+        <v>0.2122809354201503</v>
       </c>
       <c r="K21" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4583906517463234</v>
+        <v>-0.4583906523715454</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.1409564339374406</v>
+        <v>-0.1409564337333159</v>
       </c>
       <c r="N21" s="20">
         <v>20.797264</v>
@@ -4743,7 +4740,7 @@
         <v>253.7100067138672</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6419214794512311</v>
+        <v>0.6419214616278026</v>
       </c>
       <c r="G22" s="20">
         <v>1.286238812250283</v>
@@ -4755,16 +4752,16 @@
         <v>-0.05063264711205382</v>
       </c>
       <c r="J22" s="20">
-        <v>0.452464879902679</v>
+        <v>0.4524648206445526</v>
       </c>
       <c r="K22" s="20">
         <v>1.849066126306075</v>
       </c>
       <c r="L22" s="20">
-        <v>0.5039178719495193</v>
+        <v>0.5039178706954955</v>
       </c>
       <c r="M22" s="20">
-        <v>0.01427939577103855</v>
+        <v>0.01427939613667511</v>
       </c>
       <c r="N22" s="20">
         <v>5.1976376</v>
@@ -4779,10 +4776,10 @@
         <v>0.118</v>
       </c>
       <c r="R22" s="12">
-        <v>0.2491247109916046</v>
+        <v>0.2491246171502992</v>
       </c>
       <c r="S22" s="11">
-        <v>46.35496986566098</v>
+        <v>46.35496986092373</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>89</v>
@@ -4805,7 +4802,7 @@
         <v>35.47999954223633</v>
       </c>
       <c r="F23" s="17">
-        <v>0.6187519747233313</v>
+        <v>0.6187519821526637</v>
       </c>
       <c r="G23" s="20">
         <v>1.115176779328165</v>
@@ -4817,16 +4814,16 @@
         <v>-0.3840221445724293</v>
       </c>
       <c r="J23" s="20">
-        <v>2.108004395676367</v>
+        <v>2.108004420646181</v>
       </c>
       <c r="K23" s="20">
         <v>0.403590422728146</v>
       </c>
       <c r="L23" s="20">
-        <v>-0.7643769867634796</v>
+        <v>-0.7643769871887608</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.2570308513837053</v>
+        <v>-0.257030851834891</v>
       </c>
       <c r="N23" s="20">
         <v>12.458015</v>
@@ -4844,7 +4841,7 @@
         <v>0.9135080532131845</v>
       </c>
       <c r="S23" s="11">
-        <v>71.78658040239313</v>
+        <v>71.78658040207837</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>89</v>
@@ -4867,7 +4864,7 @@
         <v>102.9400024414062</v>
       </c>
       <c r="F24" s="17">
-        <v>0.6100380066154844</v>
+        <v>0.6100380140285703</v>
       </c>
       <c r="G24" s="20">
         <v>-0.6233680543607623</v>
@@ -4879,16 +4876,16 @@
         <v>0.5264142543422116</v>
       </c>
       <c r="J24" s="20">
-        <v>1.498797534054144</v>
+        <v>1.49879755877251</v>
       </c>
       <c r="K24" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L24" s="20">
-        <v>-2.467621401410658</v>
+        <v>-2.467621400722987</v>
       </c>
       <c r="M24" s="20">
-        <v>0.578951094893308</v>
+        <v>0.5789510943472597</v>
       </c>
       <c r="N24" s="20">
         <v>46.910885</v>
@@ -4929,7 +4926,7 @@
         <v>1029.180053710938</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5765399212059111</v>
+        <v>0.5765399084897844</v>
       </c>
       <c r="G25" s="20">
         <v>0.3667190394925228</v>
@@ -4941,16 +4938,16 @@
         <v>0.9154597556552251</v>
       </c>
       <c r="J25" s="20">
-        <v>0.2276284146507829</v>
+        <v>0.2276283725753302</v>
       </c>
       <c r="K25" s="20">
         <v>1.655236288736424</v>
       </c>
       <c r="L25" s="20">
-        <v>0.1228253592743591</v>
+        <v>0.1228253582693528</v>
       </c>
       <c r="M25" s="20">
-        <v>0.1625829751186763</v>
+        <v>0.1625829747037942</v>
       </c>
       <c r="N25" s="20">
         <v>16.02546</v>
@@ -4968,7 +4965,7 @@
         <v>0.3190503949464873</v>
       </c>
       <c r="S25" s="11">
-        <v>49.59336862656026</v>
+        <v>49.5933686304215</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>89</v>
@@ -4991,7 +4988,7 @@
         <v>44.72999954223633</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5661190857983124</v>
+        <v>0.5661190823210835</v>
       </c>
       <c r="G26" s="20">
         <v>1.1788603618118</v>
@@ -5003,16 +5000,16 @@
         <v>-0.2890980177519417</v>
       </c>
       <c r="J26" s="20">
-        <v>1.452616977870309</v>
+        <v>1.452616966504415</v>
       </c>
       <c r="K26" s="20">
         <v>-0.5748378530888681</v>
       </c>
       <c r="L26" s="20">
-        <v>-0.2447469088796478</v>
+        <v>-0.2447469096444711</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.7397905244528716</v>
+        <v>-0.7397905247225112</v>
       </c>
       <c r="N26" s="20">
         <v>9.023208</v>
@@ -5053,7 +5050,7 @@
         <v>121.4700012207031</v>
       </c>
       <c r="F27" s="17">
-        <v>0.548106862585914</v>
+        <v>0.5481068609073245</v>
       </c>
       <c r="G27" s="20">
         <v>0.3314207580374121</v>
@@ -5065,16 +5062,16 @@
         <v>0.5229426848176244</v>
       </c>
       <c r="J27" s="20">
-        <v>0.5329666998352387</v>
+        <v>0.5329666943539282</v>
       </c>
       <c r="K27" s="20">
         <v>1.638740132347517</v>
       </c>
       <c r="L27" s="20">
-        <v>0.1330221643240032</v>
+        <v>0.133022163312334</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.1146722049330454</v>
+        <v>-0.1146722046017475</v>
       </c>
       <c r="N27" s="20">
         <v>16.146498</v>
@@ -5115,7 +5112,7 @@
         <v>208.3000030517578</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5211228655235287</v>
+        <v>0.5211228793123472</v>
       </c>
       <c r="G28" s="20">
         <v>0.5809437263948974</v>
@@ -5127,16 +5124,16 @@
         <v>4.120745224686987</v>
       </c>
       <c r="J28" s="20">
-        <v>-0.007026706027478985</v>
+        <v>-0.007026659802694929</v>
       </c>
       <c r="K28" s="20">
         <v>0.5994822798464103</v>
       </c>
       <c r="L28" s="20">
-        <v>0.6205594412417217</v>
+        <v>0.6205594399114807</v>
       </c>
       <c r="M28" s="20">
-        <v>0.03470843509434487</v>
+        <v>0.03470843510931609</v>
       </c>
       <c r="N28" s="20">
         <v>12.092511</v>
@@ -5154,7 +5151,7 @@
         <v>0.1830537011774684</v>
       </c>
       <c r="S28" s="11">
-        <v>41.95173731730433</v>
+        <v>41.95173730919371</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>89</v>
@@ -5177,7 +5174,7 @@
         <v>118.1699981689453</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5139010334601949</v>
+        <v>0.5139010321103271</v>
       </c>
       <c r="G29" s="20">
         <v>0.3599925540636538</v>
@@ -5189,16 +5186,16 @@
         <v>0.4821804333312243</v>
       </c>
       <c r="J29" s="20">
-        <v>-0.2352352687616578</v>
+        <v>-0.2352352732388189</v>
       </c>
       <c r="K29" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L29" s="20">
-        <v>0.01383538483762773</v>
+        <v>0.0138353839038388</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.1636195730196011</v>
+        <v>-0.1636195724032518</v>
       </c>
       <c r="N29" s="20">
         <v>16.105392</v>
@@ -5239,7 +5236,7 @@
         <v>350.3699951171875</v>
       </c>
       <c r="F30" s="17">
-        <v>0.5031079639653683</v>
+        <v>0.5031079626401821</v>
       </c>
       <c r="G30" s="20">
         <v>0.09769025453656566</v>
@@ -5251,16 +5248,16 @@
         <v>0.4704496970046058</v>
       </c>
       <c r="J30" s="20">
-        <v>1.494343638290467</v>
+        <v>1.494343633819099</v>
       </c>
       <c r="K30" s="20">
         <v>1.69802319437015</v>
       </c>
       <c r="L30" s="20">
-        <v>-1.695948106532149</v>
+        <v>-1.695948106348713</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.9231173578507184</v>
+        <v>-0.923117357785492</v>
       </c>
       <c r="N30" s="20">
         <v>33.248394</v>
@@ -5301,7 +5298,7 @@
         <v>214.0599975585938</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4908089627269018</v>
+        <v>0.4908089639076276</v>
       </c>
       <c r="G31" s="20">
         <v>0.5306330587817526</v>
@@ -5313,16 +5310,16 @@
         <v>2.322186162377909</v>
       </c>
       <c r="J31" s="20">
-        <v>0.8110245372285574</v>
+        <v>0.8110245415781004</v>
       </c>
       <c r="K31" s="20">
         <v>-0.1711975264478132</v>
       </c>
       <c r="L31" s="20">
-        <v>0.8411276710349463</v>
+        <v>0.8411276695605793</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.7226139334633331</v>
+        <v>-0.7226139339092731</v>
       </c>
       <c r="N31" s="20">
         <v>20.076998</v>
@@ -5340,7 +5337,7 @@
         <v>0.1062895957896659</v>
       </c>
       <c r="S31" s="11">
-        <v>69.51936874299193</v>
+        <v>69.51936874222667</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>89</v>
@@ -5363,7 +5360,7 @@
         <v>217.1499938964844</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4829213824961959</v>
+        <v>0.4829213808748131</v>
       </c>
       <c r="G32" s="20">
         <v>0.2276945080429548</v>
@@ -5375,16 +5372,16 @@
         <v>-0.8985721544356027</v>
       </c>
       <c r="J32" s="20">
-        <v>0.5363377512297637</v>
+        <v>0.5363377459748063</v>
       </c>
       <c r="K32" s="20">
         <v>3.362072970101089</v>
       </c>
       <c r="L32" s="20">
-        <v>-0.1378791351203909</v>
+        <v>-0.1378791359550449</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.3659443941636323</v>
+        <v>-0.3659443940988363</v>
       </c>
       <c r="N32" s="20">
         <v>39.2238</v>
@@ -5425,7 +5422,7 @@
         <v>218.2899932861328</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4503678786834968</v>
+        <v>0.4503679053242157</v>
       </c>
       <c r="G33" s="20">
         <v>-1.255664189485384</v>
@@ -5437,16 +5434,16 @@
         <v>2.430954222251415</v>
       </c>
       <c r="J33" s="20">
-        <v>0.3601515821561077</v>
+        <v>0.3601516709464662</v>
       </c>
       <c r="K33" s="20">
         <v>-0.3093528362049048</v>
       </c>
       <c r="L33" s="20">
-        <v>-0.1969188089606057</v>
+        <v>-0.1969188097566814</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.05941751595953304</v>
+        <v>-0.059417515317334</v>
       </c>
       <c r="N33" s="20">
         <v>29.159492</v>
@@ -5461,10 +5458,10 @@
         <v>1.059</v>
       </c>
       <c r="R33" s="12">
-        <v>0.1946540311177754</v>
+        <v>0.1946541308810243</v>
       </c>
       <c r="S33" s="11">
-        <v>49.94178813079729</v>
+        <v>49.94178812835036</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>89</v>
@@ -5487,7 +5484,7 @@
         <v>63.63999938964844</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4412888977203814</v>
+        <v>0.44128887322844</v>
       </c>
       <c r="G34" s="20">
         <v>0.4785242056074159</v>
@@ -5499,16 +5496,16 @@
         <v>0.2335665909722698</v>
       </c>
       <c r="J34" s="20">
-        <v>0.3722765328553345</v>
+        <v>0.3722764513651591</v>
       </c>
       <c r="K34" s="20">
         <v>0.8031067102719743</v>
       </c>
       <c r="L34" s="20">
-        <v>0.5509703820045521</v>
+        <v>0.5509703807197827</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.1813711490988128</v>
+        <v>-0.1813711486963455</v>
       </c>
       <c r="N34" s="20">
         <v>14.718061</v>
@@ -5526,7 +5523,7 @@
         <v>0.1030022530335821</v>
       </c>
       <c r="S34" s="11">
-        <v>42.45064590413351</v>
+        <v>42.4506459041333</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>89</v>
@@ -5549,7 +5546,7 @@
         <v>214.3800048828125</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4345413960031605</v>
+        <v>0.4345414076806038</v>
       </c>
       <c r="G35" s="20">
         <v>0.3451625228080399</v>
@@ -5561,16 +5558,16 @@
         <v>0.3853148937972363</v>
       </c>
       <c r="J35" s="20">
-        <v>0.435411271014154</v>
+        <v>0.4354113101104577</v>
       </c>
       <c r="K35" s="20">
         <v>0.2979119208617143</v>
       </c>
       <c r="L35" s="20">
-        <v>0.5831377480819958</v>
+        <v>0.5831377467762073</v>
       </c>
       <c r="M35" s="20">
-        <v>0.108535981877513</v>
+        <v>0.1085359822137566</v>
       </c>
       <c r="N35" s="20">
         <v>17.572235</v>
@@ -5588,7 +5585,7 @@
         <v>0.4038903336206143</v>
       </c>
       <c r="S35" s="11">
-        <v>49.59978530119027</v>
+        <v>49.59978529957923</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>89</v>
@@ -5611,7 +5608,7 @@
         <v>379.7200012207031</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4194332385268906</v>
+        <v>0.419433272667214</v>
       </c>
       <c r="G36" s="20">
         <v>-1.119776310688084</v>
@@ -5623,16 +5620,16 @@
         <v>3.683499757563413</v>
       </c>
       <c r="J36" s="20">
-        <v>0.9544690723013466</v>
+        <v>0.954469186224158</v>
       </c>
       <c r="K36" s="20">
         <v>0.4185400644555927</v>
       </c>
       <c r="L36" s="20">
-        <v>-3.267237995490921</v>
+        <v>-3.267237994280757</v>
       </c>
       <c r="M36" s="20">
-        <v>0.2746737501477036</v>
+        <v>0.2746737487835807</v>
       </c>
       <c r="N36" s="20">
         <v>49.04258</v>
@@ -5647,10 +5644,10 @@
         <v>1.039</v>
       </c>
       <c r="R36" s="12">
-        <v>0.3258760256022546</v>
+        <v>0.3258761668860892</v>
       </c>
       <c r="S36" s="11">
-        <v>53.13233410611146</v>
+        <v>53.13233410644662</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>89</v>
@@ -5673,7 +5670,7 @@
         <v>137.3500061035156</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4042025067649112</v>
+        <v>0.4042025057020031</v>
       </c>
       <c r="G37" s="20">
         <v>0.5166686592886003</v>
@@ -5685,16 +5682,16 @@
         <v>0.8009706460259883</v>
       </c>
       <c r="J37" s="20">
-        <v>0.9931344554616052</v>
+        <v>0.9931344522895759</v>
       </c>
       <c r="K37" s="20">
         <v>-0.06912755879145449</v>
       </c>
       <c r="L37" s="20">
-        <v>0.5669399045497632</v>
+        <v>0.5669399032545589</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.8817182410915136</v>
+        <v>-0.8817182415113511</v>
       </c>
       <c r="N37" s="20">
         <v>17.759258</v>
@@ -5712,7 +5709,7 @@
         <v>0.1582708669984993</v>
       </c>
       <c r="S37" s="11">
-        <v>67.83650142728372</v>
+        <v>67.83650141589177</v>
       </c>
       <c r="T37" s="9" t="s">
         <v>89</v>
@@ -5735,7 +5732,7 @@
         <v>447.1799926757812</v>
       </c>
       <c r="F38" s="17">
-        <v>0.3998917584295852</v>
+        <v>0.3998918004719155</v>
       </c>
       <c r="G38" s="20">
         <v>-0.9800881674162824</v>
@@ -5747,16 +5744,16 @@
         <v>2.675284350851072</v>
       </c>
       <c r="J38" s="20">
-        <v>0.403865008371416</v>
+        <v>0.4038651476196932</v>
       </c>
       <c r="K38" s="20">
         <v>-0.2212015005016859</v>
       </c>
       <c r="L38" s="20">
-        <v>-3.28307080405615</v>
+        <v>-3.28307080283564</v>
       </c>
       <c r="M38" s="20">
-        <v>0.8451427086171256</v>
+        <v>0.8451427110498325</v>
       </c>
       <c r="N38" s="20">
         <v>17.358335</v>
@@ -5771,10 +5768,10 @@
         <v>0.438</v>
       </c>
       <c r="R38" s="12">
-        <v>0.7131486186146514</v>
+        <v>0.7131488189039898</v>
       </c>
       <c r="S38" s="11">
-        <v>43.91793140604355</v>
+        <v>43.91793139510307</v>
       </c>
       <c r="T38" s="9" t="s">
         <v>89</v>
@@ -5797,7 +5794,7 @@
         <v>30.26000022888184</v>
       </c>
       <c r="F39" s="17">
-        <v>0.397634661513634</v>
+        <v>0.3976346685421113</v>
       </c>
       <c r="G39" s="20">
         <v>0.5193752875190029</v>
@@ -5809,16 +5806,16 @@
         <v>-0.1830681180986245</v>
       </c>
       <c r="J39" s="20">
-        <v>0.9786210716079635</v>
+        <v>0.9786210952682423</v>
       </c>
       <c r="K39" s="20">
         <v>-0.4727678854325094</v>
       </c>
       <c r="L39" s="20">
-        <v>0.1894796363143733</v>
+        <v>0.189479635265813</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.5689013157994487</v>
+        <v>-0.568901315883107</v>
       </c>
       <c r="N39" s="20">
         <v>17.923977</v>
@@ -5836,7 +5833,7 @@
         <v>0.4550608701426258</v>
       </c>
       <c r="S39" s="11">
-        <v>57.77418061931306</v>
+        <v>57.77418061931316</v>
       </c>
       <c r="T39" s="9" t="s">
         <v>89</v>
@@ -5859,7 +5856,7 @@
         <v>147.3600006103516</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3973518951896139</v>
+        <v>0.3973518871613852</v>
       </c>
       <c r="G40" s="20">
         <v>0.6186160464919896</v>
@@ -5871,16 +5868,16 @@
         <v>1.428599056298859</v>
       </c>
       <c r="J40" s="20">
-        <v>0.4401632572947111</v>
+        <v>0.4401632307542995</v>
       </c>
       <c r="K40" s="20">
         <v>-0.5186478203891555</v>
       </c>
       <c r="L40" s="20">
-        <v>0.3288122235739222</v>
+        <v>0.3288122224343177</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.2606557203458318</v>
+        <v>-0.2606557203174431</v>
       </c>
       <c r="N40" s="20">
         <v>11.298833</v>
@@ -5898,7 +5895,7 @@
         <v>0.1245209739777566</v>
       </c>
       <c r="S40" s="11">
-        <v>54.45698842726613</v>
+        <v>54.45698842727787</v>
       </c>
       <c r="T40" s="9" t="s">
         <v>89</v>
@@ -5921,7 +5918,7 @@
         <v>204.9700012207031</v>
       </c>
       <c r="F41" s="17">
-        <v>0.397082720356971</v>
+        <v>0.3970827025069025</v>
       </c>
       <c r="G41" s="20">
         <v>0.6168563890519317</v>
@@ -5933,16 +5930,16 @@
         <v>1.604307978960174</v>
       </c>
       <c r="J41" s="20">
-        <v>0.5467414341207243</v>
+        <v>0.5467413748387874</v>
       </c>
       <c r="K41" s="20">
         <v>-0.1980037805797862</v>
       </c>
       <c r="L41" s="20">
-        <v>0.2824804951393964</v>
+        <v>0.2824804940300665</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.3051572185564283</v>
+        <v>-0.3051572185430234</v>
       </c>
       <c r="N41" s="20">
         <v>37.874523</v>
@@ -5960,7 +5957,7 @@
         <v>0.1707381737518001</v>
       </c>
       <c r="S41" s="11">
-        <v>56.25120194145847</v>
+        <v>56.25120194060135</v>
       </c>
       <c r="T41" s="9" t="s">
         <v>89</v>
@@ -5983,7 +5980,7 @@
         <v>28.04000091552734</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3940519539599348</v>
+        <v>0.3940519480670779</v>
       </c>
       <c r="G42" s="20">
         <v>-0.07115990276327171</v>
@@ -5995,16 +5992,16 @@
         <v>-1.178947812209808</v>
       </c>
       <c r="J42" s="20">
-        <v>0.4619663793250618</v>
+        <v>0.4619663599887935</v>
       </c>
       <c r="K42" s="20">
         <v>4.196860964161699</v>
       </c>
       <c r="L42" s="20">
-        <v>1.141149647839567</v>
+        <v>1.141149646169156</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.3320940753280518</v>
+        <v>-0.3320940752249485</v>
       </c>
       <c r="N42" s="20">
         <v>403.57144</v>
@@ -6045,7 +6042,7 @@
         <v>409.7999877929688</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3655179607761477</v>
+        <v>0.3655179421124001</v>
       </c>
       <c r="G43" s="20">
         <v>0.3688830871595546</v>
@@ -6057,16 +6054,16 @@
         <v>0.1661481722292586</v>
       </c>
       <c r="J43" s="20">
-        <v>1.624220314331475</v>
+        <v>1.624220252399921</v>
       </c>
       <c r="K43" s="20">
         <v>-0.1737750508835799</v>
       </c>
       <c r="L43" s="20">
-        <v>0.227922941045356</v>
+        <v>0.2279229399716757</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.3625256249966889</v>
+        <v>-0.3625256252449436</v>
       </c>
       <c r="N43" s="20">
         <v>38.02462</v>
@@ -6084,7 +6081,7 @@
         <v>1.522472101653082</v>
       </c>
       <c r="S43" s="11">
-        <v>63.34184072804205</v>
+        <v>63.3418407280259</v>
       </c>
       <c r="T43" s="9" t="s">
         <v>89</v>
@@ -6107,7 +6104,7 @@
         <v>126.8099975585938</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3617139958844974</v>
+        <v>0.3617139796245003</v>
       </c>
       <c r="G44" s="20">
         <v>0.462770354618154</v>
@@ -6119,16 +6116,16 @@
         <v>-0.2047856713387676</v>
       </c>
       <c r="J44" s="20">
-        <v>1.068677601527799</v>
+        <v>1.068677546500124</v>
       </c>
       <c r="K44" s="20">
         <v>-0.3340970707882645</v>
       </c>
       <c r="L44" s="20">
-        <v>-0.5008048408114121</v>
+        <v>-0.5008048414089193</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.9583372980614338</v>
+        <v>-0.9583372945094849</v>
       </c>
       <c r="N44" s="20">
         <v>16.152584</v>
@@ -6146,7 +6143,7 @@
         <v>0.1126020562190284</v>
       </c>
       <c r="S44" s="11">
-        <v>57.66914612294107</v>
+        <v>57.66914608363002</v>
       </c>
       <c r="T44" s="9" t="s">
         <v>89</v>
@@ -6514,78 +6511,78 @@
         <v>227</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>230</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>232</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="B19" s="14" t="s">
         <v>234</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>236</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B27" s="21"/>
     </row>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -17,7 +17,7 @@
     <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$T$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="245">
   <si>
     <t>DELL</t>
   </si>
@@ -54,6 +54,18 @@
     <t>APA</t>
   </si>
   <si>
+    <t>NVDA</t>
+  </si>
+  <si>
+    <t>TRV</t>
+  </si>
+  <si>
+    <t>GOOG</t>
+  </si>
+  <si>
+    <t>CNC</t>
+  </si>
+  <si>
     <t>Открытые позиции</t>
   </si>
   <si>
@@ -165,6 +177,30 @@
     <t>APA Corporation</t>
   </si>
   <si>
+    <t>Nvidia</t>
+  </si>
+  <si>
+    <t>2026-09-14</t>
+  </si>
+  <si>
+    <t>Travelers Companies (The)</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class C)</t>
+  </si>
+  <si>
+    <t>Communication Services</t>
+  </si>
+  <si>
+    <t>Centene Corporation</t>
+  </si>
+  <si>
+    <t>Health Care</t>
+  </si>
+  <si>
     <t>Итого</t>
   </si>
   <si>
@@ -297,49 +333,46 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>GOOGL</t>
+  </si>
+  <si>
+    <t>Alphabet Inc. (Class A)</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
     <t>HPE</t>
   </si>
   <si>
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
-    <t>TRV</t>
-  </si>
-  <si>
-    <t>Travelers Companies (The)</t>
-  </si>
-  <si>
-    <t>Financials</t>
-  </si>
-  <si>
-    <t>CNC</t>
-  </si>
-  <si>
-    <t>Centene Corporation</t>
-  </si>
-  <si>
-    <t>Health Care</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class A)</t>
-  </si>
-  <si>
-    <t>Communication Services</t>
-  </si>
-  <si>
-    <t>GOOG</t>
-  </si>
-  <si>
-    <t>Alphabet Inc. (Class C)</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>AMZN</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>Consumer Discretionary</t>
   </si>
   <si>
     <t>NTAP</t>
@@ -348,40 +381,46 @@
     <t>NetApp</t>
   </si>
   <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
+    <t>DLTR</t>
+  </si>
+  <si>
+    <t>Dollar Tree</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
     <t>SMCI</t>
   </si>
   <si>
     <t>Supermicro</t>
   </si>
   <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>Amazon</t>
-  </si>
-  <si>
-    <t>Consumer Discretionary</t>
-  </si>
-  <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
   </si>
   <si>
     <t>INTC</t>
@@ -390,34 +429,16 @@
     <t>Intel</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
-  </si>
-  <si>
-    <t>DLTR</t>
-  </si>
-  <si>
-    <t>Dollar Tree</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>BIIB</t>
+  </si>
+  <si>
+    <t>Biogen</t>
   </si>
   <si>
     <t>CVX</t>
@@ -426,16 +447,10 @@
     <t>Chevron Corporation</t>
   </si>
   <si>
-    <t>BIIB</t>
-  </si>
-  <si>
-    <t>Biogen</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>Nvidia</t>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
   </si>
   <si>
     <t>BMY</t>
@@ -444,16 +459,28 @@
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
     <t>MS</t>
   </si>
   <si>
     <t>Morgan Stanley</t>
   </si>
   <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>News Corp (Class A)</t>
   </si>
   <si>
     <t>COP</t>
@@ -462,43 +489,22 @@
     <t>ConocoPhillips</t>
   </si>
   <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
-  </si>
-  <si>
-    <t>WBD</t>
-  </si>
-  <si>
-    <t>Warner Bros. Discovery</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>NEM</t>
-  </si>
-  <si>
-    <t>Newmont</t>
-  </si>
-  <si>
-    <t>Materials</t>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>Regeneron Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>BBY</t>
+  </si>
+  <si>
+    <t>Best Buy</t>
+  </si>
+  <si>
+    <t>PRU</t>
+  </si>
+  <si>
+    <t>Prudential Financial</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -579,7 +585,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-15 00:43 UTC · данные на 2026-09-11 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-16 00:26 UTC · данные на 2026-09-14 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -660,7 +666,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-15 00:43 UTC</t>
+    <t>2026-09-16 00:26 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -675,7 +681,7 @@
     <t>Прошли фильтры</t>
   </si>
   <si>
-    <t>415</t>
+    <t>416</t>
   </si>
   <si>
     <t>Кандидат дня</t>
@@ -705,7 +711,7 @@
     <t>Фундаментал на дату</t>
   </si>
   <si>
-    <t>2026-09-06</t>
+    <t>2026-09-13</t>
   </si>
   <si>
     <t>Версия состояния</t>
@@ -1043,29 +1049,47 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Сводка!$B$33:$B$34</c:f>
+              <c:f>Сводка!$B$33:$B$37</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Energy</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Information Technology</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Health Care</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Communication Services</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Financials</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Сводка!$C$33:$C$34</c:f>
+              <c:f>Сводка!$C$33:$C$37</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>2396.72</c:v>
+                  <c:v>2464.36</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2104.45</c:v>
+                  <c:v>2453.6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>501.41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>495.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>479.95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1154,9 +1178,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$17</c:f>
+              <c:f>Капитал!$A$5:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1195,16 +1219,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>2026-09-11</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2026-09-14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$17</c:f>
+              <c:f>Капитал!$D$5:$D$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1243,6 +1270,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1267,9 +1297,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$17</c:f>
+              <c:f>Капитал!$A$5:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1308,16 +1338,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>2026-09-11</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2026-09-14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$17</c:f>
+              <c:f>Капитал!$F$5:$F$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1356,6 +1389,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9966.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1495,9 +1531,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$17</c:f>
+              <c:f>Капитал!$A$5:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1536,16 +1572,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>2026-09-11</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2026-09-14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$17</c:f>
+              <c:f>Капитал!$D$5:$D$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1584,6 +1623,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>10216.05</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1608,9 +1650,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$17</c:f>
+              <c:f>Капитал!$A$5:$A$18</c:f>
               <c:strCache>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1649,16 +1691,19 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>2026-09-11</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2026-09-14</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$17</c:f>
+              <c:f>Капитал!$F$5:$F$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="13"/>
+                <c:ptCount val="14"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1697,6 +1742,9 @@
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9966.08</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2181,7 +2229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:H34"/>
+  <dimension ref="A2:H37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2191,37 +2239,37 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" s="4">
-        <v>10216.05</v>
+        <v>10163.98</v>
       </c>
       <c r="D6" s="5">
-        <v>0.02160499999999987</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.008801999999999977</v>
+        <v>0.01639799999999969</v>
+      </c>
+      <c r="F6" s="6">
+        <v>-0.003392000000000062</v>
       </c>
       <c r="H6" s="6">
         <v>-0.005570108480505209</v>
@@ -2229,64 +2277,64 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>4.061872161674939</v>
+        <v>2.881440547102145</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="9" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C13" s="10">
-        <v>5714.879999999998</v>
+        <v>3768.959999999999</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="9" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="C14" s="10">
-        <v>4501.17</v>
+        <v>6395.02</v>
       </c>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="9" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="C15" s="10">
-        <v>10216.05</v>
+        <v>10163.98</v>
       </c>
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2294,7 +2342,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2302,23 +2350,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C18" s="11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C19" s="11">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2326,93 +2374,117 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C25" s="12">
-        <v>0.1121336884360717</v>
+        <v>0.1116230737431509</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C26" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
-        <v>10216.05</v>
+        <v>10163.979999999998</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C33" s="10">
-        <v>2396.72</v>
+        <v>2464.36</v>
       </c>
     </row>
     <row r="34" spans="2:3">
       <c r="B34" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C34" s="10">
-        <v>2104.45</v>
+        <v>2453.6</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="10">
+        <v>501.41</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="10">
+        <v>495.7</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="10">
+        <v>479.95</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2495,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2443,62 +2515,62 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -2506,13 +2578,13 @@
         <v>0</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E5" s="10">
         <v>443.1115</v>
@@ -2524,32 +2596,32 @@
         <v>476.19</v>
       </c>
       <c r="H5" s="18">
-        <v>524.14</v>
+        <v>534.28</v>
       </c>
       <c r="I5" s="10">
         <f>F5*H5</f>
-        <v>563.26757514</v>
+        <v>574.16453628</v>
       </c>
       <c r="J5" s="10">
         <f>I5-G5</f>
-        <v>87.07757513999996</v>
+        <v>97.97453628</v>
       </c>
       <c r="K5" s="19">
         <f>IFERROR(J5/G5,0)</f>
-        <v>0.18286309065709058</v>
+        <v>0.20574673193473192</v>
       </c>
       <c r="L5" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
       </c>
       <c r="O5" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -2557,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="10">
         <v>926.2029</v>
@@ -2575,32 +2647,32 @@
         <v>476.62</v>
       </c>
       <c r="H6" s="18">
-        <v>1016.59</v>
+        <v>924.03</v>
       </c>
       <c r="I6" s="10">
         <f>F6*H6</f>
-        <v>523.1331476400001</v>
+        <v>475.50214188</v>
       </c>
       <c r="J6" s="10">
         <f>I6-G6</f>
-        <v>46.51314764000006</v>
+        <v>-1.117858119999994</v>
       </c>
       <c r="K6" s="19">
         <f>IFERROR(J6/G6,0)</f>
-        <v>0.09758958423901652</v>
+        <v>-0.0023453865133649322</v>
       </c>
       <c r="L6" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
       </c>
       <c r="O6" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -2608,13 +2680,13 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="10">
         <v>1550.1948</v>
@@ -2626,32 +2698,32 @@
         <v>477.55</v>
       </c>
       <c r="H7" s="18">
-        <v>1740</v>
+        <v>1551.99</v>
       </c>
       <c r="I7" s="10">
         <f>F7*H7</f>
-        <v>536.02092</v>
+        <v>478.10293542</v>
       </c>
       <c r="J7" s="10">
         <f>I7-G7</f>
-        <v>58.470920000000035</v>
+        <v>0.552935419999983</v>
       </c>
       <c r="K7" s="19">
         <f>IFERROR(J7/G7,0)</f>
-        <v>0.1224393676054864</v>
+        <v>0.001157858695424527</v>
       </c>
       <c r="L7" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
       </c>
       <c r="O7" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -2659,13 +2731,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E8" s="10">
         <v>462.5311</v>
@@ -2677,32 +2749,32 @@
         <v>476.95</v>
       </c>
       <c r="H8" s="18">
-        <v>467.46</v>
+        <v>426.94</v>
       </c>
       <c r="I8" s="10">
         <f>F8*H8</f>
-        <v>482.03259804</v>
+        <v>440.24942756</v>
       </c>
       <c r="J8" s="10">
         <f>I8-G8</f>
-        <v>5.0825980399999935</v>
+        <v>-36.70057243999997</v>
       </c>
       <c r="K8" s="19">
         <f>IFERROR(J8/G8,0)</f>
-        <v>0.010656458832162687</v>
+        <v>-0.07694846931544182</v>
       </c>
       <c r="L8" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
       </c>
       <c r="O8" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -2710,13 +2782,13 @@
         <v>4</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E9" s="10">
         <v>360.14</v>
@@ -2728,32 +2800,32 @@
         <v>475.92</v>
       </c>
       <c r="H9" s="18">
-        <v>370.72</v>
+        <v>382.95</v>
       </c>
       <c r="I9" s="10">
         <f>F9*H9</f>
-        <v>489.90128992</v>
+        <v>506.0630637</v>
       </c>
       <c r="J9" s="10">
         <f>I9-G9</f>
-        <v>13.981289919999995</v>
+        <v>30.14306369999997</v>
       </c>
       <c r="K9" s="19">
         <f>IFERROR(J9/G9,0)</f>
-        <v>0.029377395192469312</v>
+        <v>0.06333640885022687</v>
       </c>
       <c r="L9" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
       </c>
       <c r="O9" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -2761,13 +2833,13 @@
         <v>5</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E10" s="10">
         <v>380.9704</v>
@@ -2779,32 +2851,32 @@
         <v>477.22</v>
       </c>
       <c r="H10" s="18">
-        <v>388.9</v>
+        <v>396.45</v>
       </c>
       <c r="I10" s="10">
         <f>F10*H10</f>
-        <v>487.15286269999996</v>
+        <v>496.61031734999995</v>
       </c>
       <c r="J10" s="10">
         <f>I10-G10</f>
-        <v>9.93286269999993</v>
+        <v>19.39031734999992</v>
       </c>
       <c r="K10" s="19">
         <f>IFERROR(J10/G10,0)</f>
-        <v>0.020814011776538976</v>
+        <v>0.04063182043921025</v>
       </c>
       <c r="L10" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -2812,13 +2884,13 @@
         <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="D11" s="16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E11" s="10">
         <v>60.1501</v>
@@ -2830,32 +2902,32 @@
         <v>474.89</v>
       </c>
       <c r="H11" s="18">
-        <v>60.04</v>
+        <v>61.78</v>
       </c>
       <c r="I11" s="10">
         <f>F11*H11</f>
-        <v>474.02108352</v>
+        <v>487.75853664000005</v>
       </c>
       <c r="J11" s="10">
         <f>I11-G11</f>
-        <v>-0.8689164799999958</v>
+        <v>12.868536640000059</v>
       </c>
       <c r="K11" s="19">
         <f>IFERROR(J11/G11,0)</f>
-        <v>-0.0018297215776284946</v>
+        <v>0.027097931394638883</v>
       </c>
       <c r="L11" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -2863,13 +2935,13 @@
         <v>7</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E12" s="10">
         <v>251.9059</v>
@@ -2881,32 +2953,32 @@
         <v>474.89</v>
       </c>
       <c r="H12" s="18">
-        <v>255.09</v>
+        <v>257.06</v>
       </c>
       <c r="I12" s="10">
         <f>F12*H12</f>
-        <v>480.89260692000005</v>
+        <v>484.60642728000005</v>
       </c>
       <c r="J12" s="10">
         <f>I12-G12</f>
-        <v>6.002606920000062</v>
+        <v>9.716427280000062</v>
       </c>
       <c r="K12" s="19">
         <f>IFERROR(J12/G12,0)</f>
-        <v>0.012639994356587973</v>
+        <v>0.020460374570953403</v>
       </c>
       <c r="L12" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
       </c>
       <c r="O12" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -2914,13 +2986,13 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E13" s="10">
         <v>43.7018</v>
@@ -2932,58 +3004,262 @@
         <v>474.89</v>
       </c>
       <c r="H13" s="18">
-        <v>42.77</v>
+        <v>45.03</v>
       </c>
       <c r="I13" s="10">
         <f>F13*H13</f>
-        <v>464.76405430000005</v>
+        <v>489.32254770000003</v>
       </c>
       <c r="J13" s="10">
         <f>I13-G13</f>
-        <v>-10.125945699999932</v>
+        <v>14.432547700000043</v>
       </c>
       <c r="K13" s="19">
         <f>IFERROR(J13/G13,0)</f>
-        <v>-0.02132271831371461</v>
+        <v>0.030391348943966064</v>
       </c>
       <c r="L13" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="F14" s="13" t="s">
-        <v>46</v>
+      <c r="A14" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="10">
+        <v>211.3456</v>
+      </c>
+      <c r="F14" s="17">
+        <v>2.301822</v>
       </c>
       <c r="G14" s="10">
-        <f>SUM(G5:G13)</f>
-        <v>4285.12</v>
+        <v>486.48</v>
+      </c>
+      <c r="H14" s="18">
+        <v>210.96</v>
       </c>
       <c r="I14" s="10">
-        <f>SUM(I5:I13)</f>
-        <v>4501.17</v>
+        <f>F14*H14</f>
+        <v>485.59236912</v>
       </c>
       <c r="J14" s="10">
-        <f>SUM(J5:J13)</f>
-        <v>216.04999999999984</v>
+        <f>I14-G14</f>
+        <v>-0.8876308800000174</v>
       </c>
       <c r="K14" s="19">
         <f>IFERROR(J14/G14,0)</f>
+        <v>-0.001824598914652231</v>
+      </c>
+      <c r="L14" s="11">
         <v>0</v>
       </c>
+      <c r="M14" s="11">
+        <f>MAX(0,21-L14)</f>
+        <v>21</v>
+      </c>
+      <c r="N14" s="20">
+        <v>0.6809721702367264</v>
+      </c>
+      <c r="O14" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E15" s="10">
+        <v>383.1915</v>
+      </c>
+      <c r="F15" s="17">
+        <v>1.269548</v>
+      </c>
+      <c r="G15" s="10">
+        <v>486.48</v>
+      </c>
+      <c r="H15" s="18">
+        <v>378.05</v>
+      </c>
+      <c r="I15" s="10">
+        <f>F15*H15</f>
+        <v>479.9526214</v>
+      </c>
+      <c r="J15" s="10">
+        <f>I15-G15</f>
+        <v>-6.52737860000002</v>
+      </c>
+      <c r="K15" s="19">
+        <f>IFERROR(J15/G15,0)</f>
+        <v>-0.013417568245354424</v>
+      </c>
+      <c r="L15" s="11">
+        <v>0</v>
+      </c>
+      <c r="M15" s="11">
+        <f>MAX(0,21-L15)</f>
+        <v>21</v>
+      </c>
+      <c r="N15" s="20">
+        <v>0.8197914702434592</v>
+      </c>
+      <c r="O15" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="10">
+        <v>339.2795</v>
+      </c>
+      <c r="F16" s="17">
+        <v>1.433862</v>
+      </c>
+      <c r="G16" s="10">
+        <v>486.48</v>
+      </c>
+      <c r="H16" s="18">
+        <v>345.71</v>
+      </c>
+      <c r="I16" s="10">
+        <f>F16*H16</f>
+        <v>495.70043201999994</v>
+      </c>
+      <c r="J16" s="10">
+        <f>I16-G16</f>
+        <v>9.220432019999919</v>
+      </c>
+      <c r="K16" s="19">
+        <f>IFERROR(J16/G16,0)</f>
+        <v>0.018953362974839495</v>
+      </c>
+      <c r="L16" s="11">
+        <v>0</v>
+      </c>
+      <c r="M16" s="11">
+        <f>MAX(0,21-L16)</f>
+        <v>21</v>
+      </c>
+      <c r="N16" s="20">
+        <v>0.776423257523575</v>
+      </c>
+      <c r="O16" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="10">
+        <v>67.3437</v>
+      </c>
+      <c r="F17" s="17">
+        <v>7.223843</v>
+      </c>
+      <c r="G17" s="10">
+        <v>486.48</v>
+      </c>
+      <c r="H17" s="18">
+        <v>69.41</v>
+      </c>
+      <c r="I17" s="10">
+        <f>F17*H17</f>
+        <v>501.40694262999995</v>
+      </c>
+      <c r="J17" s="10">
+        <f>I17-G17</f>
+        <v>14.926942629999928</v>
+      </c>
+      <c r="K17" s="19">
+        <f>IFERROR(J17/G17,0)</f>
+        <v>0.03068356896480827</v>
+      </c>
+      <c r="L17" s="11">
+        <v>0</v>
+      </c>
+      <c r="M17" s="11">
+        <f>MAX(0,21-L17)</f>
+        <v>21</v>
+      </c>
+      <c r="N17" s="20">
+        <v>0.7994794227521653</v>
+      </c>
+      <c r="O17" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="F18" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G18" s="10">
+        <f>SUM(G5:G17)</f>
+        <v>6231.039999999999</v>
+      </c>
+      <c r="I18" s="10">
+        <f>SUM(I5:I17)</f>
+        <v>6395.0199999999995</v>
+      </c>
+      <c r="J18" s="10">
+        <f>SUM(J5:J17)</f>
+        <v>163.9799999999999</v>
+      </c>
+      <c r="K18" s="19">
+        <f>IFERROR(J18/G18,0)</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P13"/>
-  <conditionalFormatting sqref="K5:K13">
+  <autoFilter ref="A4:P17"/>
+  <conditionalFormatting sqref="K5:K17">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -2995,7 +3271,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M5:M13">
+  <conditionalFormatting sqref="M5:M17">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -3024,12 +3300,76 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M5:M13</xm:sqref>
+          <xm:sqref>M5:M17</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B13:BI13</xm:f>
+              <xm:sqref>P17</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B12:BI12</xm:f>
+              <xm:sqref>P16</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B11:BI11</xm:f>
+              <xm:sqref>P15</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
+          <x14:colorSeries rgb="FF0B5FFF"/>
+          <x14:colorNegative theme="5"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers theme="4" tint="-0.499984740745262"/>
+          <x14:colorFirst theme="4" tint="0.39997558519241921"/>
+          <x14:colorLast theme="4" tint="0.39997558519241921"/>
+          <x14:colorHigh theme="4"/>
+          <x14:colorLow theme="4"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>'_данные'!B10:BI10</xm:f>
+              <xm:sqref>P14</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" high="1" low="1">
           <x14:colorSeries rgb="FF0B5FFF"/>
           <x14:colorNegative theme="5"/>
@@ -3202,64 +3542,64 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="15" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="14" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -3269,7 +3609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3281,37 +3621,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="15" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="16" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B5" s="10">
         <v>10000</v>
@@ -3332,7 +3672,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="16" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B6" s="10">
         <v>9523.809999999999</v>
@@ -3353,7 +3693,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B7" s="10">
         <v>9047.190000000001</v>
@@ -3374,7 +3714,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="16" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B8" s="10">
         <v>8569.639999999999</v>
@@ -3395,7 +3735,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B9" s="10">
         <v>8092.69</v>
@@ -3416,7 +3756,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="16" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B10" s="10">
         <v>7616.77</v>
@@ -3437,7 +3777,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="16" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B11" s="10">
         <v>7139.55</v>
@@ -3458,7 +3798,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="16" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B12" s="10">
         <v>7139.55</v>
@@ -3477,7 +3817,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="16" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B13" s="10">
         <v>7139.55</v>
@@ -3496,7 +3836,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="16" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B14" s="10">
         <v>5714.88</v>
@@ -3517,7 +3857,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="16" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B15" s="10">
         <v>5714.88</v>
@@ -3536,7 +3876,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="16" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B16" s="10">
         <v>5714.88</v>
@@ -3555,7 +3895,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="16" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B17" s="10">
         <v>5714.88</v>
@@ -3571,6 +3911,27 @@
         <v>9</v>
       </c>
       <c r="F17" s="10"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" s="10">
+        <v>3768.96</v>
+      </c>
+      <c r="C18" s="10">
+        <v>6395.02</v>
+      </c>
+      <c r="D18" s="10">
+        <f>B18+C18</f>
+        <v>10163.98</v>
+      </c>
+      <c r="E18" s="11">
+        <v>13</v>
+      </c>
+      <c r="F18" s="10">
+        <v>9966.08</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3599,74 +3960,74 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -3677,43 +4038,43 @@
         <v>4</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E5" s="10">
-        <v>390.4200134277344</v>
+        <v>382.9500122070312</v>
       </c>
       <c r="F5" s="17">
-        <v>1.047108330916111</v>
+        <v>1.01228894706075</v>
       </c>
       <c r="G5" s="20">
-        <v>0.7163099250210818</v>
+        <v>0.6555418499989493</v>
       </c>
       <c r="H5" s="20">
-        <v>-0.6808483021094016</v>
+        <v>-0.683656262521208</v>
       </c>
       <c r="I5" s="20">
-        <v>2.885035079678366</v>
+        <v>2.861941581666567</v>
       </c>
       <c r="J5" s="20">
-        <v>2.304642624456685</v>
+        <v>2.22325647473339</v>
       </c>
       <c r="K5" s="20">
-        <v>0.602059804282177</v>
+        <v>0.6103768664990419</v>
       </c>
       <c r="L5" s="20">
-        <v>0.2191623314588784</v>
+        <v>0.2191803760071019</v>
       </c>
       <c r="M5" s="20">
-        <v>-0.4773117369551982</v>
+        <v>-0.4486341382831623</v>
       </c>
       <c r="N5" s="20">
-        <v>15.453106</v>
+        <v>16.28786</v>
       </c>
       <c r="O5" s="20">
-        <v>4.269492</v>
+        <v>4.496372</v>
       </c>
       <c r="P5" s="12">
         <v>0.27637</v>
@@ -3722,13 +4083,13 @@
         <v>0.517</v>
       </c>
       <c r="R5" s="12">
-        <v>0.6699501897759226</v>
+        <v>0.6750788999361592</v>
       </c>
       <c r="S5" s="11">
-        <v>78.66166944743316</v>
+        <v>70.85054655531712</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -3736,61 +4097,61 @@
         <v>2</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E6" s="10">
-        <v>975.260009765625</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="F6" s="17">
-        <v>1.037399736457067</v>
+        <v>0.9937771760734965</v>
       </c>
       <c r="G6" s="20">
-        <v>-0.5381709417593455</v>
+        <v>0.6866590119647646</v>
       </c>
       <c r="H6" s="20">
-        <v>1.814060278794422</v>
+        <v>-0.5768953469214347</v>
       </c>
       <c r="I6" s="20">
-        <v>3.983916492932042</v>
+        <v>2.437187840999147</v>
       </c>
       <c r="J6" s="20">
-        <v>1.896417271006613</v>
+        <v>2.213632162250537</v>
       </c>
       <c r="K6" s="20">
-        <v>0.4757611069296119</v>
+        <v>0.7778806600509907</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.28307080283564</v>
+        <v>0.3043746566883123</v>
       </c>
       <c r="M6" s="20">
-        <v>0.2074618263754775</v>
+        <v>-0.711684774440313</v>
       </c>
       <c r="N6" s="20">
-        <v>22.98937</v>
+        <v>13.7380295</v>
       </c>
       <c r="O6" s="20">
-        <v>11.394834</v>
+        <v>5.8734603</v>
       </c>
       <c r="P6" s="12">
-        <v>0.66638</v>
+        <v>0.42099</v>
       </c>
       <c r="Q6" s="12">
-        <v>3.457</v>
+        <v>0.537</v>
       </c>
       <c r="R6" s="12">
-        <v>1.407351202710621</v>
+        <v>0.7643150477120724</v>
       </c>
       <c r="S6" s="11">
-        <v>52.99519951119411</v>
+        <v>74.93452245635656</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -3798,61 +4159,61 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E7" s="10">
-        <v>1633.349975585938</v>
+        <v>924.030029296875</v>
       </c>
       <c r="F7" s="17">
-        <v>1.009624307650897</v>
+        <v>0.9551442181031129</v>
       </c>
       <c r="G7" s="20">
-        <v>-0.5564495730839067</v>
+        <v>-0.495023614230421</v>
       </c>
       <c r="H7" s="20">
-        <v>2.058086531115069</v>
+        <v>1.812724042922127</v>
       </c>
       <c r="I7" s="20">
-        <v>4.120745224686987</v>
+        <v>3.960347878543698</v>
       </c>
       <c r="J7" s="20">
-        <v>1.689006681877619</v>
+        <v>1.610354219383285</v>
       </c>
       <c r="K7" s="20">
-        <v>0.08036885848301029</v>
+        <v>0.483715047300809</v>
       </c>
       <c r="L7" s="20">
-        <v>-3.28307080283564</v>
+        <v>-3.375332568109985</v>
       </c>
       <c r="M7" s="20">
-        <v>0.6131855493472688</v>
+        <v>0.2443214567274382</v>
       </c>
       <c r="N7" s="20">
-        <v>23.583628</v>
+        <v>22.024843</v>
       </c>
       <c r="O7" s="20">
-        <v>16.475557</v>
+        <v>10.93157</v>
       </c>
       <c r="P7" s="12">
-        <v>0.9164</v>
+        <v>0.66638</v>
       </c>
       <c r="Q7" s="12">
-        <v>3.716</v>
+        <v>3.457</v>
       </c>
       <c r="R7" s="12">
-        <v>1.639458899605641</v>
+        <v>1.16966743669018</v>
       </c>
       <c r="S7" s="11">
-        <v>53.57670459594432</v>
+        <v>46.41436604092988</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -3860,61 +4221,61 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E8" s="10">
-        <v>395.9299926757812</v>
+        <v>534.280029296875</v>
       </c>
       <c r="F8" s="17">
-        <v>1.008651076085922</v>
+        <v>0.9390396418388857</v>
       </c>
       <c r="G8" s="20">
-        <v>0.704035078477925</v>
+        <v>-0.1521673872440041</v>
       </c>
       <c r="H8" s="20">
-        <v>-0.5743881810314097</v>
+        <v>-0.8490211958234019</v>
       </c>
       <c r="I8" s="20">
-        <v>2.454207309239585</v>
+        <v>2.18194679071571</v>
       </c>
       <c r="J8" s="20">
-        <v>2.269552362960187</v>
+        <v>2.749859706342906</v>
       </c>
       <c r="K8" s="20">
-        <v>0.7690833877198547</v>
+        <v>1.608161809570836</v>
       </c>
       <c r="L8" s="20">
-        <v>0.2642900999037246</v>
+        <v>-2.845436735620273</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.7575872675962474</v>
+        <v>0.4608419861102997</v>
       </c>
       <c r="N8" s="20">
-        <v>13.475398</v>
+        <v>33.00116</v>
       </c>
       <c r="O8" s="20">
-        <v>5.769173</v>
+        <v>-256.4602</v>
       </c>
       <c r="P8" s="12">
-        <v>0.42099</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.537</v>
+        <v>0.577</v>
       </c>
       <c r="R8" s="12">
-        <v>0.7322089986164448</v>
+        <v>2.540553811407082</v>
       </c>
       <c r="S8" s="11">
-        <v>74.73609888428106</v>
+        <v>59.27403744918696</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -3922,61 +4283,61 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E9" s="10">
-        <v>567.2899780273438</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9904077039269833</v>
+        <v>0.92078027148921</v>
       </c>
       <c r="G9" s="20">
-        <v>-0.2096896716004668</v>
+        <v>-0.4801631684214276</v>
       </c>
       <c r="H9" s="20">
-        <v>-0.8459922326108509</v>
+        <v>2.05728233065155</v>
       </c>
       <c r="I9" s="20">
-        <v>2.195812652927404</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J9" s="20">
-        <v>3.057004107730039</v>
+        <v>1.394863130104923</v>
       </c>
       <c r="K9" s="20">
-        <v>1.596984236488098</v>
+        <v>0.0871860051577696</v>
       </c>
       <c r="L9" s="20">
-        <v>-2.879147615983456</v>
+        <v>-3.375332568109985</v>
       </c>
       <c r="M9" s="20">
-        <v>0.09923566251858906</v>
+        <v>0.499055539385301</v>
       </c>
       <c r="N9" s="20">
-        <v>30.490984</v>
+        <v>22.12312</v>
       </c>
       <c r="O9" s="20">
-        <v>-236.953</v>
+        <v>15.465718</v>
       </c>
       <c r="P9" s="12">
-        <v>0</v>
+        <v>0.9164</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.577</v>
+        <v>3.716</v>
       </c>
       <c r="R9" s="12">
-        <v>2.802185284799948</v>
+        <v>1.345742271527757</v>
       </c>
       <c r="S9" s="11">
-        <v>66.57472265866397</v>
+        <v>48.83790364120002</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -3984,61 +4345,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E10" s="10">
-        <v>62.09000015258789</v>
+        <v>69.41000366210938</v>
       </c>
       <c r="F10" s="17">
-        <v>0.939245154268785</v>
+        <v>0.9006741142353692</v>
       </c>
       <c r="G10" s="20">
-        <v>0.5218225520995097</v>
+        <v>1.282244047014282</v>
       </c>
       <c r="H10" s="20">
-        <v>-0.5332485103967138</v>
+        <v>-1.356970430261629</v>
       </c>
       <c r="I10" s="20">
-        <v>2.225163086097977</v>
+        <v>-0.5801056520622042</v>
       </c>
       <c r="J10" s="20">
-        <v>2.61144298994151</v>
+        <v>1.532770805520431</v>
       </c>
       <c r="K10" s="20">
-        <v>0.3221406505579205</v>
+        <v>4.197997932171494</v>
       </c>
       <c r="L10" s="20">
-        <v>-1.730503073576264</v>
+        <v>-0.02542500209616996</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.126738033628476</v>
+        <v>-0.2133684196257324</v>
       </c>
       <c r="N10" s="20">
-        <v>26.804123</v>
+        <v>12.502541</v>
       </c>
       <c r="O10" s="20">
-        <v>2.7206612</v>
+        <v>1.4542508</v>
       </c>
       <c r="P10" s="12">
-        <v>0.10936</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.337</v>
+        <v>0.046</v>
       </c>
       <c r="R10" s="12">
-        <v>1.904225712994388</v>
+        <v>1.014804125542404</v>
       </c>
       <c r="S10" s="11">
-        <v>64.11120072894144</v>
+        <v>61.40478798365034</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4046,61 +4407,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E11" s="10">
-        <v>259.4700012207031</v>
+        <v>378.0499877929688</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8588014094590573</v>
+        <v>0.8631958713640447</v>
       </c>
       <c r="G11" s="20">
-        <v>0.4937473502003348</v>
+        <v>1.195906561845193</v>
       </c>
       <c r="H11" s="20">
-        <v>-0.7878254537509429</v>
+        <v>-0.1235890761074189</v>
       </c>
       <c r="I11" s="20">
-        <v>2.423226908404409</v>
+        <v>-0.3802373592559733</v>
       </c>
       <c r="J11" s="20">
-        <v>2.035052537658677</v>
+        <v>0.7947370846814427</v>
       </c>
       <c r="K11" s="20">
-        <v>0.6850560911138626</v>
+        <v>3.830172009219837</v>
       </c>
       <c r="L11" s="20">
-        <v>0.4590621597480739</v>
+        <v>0.5684774989845738</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.8326244204180518</v>
+        <v>-0.3302467264399167</v>
       </c>
       <c r="N11" s="20">
-        <v>14.559931</v>
+        <v>10.080602</v>
       </c>
       <c r="O11" s="20">
-        <v>3.2307048</v>
+        <v>2.3630478</v>
       </c>
       <c r="P11" s="12">
-        <v>0.23452999</v>
+        <v>0.26511</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.531</v>
+        <v>0.003</v>
       </c>
       <c r="R11" s="12">
-        <v>0.5092246674773435</v>
+        <v>0.2593092288545</v>
       </c>
       <c r="S11" s="11">
-        <v>74.6143159237013</v>
+        <v>60.97994843730039</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4108,61 +4469,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="E12" s="10">
-        <v>375.2000122070312</v>
+        <v>349.3900146484375</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8511590141827708</v>
+        <v>0.8410723709429708</v>
       </c>
       <c r="G12" s="20">
-        <v>1.215230467965422</v>
+        <v>-0.3791628567675373</v>
       </c>
       <c r="H12" s="20">
-        <v>-0.1214453608752054</v>
+        <v>1.461933114403917</v>
       </c>
       <c r="I12" s="20">
-        <v>-0.3758707799348074</v>
+        <v>1.394253875646282</v>
       </c>
       <c r="J12" s="20">
-        <v>0.759023881299384</v>
+        <v>0.09775964055743695</v>
       </c>
       <c r="K12" s="20">
-        <v>3.812624241473097</v>
+        <v>4.197997932171494</v>
       </c>
       <c r="L12" s="20">
-        <v>0.5726267259849146</v>
+        <v>0.04290532467272344</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.3767976405396661</v>
+        <v>0.00406294729623613</v>
       </c>
       <c r="N12" s="20">
-        <v>9.931433999999999</v>
+        <v>16.975927</v>
       </c>
       <c r="O12" s="20">
-        <v>2.3262038</v>
+        <v>6.6508174</v>
       </c>
       <c r="P12" s="12">
-        <v>0.26511</v>
+        <v>0.48676</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.003</v>
+        <v>0.242</v>
       </c>
       <c r="R12" s="12">
-        <v>0.2518020698297732</v>
+        <v>0.1572827577604365</v>
       </c>
       <c r="S12" s="11">
-        <v>58.68437519657044</v>
+        <v>55.27304228383611</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4170,61 +4531,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>95</v>
+        <v>11</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="E13" s="10">
-        <v>66.41999816894531</v>
+        <v>345.7099914550781</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8362185200337082</v>
+        <v>0.8359806889782336</v>
       </c>
       <c r="G13" s="20">
-        <v>1.296202382232963</v>
+        <v>-0.3694515340244113</v>
       </c>
       <c r="H13" s="20">
-        <v>-1.353261681376673</v>
+        <v>1.461933114403917</v>
       </c>
       <c r="I13" s="20">
-        <v>-0.5780959126470824</v>
+        <v>1.394253875646282</v>
       </c>
       <c r="J13" s="20">
-        <v>1.269140502497847</v>
+        <v>0.05994526779680345</v>
       </c>
       <c r="K13" s="20">
-        <v>4.196860964161699</v>
+        <v>4.197997932171494</v>
       </c>
       <c r="L13" s="20">
-        <v>0.02559509881647475</v>
+        <v>0.06749015820869138</v>
       </c>
       <c r="M13" s="20">
-        <v>-0.1083452607624456</v>
+        <v>0.04193171926538725</v>
       </c>
       <c r="N13" s="20">
-        <v>12.6192465</v>
+        <v>16.83141</v>
       </c>
       <c r="O13" s="20">
-        <v>1.4678257</v>
+        <v>6.5908914</v>
       </c>
       <c r="P13" s="12">
-        <v>-0.20358999</v>
+        <v>0.48676</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.046</v>
+        <v>0.242</v>
       </c>
       <c r="R13" s="12">
-        <v>0.9213190267655582</v>
+        <v>0.1482207138835352</v>
       </c>
       <c r="S13" s="11">
-        <v>53.48937920497259</v>
+        <v>54.86677435742562</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4232,61 +4593,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="E14" s="10">
-        <v>338.5</v>
+        <v>259.4299926757812</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7901120390773569</v>
+        <v>0.8296267170835715</v>
       </c>
       <c r="G14" s="20">
-        <v>-0.3753606373785415</v>
+        <v>0.3415976968814792</v>
       </c>
       <c r="H14" s="20">
-        <v>1.463709249725696</v>
+        <v>0.5361174605758535</v>
       </c>
       <c r="I14" s="20">
-        <v>1.40880022334584</v>
+        <v>0.1958909336866145</v>
       </c>
       <c r="J14" s="20">
-        <v>-0.1284958515787564</v>
+        <v>1.334480265558949</v>
       </c>
       <c r="K14" s="20">
-        <v>4.196860964161699</v>
+        <v>3.532387487349705</v>
       </c>
       <c r="L14" s="20">
-        <v>0.05388730638834549</v>
+        <v>-1.53918117489099</v>
       </c>
       <c r="M14" s="20">
-        <v>0.1786956613215165</v>
+        <v>-0.8638557884010362</v>
       </c>
       <c r="N14" s="20">
-        <v>16.97392</v>
+        <v>22.684982</v>
       </c>
       <c r="O14" s="20">
-        <v>6.650031</v>
+        <v>5.312232</v>
       </c>
       <c r="P14" s="12">
-        <v>0.48676</v>
+        <v>0.19381</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.242</v>
+        <v>0.108</v>
       </c>
       <c r="R14" s="12">
-        <v>0.1165208417657306</v>
+        <v>0.3522277194846328</v>
       </c>
       <c r="S14" s="11">
-        <v>46.91265079040681</v>
+        <v>69.75681441978077</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4294,61 +4655,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="10">
+        <v>257.0599975585938</v>
+      </c>
+      <c r="F15" s="17">
+        <v>0.824071231833528</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0.4728319185405508</v>
+      </c>
+      <c r="H15" s="20">
+        <v>-0.7907783719627398</v>
+      </c>
+      <c r="I15" s="20">
+        <v>2.406342473145227</v>
+      </c>
+      <c r="J15" s="20">
+        <v>1.929147647251266</v>
+      </c>
+      <c r="K15" s="20">
+        <v>0.6936117762578806</v>
+      </c>
+      <c r="L15" s="20">
+        <v>0.4992828079226008</v>
+      </c>
+      <c r="M15" s="20">
+        <v>-0.8385362138242139</v>
+      </c>
+      <c r="N15" s="20">
+        <v>14.818389</v>
+      </c>
+      <c r="O15" s="20">
+        <v>3.2861774</v>
+      </c>
+      <c r="P15" s="12">
+        <v>0.23452999</v>
+      </c>
+      <c r="Q15" s="12">
+        <v>0.531</v>
+      </c>
+      <c r="R15" s="12">
+        <v>0.5068919214337058</v>
+      </c>
+      <c r="S15" s="11">
+        <v>70.26503245998802</v>
+      </c>
+      <c r="T15" s="9" t="s">
         <v>101</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="E15" s="10">
-        <v>335.4500122070312</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0.7897842317984384</v>
-      </c>
-      <c r="G15" s="20">
-        <v>-0.3654991602347105</v>
-      </c>
-      <c r="H15" s="20">
-        <v>1.463709249725696</v>
-      </c>
-      <c r="I15" s="20">
-        <v>1.40880022334584</v>
-      </c>
-      <c r="J15" s="20">
-        <v>-0.1561099043153476</v>
-      </c>
-      <c r="K15" s="20">
-        <v>4.196860964161699</v>
-      </c>
-      <c r="L15" s="20">
-        <v>0.07778047252595303</v>
-      </c>
-      <c r="M15" s="20">
-        <v>0.2380425699204254</v>
-      </c>
-      <c r="N15" s="20">
-        <v>16.83283</v>
-      </c>
-      <c r="O15" s="20">
-        <v>6.5881405</v>
-      </c>
-      <c r="P15" s="12">
-        <v>0.48676</v>
-      </c>
-      <c r="Q15" s="12">
-        <v>0.242</v>
-      </c>
-      <c r="R15" s="12">
-        <v>0.1077134950968779</v>
-      </c>
-      <c r="S15" s="11">
-        <v>46.26375761869606</v>
-      </c>
-      <c r="T15" s="9" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4356,61 +4717,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E16" s="10">
-        <v>247.7200012207031</v>
+        <v>55.40999984741211</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7866722272056267</v>
+        <v>0.7981458632159613</v>
       </c>
       <c r="G16" s="20">
-        <v>0.313884107527872</v>
+        <v>0.3530298731450531</v>
       </c>
       <c r="H16" s="20">
-        <v>0.5379536582452412</v>
+        <v>-0.5362564771804156</v>
       </c>
       <c r="I16" s="20">
-        <v>0.202940183485447</v>
+        <v>2.205637651643404</v>
       </c>
       <c r="J16" s="20">
-        <v>1.238107967545342</v>
+        <v>1.950292945949812</v>
       </c>
       <c r="K16" s="20">
-        <v>3.515693426472779</v>
+        <v>0</v>
       </c>
       <c r="L16" s="20">
-        <v>-1.611896355949384</v>
+        <v>-1.927064249293187</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.9099416987568313</v>
+        <v>0.4324528102638764</v>
       </c>
       <c r="N16" s="20">
-        <v>23.76077</v>
+        <v>32.005154</v>
       </c>
       <c r="O16" s="20">
-        <v>5.559058</v>
+        <v>3.1100981</v>
       </c>
       <c r="P16" s="12">
-        <v>0.19381</v>
+        <v>0.10936</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.108</v>
+        <v>0.337</v>
       </c>
       <c r="R16" s="12">
-        <v>0.2494004299711519</v>
+        <v>1.591772361385027</v>
       </c>
       <c r="S16" s="11">
-        <v>64.89234821607687</v>
+        <v>52.07947637617934</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4421,43 +4782,43 @@
         <v>6</v>
       </c>
       <c r="C17" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>38</v>
-      </c>
       <c r="E17" s="10">
-        <v>61.45999908447266</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7481695457661486</v>
+        <v>0.7488325358416236</v>
       </c>
       <c r="G17" s="20">
-        <v>0.6321397772136792</v>
+        <v>0.6018835051913498</v>
       </c>
       <c r="H17" s="20">
-        <v>0.6155406581429993</v>
+        <v>0.6139340215135211</v>
       </c>
       <c r="I17" s="20">
-        <v>2.930171312463986</v>
+        <v>2.907067021605936</v>
       </c>
       <c r="J17" s="20">
-        <v>0.5613260562665766</v>
+        <v>0.5639565866142032</v>
       </c>
       <c r="K17" s="20">
-        <v>0.8675448211661402</v>
+        <v>0.9185011287118862</v>
       </c>
       <c r="L17" s="20">
-        <v>0.3417502417115755</v>
+        <v>0.3496493944465213</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.6265932575524594</v>
+        <v>-0.6103589474006887</v>
       </c>
       <c r="N17" s="20">
-        <v>17.710915</v>
+        <v>18.129793</v>
       </c>
       <c r="O17" s="20">
-        <v>1.7938988</v>
+        <v>1.836326</v>
       </c>
       <c r="P17" s="12">
         <v>0.10629</v>
@@ -4466,13 +4827,13 @@
         <v>0.534</v>
       </c>
       <c r="R17" s="12">
-        <v>0.06192779992740483</v>
+        <v>0.0772313801886213</v>
       </c>
       <c r="S17" s="11">
-        <v>63.75161075517163</v>
+        <v>65.06265728902758</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4480,61 +4841,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="E18" s="10">
-        <v>199.2799987792969</v>
+        <v>158.6999969482422</v>
       </c>
       <c r="F18" s="17">
-        <v>0.7307640765324444</v>
+        <v>0.6704875708320357</v>
       </c>
       <c r="G18" s="20">
-        <v>-0.3904668641526476</v>
+        <v>0.5169435305631409</v>
       </c>
       <c r="H18" s="20">
-        <v>1.359179679828218</v>
+        <v>-0.5609987008817506</v>
       </c>
       <c r="I18" s="20">
-        <v>0.4411015820383316</v>
+        <v>-0.03865308917984001</v>
       </c>
       <c r="J18" s="20">
-        <v>1.866696481641062</v>
+        <v>1.078124005853262</v>
       </c>
       <c r="K18" s="20">
-        <v>0.4834936802369117</v>
+        <v>3.298192368587258</v>
       </c>
       <c r="L18" s="20">
-        <v>-0.38721926216302</v>
+        <v>0.2949725556201062</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.6915728160924274</v>
+        <v>-0.8231975366740211</v>
       </c>
       <c r="N18" s="20">
-        <v>26.250353</v>
+        <v>16.148188</v>
       </c>
       <c r="O18" s="20">
-        <v>26.924416</v>
+        <v>3.9674618</v>
       </c>
       <c r="P18" s="12">
-        <v>1.14818</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.299</v>
+        <v>0.053</v>
       </c>
       <c r="R18" s="12">
-        <v>1.072723636880157</v>
+        <v>0.3757373933555348</v>
       </c>
       <c r="S18" s="11">
-        <v>61.61763607406569</v>
+        <v>52.9546715385213</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4542,61 +4903,61 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E19" s="10">
-        <v>40.09999847412109</v>
+        <v>258.4800109863281</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6640922650584004</v>
+        <v>0.6636239767702646</v>
       </c>
       <c r="G19" s="20">
-        <v>0.09785741135882757</v>
+        <v>1.275714742496789</v>
       </c>
       <c r="H19" s="20">
-        <v>-0.81219220040201</v>
+        <v>0.1637485141969772</v>
       </c>
       <c r="I19" s="20">
-        <v>3.920900829953943</v>
+        <v>-0.05524579084430264</v>
       </c>
       <c r="J19" s="20">
-        <v>0.7484635777842236</v>
+        <v>0.5771411111412715</v>
       </c>
       <c r="K19" s="20">
-        <v>3.370836553182694</v>
+        <v>1.860968460950166</v>
       </c>
       <c r="L19" s="20">
-        <v>-3.28307080283564</v>
+        <v>0.4908272472238406</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.5964576433039166</v>
+        <v>-0.1573505444509424</v>
       </c>
       <c r="N19" s="20">
-        <v>12.144172</v>
+        <v>5.081314</v>
       </c>
       <c r="O19" s="20">
-        <v>2.3688147</v>
+        <v>2.0330794</v>
       </c>
       <c r="P19" s="12">
-        <v>0.21465999</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="R19" s="12">
-        <v>0.2977345944714418</v>
+        <v>0.2655726794771835</v>
       </c>
       <c r="S19" s="11">
-        <v>60.49859041306437</v>
+        <v>52.03093909583132</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -4604,61 +4965,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E20" s="10">
-        <v>155.8300018310547</v>
+        <v>253.5399932861328</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6514352314021793</v>
+        <v>0.6492655173943512</v>
       </c>
       <c r="G20" s="20">
-        <v>0.4941985872113094</v>
+        <v>-0.04046750433284103</v>
       </c>
       <c r="H20" s="20">
-        <v>-0.5581494893912904</v>
+        <v>0.1570571804969511</v>
       </c>
       <c r="I20" s="20">
-        <v>-0.03241763381358259</v>
+        <v>1.023343627582307</v>
       </c>
       <c r="J20" s="20">
-        <v>0.9791291122804968</v>
+        <v>0.1552359262998876</v>
       </c>
       <c r="K20" s="20">
-        <v>3.282169712592323</v>
+        <v>4.197997932171494</v>
       </c>
       <c r="L20" s="20">
-        <v>0.2185710594544033</v>
+        <v>-0.4046724909683029</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.5711024421797948</v>
+        <v>0.037949703050905</v>
       </c>
       <c r="N20" s="20">
-        <v>17.05809</v>
+        <v>20.658085</v>
       </c>
       <c r="O20" s="20">
-        <v>4.186674</v>
+        <v>5.0195484</v>
       </c>
       <c r="P20" s="12">
-        <v>0.26408002</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.053</v>
+        <v>0.196</v>
       </c>
       <c r="R20" s="12">
-        <v>0.369413942364327</v>
+        <v>0.2208792580614893</v>
       </c>
       <c r="S20" s="11">
-        <v>48.25302803577884</v>
+        <v>45.84245200474109</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -4666,61 +5027,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="E21" s="10">
-        <v>256.7799987792969</v>
+        <v>188.2799987792969</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6494692717513246</v>
+        <v>0.6404347402016241</v>
       </c>
       <c r="G21" s="20">
-        <v>-0.04482148267622166</v>
+        <v>-0.4603187739276002</v>
       </c>
       <c r="H21" s="20">
-        <v>0.1590141648378586</v>
+        <v>1.359216064961746</v>
       </c>
       <c r="I21" s="20">
-        <v>1.035672297744961</v>
+        <v>0.4362761666871086</v>
       </c>
       <c r="J21" s="20">
-        <v>0.2122809354201503</v>
+        <v>1.396710524583753</v>
       </c>
       <c r="K21" s="20">
-        <v>4.196860964161699</v>
+        <v>0</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4583906523715454</v>
+        <v>-0.416347229748139</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.1409564337333159</v>
+        <v>-0.108681999605382</v>
       </c>
       <c r="N21" s="20">
-        <v>20.797264</v>
+        <v>28.186703</v>
       </c>
       <c r="O21" s="20">
-        <v>5.0533667</v>
+        <v>26.124804</v>
       </c>
       <c r="P21" s="12">
-        <v>0.30558002</v>
+        <v>1.14818</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.196</v>
+        <v>0.299</v>
       </c>
       <c r="R21" s="12">
-        <v>0.2255047023112409</v>
+        <v>0.9239728482142766</v>
       </c>
       <c r="S21" s="11">
-        <v>48.9135507648596</v>
+        <v>50.89744488112564</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -4728,61 +5089,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E22" s="10">
-        <v>253.7100067138672</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6419214616278026</v>
+        <v>0.5542611253698945</v>
       </c>
       <c r="G22" s="20">
-        <v>1.286238812250283</v>
+        <v>0.3560597278471356</v>
       </c>
       <c r="H22" s="20">
-        <v>0.1653558428199913</v>
+        <v>0.5036708481790161</v>
       </c>
       <c r="I22" s="20">
-        <v>-0.05063264711205382</v>
+        <v>0.5191598695187023</v>
       </c>
       <c r="J22" s="20">
-        <v>0.4524648206445526</v>
+        <v>0.5733477433246573</v>
       </c>
       <c r="K22" s="20">
-        <v>1.849066126306075</v>
+        <v>1.650037757958823</v>
       </c>
       <c r="L22" s="20">
-        <v>0.5039178706954955</v>
+        <v>0.1426259815604311</v>
       </c>
       <c r="M22" s="20">
-        <v>0.01427939613667511</v>
+        <v>-0.2612420143648083</v>
       </c>
       <c r="N22" s="20">
-        <v>5.1976376</v>
+        <v>15.473886</v>
       </c>
       <c r="O22" s="20">
-        <v>2.0800378</v>
+        <v>3.847884</v>
       </c>
       <c r="P22" s="12">
-        <v>0.46113998</v>
+        <v>0.30667</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.118</v>
+        <v>0.377</v>
       </c>
       <c r="R22" s="12">
-        <v>0.2491246171502992</v>
+        <v>0.3204020016483911</v>
       </c>
       <c r="S22" s="11">
-        <v>46.35496986092373</v>
+        <v>46.46241016422281</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -4790,46 +5151,46 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E23" s="10">
-        <v>35.47999954223633</v>
+        <v>34.02000045776367</v>
       </c>
       <c r="F23" s="17">
-        <v>0.6187519821526637</v>
+        <v>0.5526847296036832</v>
       </c>
       <c r="G23" s="20">
-        <v>1.115176779328165</v>
+        <v>0.9932091735796537</v>
       </c>
       <c r="H23" s="20">
-        <v>-0.9874044575767369</v>
+        <v>-0.9910800207632466</v>
       </c>
       <c r="I23" s="20">
-        <v>-0.3840221445724293</v>
+        <v>-0.385570790078564</v>
       </c>
       <c r="J23" s="20">
-        <v>2.108004420646181</v>
+        <v>1.867556802628306</v>
       </c>
       <c r="K23" s="20">
-        <v>0.403590422728146</v>
+        <v>0.4113368649018186</v>
       </c>
       <c r="L23" s="20">
-        <v>-0.7643769871887608</v>
+        <v>-0.7230916617578612</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.257030851834891</v>
+        <v>0.05993744772603726</v>
       </c>
       <c r="N23" s="20">
-        <v>12.458015</v>
+        <v>13.5419855</v>
       </c>
       <c r="O23" s="20">
-        <v>-320</v>
+        <v>-347.84314</v>
       </c>
       <c r="P23" s="12">
         <v>0</v>
@@ -4838,13 +5199,13 @@
         <v>0.125</v>
       </c>
       <c r="R23" s="12">
-        <v>0.9135080532131845</v>
+        <v>0.8367060329642197</v>
       </c>
       <c r="S23" s="11">
-        <v>71.78658040207837</v>
+        <v>64.02313735821257</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -4852,61 +5213,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>119</v>
+        <v>8</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E24" s="10">
-        <v>102.9400024414062</v>
+        <v>45.02999877929688</v>
       </c>
       <c r="F24" s="17">
-        <v>0.6100380140285703</v>
+        <v>0.5521464870932067</v>
       </c>
       <c r="G24" s="20">
-        <v>-0.6233680543607623</v>
+        <v>1.099839703019805</v>
       </c>
       <c r="H24" s="20">
-        <v>-1.136990927851701</v>
+        <v>0.5600572175760307</v>
       </c>
       <c r="I24" s="20">
-        <v>0.5264142543422116</v>
+        <v>-0.2922173294313919</v>
       </c>
       <c r="J24" s="20">
-        <v>1.49879755877251</v>
+        <v>1.450373048581954</v>
       </c>
       <c r="K24" s="20">
-        <v>4.196860964161699</v>
+        <v>-0.5699044936216348</v>
       </c>
       <c r="L24" s="20">
-        <v>-2.467621400722987</v>
+        <v>-0.2228253554151386</v>
       </c>
       <c r="M24" s="20">
-        <v>0.5789510943472597</v>
+        <v>-0.7445741916808229</v>
       </c>
       <c r="N24" s="20">
-        <v>46.910885</v>
+        <v>9.436709</v>
       </c>
       <c r="O24" s="20">
-        <v>5.5187516</v>
+        <v>2.2340426</v>
       </c>
       <c r="P24" s="12">
-        <v>-0.10715</v>
+        <v>0.26659</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.254</v>
+        <v>0.092</v>
       </c>
       <c r="R24" s="12">
-        <v>1.274917181025553</v>
+        <v>0.3243533335450024</v>
       </c>
       <c r="S24" s="11">
-        <v>57.53295415212876</v>
+        <v>64.65499916721588</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -4914,61 +5275,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="E25" s="10">
-        <v>1029.180053710938</v>
+        <v>119.1699981689453</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5765399084897844</v>
+        <v>0.5469331124930834</v>
       </c>
       <c r="G25" s="20">
-        <v>0.3667190394925228</v>
+        <v>0.4228371578138432</v>
       </c>
       <c r="H25" s="20">
-        <v>0.8230717495135815</v>
+        <v>-0.1266107877394232</v>
       </c>
       <c r="I25" s="20">
-        <v>0.9154597556552251</v>
+        <v>0.4718408509917099</v>
       </c>
       <c r="J25" s="20">
-        <v>0.2276283725753302</v>
+        <v>-0.1268757252433695</v>
       </c>
       <c r="K25" s="20">
-        <v>1.655236288736424</v>
+        <v>4.197997932171494</v>
       </c>
       <c r="L25" s="20">
-        <v>0.1228253582693528</v>
+        <v>0.08136732697339379</v>
       </c>
       <c r="M25" s="20">
-        <v>0.1625829747037942</v>
+        <v>-0.3335376110030455</v>
       </c>
       <c r="N25" s="20">
-        <v>16.02546</v>
+        <v>14.463892</v>
       </c>
       <c r="O25" s="20">
-        <v>2.8687</v>
+        <v>6.474714</v>
       </c>
       <c r="P25" s="12">
-        <v>0.16902</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.425</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R25" s="12">
-        <v>0.3190503949464873</v>
+        <v>0.1089707722337463</v>
       </c>
       <c r="S25" s="11">
-        <v>49.5933686304215</v>
+        <v>37.63397580688533</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -4976,61 +5337,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="E26" s="10">
-        <v>44.72999954223633</v>
+        <v>988.4500122070312</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5661190823210835</v>
+        <v>0.5251208465853666</v>
       </c>
       <c r="G26" s="20">
-        <v>1.1788603618118</v>
+        <v>0.3658514008022524</v>
       </c>
       <c r="H26" s="20">
-        <v>0.561859549662265</v>
+        <v>0.8216781549389145</v>
       </c>
       <c r="I26" s="20">
-        <v>-0.2890980177519417</v>
+        <v>0.9093352353792101</v>
       </c>
       <c r="J26" s="20">
-        <v>1.452616966504415</v>
+        <v>-0.04145999161670547</v>
       </c>
       <c r="K26" s="20">
-        <v>-0.5748378530888681</v>
+        <v>1.666581342507164</v>
       </c>
       <c r="L26" s="20">
-        <v>-0.2447469096444711</v>
+        <v>0.07543324747431411</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.7397905247225112</v>
+        <v>0.5598475956063371</v>
       </c>
       <c r="N26" s="20">
-        <v>9.023208</v>
+        <v>15.897128</v>
       </c>
       <c r="O26" s="20">
-        <v>2.1361504</v>
+        <v>2.842654</v>
       </c>
       <c r="P26" s="12">
-        <v>0.26659</v>
+        <v>0.16902</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.092</v>
+        <v>0.425</v>
       </c>
       <c r="R26" s="12">
-        <v>0.3491915517697861</v>
+        <v>0.2754486009594632</v>
       </c>
       <c r="S26" s="11">
-        <v>63.61064997140362</v>
+        <v>39.52991259648539</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -5038,61 +5399,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="E27" s="10">
-        <v>121.4700012207031</v>
+        <v>36.7400016784668</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5481068609073245</v>
+        <v>0.5154468331968604</v>
       </c>
       <c r="G27" s="20">
-        <v>0.3314207580374121</v>
+        <v>0.005970682120931148</v>
       </c>
       <c r="H27" s="20">
-        <v>0.5050654897521694</v>
+        <v>-0.8151434307759278</v>
       </c>
       <c r="I27" s="20">
-        <v>0.5229426848176244</v>
+        <v>3.899748911067756</v>
       </c>
       <c r="J27" s="20">
-        <v>0.5329666943539282</v>
+        <v>0.2873587861215741</v>
       </c>
       <c r="K27" s="20">
-        <v>1.638740132347517</v>
+        <v>3.387114135534589</v>
       </c>
       <c r="L27" s="20">
-        <v>0.133022163312334</v>
+        <v>-3.375332568109985</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.1146722046017475</v>
+        <v>-0.4415151222694788</v>
       </c>
       <c r="N27" s="20">
-        <v>16.146498</v>
+        <v>12.300613</v>
       </c>
       <c r="O27" s="20">
-        <v>4.015142</v>
+        <v>2.5690305</v>
       </c>
       <c r="P27" s="12">
-        <v>0.30667</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.377</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R27" s="12">
-        <v>0.3198957169608165</v>
+        <v>0.1947968025517657</v>
       </c>
       <c r="S27" s="11">
-        <v>44.8250673854801</v>
+        <v>50.70653346487457</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5100,46 +5461,46 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
       <c r="E28" s="10">
-        <v>208.3000030517578</v>
+        <v>206.6799926757812</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5211228793123472</v>
+        <v>0.504567505531323</v>
       </c>
       <c r="G28" s="20">
-        <v>0.5809437263948974</v>
+        <v>0.5982241598157348</v>
       </c>
       <c r="H28" s="20">
-        <v>-0.6585101921976751</v>
+        <v>-0.6609329225841165</v>
       </c>
       <c r="I28" s="20">
-        <v>4.120745224686987</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J28" s="20">
-        <v>-0.007026659802694929</v>
+        <v>-0.07830011893937884</v>
       </c>
       <c r="K28" s="20">
-        <v>0.5994822798464103</v>
+        <v>0.6077919314133636</v>
       </c>
       <c r="L28" s="20">
-        <v>0.6205594399114807</v>
+        <v>0.6090994367614738</v>
       </c>
       <c r="M28" s="20">
-        <v>0.03470843510931609</v>
+        <v>0.06158427372857556</v>
       </c>
       <c r="N28" s="20">
-        <v>12.092511</v>
+        <v>11.482911</v>
       </c>
       <c r="O28" s="20">
-        <v>1.3082409</v>
+        <v>1.2409225</v>
       </c>
       <c r="P28" s="12">
         <v>0.09031</v>
@@ -5148,13 +5509,13 @@
         <v>11.11</v>
       </c>
       <c r="R28" s="12">
-        <v>0.1830537011774684</v>
+        <v>0.1585748780907137</v>
       </c>
       <c r="S28" s="11">
-        <v>41.95173730919371</v>
+        <v>40.13111347997287</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5162,61 +5523,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>111</v>
+        <v>32</v>
       </c>
       <c r="E29" s="10">
-        <v>118.1699981689453</v>
+        <v>351.8099975585938</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5139010321103271</v>
+        <v>0.5022143598943355</v>
       </c>
       <c r="G29" s="20">
-        <v>0.3599925540636538</v>
+        <v>0.116365121381956</v>
       </c>
       <c r="H29" s="20">
-        <v>-0.1244310120248844</v>
+        <v>-0.2401012663427755</v>
       </c>
       <c r="I29" s="20">
-        <v>0.4821804333312243</v>
+        <v>0.4632294407463022</v>
       </c>
       <c r="J29" s="20">
-        <v>-0.2352352732388189</v>
+        <v>1.46904739909879</v>
       </c>
       <c r="K29" s="20">
-        <v>4.196860964161699</v>
+        <v>1.709491264929422</v>
       </c>
       <c r="L29" s="20">
-        <v>0.0138353839038388</v>
+        <v>-1.628486928373788</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.1636195724032518</v>
+        <v>-0.9347757404117922</v>
       </c>
       <c r="N29" s="20">
-        <v>16.105392</v>
+        <v>32.14404</v>
       </c>
       <c r="O29" s="20">
-        <v>7.2471595</v>
+        <v>4.8336897</v>
       </c>
       <c r="P29" s="12">
-        <v>0.46032003</v>
+        <v>0.15286</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.204</v>
       </c>
       <c r="R29" s="12">
-        <v>0.05792302056821974</v>
+        <v>0.7354478859516924</v>
       </c>
       <c r="S29" s="11">
-        <v>35.54601186970746</v>
+        <v>53.41973379161933</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5224,61 +5585,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E30" s="10">
-        <v>350.3699951171875</v>
+        <v>97.19000244140625</v>
       </c>
       <c r="F30" s="17">
-        <v>0.5031079626401821</v>
+        <v>0.4977545090094619</v>
       </c>
       <c r="G30" s="20">
-        <v>0.09769025453656566</v>
+        <v>-0.7359494773385853</v>
       </c>
       <c r="H30" s="20">
-        <v>-0.2373803208952873</v>
+        <v>-1.140633242548325</v>
       </c>
       <c r="I30" s="20">
-        <v>0.4704496970046058</v>
+        <v>0.5241404076306111</v>
       </c>
       <c r="J30" s="20">
-        <v>1.494343633819099</v>
+        <v>1.090085289670754</v>
       </c>
       <c r="K30" s="20">
-        <v>1.69802319437015</v>
+        <v>4.197997932171494</v>
       </c>
       <c r="L30" s="20">
-        <v>-1.695948106348713</v>
+        <v>-2.421908977065426</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.923117357785492</v>
+        <v>0.9355236604649794</v>
       </c>
       <c r="N30" s="20">
-        <v>33.248394</v>
+        <v>50.34258</v>
       </c>
       <c r="O30" s="20">
-        <v>5.0043454</v>
+        <v>5.9300656</v>
       </c>
       <c r="P30" s="12">
-        <v>0.15286</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.204</v>
+        <v>0.254</v>
       </c>
       <c r="R30" s="12">
-        <v>0.717079097657819</v>
+        <v>1.123443335577257</v>
       </c>
       <c r="S30" s="11">
-        <v>52.57590743069353</v>
+        <v>50.33356514283881</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5286,61 +5647,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E31" s="10">
-        <v>214.0599975585938</v>
+        <v>170.1799926757812</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4908089639076276</v>
+        <v>0.4946433876191874</v>
       </c>
       <c r="G31" s="20">
-        <v>0.5306330587817526</v>
+        <v>-2.045758834681303</v>
       </c>
       <c r="H31" s="20">
-        <v>-0.3271612979466518</v>
+        <v>1.763423185417039</v>
       </c>
       <c r="I31" s="20">
-        <v>2.322186162377909</v>
+        <v>0.2278103986420596</v>
       </c>
       <c r="J31" s="20">
-        <v>0.8110245415781004</v>
+        <v>1.855770303469042</v>
       </c>
       <c r="K31" s="20">
-        <v>-0.1711975264478132</v>
+        <v>0.4392541638271436</v>
       </c>
       <c r="L31" s="20">
-        <v>0.8411276695605793</v>
+        <v>-0.5582201727433476</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.7226139339092731</v>
+        <v>-0.2249644000559904</v>
       </c>
       <c r="N31" s="20">
-        <v>20.076998</v>
+        <v>55.343975</v>
       </c>
       <c r="O31" s="20">
-        <v>2.1549587</v>
+        <v>73.826866</v>
       </c>
       <c r="P31" s="12">
-        <v>0.12231</v>
+        <v>1.17442</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.535</v>
+        <v>0.256</v>
       </c>
       <c r="R31" s="12">
-        <v>0.1062895957896659</v>
+        <v>1.039549229343397</v>
       </c>
       <c r="S31" s="11">
-        <v>69.51936874222667</v>
+        <v>59.88350413991242</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5348,46 +5709,46 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="E32" s="10">
-        <v>217.1499938964844</v>
+        <v>217.3600006103516</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4829213808748131</v>
+        <v>0.4914478888561534</v>
       </c>
       <c r="G32" s="20">
-        <v>0.2276945080429548</v>
+        <v>0.2268704470519779</v>
       </c>
       <c r="H32" s="20">
-        <v>0.03119877719549098</v>
+        <v>0.02833393151366955</v>
       </c>
       <c r="I32" s="20">
-        <v>-0.8985721544356027</v>
+        <v>-0.8973367206108911</v>
       </c>
       <c r="J32" s="20">
-        <v>0.5363377459748063</v>
+        <v>0.5470984017590618</v>
       </c>
       <c r="K32" s="20">
-        <v>3.362072970101089</v>
+        <v>3.378325356243283</v>
       </c>
       <c r="L32" s="20">
-        <v>-0.1378791359550449</v>
+        <v>-0.1193469719306684</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.3659443940988363</v>
+        <v>-0.3319536694421627</v>
       </c>
       <c r="N32" s="20">
-        <v>39.2238</v>
+        <v>38.63879</v>
       </c>
       <c r="O32" s="20">
-        <v>1.730507</v>
+        <v>1.7016691</v>
       </c>
       <c r="P32" s="12">
         <v>0.04575</v>
@@ -5396,13 +5757,13 @@
         <v>0.034</v>
       </c>
       <c r="R32" s="12">
-        <v>0.1744186104086896</v>
+        <v>0.1972459209950259</v>
       </c>
       <c r="S32" s="11">
-        <v>53.18370664558372</v>
+        <v>53.41396335420527</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5410,61 +5771,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E33" s="10">
-        <v>218.2899932861328</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4503679053242157</v>
+        <v>0.4645998663918035</v>
       </c>
       <c r="G33" s="20">
-        <v>-1.255664189485384</v>
+        <v>0.5000449645463003</v>
       </c>
       <c r="H33" s="20">
-        <v>2.368358787986747</v>
+        <v>-0.3299402274497991</v>
       </c>
       <c r="I33" s="20">
-        <v>2.430954222251415</v>
+        <v>2.306272783126228</v>
       </c>
       <c r="J33" s="20">
-        <v>0.3601516709464662</v>
+        <v>0.7195024761276629</v>
       </c>
       <c r="K33" s="20">
-        <v>-0.3093528362049048</v>
+        <v>-0.165103659204425</v>
       </c>
       <c r="L33" s="20">
-        <v>-0.1969188097566814</v>
+        <v>0.835800977246664</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.059417515317334</v>
+        <v>-0.617892893946917</v>
       </c>
       <c r="N33" s="20">
-        <v>29.159492</v>
+        <v>20.62235</v>
       </c>
       <c r="O33" s="20">
-        <v>24.291891</v>
+        <v>2.2113636</v>
       </c>
       <c r="P33" s="12">
-        <v>1.17211</v>
+        <v>0.12231</v>
       </c>
       <c r="Q33" s="12">
-        <v>1.059</v>
+        <v>0.535</v>
       </c>
       <c r="R33" s="12">
-        <v>0.1946541308810243</v>
+        <v>0.0973574364996117</v>
       </c>
       <c r="S33" s="11">
-        <v>49.94178812835036</v>
+        <v>65.04431477195874</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5472,61 +5833,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="E34" s="10">
-        <v>63.63999938964844</v>
+        <v>31.40999984741211</v>
       </c>
       <c r="F34" s="17">
-        <v>0.44128887322844</v>
+        <v>0.4615724621097789</v>
       </c>
       <c r="G34" s="20">
-        <v>0.4785242056074159</v>
+        <v>0.5071505500348842</v>
       </c>
       <c r="H34" s="20">
-        <v>0.6574599095763384</v>
+        <v>0.7469802265893087</v>
       </c>
       <c r="I34" s="20">
-        <v>0.2335665909722698</v>
+        <v>-0.1877648684685418</v>
       </c>
       <c r="J34" s="20">
-        <v>0.3722764513651591</v>
+        <v>1.241815959815756</v>
       </c>
       <c r="K34" s="20">
-        <v>0.8031067102719743</v>
+        <v>-0.4675410642287771</v>
       </c>
       <c r="L34" s="20">
-        <v>0.5509703807197827</v>
+        <v>0.1846712921650581</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.1813711486963455</v>
+        <v>-0.7246890508889072</v>
       </c>
       <c r="N34" s="20">
-        <v>14.718061</v>
+        <v>17.695906</v>
       </c>
       <c r="O34" s="20">
-        <v>6.116247</v>
+        <v>6.8245378</v>
       </c>
       <c r="P34" s="12">
-        <v>0.46598998</v>
+        <v>0.41944</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="R34" s="12">
-        <v>0.1030022530335821</v>
+        <v>0.5337299998100054</v>
       </c>
       <c r="S34" s="11">
-        <v>42.4506459041333</v>
+        <v>64.38687725087902</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5534,61 +5895,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>94</v>
+        <v>57</v>
       </c>
       <c r="E35" s="10">
-        <v>214.3800048828125</v>
+        <v>64.09999847412109</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4345414076806038</v>
+        <v>0.4464677891271827</v>
       </c>
       <c r="G35" s="20">
-        <v>0.3451625228080399</v>
+        <v>0.5011052908132025</v>
       </c>
       <c r="H35" s="20">
-        <v>0.7739793579701058</v>
+        <v>0.6560191381210976</v>
       </c>
       <c r="I35" s="20">
-        <v>0.3853148937972363</v>
+        <v>0.2251020255328333</v>
       </c>
       <c r="J35" s="20">
-        <v>0.4354113101104577</v>
+        <v>0.4190087502398802</v>
       </c>
       <c r="K35" s="20">
-        <v>0.2979119208617143</v>
+        <v>0.8120018031819431</v>
       </c>
       <c r="L35" s="20">
-        <v>0.5831377467762073</v>
+        <v>0.5531957554170509</v>
       </c>
       <c r="M35" s="20">
-        <v>0.1085359822137566</v>
+        <v>-0.344237683133413</v>
       </c>
       <c r="N35" s="20">
-        <v>17.572235</v>
+        <v>14.017621</v>
       </c>
       <c r="O35" s="20">
-        <v>3.211162</v>
+        <v>5.8251715</v>
       </c>
       <c r="P35" s="12">
-        <v>0.17969999</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.28</v>
+        <v>0.057</v>
       </c>
       <c r="R35" s="12">
-        <v>0.4038903336206143</v>
+        <v>0.1085302727958339</v>
       </c>
       <c r="S35" s="11">
-        <v>49.59978529957923</v>
+        <v>44.99825693028483</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5596,61 +5957,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>141</v>
+        <v>9</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E36" s="10">
-        <v>379.7200012207031</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="F36" s="17">
-        <v>0.419433272667214</v>
+        <v>0.4061175674949531</v>
       </c>
       <c r="G36" s="20">
-        <v>-1.119776310688084</v>
+        <v>-1.171878848863184</v>
       </c>
       <c r="H36" s="20">
-        <v>0.5633615561685517</v>
+        <v>2.368118728722743</v>
       </c>
       <c r="I36" s="20">
-        <v>3.683499757563413</v>
+        <v>2.422793453764177</v>
       </c>
       <c r="J36" s="20">
-        <v>0.954469186224158</v>
+        <v>0.14840354654265</v>
       </c>
       <c r="K36" s="20">
-        <v>0.4185400644555927</v>
+        <v>-0.3036561797967777</v>
       </c>
       <c r="L36" s="20">
-        <v>-3.267237994280757</v>
+        <v>-0.2158843142054807</v>
       </c>
       <c r="M36" s="20">
-        <v>0.2746737487835807</v>
+        <v>0.009351934792708835</v>
       </c>
       <c r="N36" s="20">
-        <v>49.04258</v>
+        <v>27.631645</v>
       </c>
       <c r="O36" s="20">
-        <v>16.253017</v>
+        <v>23.019087</v>
       </c>
       <c r="P36" s="12">
-        <v>0.36465</v>
+        <v>1.17211</v>
       </c>
       <c r="Q36" s="12">
-        <v>1.039</v>
+        <v>1.059</v>
       </c>
       <c r="R36" s="12">
-        <v>0.3258761668860892</v>
+        <v>0.17304963335504</v>
       </c>
       <c r="S36" s="11">
-        <v>53.13233410644662</v>
+        <v>44.06645392019853</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -5658,61 +6019,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E37" s="10">
-        <v>137.3500061035156</v>
+        <v>148.5399932861328</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4042025057020031</v>
+        <v>0.4059299958043636</v>
       </c>
       <c r="G37" s="20">
-        <v>0.5166686592886003</v>
+        <v>0.6042209697867998</v>
       </c>
       <c r="H37" s="20">
-        <v>-0.1376180067425467</v>
+        <v>0.4636940000902633</v>
       </c>
       <c r="I37" s="20">
-        <v>0.8009706460259883</v>
+        <v>1.421647839457134</v>
       </c>
       <c r="J37" s="20">
-        <v>0.9931344522895759</v>
+        <v>0.4863464245768306</v>
       </c>
       <c r="K37" s="20">
-        <v>-0.06912755879145449</v>
+        <v>-0.5135529087538494</v>
       </c>
       <c r="L37" s="20">
-        <v>0.5669399032545589</v>
+        <v>0.3291780617737359</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.8817182415113511</v>
+        <v>-0.290173309330341</v>
       </c>
       <c r="N37" s="20">
-        <v>17.759258</v>
+        <v>11.467704</v>
       </c>
       <c r="O37" s="20">
-        <v>2.4681509</v>
+        <v>2.4302394</v>
       </c>
       <c r="P37" s="12">
-        <v>0.1418</v>
+        <v>0.22507</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.355</v>
+        <v>0.587</v>
       </c>
       <c r="R37" s="12">
-        <v>0.1582708669984993</v>
+        <v>0.1287743438540248</v>
       </c>
       <c r="S37" s="11">
-        <v>67.83650141589177</v>
+        <v>56.75913156885876</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -5720,61 +6081,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>3</v>
+        <v>146</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>35</v>
+        <v>147</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="E38" s="10">
-        <v>447.1799926757812</v>
+        <v>206.5800018310547</v>
       </c>
       <c r="F38" s="17">
-        <v>0.3998918004719155</v>
+        <v>0.3933324678735144</v>
       </c>
       <c r="G38" s="20">
-        <v>-0.9800881674162824</v>
+        <v>0.3472624676162839</v>
       </c>
       <c r="H38" s="20">
-        <v>2.147104391138658</v>
+        <v>0.7723653122279558</v>
       </c>
       <c r="I38" s="20">
-        <v>2.675284350851072</v>
+        <v>0.38054810430196</v>
       </c>
       <c r="J38" s="20">
-        <v>0.4038651476196932</v>
+        <v>0.1945124556594171</v>
       </c>
       <c r="K38" s="20">
-        <v>-0.2212015005016859</v>
+        <v>0.3053545263890117</v>
       </c>
       <c r="L38" s="20">
-        <v>-3.28307080283564</v>
+        <v>0.534156262049035</v>
       </c>
       <c r="M38" s="20">
-        <v>0.8451427110498325</v>
+        <v>0.5268288466058211</v>
       </c>
       <c r="N38" s="20">
-        <v>17.358335</v>
+        <v>17.330639</v>
       </c>
       <c r="O38" s="20">
-        <v>22.350464</v>
+        <v>3.1619003</v>
       </c>
       <c r="P38" s="12">
-        <v>1.30853</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.438</v>
+        <v>0.28</v>
       </c>
       <c r="R38" s="12">
-        <v>0.7131488189039898</v>
+        <v>0.3484435320974817</v>
       </c>
       <c r="S38" s="11">
-        <v>43.91793139510307</v>
+        <v>39.02348633706364</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -5782,61 +6143,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E39" s="10">
-        <v>30.26000022888184</v>
+        <v>205.7200012207031</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3976346685421113</v>
+        <v>0.3920595159076784</v>
       </c>
       <c r="G39" s="20">
-        <v>0.5193752875190029</v>
+        <v>0.5627498454653113</v>
       </c>
       <c r="H39" s="20">
-        <v>0.748394208904259</v>
+        <v>-0.0477566135254233</v>
       </c>
       <c r="I39" s="20">
-        <v>-0.1830681180986245</v>
+        <v>1.594428774498311</v>
       </c>
       <c r="J39" s="20">
-        <v>0.9786210952682423</v>
+        <v>0.550469595109168</v>
       </c>
       <c r="K39" s="20">
-        <v>-0.4727678854325094</v>
+        <v>-0.1919869840954785</v>
       </c>
       <c r="L39" s="20">
-        <v>0.189479635265813</v>
+        <v>0.2937031583342088</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.568901315883107</v>
+        <v>-0.2595238187898328</v>
       </c>
       <c r="N39" s="20">
-        <v>17.923977</v>
+        <v>39.041904</v>
       </c>
       <c r="O39" s="20">
-        <v>6.912494</v>
+        <v>1.5173635</v>
       </c>
       <c r="P39" s="12">
-        <v>0.41944</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.063</v>
+        <v>0.525</v>
       </c>
       <c r="R39" s="12">
-        <v>0.4550608701426258</v>
+        <v>0.1404870673104863</v>
       </c>
       <c r="S39" s="11">
-        <v>57.77418061931316</v>
+        <v>57.25834194063431</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -5844,61 +6205,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="E40" s="10">
-        <v>147.3600006103516</v>
+        <v>30.55999946594238</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3973518871613852</v>
+        <v>0.3900271290579442</v>
       </c>
       <c r="G40" s="20">
-        <v>0.6186160464919896</v>
+        <v>0.4737570391617266</v>
       </c>
       <c r="H40" s="20">
-        <v>0.4653349166417897</v>
+        <v>-0.2868604961518937</v>
       </c>
       <c r="I40" s="20">
-        <v>1.428599056298859</v>
+        <v>-0.7009083349924576</v>
       </c>
       <c r="J40" s="20">
-        <v>0.4401632307542995</v>
+        <v>0.697337619245387</v>
       </c>
       <c r="K40" s="20">
-        <v>-0.5186478203891555</v>
+        <v>2.026921293450708</v>
       </c>
       <c r="L40" s="20">
-        <v>0.3288122224343177</v>
+        <v>0.5468694977199896</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.2606557203174431</v>
+        <v>-0.8063079494814781</v>
       </c>
       <c r="N40" s="20">
-        <v>11.298833</v>
+        <v>28.582525</v>
       </c>
       <c r="O40" s="20">
-        <v>2.394452</v>
+        <v>1.876474</v>
       </c>
       <c r="P40" s="12">
-        <v>0.22507</v>
+        <v>0.07979</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.587</v>
+        <v>0.108</v>
       </c>
       <c r="R40" s="12">
-        <v>0.1245209739777566</v>
+        <v>0.2937901027918621</v>
       </c>
       <c r="S40" s="11">
-        <v>54.45698842727787</v>
+        <v>59.65608369551476</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -5906,61 +6267,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E41" s="10">
-        <v>204.9700012207031</v>
+        <v>136.6699981689453</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3970827025069025</v>
+        <v>0.3721303453043072</v>
       </c>
       <c r="G41" s="20">
-        <v>0.6168563890519317</v>
+        <v>0.4918102935471612</v>
       </c>
       <c r="H41" s="20">
-        <v>-0.04487785224304153</v>
+        <v>-0.1401007530318513</v>
       </c>
       <c r="I41" s="20">
-        <v>1.604307978960174</v>
+        <v>0.7942683123659047</v>
       </c>
       <c r="J41" s="20">
-        <v>0.5467413748387874</v>
+        <v>0.8963141260411401</v>
       </c>
       <c r="K41" s="20">
-        <v>-0.1980037805797862</v>
+        <v>-0.09169150277116346</v>
       </c>
       <c r="L41" s="20">
-        <v>0.2824804940300665</v>
+        <v>0.5579982189079566</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.3051572185430234</v>
+        <v>-0.8097171112494491</v>
       </c>
       <c r="N41" s="20">
-        <v>37.874523</v>
+        <v>18.192053</v>
       </c>
       <c r="O41" s="20">
-        <v>1.474797</v>
+        <v>2.5249555</v>
       </c>
       <c r="P41" s="12">
-        <v>0.034930002</v>
+        <v>0.1418</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.525</v>
+        <v>0.355</v>
       </c>
       <c r="R41" s="12">
-        <v>0.1707381737518001</v>
+        <v>0.1371238456011952</v>
       </c>
       <c r="S41" s="11">
-        <v>56.25120194060135</v>
+        <v>65.58973752517147</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -5968,61 +6329,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="E42" s="10">
-        <v>28.04000091552734</v>
+        <v>793.739990234375</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3940519480670779</v>
+        <v>0.368973775574238</v>
       </c>
       <c r="G42" s="20">
-        <v>-0.07115990276327171</v>
+        <v>0.1788464932883841</v>
       </c>
       <c r="H42" s="20">
-        <v>-0.995994779142174</v>
+        <v>0.1776972721221774</v>
       </c>
       <c r="I42" s="20">
-        <v>-1.178947812209808</v>
+        <v>-0.2413594266157033</v>
       </c>
       <c r="J42" s="20">
-        <v>0.4619663599887935</v>
+        <v>0.63685502750477</v>
       </c>
       <c r="K42" s="20">
-        <v>4.196860964161699</v>
+        <v>1.445310899173108</v>
       </c>
       <c r="L42" s="20">
-        <v>1.141149646169156</v>
+        <v>0.454061519965289</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.3320940752249485</v>
+        <v>-0.7406465180721314</v>
       </c>
       <c r="N42" s="20">
-        <v>403.57144</v>
+        <v>19.343811</v>
       </c>
       <c r="O42" s="20">
-        <v>2.1576414</v>
+        <v>2.4722013</v>
       </c>
       <c r="P42" s="12">
-        <v>-0.08785999999999999</v>
+        <v>0.14043</v>
       </c>
       <c r="Q42" s="12">
-        <v>-0.112</v>
+        <v>0.167</v>
       </c>
       <c r="R42" s="12">
-        <v>0.02223844708585232</v>
+        <v>0.06715712135397278</v>
       </c>
       <c r="S42" s="11">
-        <v>51.97980644831724</v>
+        <v>49.68973050061668</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -6030,61 +6391,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="E43" s="10">
-        <v>409.7999877929688</v>
+        <v>94.83000183105469</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3655179421124001</v>
+        <v>0.3631360821217977</v>
       </c>
       <c r="G43" s="20">
-        <v>0.3688830871595546</v>
+        <v>0.6594637779990824</v>
       </c>
       <c r="H43" s="20">
-        <v>-1.053638917449358</v>
+        <v>-0.4971404169201537</v>
       </c>
       <c r="I43" s="20">
-        <v>0.1661481722292586</v>
+        <v>-0.2300784505986128</v>
       </c>
       <c r="J43" s="20">
-        <v>1.624220252399921</v>
+        <v>1.27602183415249</v>
       </c>
       <c r="K43" s="20">
-        <v>-0.1737750508835799</v>
+        <v>-0.2845276601627589</v>
       </c>
       <c r="L43" s="20">
-        <v>0.2279229399716757</v>
+        <v>0.0885615046222254</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.3625256252449436</v>
+        <v>-0.08742509318125991</v>
       </c>
       <c r="N43" s="20">
-        <v>38.02462</v>
+        <v>15.108153</v>
       </c>
       <c r="O43" s="20">
-        <v>2.5096092</v>
+        <v>6.0021152</v>
       </c>
       <c r="P43" s="12">
-        <v>0.06893000000000001</v>
+        <v>0.43126</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.262</v>
+        <v>0.036</v>
       </c>
       <c r="R43" s="12">
-        <v>1.522472101653082</v>
+        <v>0.5586363090029245</v>
       </c>
       <c r="S43" s="11">
-        <v>63.3418407280259</v>
+        <v>66.09833206083282</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6092,61 +6453,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>157</v>
+        <v>53</v>
       </c>
       <c r="E44" s="10">
-        <v>126.8099975585938</v>
+        <v>119.5</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3617139796245003</v>
+        <v>0.354802417641556</v>
       </c>
       <c r="G44" s="20">
-        <v>0.462770354618154</v>
+        <v>1.17687233316855</v>
       </c>
       <c r="H44" s="20">
-        <v>0.7818596344809873</v>
+        <v>-0.6497553567411484</v>
       </c>
       <c r="I44" s="20">
-        <v>-0.2047856713387676</v>
+        <v>0.1405562026344188</v>
       </c>
       <c r="J44" s="20">
-        <v>1.068677546500124</v>
+        <v>0.5044582089342483</v>
       </c>
       <c r="K44" s="20">
-        <v>-0.3340970707882645</v>
+        <v>0.2040250710304253</v>
       </c>
       <c r="L44" s="20">
-        <v>-0.5008048414089193</v>
+        <v>1.038566297027085</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.9583372945094849</v>
+        <v>-0.06579768173989665</v>
       </c>
       <c r="N44" s="20">
-        <v>16.152584</v>
+        <v>10.810517</v>
       </c>
       <c r="O44" s="20">
-        <v>3.848858</v>
+        <v>1.3035825</v>
       </c>
       <c r="P44" s="12">
-        <v>0.25905</v>
+        <v>0.12011</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.151</v>
+        <v>0.141</v>
       </c>
       <c r="R44" s="12">
-        <v>0.1126020562190284</v>
+        <v>0.3318159648837586</v>
       </c>
       <c r="S44" s="11">
-        <v>57.66914608363002</v>
+        <v>50.06186264628786</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -6212,110 +6573,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -6324,22 +6685,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -6418,171 +6779,171 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -6600,7 +6961,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI9"/>
+  <dimension ref="A1:BI13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:61">
@@ -6608,184 +6969,184 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>418.6282348632812</v>
+        <v>408.8244323730469</v>
       </c>
       <c r="C1">
-        <v>408.8244323730469</v>
+        <v>418.0192260742188</v>
       </c>
       <c r="D1">
-        <v>418.0192260742188</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="E1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="F1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="G1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="H1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="I1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="J1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="K1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="L1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="M1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="N1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="O1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="P1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="Q1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="R1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="S1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="T1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="U1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="V1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="W1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="X1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="Y1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="Z1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="AA1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="AB1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AC1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AD1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AE1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AF1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AG1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AH1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AI1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AJ1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AK1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AL1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AM1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AN1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AO1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AP1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AQ1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AR1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AS1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AT1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AU1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AV1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="AW1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="AX1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="AY1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="AZ1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="BA1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="BB1">
-        <v>425</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="BC1">
-        <v>492.2000122070312</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="BD1">
-        <v>516.3900146484375</v>
+        <v>524.1400146484375</v>
       </c>
       <c r="BE1">
-        <v>524.1400146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="BF1">
-        <v>533.8800048828125</v>
+        <v>535.25</v>
       </c>
       <c r="BG1">
-        <v>535.25</v>
+        <v>506.6199951171875</v>
       </c>
       <c r="BH1">
-        <v>506.6199951171875</v>
+        <v>567.2899780273438</v>
       </c>
       <c r="BI1">
-        <v>567.2899780273438</v>
+        <v>534.280029296875</v>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -6793,184 +7154,184 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1043.029541015625</v>
+        <v>1133.815551757812</v>
       </c>
       <c r="C2">
-        <v>1133.815551757812</v>
+        <v>1211.193725585938</v>
       </c>
       <c r="D2">
-        <v>1211.193725585938</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="E2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="F2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="G2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="H2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="I2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="J2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="K2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="L2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="M2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="N2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="O2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="P2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="Q2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="R2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="S2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="T2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="U2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="V2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="W2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="X2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="Y2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="Z2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="AA2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="AB2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AC2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AD2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AE2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AF2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AG2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AH2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AI2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AJ2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AK2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AL2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AM2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AN2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AO2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AP2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AQ2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AR2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AS2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AT2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AU2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AV2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="AW2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="AX2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="AY2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="AZ2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="BA2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="BB2">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="BC2">
-        <v>956.0800170898438</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="BD2">
-        <v>958.1599731445312</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="BE2">
-        <v>1016.590026855469</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="BF2">
-        <v>1000.260009765625</v>
+        <v>1027.77001953125</v>
       </c>
       <c r="BG2">
-        <v>1027.77001953125</v>
+        <v>977.4099731445312</v>
       </c>
       <c r="BH2">
-        <v>977.4099731445312</v>
+        <v>975.260009765625</v>
       </c>
       <c r="BI2">
-        <v>975.260009765625</v>
+        <v>924.030029296875</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -6978,184 +7339,184 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1958.800048828125</v>
+        <v>2184.75</v>
       </c>
       <c r="C3">
-        <v>2184.75</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="D3">
+        <v>1963.599975585938</v>
+      </c>
+      <c r="E3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="F3">
+        <v>2335</v>
+      </c>
+      <c r="G3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="H3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="I3">
         <v>2273.72998046875</v>
       </c>
-      <c r="E3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="F3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="G3">
-        <v>2335</v>
-      </c>
-      <c r="H3">
-        <v>2090.7099609375</v>
-      </c>
-      <c r="I3">
-        <v>2050.389892578125</v>
-      </c>
       <c r="J3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="K3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="L3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="M3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="N3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="O3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="P3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="Q3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="R3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="S3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="T3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="U3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="V3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="W3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="X3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="Y3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="Z3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="AA3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="AB3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AC3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AD3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AE3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AF3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AG3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AH3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AI3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AJ3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AK3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AL3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AM3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AN3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AO3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AP3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AQ3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AR3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AS3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AT3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AU3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AV3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="AW3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AX3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="AY3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="AZ3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="BA3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="BB3">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="BC3">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="BD3">
-        <v>1554.989990234375</v>
+        <v>1740</v>
       </c>
       <c r="BE3">
-        <v>1740</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="BF3">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="BG3">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="BH3">
-        <v>1692.589965820312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="BI3">
-        <v>1633.349975585938</v>
+        <v>1551.989990234375</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -7163,184 +7524,184 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>711.9014892578125</v>
+        <v>745.990478515625</v>
       </c>
       <c r="C4">
-        <v>745.990478515625</v>
+        <v>732.3848876953125</v>
       </c>
       <c r="D4">
-        <v>732.3848876953125</v>
+        <v>670.5347290039062</v>
       </c>
       <c r="E4">
-        <v>670.5347290039062</v>
+        <v>643.6234130859375</v>
       </c>
       <c r="F4">
-        <v>643.6234130859375</v>
+        <v>675.1732788085938</v>
       </c>
       <c r="G4">
-        <v>675.1732788085938</v>
+        <v>586.2618408203125</v>
       </c>
       <c r="H4">
-        <v>586.2618408203125</v>
+        <v>651.6708374023438</v>
       </c>
       <c r="I4">
-        <v>651.6708374023438</v>
+        <v>638.5150146484375</v>
       </c>
       <c r="J4">
-        <v>638.5150146484375</v>
+        <v>598.177978515625</v>
       </c>
       <c r="K4">
-        <v>598.177978515625</v>
+        <v>538.8270263671875</v>
       </c>
       <c r="L4">
-        <v>538.8270263671875</v>
+        <v>577.2747192382812</v>
       </c>
       <c r="M4">
-        <v>577.2747192382812</v>
+        <v>531.92919921875</v>
       </c>
       <c r="N4">
-        <v>531.92919921875</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="O4">
-        <v>550.1234130859375</v>
+        <v>577.864501953125</v>
       </c>
       <c r="P4">
-        <v>577.864501953125</v>
+        <v>582.403076171875</v>
       </c>
       <c r="Q4">
-        <v>582.403076171875</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="R4">
-        <v>555.3717041015625</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="S4">
-        <v>563.1392211914062</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="T4">
-        <v>513.6751098632812</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="U4">
-        <v>466.6601867675781</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="V4">
-        <v>477.0668640136719</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="W4">
-        <v>487.2635803222656</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="X4">
-        <v>548.2140502929688</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="Y4">
-        <v>556.4913330078125</v>
+        <v>558.120849609375</v>
       </c>
       <c r="Z4">
-        <v>558.120849609375</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="AA4">
-        <v>519.6331787109375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="AB4">
-        <v>497.7602233886719</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="AC4">
-        <v>463.3612670898438</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="AD4">
-        <v>461.8917236328125</v>
+        <v>532.868896484375</v>
       </c>
       <c r="AE4">
-        <v>532.868896484375</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="AF4">
-        <v>544.6651611328125</v>
+        <v>527.05078125</v>
       </c>
       <c r="AG4">
-        <v>527.05078125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="AH4">
-        <v>548.3839721679688</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="AI4">
-        <v>519.0033569335938</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="AJ4">
-        <v>451.3750915527344</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="AK4">
-        <v>434.1606140136719</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AL4">
-        <v>438.1993408203125</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AM4">
-        <v>437.7894592285156</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AN4">
-        <v>453.9542846679688</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AO4">
-        <v>487.1336364746094</v>
+        <v>508.63671875</v>
       </c>
       <c r="AP4">
-        <v>508.63671875</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AQ4">
-        <v>535.8380126953125</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AR4">
-        <v>496.0007934570312</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AS4">
-        <v>461.9417114257812</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AT4">
-        <v>468.8994750976562</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AU4">
-        <v>459.2925720214844</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AV4">
-        <v>435.2402954101562</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="AW4">
-        <v>450.6053466796875</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AX4">
-        <v>468.7295227050781</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="AY4">
-        <v>461.8517456054688</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="AZ4">
-        <v>459.3025817871094</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="BA4">
-        <v>450.4053955078125</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="BB4">
-        <v>450.2954406738281</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="BC4">
-        <v>448.7559509277344</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="BD4">
-        <v>441.4283142089844</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="BE4">
-        <v>467.3099670410156</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="BF4">
-        <v>477.2999877929688</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="BG4">
-        <v>482.2799987792969</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="BH4">
-        <v>460.9299926757812</v>
+        <v>447.1799926757812</v>
       </c>
       <c r="BI4">
-        <v>447.1799926757812</v>
+        <v>426.9400024414062</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -7348,184 +7709,184 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>238.8469543457031</v>
+        <v>235.3903045654297</v>
       </c>
       <c r="C5">
-        <v>235.3903045654297</v>
+        <v>242.8415069580078</v>
       </c>
       <c r="D5">
-        <v>242.8415069580078</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="E5">
-        <v>242.7418823242188</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="F5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="G5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="H5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="I5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="J5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="K5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="L5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="M5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="N5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="O5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="P5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="Q5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="R5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="S5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="T5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="U5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="V5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="W5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="X5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="Y5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="Z5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="AA5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="AB5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AC5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AD5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AE5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AF5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AG5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AH5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AI5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AJ5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AK5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AL5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AM5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AN5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AO5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AP5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AQ5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AR5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AS5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AT5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AU5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="AV5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="AW5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AX5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="AY5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="AZ5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="BA5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="BB5">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="BC5">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="BD5">
-        <v>370.6900024414062</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="BE5">
-        <v>370.7200012207031</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="BF5">
-        <v>382.8500061035156</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="BG5">
-        <v>388.9500122070312</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="BH5">
-        <v>385.4299926757812</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="BI5">
-        <v>390.4200134277344</v>
+        <v>382.9500122070312</v>
       </c>
     </row>
     <row r="6" spans="1:61">
@@ -7533,184 +7894,184 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>243.9420471191406</v>
+        <v>242.2467041015625</v>
       </c>
       <c r="C6">
-        <v>242.2467041015625</v>
+        <v>246.6147308349609</v>
       </c>
       <c r="D6">
-        <v>246.6147308349609</v>
+        <v>247.8413848876953</v>
       </c>
       <c r="E6">
-        <v>247.8413848876953</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="F6">
-        <v>245.8368530273438</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="G6">
-        <v>252.8676147460938</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="H6">
-        <v>253.3662414550781</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="I6">
-        <v>258.5121459960938</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="J6">
-        <v>254.9718475341797</v>
+        <v>264.146728515625</v>
       </c>
       <c r="K6">
-        <v>264.146728515625</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="L6">
-        <v>265.6226806640625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="M6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="N6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="O6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="P6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="Q6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="R6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="S6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="T6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="U6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="V6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="W6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="X6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="Y6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="Z6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="AA6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="AB6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="AC6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AD6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AE6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AF6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AG6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AH6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AI6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AJ6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AK6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AL6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AM6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AN6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AO6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AP6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AQ6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AR6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AS6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AT6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AU6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AV6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="AW6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AX6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="AY6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="AZ6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="BA6">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="BB6">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="BC6">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="BD6">
-        <v>387.7099914550781</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="BE6">
-        <v>388.8999938964844</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="BF6">
-        <v>397.7699890136719</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="BG6">
-        <v>399.4400024414062</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="BH6">
-        <v>392.4200134277344</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="BI6">
-        <v>395.9299926757812</v>
+        <v>396.4500122070312</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -7718,184 +8079,184 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>52.7977294921875</v>
+        <v>51.58330154418945</v>
       </c>
       <c r="C7">
-        <v>51.58330154418945</v>
+        <v>51.76248168945312</v>
       </c>
       <c r="D7">
-        <v>51.76248168945312</v>
+        <v>51.99142837524414</v>
       </c>
       <c r="E7">
-        <v>51.99142837524414</v>
+        <v>50.85663604736328</v>
       </c>
       <c r="F7">
-        <v>50.85663604736328</v>
+        <v>50.97608947753906</v>
       </c>
       <c r="G7">
-        <v>50.97608947753906</v>
+        <v>49.76166152954102</v>
       </c>
       <c r="H7">
-        <v>49.76166152954102</v>
+        <v>48.86577224731445</v>
       </c>
       <c r="I7">
-        <v>48.86577224731445</v>
+        <v>48.34814834594727</v>
       </c>
       <c r="J7">
-        <v>48.34814834594727</v>
+        <v>47.72102355957031</v>
       </c>
       <c r="K7">
-        <v>47.72102355957031</v>
+        <v>48.68659591674805</v>
       </c>
       <c r="L7">
-        <v>48.68659591674805</v>
+        <v>48.58705139160156</v>
       </c>
       <c r="M7">
-        <v>48.58705139160156</v>
+        <v>51.44394302368164</v>
       </c>
       <c r="N7">
-        <v>51.44394302368164</v>
+        <v>53.34521865844727</v>
       </c>
       <c r="O7">
-        <v>53.34521865844727</v>
+        <v>52.06110763549805</v>
       </c>
       <c r="P7">
-        <v>52.06110763549805</v>
+        <v>52.64841461181641</v>
       </c>
       <c r="Q7">
-        <v>52.64841461181641</v>
+        <v>54.55964660644531</v>
       </c>
       <c r="R7">
-        <v>54.55964660644531</v>
+        <v>54.32073974609375</v>
       </c>
       <c r="S7">
-        <v>54.32073974609375</v>
+        <v>53.52439498901367</v>
       </c>
       <c r="T7">
-        <v>53.52439498901367</v>
+        <v>53.40494537353516</v>
       </c>
       <c r="U7">
-        <v>53.40494537353516</v>
+        <v>54.60941696166992</v>
       </c>
       <c r="V7">
-        <v>54.60941696166992</v>
+        <v>54.93790817260742</v>
       </c>
       <c r="W7">
-        <v>54.93790817260742</v>
+        <v>56.24192428588867</v>
       </c>
       <c r="X7">
-        <v>56.24192428588867</v>
+        <v>57.23735809326172</v>
       </c>
       <c r="Y7">
-        <v>57.23735809326172</v>
+        <v>57.33689880371094</v>
       </c>
       <c r="Z7">
-        <v>57.33689880371094</v>
+        <v>57.03827285766602</v>
       </c>
       <c r="AA7">
-        <v>57.03827285766602</v>
+        <v>54.67909622192383</v>
       </c>
       <c r="AB7">
-        <v>54.67909622192383</v>
+        <v>53.68366622924805</v>
       </c>
       <c r="AC7">
-        <v>53.68366622924805</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="AD7">
-        <v>55.77407073974609</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="AE7">
-        <v>55.69443893432617</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="AF7">
-        <v>56.80932235717773</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="AG7">
-        <v>55.21663284301758</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="AH7">
-        <v>54.8383674621582</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="AI7">
-        <v>53.56421279907227</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="AJ7">
-        <v>55.78402709960938</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="AK7">
-        <v>55.65462112426758</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="AL7">
-        <v>58.38210678100586</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="AM7">
-        <v>58.79023361206055</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="AN7">
-        <v>58.28256225585938</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="AO7">
-        <v>57.43644714355469</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="AP7">
-        <v>58.09342956542969</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="AQ7">
-        <v>58.77032470703125</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="AR7">
-        <v>59.52685165405273</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="AS7">
-        <v>59.81552886962891</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="AT7">
-        <v>61.23899841308594</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="AU7">
+        <v>59.8354377746582</v>
+      </c>
+      <c r="AV7">
+        <v>58.1431999206543</v>
+      </c>
+      <c r="AW7">
+        <v>58.35224151611328</v>
+      </c>
+      <c r="AX7">
+        <v>58.89972686767578</v>
+      </c>
+      <c r="AY7">
+        <v>58.83004760742188</v>
+      </c>
+      <c r="AZ7">
+        <v>59.90511703491211</v>
+      </c>
+      <c r="BA7">
+        <v>60.67160034179688</v>
+      </c>
+      <c r="BB7">
+        <v>60.63178253173828</v>
+      </c>
+      <c r="BC7">
+        <v>60.33315277099609</v>
+      </c>
+      <c r="BD7">
+        <v>59.7657585144043</v>
+      </c>
+      <c r="BE7">
+        <v>60.37297058105469</v>
+      </c>
+      <c r="BF7">
         <v>61.02000045776367</v>
       </c>
-      <c r="AV7">
-        <v>59.8354377746582</v>
-      </c>
-      <c r="AW7">
-        <v>58.1431999206543</v>
-      </c>
-      <c r="AX7">
-        <v>58.35224151611328</v>
-      </c>
-      <c r="AY7">
-        <v>58.89972686767578</v>
-      </c>
-      <c r="AZ7">
-        <v>58.83004760742188</v>
-      </c>
-      <c r="BA7">
-        <v>59.90511703491211</v>
-      </c>
-      <c r="BB7">
-        <v>60.67160034179688</v>
-      </c>
-      <c r="BC7">
-        <v>60.63178253173828</v>
-      </c>
-      <c r="BD7">
-        <v>60.33315277099609</v>
-      </c>
-      <c r="BE7">
-        <v>59.7657585144043</v>
-      </c>
-      <c r="BF7">
-        <v>60.37297058105469</v>
-      </c>
       <c r="BG7">
-        <v>61.02000045776367</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="BH7">
-        <v>61.15999984741211</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="BI7">
-        <v>61.45999908447266</v>
+        <v>61.77999877929688</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -7903,184 +8264,184 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>166.2874145507812</v>
+        <v>165.2628631591797</v>
       </c>
       <c r="C8">
-        <v>165.2628631591797</v>
+        <v>167.5208740234375</v>
       </c>
       <c r="D8">
-        <v>167.5208740234375</v>
+        <v>169.440673828125</v>
       </c>
       <c r="E8">
-        <v>169.440673828125</v>
+        <v>167.7496643066406</v>
       </c>
       <c r="F8">
-        <v>167.7496643066406</v>
+        <v>170.8531799316406</v>
       </c>
       <c r="G8">
-        <v>170.8531799316406</v>
+        <v>170.7437591552734</v>
       </c>
       <c r="H8">
-        <v>170.7437591552734</v>
+        <v>173.131103515625</v>
       </c>
       <c r="I8">
-        <v>173.131103515625</v>
+        <v>168.1575012207031</v>
       </c>
       <c r="J8">
-        <v>168.1575012207031</v>
+        <v>173.5787200927734</v>
       </c>
       <c r="K8">
-        <v>173.5787200927734</v>
+        <v>175.4885864257812</v>
       </c>
       <c r="L8">
-        <v>175.4885864257812</v>
+        <v>176.3937835693359</v>
       </c>
       <c r="M8">
-        <v>176.3937835693359</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="N8">
-        <v>177.8957977294922</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="O8">
-        <v>186.8184509277344</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="P8">
-        <v>188.8178405761719</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="Q8">
-        <v>187.3655395507812</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="R8">
-        <v>197.2431182861328</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="S8">
-        <v>200.3864288330078</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="T8">
-        <v>195.1243743896484</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="U8">
-        <v>200.2571258544922</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="V8">
-        <v>205.7678680419922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="W8">
-        <v>207.6976318359375</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="X8">
-        <v>211.1493225097656</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="Y8">
-        <v>210.2938537597656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="Z8">
-        <v>205.8872375488281</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="AA8">
-        <v>205.6783599853516</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="AB8">
-        <v>206.7228088378906</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="AC8">
-        <v>204.7632141113281</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="AD8">
-        <v>205.7181396484375</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="AE8">
-        <v>209.4881286621094</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="AF8">
-        <v>210.5624237060547</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="AG8">
-        <v>205.1014099121094</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="AH8">
-        <v>204.8029937744141</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="AI8">
-        <v>201.4806365966797</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="AJ8">
-        <v>204.4349517822266</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="AK8">
-        <v>202.8334503173828</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AL8">
-        <v>214.3821563720703</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AM8">
-        <v>223.1754760742188</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AN8">
-        <v>224.3890380859375</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AO8">
-        <v>231.3819274902344</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AP8">
-        <v>232.3766479492188</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AQ8">
-        <v>239.2800140380859</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AR8">
-        <v>243.4900054931641</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AS8">
-        <v>242.2899932861328</v>
+        <v>240</v>
       </c>
       <c r="AT8">
-        <v>240</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AU8">
-        <v>242.8699951171875</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AV8">
-        <v>241.9600067138672</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="AW8">
-        <v>236.8999938964844</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AX8">
-        <v>242.2299957275391</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="AY8">
-        <v>239.8099975585938</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="AZ8">
-        <v>244.0099945068359</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="BA8">
-        <v>246.5800018310547</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="BB8">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="BC8">
-        <v>256.0899963378906</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="BD8">
-        <v>254.6600036621094</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="BE8">
-        <v>255.0899963378906</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="BF8">
-        <v>259.1400146484375</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="BG8">
-        <v>260.7799987792969</v>
+        <v>258.510009765625</v>
       </c>
       <c r="BH8">
-        <v>258.510009765625</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="BI8">
-        <v>259.4700012207031</v>
+        <v>257.0599975585938</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -8088,184 +8449,924 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>33.6928596496582</v>
+        <v>32.79914855957031</v>
       </c>
       <c r="C9">
-        <v>32.79914855957031</v>
+        <v>33.96097183227539</v>
       </c>
       <c r="D9">
-        <v>33.96097183227539</v>
+        <v>33.9808349609375</v>
       </c>
       <c r="E9">
-        <v>33.9808349609375</v>
+        <v>33.09705352783203</v>
       </c>
       <c r="F9">
-        <v>33.09705352783203</v>
+        <v>33.18642044067383</v>
       </c>
       <c r="G9">
-        <v>33.18642044067383</v>
+        <v>32.77928924560547</v>
       </c>
       <c r="H9">
-        <v>32.77928924560547</v>
+        <v>32.72963714599609</v>
       </c>
       <c r="I9">
-        <v>32.72963714599609</v>
+        <v>32.34236526489258</v>
       </c>
       <c r="J9">
-        <v>32.34236526489258</v>
+        <v>31.64725685119629</v>
       </c>
       <c r="K9">
-        <v>31.64725685119629</v>
+        <v>32.13383102416992</v>
       </c>
       <c r="L9">
-        <v>32.13383102416992</v>
+        <v>32.23313140869141</v>
       </c>
       <c r="M9">
-        <v>32.23313140869141</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="N9">
-        <v>33.76237106323242</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="O9">
-        <v>34.81496429443359</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="P9">
-        <v>33.05733489990234</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="Q9">
-        <v>33.20628356933594</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="R9">
-        <v>34.42768478393555</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="S9">
-        <v>34.28866577148438</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="T9">
-        <v>34.03048324584961</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="U9">
-        <v>34.04041290283203</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="V9">
-        <v>34.97384262084961</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="W9">
-        <v>34.59650039672852</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="X9">
-        <v>35.52000045776367</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="Y9">
-        <v>36.18000030517578</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="Z9">
-        <v>36.41999816894531</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="AA9">
-        <v>36.15000152587891</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="AB9">
-        <v>34.7400016784668</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="AC9">
-        <v>34.93000030517578</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="AD9">
-        <v>36.70000076293945</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="AE9">
-        <v>36.33000183105469</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="AF9">
-        <v>37.31999969482422</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="AG9">
-        <v>36.86999893188477</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="AH9">
-        <v>35.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="AI9">
-        <v>34.65999984741211</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="AJ9">
-        <v>36.52999877929688</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="AK9">
-        <v>37.63000106811523</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AL9">
-        <v>41.02000045776367</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AM9">
-        <v>40.61999893188477</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AN9">
-        <v>39.97000122070312</v>
+        <v>40</v>
       </c>
       <c r="AO9">
-        <v>40</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AP9">
-        <v>40.47000122070312</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AQ9">
-        <v>41.58000183105469</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AR9">
-        <v>42.36999893188477</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AS9">
-        <v>43.45000076293945</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AT9">
-        <v>44.38999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AU9">
-        <v>43.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AV9">
-        <v>42.95999908447266</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="AW9">
-        <v>41.34999847412109</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AX9">
-        <v>41.18999862670898</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="AY9">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="AZ9">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="BA9">
-        <v>43.15000152587891</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="BB9">
-        <v>44.29999923706055</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="BC9">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="BD9">
-        <v>44.18000030517578</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="BE9">
-        <v>42.77000045776367</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="BF9">
-        <v>43.54999923706055</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="BG9">
-        <v>44.84000015258789</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="BH9">
-        <v>44.52999877929688</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="BI9">
-        <v>44.72999954223633</v>
+        <v>45.02999877929688</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>210.4545135498047</v>
+      </c>
+      <c r="C10">
+        <v>208.4167785644531</v>
+      </c>
+      <c r="D10">
+        <v>199.81640625</v>
+      </c>
+      <c r="E10">
+        <v>198.7775726318359</v>
+      </c>
+      <c r="F10">
+        <v>195.5212249755859</v>
+      </c>
+      <c r="G10">
+        <v>192.3148040771484</v>
+      </c>
+      <c r="H10">
+        <v>194.7520751953125</v>
+      </c>
+      <c r="I10">
+        <v>199.8663482666016</v>
+      </c>
+      <c r="J10">
+        <v>197.3591613769531</v>
+      </c>
+      <c r="K10">
+        <v>194.6122436523438</v>
+      </c>
+      <c r="L10">
+        <v>195.3314361572266</v>
+      </c>
+      <c r="M10">
+        <v>196.7098846435547</v>
+      </c>
+      <c r="N10">
+        <v>203.891845703125</v>
+      </c>
+      <c r="O10">
+        <v>202.5533447265625</v>
+      </c>
+      <c r="P10">
+        <v>210.7242126464844</v>
+      </c>
+      <c r="Q10">
+        <v>203.3025054931641</v>
+      </c>
+      <c r="R10">
+        <v>211.5632781982422</v>
+      </c>
+      <c r="S10">
+        <v>212.2624816894531</v>
+      </c>
+      <c r="T10">
+        <v>207.1681823730469</v>
+      </c>
+      <c r="U10">
+        <v>202.5833129882812</v>
+      </c>
+      <c r="V10">
+        <v>203.0527954101562</v>
+      </c>
+      <c r="W10">
+        <v>207.0583038330078</v>
+      </c>
+      <c r="X10">
+        <v>211.8229827880859</v>
+      </c>
+      <c r="Y10">
+        <v>208.5266571044922</v>
+      </c>
+      <c r="Z10">
+        <v>206.6088104248047</v>
+      </c>
+      <c r="AA10">
+        <v>196.2903594970703</v>
+      </c>
+      <c r="AB10">
+        <v>196.789794921875</v>
+      </c>
+      <c r="AC10">
+        <v>189.7976226806641</v>
+      </c>
+      <c r="AD10">
+        <v>194.8219909667969</v>
+      </c>
+      <c r="AE10">
+        <v>200.5256195068359</v>
+      </c>
+      <c r="AF10">
+        <v>206.4090423583984</v>
+      </c>
+      <c r="AG10">
+        <v>211.7031097412109</v>
+      </c>
+      <c r="AH10">
+        <v>218.9749755859375</v>
+      </c>
+      <c r="AI10">
+        <v>218.7452392578125</v>
+      </c>
+      <c r="AJ10">
+        <v>223.7096862792969</v>
+      </c>
+      <c r="AK10">
+        <v>217.3068389892578</v>
+      </c>
+      <c r="AL10">
+        <v>217.2568969726562</v>
+      </c>
+      <c r="AM10">
+        <v>223.8395233154297</v>
+      </c>
+      <c r="AN10">
+        <v>225.0481872558594</v>
+      </c>
+      <c r="AO10">
+        <v>224.9083404541016</v>
+      </c>
+      <c r="AP10">
+        <v>224.7584991455078</v>
+      </c>
+      <c r="AQ10">
+        <v>219.4944000244141</v>
+      </c>
+      <c r="AR10">
+        <v>217.3168334960938</v>
+      </c>
+      <c r="AS10">
+        <v>216.6076354980469</v>
+      </c>
+      <c r="AT10">
+        <v>214.4800109863281</v>
+      </c>
+      <c r="AU10">
+        <v>208.2469787597656</v>
+      </c>
+      <c r="AV10">
+        <v>212.8118743896484</v>
+      </c>
+      <c r="AW10">
+        <v>209.4256591796875</v>
+      </c>
+      <c r="AX10">
+        <v>227.7251739501953</v>
+      </c>
+      <c r="AY10">
+        <v>217.3068389892578</v>
+      </c>
+      <c r="AZ10">
+        <v>220.5332336425781</v>
+      </c>
+      <c r="BA10">
+        <v>217.1969757080078</v>
+      </c>
+      <c r="BB10">
+        <v>224.1591796875</v>
+      </c>
+      <c r="BC10">
+        <v>228.1946563720703</v>
+      </c>
+      <c r="BD10">
+        <v>230.1025238037109</v>
+      </c>
+      <c r="BE10">
+        <v>225.4776916503906</v>
+      </c>
+      <c r="BF10">
+        <v>223.4199981689453</v>
+      </c>
+      <c r="BG10">
+        <v>218.3600006103516</v>
+      </c>
+      <c r="BH10">
+        <v>218.2899932861328</v>
+      </c>
+      <c r="BI10">
+        <v>210.9600067138672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>306.7611694335938</v>
+      </c>
+      <c r="C11">
+        <v>309.5516357421875</v>
+      </c>
+      <c r="D11">
+        <v>315.8800048828125</v>
+      </c>
+      <c r="E11">
+        <v>319.6471252441406</v>
+      </c>
+      <c r="F11">
+        <v>317.2054748535156</v>
+      </c>
+      <c r="G11">
+        <v>326.2545166015625</v>
+      </c>
+      <c r="H11">
+        <v>330.7491760253906</v>
+      </c>
+      <c r="I11">
+        <v>328.9951477050781</v>
+      </c>
+      <c r="J11">
+        <v>333.4798278808594</v>
+      </c>
+      <c r="K11">
+        <v>341.1436157226562</v>
+      </c>
+      <c r="L11">
+        <v>338.0143432617188</v>
+      </c>
+      <c r="M11">
+        <v>342.5588073730469</v>
+      </c>
+      <c r="N11">
+        <v>336.7885131835938</v>
+      </c>
+      <c r="O11">
+        <v>336.3301086425781</v>
+      </c>
+      <c r="P11">
+        <v>337.7651977539062</v>
+      </c>
+      <c r="Q11">
+        <v>340.3463745117188</v>
+      </c>
+      <c r="R11">
+        <v>335.6822814941406</v>
+      </c>
+      <c r="S11">
+        <v>328.0683288574219</v>
+      </c>
+      <c r="T11">
+        <v>336.6689453125</v>
+      </c>
+      <c r="U11">
+        <v>367.7227783203125</v>
+      </c>
+      <c r="V11">
+        <v>367.244384765625</v>
+      </c>
+      <c r="W11">
+        <v>368.3705444335938</v>
+      </c>
+      <c r="X11">
+        <v>370.8121643066406</v>
+      </c>
+      <c r="Y11">
+        <v>375.0875549316406</v>
+      </c>
+      <c r="Z11">
+        <v>385.9404907226562</v>
+      </c>
+      <c r="AA11">
+        <v>389.0199584960938</v>
+      </c>
+      <c r="AB11">
+        <v>395.8665161132812</v>
+      </c>
+      <c r="AC11">
+        <v>387.6845092773438</v>
+      </c>
+      <c r="AD11">
+        <v>374.7088623046875</v>
+      </c>
+      <c r="AE11">
+        <v>373.0844116210938</v>
+      </c>
+      <c r="AF11">
+        <v>372.5462646484375</v>
+      </c>
+      <c r="AG11">
+        <v>375.8648986816406</v>
+      </c>
+      <c r="AH11">
+        <v>381.1468811035156</v>
+      </c>
+      <c r="AI11">
+        <v>384.6847534179688</v>
+      </c>
+      <c r="AJ11">
+        <v>383.0005187988281</v>
+      </c>
+      <c r="AK11">
+        <v>374.3401184082031</v>
+      </c>
+      <c r="AL11">
+        <v>374.3301391601562</v>
+      </c>
+      <c r="AM11">
+        <v>368.8987426757812</v>
+      </c>
+      <c r="AN11">
+        <v>368.7392883300781</v>
+      </c>
+      <c r="AO11">
+        <v>369.0980224609375</v>
+      </c>
+      <c r="AP11">
+        <v>363.2680053710938</v>
+      </c>
+      <c r="AQ11">
+        <v>366.6763305664062</v>
+      </c>
+      <c r="AR11">
+        <v>360.9857788085938</v>
+      </c>
+      <c r="AS11">
+        <v>363.248046875</v>
+      </c>
+      <c r="AT11">
+        <v>362.3411254882812</v>
+      </c>
+      <c r="AU11">
+        <v>369.2873840332031</v>
+      </c>
+      <c r="AV11">
+        <v>368.4004516601562</v>
+      </c>
+      <c r="AW11">
+        <v>369.8853454589844</v>
+      </c>
+      <c r="AX11">
+        <v>368.071533203125</v>
+      </c>
+      <c r="AY11">
+        <v>368.6396179199219</v>
+      </c>
+      <c r="AZ11">
+        <v>364.6831359863281</v>
+      </c>
+      <c r="BA11">
+        <v>362.6799926757812</v>
+      </c>
+      <c r="BB11">
+        <v>364.9322814941406</v>
+      </c>
+      <c r="BC11">
+        <v>373.0644836425781</v>
+      </c>
+      <c r="BD11">
+        <v>368.0914916992188</v>
+      </c>
+      <c r="BE11">
+        <v>364.4140625</v>
+      </c>
+      <c r="BF11">
+        <v>365.6000061035156</v>
+      </c>
+      <c r="BG11">
+        <v>367.5599975585938</v>
+      </c>
+      <c r="BH11">
+        <v>375.2000122070312</v>
+      </c>
+      <c r="BI11">
+        <v>378.0499877929688</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>367.2215881347656</v>
+      </c>
+      <c r="C12">
+        <v>348.5537109375</v>
+      </c>
+      <c r="D12">
+        <v>345.8554382324219</v>
+      </c>
+      <c r="E12">
+        <v>344.816162109375</v>
+      </c>
+      <c r="F12">
+        <v>341.9679870605469</v>
+      </c>
+      <c r="G12">
+        <v>334.4728698730469</v>
+      </c>
+      <c r="H12">
+        <v>351.0520935058594</v>
+      </c>
+      <c r="I12">
+        <v>353.1007385253906</v>
+      </c>
+      <c r="J12">
+        <v>357.6578063964844</v>
+      </c>
+      <c r="K12">
+        <v>355.9489135742188</v>
+      </c>
+      <c r="L12">
+        <v>364.6632385253906</v>
+      </c>
+      <c r="M12">
+        <v>363.3840942382812</v>
+      </c>
+      <c r="N12">
+        <v>358.4772644042969</v>
+      </c>
+      <c r="O12">
+        <v>356.0088500976562</v>
+      </c>
+      <c r="P12">
+        <v>354.7996520996094</v>
+      </c>
+      <c r="Q12">
+        <v>350.4425048828125</v>
+      </c>
+      <c r="R12">
+        <v>357.09814453125</v>
+      </c>
+      <c r="S12">
+        <v>369.9697875976562</v>
+      </c>
+      <c r="T12">
+        <v>353.5804443359375</v>
+      </c>
+      <c r="U12">
+        <v>345.8954467773438</v>
+      </c>
+      <c r="V12">
+        <v>351.1420288085938</v>
+      </c>
+      <c r="W12">
+        <v>345.9653930664062</v>
+      </c>
+      <c r="X12">
+        <v>341.6881713867188</v>
+      </c>
+      <c r="Y12">
+        <v>318.1334533691406</v>
+      </c>
+      <c r="Z12">
+        <v>318.8829650878906</v>
+      </c>
+      <c r="AA12">
+        <v>326.3581237792969</v>
+      </c>
+      <c r="AB12">
+        <v>332.3842163085938</v>
+      </c>
+      <c r="AC12">
+        <v>335.5421752929688</v>
+      </c>
+      <c r="AD12">
+        <v>333.4635009765625</v>
+      </c>
+      <c r="AE12">
+        <v>356.4186096191406</v>
+      </c>
+      <c r="AF12">
+        <v>372.2283325195312</v>
+      </c>
+      <c r="AG12">
+        <v>375.1064758300781</v>
+      </c>
+      <c r="AH12">
+        <v>359.8963623046875</v>
+      </c>
+      <c r="AI12">
+        <v>356.3886108398438</v>
+      </c>
+      <c r="AJ12">
+        <v>353.2406616210938</v>
+      </c>
+      <c r="AK12">
+        <v>355.609130859375</v>
+      </c>
+      <c r="AL12">
+        <v>342.7774658203125</v>
+      </c>
+      <c r="AM12">
+        <v>342.1478576660156</v>
+      </c>
+      <c r="AN12">
+        <v>343.7168579101562</v>
+      </c>
+      <c r="AO12">
+        <v>343.3171081542969</v>
+      </c>
+      <c r="AP12">
+        <v>341.2284851074219</v>
+      </c>
+      <c r="AQ12">
+        <v>341.0585632324219</v>
+      </c>
+      <c r="AR12">
+        <v>341.4783325195312</v>
+      </c>
+      <c r="AS12">
+        <v>337.9805908203125</v>
+      </c>
+      <c r="AT12">
+        <v>341.5282592773438</v>
+      </c>
+      <c r="AU12">
+        <v>344.3664245605469</v>
+      </c>
+      <c r="AV12">
+        <v>343.1172485351562</v>
+      </c>
+      <c r="AW12">
+        <v>338.8800048828125</v>
+      </c>
+      <c r="AX12">
+        <v>337.4908752441406</v>
+      </c>
+      <c r="AY12">
+        <v>342.6575317382812</v>
+      </c>
+      <c r="AZ12">
+        <v>335.1923828125</v>
+      </c>
+      <c r="BA12">
+        <v>331.8145751953125</v>
+      </c>
+      <c r="BB12">
+        <v>333.5634460449219</v>
+      </c>
+      <c r="BC12">
+        <v>338.8599853515625</v>
+      </c>
+      <c r="BD12">
+        <v>335.3099975585938</v>
+      </c>
+      <c r="BE12">
+        <v>335.3800048828125</v>
+      </c>
+      <c r="BF12">
+        <v>328.3800048828125</v>
+      </c>
+      <c r="BG12">
+        <v>330.3900146484375</v>
+      </c>
+      <c r="BH12">
+        <v>335.4500122070312</v>
+      </c>
+      <c r="BI12">
+        <v>345.7099914550781</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>61.02000045776367</v>
+      </c>
+      <c r="C13">
+        <v>63.68000030517578</v>
+      </c>
+      <c r="D13">
+        <v>63.13999938964844</v>
+      </c>
+      <c r="E13">
+        <v>62.97000122070312</v>
+      </c>
+      <c r="F13">
+        <v>64.76999664306641</v>
+      </c>
+      <c r="G13">
+        <v>65.73000335693359</v>
+      </c>
+      <c r="H13">
+        <v>64.54000091552734</v>
+      </c>
+      <c r="I13">
+        <v>64.19000244140625</v>
+      </c>
+      <c r="J13">
+        <v>68.34999847412109</v>
+      </c>
+      <c r="K13">
+        <v>67.86000061035156</v>
+      </c>
+      <c r="L13">
+        <v>66.05000305175781</v>
+      </c>
+      <c r="M13">
+        <v>66.12000274658203</v>
+      </c>
+      <c r="N13">
+        <v>67.08999633789062</v>
+      </c>
+      <c r="O13">
+        <v>67.59999847412109</v>
+      </c>
+      <c r="P13">
+        <v>67.34999847412109</v>
+      </c>
+      <c r="Q13">
+        <v>68.29000091552734</v>
+      </c>
+      <c r="R13">
+        <v>68.72000122070312</v>
+      </c>
+      <c r="S13">
+        <v>66.61000061035156</v>
+      </c>
+      <c r="T13">
+        <v>63.88999938964844</v>
+      </c>
+      <c r="U13">
+        <v>66.44000244140625</v>
+      </c>
+      <c r="V13">
+        <v>65.83999633789062</v>
+      </c>
+      <c r="W13">
+        <v>67.58999633789062</v>
+      </c>
+      <c r="X13">
+        <v>65.88999938964844</v>
+      </c>
+      <c r="Y13">
+        <v>63.7400016784668</v>
+      </c>
+      <c r="Z13">
+        <v>63.40999984741211</v>
+      </c>
+      <c r="AA13">
+        <v>64.08000183105469</v>
+      </c>
+      <c r="AB13">
+        <v>63.90999984741211</v>
+      </c>
+      <c r="AC13">
+        <v>61.81999969482422</v>
+      </c>
+      <c r="AD13">
+        <v>60.84000015258789</v>
+      </c>
+      <c r="AE13">
+        <v>62.22000122070312</v>
+      </c>
+      <c r="AF13">
+        <v>63.7599983215332</v>
+      </c>
+      <c r="AG13">
+        <v>64.06999969482422</v>
+      </c>
+      <c r="AH13">
+        <v>66.98999786376953</v>
+      </c>
+      <c r="AI13">
+        <v>64.19999694824219</v>
+      </c>
+      <c r="AJ13">
+        <v>65.76999664306641</v>
+      </c>
+      <c r="AK13">
+        <v>66.56999969482422</v>
+      </c>
+      <c r="AL13">
+        <v>64.87999725341797</v>
+      </c>
+      <c r="AM13">
+        <v>67.06999969482422</v>
+      </c>
+      <c r="AN13">
+        <v>66.04000091552734</v>
+      </c>
+      <c r="AO13">
+        <v>67.47000122070312</v>
+      </c>
+      <c r="AP13">
+        <v>64.41000366210938</v>
+      </c>
+      <c r="AQ13">
+        <v>65.22000122070312</v>
+      </c>
+      <c r="AR13">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="AS13">
+        <v>64.13999938964844</v>
+      </c>
+      <c r="AT13">
+        <v>65.01999664306641</v>
+      </c>
+      <c r="AU13">
+        <v>65.65000152587891</v>
+      </c>
+      <c r="AV13">
+        <v>65</v>
+      </c>
+      <c r="AW13">
+        <v>65.47000122070312</v>
+      </c>
+      <c r="AX13">
+        <v>65.33000183105469</v>
+      </c>
+      <c r="AY13">
+        <v>64.75</v>
+      </c>
+      <c r="AZ13">
+        <v>64.33999633789062</v>
+      </c>
+      <c r="BA13">
+        <v>65.23000335693359</v>
+      </c>
+      <c r="BB13">
+        <v>67.33999633789062</v>
+      </c>
+      <c r="BC13">
+        <v>68.01999664306641</v>
+      </c>
+      <c r="BD13">
+        <v>67.04000091552734</v>
+      </c>
+      <c r="BE13">
+        <v>64.58000183105469</v>
+      </c>
+      <c r="BF13">
+        <v>64.05999755859375</v>
+      </c>
+      <c r="BG13">
+        <v>65.40000152587891</v>
+      </c>
+      <c r="BH13">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="BI13">
+        <v>69.41000366210938</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="246">
   <si>
     <t>DELL</t>
   </si>
@@ -276,6 +276,9 @@
     <t>2026-09-11</t>
   </si>
   <si>
+    <t>2026-09-16</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -351,6 +354,18 @@
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>Allstate</t>
+  </si>
+  <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
     <t>TGT</t>
   </si>
   <si>
@@ -360,12 +375,6 @@
     <t>Consumer Staples</t>
   </si>
   <si>
-    <t>ALL</t>
-  </si>
-  <si>
-    <t>Allstate</t>
-  </si>
-  <si>
     <t>AMZN</t>
   </si>
   <si>
@@ -375,12 +384,6 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
     <t>INCY</t>
   </si>
   <si>
@@ -393,16 +396,82 @@
     <t>HP Inc.</t>
   </si>
   <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
+    <t>BIIB</t>
+  </si>
+  <si>
+    <t>Biogen</t>
+  </si>
+  <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
     <t>DLTR</t>
   </si>
   <si>
     <t>Dollar Tree</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
   </si>
   <si>
     <t>SMCI</t>
@@ -411,58 +480,16 @@
     <t>Supermicro</t>
   </si>
   <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
-    <t>BIIB</t>
-  </si>
-  <si>
-    <t>Biogen</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>Devon Energy</t>
+  </si>
+  <si>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>News Corp (Class A)</t>
   </si>
   <si>
     <t>MS</t>
@@ -471,34 +498,10 @@
     <t>Morgan Stanley</t>
   </si>
   <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>News Corp (Class A)</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
-    <t>REGN</t>
-  </si>
-  <si>
-    <t>Regeneron Pharmaceuticals</t>
-  </si>
-  <si>
-    <t>BBY</t>
-  </si>
-  <si>
-    <t>Best Buy</t>
+    <t>FFIV</t>
+  </si>
+  <si>
+    <t>F5, Inc.</t>
   </si>
   <si>
     <t>PRU</t>
@@ -585,7 +588,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-16 00:26 UTC · данные на 2026-09-14 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-17 00:37 UTC · данные на 2026-09-16 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -666,7 +669,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-16 00:26 UTC</t>
+    <t>2026-09-17 00:37 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1178,9 +1181,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$18</c:f>
+              <c:f>Капитал!$A$5:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1222,16 +1225,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2026-09-14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2026-09-16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$18</c:f>
+              <c:f>Капитал!$D$5:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1272,6 +1278,9 @@
                   <c:v>10216.05</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>10163.98</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -1297,9 +1306,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$18</c:f>
+              <c:f>Капитал!$A$5:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1341,16 +1350,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2026-09-14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2026-09-16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$18</c:f>
+              <c:f>Капитал!$F$5:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1392,6 +1404,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>9966.08</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1531,9 +1546,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$18</c:f>
+              <c:f>Капитал!$A$5:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1575,16 +1590,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2026-09-14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2026-09-16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$18</c:f>
+              <c:f>Капитал!$D$5:$D$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1625,6 +1643,9 @@
                   <c:v>10216.05</c:v>
                 </c:pt>
                 <c:pt idx="13">
+                  <c:v>10163.98</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -1650,9 +1671,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$18</c:f>
+              <c:f>Капитал!$A$5:$A$19</c:f>
               <c:strCache>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1694,16 +1715,19 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>2026-09-14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2026-09-16</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$18</c:f>
+              <c:f>Капитал!$F$5:$F$19</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="14"/>
+                <c:ptCount val="15"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1745,6 +1769,9 @@
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>9966.08</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2239,12 +2266,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2252,13 +2279,13 @@
         <v>74</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2277,27 +2304,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>2.881440547102145</v>
+        <v>2.773364125231443</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H9" s="7">
         <v>13</v>
@@ -2305,7 +2332,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2334,7 +2361,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2342,7 +2369,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2350,23 +2377,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="11">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2374,55 +2401,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C25" s="12">
-        <v>0.1116230737431509</v>
+        <v>0.1076891784535971</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C26" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2431,12 +2458,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2611,11 +2638,11 @@
         <v>0.20574673193473192</v>
       </c>
       <c r="L5" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
@@ -2662,11 +2689,11 @@
         <v>-0.0023453865133649322</v>
       </c>
       <c r="L6" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
@@ -2713,11 +2740,11 @@
         <v>0.001157858695424527</v>
       </c>
       <c r="L7" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
@@ -2764,11 +2791,11 @@
         <v>-0.07694846931544182</v>
       </c>
       <c r="L8" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
@@ -2815,11 +2842,11 @@
         <v>0.06333640885022687</v>
       </c>
       <c r="L9" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
@@ -2866,11 +2893,11 @@
         <v>0.04063182043921025</v>
       </c>
       <c r="L10" s="11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
@@ -2917,11 +2944,11 @@
         <v>0.027097931394638883</v>
       </c>
       <c r="L11" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
@@ -2968,11 +2995,11 @@
         <v>0.020460374570953403</v>
       </c>
       <c r="L12" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
@@ -3019,11 +3046,11 @@
         <v>0.030391348943966064</v>
       </c>
       <c r="L13" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
@@ -3070,11 +3097,11 @@
         <v>-0.001824598914652231</v>
       </c>
       <c r="L14" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="11">
         <f>MAX(0,21-L14)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N14" s="20">
         <v>0.6809721702367264</v>
@@ -3121,11 +3148,11 @@
         <v>-0.013417568245354424</v>
       </c>
       <c r="L15" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" s="11">
         <f>MAX(0,21-L15)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N15" s="20">
         <v>0.8197914702434592</v>
@@ -3172,11 +3199,11 @@
         <v>0.018953362974839495</v>
       </c>
       <c r="L16" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" s="11">
         <f>MAX(0,21-L16)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N16" s="20">
         <v>0.776423257523575</v>
@@ -3223,11 +3250,11 @@
         <v>0.03068356896480827</v>
       </c>
       <c r="L17" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" s="11">
         <f>MAX(0,21-L17)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N17" s="20">
         <v>0.7994794227521653</v>
@@ -3609,7 +3636,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3932,6 +3959,25 @@
       <c r="F18" s="10">
         <v>9966.08</v>
       </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" s="10">
+        <v>3768.96</v>
+      </c>
+      <c r="C19" s="10">
+        <v>6395.02</v>
+      </c>
+      <c r="D19" s="10">
+        <f>B19+C19</f>
+        <v>10163.98</v>
+      </c>
+      <c r="E19" s="11">
+        <v>13</v>
+      </c>
+      <c r="F19" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3960,12 +4006,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -3982,52 +4028,52 @@
         <v>17</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -4044,10 +4090,10 @@
         <v>42</v>
       </c>
       <c r="E5" s="10">
-        <v>382.9500122070312</v>
+        <v>397.0400085449219</v>
       </c>
       <c r="F5" s="17">
-        <v>1.01228894706075</v>
+        <v>1.01764041912561</v>
       </c>
       <c r="G5" s="20">
         <v>0.6555418499989493</v>
@@ -4059,16 +4105,16 @@
         <v>2.861941581666567</v>
       </c>
       <c r="J5" s="20">
-        <v>2.22325647473339</v>
+        <v>2.288032401453355</v>
       </c>
       <c r="K5" s="20">
-        <v>0.6103768664990419</v>
+        <v>0.6078226360490273</v>
       </c>
       <c r="L5" s="20">
-        <v>0.2191803760071019</v>
+        <v>0.1995744490045689</v>
       </c>
       <c r="M5" s="20">
-        <v>-0.4486341382831623</v>
+        <v>-0.6061146717453501</v>
       </c>
       <c r="N5" s="20">
         <v>16.28786</v>
@@ -4083,13 +4129,13 @@
         <v>0.517</v>
       </c>
       <c r="R5" s="12">
-        <v>0.6750788999361592</v>
+        <v>0.7219249305616033</v>
       </c>
       <c r="S5" s="11">
-        <v>70.85054655531712</v>
+        <v>75.74333366737011</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -4106,10 +4152,10 @@
         <v>42</v>
       </c>
       <c r="E6" s="10">
-        <v>396.4500122070312</v>
+        <v>410.8399963378906</v>
       </c>
       <c r="F6" s="17">
-        <v>0.9937771760734965</v>
+        <v>0.9983420839881402</v>
       </c>
       <c r="G6" s="20">
         <v>0.6866590119647646</v>
@@ -4121,16 +4167,16 @@
         <v>2.437187840999147</v>
       </c>
       <c r="J6" s="20">
-        <v>2.213632162250537</v>
+        <v>2.263230960013805</v>
       </c>
       <c r="K6" s="20">
-        <v>0.7778806600509907</v>
+        <v>0.7750429067476208</v>
       </c>
       <c r="L6" s="20">
-        <v>0.3043746566883123</v>
+        <v>0.2750647875044709</v>
       </c>
       <c r="M6" s="20">
-        <v>-0.711684774440313</v>
+        <v>-0.8143798852765898</v>
       </c>
       <c r="N6" s="20">
         <v>13.7380295</v>
@@ -4145,13 +4191,13 @@
         <v>0.537</v>
       </c>
       <c r="R6" s="12">
-        <v>0.7643150477120724</v>
+        <v>0.8063125517704235</v>
       </c>
       <c r="S6" s="11">
-        <v>74.93452245635656</v>
+        <v>79.6885292911436</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -4159,61 +4205,61 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="10">
-        <v>924.030029296875</v>
+        <v>543.510009765625</v>
       </c>
       <c r="F7" s="17">
-        <v>0.9551442181031129</v>
+        <v>0.9350270020838893</v>
       </c>
       <c r="G7" s="20">
-        <v>-0.495023614230421</v>
+        <v>-0.1521673872440041</v>
       </c>
       <c r="H7" s="20">
-        <v>1.812724042922127</v>
+        <v>-0.8490211958234019</v>
       </c>
       <c r="I7" s="20">
-        <v>3.960347878543698</v>
+        <v>2.18194679071571</v>
       </c>
       <c r="J7" s="20">
-        <v>1.610354219383285</v>
+        <v>2.755754922011613</v>
       </c>
       <c r="K7" s="20">
-        <v>0.483715047300809</v>
+        <v>1.603918692988181</v>
       </c>
       <c r="L7" s="20">
-        <v>-3.375332568109985</v>
+        <v>-2.880273852553483</v>
       </c>
       <c r="M7" s="20">
-        <v>0.2443214567274382</v>
+        <v>0.4210694429890847</v>
       </c>
       <c r="N7" s="20">
-        <v>22.024843</v>
+        <v>33.00116</v>
       </c>
       <c r="O7" s="20">
-        <v>10.93157</v>
+        <v>-256.4602</v>
       </c>
       <c r="P7" s="12">
-        <v>0.66638</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="12">
-        <v>3.457</v>
+        <v>0.577</v>
       </c>
       <c r="R7" s="12">
-        <v>1.16966743669018</v>
+        <v>2.48851808062455</v>
       </c>
       <c r="S7" s="11">
-        <v>46.41436604092988</v>
+        <v>60.57587541036946</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -4221,61 +4267,61 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="10">
-        <v>534.280029296875</v>
+        <v>927.5999755859375</v>
       </c>
       <c r="F8" s="17">
-        <v>0.9390396418388857</v>
+        <v>0.8985111363697914</v>
       </c>
       <c r="G8" s="20">
-        <v>-0.1521673872440041</v>
+        <v>-0.495023614230421</v>
       </c>
       <c r="H8" s="20">
-        <v>-0.8490211958234019</v>
+        <v>1.812724042922127</v>
       </c>
       <c r="I8" s="20">
-        <v>2.18194679071571</v>
+        <v>3.960347878543698</v>
       </c>
       <c r="J8" s="20">
-        <v>2.749859706342906</v>
+        <v>1.504674396622836</v>
       </c>
       <c r="K8" s="20">
-        <v>1.608161809570836</v>
+        <v>0.4813752091318809</v>
       </c>
       <c r="L8" s="20">
-        <v>-2.845436735620273</v>
+        <v>-3.347756939201326</v>
       </c>
       <c r="M8" s="20">
-        <v>0.4608419861102997</v>
+        <v>-0.08446469401550172</v>
       </c>
       <c r="N8" s="20">
-        <v>33.00116</v>
+        <v>22.024843</v>
       </c>
       <c r="O8" s="20">
-        <v>-256.4602</v>
+        <v>10.93157</v>
       </c>
       <c r="P8" s="12">
-        <v>0</v>
+        <v>0.66638</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.577</v>
+        <v>3.457</v>
       </c>
       <c r="R8" s="12">
-        <v>2.540553811407082</v>
+        <v>1.100797603195555</v>
       </c>
       <c r="S8" s="11">
-        <v>59.27403744918696</v>
+        <v>46.90911682891834</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -4283,61 +4329,61 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E9" s="10">
-        <v>1551.989990234375</v>
+        <v>67.66000366210938</v>
       </c>
       <c r="F9" s="17">
-        <v>0.92078027148921</v>
+        <v>0.8854219201003662</v>
       </c>
       <c r="G9" s="20">
-        <v>-0.4801631684214276</v>
+        <v>1.282244047014282</v>
       </c>
       <c r="H9" s="20">
-        <v>2.05728233065155</v>
+        <v>-1.356970430261629</v>
       </c>
       <c r="I9" s="20">
-        <v>4.117187201861848</v>
+        <v>-0.5801056520622042</v>
       </c>
       <c r="J9" s="20">
-        <v>1.394863130104923</v>
+        <v>1.395587164196497</v>
       </c>
       <c r="K9" s="20">
-        <v>0.0871860051577696</v>
+        <v>4.198114103620362</v>
       </c>
       <c r="L9" s="20">
-        <v>-3.375332568109985</v>
+        <v>-0.06369499479731604</v>
       </c>
       <c r="M9" s="20">
-        <v>0.499055539385301</v>
+        <v>0.1389460460040365</v>
       </c>
       <c r="N9" s="20">
-        <v>22.12312</v>
+        <v>12.502541</v>
       </c>
       <c r="O9" s="20">
-        <v>15.465718</v>
+        <v>1.4542508</v>
       </c>
       <c r="P9" s="12">
-        <v>0.9164</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q9" s="12">
-        <v>3.716</v>
+        <v>0.046</v>
       </c>
       <c r="R9" s="12">
-        <v>1.345742271527757</v>
+        <v>0.9464904179870228</v>
       </c>
       <c r="S9" s="11">
-        <v>48.83790364120002</v>
+        <v>55.45609886456371</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -4345,61 +4391,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E10" s="10">
-        <v>69.41000366210938</v>
+        <v>377.9700012207031</v>
       </c>
       <c r="F10" s="17">
-        <v>0.9006741142353692</v>
+        <v>0.8650155013620733</v>
       </c>
       <c r="G10" s="20">
-        <v>1.282244047014282</v>
+        <v>1.195906561845193</v>
       </c>
       <c r="H10" s="20">
-        <v>-1.356970430261629</v>
+        <v>-0.1235890761074189</v>
       </c>
       <c r="I10" s="20">
-        <v>-0.5801056520622042</v>
+        <v>-0.3802373592559733</v>
       </c>
       <c r="J10" s="20">
-        <v>1.532770805520431</v>
+        <v>0.7788658346716076</v>
       </c>
       <c r="K10" s="20">
-        <v>4.197997932171494</v>
+        <v>3.822167839477549</v>
       </c>
       <c r="L10" s="20">
-        <v>-0.02542500209616996</v>
+        <v>0.5633054705938957</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.2133684196257324</v>
+        <v>-0.2320988880212402</v>
       </c>
       <c r="N10" s="20">
-        <v>12.502541</v>
+        <v>10.080602</v>
       </c>
       <c r="O10" s="20">
-        <v>1.4542508</v>
+        <v>2.3630478</v>
       </c>
       <c r="P10" s="12">
-        <v>-0.20358999</v>
+        <v>0.26511</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.046</v>
+        <v>0.003</v>
       </c>
       <c r="R10" s="12">
-        <v>1.014804125542404</v>
+        <v>0.2501569342848344</v>
       </c>
       <c r="S10" s="11">
-        <v>61.40478798365034</v>
+        <v>60.87771432988801</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4407,61 +4453,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E11" s="10">
-        <v>378.0499877929688</v>
+        <v>1530.89501953125</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8631958713640447</v>
+        <v>0.8533122300924563</v>
       </c>
       <c r="G11" s="20">
-        <v>1.195906561845193</v>
+        <v>-0.4801631684214276</v>
       </c>
       <c r="H11" s="20">
-        <v>-0.1235890761074189</v>
+        <v>2.05728233065155</v>
       </c>
       <c r="I11" s="20">
-        <v>-0.3802373592559733</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J11" s="20">
-        <v>0.7947370846814427</v>
+        <v>1.283614597660989</v>
       </c>
       <c r="K11" s="20">
-        <v>3.830172009219837</v>
+        <v>0.08551734608922254</v>
       </c>
       <c r="L11" s="20">
-        <v>0.5684774989845738</v>
+        <v>-3.347756939201326</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.3302467264399167</v>
+        <v>0.05470828551195824</v>
       </c>
       <c r="N11" s="20">
-        <v>10.080602</v>
+        <v>22.12312</v>
       </c>
       <c r="O11" s="20">
-        <v>2.3630478</v>
+        <v>15.465718</v>
       </c>
       <c r="P11" s="12">
-        <v>0.26511</v>
+        <v>0.9164</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.003</v>
+        <v>3.716</v>
       </c>
       <c r="R11" s="12">
-        <v>0.2593092288545</v>
+        <v>1.175710258101083</v>
       </c>
       <c r="S11" s="11">
-        <v>60.97994843730039</v>
+        <v>47.66082157617929</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4469,61 +4515,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="10">
+        <v>264.9299926757812</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0.8449014145413066</v>
+      </c>
+      <c r="G12" s="20">
+        <v>0.4728319185405508</v>
+      </c>
+      <c r="H12" s="20">
+        <v>-0.7907783719627398</v>
+      </c>
+      <c r="I12" s="20">
+        <v>2.406342473145227</v>
+      </c>
+      <c r="J12" s="20">
+        <v>2.04290033251477</v>
+      </c>
+      <c r="K12" s="20">
+        <v>0.6909166594517234</v>
+      </c>
+      <c r="L12" s="20">
+        <v>0.4787318536549871</v>
+      </c>
+      <c r="M12" s="20">
+        <v>-0.9852756088051771</v>
+      </c>
+      <c r="N12" s="20">
+        <v>14.818389</v>
+      </c>
+      <c r="O12" s="20">
+        <v>3.2861774</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0.23452999</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0.531</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0.5464015259473756</v>
+      </c>
+      <c r="S12" s="11">
+        <v>75.3235154586028</v>
+      </c>
+      <c r="T12" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="10">
-        <v>349.3900146484375</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0.8410723709429708</v>
-      </c>
-      <c r="G12" s="20">
-        <v>-0.3791628567675373</v>
-      </c>
-      <c r="H12" s="20">
-        <v>1.461933114403917</v>
-      </c>
-      <c r="I12" s="20">
-        <v>1.394253875646282</v>
-      </c>
-      <c r="J12" s="20">
-        <v>0.09775964055743695</v>
-      </c>
-      <c r="K12" s="20">
-        <v>4.197997932171494</v>
-      </c>
-      <c r="L12" s="20">
-        <v>0.04290532467272344</v>
-      </c>
-      <c r="M12" s="20">
-        <v>0.00406294729623613</v>
-      </c>
-      <c r="N12" s="20">
-        <v>16.975927</v>
-      </c>
-      <c r="O12" s="20">
-        <v>6.6508174</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0.48676</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0.242</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0.1572827577604365</v>
-      </c>
-      <c r="S12" s="11">
-        <v>55.27304228383611</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4531,22 +4577,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="10">
-        <v>345.7099914550781</v>
+        <v>344.9800109863281</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8359806889782336</v>
+        <v>0.8374014679330111</v>
       </c>
       <c r="G13" s="20">
-        <v>-0.3694515340244113</v>
+        <v>-0.3791628567675373</v>
       </c>
       <c r="H13" s="20">
         <v>1.461933114403917</v>
@@ -4555,22 +4601,22 @@
         <v>1.394253875646282</v>
       </c>
       <c r="J13" s="20">
-        <v>0.05994526779680345</v>
+        <v>0.01905145690521837</v>
       </c>
       <c r="K13" s="20">
-        <v>4.197997932171494</v>
+        <v>4.198114103620362</v>
       </c>
       <c r="L13" s="20">
-        <v>0.06749015820869138</v>
+        <v>0.03202592099213238</v>
       </c>
       <c r="M13" s="20">
-        <v>0.04193171926538725</v>
+        <v>0.2613176439546983</v>
       </c>
       <c r="N13" s="20">
-        <v>16.83141</v>
+        <v>16.975927</v>
       </c>
       <c r="O13" s="20">
-        <v>6.5908914</v>
+        <v>6.6508174</v>
       </c>
       <c r="P13" s="12">
         <v>0.48676</v>
@@ -4579,13 +4625,13 @@
         <v>0.242</v>
       </c>
       <c r="R13" s="12">
-        <v>0.1482207138835352</v>
+        <v>0.1304095874226328</v>
       </c>
       <c r="S13" s="11">
-        <v>54.86677435742562</v>
+        <v>51.72085052727156</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4593,61 +4639,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>104</v>
+        <v>11</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E14" s="10">
-        <v>259.4299926757812</v>
+        <v>341.4299926757812</v>
       </c>
       <c r="F14" s="17">
-        <v>0.8296267170835715</v>
+        <v>0.8341785756102056</v>
       </c>
       <c r="G14" s="20">
-        <v>0.3415976968814792</v>
+        <v>-0.3694515340244113</v>
       </c>
       <c r="H14" s="20">
-        <v>0.5361174605758535</v>
+        <v>1.461933114403917</v>
       </c>
       <c r="I14" s="20">
-        <v>0.1958909336866145</v>
+        <v>1.394253875646282</v>
       </c>
       <c r="J14" s="20">
-        <v>1.334480265558949</v>
+        <v>-0.01298167389032759</v>
       </c>
       <c r="K14" s="20">
-        <v>3.532387487349705</v>
+        <v>4.198114103620362</v>
       </c>
       <c r="L14" s="20">
-        <v>-1.53918117489099</v>
+        <v>0.06064050491953007</v>
       </c>
       <c r="M14" s="20">
-        <v>-0.8638557884010362</v>
+        <v>0.2978443162853454</v>
       </c>
       <c r="N14" s="20">
-        <v>22.684982</v>
+        <v>16.83141</v>
       </c>
       <c r="O14" s="20">
-        <v>5.312232</v>
+        <v>6.5908914</v>
       </c>
       <c r="P14" s="12">
-        <v>0.19381</v>
+        <v>0.48676</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.108</v>
+        <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>0.3522277194846328</v>
+        <v>0.1229789876647722</v>
       </c>
       <c r="S14" s="11">
-        <v>69.75681441978077</v>
+        <v>51.18538862480936</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4655,61 +4701,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>42</v>
       </c>
       <c r="E15" s="10">
-        <v>257.0599975585938</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="F15" s="17">
-        <v>0.824071231833528</v>
+        <v>0.8144457689120104</v>
       </c>
       <c r="G15" s="20">
-        <v>0.4728319185405508</v>
+        <v>0.6018835051913498</v>
       </c>
       <c r="H15" s="20">
-        <v>-0.7907783719627398</v>
+        <v>0.6139340215135211</v>
       </c>
       <c r="I15" s="20">
-        <v>2.406342473145227</v>
+        <v>2.907067021605936</v>
       </c>
       <c r="J15" s="20">
-        <v>1.929147647251266</v>
+        <v>0.81025577985074</v>
       </c>
       <c r="K15" s="20">
-        <v>0.6936117762578806</v>
+        <v>0.9154253562229835</v>
       </c>
       <c r="L15" s="20">
-        <v>0.4992828079226008</v>
+        <v>0.3452148038147002</v>
       </c>
       <c r="M15" s="20">
-        <v>-0.8385362138242139</v>
+        <v>-0.7058759069506468</v>
       </c>
       <c r="N15" s="20">
-        <v>14.818389</v>
+        <v>18.129793</v>
       </c>
       <c r="O15" s="20">
-        <v>3.2861774</v>
+        <v>1.836326</v>
       </c>
       <c r="P15" s="12">
-        <v>0.23452999</v>
+        <v>0.10629</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.531</v>
+        <v>0.534</v>
       </c>
       <c r="R15" s="12">
-        <v>0.5068919214337058</v>
+        <v>0.119759123225649</v>
       </c>
       <c r="S15" s="11">
-        <v>70.26503245998802</v>
+        <v>71.16891540451111</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4717,61 +4763,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>107</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="10">
-        <v>55.40999984741211</v>
+        <v>255.6499938964844</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7981458632159613</v>
+        <v>0.8005310238731026</v>
       </c>
       <c r="G16" s="20">
-        <v>0.3530298731450531</v>
+        <v>0.3415976968814792</v>
       </c>
       <c r="H16" s="20">
-        <v>-0.5362564771804156</v>
+        <v>0.5361174605758535</v>
       </c>
       <c r="I16" s="20">
-        <v>2.205637651643404</v>
+        <v>0.1958909336866145</v>
       </c>
       <c r="J16" s="20">
-        <v>1.950292945949812</v>
+        <v>1.26347958635133</v>
       </c>
       <c r="K16" s="20">
-        <v>0</v>
+        <v>3.524887358235604</v>
       </c>
       <c r="L16" s="20">
-        <v>-1.927064249293187</v>
+        <v>-1.562192545310308</v>
       </c>
       <c r="M16" s="20">
-        <v>0.4324528102638764</v>
+        <v>-0.9327906850176849</v>
       </c>
       <c r="N16" s="20">
-        <v>32.005154</v>
+        <v>22.684982</v>
       </c>
       <c r="O16" s="20">
-        <v>3.1100981</v>
+        <v>5.312232</v>
       </c>
       <c r="P16" s="12">
-        <v>0.10936</v>
+        <v>0.19381</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.337</v>
+        <v>0.108</v>
       </c>
       <c r="R16" s="12">
-        <v>1.591772361385027</v>
+        <v>0.2955069218851827</v>
       </c>
       <c r="S16" s="11">
-        <v>52.07947637617934</v>
+        <v>66.55121562547168</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4779,61 +4825,61 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>6</v>
+        <v>107</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E17" s="10">
-        <v>61.77999877929688</v>
+        <v>55.88000106811523</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7488325358416236</v>
+        <v>0.7781049213844827</v>
       </c>
       <c r="G17" s="20">
-        <v>0.6018835051913498</v>
+        <v>0.3530298731450531</v>
       </c>
       <c r="H17" s="20">
-        <v>0.6139340215135211</v>
+        <v>-0.5362564771804156</v>
       </c>
       <c r="I17" s="20">
-        <v>2.907067021605936</v>
+        <v>2.205637651643404</v>
       </c>
       <c r="J17" s="20">
-        <v>0.5639565866142032</v>
+        <v>1.955978391767738</v>
       </c>
       <c r="K17" s="20">
-        <v>0.9185011287118862</v>
+        <v>0</v>
       </c>
       <c r="L17" s="20">
-        <v>0.3496493944465213</v>
+        <v>-1.955038451555946</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.6103589474006887</v>
+        <v>0.2116626799974562</v>
       </c>
       <c r="N17" s="20">
-        <v>18.129793</v>
+        <v>32.005154</v>
       </c>
       <c r="O17" s="20">
-        <v>1.836326</v>
+        <v>3.1100981</v>
       </c>
       <c r="P17" s="12">
-        <v>0.10629</v>
+        <v>0.10936</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.534</v>
+        <v>0.337</v>
       </c>
       <c r="R17" s="12">
-        <v>0.0772313801886213</v>
+        <v>1.581458169131547</v>
       </c>
       <c r="S17" s="11">
-        <v>65.06265728902758</v>
+        <v>52.75135451824926</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4841,61 +4887,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="E18" s="10">
-        <v>158.6999969482422</v>
+        <v>257.2099914550781</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6704875708320357</v>
+        <v>0.6643531276938139</v>
       </c>
       <c r="G18" s="20">
-        <v>0.5169435305631409</v>
+        <v>1.275714742496789</v>
       </c>
       <c r="H18" s="20">
-        <v>-0.5609987008817506</v>
+        <v>0.1637485141969772</v>
       </c>
       <c r="I18" s="20">
-        <v>-0.03865308917984001</v>
+        <v>-0.05524579084430264</v>
       </c>
       <c r="J18" s="20">
-        <v>1.078124005853262</v>
+        <v>0.5533737975568457</v>
       </c>
       <c r="K18" s="20">
-        <v>3.298192368587258</v>
+        <v>1.856297434875873</v>
       </c>
       <c r="L18" s="20">
-        <v>0.2949725556201062</v>
+        <v>0.4836670935941778</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.8231975366740211</v>
+        <v>-0.04673207763129128</v>
       </c>
       <c r="N18" s="20">
-        <v>16.148188</v>
+        <v>5.081314</v>
       </c>
       <c r="O18" s="20">
-        <v>3.9674618</v>
+        <v>2.0330794</v>
       </c>
       <c r="P18" s="12">
-        <v>0.26408002</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.053</v>
+        <v>0.118</v>
       </c>
       <c r="R18" s="12">
-        <v>0.3757373933555348</v>
+        <v>0.2494158551196175</v>
       </c>
       <c r="S18" s="11">
-        <v>52.9546715385213</v>
+        <v>50.49890368250308</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4903,61 +4949,61 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>112</v>
+        <v>49</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E19" s="10">
-        <v>258.4800109863281</v>
+        <v>47.40999984741211</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6636239767702646</v>
+        <v>0.6506104419219966</v>
       </c>
       <c r="G19" s="20">
-        <v>1.275714742496789</v>
+        <v>1.099839703019805</v>
       </c>
       <c r="H19" s="20">
-        <v>0.1637485141969772</v>
+        <v>0.5600572175760307</v>
       </c>
       <c r="I19" s="20">
-        <v>-0.05524579084430264</v>
+        <v>-0.2922173294313919</v>
       </c>
       <c r="J19" s="20">
-        <v>0.5771411111412715</v>
+        <v>1.792187259161045</v>
       </c>
       <c r="K19" s="20">
-        <v>1.860968460950166</v>
+        <v>-0.570460938040137</v>
       </c>
       <c r="L19" s="20">
-        <v>0.4908272472238406</v>
+        <v>-0.2753998992412363</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.1573505444509424</v>
+        <v>-0.7553124714952126</v>
       </c>
       <c r="N19" s="20">
-        <v>5.081314</v>
+        <v>9.436709</v>
       </c>
       <c r="O19" s="20">
-        <v>2.0330794</v>
+        <v>2.2340426</v>
       </c>
       <c r="P19" s="12">
-        <v>0.46113998</v>
+        <v>0.26659</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.118</v>
+        <v>0.092</v>
       </c>
       <c r="R19" s="12">
-        <v>0.2655726794771835</v>
+        <v>0.3915245433828938</v>
       </c>
       <c r="S19" s="11">
-        <v>52.03093909583132</v>
+        <v>71.61490644470551</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -4965,61 +5011,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="E20" s="10">
-        <v>253.5399932861328</v>
+        <v>189.9299926757812</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6492655173943512</v>
+        <v>0.6453205619024445</v>
       </c>
       <c r="G20" s="20">
-        <v>-0.04046750433284103</v>
+        <v>-0.4603187739276002</v>
       </c>
       <c r="H20" s="20">
-        <v>0.1570571804969511</v>
+        <v>1.359216064961746</v>
       </c>
       <c r="I20" s="20">
-        <v>1.023343627582307</v>
+        <v>0.4362761666871086</v>
       </c>
       <c r="J20" s="20">
-        <v>0.1552359262998876</v>
+        <v>1.420391617147448</v>
       </c>
       <c r="K20" s="20">
-        <v>4.197997932171494</v>
+        <v>0</v>
       </c>
       <c r="L20" s="20">
-        <v>-0.4046724909683029</v>
+        <v>-0.4094634044217691</v>
       </c>
       <c r="M20" s="20">
-        <v>0.037949703050905</v>
+        <v>-0.1489049270049929</v>
       </c>
       <c r="N20" s="20">
-        <v>20.658085</v>
+        <v>28.186703</v>
       </c>
       <c r="O20" s="20">
-        <v>5.0195484</v>
+        <v>26.124804</v>
       </c>
       <c r="P20" s="12">
-        <v>0.30558002</v>
+        <v>1.14818</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.196</v>
+        <v>0.299</v>
       </c>
       <c r="R20" s="12">
-        <v>0.2208792580614893</v>
+        <v>0.8728741852609276</v>
       </c>
       <c r="S20" s="11">
-        <v>45.84245200474109</v>
+        <v>52.23971145746755</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -5027,61 +5073,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="E21" s="10">
-        <v>188.2799987792969</v>
+        <v>154.3999938964844</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6404347402016241</v>
+        <v>0.629749702539554</v>
       </c>
       <c r="G21" s="20">
-        <v>-0.4603187739276002</v>
+        <v>0.5169435305631409</v>
       </c>
       <c r="H21" s="20">
-        <v>1.359216064961746</v>
+        <v>-0.5609987008817506</v>
       </c>
       <c r="I21" s="20">
-        <v>0.4362761666871086</v>
+        <v>-0.03865308917984001</v>
       </c>
       <c r="J21" s="20">
-        <v>1.396710524583753</v>
+        <v>0.9018502104981442</v>
       </c>
       <c r="K21" s="20">
-        <v>0</v>
+        <v>3.291088646425534</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.416347229748139</v>
+        <v>0.2638189685730646</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.108681999605382</v>
+        <v>-0.6373733842204831</v>
       </c>
       <c r="N21" s="20">
-        <v>28.186703</v>
+        <v>16.148188</v>
       </c>
       <c r="O21" s="20">
-        <v>26.124804</v>
+        <v>3.9674618</v>
       </c>
       <c r="P21" s="12">
-        <v>1.14818</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.299</v>
+        <v>0.053</v>
       </c>
       <c r="R21" s="12">
-        <v>0.9239728482142766</v>
+        <v>0.3417775802287879</v>
       </c>
       <c r="S21" s="11">
-        <v>50.89744488112564</v>
+        <v>46.18404292940898</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -5089,61 +5135,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>57</v>
-      </c>
       <c r="E22" s="10">
-        <v>122.1900024414062</v>
+        <v>248.4199981689453</v>
       </c>
       <c r="F22" s="17">
-        <v>0.5542611253698945</v>
+        <v>0.6095747712110319</v>
       </c>
       <c r="G22" s="20">
-        <v>0.3560597278471356</v>
+        <v>-0.04046750433284103</v>
       </c>
       <c r="H22" s="20">
-        <v>0.5036708481790161</v>
+        <v>0.1570571804969511</v>
       </c>
       <c r="I22" s="20">
-        <v>0.5191598695187023</v>
+        <v>1.023343627582307</v>
       </c>
       <c r="J22" s="20">
-        <v>0.5733477433246573</v>
+        <v>0.003946071370269246</v>
       </c>
       <c r="K22" s="20">
-        <v>1.650037757958823</v>
+        <v>4.198114103620362</v>
       </c>
       <c r="L22" s="20">
-        <v>0.1426259815604311</v>
+        <v>-0.410995729271467</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.2612420143648083</v>
+        <v>0.11372050329955</v>
       </c>
       <c r="N22" s="20">
-        <v>15.473886</v>
+        <v>20.658085</v>
       </c>
       <c r="O22" s="20">
-        <v>3.847884</v>
+        <v>5.0195484</v>
       </c>
       <c r="P22" s="12">
-        <v>0.30667</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.377</v>
+        <v>0.196</v>
       </c>
       <c r="R22" s="12">
-        <v>0.3204020016483911</v>
+        <v>0.1732312823471871</v>
       </c>
       <c r="S22" s="11">
-        <v>46.46241016422281</v>
+        <v>41.41705451283759</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -5151,61 +5197,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>121</v>
-      </c>
       <c r="D23" s="9" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E23" s="10">
-        <v>34.02000045776367</v>
+        <v>121.7399978637695</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5526847296036832</v>
+        <v>0.5727022719586583</v>
       </c>
       <c r="G23" s="20">
-        <v>0.9932091735796537</v>
+        <v>0.3560597278471356</v>
       </c>
       <c r="H23" s="20">
-        <v>-0.9910800207632466</v>
+        <v>0.5036708481790161</v>
       </c>
       <c r="I23" s="20">
-        <v>-0.385570790078564</v>
+        <v>0.5191598695187023</v>
       </c>
       <c r="J23" s="20">
-        <v>1.867556802628306</v>
+        <v>0.6476358906946246</v>
       </c>
       <c r="K23" s="20">
-        <v>0.4113368649018186</v>
+        <v>1.645723760662829</v>
       </c>
       <c r="L23" s="20">
-        <v>-0.7230916617578612</v>
+        <v>0.13576854676561</v>
       </c>
       <c r="M23" s="20">
-        <v>0.05993744772603726</v>
+        <v>-0.2976941626025293</v>
       </c>
       <c r="N23" s="20">
-        <v>13.5419855</v>
+        <v>15.473886</v>
       </c>
       <c r="O23" s="20">
-        <v>-347.84314</v>
+        <v>3.847884</v>
       </c>
       <c r="P23" s="12">
-        <v>0</v>
+        <v>0.30667</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.125</v>
+        <v>0.377</v>
       </c>
       <c r="R23" s="12">
-        <v>0.8367060329642197</v>
+        <v>0.309032235094296</v>
       </c>
       <c r="S23" s="11">
-        <v>64.02313735821257</v>
+        <v>45.55254132787277</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -5213,61 +5259,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>8</v>
+        <v>121</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>49</v>
+        <v>122</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E24" s="10">
-        <v>45.02999877929688</v>
+        <v>33.81999969482422</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5521464870932067</v>
+        <v>0.5569433906580628</v>
       </c>
       <c r="G24" s="20">
-        <v>1.099839703019805</v>
+        <v>0.9932091735796537</v>
       </c>
       <c r="H24" s="20">
-        <v>0.5600572175760307</v>
+        <v>-0.9910800207632466</v>
       </c>
       <c r="I24" s="20">
-        <v>-0.2922173294313919</v>
+        <v>-0.385570790078564</v>
       </c>
       <c r="J24" s="20">
-        <v>1.450373048581954</v>
+        <v>1.886173261218317</v>
       </c>
       <c r="K24" s="20">
-        <v>-0.5699044936216348</v>
+        <v>0.4091195366077971</v>
       </c>
       <c r="L24" s="20">
-        <v>-0.2228253554151386</v>
+        <v>-0.7467573774481366</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.7445741916808229</v>
+        <v>0.06443427040197813</v>
       </c>
       <c r="N24" s="20">
-        <v>9.436709</v>
+        <v>13.5419855</v>
       </c>
       <c r="O24" s="20">
-        <v>2.2340426</v>
+        <v>-347.84314</v>
       </c>
       <c r="P24" s="12">
-        <v>0.26659</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.092</v>
+        <v>0.125</v>
       </c>
       <c r="R24" s="12">
-        <v>0.3243533335450024</v>
+        <v>0.8503446708392963</v>
       </c>
       <c r="S24" s="11">
-        <v>64.65499916721588</v>
+        <v>63.01774012836682</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -5275,61 +5321,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>110</v>
+        <v>32</v>
       </c>
       <c r="E25" s="10">
-        <v>119.1699981689453</v>
+        <v>172.3699951171875</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5469331124930834</v>
+        <v>0.5220751939514237</v>
       </c>
       <c r="G25" s="20">
-        <v>0.4228371578138432</v>
+        <v>-2.045758834681303</v>
       </c>
       <c r="H25" s="20">
-        <v>-0.1266107877394232</v>
+        <v>1.763423185417039</v>
       </c>
       <c r="I25" s="20">
-        <v>0.4718408509917099</v>
+        <v>0.2278103986420596</v>
       </c>
       <c r="J25" s="20">
-        <v>-0.1268757252433695</v>
+        <v>1.882835690231804</v>
       </c>
       <c r="K25" s="20">
-        <v>4.197997932171494</v>
+        <v>0.4369895817242295</v>
       </c>
       <c r="L25" s="20">
-        <v>0.08136732697339379</v>
+        <v>-0.5793723082203702</v>
       </c>
       <c r="M25" s="20">
-        <v>-0.3335376110030455</v>
+        <v>0.03569895349874286</v>
       </c>
       <c r="N25" s="20">
-        <v>14.463892</v>
+        <v>55.343975</v>
       </c>
       <c r="O25" s="20">
-        <v>6.474714</v>
+        <v>73.826866</v>
       </c>
       <c r="P25" s="12">
-        <v>0.46032003</v>
+        <v>1.17442</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.256</v>
       </c>
       <c r="R25" s="12">
-        <v>0.1089707722337463</v>
+        <v>1.040123085280632</v>
       </c>
       <c r="S25" s="11">
-        <v>37.63397580688533</v>
+        <v>61.40356577742246</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -5337,61 +5383,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E26" s="10">
-        <v>988.4500122070312</v>
+        <v>217.7700042724609</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5251208465853666</v>
+        <v>0.512176032614258</v>
       </c>
       <c r="G26" s="20">
-        <v>0.3658514008022524</v>
+        <v>0.5000449645463003</v>
       </c>
       <c r="H26" s="20">
-        <v>0.8216781549389145</v>
+        <v>-0.3299402274497991</v>
       </c>
       <c r="I26" s="20">
-        <v>0.9093352353792101</v>
+        <v>2.306272783126228</v>
       </c>
       <c r="J26" s="20">
-        <v>-0.04145999161670547</v>
+        <v>0.9235329140507406</v>
       </c>
       <c r="K26" s="20">
-        <v>1.666581342507164</v>
+        <v>-0.1663452838518691</v>
       </c>
       <c r="L26" s="20">
-        <v>0.07543324747431411</v>
+        <v>0.8430070564342445</v>
       </c>
       <c r="M26" s="20">
-        <v>0.5598475956063371</v>
+        <v>-0.7918470807972934</v>
       </c>
       <c r="N26" s="20">
-        <v>15.897128</v>
+        <v>20.62235</v>
       </c>
       <c r="O26" s="20">
-        <v>2.842654</v>
+        <v>2.2113636</v>
       </c>
       <c r="P26" s="12">
-        <v>0.16902</v>
+        <v>0.12231</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.425</v>
+        <v>0.535</v>
       </c>
       <c r="R26" s="12">
-        <v>0.2754486009594632</v>
+        <v>0.1262067437900027</v>
       </c>
       <c r="S26" s="11">
-        <v>39.52991259648539</v>
+        <v>71.00079912649116</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -5399,61 +5445,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E27" s="10">
-        <v>36.7400016784668</v>
+        <v>97.13999938964844</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5154468331968604</v>
+        <v>0.5099304722649342</v>
       </c>
       <c r="G27" s="20">
-        <v>0.005970682120931148</v>
+        <v>-0.7359494773385853</v>
       </c>
       <c r="H27" s="20">
-        <v>-0.8151434307759278</v>
+        <v>-1.140633242548325</v>
       </c>
       <c r="I27" s="20">
-        <v>3.899748911067756</v>
+        <v>0.5241404076306111</v>
       </c>
       <c r="J27" s="20">
-        <v>0.2873587861215741</v>
+        <v>1.098580246187481</v>
       </c>
       <c r="K27" s="20">
-        <v>3.387114135534589</v>
+        <v>4.198114103620362</v>
       </c>
       <c r="L27" s="20">
-        <v>-3.375332568109985</v>
+        <v>-2.243486277693008</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.4415151222694788</v>
+        <v>0.921875832518037</v>
       </c>
       <c r="N27" s="20">
-        <v>12.300613</v>
+        <v>50.34258</v>
       </c>
       <c r="O27" s="20">
-        <v>2.5690305</v>
+        <v>5.9300656</v>
       </c>
       <c r="P27" s="12">
-        <v>0.21465999</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.254</v>
       </c>
       <c r="R27" s="12">
-        <v>0.1947968025517657</v>
+        <v>1.122814749840964</v>
       </c>
       <c r="S27" s="11">
-        <v>50.70653346487457</v>
+        <v>50.27464804382547</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5461,61 +5507,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E28" s="10">
-        <v>206.6799926757812</v>
+        <v>976.6699829101562</v>
       </c>
       <c r="F28" s="17">
-        <v>0.504567505531323</v>
+        <v>0.4955517800725586</v>
       </c>
       <c r="G28" s="20">
-        <v>0.5982241598157348</v>
+        <v>0.3658514008022524</v>
       </c>
       <c r="H28" s="20">
-        <v>-0.6609329225841165</v>
+        <v>0.8216781549389145</v>
       </c>
       <c r="I28" s="20">
-        <v>4.117187201861848</v>
+        <v>0.9093352353792101</v>
       </c>
       <c r="J28" s="20">
-        <v>-0.07830011893937884</v>
+        <v>-0.09630682543835871</v>
       </c>
       <c r="K28" s="20">
-        <v>0.6077919314133636</v>
+        <v>1.662239342954049</v>
       </c>
       <c r="L28" s="20">
-        <v>0.6090994367614738</v>
+        <v>0.06072157930923498</v>
       </c>
       <c r="M28" s="20">
-        <v>0.06158427372857556</v>
+        <v>0.4134566414809195</v>
       </c>
       <c r="N28" s="20">
-        <v>11.482911</v>
+        <v>15.897128</v>
       </c>
       <c r="O28" s="20">
-        <v>1.2409225</v>
+        <v>2.842654</v>
       </c>
       <c r="P28" s="12">
-        <v>0.09031</v>
+        <v>0.16902</v>
       </c>
       <c r="Q28" s="12">
-        <v>11.11</v>
+        <v>0.425</v>
       </c>
       <c r="R28" s="12">
-        <v>0.1585748780907137</v>
+        <v>0.2403321709082651</v>
       </c>
       <c r="S28" s="11">
-        <v>40.13111347997287</v>
+        <v>37.18001314071405</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5523,61 +5569,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E29" s="10">
-        <v>351.8099975585938</v>
+        <v>216.1699981689453</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5022143598943355</v>
+        <v>0.4914891493246438</v>
       </c>
       <c r="G29" s="20">
-        <v>0.116365121381956</v>
+        <v>0.2268704470519779</v>
       </c>
       <c r="H29" s="20">
-        <v>-0.2401012663427755</v>
+        <v>0.02833393151366955</v>
       </c>
       <c r="I29" s="20">
-        <v>0.4632294407463022</v>
+        <v>-0.8973367206108911</v>
       </c>
       <c r="J29" s="20">
-        <v>1.46904739909879</v>
+        <v>0.5360470716400234</v>
       </c>
       <c r="K29" s="20">
-        <v>1.709491264929422</v>
+        <v>3.371085998148626</v>
       </c>
       <c r="L29" s="20">
-        <v>-1.628486928373788</v>
+        <v>-0.1290051695354112</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.9347757404117922</v>
+        <v>-0.271892740294098</v>
       </c>
       <c r="N29" s="20">
-        <v>32.14404</v>
+        <v>38.63879</v>
       </c>
       <c r="O29" s="20">
-        <v>4.8336897</v>
+        <v>1.7016691</v>
       </c>
       <c r="P29" s="12">
-        <v>0.15286</v>
+        <v>0.04575</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.204</v>
+        <v>0.034</v>
       </c>
       <c r="R29" s="12">
-        <v>0.7354478859516924</v>
+        <v>0.1795809486444231</v>
       </c>
       <c r="S29" s="11">
-        <v>53.41973379161933</v>
+        <v>51.85754419140703</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5585,61 +5631,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E30" s="10">
-        <v>97.19000244140625</v>
+        <v>206.8500061035156</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4977545090094619</v>
+        <v>0.4904824223141894</v>
       </c>
       <c r="G30" s="20">
-        <v>-0.7359494773385853</v>
+        <v>0.5982241598157348</v>
       </c>
       <c r="H30" s="20">
-        <v>-1.140633242548325</v>
+        <v>-0.6609329225841165</v>
       </c>
       <c r="I30" s="20">
-        <v>0.5241404076306111</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J30" s="20">
-        <v>1.090085289670754</v>
+        <v>-0.09942068668727556</v>
       </c>
       <c r="K30" s="20">
-        <v>4.197997932171494</v>
+        <v>0.6052420763160242</v>
       </c>
       <c r="L30" s="20">
-        <v>-2.421908977065426</v>
+        <v>0.6052976196963868</v>
       </c>
       <c r="M30" s="20">
-        <v>0.9355236604649794</v>
+        <v>-0.02860099198615679</v>
       </c>
       <c r="N30" s="20">
-        <v>50.34258</v>
+        <v>11.482911</v>
       </c>
       <c r="O30" s="20">
-        <v>5.9300656</v>
+        <v>1.2409225</v>
       </c>
       <c r="P30" s="12">
-        <v>-0.10715</v>
+        <v>0.09031</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.254</v>
+        <v>11.11</v>
       </c>
       <c r="R30" s="12">
-        <v>1.123443335577257</v>
+        <v>0.1532417916908129</v>
       </c>
       <c r="S30" s="11">
-        <v>50.33356514283881</v>
+        <v>40.42332454892806</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5647,61 +5693,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E31" s="10">
-        <v>170.1799926757812</v>
+        <v>153.7400054931641</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4946433876191874</v>
+        <v>0.4732573120190842</v>
       </c>
       <c r="G31" s="20">
-        <v>-2.045758834681303</v>
+        <v>0.6042209697867998</v>
       </c>
       <c r="H31" s="20">
-        <v>1.763423185417039</v>
+        <v>0.4636940000902633</v>
       </c>
       <c r="I31" s="20">
-        <v>0.2278103986420596</v>
+        <v>1.421647839457134</v>
       </c>
       <c r="J31" s="20">
-        <v>1.855770303469042</v>
+        <v>0.7660990481666766</v>
       </c>
       <c r="K31" s="20">
-        <v>0.4392541638271436</v>
+        <v>-0.5142047358606719</v>
       </c>
       <c r="L31" s="20">
-        <v>-0.5582201727433476</v>
+        <v>0.3085958244441517</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.2249644000559904</v>
+        <v>-0.481239776450836</v>
       </c>
       <c r="N31" s="20">
-        <v>55.343975</v>
+        <v>11.467704</v>
       </c>
       <c r="O31" s="20">
-        <v>73.826866</v>
+        <v>2.4302394</v>
       </c>
       <c r="P31" s="12">
-        <v>1.17442</v>
+        <v>0.22507</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.256</v>
+        <v>0.587</v>
       </c>
       <c r="R31" s="12">
-        <v>1.039549229343397</v>
+        <v>0.1603861156826818</v>
       </c>
       <c r="S31" s="11">
-        <v>59.88350413991242</v>
+        <v>65.12536509400445</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5709,61 +5755,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E32" s="10">
-        <v>217.3600006103516</v>
+        <v>31.22999954223633</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4914478888561534</v>
+        <v>0.4551546175425572</v>
       </c>
       <c r="G32" s="20">
-        <v>0.2268704470519779</v>
+        <v>0.5071505500348842</v>
       </c>
       <c r="H32" s="20">
-        <v>0.02833393151366955</v>
+        <v>0.7469802265893087</v>
       </c>
       <c r="I32" s="20">
-        <v>-0.8973367206108911</v>
+        <v>-0.1877648684685418</v>
       </c>
       <c r="J32" s="20">
-        <v>0.5470984017590618</v>
+        <v>1.173776721556721</v>
       </c>
       <c r="K32" s="20">
-        <v>3.378325356243283</v>
+        <v>-0.4682707726132187</v>
       </c>
       <c r="L32" s="20">
-        <v>-0.1193469719306684</v>
+        <v>0.1723281815137133</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.3319536694421627</v>
+        <v>-0.5394130689426249</v>
       </c>
       <c r="N32" s="20">
-        <v>38.63879</v>
+        <v>17.695906</v>
       </c>
       <c r="O32" s="20">
-        <v>1.7016691</v>
+        <v>6.8245378</v>
       </c>
       <c r="P32" s="12">
-        <v>0.04575</v>
+        <v>0.41944</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.034</v>
+        <v>0.063</v>
       </c>
       <c r="R32" s="12">
-        <v>0.1972459209950259</v>
+        <v>0.5301199797697445</v>
       </c>
       <c r="S32" s="11">
-        <v>53.41396335420527</v>
+        <v>62.73094495468379</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5771,61 +5817,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E33" s="10">
-        <v>212.1699981689453</v>
+        <v>342.7300109863281</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4645998663918035</v>
+        <v>0.4529808587094866</v>
       </c>
       <c r="G33" s="20">
-        <v>0.5000449645463003</v>
+        <v>0.116365121381956</v>
       </c>
       <c r="H33" s="20">
-        <v>-0.3299402274497991</v>
+        <v>-0.2401012663427755</v>
       </c>
       <c r="I33" s="20">
-        <v>2.306272783126228</v>
+        <v>0.4632294407463022</v>
       </c>
       <c r="J33" s="20">
-        <v>0.7195024761276629</v>
+        <v>1.266403709696704</v>
       </c>
       <c r="K33" s="20">
-        <v>-0.165103659204425</v>
+        <v>1.705076634521898</v>
       </c>
       <c r="L33" s="20">
-        <v>0.835800977246664</v>
+        <v>-1.682739603689381</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.617892893946917</v>
+        <v>-0.7429692178665943</v>
       </c>
       <c r="N33" s="20">
-        <v>20.62235</v>
+        <v>32.14404</v>
       </c>
       <c r="O33" s="20">
-        <v>2.2113636</v>
+        <v>4.8336897</v>
       </c>
       <c r="P33" s="12">
-        <v>0.12231</v>
+        <v>0.15286</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.535</v>
+        <v>0.204</v>
       </c>
       <c r="R33" s="12">
-        <v>0.0973574364996117</v>
+        <v>0.6802961657850926</v>
       </c>
       <c r="S33" s="11">
-        <v>65.04431477195874</v>
+        <v>47.66103705998034</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5833,61 +5879,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>32</v>
+        <v>115</v>
       </c>
       <c r="E34" s="10">
-        <v>31.40999984741211</v>
+        <v>112.7900009155273</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4615724621097789</v>
+        <v>0.4488737267904408</v>
       </c>
       <c r="G34" s="20">
-        <v>0.5071505500348842</v>
+        <v>0.4228371578138432</v>
       </c>
       <c r="H34" s="20">
-        <v>0.7469802265893087</v>
+        <v>-0.1266107877394232</v>
       </c>
       <c r="I34" s="20">
-        <v>-0.1877648684685418</v>
+        <v>0.4718408509917099</v>
       </c>
       <c r="J34" s="20">
-        <v>1.241815959815756</v>
+        <v>-0.4348535511575777</v>
       </c>
       <c r="K34" s="20">
-        <v>-0.4675410642287771</v>
+        <v>4.198114103620362</v>
       </c>
       <c r="L34" s="20">
-        <v>0.1846712921650581</v>
+        <v>0.04442235692376011</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.7246890508889072</v>
+        <v>-0.3768286147438763</v>
       </c>
       <c r="N34" s="20">
-        <v>17.695906</v>
+        <v>14.463892</v>
       </c>
       <c r="O34" s="20">
-        <v>6.8245378</v>
+        <v>6.474714</v>
       </c>
       <c r="P34" s="12">
-        <v>0.41944</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R34" s="12">
-        <v>0.5337299998100054</v>
+        <v>-0.01372857368349911</v>
       </c>
       <c r="S34" s="11">
-        <v>64.38687725087902</v>
+        <v>30.78252408731522</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5895,19 +5941,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E35" s="10">
-        <v>64.09999847412109</v>
+        <v>63.72999954223633</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4464677891271827</v>
+        <v>0.4472788505659449</v>
       </c>
       <c r="G35" s="20">
         <v>0.5011052908132025</v>
@@ -5919,16 +5965,16 @@
         <v>0.2251020255328333</v>
       </c>
       <c r="J35" s="20">
-        <v>0.4190087502398802</v>
+        <v>0.4115044507124895</v>
       </c>
       <c r="K35" s="20">
-        <v>0.8120018031819431</v>
+        <v>0.8091062952232603</v>
       </c>
       <c r="L35" s="20">
-        <v>0.5531957554170509</v>
+        <v>0.5773297160473794</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.344237683133413</v>
+        <v>-0.3197155004558923</v>
       </c>
       <c r="N35" s="20">
         <v>14.017621</v>
@@ -5943,13 +5989,13 @@
         <v>0.057</v>
       </c>
       <c r="R35" s="12">
-        <v>0.1085302727958339</v>
+        <v>0.09050312550281703</v>
       </c>
       <c r="S35" s="11">
-        <v>44.99825693028483</v>
+        <v>43.33647351399254</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -5957,61 +6003,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>9</v>
+        <v>145</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>50</v>
+        <v>146</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E36" s="10">
-        <v>210.9600067138672</v>
+        <v>211.5299987792969</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4061175674949531</v>
+        <v>0.4436383808391406</v>
       </c>
       <c r="G36" s="20">
-        <v>-1.171878848863184</v>
+        <v>0.5627498454653113</v>
       </c>
       <c r="H36" s="20">
-        <v>2.368118728722743</v>
+        <v>-0.0477566135254233</v>
       </c>
       <c r="I36" s="20">
-        <v>2.422793453764177</v>
+        <v>1.594428774498311</v>
       </c>
       <c r="J36" s="20">
-        <v>0.14840354654265</v>
+        <v>0.7695053261445053</v>
       </c>
       <c r="K36" s="20">
-        <v>-0.3036561797967777</v>
+        <v>-0.1931831050751002</v>
       </c>
       <c r="L36" s="20">
-        <v>-0.2158843142054807</v>
+        <v>0.2650627690734423</v>
       </c>
       <c r="M36" s="20">
-        <v>0.009351934792708835</v>
+        <v>-0.4128975251140614</v>
       </c>
       <c r="N36" s="20">
-        <v>27.631645</v>
+        <v>39.041904</v>
       </c>
       <c r="O36" s="20">
-        <v>23.019087</v>
+        <v>1.5173635</v>
       </c>
       <c r="P36" s="12">
-        <v>1.17211</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q36" s="12">
-        <v>1.059</v>
+        <v>0.525</v>
       </c>
       <c r="R36" s="12">
-        <v>0.17304963335504</v>
+        <v>0.1729542852743062</v>
       </c>
       <c r="S36" s="11">
-        <v>44.06645392019853</v>
+        <v>64.1445250755504</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -6019,61 +6065,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>42</v>
       </c>
       <c r="E37" s="10">
-        <v>148.5399932861328</v>
+        <v>141.2200012207031</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4059299958043636</v>
+        <v>0.4413545969293228</v>
       </c>
       <c r="G37" s="20">
-        <v>0.6042209697867998</v>
+        <v>0.4918102935471612</v>
       </c>
       <c r="H37" s="20">
-        <v>0.4636940000902633</v>
+        <v>-0.1401007530318513</v>
       </c>
       <c r="I37" s="20">
-        <v>1.421647839457134</v>
+        <v>0.7942683123659047</v>
       </c>
       <c r="J37" s="20">
-        <v>0.4863464245768306</v>
+        <v>1.148898099295417</v>
       </c>
       <c r="K37" s="20">
-        <v>-0.5135529087538494</v>
+        <v>-0.09305738743458426</v>
       </c>
       <c r="L37" s="20">
-        <v>0.3291780617737359</v>
+        <v>0.572985485756923</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.290173309330341</v>
+        <v>-0.9007954887818863</v>
       </c>
       <c r="N37" s="20">
-        <v>11.467704</v>
+        <v>18.192053</v>
       </c>
       <c r="O37" s="20">
-        <v>2.4302394</v>
+        <v>2.5249555</v>
       </c>
       <c r="P37" s="12">
-        <v>0.22507</v>
+        <v>0.1418</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.587</v>
+        <v>0.355</v>
       </c>
       <c r="R37" s="12">
-        <v>0.1287743438540248</v>
+        <v>0.1805013198855161</v>
       </c>
       <c r="S37" s="11">
-        <v>56.75913156885876</v>
+        <v>72.21972770677463</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -6081,61 +6127,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E38" s="10">
-        <v>206.5800018310547</v>
+        <v>35.63999938964844</v>
       </c>
       <c r="F38" s="17">
-        <v>0.3933324678735144</v>
+        <v>0.4167896333894786</v>
       </c>
       <c r="G38" s="20">
-        <v>0.3472624676162839</v>
+        <v>0.005970682120931148</v>
       </c>
       <c r="H38" s="20">
-        <v>0.7723653122279558</v>
+        <v>-0.8151434307759278</v>
       </c>
       <c r="I38" s="20">
-        <v>0.38054810430196</v>
+        <v>3.899748911067756</v>
       </c>
       <c r="J38" s="20">
-        <v>0.1945124556594171</v>
+        <v>0.04681825340282978</v>
       </c>
       <c r="K38" s="20">
-        <v>0.3053545263890117</v>
+        <v>3.379859901240836</v>
       </c>
       <c r="L38" s="20">
-        <v>0.534156262049035</v>
+        <v>-3.347756939201326</v>
       </c>
       <c r="M38" s="20">
-        <v>0.5268288466058211</v>
+        <v>-0.782503492407324</v>
       </c>
       <c r="N38" s="20">
-        <v>17.330639</v>
+        <v>12.300613</v>
       </c>
       <c r="O38" s="20">
-        <v>3.1619003</v>
+        <v>2.5690305</v>
       </c>
       <c r="P38" s="12">
-        <v>0.17969999</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.28</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R38" s="12">
-        <v>0.3484435320974817</v>
+        <v>0.118644027209112</v>
       </c>
       <c r="S38" s="11">
-        <v>39.02348633706364</v>
+        <v>47.96918299203491</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -6143,61 +6189,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>42</v>
       </c>
       <c r="E39" s="10">
-        <v>205.7200012207031</v>
+        <v>51.33000183105469</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3920595159076784</v>
+        <v>0.4163086228636527</v>
       </c>
       <c r="G39" s="20">
-        <v>0.5627498454653113</v>
+        <v>0.3586551873076412</v>
       </c>
       <c r="H39" s="20">
-        <v>-0.0477566135254233</v>
+        <v>-0.04613112172066019</v>
       </c>
       <c r="I39" s="20">
-        <v>1.594428774498311</v>
+        <v>1.252904578771813</v>
       </c>
       <c r="J39" s="20">
-        <v>0.550469595109168</v>
+        <v>0.9015850912760487</v>
       </c>
       <c r="K39" s="20">
-        <v>-0.1919869840954785</v>
+        <v>-0.04144619277452451</v>
       </c>
       <c r="L39" s="20">
-        <v>0.2937031583342088</v>
+        <v>0.2814300457798175</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.2595238187898328</v>
+        <v>-0.6068322031282389</v>
       </c>
       <c r="N39" s="20">
-        <v>39.041904</v>
+        <v>10.919565</v>
       </c>
       <c r="O39" s="20">
-        <v>1.5173635</v>
+        <v>1.383556</v>
       </c>
       <c r="P39" s="12">
-        <v>0.034930002</v>
+        <v>0.11522</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.525</v>
+        <v>0.642</v>
       </c>
       <c r="R39" s="12">
-        <v>0.1404870673104863</v>
+        <v>0.1153246429446486</v>
       </c>
       <c r="S39" s="11">
-        <v>57.25834194063431</v>
+        <v>70.13798603559555</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -6205,19 +6251,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E40" s="10">
-        <v>30.55999946594238</v>
+        <v>30.44000053405762</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3900271290579442</v>
+        <v>0.3936430844956686</v>
       </c>
       <c r="G40" s="20">
         <v>0.4737570391617266</v>
@@ -6229,16 +6275,16 @@
         <v>-0.7009083349924576</v>
       </c>
       <c r="J40" s="20">
-        <v>0.697337619245387</v>
+        <v>0.6560846661254683</v>
       </c>
       <c r="K40" s="20">
-        <v>2.026921293450708</v>
+        <v>2.021969369734665</v>
       </c>
       <c r="L40" s="20">
-        <v>0.5468694977199896</v>
+        <v>0.5827828340111484</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.8063079494814781</v>
+        <v>-0.625917048954533</v>
       </c>
       <c r="N40" s="20">
         <v>28.582525</v>
@@ -6253,13 +6299,13 @@
         <v>0.108</v>
       </c>
       <c r="R40" s="12">
-        <v>0.2937901027918621</v>
+        <v>0.2620835759150768</v>
       </c>
       <c r="S40" s="11">
-        <v>59.65608369551476</v>
+        <v>58.16154823442542</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -6267,61 +6313,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>152</v>
+        <v>9</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>153</v>
+        <v>50</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E41" s="10">
-        <v>136.6699981689453</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3721303453043072</v>
+        <v>0.3906092319110401</v>
       </c>
       <c r="G41" s="20">
-        <v>0.4918102935471612</v>
+        <v>-1.171878848863184</v>
       </c>
       <c r="H41" s="20">
-        <v>-0.1401007530318513</v>
+        <v>2.368118728722743</v>
       </c>
       <c r="I41" s="20">
-        <v>0.7942683123659047</v>
+        <v>2.422793453764177</v>
       </c>
       <c r="J41" s="20">
-        <v>0.8963141260411401</v>
+        <v>0.1594050218291876</v>
       </c>
       <c r="K41" s="20">
-        <v>-0.09169150277116346</v>
+        <v>-0.3046632855408293</v>
       </c>
       <c r="L41" s="20">
-        <v>0.5579982189079566</v>
+        <v>-0.2032428307471127</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.8097171112494491</v>
+        <v>-0.2337282463084194</v>
       </c>
       <c r="N41" s="20">
-        <v>18.192053</v>
+        <v>27.631645</v>
       </c>
       <c r="O41" s="20">
-        <v>2.5249555</v>
+        <v>23.019087</v>
       </c>
       <c r="P41" s="12">
-        <v>0.1418</v>
+        <v>1.17211</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.355</v>
+        <v>1.059</v>
       </c>
       <c r="R41" s="12">
-        <v>0.1371238456011952</v>
+        <v>0.1606536093160311</v>
       </c>
       <c r="S41" s="11">
-        <v>65.58973752517147</v>
+        <v>45.21227177839541</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -6329,61 +6375,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E42" s="10">
-        <v>793.739990234375</v>
+        <v>206.2799987792969</v>
       </c>
       <c r="F42" s="17">
-        <v>0.368973775574238</v>
+        <v>0.3784873117499491</v>
       </c>
       <c r="G42" s="20">
-        <v>0.1788464932883841</v>
+        <v>0.3472624676162839</v>
       </c>
       <c r="H42" s="20">
-        <v>0.1776972721221774</v>
+        <v>0.7723653122279558</v>
       </c>
       <c r="I42" s="20">
-        <v>-0.2413594266157033</v>
+        <v>0.38054810430196</v>
       </c>
       <c r="J42" s="20">
-        <v>0.63685502750477</v>
+        <v>0.1959836333250878</v>
       </c>
       <c r="K42" s="20">
-        <v>1.445310899173108</v>
+        <v>0.3033165875546748</v>
       </c>
       <c r="L42" s="20">
-        <v>0.454061519965289</v>
+        <v>0.5312936648915446</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.7406465180721314</v>
+        <v>0.3409513349346129</v>
       </c>
       <c r="N42" s="20">
-        <v>19.343811</v>
+        <v>17.330639</v>
       </c>
       <c r="O42" s="20">
-        <v>2.4722013</v>
+        <v>3.1619003</v>
       </c>
       <c r="P42" s="12">
-        <v>0.14043</v>
+        <v>0.17969999</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.167</v>
+        <v>0.28</v>
       </c>
       <c r="R42" s="12">
-        <v>0.06715712135397278</v>
+        <v>0.3393074672810608</v>
       </c>
       <c r="S42" s="11">
-        <v>49.68973050061668</v>
+        <v>38.68184012380173</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -6391,61 +6437,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="E43" s="10">
-        <v>94.83000183105469</v>
+        <v>430.8800048828125</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3631360821217977</v>
+        <v>0.3679778944704148</v>
       </c>
       <c r="G43" s="20">
-        <v>0.6594637779990824</v>
+        <v>-0.2429950411639331</v>
       </c>
       <c r="H43" s="20">
-        <v>-0.4971404169201537</v>
+        <v>0.6042118867300035</v>
       </c>
       <c r="I43" s="20">
-        <v>-0.2300784505986128</v>
+        <v>-0.3187981010065978</v>
       </c>
       <c r="J43" s="20">
-        <v>1.27602183415249</v>
+        <v>0.9868619540258891</v>
       </c>
       <c r="K43" s="20">
-        <v>-0.2845276601627589</v>
+        <v>0.3193160578992932</v>
       </c>
       <c r="L43" s="20">
-        <v>0.0885615046222254</v>
+        <v>-0.003229163962673475</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.08742509318125991</v>
+        <v>0.1592518348232557</v>
       </c>
       <c r="N43" s="20">
-        <v>15.108153</v>
+        <v>32.779457</v>
       </c>
       <c r="O43" s="20">
-        <v>6.0021152</v>
+        <v>6.0678544</v>
       </c>
       <c r="P43" s="12">
-        <v>0.43126</v>
+        <v>0.1983</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.036</v>
+        <v>0.109</v>
       </c>
       <c r="R43" s="12">
-        <v>0.5586363090029245</v>
+        <v>0.5186268219739891</v>
       </c>
       <c r="S43" s="11">
-        <v>66.09833206083282</v>
+        <v>63.56016959275873</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6453,19 +6499,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D44" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E44" s="10">
-        <v>119.5</v>
+        <v>119.3099975585938</v>
       </c>
       <c r="F44" s="17">
-        <v>0.354802417641556</v>
+        <v>0.3544353023792072</v>
       </c>
       <c r="G44" s="20">
         <v>1.17687233316855</v>
@@ -6477,16 +6523,16 @@
         <v>0.1405562026344188</v>
       </c>
       <c r="J44" s="20">
-        <v>0.5044582089342483</v>
+        <v>0.4966982537321346</v>
       </c>
       <c r="K44" s="20">
-        <v>0.2040250710304253</v>
+        <v>0.2021586460209576</v>
       </c>
       <c r="L44" s="20">
-        <v>1.038566297027085</v>
+        <v>1.041656281575517</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.06579768173989665</v>
+        <v>-0.04080464140845316</v>
       </c>
       <c r="N44" s="20">
         <v>10.810517</v>
@@ -6501,13 +6547,13 @@
         <v>0.141</v>
       </c>
       <c r="R44" s="12">
-        <v>0.3318159648837586</v>
+        <v>0.3122962465433923</v>
       </c>
       <c r="S44" s="11">
-        <v>50.06186264628786</v>
+        <v>49.47845389350844</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -6573,110 +6619,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -6685,22 +6731,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -6779,57 +6825,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>34</v>
@@ -6837,113 +6883,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -6961,2412 +7007,2373 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI13"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:60">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>408.8244323730469</v>
+        <v>427.0742797851562</v>
       </c>
       <c r="C1">
-        <v>418.0192260742188</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="D1">
-        <v>427.0742797851562</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="E1">
-        <v>433.3439025878906</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="F1">
-        <v>408.7745361328125</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="G1">
-        <v>398.8309326171875</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="H1">
-        <v>413.9259948730469</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="I1">
-        <v>430.7481994628906</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="J1">
-        <v>424.5484619140625</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="K1">
-        <v>393.6694946289062</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="L1">
-        <v>411.1206359863281</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="M1">
-        <v>416.5915832519531</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="N1">
-        <v>431.2573547363281</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="O1">
-        <v>449.4772644042969</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="P1">
-        <v>434.2524108886719</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="Q1">
-        <v>426.4053649902344</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="R1">
-        <v>456.7851867675781</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="S1">
-        <v>411.9991760253906</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="T1">
-        <v>390.7343444824219</v>
+        <v>381.25</v>
       </c>
       <c r="U1">
-        <v>395.6861267089844</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="V1">
-        <v>381.25</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="W1">
-        <v>404.1499938964844</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="X1">
-        <v>441.7999877929688</v>
+        <v>437.5</v>
       </c>
       <c r="Y1">
-        <v>439.3399963378906</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="Z1">
-        <v>437.5</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="AA1">
-        <v>426.9100036621094</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AB1">
-        <v>392.1000061035156</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AC1">
-        <v>369.6400146484375</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AD1">
-        <v>404.8099975585938</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AE1">
-        <v>405.3699951171875</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AF1">
-        <v>429.0199890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AG1">
-        <v>467.2699890136719</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AH1">
-        <v>462.7000122070312</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AI1">
-        <v>437.6499938964844</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AJ1">
-        <v>453.7699890136719</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AK1">
-        <v>457.8800048828125</v>
+        <v>484.5</v>
       </c>
       <c r="AL1">
-        <v>440.9700012207031</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AM1">
-        <v>484.5</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AN1">
-        <v>494.510009765625</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AO1">
-        <v>490.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AP1">
-        <v>479.8099975585938</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AQ1">
-        <v>468.6499938964844</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AR1">
-        <v>437.5499877929688</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AS1">
-        <v>434.7799987792969</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AT1">
-        <v>442.0799865722656</v>
+        <v>451.5</v>
       </c>
       <c r="AU1">
-        <v>433.1900024414062</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="AV1">
-        <v>451.5</v>
+        <v>472.260009765625</v>
       </c>
       <c r="AW1">
-        <v>463.8200073242188</v>
+        <v>456.239990234375</v>
       </c>
       <c r="AX1">
-        <v>472.260009765625</v>
+        <v>456.010009765625</v>
       </c>
       <c r="AY1">
-        <v>456.239990234375</v>
+        <v>425</v>
       </c>
       <c r="AZ1">
-        <v>456.010009765625</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="BA1">
-        <v>425</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="BB1">
-        <v>492.2000122070312</v>
+        <v>524.1400146484375</v>
       </c>
       <c r="BC1">
-        <v>516.3900146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="BD1">
-        <v>524.1400146484375</v>
+        <v>535.25</v>
       </c>
       <c r="BE1">
-        <v>533.8800048828125</v>
+        <v>506.6199951171875</v>
       </c>
       <c r="BF1">
-        <v>535.25</v>
+        <v>567.2899780273438</v>
       </c>
       <c r="BG1">
-        <v>506.6199951171875</v>
+        <v>534.280029296875</v>
       </c>
       <c r="BH1">
-        <v>567.2899780273438</v>
-      </c>
-      <c r="BI1">
-        <v>534.280029296875</v>
-      </c>
-    </row>
-    <row r="2" spans="1:61">
+        <v>543.510009765625</v>
+      </c>
+    </row>
+    <row r="2" spans="1:60">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1133.815551757812</v>
+        <v>1051.608276367188</v>
       </c>
       <c r="C2">
-        <v>1211.193725585938</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="D2">
-        <v>1051.608276367188</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="E2">
-        <v>1048.348754882812</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="F2">
-        <v>1213.373413085938</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="G2">
-        <v>1132.155883789062</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="H2">
-        <v>1145.103881835938</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="I2">
-        <v>1154.112548828125</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="J2">
-        <v>1032.121337890625</v>
+        <v>984.75</v>
       </c>
       <c r="K2">
-        <v>975.4099731445312</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="L2">
-        <v>984.75</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="M2">
-        <v>938.3800048828125</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="N2">
-        <v>948.7999877929688</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="O2">
-        <v>991.6400146484375</v>
+        <v>937</v>
       </c>
       <c r="P2">
-        <v>979.2999877929688</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="Q2">
-        <v>937</v>
+        <v>904.280029296875</v>
       </c>
       <c r="R2">
-        <v>983.1199951171875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="S2">
-        <v>904.280029296875</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="T2">
-        <v>853.2000122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="U2">
-        <v>848.9500122070312</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="V2">
-        <v>865.4600219726562</v>
+        <v>959.47998046875</v>
       </c>
       <c r="W2">
-        <v>970.8200073242188</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="X2">
-        <v>959.47998046875</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="Y2">
-        <v>990.2100219726562</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="Z2">
-        <v>920.9500122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="AA2">
-        <v>900.2000122070312</v>
+        <v>739</v>
       </c>
       <c r="AB2">
-        <v>820.530029296875</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AC2">
-        <v>739</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AD2">
-        <v>874.6599731445312</v>
+        <v>829.5</v>
       </c>
       <c r="AE2">
-        <v>823.030029296875</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AF2">
-        <v>829.5</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AG2">
-        <v>892.6699829101562</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AH2">
-        <v>893.1900024414062</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AI2">
-        <v>881.469970703125</v>
+        <v>861</v>
       </c>
       <c r="AJ2">
-        <v>877.5700073242188</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AK2">
-        <v>861</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AL2">
-        <v>868.52001953125</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AM2">
-        <v>911.2899780273438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AN2">
-        <v>949.8300170898438</v>
+        <v>1011.75</v>
       </c>
       <c r="AO2">
-        <v>971.6599731445312</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AP2">
-        <v>1011.75</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AQ2">
-        <v>940.760009765625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AR2">
-        <v>937.1099853515625</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AS2">
-        <v>974.3300170898438</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AT2">
-        <v>966.780029296875</v>
+        <v>932.969970703125</v>
       </c>
       <c r="AU2">
-        <v>910.4299926757812</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="AV2">
-        <v>932.969970703125</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="AW2">
-        <v>938.4000244140625</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="AX2">
-        <v>935.3900146484375</v>
+        <v>958.72998046875</v>
       </c>
       <c r="AY2">
-        <v>932.8599853515625</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="AZ2">
-        <v>958.72998046875</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="BA2">
-        <v>933.4400024414062</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="BB2">
-        <v>956.0800170898438</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="BC2">
-        <v>958.1599731445312</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="BD2">
-        <v>1016.590026855469</v>
+        <v>1027.77001953125</v>
       </c>
       <c r="BE2">
-        <v>1000.260009765625</v>
+        <v>977.4099731445312</v>
       </c>
       <c r="BF2">
-        <v>1027.77001953125</v>
+        <v>975.260009765625</v>
       </c>
       <c r="BG2">
-        <v>977.4099731445312</v>
+        <v>924.030029296875</v>
       </c>
       <c r="BH2">
-        <v>975.260009765625</v>
-      </c>
-      <c r="BI2">
-        <v>924.030029296875</v>
-      </c>
-    </row>
-    <row r="3" spans="1:61">
+        <v>927.5999755859375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:60">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2184.75</v>
+        <v>1963.599975585938</v>
       </c>
       <c r="C3">
+        <v>1914.4599609375</v>
+      </c>
+      <c r="D3">
+        <v>2335</v>
+      </c>
+      <c r="E3">
+        <v>2090.7099609375</v>
+      </c>
+      <c r="F3">
+        <v>2050.389892578125</v>
+      </c>
+      <c r="G3">
         <v>2273.72998046875</v>
       </c>
-      <c r="D3">
-        <v>1963.599975585938</v>
-      </c>
-      <c r="E3">
-        <v>1914.4599609375</v>
-      </c>
-      <c r="F3">
-        <v>2335</v>
-      </c>
-      <c r="G3">
-        <v>2090.7099609375</v>
-      </c>
       <c r="H3">
-        <v>2050.389892578125</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="I3">
-        <v>2273.72998046875</v>
+        <v>1745</v>
       </c>
       <c r="J3">
-        <v>2032.219970703125</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="K3">
-        <v>1745</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="L3">
-        <v>1744.430053710938</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="M3">
-        <v>1617.699951171875</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="N3">
-        <v>1727.180053710938</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="O3">
-        <v>1858.27001953125</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="P3">
-        <v>1915.920043945312</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="Q3">
-        <v>1673.969970703125</v>
+        <v>1615</v>
       </c>
       <c r="R3">
-        <v>1757.819946289062</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="S3">
-        <v>1615</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="T3">
-        <v>1411.079956054688</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="U3">
-        <v>1354.819946289062</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="V3">
-        <v>1390.949951171875</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="W3">
-        <v>1589.400024414062</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="X3">
-        <v>1599.27001953125</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="Y3">
-        <v>1610.329956054688</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="Z3">
-        <v>1436.56005859375</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="AA3">
-        <v>1278.22998046875</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AB3">
-        <v>1096.099975585938</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AC3">
-        <v>1015.890014648438</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AD3">
-        <v>1279.9599609375</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AE3">
-        <v>1214.829956054688</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AF3">
-        <v>1288.030029296875</v>
+        <v>1350.5</v>
       </c>
       <c r="AG3">
-        <v>1427.619995117188</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AH3">
-        <v>1350.5</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AI3">
-        <v>1258.579956054688</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AJ3">
-        <v>1212.2099609375</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AK3">
-        <v>1237.920043945312</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AL3">
-        <v>1271.050048828125</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AM3">
-        <v>1344.2900390625</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AN3">
-        <v>1528.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AO3">
-        <v>1641.109985351562</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AP3">
-        <v>1786.849975585938</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AQ3">
-        <v>1625.780029296875</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AR3">
-        <v>1568.869995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AS3">
-        <v>1600.619995117188</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AT3">
-        <v>1596.079956054688</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="AU3">
-        <v>1493.119995117188</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AV3">
-        <v>1480.77001953125</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="AW3">
-        <v>1499.369995117188</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="AX3">
-        <v>1484.949951171875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="AY3">
-        <v>1484.97998046875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="AZ3">
-        <v>1566.699951171875</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="BA3">
-        <v>1536.869995117188</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="BB3">
-        <v>1553.400024414062</v>
+        <v>1740</v>
       </c>
       <c r="BC3">
-        <v>1554.989990234375</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="BD3">
-        <v>1740</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="BE3">
-        <v>1737.989990234375</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="BF3">
-        <v>1764.170043945312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="BG3">
-        <v>1692.589965820312</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="BH3">
-        <v>1633.349975585938</v>
-      </c>
-      <c r="BI3">
-        <v>1551.989990234375</v>
-      </c>
-    </row>
-    <row r="4" spans="1:61">
+        <v>1530.89501953125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:60">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>745.990478515625</v>
+        <v>670.5347290039062</v>
       </c>
       <c r="C4">
-        <v>732.3848876953125</v>
+        <v>643.6234130859375</v>
       </c>
       <c r="D4">
-        <v>670.5347290039062</v>
+        <v>675.1732788085938</v>
       </c>
       <c r="E4">
-        <v>643.6234130859375</v>
+        <v>586.2618408203125</v>
       </c>
       <c r="F4">
-        <v>675.1732788085938</v>
+        <v>651.6708374023438</v>
       </c>
       <c r="G4">
-        <v>586.2618408203125</v>
+        <v>638.5150146484375</v>
       </c>
       <c r="H4">
-        <v>651.6708374023438</v>
+        <v>598.177978515625</v>
       </c>
       <c r="I4">
-        <v>638.5150146484375</v>
+        <v>538.8270263671875</v>
       </c>
       <c r="J4">
-        <v>598.177978515625</v>
+        <v>577.2747192382812</v>
       </c>
       <c r="K4">
-        <v>538.8270263671875</v>
+        <v>531.92919921875</v>
       </c>
       <c r="L4">
-        <v>577.2747192382812</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="M4">
-        <v>531.92919921875</v>
+        <v>577.864501953125</v>
       </c>
       <c r="N4">
-        <v>550.1234130859375</v>
+        <v>582.403076171875</v>
       </c>
       <c r="O4">
-        <v>577.864501953125</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="P4">
-        <v>582.403076171875</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="Q4">
-        <v>555.3717041015625</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="R4">
-        <v>563.1392211914062</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="S4">
-        <v>513.6751098632812</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="T4">
-        <v>466.6601867675781</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="U4">
-        <v>477.0668640136719</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="V4">
-        <v>487.2635803222656</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="W4">
-        <v>548.2140502929688</v>
+        <v>558.120849609375</v>
       </c>
       <c r="X4">
-        <v>556.4913330078125</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="Y4">
-        <v>558.120849609375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="Z4">
-        <v>519.6331787109375</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="AA4">
-        <v>497.7602233886719</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="AB4">
-        <v>463.3612670898438</v>
+        <v>532.868896484375</v>
       </c>
       <c r="AC4">
-        <v>461.8917236328125</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="AD4">
-        <v>532.868896484375</v>
+        <v>527.05078125</v>
       </c>
       <c r="AE4">
-        <v>544.6651611328125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="AF4">
-        <v>527.05078125</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="AG4">
-        <v>548.3839721679688</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="AH4">
-        <v>519.0033569335938</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="AI4">
-        <v>451.3750915527344</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AJ4">
-        <v>434.1606140136719</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AK4">
-        <v>438.1993408203125</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AL4">
-        <v>437.7894592285156</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AM4">
-        <v>453.9542846679688</v>
+        <v>508.63671875</v>
       </c>
       <c r="AN4">
-        <v>487.1336364746094</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AO4">
-        <v>508.63671875</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AP4">
-        <v>535.8380126953125</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AQ4">
-        <v>496.0007934570312</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AR4">
-        <v>461.9417114257812</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AS4">
-        <v>468.8994750976562</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AT4">
-        <v>459.2925720214844</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="AU4">
-        <v>435.2402954101562</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AV4">
-        <v>450.6053466796875</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="AW4">
-        <v>468.7295227050781</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="AX4">
-        <v>461.8517456054688</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="AY4">
-        <v>459.3025817871094</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="AZ4">
-        <v>450.4053955078125</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="BA4">
-        <v>450.2954406738281</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="BB4">
-        <v>448.7559509277344</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="BC4">
-        <v>441.4283142089844</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="BD4">
-        <v>467.3099670410156</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="BE4">
-        <v>477.2999877929688</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="BF4">
-        <v>482.2799987792969</v>
+        <v>447.1799926757812</v>
       </c>
       <c r="BG4">
-        <v>460.9299926757812</v>
+        <v>426.9400024414062</v>
       </c>
       <c r="BH4">
-        <v>447.1799926757812</v>
-      </c>
-      <c r="BI4">
-        <v>426.9400024414062</v>
-      </c>
-    </row>
-    <row r="5" spans="1:61">
+        <v>411.9599914550781</v>
+      </c>
+    </row>
+    <row r="5" spans="1:60">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>235.3903045654297</v>
+        <v>242.7418823242188</v>
       </c>
       <c r="C5">
-        <v>242.8415069580078</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="D5">
-        <v>242.7418823242188</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="E5">
-        <v>241.4967041015625</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="F5">
-        <v>254.0780792236328</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="G5">
-        <v>258.3714904785156</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="H5">
-        <v>265.2947387695312</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="I5">
-        <v>259.4373779296875</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="J5">
-        <v>268.4027404785156</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="K5">
-        <v>266.7291870117188</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="L5">
-        <v>269.2793579101562</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="M5">
-        <v>265.1951293945312</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="N5">
-        <v>281.7909851074219</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="O5">
-        <v>280.1672668457031</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="P5">
-        <v>279.6094055175781</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="Q5">
-        <v>294.6513061523438</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="R5">
-        <v>300.2695617675781</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="S5">
-        <v>291.5333251953125</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="T5">
-        <v>299.1040954589844</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="U5">
-        <v>308.4579162597656</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="V5">
-        <v>312.1038208007812</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="W5">
-        <v>313.5880737304688</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="X5">
-        <v>309.7230529785156</v>
+        <v>301.33544921875</v>
       </c>
       <c r="Y5">
-        <v>304.0848388671875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="Z5">
-        <v>301.33544921875</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="AA5">
-        <v>303.756103515625</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AB5">
-        <v>297.7294006347656</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AC5">
-        <v>300.1600036621094</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AD5">
-        <v>310.5099792480469</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AE5">
-        <v>312.8999938964844</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AF5">
-        <v>307.5400085449219</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AG5">
-        <v>308.7300109863281</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AH5">
-        <v>302.3900146484375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AI5">
-        <v>302.989990234375</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AJ5">
-        <v>298.3099975585938</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AK5">
-        <v>314.9500122070312</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AL5">
-        <v>323.9200134277344</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AM5">
-        <v>330.2099914550781</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AN5">
-        <v>342.9200134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AO5">
-        <v>341.6700134277344</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AP5">
-        <v>347.1900024414062</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AQ5">
-        <v>350.0499877929688</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AR5">
-        <v>346.260009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AS5">
-        <v>341.510009765625</v>
+        <v>346</v>
       </c>
       <c r="AT5">
-        <v>348.8599853515625</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="AU5">
-        <v>346</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AV5">
-        <v>340.4100036621094</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="AW5">
-        <v>348.0299987792969</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="AX5">
-        <v>346.5899963378906</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="AY5">
-        <v>352.3599853515625</v>
+        <v>361.989990234375</v>
       </c>
       <c r="AZ5">
-        <v>358.9200134277344</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="BA5">
-        <v>361.989990234375</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="BB5">
-        <v>366.0899963378906</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="BC5">
-        <v>370.6900024414062</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="BD5">
-        <v>370.7200012207031</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="BE5">
-        <v>382.8500061035156</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="BF5">
-        <v>388.9500122070312</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="BG5">
-        <v>385.4299926757812</v>
+        <v>382.9500122070312</v>
       </c>
       <c r="BH5">
-        <v>390.4200134277344</v>
-      </c>
-      <c r="BI5">
-        <v>382.9500122070312</v>
-      </c>
-    </row>
-    <row r="6" spans="1:61">
+        <v>397.0400085449219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:60">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>242.2467041015625</v>
+        <v>247.8413848876953</v>
       </c>
       <c r="C6">
-        <v>246.6147308349609</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="D6">
-        <v>247.8413848876953</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="E6">
-        <v>245.8368530273438</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="F6">
-        <v>252.8676147460938</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="G6">
-        <v>253.3662414550781</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="H6">
-        <v>258.5121459960938</v>
+        <v>264.146728515625</v>
       </c>
       <c r="I6">
-        <v>254.9718475341797</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="J6">
-        <v>264.146728515625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="K6">
-        <v>265.6226806640625</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="L6">
-        <v>268.2554626464844</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="M6">
-        <v>265.6027221679688</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="N6">
-        <v>279.9135437011719</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="O6">
-        <v>282.5263977050781</v>
+        <v>296.0693359375</v>
       </c>
       <c r="P6">
-        <v>282.9651794433594</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="Q6">
-        <v>296.0693359375</v>
+        <v>298.363037109375</v>
       </c>
       <c r="R6">
-        <v>302.5715026855469</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="S6">
-        <v>298.363037109375</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="T6">
-        <v>305.0148315429688</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="U6">
-        <v>311.7463989257812</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="V6">
-        <v>314.4490051269531</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="W6">
-        <v>318.8868408203125</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="X6">
-        <v>314.9576110839844</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="Y6">
-        <v>311.4172973632812</v>
+        <v>311.4970703125</v>
       </c>
       <c r="Z6">
-        <v>308.3955688476562</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="AA6">
-        <v>311.4970703125</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AB6">
-        <v>305.2142639160156</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AC6">
-        <v>307.8769836425781</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AD6">
-        <v>313.2223510742188</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AE6">
-        <v>315.6058349609375</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AF6">
-        <v>306.1915893554688</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AG6">
-        <v>311.75634765625</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AH6">
-        <v>296.9369506835938</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AI6">
-        <v>298.432861328125</v>
+        <v>319.4453125</v>
       </c>
       <c r="AJ6">
-        <v>297.3857421875</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AK6">
-        <v>319.4453125</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AL6">
-        <v>335.5013732910156</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AM6">
-        <v>347.2990417480469</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AN6">
-        <v>355.3968811035156</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AO6">
-        <v>354.4494934082031</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AP6">
-        <v>357.2019348144531</v>
+        <v>360.75</v>
       </c>
       <c r="AQ6">
-        <v>365.2099914550781</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AR6">
-        <v>360.75</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AS6">
-        <v>358.2300109863281</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AT6">
-        <v>360.7200012207031</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="AU6">
-        <v>362.5199890136719</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AV6">
-        <v>354.8800048828125</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="AW6">
-        <v>362.2699890136719</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="AX6">
-        <v>363.5400085449219</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="AY6">
-        <v>368.8299865722656</v>
+        <v>383</v>
       </c>
       <c r="AZ6">
-        <v>373.3200073242188</v>
+        <v>387</v>
       </c>
       <c r="BA6">
-        <v>383</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="BB6">
-        <v>387</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="BC6">
-        <v>387.7099914550781</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="BD6">
-        <v>388.8999938964844</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="BE6">
-        <v>397.7699890136719</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="BF6">
-        <v>399.4400024414062</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="BG6">
-        <v>392.4200134277344</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="BH6">
-        <v>395.9299926757812</v>
-      </c>
-      <c r="BI6">
-        <v>396.4500122070312</v>
-      </c>
-    </row>
-    <row r="7" spans="1:61">
+        <v>410.8399963378906</v>
+      </c>
+    </row>
+    <row r="7" spans="1:60">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>51.58330154418945</v>
+        <v>51.99142837524414</v>
       </c>
       <c r="C7">
-        <v>51.76248168945312</v>
+        <v>50.85663604736328</v>
       </c>
       <c r="D7">
-        <v>51.99142837524414</v>
+        <v>50.97608947753906</v>
       </c>
       <c r="E7">
-        <v>50.85663604736328</v>
+        <v>49.76166152954102</v>
       </c>
       <c r="F7">
-        <v>50.97608947753906</v>
+        <v>48.86577224731445</v>
       </c>
       <c r="G7">
-        <v>49.76166152954102</v>
+        <v>48.34814834594727</v>
       </c>
       <c r="H7">
-        <v>48.86577224731445</v>
+        <v>47.72102355957031</v>
       </c>
       <c r="I7">
-        <v>48.34814834594727</v>
+        <v>48.68659591674805</v>
       </c>
       <c r="J7">
-        <v>47.72102355957031</v>
+        <v>48.58705139160156</v>
       </c>
       <c r="K7">
-        <v>48.68659591674805</v>
+        <v>51.44394302368164</v>
       </c>
       <c r="L7">
-        <v>48.58705139160156</v>
+        <v>53.34521865844727</v>
       </c>
       <c r="M7">
-        <v>51.44394302368164</v>
+        <v>52.06110763549805</v>
       </c>
       <c r="N7">
-        <v>53.34521865844727</v>
+        <v>52.64841461181641</v>
       </c>
       <c r="O7">
-        <v>52.06110763549805</v>
+        <v>54.55964660644531</v>
       </c>
       <c r="P7">
-        <v>52.64841461181641</v>
+        <v>54.32073974609375</v>
       </c>
       <c r="Q7">
-        <v>54.55964660644531</v>
+        <v>53.52439498901367</v>
       </c>
       <c r="R7">
-        <v>54.32073974609375</v>
+        <v>53.40494537353516</v>
       </c>
       <c r="S7">
-        <v>53.52439498901367</v>
+        <v>54.60941696166992</v>
       </c>
       <c r="T7">
-        <v>53.40494537353516</v>
+        <v>54.93790817260742</v>
       </c>
       <c r="U7">
-        <v>54.60941696166992</v>
+        <v>56.24192428588867</v>
       </c>
       <c r="V7">
-        <v>54.93790817260742</v>
+        <v>57.23735809326172</v>
       </c>
       <c r="W7">
-        <v>56.24192428588867</v>
+        <v>57.33689880371094</v>
       </c>
       <c r="X7">
-        <v>57.23735809326172</v>
+        <v>57.03827285766602</v>
       </c>
       <c r="Y7">
-        <v>57.33689880371094</v>
+        <v>54.67909622192383</v>
       </c>
       <c r="Z7">
-        <v>57.03827285766602</v>
+        <v>53.68366622924805</v>
       </c>
       <c r="AA7">
-        <v>54.67909622192383</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="AB7">
-        <v>53.68366622924805</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="AC7">
-        <v>55.77407073974609</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="AD7">
-        <v>55.69443893432617</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="AE7">
-        <v>56.80932235717773</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="AF7">
-        <v>55.21663284301758</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="AG7">
-        <v>54.8383674621582</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="AH7">
-        <v>53.56421279907227</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="AI7">
-        <v>55.78402709960938</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="AJ7">
-        <v>55.65462112426758</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="AK7">
-        <v>58.38210678100586</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="AL7">
-        <v>58.79023361206055</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="AM7">
-        <v>58.28256225585938</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="AN7">
-        <v>57.43644714355469</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="AO7">
-        <v>58.09342956542969</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="AP7">
-        <v>58.77032470703125</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="AQ7">
-        <v>59.52685165405273</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="AR7">
-        <v>59.81552886962891</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="AS7">
-        <v>61.23899841308594</v>
+        <v>59.8354377746582</v>
       </c>
       <c r="AT7">
+        <v>58.1431999206543</v>
+      </c>
+      <c r="AU7">
+        <v>58.35224151611328</v>
+      </c>
+      <c r="AV7">
+        <v>58.89972686767578</v>
+      </c>
+      <c r="AW7">
+        <v>58.83004760742188</v>
+      </c>
+      <c r="AX7">
+        <v>59.90511703491211</v>
+      </c>
+      <c r="AY7">
+        <v>60.67160034179688</v>
+      </c>
+      <c r="AZ7">
+        <v>60.63178253173828</v>
+      </c>
+      <c r="BA7">
+        <v>60.33315277099609</v>
+      </c>
+      <c r="BB7">
+        <v>59.7657585144043</v>
+      </c>
+      <c r="BC7">
+        <v>60.37297058105469</v>
+      </c>
+      <c r="BD7">
         <v>61.02000045776367</v>
       </c>
-      <c r="AU7">
-        <v>59.8354377746582</v>
-      </c>
-      <c r="AV7">
-        <v>58.1431999206543</v>
-      </c>
-      <c r="AW7">
-        <v>58.35224151611328</v>
-      </c>
-      <c r="AX7">
-        <v>58.89972686767578</v>
-      </c>
-      <c r="AY7">
-        <v>58.83004760742188</v>
-      </c>
-      <c r="AZ7">
-        <v>59.90511703491211</v>
-      </c>
-      <c r="BA7">
-        <v>60.67160034179688</v>
-      </c>
-      <c r="BB7">
-        <v>60.63178253173828</v>
-      </c>
-      <c r="BC7">
-        <v>60.33315277099609</v>
-      </c>
-      <c r="BD7">
-        <v>59.7657585144043</v>
-      </c>
       <c r="BE7">
-        <v>60.37297058105469</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="BF7">
-        <v>61.02000045776367</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="BG7">
-        <v>61.15999984741211</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="BH7">
-        <v>61.45999908447266</v>
-      </c>
-      <c r="BI7">
-        <v>61.77999877929688</v>
-      </c>
-    </row>
-    <row r="8" spans="1:61">
+        <v>63.52000045776367</v>
+      </c>
+    </row>
+    <row r="8" spans="1:60">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>165.2628631591797</v>
+        <v>169.440673828125</v>
       </c>
       <c r="C8">
-        <v>167.5208740234375</v>
+        <v>167.7496643066406</v>
       </c>
       <c r="D8">
-        <v>169.440673828125</v>
+        <v>170.8531799316406</v>
       </c>
       <c r="E8">
-        <v>167.7496643066406</v>
+        <v>170.7437591552734</v>
       </c>
       <c r="F8">
-        <v>170.8531799316406</v>
+        <v>173.131103515625</v>
       </c>
       <c r="G8">
-        <v>170.7437591552734</v>
+        <v>168.1575012207031</v>
       </c>
       <c r="H8">
-        <v>173.131103515625</v>
+        <v>173.5787200927734</v>
       </c>
       <c r="I8">
-        <v>168.1575012207031</v>
+        <v>175.4885864257812</v>
       </c>
       <c r="J8">
-        <v>173.5787200927734</v>
+        <v>176.3937835693359</v>
       </c>
       <c r="K8">
-        <v>175.4885864257812</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="L8">
-        <v>176.3937835693359</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="M8">
-        <v>177.8957977294922</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="N8">
-        <v>186.8184509277344</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="O8">
-        <v>188.8178405761719</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="P8">
-        <v>187.3655395507812</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="Q8">
-        <v>197.2431182861328</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="R8">
-        <v>200.3864288330078</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="S8">
-        <v>195.1243743896484</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="T8">
-        <v>200.2571258544922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="U8">
-        <v>205.7678680419922</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="V8">
-        <v>207.6976318359375</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="W8">
-        <v>211.1493225097656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="X8">
-        <v>210.2938537597656</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="Y8">
-        <v>205.8872375488281</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="Z8">
-        <v>205.6783599853516</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="AA8">
-        <v>206.7228088378906</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="AB8">
-        <v>204.7632141113281</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="AC8">
-        <v>205.7181396484375</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="AD8">
-        <v>209.4881286621094</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="AE8">
-        <v>210.5624237060547</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="AF8">
-        <v>205.1014099121094</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="AG8">
-        <v>204.8029937744141</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="AH8">
-        <v>201.4806365966797</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="AI8">
-        <v>204.4349517822266</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AJ8">
-        <v>202.8334503173828</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AK8">
-        <v>214.3821563720703</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AL8">
-        <v>223.1754760742188</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AM8">
-        <v>224.3890380859375</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AN8">
-        <v>231.3819274902344</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AO8">
-        <v>232.3766479492188</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AP8">
-        <v>239.2800140380859</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AQ8">
-        <v>243.4900054931641</v>
+        <v>240</v>
       </c>
       <c r="AR8">
-        <v>242.2899932861328</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AS8">
-        <v>240</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AT8">
-        <v>242.8699951171875</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="AU8">
-        <v>241.9600067138672</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AV8">
-        <v>236.8999938964844</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="AW8">
-        <v>242.2299957275391</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="AX8">
-        <v>239.8099975585938</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="AY8">
-        <v>244.0099945068359</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="AZ8">
-        <v>246.5800018310547</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="BA8">
-        <v>252.0200042724609</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="BB8">
-        <v>256.0899963378906</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="BC8">
-        <v>254.6600036621094</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="BD8">
-        <v>255.0899963378906</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="BE8">
-        <v>259.1400146484375</v>
+        <v>258.510009765625</v>
       </c>
       <c r="BF8">
-        <v>260.7799987792969</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="BG8">
-        <v>258.510009765625</v>
+        <v>257.0599975585938</v>
       </c>
       <c r="BH8">
-        <v>259.4700012207031</v>
-      </c>
-      <c r="BI8">
-        <v>257.0599975585938</v>
-      </c>
-    </row>
-    <row r="9" spans="1:61">
+        <v>264.9299926757812</v>
+      </c>
+    </row>
+    <row r="9" spans="1:60">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32.79914855957031</v>
+        <v>33.9808349609375</v>
       </c>
       <c r="C9">
-        <v>33.96097183227539</v>
+        <v>33.09705352783203</v>
       </c>
       <c r="D9">
-        <v>33.9808349609375</v>
+        <v>33.18642044067383</v>
       </c>
       <c r="E9">
-        <v>33.09705352783203</v>
+        <v>32.77928924560547</v>
       </c>
       <c r="F9">
-        <v>33.18642044067383</v>
+        <v>32.72963714599609</v>
       </c>
       <c r="G9">
-        <v>32.77928924560547</v>
+        <v>32.34236526489258</v>
       </c>
       <c r="H9">
-        <v>32.72963714599609</v>
+        <v>31.64725685119629</v>
       </c>
       <c r="I9">
-        <v>32.34236526489258</v>
+        <v>32.13383102416992</v>
       </c>
       <c r="J9">
-        <v>31.64725685119629</v>
+        <v>32.23313140869141</v>
       </c>
       <c r="K9">
-        <v>32.13383102416992</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="L9">
-        <v>32.23313140869141</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="M9">
-        <v>33.76237106323242</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="N9">
-        <v>34.81496429443359</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="O9">
-        <v>33.05733489990234</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="P9">
-        <v>33.20628356933594</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="Q9">
-        <v>34.42768478393555</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="R9">
-        <v>34.28866577148438</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="S9">
-        <v>34.03048324584961</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="T9">
-        <v>34.04041290283203</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="U9">
-        <v>34.97384262084961</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="V9">
-        <v>34.59650039672852</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="W9">
-        <v>35.52000045776367</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="X9">
-        <v>36.18000030517578</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="Y9">
-        <v>36.41999816894531</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="Z9">
-        <v>36.15000152587891</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="AA9">
-        <v>34.7400016784668</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="AB9">
-        <v>34.93000030517578</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="AC9">
-        <v>36.70000076293945</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="AD9">
-        <v>36.33000183105469</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="AE9">
-        <v>37.31999969482422</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="AF9">
-        <v>36.86999893188477</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="AG9">
-        <v>35.79999923706055</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="AH9">
-        <v>34.65999984741211</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="AI9">
-        <v>36.52999877929688</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AJ9">
-        <v>37.63000106811523</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AK9">
-        <v>41.02000045776367</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AL9">
-        <v>40.61999893188477</v>
+        <v>40</v>
       </c>
       <c r="AM9">
-        <v>39.97000122070312</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AN9">
-        <v>40</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AO9">
-        <v>40.47000122070312</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AP9">
-        <v>41.58000183105469</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AQ9">
-        <v>42.36999893188477</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AR9">
-        <v>43.45000076293945</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AS9">
-        <v>44.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AT9">
-        <v>43.38999938964844</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="AU9">
-        <v>42.95999908447266</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AV9">
-        <v>41.34999847412109</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="AW9">
-        <v>41.18999862670898</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="AX9">
-        <v>42.38000106811523</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="AY9">
-        <v>42.54000091552734</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="AZ9">
-        <v>43.15000152587891</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="BA9">
-        <v>44.29999923706055</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="BB9">
-        <v>44.70000076293945</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="BC9">
-        <v>44.18000030517578</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="BD9">
-        <v>42.77000045776367</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="BE9">
-        <v>43.54999923706055</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="BF9">
-        <v>44.84000015258789</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="BG9">
-        <v>44.52999877929688</v>
+        <v>45.02999877929688</v>
       </c>
       <c r="BH9">
-        <v>44.72999954223633</v>
-      </c>
-      <c r="BI9">
-        <v>45.02999877929688</v>
-      </c>
-    </row>
-    <row r="10" spans="1:61">
+        <v>47.40999984741211</v>
+      </c>
+    </row>
+    <row r="10" spans="1:60">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>210.4545135498047</v>
+        <v>199.81640625</v>
       </c>
       <c r="C10">
-        <v>208.4167785644531</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="D10">
-        <v>199.81640625</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="E10">
-        <v>198.7775726318359</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="F10">
-        <v>195.5212249755859</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="G10">
-        <v>192.3148040771484</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="H10">
-        <v>194.7520751953125</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="I10">
-        <v>199.8663482666016</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="J10">
-        <v>197.3591613769531</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="K10">
-        <v>194.6122436523438</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="L10">
-        <v>195.3314361572266</v>
+        <v>203.891845703125</v>
       </c>
       <c r="M10">
-        <v>196.7098846435547</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="N10">
-        <v>203.891845703125</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="O10">
-        <v>202.5533447265625</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="P10">
-        <v>210.7242126464844</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="Q10">
-        <v>203.3025054931641</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="R10">
-        <v>211.5632781982422</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="S10">
-        <v>212.2624816894531</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="T10">
-        <v>207.1681823730469</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="U10">
-        <v>202.5833129882812</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="V10">
-        <v>203.0527954101562</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="W10">
-        <v>207.0583038330078</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="X10">
-        <v>211.8229827880859</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="Y10">
-        <v>208.5266571044922</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="Z10">
-        <v>206.6088104248047</v>
+        <v>196.789794921875</v>
       </c>
       <c r="AA10">
-        <v>196.2903594970703</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="AB10">
-        <v>196.789794921875</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="AC10">
-        <v>189.7976226806641</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="AD10">
-        <v>194.8219909667969</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="AE10">
-        <v>200.5256195068359</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="AF10">
-        <v>206.4090423583984</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="AG10">
-        <v>211.7031097412109</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="AH10">
-        <v>218.9749755859375</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="AI10">
-        <v>218.7452392578125</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="AJ10">
-        <v>223.7096862792969</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="AK10">
+        <v>223.8395233154297</v>
+      </c>
+      <c r="AL10">
+        <v>225.0481872558594</v>
+      </c>
+      <c r="AM10">
+        <v>224.9083404541016</v>
+      </c>
+      <c r="AN10">
+        <v>224.7584991455078</v>
+      </c>
+      <c r="AO10">
+        <v>219.4944000244141</v>
+      </c>
+      <c r="AP10">
+        <v>217.3168334960938</v>
+      </c>
+      <c r="AQ10">
+        <v>216.6076354980469</v>
+      </c>
+      <c r="AR10">
+        <v>214.4800109863281</v>
+      </c>
+      <c r="AS10">
+        <v>208.2469787597656</v>
+      </c>
+      <c r="AT10">
+        <v>212.8118743896484</v>
+      </c>
+      <c r="AU10">
+        <v>209.4256591796875</v>
+      </c>
+      <c r="AV10">
+        <v>227.7251739501953</v>
+      </c>
+      <c r="AW10">
         <v>217.3068389892578</v>
       </c>
-      <c r="AL10">
-        <v>217.2568969726562</v>
-      </c>
-      <c r="AM10">
-        <v>223.8395233154297</v>
-      </c>
-      <c r="AN10">
-        <v>225.0481872558594</v>
-      </c>
-      <c r="AO10">
-        <v>224.9083404541016</v>
-      </c>
-      <c r="AP10">
-        <v>224.7584991455078</v>
-      </c>
-      <c r="AQ10">
-        <v>219.4944000244141</v>
-      </c>
-      <c r="AR10">
-        <v>217.3168334960938</v>
-      </c>
-      <c r="AS10">
-        <v>216.6076354980469</v>
-      </c>
-      <c r="AT10">
-        <v>214.4800109863281</v>
-      </c>
-      <c r="AU10">
-        <v>208.2469787597656</v>
-      </c>
-      <c r="AV10">
-        <v>212.8118743896484</v>
-      </c>
-      <c r="AW10">
-        <v>209.4256591796875</v>
-      </c>
       <c r="AX10">
-        <v>227.7251739501953</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="AY10">
-        <v>217.3068389892578</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="AZ10">
-        <v>220.5332336425781</v>
+        <v>224.1591796875</v>
       </c>
       <c r="BA10">
-        <v>217.1969757080078</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="BB10">
-        <v>224.1591796875</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="BC10">
-        <v>228.1946563720703</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="BD10">
-        <v>230.1025238037109</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="BE10">
-        <v>225.4776916503906</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="BF10">
-        <v>223.4199981689453</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="BG10">
-        <v>218.3600006103516</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="BH10">
-        <v>218.2899932861328</v>
-      </c>
-      <c r="BI10">
-        <v>210.9600067138672</v>
-      </c>
-    </row>
-    <row r="11" spans="1:61">
+        <v>212.1699981689453</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>306.7611694335938</v>
+        <v>315.8800048828125</v>
       </c>
       <c r="C11">
-        <v>309.5516357421875</v>
+        <v>319.6471252441406</v>
       </c>
       <c r="D11">
-        <v>315.8800048828125</v>
+        <v>317.2054748535156</v>
       </c>
       <c r="E11">
-        <v>319.6471252441406</v>
+        <v>326.2545166015625</v>
       </c>
       <c r="F11">
-        <v>317.2054748535156</v>
+        <v>330.7491760253906</v>
       </c>
       <c r="G11">
-        <v>326.2545166015625</v>
+        <v>328.9951477050781</v>
       </c>
       <c r="H11">
-        <v>330.7491760253906</v>
+        <v>333.4798278808594</v>
       </c>
       <c r="I11">
-        <v>328.9951477050781</v>
+        <v>341.1436157226562</v>
       </c>
       <c r="J11">
-        <v>333.4798278808594</v>
+        <v>338.0143432617188</v>
       </c>
       <c r="K11">
-        <v>341.1436157226562</v>
+        <v>342.5588073730469</v>
       </c>
       <c r="L11">
-        <v>338.0143432617188</v>
+        <v>336.7885131835938</v>
       </c>
       <c r="M11">
-        <v>342.5588073730469</v>
+        <v>336.3301086425781</v>
       </c>
       <c r="N11">
-        <v>336.7885131835938</v>
+        <v>337.7651977539062</v>
       </c>
       <c r="O11">
-        <v>336.3301086425781</v>
+        <v>340.3463745117188</v>
       </c>
       <c r="P11">
-        <v>337.7651977539062</v>
+        <v>335.6822814941406</v>
       </c>
       <c r="Q11">
-        <v>340.3463745117188</v>
+        <v>328.0683288574219</v>
       </c>
       <c r="R11">
-        <v>335.6822814941406</v>
+        <v>336.6689453125</v>
       </c>
       <c r="S11">
-        <v>328.0683288574219</v>
+        <v>367.7227783203125</v>
       </c>
       <c r="T11">
-        <v>336.6689453125</v>
+        <v>367.244384765625</v>
       </c>
       <c r="U11">
-        <v>367.7227783203125</v>
+        <v>368.3705444335938</v>
       </c>
       <c r="V11">
-        <v>367.244384765625</v>
+        <v>370.8121643066406</v>
       </c>
       <c r="W11">
-        <v>368.3705444335938</v>
+        <v>375.0875549316406</v>
       </c>
       <c r="X11">
-        <v>370.8121643066406</v>
+        <v>385.9404907226562</v>
       </c>
       <c r="Y11">
-        <v>375.0875549316406</v>
+        <v>389.0199584960938</v>
       </c>
       <c r="Z11">
-        <v>385.9404907226562</v>
+        <v>395.8665161132812</v>
       </c>
       <c r="AA11">
-        <v>389.0199584960938</v>
+        <v>387.6845092773438</v>
       </c>
       <c r="AB11">
-        <v>395.8665161132812</v>
+        <v>374.7088623046875</v>
       </c>
       <c r="AC11">
-        <v>387.6845092773438</v>
+        <v>373.0844116210938</v>
       </c>
       <c r="AD11">
-        <v>374.7088623046875</v>
+        <v>372.5462646484375</v>
       </c>
       <c r="AE11">
-        <v>373.0844116210938</v>
+        <v>375.8648986816406</v>
       </c>
       <c r="AF11">
-        <v>372.5462646484375</v>
+        <v>381.1468811035156</v>
       </c>
       <c r="AG11">
-        <v>375.8648986816406</v>
+        <v>384.6847534179688</v>
       </c>
       <c r="AH11">
-        <v>381.1468811035156</v>
+        <v>383.0005187988281</v>
       </c>
       <c r="AI11">
-        <v>384.6847534179688</v>
+        <v>374.3401184082031</v>
       </c>
       <c r="AJ11">
-        <v>383.0005187988281</v>
+        <v>374.3301391601562</v>
       </c>
       <c r="AK11">
-        <v>374.3401184082031</v>
+        <v>368.8987426757812</v>
       </c>
       <c r="AL11">
-        <v>374.3301391601562</v>
+        <v>368.7392883300781</v>
       </c>
       <c r="AM11">
-        <v>368.8987426757812</v>
+        <v>369.0980224609375</v>
       </c>
       <c r="AN11">
-        <v>368.7392883300781</v>
+        <v>363.2680053710938</v>
       </c>
       <c r="AO11">
-        <v>369.0980224609375</v>
+        <v>366.6763305664062</v>
       </c>
       <c r="AP11">
-        <v>363.2680053710938</v>
+        <v>360.9857788085938</v>
       </c>
       <c r="AQ11">
-        <v>366.6763305664062</v>
+        <v>363.248046875</v>
       </c>
       <c r="AR11">
-        <v>360.9857788085938</v>
+        <v>362.3411254882812</v>
       </c>
       <c r="AS11">
-        <v>363.248046875</v>
+        <v>369.2873840332031</v>
       </c>
       <c r="AT11">
-        <v>362.3411254882812</v>
+        <v>368.4004516601562</v>
       </c>
       <c r="AU11">
-        <v>369.2873840332031</v>
+        <v>369.8853454589844</v>
       </c>
       <c r="AV11">
-        <v>368.4004516601562</v>
+        <v>368.071533203125</v>
       </c>
       <c r="AW11">
-        <v>369.8853454589844</v>
+        <v>368.6396179199219</v>
       </c>
       <c r="AX11">
-        <v>368.071533203125</v>
+        <v>364.6831359863281</v>
       </c>
       <c r="AY11">
-        <v>368.6396179199219</v>
+        <v>362.6799926757812</v>
       </c>
       <c r="AZ11">
-        <v>364.6831359863281</v>
+        <v>364.9322814941406</v>
       </c>
       <c r="BA11">
-        <v>362.6799926757812</v>
+        <v>373.0644836425781</v>
       </c>
       <c r="BB11">
-        <v>364.9322814941406</v>
+        <v>368.0914916992188</v>
       </c>
       <c r="BC11">
-        <v>373.0644836425781</v>
+        <v>364.4140625</v>
       </c>
       <c r="BD11">
-        <v>368.0914916992188</v>
+        <v>365.6000061035156</v>
       </c>
       <c r="BE11">
-        <v>364.4140625</v>
+        <v>367.5599975585938</v>
       </c>
       <c r="BF11">
-        <v>365.6000061035156</v>
+        <v>375.2000122070312</v>
       </c>
       <c r="BG11">
-        <v>367.5599975585938</v>
+        <v>378.0499877929688</v>
       </c>
       <c r="BH11">
-        <v>375.2000122070312</v>
-      </c>
-      <c r="BI11">
-        <v>378.0499877929688</v>
-      </c>
-    </row>
-    <row r="12" spans="1:61">
+        <v>377.9700012207031</v>
+      </c>
+    </row>
+    <row r="12" spans="1:60">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>367.2215881347656</v>
+        <v>345.8554382324219</v>
       </c>
       <c r="C12">
-        <v>348.5537109375</v>
+        <v>344.816162109375</v>
       </c>
       <c r="D12">
-        <v>345.8554382324219</v>
+        <v>341.9679870605469</v>
       </c>
       <c r="E12">
-        <v>344.816162109375</v>
+        <v>334.4728698730469</v>
       </c>
       <c r="F12">
-        <v>341.9679870605469</v>
+        <v>351.0520935058594</v>
       </c>
       <c r="G12">
-        <v>334.4728698730469</v>
+        <v>353.1007385253906</v>
       </c>
       <c r="H12">
-        <v>351.0520935058594</v>
+        <v>357.6578063964844</v>
       </c>
       <c r="I12">
-        <v>353.1007385253906</v>
+        <v>355.9489135742188</v>
       </c>
       <c r="J12">
-        <v>357.6578063964844</v>
+        <v>364.6632385253906</v>
       </c>
       <c r="K12">
-        <v>355.9489135742188</v>
+        <v>363.3840942382812</v>
       </c>
       <c r="L12">
-        <v>364.6632385253906</v>
+        <v>358.4772644042969</v>
       </c>
       <c r="M12">
-        <v>363.3840942382812</v>
+        <v>356.0088500976562</v>
       </c>
       <c r="N12">
-        <v>358.4772644042969</v>
+        <v>354.7996520996094</v>
       </c>
       <c r="O12">
-        <v>356.0088500976562</v>
+        <v>350.4425048828125</v>
       </c>
       <c r="P12">
-        <v>354.7996520996094</v>
+        <v>357.09814453125</v>
       </c>
       <c r="Q12">
-        <v>350.4425048828125</v>
+        <v>369.9697875976562</v>
       </c>
       <c r="R12">
-        <v>357.09814453125</v>
+        <v>353.5804443359375</v>
       </c>
       <c r="S12">
-        <v>369.9697875976562</v>
+        <v>345.8954467773438</v>
       </c>
       <c r="T12">
-        <v>353.5804443359375</v>
+        <v>351.1420288085938</v>
       </c>
       <c r="U12">
-        <v>345.8954467773438</v>
+        <v>345.9653930664062</v>
       </c>
       <c r="V12">
-        <v>351.1420288085938</v>
+        <v>341.6881713867188</v>
       </c>
       <c r="W12">
-        <v>345.9653930664062</v>
+        <v>318.1334533691406</v>
       </c>
       <c r="X12">
-        <v>341.6881713867188</v>
+        <v>318.8829650878906</v>
       </c>
       <c r="Y12">
-        <v>318.1334533691406</v>
+        <v>326.3581237792969</v>
       </c>
       <c r="Z12">
-        <v>318.8829650878906</v>
+        <v>332.3842163085938</v>
       </c>
       <c r="AA12">
-        <v>326.3581237792969</v>
+        <v>335.5421752929688</v>
       </c>
       <c r="AB12">
-        <v>332.3842163085938</v>
+        <v>333.4635009765625</v>
       </c>
       <c r="AC12">
-        <v>335.5421752929688</v>
+        <v>356.4186096191406</v>
       </c>
       <c r="AD12">
-        <v>333.4635009765625</v>
+        <v>372.2283325195312</v>
       </c>
       <c r="AE12">
-        <v>356.4186096191406</v>
+        <v>375.1064758300781</v>
       </c>
       <c r="AF12">
-        <v>372.2283325195312</v>
+        <v>359.8963623046875</v>
       </c>
       <c r="AG12">
-        <v>375.1064758300781</v>
+        <v>356.3886108398438</v>
       </c>
       <c r="AH12">
-        <v>359.8963623046875</v>
+        <v>353.2406616210938</v>
       </c>
       <c r="AI12">
-        <v>356.3886108398438</v>
+        <v>355.609130859375</v>
       </c>
       <c r="AJ12">
-        <v>353.2406616210938</v>
+        <v>342.7774658203125</v>
       </c>
       <c r="AK12">
-        <v>355.609130859375</v>
+        <v>342.1478576660156</v>
       </c>
       <c r="AL12">
-        <v>342.7774658203125</v>
+        <v>343.7168579101562</v>
       </c>
       <c r="AM12">
-        <v>342.1478576660156</v>
+        <v>343.3171081542969</v>
       </c>
       <c r="AN12">
-        <v>343.7168579101562</v>
+        <v>341.2284851074219</v>
       </c>
       <c r="AO12">
-        <v>343.3171081542969</v>
+        <v>341.0585632324219</v>
       </c>
       <c r="AP12">
-        <v>341.2284851074219</v>
+        <v>341.4783325195312</v>
       </c>
       <c r="AQ12">
-        <v>341.0585632324219</v>
+        <v>337.9805908203125</v>
       </c>
       <c r="AR12">
-        <v>341.4783325195312</v>
+        <v>341.5282592773438</v>
       </c>
       <c r="AS12">
-        <v>337.9805908203125</v>
+        <v>344.3664245605469</v>
       </c>
       <c r="AT12">
-        <v>341.5282592773438</v>
+        <v>343.1172485351562</v>
       </c>
       <c r="AU12">
-        <v>344.3664245605469</v>
+        <v>338.8800048828125</v>
       </c>
       <c r="AV12">
-        <v>343.1172485351562</v>
+        <v>337.4908752441406</v>
       </c>
       <c r="AW12">
-        <v>338.8800048828125</v>
+        <v>342.6575317382812</v>
       </c>
       <c r="AX12">
-        <v>337.4908752441406</v>
+        <v>335.1923828125</v>
       </c>
       <c r="AY12">
-        <v>342.6575317382812</v>
+        <v>331.8145751953125</v>
       </c>
       <c r="AZ12">
-        <v>335.1923828125</v>
+        <v>333.5634460449219</v>
       </c>
       <c r="BA12">
-        <v>331.8145751953125</v>
+        <v>338.8599853515625</v>
       </c>
       <c r="BB12">
-        <v>333.5634460449219</v>
+        <v>335.3099975585938</v>
       </c>
       <c r="BC12">
-        <v>338.8599853515625</v>
+        <v>335.3800048828125</v>
       </c>
       <c r="BD12">
-        <v>335.3099975585938</v>
+        <v>328.3800048828125</v>
       </c>
       <c r="BE12">
-        <v>335.3800048828125</v>
+        <v>330.3900146484375</v>
       </c>
       <c r="BF12">
-        <v>328.3800048828125</v>
+        <v>335.4500122070312</v>
       </c>
       <c r="BG12">
-        <v>330.3900146484375</v>
+        <v>345.7099914550781</v>
       </c>
       <c r="BH12">
-        <v>335.4500122070312</v>
-      </c>
-      <c r="BI12">
-        <v>345.7099914550781</v>
-      </c>
-    </row>
-    <row r="13" spans="1:61">
+        <v>341.4299926757812</v>
+      </c>
+    </row>
+    <row r="13" spans="1:60">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>61.02000045776367</v>
+        <v>63.13999938964844</v>
       </c>
       <c r="C13">
-        <v>63.68000030517578</v>
+        <v>62.97000122070312</v>
       </c>
       <c r="D13">
-        <v>63.13999938964844</v>
+        <v>64.76999664306641</v>
       </c>
       <c r="E13">
-        <v>62.97000122070312</v>
+        <v>65.73000335693359</v>
       </c>
       <c r="F13">
-        <v>64.76999664306641</v>
+        <v>64.54000091552734</v>
       </c>
       <c r="G13">
-        <v>65.73000335693359</v>
+        <v>64.19000244140625</v>
       </c>
       <c r="H13">
-        <v>64.54000091552734</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="I13">
-        <v>64.19000244140625</v>
+        <v>67.86000061035156</v>
       </c>
       <c r="J13">
-        <v>68.34999847412109</v>
+        <v>66.05000305175781</v>
       </c>
       <c r="K13">
-        <v>67.86000061035156</v>
+        <v>66.12000274658203</v>
       </c>
       <c r="L13">
-        <v>66.05000305175781</v>
+        <v>67.08999633789062</v>
       </c>
       <c r="M13">
-        <v>66.12000274658203</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="N13">
-        <v>67.08999633789062</v>
+        <v>67.34999847412109</v>
       </c>
       <c r="O13">
-        <v>67.59999847412109</v>
+        <v>68.29000091552734</v>
       </c>
       <c r="P13">
-        <v>67.34999847412109</v>
+        <v>68.72000122070312</v>
       </c>
       <c r="Q13">
-        <v>68.29000091552734</v>
+        <v>66.61000061035156</v>
       </c>
       <c r="R13">
-        <v>68.72000122070312</v>
+        <v>63.88999938964844</v>
       </c>
       <c r="S13">
-        <v>66.61000061035156</v>
+        <v>66.44000244140625</v>
       </c>
       <c r="T13">
-        <v>63.88999938964844</v>
+        <v>65.83999633789062</v>
       </c>
       <c r="U13">
-        <v>66.44000244140625</v>
+        <v>67.58999633789062</v>
       </c>
       <c r="V13">
-        <v>65.83999633789062</v>
+        <v>65.88999938964844</v>
       </c>
       <c r="W13">
-        <v>67.58999633789062</v>
+        <v>63.7400016784668</v>
       </c>
       <c r="X13">
-        <v>65.88999938964844</v>
+        <v>63.40999984741211</v>
       </c>
       <c r="Y13">
-        <v>63.7400016784668</v>
+        <v>64.08000183105469</v>
       </c>
       <c r="Z13">
-        <v>63.40999984741211</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="AA13">
-        <v>64.08000183105469</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="AB13">
-        <v>63.90999984741211</v>
+        <v>60.84000015258789</v>
       </c>
       <c r="AC13">
-        <v>61.81999969482422</v>
+        <v>62.22000122070312</v>
       </c>
       <c r="AD13">
-        <v>60.84000015258789</v>
+        <v>63.7599983215332</v>
       </c>
       <c r="AE13">
-        <v>62.22000122070312</v>
+        <v>64.06999969482422</v>
       </c>
       <c r="AF13">
-        <v>63.7599983215332</v>
+        <v>66.98999786376953</v>
       </c>
       <c r="AG13">
-        <v>64.06999969482422</v>
+        <v>64.19999694824219</v>
       </c>
       <c r="AH13">
-        <v>66.98999786376953</v>
+        <v>65.76999664306641</v>
       </c>
       <c r="AI13">
-        <v>64.19999694824219</v>
+        <v>66.56999969482422</v>
       </c>
       <c r="AJ13">
-        <v>65.76999664306641</v>
+        <v>64.87999725341797</v>
       </c>
       <c r="AK13">
-        <v>66.56999969482422</v>
+        <v>67.06999969482422</v>
       </c>
       <c r="AL13">
-        <v>64.87999725341797</v>
+        <v>66.04000091552734</v>
       </c>
       <c r="AM13">
-        <v>67.06999969482422</v>
+        <v>67.47000122070312</v>
       </c>
       <c r="AN13">
-        <v>66.04000091552734</v>
+        <v>64.41000366210938</v>
       </c>
       <c r="AO13">
-        <v>67.47000122070312</v>
+        <v>65.22000122070312</v>
       </c>
       <c r="AP13">
-        <v>64.41000366210938</v>
+        <v>64.69999694824219</v>
       </c>
       <c r="AQ13">
-        <v>65.22000122070312</v>
+        <v>64.13999938964844</v>
       </c>
       <c r="AR13">
-        <v>64.69999694824219</v>
+        <v>65.01999664306641</v>
       </c>
       <c r="AS13">
-        <v>64.13999938964844</v>
+        <v>65.65000152587891</v>
       </c>
       <c r="AT13">
-        <v>65.01999664306641</v>
+        <v>65</v>
       </c>
       <c r="AU13">
-        <v>65.65000152587891</v>
+        <v>65.47000122070312</v>
       </c>
       <c r="AV13">
-        <v>65</v>
+        <v>65.33000183105469</v>
       </c>
       <c r="AW13">
-        <v>65.47000122070312</v>
+        <v>64.75</v>
       </c>
       <c r="AX13">
-        <v>65.33000183105469</v>
+        <v>64.33999633789062</v>
       </c>
       <c r="AY13">
-        <v>64.75</v>
+        <v>65.23000335693359</v>
       </c>
       <c r="AZ13">
-        <v>64.33999633789062</v>
+        <v>67.33999633789062</v>
       </c>
       <c r="BA13">
-        <v>65.23000335693359</v>
+        <v>68.01999664306641</v>
       </c>
       <c r="BB13">
-        <v>67.33999633789062</v>
+        <v>67.04000091552734</v>
       </c>
       <c r="BC13">
-        <v>68.01999664306641</v>
+        <v>64.58000183105469</v>
       </c>
       <c r="BD13">
-        <v>67.04000091552734</v>
+        <v>64.05999755859375</v>
       </c>
       <c r="BE13">
-        <v>64.58000183105469</v>
+        <v>65.40000152587891</v>
       </c>
       <c r="BF13">
-        <v>64.05999755859375</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="BG13">
-        <v>65.40000152587891</v>
+        <v>69.41000366210938</v>
       </c>
       <c r="BH13">
-        <v>66.41999816894531</v>
-      </c>
-      <c r="BI13">
-        <v>69.41000366210938</v>
+        <v>67.66000366210938</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="247">
   <si>
     <t>DELL</t>
   </si>
@@ -279,6 +279,9 @@
     <t>2026-09-16</t>
   </si>
   <si>
+    <t>2026-09-17</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -342,16 +345,22 @@
     <t>Alphabet Inc. (Class A)</t>
   </si>
   <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
     <t>CRM</t>
   </si>
   <si>
     <t>Salesforce</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
   </si>
   <si>
     <t>ALL</t>
@@ -360,12 +369,6 @@
     <t>Allstate</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
     <t>TGT</t>
   </si>
   <si>
@@ -375,6 +378,18 @@
     <t>Consumer Staples</t>
   </si>
   <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
     <t>AMZN</t>
   </si>
   <si>
@@ -384,10 +399,28 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>BIIB</t>
+  </si>
+  <si>
+    <t>Biogen</t>
+  </si>
+  <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
+  </si>
+  <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
   </si>
   <si>
     <t>HPQ</t>
@@ -396,22 +429,40 @@
     <t>HP Inc.</t>
   </si>
   <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel</t>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>DLTR</t>
+  </si>
+  <si>
+    <t>Dollar Tree</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
+    <t>RVTY</t>
+  </si>
+  <si>
+    <t>Revvity</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>Gen Digital</t>
   </si>
   <si>
     <t>GS</t>
@@ -420,52 +471,40 @@
     <t>Goldman Sachs</t>
   </si>
   <si>
-    <t>BIIB</t>
-  </si>
-  <si>
-    <t>Biogen</t>
-  </si>
-  <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
-  </si>
-  <si>
     <t>EOG</t>
   </si>
   <si>
     <t>EOG Resources</t>
   </si>
   <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>Gen Digital</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>DLTR</t>
-  </si>
-  <si>
-    <t>Dollar Tree</t>
-  </si>
-  <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>News Corp (Class A)</t>
+  </si>
+  <si>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
+  </si>
+  <si>
+    <t>FFIV</t>
+  </si>
+  <si>
+    <t>F5, Inc.</t>
+  </si>
+  <si>
+    <t>AIZ</t>
+  </si>
+  <si>
+    <t>Assurant</t>
+  </si>
+  <si>
+    <t>BBY</t>
+  </si>
+  <si>
+    <t>Best Buy</t>
   </si>
   <si>
     <t>COP</t>
@@ -474,42 +513,6 @@
     <t>ConocoPhillips</t>
   </si>
   <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>Supermicro</t>
-  </si>
-  <si>
-    <t>DVN</t>
-  </si>
-  <si>
-    <t>Devon Energy</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>News Corp (Class A)</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>Morgan Stanley</t>
-  </si>
-  <si>
-    <t>FFIV</t>
-  </si>
-  <si>
-    <t>F5, Inc.</t>
-  </si>
-  <si>
-    <t>PRU</t>
-  </si>
-  <si>
-    <t>Prudential Financial</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -588,7 +591,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-17 00:37 UTC · данные на 2026-09-16 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-18 00:25 UTC · данные на 2026-09-17 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -669,7 +672,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-17 00:37 UTC</t>
+    <t>2026-09-18 00:25 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1181,9 +1184,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$19</c:f>
+              <c:f>Капитал!$A$5:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1228,16 +1231,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>2026-09-16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2026-09-17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$19</c:f>
+              <c:f>Капитал!$D$5:$D$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1281,6 +1287,9 @@
                   <c:v>10163.98</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>10163.98</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -1306,9 +1315,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$19</c:f>
+              <c:f>Капитал!$A$5:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1353,16 +1362,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>2026-09-16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2026-09-17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$19</c:f>
+              <c:f>Капитал!$F$5:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1406,6 +1418,9 @@
                   <c:v>9966.08</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1546,9 +1561,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$19</c:f>
+              <c:f>Капитал!$A$5:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1593,16 +1608,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>2026-09-16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2026-09-17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$19</c:f>
+              <c:f>Капитал!$D$5:$D$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1646,6 +1664,9 @@
                   <c:v>10163.98</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>10163.98</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -1671,9 +1692,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$19</c:f>
+              <c:f>Капитал!$A$5:$A$20</c:f>
               <c:strCache>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1718,16 +1739,19 @@
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>2026-09-16</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2026-09-17</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$19</c:f>
+              <c:f>Капитал!$F$5:$F$20</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="15"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1771,6 +1795,9 @@
                   <c:v>9966.08</c:v>
                 </c:pt>
                 <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2266,12 +2293,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2279,13 +2306,13 @@
         <v>74</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2304,27 +2331,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>2.773364125231443</v>
+        <v>2.67660249974473</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H9" s="7">
         <v>13</v>
@@ -2332,7 +2359,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2361,7 +2388,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2369,7 +2396,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2377,23 +2404,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C18" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C19" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2401,55 +2428,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C25" s="12">
-        <v>0.1076891784535971</v>
+        <v>0.1041434245885151</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C26" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2458,12 +2485,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2638,11 +2665,11 @@
         <v>0.20574673193473192</v>
       </c>
       <c r="L5" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
@@ -2689,11 +2716,11 @@
         <v>-0.0023453865133649322</v>
       </c>
       <c r="L6" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
@@ -2740,11 +2767,11 @@
         <v>0.001157858695424527</v>
       </c>
       <c r="L7" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
@@ -2791,11 +2818,11 @@
         <v>-0.07694846931544182</v>
       </c>
       <c r="L8" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
@@ -2842,11 +2869,11 @@
         <v>0.06333640885022687</v>
       </c>
       <c r="L9" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
@@ -2893,11 +2920,11 @@
         <v>0.04063182043921025</v>
       </c>
       <c r="L10" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
@@ -2944,11 +2971,11 @@
         <v>0.027097931394638883</v>
       </c>
       <c r="L11" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
@@ -2995,11 +3022,11 @@
         <v>0.020460374570953403</v>
       </c>
       <c r="L12" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
@@ -3046,11 +3073,11 @@
         <v>0.030391348943966064</v>
       </c>
       <c r="L13" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
@@ -3097,11 +3124,11 @@
         <v>-0.001824598914652231</v>
       </c>
       <c r="L14" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" s="11">
         <f>MAX(0,21-L14)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N14" s="20">
         <v>0.6809721702367264</v>
@@ -3148,11 +3175,11 @@
         <v>-0.013417568245354424</v>
       </c>
       <c r="L15" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M15" s="11">
         <f>MAX(0,21-L15)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N15" s="20">
         <v>0.8197914702434592</v>
@@ -3199,11 +3226,11 @@
         <v>0.018953362974839495</v>
       </c>
       <c r="L16" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M16" s="11">
         <f>MAX(0,21-L16)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N16" s="20">
         <v>0.776423257523575</v>
@@ -3250,11 +3277,11 @@
         <v>0.03068356896480827</v>
       </c>
       <c r="L17" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M17" s="11">
         <f>MAX(0,21-L17)</f>
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N17" s="20">
         <v>0.7994794227521653</v>
@@ -3636,7 +3663,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3978,6 +4005,25 @@
         <v>13</v>
       </c>
       <c r="F19" s="10"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B20" s="10">
+        <v>3768.96</v>
+      </c>
+      <c r="C20" s="10">
+        <v>6395.02</v>
+      </c>
+      <c r="D20" s="10">
+        <f>B20+C20</f>
+        <v>10163.98</v>
+      </c>
+      <c r="E20" s="11">
+        <v>13</v>
+      </c>
+      <c r="F20" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4006,12 +4052,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4028,52 +4074,52 @@
         <v>17</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -4090,10 +4136,10 @@
         <v>42</v>
       </c>
       <c r="E5" s="10">
-        <v>397.0400085449219</v>
+        <v>403.2799987792969</v>
       </c>
       <c r="F5" s="17">
-        <v>1.01764041912561</v>
+        <v>1.050913661811838</v>
       </c>
       <c r="G5" s="20">
         <v>0.6555418499989493</v>
@@ -4105,16 +4151,16 @@
         <v>2.861941581666567</v>
       </c>
       <c r="J5" s="20">
-        <v>2.288032401453355</v>
+        <v>2.344480223395413</v>
       </c>
       <c r="K5" s="20">
-        <v>0.6078226360490273</v>
+        <v>0.6053625381238342</v>
       </c>
       <c r="L5" s="20">
-        <v>0.1995744490045689</v>
+        <v>0.220086459678554</v>
       </c>
       <c r="M5" s="20">
-        <v>-0.6061146717453501</v>
+        <v>-0.4135723315679154</v>
       </c>
       <c r="N5" s="20">
         <v>16.28786</v>
@@ -4129,13 +4175,13 @@
         <v>0.517</v>
       </c>
       <c r="R5" s="12">
-        <v>0.7219249305616033</v>
+        <v>0.723859783852866</v>
       </c>
       <c r="S5" s="11">
-        <v>75.74333366737011</v>
+        <v>77.54124888161878</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -4152,10 +4198,10 @@
         <v>42</v>
       </c>
       <c r="E6" s="10">
-        <v>410.8399963378906</v>
+        <v>413.9200134277344</v>
       </c>
       <c r="F6" s="17">
-        <v>0.9983420839881402</v>
+        <v>1.02708127080466</v>
       </c>
       <c r="G6" s="20">
         <v>0.6866590119647646</v>
@@ -4167,16 +4213,16 @@
         <v>2.437187840999147</v>
       </c>
       <c r="J6" s="20">
-        <v>2.263230960013805</v>
+        <v>2.307933742479242</v>
       </c>
       <c r="K6" s="20">
-        <v>0.7750429067476208</v>
+        <v>0.7722871304671322</v>
       </c>
       <c r="L6" s="20">
-        <v>0.2750647875044709</v>
+        <v>0.2804577175280851</v>
       </c>
       <c r="M6" s="20">
-        <v>-0.8143798852765898</v>
+        <v>-0.6226865174124547</v>
       </c>
       <c r="N6" s="20">
         <v>13.7380295</v>
@@ -4191,13 +4237,13 @@
         <v>0.537</v>
       </c>
       <c r="R6" s="12">
-        <v>0.8063125517704235</v>
+        <v>0.7861504747971995</v>
       </c>
       <c r="S6" s="11">
-        <v>79.6885292911436</v>
+        <v>80.53931347979024</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -4214,10 +4260,10 @@
         <v>32</v>
       </c>
       <c r="E7" s="10">
-        <v>543.510009765625</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="F7" s="17">
-        <v>0.9350270020838893</v>
+        <v>0.9721358964097886</v>
       </c>
       <c r="G7" s="20">
         <v>-0.1521673872440041</v>
@@ -4229,16 +4275,16 @@
         <v>2.18194679071571</v>
       </c>
       <c r="J7" s="20">
-        <v>2.755754922011613</v>
+        <v>2.9508924467175</v>
       </c>
       <c r="K7" s="20">
-        <v>1.603918692988181</v>
+        <v>1.599697301156443</v>
       </c>
       <c r="L7" s="20">
-        <v>-2.880273852553483</v>
+        <v>-2.913898944425201</v>
       </c>
       <c r="M7" s="20">
-        <v>0.4210694429890847</v>
+        <v>0.1847158110671452</v>
       </c>
       <c r="N7" s="20">
         <v>33.00116</v>
@@ -4253,13 +4299,13 @@
         <v>0.577</v>
       </c>
       <c r="R7" s="12">
-        <v>2.48851808062455</v>
+        <v>2.69888619912948</v>
       </c>
       <c r="S7" s="11">
-        <v>60.57587541036946</v>
+        <v>63.28447499851127</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -4276,10 +4322,10 @@
         <v>32</v>
       </c>
       <c r="E8" s="10">
-        <v>927.5999755859375</v>
+        <v>926.5499877929688</v>
       </c>
       <c r="F8" s="17">
-        <v>0.8985111363697914</v>
+        <v>0.8979010563309927</v>
       </c>
       <c r="G8" s="20">
         <v>-0.495023614230421</v>
@@ -4291,16 +4337,16 @@
         <v>3.960347878543698</v>
       </c>
       <c r="J8" s="20">
-        <v>1.504674396622836</v>
+        <v>1.575069734885173</v>
       </c>
       <c r="K8" s="20">
-        <v>0.4813752091318809</v>
+        <v>0.4791386951481922</v>
       </c>
       <c r="L8" s="20">
-        <v>-3.347756939201326</v>
+        <v>-3.355540730004984</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.08446469401550172</v>
+        <v>-0.3468805989059708</v>
       </c>
       <c r="N8" s="20">
         <v>22.024843</v>
@@ -4315,13 +4361,13 @@
         <v>3.457</v>
       </c>
       <c r="R8" s="12">
-        <v>1.100797603195555</v>
+        <v>1.008018000554102</v>
       </c>
       <c r="S8" s="11">
-        <v>46.90911682891834</v>
+        <v>46.772333110083</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -4329,61 +4375,61 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E9" s="10">
-        <v>67.66000366210938</v>
+        <v>264.6300048828125</v>
       </c>
       <c r="F9" s="17">
-        <v>0.8854219201003662</v>
+        <v>0.8787721910309617</v>
       </c>
       <c r="G9" s="20">
-        <v>1.282244047014282</v>
+        <v>0.4728319185405508</v>
       </c>
       <c r="H9" s="20">
-        <v>-1.356970430261629</v>
+        <v>-0.7907783719627398</v>
       </c>
       <c r="I9" s="20">
-        <v>-0.5801056520622042</v>
+        <v>2.406342473145227</v>
       </c>
       <c r="J9" s="20">
-        <v>1.395587164196497</v>
+        <v>2.122891940215747</v>
       </c>
       <c r="K9" s="20">
-        <v>4.198114103620362</v>
+        <v>0.688309634936399</v>
       </c>
       <c r="L9" s="20">
-        <v>-0.06369499479731604</v>
+        <v>0.4801287330810596</v>
       </c>
       <c r="M9" s="20">
-        <v>0.1389460460040365</v>
+        <v>-0.8589965543597157</v>
       </c>
       <c r="N9" s="20">
-        <v>12.502541</v>
+        <v>14.818389</v>
       </c>
       <c r="O9" s="20">
-        <v>1.4542508</v>
+        <v>3.2861774</v>
       </c>
       <c r="P9" s="12">
-        <v>-0.20358999</v>
+        <v>0.23452999</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.046</v>
+        <v>0.531</v>
       </c>
       <c r="R9" s="12">
-        <v>0.9464904179870228</v>
+        <v>0.5515369999894433</v>
       </c>
       <c r="S9" s="11">
-        <v>55.45609886456371</v>
+        <v>74.80114937992263</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -4400,10 +4446,10 @@
         <v>53</v>
       </c>
       <c r="E10" s="10">
-        <v>377.9700012207031</v>
+        <v>378.9200134277344</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8650155013620733</v>
+        <v>0.8750341800101787</v>
       </c>
       <c r="G10" s="20">
         <v>1.195906561845193</v>
@@ -4415,16 +4461,16 @@
         <v>-0.3802373592559733</v>
       </c>
       <c r="J10" s="20">
-        <v>0.7788658346716076</v>
+        <v>0.8562439430385483</v>
       </c>
       <c r="K10" s="20">
-        <v>3.822167839477549</v>
+        <v>3.814024146500563</v>
       </c>
       <c r="L10" s="20">
-        <v>0.5633054705938957</v>
+        <v>0.5690662211524231</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.2320988880212402</v>
+        <v>-0.3891383347493648</v>
       </c>
       <c r="N10" s="20">
         <v>10.080602</v>
@@ -4439,13 +4485,13 @@
         <v>0.003</v>
       </c>
       <c r="R10" s="12">
-        <v>0.2501569342848344</v>
+        <v>0.2463848523163887</v>
       </c>
       <c r="S10" s="11">
-        <v>60.87771432988801</v>
+        <v>61.69903963485483</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4453,61 +4499,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E11" s="10">
-        <v>1530.89501953125</v>
+        <v>66.01000213623047</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8533122300924563</v>
+        <v>0.8553863213010248</v>
       </c>
       <c r="G11" s="20">
-        <v>-0.4801631684214276</v>
+        <v>1.282244047014282</v>
       </c>
       <c r="H11" s="20">
-        <v>2.05728233065155</v>
+        <v>-1.356970430261629</v>
       </c>
       <c r="I11" s="20">
-        <v>4.117187201861848</v>
+        <v>-0.5801056520622042</v>
       </c>
       <c r="J11" s="20">
-        <v>1.283614597660989</v>
+        <v>1.286272228593575</v>
       </c>
       <c r="K11" s="20">
-        <v>0.08551734608922254</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L11" s="20">
-        <v>-3.347756939201326</v>
+        <v>-0.02434954714148995</v>
       </c>
       <c r="M11" s="20">
-        <v>0.05470828551195824</v>
+        <v>0.1440444280304993</v>
       </c>
       <c r="N11" s="20">
-        <v>22.12312</v>
+        <v>12.502541</v>
       </c>
       <c r="O11" s="20">
-        <v>15.465718</v>
+        <v>1.4542508</v>
       </c>
       <c r="P11" s="12">
-        <v>0.9164</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q11" s="12">
-        <v>3.716</v>
+        <v>0.046</v>
       </c>
       <c r="R11" s="12">
-        <v>1.175710258101083</v>
+        <v>0.8892388303006635</v>
       </c>
       <c r="S11" s="11">
-        <v>47.66082157617929</v>
+        <v>50.48958326877084</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4515,61 +4561,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E12" s="10">
-        <v>264.9299926757812</v>
+        <v>342.8699951171875</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8449014145413066</v>
+        <v>0.835172506044463</v>
       </c>
       <c r="G12" s="20">
-        <v>0.4728319185405508</v>
+        <v>-0.3791628567675373</v>
       </c>
       <c r="H12" s="20">
-        <v>-0.7907783719627398</v>
+        <v>1.461933114403917</v>
       </c>
       <c r="I12" s="20">
-        <v>2.406342473145227</v>
+        <v>1.394253875646282</v>
       </c>
       <c r="J12" s="20">
-        <v>2.04290033251477</v>
+        <v>-0.003775951465358696</v>
       </c>
       <c r="K12" s="20">
-        <v>0.6909166594517234</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L12" s="20">
-        <v>0.4787318536549871</v>
+        <v>0.123577911699675</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.9852756088051771</v>
+        <v>0.2505158529559968</v>
       </c>
       <c r="N12" s="20">
-        <v>14.818389</v>
+        <v>16.975927</v>
       </c>
       <c r="O12" s="20">
-        <v>3.2861774</v>
+        <v>6.6508174</v>
       </c>
       <c r="P12" s="12">
-        <v>0.23452999</v>
+        <v>0.48676</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.531</v>
+        <v>0.242</v>
       </c>
       <c r="R12" s="12">
-        <v>0.5464015259473756</v>
+        <v>0.1041274798036558</v>
       </c>
       <c r="S12" s="11">
-        <v>75.3235154586028</v>
+        <v>50.06305178655397</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4577,22 +4623,22 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>103</v>
+        <v>11</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="D13" s="9" t="s">
         <v>55</v>
       </c>
       <c r="E13" s="10">
-        <v>344.9800109863281</v>
+        <v>339.3599853515625</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8374014679330111</v>
+        <v>0.8328083216241077</v>
       </c>
       <c r="G13" s="20">
-        <v>-0.3791628567675373</v>
+        <v>-0.3694515340244113</v>
       </c>
       <c r="H13" s="20">
         <v>1.461933114403917</v>
@@ -4601,22 +4647,22 @@
         <v>1.394253875646282</v>
       </c>
       <c r="J13" s="20">
-        <v>0.01905145690521837</v>
+        <v>-0.03465443555860494</v>
       </c>
       <c r="K13" s="20">
-        <v>4.198114103620362</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L13" s="20">
-        <v>0.03202592099213238</v>
+        <v>0.1569421732261793</v>
       </c>
       <c r="M13" s="20">
-        <v>0.2613176439546983</v>
+        <v>0.289884190734319</v>
       </c>
       <c r="N13" s="20">
-        <v>16.975927</v>
+        <v>16.83141</v>
       </c>
       <c r="O13" s="20">
-        <v>6.6508174</v>
+        <v>6.5908914</v>
       </c>
       <c r="P13" s="12">
         <v>0.48676</v>
@@ -4625,13 +4671,13 @@
         <v>0.242</v>
       </c>
       <c r="R13" s="12">
-        <v>0.1304095874226328</v>
+        <v>0.09816962643472427</v>
       </c>
       <c r="S13" s="11">
-        <v>51.72085052727156</v>
+        <v>49.45699543810807</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4639,61 +4685,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E14" s="10">
-        <v>341.4299926757812</v>
+        <v>1519.969970703125</v>
       </c>
       <c r="F14" s="17">
-        <v>0.8341785756102056</v>
+        <v>0.8316214410685321</v>
       </c>
       <c r="G14" s="20">
-        <v>-0.3694515340244113</v>
+        <v>-0.4801631684214276</v>
       </c>
       <c r="H14" s="20">
-        <v>1.461933114403917</v>
+        <v>2.05728233065155</v>
       </c>
       <c r="I14" s="20">
-        <v>1.394253875646282</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J14" s="20">
-        <v>-0.01298167389032759</v>
+        <v>1.328125305747322</v>
       </c>
       <c r="K14" s="20">
-        <v>4.198114103620362</v>
+        <v>0.08398078673057012</v>
       </c>
       <c r="L14" s="20">
-        <v>0.06064050491953007</v>
+        <v>-3.355540730004984</v>
       </c>
       <c r="M14" s="20">
-        <v>0.2978443162853454</v>
+        <v>-0.3751990504701193</v>
       </c>
       <c r="N14" s="20">
-        <v>16.83141</v>
+        <v>22.12312</v>
       </c>
       <c r="O14" s="20">
-        <v>6.5908914</v>
+        <v>15.465718</v>
       </c>
       <c r="P14" s="12">
-        <v>0.48676</v>
+        <v>0.9164</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.242</v>
+        <v>3.716</v>
       </c>
       <c r="R14" s="12">
-        <v>0.1229789876647722</v>
+        <v>1.110571124557335</v>
       </c>
       <c r="S14" s="11">
-        <v>51.18538862480936</v>
+        <v>47.02864077974324</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4701,61 +4747,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E15" s="10">
-        <v>63.52000045776367</v>
+        <v>56.68000030517578</v>
       </c>
       <c r="F15" s="17">
-        <v>0.8144457689120104</v>
+        <v>0.7980632895236915</v>
       </c>
       <c r="G15" s="20">
-        <v>0.6018835051913498</v>
+        <v>0.3530298731450531</v>
       </c>
       <c r="H15" s="20">
-        <v>0.6139340215135211</v>
+        <v>-0.5362564771804156</v>
       </c>
       <c r="I15" s="20">
-        <v>2.907067021605936</v>
+        <v>2.205637651643404</v>
       </c>
       <c r="J15" s="20">
-        <v>0.81025577985074</v>
+        <v>2.08388478101543</v>
       </c>
       <c r="K15" s="20">
-        <v>0.9154253562229835</v>
+        <v>0</v>
       </c>
       <c r="L15" s="20">
-        <v>0.3452148038147002</v>
+        <v>-1.966963505523411</v>
       </c>
       <c r="M15" s="20">
-        <v>-0.7058759069506468</v>
+        <v>-0.03950043967449224</v>
       </c>
       <c r="N15" s="20">
-        <v>18.129793</v>
+        <v>32.005154</v>
       </c>
       <c r="O15" s="20">
-        <v>1.836326</v>
+        <v>3.1100981</v>
       </c>
       <c r="P15" s="12">
-        <v>0.10629</v>
+        <v>0.10936</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.534</v>
+        <v>0.337</v>
       </c>
       <c r="R15" s="12">
-        <v>0.119759123225649</v>
+        <v>1.640165016510447</v>
       </c>
       <c r="S15" s="11">
-        <v>71.16891540451111</v>
+        <v>53.93524889252662</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4763,19 +4809,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="10">
-        <v>255.6499938964844</v>
+        <v>250.5399932861328</v>
       </c>
       <c r="F16" s="17">
-        <v>0.8005310238731026</v>
+        <v>0.7906584234424111</v>
       </c>
       <c r="G16" s="20">
         <v>0.3415976968814792</v>
@@ -4787,16 +4833,16 @@
         <v>0.1958909336866145</v>
       </c>
       <c r="J16" s="20">
-        <v>1.26347958635133</v>
+        <v>1.282577727845992</v>
       </c>
       <c r="K16" s="20">
-        <v>3.524887358235604</v>
+        <v>3.517269315668033</v>
       </c>
       <c r="L16" s="20">
-        <v>-1.562192545310308</v>
+        <v>-1.584593559956525</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.9327906850176849</v>
+        <v>-1.099588396170294</v>
       </c>
       <c r="N16" s="20">
         <v>22.684982</v>
@@ -4811,13 +4857,13 @@
         <v>0.108</v>
       </c>
       <c r="R16" s="12">
-        <v>0.2955069218851827</v>
+        <v>0.2893085099491286</v>
       </c>
       <c r="S16" s="11">
-        <v>66.55121562547168</v>
+        <v>62.37802591327755</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4825,61 +4871,61 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>107</v>
+        <v>6</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E17" s="10">
-        <v>55.88000106811523</v>
+        <v>59.36000061035156</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7781049213844827</v>
+        <v>0.7430174975106851</v>
       </c>
       <c r="G17" s="20">
-        <v>0.3530298731450531</v>
+        <v>0.6018835051913498</v>
       </c>
       <c r="H17" s="20">
-        <v>-0.5362564771804156</v>
+        <v>0.6139340215135211</v>
       </c>
       <c r="I17" s="20">
-        <v>2.205637651643404</v>
+        <v>2.907067021605936</v>
       </c>
       <c r="J17" s="20">
-        <v>1.955978391767738</v>
+        <v>0.4312446123095364</v>
       </c>
       <c r="K17" s="20">
-        <v>0</v>
+        <v>0.9124213561380491</v>
       </c>
       <c r="L17" s="20">
-        <v>-1.955038451555946</v>
+        <v>0.1548656291033269</v>
       </c>
       <c r="M17" s="20">
-        <v>0.2116626799974562</v>
+        <v>-0.03016954002676753</v>
       </c>
       <c r="N17" s="20">
-        <v>32.005154</v>
+        <v>18.129793</v>
       </c>
       <c r="O17" s="20">
-        <v>3.1100981</v>
+        <v>1.836326</v>
       </c>
       <c r="P17" s="12">
-        <v>0.10936</v>
+        <v>0.10629</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.337</v>
+        <v>0.534</v>
       </c>
       <c r="R17" s="12">
-        <v>1.581458169131547</v>
+        <v>0.03772424029952015</v>
       </c>
       <c r="S17" s="11">
-        <v>52.75135451824926</v>
+        <v>49.08197179589703</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4887,61 +4933,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E18" s="10">
-        <v>257.2099914550781</v>
+        <v>191.4900054931641</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6643531276938139</v>
+        <v>0.6779452139495242</v>
       </c>
       <c r="G18" s="20">
-        <v>1.275714742496789</v>
+        <v>-0.4603187739276002</v>
       </c>
       <c r="H18" s="20">
-        <v>0.1637485141969772</v>
+        <v>1.359216064961746</v>
       </c>
       <c r="I18" s="20">
-        <v>-0.05524579084430264</v>
+        <v>0.4362761666871086</v>
       </c>
       <c r="J18" s="20">
-        <v>0.5533737975568457</v>
+        <v>1.546273857635937</v>
       </c>
       <c r="K18" s="20">
-        <v>1.856297434875873</v>
+        <v>0</v>
       </c>
       <c r="L18" s="20">
-        <v>0.4836670935941778</v>
+        <v>-0.4088640220953557</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.04673207763129128</v>
+        <v>-0.2625416930637556</v>
       </c>
       <c r="N18" s="20">
-        <v>5.081314</v>
+        <v>28.186703</v>
       </c>
       <c r="O18" s="20">
-        <v>2.0330794</v>
+        <v>26.124804</v>
       </c>
       <c r="P18" s="12">
-        <v>0.46113998</v>
+        <v>1.14818</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.118</v>
+        <v>0.299</v>
       </c>
       <c r="R18" s="12">
-        <v>0.2494158551196175</v>
+        <v>0.8941858653868795</v>
       </c>
       <c r="S18" s="11">
-        <v>50.49890368250308</v>
+        <v>53.53304172382524</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4949,61 +4995,61 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>8</v>
+        <v>112</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E19" s="10">
-        <v>47.40999984741211</v>
+        <v>254.8500061035156</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6506104419219966</v>
+        <v>0.6661245476929314</v>
       </c>
       <c r="G19" s="20">
-        <v>1.099839703019805</v>
+        <v>1.275714742496789</v>
       </c>
       <c r="H19" s="20">
-        <v>0.5600572175760307</v>
+        <v>0.1637485141969772</v>
       </c>
       <c r="I19" s="20">
-        <v>-0.2922173294313919</v>
+        <v>-0.05524579084430264</v>
       </c>
       <c r="J19" s="20">
-        <v>1.792187259161045</v>
+        <v>0.5540854391486315</v>
       </c>
       <c r="K19" s="20">
-        <v>-0.570460938040137</v>
+        <v>1.851629787748643</v>
       </c>
       <c r="L19" s="20">
-        <v>-0.2753998992412363</v>
+        <v>0.48158007204799</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.7553124714952126</v>
+        <v>-0.0186912467610337</v>
       </c>
       <c r="N19" s="20">
-        <v>9.436709</v>
+        <v>5.081314</v>
       </c>
       <c r="O19" s="20">
-        <v>2.2340426</v>
+        <v>2.0330794</v>
       </c>
       <c r="P19" s="12">
-        <v>0.26659</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.092</v>
+        <v>0.118</v>
       </c>
       <c r="R19" s="12">
-        <v>0.3915245433828938</v>
+        <v>0.2411771923059403</v>
       </c>
       <c r="S19" s="11">
-        <v>71.61490644470551</v>
+        <v>47.68889299433403</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -5011,61 +5057,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="E20" s="10">
-        <v>189.9299926757812</v>
+        <v>154.6799926757812</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6453205619024445</v>
+        <v>0.6369924288836575</v>
       </c>
       <c r="G20" s="20">
-        <v>-0.4603187739276002</v>
+        <v>0.5169435305631409</v>
       </c>
       <c r="H20" s="20">
-        <v>1.359216064961746</v>
+        <v>-0.5609987008817506</v>
       </c>
       <c r="I20" s="20">
-        <v>0.4362761666871086</v>
+        <v>-0.03865308917984001</v>
       </c>
       <c r="J20" s="20">
-        <v>1.420391617147448</v>
+        <v>0.9671948687367055</v>
       </c>
       <c r="K20" s="20">
-        <v>0</v>
+        <v>3.283884006002866</v>
       </c>
       <c r="L20" s="20">
-        <v>-0.4094634044217691</v>
+        <v>0.2706473752441712</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.1489049270049929</v>
+        <v>-0.7861961176831198</v>
       </c>
       <c r="N20" s="20">
-        <v>28.186703</v>
+        <v>16.148188</v>
       </c>
       <c r="O20" s="20">
-        <v>26.124804</v>
+        <v>3.9674618</v>
       </c>
       <c r="P20" s="12">
-        <v>1.14818</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q20" s="12">
-        <v>0.299</v>
+        <v>0.053</v>
       </c>
       <c r="R20" s="12">
-        <v>0.8728741852609276</v>
+        <v>0.3475494720990973</v>
       </c>
       <c r="S20" s="11">
-        <v>52.23971145746755</v>
+        <v>46.66226687311799</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -5073,61 +5119,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="E21" s="10">
-        <v>154.3999938964844</v>
+        <v>124.75</v>
       </c>
       <c r="F21" s="17">
-        <v>0.629749702539554</v>
+        <v>0.6343377358279289</v>
       </c>
       <c r="G21" s="20">
-        <v>0.5169435305631409</v>
+        <v>0.3560597278471356</v>
       </c>
       <c r="H21" s="20">
-        <v>-0.5609987008817506</v>
+        <v>0.5036708481790161</v>
       </c>
       <c r="I21" s="20">
-        <v>-0.03865308917984001</v>
+        <v>0.5191598695187023</v>
       </c>
       <c r="J21" s="20">
-        <v>0.9018502104981442</v>
+        <v>0.9181217381261554</v>
       </c>
       <c r="K21" s="20">
-        <v>3.291088646425534</v>
+        <v>1.641428449242267</v>
       </c>
       <c r="L21" s="20">
-        <v>0.2638189685730646</v>
+        <v>0.2255947427853154</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.6373733842204831</v>
+        <v>-0.6024994719888253</v>
       </c>
       <c r="N21" s="20">
-        <v>16.148188</v>
+        <v>15.473886</v>
       </c>
       <c r="O21" s="20">
-        <v>3.9674618</v>
+        <v>3.847884</v>
       </c>
       <c r="P21" s="12">
-        <v>0.26408002</v>
+        <v>0.30667</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.053</v>
+        <v>0.377</v>
       </c>
       <c r="R21" s="12">
-        <v>0.3417775802287879</v>
+        <v>0.3240288514514311</v>
       </c>
       <c r="S21" s="11">
-        <v>46.18404292940898</v>
+        <v>52.28354439180455</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -5135,61 +5181,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>118</v>
+        <v>32</v>
       </c>
       <c r="E22" s="10">
-        <v>248.4199981689453</v>
+        <v>101.0500030517578</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6095747712110319</v>
+        <v>0.6118537687214308</v>
       </c>
       <c r="G22" s="20">
-        <v>-0.04046750433284103</v>
+        <v>-0.7359494773385853</v>
       </c>
       <c r="H22" s="20">
-        <v>0.1570571804969511</v>
+        <v>-1.140633242548325</v>
       </c>
       <c r="I22" s="20">
-        <v>1.023343627582307</v>
+        <v>0.5241404076306111</v>
       </c>
       <c r="J22" s="20">
-        <v>0.003946071370269246</v>
+        <v>1.512983593088108</v>
       </c>
       <c r="K22" s="20">
-        <v>4.198114103620362</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L22" s="20">
-        <v>-0.410995729271467</v>
+        <v>-2.239284587221917</v>
       </c>
       <c r="M22" s="20">
-        <v>0.11372050329955</v>
+        <v>0.6388746637427194</v>
       </c>
       <c r="N22" s="20">
-        <v>20.658085</v>
+        <v>50.34258</v>
       </c>
       <c r="O22" s="20">
-        <v>5.0195484</v>
+        <v>5.9300656</v>
       </c>
       <c r="P22" s="12">
-        <v>0.30558002</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.196</v>
+        <v>0.254</v>
       </c>
       <c r="R22" s="12">
-        <v>0.1732312823471871</v>
+        <v>1.293463456699162</v>
       </c>
       <c r="S22" s="11">
-        <v>41.41705451283759</v>
+        <v>54.73633143599216</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -5197,61 +5243,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>57</v>
+        <v>123</v>
       </c>
       <c r="E23" s="10">
-        <v>121.7399978637695</v>
+        <v>245.9600067138672</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5727022719586583</v>
+        <v>0.6019631473569113</v>
       </c>
       <c r="G23" s="20">
-        <v>0.3560597278471356</v>
+        <v>-0.04046750433284103</v>
       </c>
       <c r="H23" s="20">
-        <v>0.5036708481790161</v>
+        <v>0.1570571804969511</v>
       </c>
       <c r="I23" s="20">
-        <v>0.5191598695187023</v>
+        <v>1.023343627582307</v>
       </c>
       <c r="J23" s="20">
-        <v>0.6476358906946246</v>
+        <v>-0.01861746216667653</v>
       </c>
       <c r="K23" s="20">
-        <v>1.645723760662829</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L23" s="20">
-        <v>0.13576854676561</v>
+        <v>-0.3439566034803255</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.2976941626025293</v>
+        <v>0.05303055579237728</v>
       </c>
       <c r="N23" s="20">
-        <v>15.473886</v>
+        <v>20.658085</v>
       </c>
       <c r="O23" s="20">
-        <v>3.847884</v>
+        <v>5.0195484</v>
       </c>
       <c r="P23" s="12">
-        <v>0.30667</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.377</v>
+        <v>0.196</v>
       </c>
       <c r="R23" s="12">
-        <v>0.309032235094296</v>
+        <v>0.1429368503802679</v>
       </c>
       <c r="S23" s="11">
-        <v>45.55254132787277</v>
+        <v>39.4467022217616</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -5259,61 +5305,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>121</v>
+        <v>8</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>122</v>
+        <v>49</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E24" s="10">
-        <v>33.81999969482422</v>
+        <v>44.79000091552734</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5569433906580628</v>
+        <v>0.5764342161264837</v>
       </c>
       <c r="G24" s="20">
-        <v>0.9932091735796537</v>
+        <v>1.099839703019805</v>
       </c>
       <c r="H24" s="20">
-        <v>-0.9910800207632466</v>
+        <v>0.5600572175760307</v>
       </c>
       <c r="I24" s="20">
-        <v>-0.385570790078564</v>
+        <v>-0.2922173294313919</v>
       </c>
       <c r="J24" s="20">
-        <v>1.886173261218317</v>
+        <v>1.480407990773791</v>
       </c>
       <c r="K24" s="20">
-        <v>0.4091195366077971</v>
+        <v>-0.5708375986655156</v>
       </c>
       <c r="L24" s="20">
-        <v>-0.7467573774481366</v>
+        <v>-0.3693923024749571</v>
       </c>
       <c r="M24" s="20">
-        <v>0.06443427040197813</v>
+        <v>-0.4422837441235606</v>
       </c>
       <c r="N24" s="20">
-        <v>13.5419855</v>
+        <v>9.436709</v>
       </c>
       <c r="O24" s="20">
-        <v>-347.84314</v>
+        <v>2.2340426</v>
       </c>
       <c r="P24" s="12">
-        <v>0</v>
+        <v>0.26659</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.125</v>
+        <v>0.092</v>
       </c>
       <c r="R24" s="12">
-        <v>0.8503446708392963</v>
+        <v>0.2658811540583801</v>
       </c>
       <c r="S24" s="11">
-        <v>63.01774012836682</v>
+        <v>58.06089547230191</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -5321,19 +5367,19 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="10">
-        <v>172.3699951171875</v>
+        <v>171.7700042724609</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5220751939514237</v>
+        <v>0.5398387336236281</v>
       </c>
       <c r="G25" s="20">
         <v>-2.045758834681303</v>
@@ -5345,16 +5391,16 @@
         <v>0.2278103986420596</v>
       </c>
       <c r="J25" s="20">
-        <v>1.882835690231804</v>
+        <v>1.933551989184213</v>
       </c>
       <c r="K25" s="20">
-        <v>0.4369895817242295</v>
+        <v>0.4348315502669465</v>
       </c>
       <c r="L25" s="20">
-        <v>-0.5793723082203702</v>
+        <v>-0.5853713061099342</v>
       </c>
       <c r="M25" s="20">
-        <v>0.03569895349874286</v>
+        <v>0.07529337393286417</v>
       </c>
       <c r="N25" s="20">
         <v>55.343975</v>
@@ -5369,13 +5415,13 @@
         <v>0.256</v>
       </c>
       <c r="R25" s="12">
-        <v>1.040123085280632</v>
+        <v>1.065536275952876</v>
       </c>
       <c r="S25" s="11">
-        <v>61.40356577742246</v>
+        <v>60.72469323234478</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -5383,61 +5429,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E26" s="10">
-        <v>217.7700042724609</v>
+        <v>216.0099945068359</v>
       </c>
       <c r="F26" s="17">
-        <v>0.512176032614258</v>
+        <v>0.5049937466329726</v>
       </c>
       <c r="G26" s="20">
-        <v>0.5000449645463003</v>
+        <v>0.2268704470519779</v>
       </c>
       <c r="H26" s="20">
-        <v>-0.3299402274497991</v>
+        <v>0.02833393151366955</v>
       </c>
       <c r="I26" s="20">
-        <v>2.306272783126228</v>
+        <v>-0.8973367206108911</v>
       </c>
       <c r="J26" s="20">
-        <v>0.9235329140507406</v>
+        <v>0.6115715297193677</v>
       </c>
       <c r="K26" s="20">
-        <v>-0.1663452838518691</v>
+        <v>3.363739906660925</v>
       </c>
       <c r="L26" s="20">
-        <v>0.8430070564342445</v>
+        <v>-0.1233603963317929</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.7918470807972934</v>
+        <v>-0.3795164344086904</v>
       </c>
       <c r="N26" s="20">
-        <v>20.62235</v>
+        <v>38.63879</v>
       </c>
       <c r="O26" s="20">
-        <v>2.2113636</v>
+        <v>1.7016691</v>
       </c>
       <c r="P26" s="12">
-        <v>0.12231</v>
+        <v>0.04575</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.535</v>
+        <v>0.034</v>
       </c>
       <c r="R26" s="12">
-        <v>0.1262067437900027</v>
+        <v>0.1657941731006702</v>
       </c>
       <c r="S26" s="11">
-        <v>71.00079912649116</v>
+        <v>51.63966191247673</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -5445,61 +5491,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E27" s="10">
-        <v>97.13999938964844</v>
+        <v>36.84999847412109</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5099304722649342</v>
+        <v>0.4952539808894236</v>
       </c>
       <c r="G27" s="20">
-        <v>-0.7359494773385853</v>
+        <v>0.005970682120931148</v>
       </c>
       <c r="H27" s="20">
-        <v>-1.140633242548325</v>
+        <v>-0.8151434307759278</v>
       </c>
       <c r="I27" s="20">
-        <v>0.5241404076306111</v>
+        <v>3.899748911067756</v>
       </c>
       <c r="J27" s="20">
-        <v>1.098580246187481</v>
+        <v>0.3982040469689888</v>
       </c>
       <c r="K27" s="20">
-        <v>4.198114103620362</v>
+        <v>3.372498295765357</v>
       </c>
       <c r="L27" s="20">
-        <v>-2.243486277693008</v>
+        <v>-3.355540730004984</v>
       </c>
       <c r="M27" s="20">
-        <v>0.921875832518037</v>
+        <v>-1.102515623215146</v>
       </c>
       <c r="N27" s="20">
-        <v>50.34258</v>
+        <v>12.300613</v>
       </c>
       <c r="O27" s="20">
-        <v>5.9300656</v>
+        <v>2.5690305</v>
       </c>
       <c r="P27" s="12">
-        <v>-0.10715</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.254</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R27" s="12">
-        <v>1.122814749840964</v>
+        <v>0.1694699526007828</v>
       </c>
       <c r="S27" s="11">
-        <v>50.27464804382547</v>
+        <v>51.09657212217164</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5507,61 +5553,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E28" s="10">
-        <v>976.6699829101562</v>
+        <v>211.5399932861328</v>
       </c>
       <c r="F28" s="17">
-        <v>0.4955517800725586</v>
+        <v>0.4939930498965755</v>
       </c>
       <c r="G28" s="20">
-        <v>0.3658514008022524</v>
+        <v>0.5000449645463003</v>
       </c>
       <c r="H28" s="20">
-        <v>0.8216781549389145</v>
+        <v>-0.3299402274497991</v>
       </c>
       <c r="I28" s="20">
-        <v>0.9093352353792101</v>
+        <v>2.306272783126228</v>
       </c>
       <c r="J28" s="20">
-        <v>-0.09630682543835871</v>
+        <v>0.7933612633358079</v>
       </c>
       <c r="K28" s="20">
-        <v>1.662239342954049</v>
+        <v>-0.1674365005025454</v>
       </c>
       <c r="L28" s="20">
-        <v>0.06072157930923498</v>
+        <v>0.7921113334440001</v>
       </c>
       <c r="M28" s="20">
-        <v>0.4134566414809195</v>
+        <v>-0.4911820573686303</v>
       </c>
       <c r="N28" s="20">
-        <v>15.897128</v>
+        <v>20.62235</v>
       </c>
       <c r="O28" s="20">
-        <v>2.842654</v>
+        <v>2.2113636</v>
       </c>
       <c r="P28" s="12">
-        <v>0.16902</v>
+        <v>0.12231</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.425</v>
+        <v>0.535</v>
       </c>
       <c r="R28" s="12">
-        <v>0.2403321709082651</v>
+        <v>0.08774345185736498</v>
       </c>
       <c r="S28" s="11">
-        <v>37.18001314071405</v>
+        <v>58.9632379873061</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5569,61 +5615,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E29" s="10">
-        <v>216.1699981689453</v>
+        <v>32.70000076293945</v>
       </c>
       <c r="F29" s="17">
-        <v>0.4914891493246438</v>
+        <v>0.4929571211974721</v>
       </c>
       <c r="G29" s="20">
-        <v>0.2268704470519779</v>
+        <v>0.9932091735796537</v>
       </c>
       <c r="H29" s="20">
-        <v>0.02833393151366955</v>
+        <v>-0.9910800207632466</v>
       </c>
       <c r="I29" s="20">
-        <v>-0.8973367206108911</v>
+        <v>-0.385570790078564</v>
       </c>
       <c r="J29" s="20">
-        <v>0.5360470716400234</v>
+        <v>1.726676428199873</v>
       </c>
       <c r="K29" s="20">
-        <v>3.371085998148626</v>
+        <v>0.4070107848763967</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.1290051695354112</v>
+        <v>-0.7954372773962688</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.271892740294098</v>
+        <v>-0.0976079214780381</v>
       </c>
       <c r="N29" s="20">
-        <v>38.63879</v>
+        <v>13.5419855</v>
       </c>
       <c r="O29" s="20">
-        <v>1.7016691</v>
+        <v>-347.84314</v>
       </c>
       <c r="P29" s="12">
-        <v>0.04575</v>
+        <v>0</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.034</v>
+        <v>0.125</v>
       </c>
       <c r="R29" s="12">
-        <v>0.1795809486444231</v>
+        <v>0.7823887385736601</v>
       </c>
       <c r="S29" s="11">
-        <v>51.85754419140703</v>
+        <v>57.56597385475121</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5631,19 +5677,19 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E30" s="10">
-        <v>206.8500061035156</v>
+        <v>203.1900024414062</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4904824223141894</v>
+        <v>0.4636201602627125</v>
       </c>
       <c r="G30" s="20">
         <v>0.5982241598157348</v>
@@ -5655,16 +5701,16 @@
         <v>4.117187201861848</v>
       </c>
       <c r="J30" s="20">
-        <v>-0.09942068668727556</v>
+        <v>-0.2047910416787346</v>
       </c>
       <c r="K30" s="20">
-        <v>0.6052420763160242</v>
+        <v>0.6027865413284129</v>
       </c>
       <c r="L30" s="20">
-        <v>0.6052976196963868</v>
+        <v>0.5947250854245805</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.02860099198615679</v>
+        <v>0.04237226677362493</v>
       </c>
       <c r="N30" s="20">
         <v>11.482911</v>
@@ -5679,13 +5725,13 @@
         <v>11.11</v>
       </c>
       <c r="R30" s="12">
-        <v>0.1532417916908129</v>
+        <v>0.116469396289933</v>
       </c>
       <c r="S30" s="11">
-        <v>40.42332454892806</v>
+        <v>36.31415219988843</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5693,61 +5739,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E31" s="10">
-        <v>153.7400054931641</v>
+        <v>63.59999847412109</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4732573120190842</v>
+        <v>0.4623359647836967</v>
       </c>
       <c r="G31" s="20">
-        <v>0.6042209697867998</v>
+        <v>0.5011052908132025</v>
       </c>
       <c r="H31" s="20">
-        <v>0.4636940000902633</v>
+        <v>0.6560191381210976</v>
       </c>
       <c r="I31" s="20">
-        <v>1.421647839457134</v>
+        <v>0.2251020255328333</v>
       </c>
       <c r="J31" s="20">
-        <v>0.7660990481666766</v>
+        <v>0.4698457022616294</v>
       </c>
       <c r="K31" s="20">
-        <v>-0.5142047358606719</v>
+        <v>0.8062902881666928</v>
       </c>
       <c r="L31" s="20">
-        <v>0.3085958244441517</v>
+        <v>0.5854092200235509</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.481239776450836</v>
+        <v>-0.3521168834405475</v>
       </c>
       <c r="N31" s="20">
-        <v>11.467704</v>
+        <v>14.017621</v>
       </c>
       <c r="O31" s="20">
-        <v>2.4302394</v>
+        <v>5.8251715</v>
       </c>
       <c r="P31" s="12">
-        <v>0.22507</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.587</v>
+        <v>0.057</v>
       </c>
       <c r="R31" s="12">
-        <v>0.1603861156826818</v>
+        <v>0.08827863825792992</v>
       </c>
       <c r="S31" s="11">
-        <v>65.12536509400445</v>
+        <v>42.73925018817186</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5755,61 +5801,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="E32" s="10">
-        <v>31.22999954223633</v>
+        <v>112.4000015258789</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4551546175425572</v>
+        <v>0.459637525640187</v>
       </c>
       <c r="G32" s="20">
-        <v>0.5071505500348842</v>
+        <v>0.4228371578138432</v>
       </c>
       <c r="H32" s="20">
-        <v>0.7469802265893087</v>
+        <v>-0.1266107877394232</v>
       </c>
       <c r="I32" s="20">
-        <v>-0.1877648684685418</v>
+        <v>0.4718408509917099</v>
       </c>
       <c r="J32" s="20">
-        <v>1.173776721556721</v>
+        <v>-0.3746281810304646</v>
       </c>
       <c r="K32" s="20">
-        <v>-0.4682707726132187</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L32" s="20">
-        <v>0.1723281815137133</v>
+        <v>0.05943715192242162</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.5394130689426249</v>
+        <v>-0.4792659190985764</v>
       </c>
       <c r="N32" s="20">
-        <v>17.695906</v>
+        <v>14.463892</v>
       </c>
       <c r="O32" s="20">
-        <v>6.8245378</v>
+        <v>6.474714</v>
       </c>
       <c r="P32" s="12">
-        <v>0.41944</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.063</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R32" s="12">
-        <v>0.5301199797697445</v>
+        <v>0.005007199627371284</v>
       </c>
       <c r="S32" s="11">
-        <v>62.73094495468379</v>
+        <v>30.41797093341378</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5817,19 +5863,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E33" s="10">
-        <v>342.7300109863281</v>
+        <v>341.1799926757812</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4529808587094866</v>
+        <v>0.4542642581522554</v>
       </c>
       <c r="G33" s="20">
         <v>0.116365121381956</v>
@@ -5841,16 +5887,16 @@
         <v>0.4632294407463022</v>
       </c>
       <c r="J33" s="20">
-        <v>1.266403709696704</v>
+        <v>1.29269119042493</v>
       </c>
       <c r="K33" s="20">
-        <v>1.705076634521898</v>
+        <v>1.700676375536956</v>
       </c>
       <c r="L33" s="20">
-        <v>-1.682739603689381</v>
+        <v>-1.673163442386504</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.7429692178665943</v>
+        <v>-0.8260865100625787</v>
       </c>
       <c r="N33" s="20">
         <v>32.14404</v>
@@ -5865,13 +5911,13 @@
         <v>0.204</v>
       </c>
       <c r="R33" s="12">
-        <v>0.6802961657850926</v>
+        <v>0.6319716667946382</v>
       </c>
       <c r="S33" s="11">
-        <v>47.66103705998034</v>
+        <v>46.73484803783356</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5879,61 +5925,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>115</v>
+        <v>57</v>
       </c>
       <c r="E34" s="10">
-        <v>112.7900009155273</v>
+        <v>145.7299957275391</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4488737267904408</v>
+        <v>0.4532303251400961</v>
       </c>
       <c r="G34" s="20">
-        <v>0.4228371578138432</v>
+        <v>-0.07531619732868289</v>
       </c>
       <c r="H34" s="20">
-        <v>-0.1266107877394232</v>
+        <v>-0.3184017151882295</v>
       </c>
       <c r="I34" s="20">
-        <v>0.4718408509917099</v>
+        <v>-0.6227115884361363</v>
       </c>
       <c r="J34" s="20">
-        <v>-0.4348535511575777</v>
+        <v>1.941074068433888</v>
       </c>
       <c r="K34" s="20">
-        <v>4.198114103620362</v>
+        <v>0.19783984508819</v>
       </c>
       <c r="L34" s="20">
-        <v>0.04442235692376011</v>
+        <v>-0.2185952407681761</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.3768286147438763</v>
+        <v>-0.1618076695208644</v>
       </c>
       <c r="N34" s="20">
-        <v>14.463892</v>
+        <v>59.764423</v>
       </c>
       <c r="O34" s="20">
-        <v>6.474714</v>
+        <v>1.9188677</v>
       </c>
       <c r="P34" s="12">
-        <v>0.46032003</v>
+        <v>0.03211</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.013</v>
       </c>
       <c r="R34" s="12">
-        <v>-0.01372857368349911</v>
+        <v>0.6703156693689796</v>
       </c>
       <c r="S34" s="11">
-        <v>30.78252408731522</v>
+        <v>74.43373683500241</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5941,61 +5987,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E35" s="10">
-        <v>63.72999954223633</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4472788505659449</v>
+        <v>0.4365584798732851</v>
       </c>
       <c r="G35" s="20">
-        <v>0.5011052908132025</v>
+        <v>0.5071505500348842</v>
       </c>
       <c r="H35" s="20">
-        <v>0.6560191381210976</v>
+        <v>0.7469802265893087</v>
       </c>
       <c r="I35" s="20">
-        <v>0.2251020255328333</v>
+        <v>-0.1877648684685418</v>
       </c>
       <c r="J35" s="20">
-        <v>0.4115044507124895</v>
+        <v>1.085097457861382</v>
       </c>
       <c r="K35" s="20">
-        <v>0.8091062952232603</v>
+        <v>-0.4688281255668335</v>
       </c>
       <c r="L35" s="20">
-        <v>0.5773297160473794</v>
+        <v>0.2659109094270264</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.3197155004558923</v>
+        <v>-0.508668567455568</v>
       </c>
       <c r="N35" s="20">
-        <v>14.017621</v>
+        <v>17.695906</v>
       </c>
       <c r="O35" s="20">
-        <v>5.8251715</v>
+        <v>6.8245378</v>
       </c>
       <c r="P35" s="12">
-        <v>0.46598998</v>
+        <v>0.41944</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.057</v>
+        <v>0.063</v>
       </c>
       <c r="R35" s="12">
-        <v>0.09050312550281703</v>
+        <v>0.4724118186748609</v>
       </c>
       <c r="S35" s="11">
-        <v>43.33647351399254</v>
+        <v>57.59120930053963</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -6003,61 +6049,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E36" s="10">
-        <v>211.5299987792969</v>
+        <v>937.97998046875</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4436383808391406</v>
+        <v>0.4226096010620854</v>
       </c>
       <c r="G36" s="20">
-        <v>0.5627498454653113</v>
+        <v>0.3658514008022524</v>
       </c>
       <c r="H36" s="20">
-        <v>-0.0477566135254233</v>
+        <v>0.8216781549389145</v>
       </c>
       <c r="I36" s="20">
-        <v>1.594428774498311</v>
+        <v>0.9093352353792101</v>
       </c>
       <c r="J36" s="20">
-        <v>0.7695053261445053</v>
+        <v>-0.3149927963481021</v>
       </c>
       <c r="K36" s="20">
-        <v>-0.1931831050751002</v>
+        <v>1.657914828732963</v>
       </c>
       <c r="L36" s="20">
-        <v>0.2650627690734423</v>
+        <v>0.01282148064049671</v>
       </c>
       <c r="M36" s="20">
-        <v>-0.4128975251140614</v>
+        <v>0.3641636400947232</v>
       </c>
       <c r="N36" s="20">
-        <v>39.041904</v>
+        <v>15.897128</v>
       </c>
       <c r="O36" s="20">
-        <v>1.5173635</v>
+        <v>2.842654</v>
       </c>
       <c r="P36" s="12">
-        <v>0.034930002</v>
+        <v>0.16902</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.525</v>
+        <v>0.425</v>
       </c>
       <c r="R36" s="12">
-        <v>0.1729542852743062</v>
+        <v>0.1730868831649932</v>
       </c>
       <c r="S36" s="11">
-        <v>64.1445250755504</v>
+        <v>30.72063526231409</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -6065,61 +6111,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>147</v>
+        <v>9</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E37" s="10">
-        <v>141.2200012207031</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4413545969293228</v>
+        <v>0.4172954278442738</v>
       </c>
       <c r="G37" s="20">
-        <v>0.4918102935471612</v>
+        <v>-1.171878848863184</v>
       </c>
       <c r="H37" s="20">
-        <v>-0.1401007530318513</v>
+        <v>2.368118728722743</v>
       </c>
       <c r="I37" s="20">
-        <v>0.7942683123659047</v>
+        <v>2.422793453764177</v>
       </c>
       <c r="J37" s="20">
-        <v>1.148898099295417</v>
+        <v>0.3018678144661496</v>
       </c>
       <c r="K37" s="20">
-        <v>-0.09305738743458426</v>
+        <v>-0.3055099287371252</v>
       </c>
       <c r="L37" s="20">
-        <v>0.572985485756923</v>
+        <v>-0.2033262857763942</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.9007954887818863</v>
+        <v>-0.4330537134651998</v>
       </c>
       <c r="N37" s="20">
-        <v>18.192053</v>
+        <v>27.631645</v>
       </c>
       <c r="O37" s="20">
-        <v>2.5249555</v>
+        <v>23.019087</v>
       </c>
       <c r="P37" s="12">
-        <v>0.1418</v>
+        <v>1.17211</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.355</v>
+        <v>1.059</v>
       </c>
       <c r="R37" s="12">
-        <v>0.1805013198855161</v>
+        <v>0.1784142839297385</v>
       </c>
       <c r="S37" s="11">
-        <v>72.21972770677463</v>
+        <v>46.88755014454045</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -6127,61 +6173,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>150</v>
-      </c>
       <c r="D38" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E38" s="10">
-        <v>35.63999938964844</v>
+        <v>144.9299926757812</v>
       </c>
       <c r="F38" s="17">
-        <v>0.4167896333894786</v>
+        <v>0.4092484779260411</v>
       </c>
       <c r="G38" s="20">
-        <v>0.005970682120931148</v>
+        <v>0.6042209697867998</v>
       </c>
       <c r="H38" s="20">
-        <v>-0.8151434307759278</v>
+        <v>0.4636940000902633</v>
       </c>
       <c r="I38" s="20">
-        <v>3.899748911067756</v>
+        <v>1.421647839457134</v>
       </c>
       <c r="J38" s="20">
-        <v>0.04681825340282978</v>
+        <v>0.4347164752903636</v>
       </c>
       <c r="K38" s="20">
-        <v>3.379859901240836</v>
+        <v>-0.514680868525332</v>
       </c>
       <c r="L38" s="20">
-        <v>-3.347756939201326</v>
+        <v>0.1802405499461859</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.782503492407324</v>
+        <v>0.05831510054276418</v>
       </c>
       <c r="N38" s="20">
-        <v>12.300613</v>
+        <v>11.467704</v>
       </c>
       <c r="O38" s="20">
-        <v>2.5690305</v>
+        <v>2.4302394</v>
       </c>
       <c r="P38" s="12">
-        <v>0.21465999</v>
+        <v>0.22507</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.587</v>
       </c>
       <c r="R38" s="12">
-        <v>0.118644027209112</v>
+        <v>0.08413800754913914</v>
       </c>
       <c r="S38" s="11">
-        <v>47.96918299203491</v>
+        <v>48.13353392864501</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -6189,61 +6235,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="C39" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C39" s="9" t="s">
-        <v>152</v>
-      </c>
       <c r="D39" s="9" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="E39" s="10">
-        <v>51.33000183105469</v>
+        <v>30.19000053405762</v>
       </c>
       <c r="F39" s="17">
-        <v>0.4163086228636527</v>
+        <v>0.3955058451285168</v>
       </c>
       <c r="G39" s="20">
-        <v>0.3586551873076412</v>
+        <v>0.4737570391617266</v>
       </c>
       <c r="H39" s="20">
-        <v>-0.04613112172066019</v>
+        <v>-0.2868604961518937</v>
       </c>
       <c r="I39" s="20">
-        <v>1.252904578771813</v>
+        <v>-0.7009083349924576</v>
       </c>
       <c r="J39" s="20">
-        <v>0.9015850912760487</v>
+        <v>0.6460908200535177</v>
       </c>
       <c r="K39" s="20">
-        <v>-0.04144619277452451</v>
+        <v>2.017008782014688</v>
       </c>
       <c r="L39" s="20">
-        <v>0.2814300457798175</v>
+        <v>0.6247865910761435</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.6068322031282389</v>
+        <v>-0.589217554492896</v>
       </c>
       <c r="N39" s="20">
-        <v>10.919565</v>
+        <v>28.582525</v>
       </c>
       <c r="O39" s="20">
-        <v>1.383556</v>
+        <v>1.876474</v>
       </c>
       <c r="P39" s="12">
-        <v>0.11522</v>
+        <v>0.07979</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.642</v>
+        <v>0.108</v>
       </c>
       <c r="R39" s="12">
-        <v>0.1153246429446486</v>
+        <v>0.2445185611747915</v>
       </c>
       <c r="S39" s="11">
-        <v>70.13798603559555</v>
+        <v>55.06637281709288</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -6251,61 +6297,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C40" s="9" t="s">
-        <v>154</v>
-      </c>
       <c r="D40" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E40" s="10">
-        <v>30.44000053405762</v>
+        <v>418.6400146484375</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3936430844956686</v>
+        <v>0.3647940503203134</v>
       </c>
       <c r="G40" s="20">
-        <v>0.4737570391617266</v>
+        <v>-1.007090388729049</v>
       </c>
       <c r="H40" s="20">
-        <v>-0.2868604961518937</v>
+        <v>-0.4359035064486783</v>
       </c>
       <c r="I40" s="20">
-        <v>-0.7009083349924576</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J40" s="20">
-        <v>0.6560846661254683</v>
+        <v>0.9353876006177274</v>
       </c>
       <c r="K40" s="20">
-        <v>2.021969369734665</v>
+        <v>-0.5502296243021455</v>
       </c>
       <c r="L40" s="20">
-        <v>0.5827828340111484</v>
+        <v>0.6430986395924994</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.625917048954533</v>
+        <v>-0.6134810313433108</v>
       </c>
       <c r="N40" s="20">
-        <v>28.582525</v>
+        <v>103.11616</v>
       </c>
       <c r="O40" s="20">
-        <v>1.876474</v>
+        <v>2.6396286</v>
       </c>
       <c r="P40" s="12">
-        <v>0.07979</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.108</v>
+        <v>1.134</v>
       </c>
       <c r="R40" s="12">
-        <v>0.2620835759150768</v>
+        <v>0.4096098468438623</v>
       </c>
       <c r="S40" s="11">
-        <v>58.16154823442542</v>
+        <v>59.89767420130005</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -6313,61 +6359,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>9</v>
+        <v>154</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>50</v>
+        <v>155</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E41" s="10">
-        <v>212.1699981689453</v>
+        <v>423.5899963378906</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3906092319110401</v>
+        <v>0.3634783352910164</v>
       </c>
       <c r="G41" s="20">
-        <v>-1.171878848863184</v>
+        <v>-0.2429950411639331</v>
       </c>
       <c r="H41" s="20">
-        <v>2.368118728722743</v>
+        <v>0.6042118867300035</v>
       </c>
       <c r="I41" s="20">
-        <v>2.422793453764177</v>
+        <v>-0.3187981010065978</v>
       </c>
       <c r="J41" s="20">
-        <v>0.1594050218291876</v>
+        <v>0.9427973244719356</v>
       </c>
       <c r="K41" s="20">
-        <v>-0.3046632855408293</v>
+        <v>0.3173660963957367</v>
       </c>
       <c r="L41" s="20">
-        <v>-0.2032428307471127</v>
+        <v>-0.009964680998773449</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.2337282463084194</v>
+        <v>0.2762262859405108</v>
       </c>
       <c r="N41" s="20">
-        <v>27.631645</v>
+        <v>32.779457</v>
       </c>
       <c r="O41" s="20">
-        <v>23.019087</v>
+        <v>6.0678544</v>
       </c>
       <c r="P41" s="12">
-        <v>1.17211</v>
+        <v>0.1983</v>
       </c>
       <c r="Q41" s="12">
-        <v>1.059</v>
+        <v>0.109</v>
       </c>
       <c r="R41" s="12">
-        <v>0.1606536093160311</v>
+        <v>0.4809285674428023</v>
       </c>
       <c r="S41" s="11">
-        <v>45.21227177839541</v>
+        <v>59.53715783994979</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -6375,61 +6421,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E42" s="10">
-        <v>206.2799987792969</v>
+        <v>283.5599975585938</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3784873117499491</v>
+        <v>0.3626886008109039</v>
       </c>
       <c r="G42" s="20">
-        <v>0.3472624676162839</v>
+        <v>1.154887046419179</v>
       </c>
       <c r="H42" s="20">
-        <v>0.7723653122279558</v>
+        <v>-0.7540543836248536</v>
       </c>
       <c r="I42" s="20">
-        <v>0.38054810430196</v>
+        <v>-0.2666959649926476</v>
       </c>
       <c r="J42" s="20">
-        <v>0.1959836333250878</v>
+        <v>0.6099495867240897</v>
       </c>
       <c r="K42" s="20">
-        <v>0.3033165875546748</v>
+        <v>0.5996953451739074</v>
       </c>
       <c r="L42" s="20">
-        <v>0.5312936648915446</v>
+        <v>0.977367768157744</v>
       </c>
       <c r="M42" s="20">
-        <v>0.3409513349346129</v>
+        <v>-0.1432894149108433</v>
       </c>
       <c r="N42" s="20">
-        <v>17.330639</v>
+        <v>13.5148325</v>
       </c>
       <c r="O42" s="20">
-        <v>3.1619003</v>
+        <v>2.2874217</v>
       </c>
       <c r="P42" s="12">
-        <v>0.17969999</v>
+        <v>0.18341999</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.28</v>
+        <v>0.094</v>
       </c>
       <c r="R42" s="12">
-        <v>0.3393074672810608</v>
+        <v>0.3133269120670266</v>
       </c>
       <c r="S42" s="11">
-        <v>38.68184012380173</v>
+        <v>51.70218784966599</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -6437,61 +6483,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="E43" s="10">
-        <v>430.8800048828125</v>
+        <v>92.44999694824219</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3679778944704148</v>
+        <v>0.3607236851369043</v>
       </c>
       <c r="G43" s="20">
-        <v>-0.2429950411639331</v>
+        <v>0.6594637779990824</v>
       </c>
       <c r="H43" s="20">
-        <v>0.6042118867300035</v>
+        <v>-0.4971404169201537</v>
       </c>
       <c r="I43" s="20">
-        <v>-0.3187981010065978</v>
+        <v>-0.2300784505986128</v>
       </c>
       <c r="J43" s="20">
-        <v>0.9868619540258891</v>
+        <v>1.2184990847352</v>
       </c>
       <c r="K43" s="20">
-        <v>0.3193160578992932</v>
+        <v>-0.2864475524510079</v>
       </c>
       <c r="L43" s="20">
-        <v>-0.003229163962673475</v>
+        <v>0.1005261043608595</v>
       </c>
       <c r="M43" s="20">
-        <v>0.1592518348232557</v>
+        <v>0.09203664345080942</v>
       </c>
       <c r="N43" s="20">
-        <v>32.779457</v>
+        <v>15.108153</v>
       </c>
       <c r="O43" s="20">
-        <v>6.0678544</v>
+        <v>6.0021152</v>
       </c>
       <c r="P43" s="12">
-        <v>0.1983</v>
+        <v>0.43126</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.109</v>
+        <v>0.036</v>
       </c>
       <c r="R43" s="12">
-        <v>0.5186268219739891</v>
+        <v>0.5187902826849144</v>
       </c>
       <c r="S43" s="11">
-        <v>63.56016959275873</v>
+        <v>60.28087623970859</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6499,61 +6545,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="E44" s="10">
-        <v>119.3099975585938</v>
+        <v>132.5399932861328</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3544353023792072</v>
+        <v>0.3597597139357274</v>
       </c>
       <c r="G44" s="20">
-        <v>1.17687233316855</v>
+        <v>0.4918102935471612</v>
       </c>
       <c r="H44" s="20">
-        <v>-0.6497553567411484</v>
+        <v>-0.1401007530318513</v>
       </c>
       <c r="I44" s="20">
-        <v>0.1405562026344188</v>
+        <v>0.7942683123659047</v>
       </c>
       <c r="J44" s="20">
-        <v>0.4966982537321346</v>
+        <v>0.7739541985332267</v>
       </c>
       <c r="K44" s="20">
-        <v>0.2021586460209576</v>
+        <v>-0.09427819151258149</v>
       </c>
       <c r="L44" s="20">
-        <v>1.041656281575517</v>
+        <v>0.3884954945912291</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.04080464140845316</v>
+        <v>-0.3744931988523483</v>
       </c>
       <c r="N44" s="20">
-        <v>10.810517</v>
+        <v>18.192053</v>
       </c>
       <c r="O44" s="20">
-        <v>1.3035825</v>
+        <v>2.5249555</v>
       </c>
       <c r="P44" s="12">
-        <v>0.12011</v>
+        <v>0.1418</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.141</v>
+        <v>0.355</v>
       </c>
       <c r="R44" s="12">
-        <v>0.3122962465433923</v>
+        <v>0.09396580474072702</v>
       </c>
       <c r="S44" s="11">
-        <v>49.47845389350844</v>
+        <v>51.73931540348961</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
@@ -6619,110 +6665,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -6731,22 +6777,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -6825,57 +6871,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>34</v>
@@ -6883,113 +6929,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -7015,181 +7061,181 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>427.0742797851562</v>
+        <v>433.3439025878906</v>
       </c>
       <c r="C1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="D1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="E1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="F1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="G1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="H1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="I1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="J1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="K1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="L1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="M1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="N1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="O1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="P1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="Q1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="R1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="S1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="T1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="U1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="V1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="W1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="X1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="Y1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="Z1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="AA1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AB1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AC1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AD1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AE1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AF1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AG1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AH1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AI1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AJ1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AK1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AL1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AM1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AN1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AO1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AP1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AQ1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AR1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AS1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="AT1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="AU1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="AV1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="AW1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="AX1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="AY1">
-        <v>425</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="AZ1">
-        <v>492.2000122070312</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="BA1">
-        <v>516.3900146484375</v>
+        <v>524.1400146484375</v>
       </c>
       <c r="BB1">
-        <v>524.1400146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="BC1">
-        <v>533.8800048828125</v>
+        <v>535.25</v>
       </c>
       <c r="BD1">
-        <v>535.25</v>
+        <v>506.6199951171875</v>
       </c>
       <c r="BE1">
-        <v>506.6199951171875</v>
+        <v>567.2899780273438</v>
       </c>
       <c r="BF1">
-        <v>567.2899780273438</v>
+        <v>534.280029296875</v>
       </c>
       <c r="BG1">
-        <v>534.280029296875</v>
+        <v>543.510009765625</v>
       </c>
       <c r="BH1">
-        <v>543.510009765625</v>
+        <v>563.2899780273438</v>
       </c>
     </row>
     <row r="2" spans="1:60">
@@ -7197,181 +7243,181 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1051.608276367188</v>
+        <v>1048.348754882812</v>
       </c>
       <c r="C2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="D2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="E2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="F2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="G2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="H2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="I2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="J2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="K2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="L2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="M2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="N2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="O2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="P2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="Q2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="R2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="S2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="T2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="U2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="V2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="W2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="X2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="Y2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="Z2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="AA2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AB2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AC2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AD2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AE2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AF2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AG2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AH2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AI2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AJ2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AK2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AL2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AM2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AN2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AO2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AP2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AQ2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AR2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AS2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="AT2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="AU2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="AV2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="AW2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="AX2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="AY2">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="AZ2">
-        <v>956.0800170898438</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="BA2">
-        <v>958.1599731445312</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="BB2">
-        <v>1016.590026855469</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="BC2">
-        <v>1000.260009765625</v>
+        <v>1027.77001953125</v>
       </c>
       <c r="BD2">
-        <v>1027.77001953125</v>
+        <v>977.4099731445312</v>
       </c>
       <c r="BE2">
-        <v>977.4099731445312</v>
+        <v>975.260009765625</v>
       </c>
       <c r="BF2">
-        <v>975.260009765625</v>
+        <v>924.030029296875</v>
       </c>
       <c r="BG2">
-        <v>924.030029296875</v>
+        <v>927.5999755859375</v>
       </c>
       <c r="BH2">
-        <v>927.5999755859375</v>
+        <v>926.5499877929688</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -7379,181 +7425,181 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1963.599975585938</v>
+        <v>1914.4599609375</v>
       </c>
       <c r="C3">
-        <v>1914.4599609375</v>
+        <v>2335</v>
       </c>
       <c r="D3">
-        <v>2335</v>
+        <v>2090.7099609375</v>
       </c>
       <c r="E3">
-        <v>2090.7099609375</v>
+        <v>2050.389892578125</v>
       </c>
       <c r="F3">
-        <v>2050.389892578125</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="G3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="H3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="I3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="J3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="K3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="L3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="M3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="N3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="O3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="P3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="Q3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="R3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="S3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="T3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="U3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="V3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="W3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="X3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="Y3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="Z3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="AA3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AB3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AC3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AD3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AE3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AF3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AG3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AH3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AI3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AJ3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AK3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AL3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AM3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AN3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AO3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AP3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AQ3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AR3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AS3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="AT3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AU3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="AV3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="AW3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="AX3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="AY3">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="AZ3">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="BA3">
-        <v>1554.989990234375</v>
+        <v>1740</v>
       </c>
       <c r="BB3">
-        <v>1740</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="BC3">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="BD3">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="BE3">
-        <v>1692.589965820312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="BF3">
-        <v>1633.349975585938</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="BG3">
-        <v>1551.989990234375</v>
+        <v>1530.89501953125</v>
       </c>
       <c r="BH3">
-        <v>1530.89501953125</v>
+        <v>1519.969970703125</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -7561,181 +7607,181 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>670.5347290039062</v>
+        <v>643.6234130859375</v>
       </c>
       <c r="C4">
-        <v>643.6234130859375</v>
+        <v>675.1732788085938</v>
       </c>
       <c r="D4">
-        <v>675.1732788085938</v>
+        <v>586.2618408203125</v>
       </c>
       <c r="E4">
-        <v>586.2618408203125</v>
+        <v>651.6708374023438</v>
       </c>
       <c r="F4">
-        <v>651.6708374023438</v>
+        <v>638.5150146484375</v>
       </c>
       <c r="G4">
-        <v>638.5150146484375</v>
+        <v>598.177978515625</v>
       </c>
       <c r="H4">
-        <v>598.177978515625</v>
+        <v>538.8270263671875</v>
       </c>
       <c r="I4">
-        <v>538.8270263671875</v>
+        <v>577.2747192382812</v>
       </c>
       <c r="J4">
-        <v>577.2747192382812</v>
+        <v>531.92919921875</v>
       </c>
       <c r="K4">
-        <v>531.92919921875</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="L4">
-        <v>550.1234130859375</v>
+        <v>577.864501953125</v>
       </c>
       <c r="M4">
-        <v>577.864501953125</v>
+        <v>582.403076171875</v>
       </c>
       <c r="N4">
-        <v>582.403076171875</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="O4">
-        <v>555.3717041015625</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="P4">
-        <v>563.1392211914062</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="Q4">
-        <v>513.6751098632812</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="R4">
-        <v>466.6601867675781</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="S4">
-        <v>477.0668640136719</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="T4">
-        <v>487.2635803222656</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="U4">
-        <v>548.2140502929688</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="V4">
-        <v>556.4913330078125</v>
+        <v>558.120849609375</v>
       </c>
       <c r="W4">
-        <v>558.120849609375</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="X4">
-        <v>519.6331787109375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="Y4">
-        <v>497.7602233886719</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="Z4">
-        <v>463.3612670898438</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="AA4">
-        <v>461.8917236328125</v>
+        <v>532.868896484375</v>
       </c>
       <c r="AB4">
-        <v>532.868896484375</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="AC4">
-        <v>544.6651611328125</v>
+        <v>527.05078125</v>
       </c>
       <c r="AD4">
-        <v>527.05078125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="AE4">
-        <v>548.3839721679688</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="AF4">
-        <v>519.0033569335938</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="AG4">
-        <v>451.3750915527344</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="AH4">
-        <v>434.1606140136719</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AI4">
-        <v>438.1993408203125</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AJ4">
-        <v>437.7894592285156</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AK4">
-        <v>453.9542846679688</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AL4">
-        <v>487.1336364746094</v>
+        <v>508.63671875</v>
       </c>
       <c r="AM4">
-        <v>508.63671875</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AN4">
-        <v>535.8380126953125</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AO4">
-        <v>496.0007934570312</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AP4">
-        <v>461.9417114257812</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AQ4">
-        <v>468.8994750976562</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AR4">
-        <v>459.2925720214844</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AS4">
-        <v>435.2402954101562</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="AT4">
-        <v>450.6053466796875</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AU4">
-        <v>468.7295227050781</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="AV4">
-        <v>461.8517456054688</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="AW4">
-        <v>459.3025817871094</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="AX4">
-        <v>450.4053955078125</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="AY4">
-        <v>450.2954406738281</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="AZ4">
-        <v>448.7559509277344</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="BA4">
-        <v>441.4283142089844</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="BB4">
-        <v>467.3099670410156</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="BC4">
-        <v>477.2999877929688</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="BD4">
-        <v>482.2799987792969</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="BE4">
-        <v>460.9299926757812</v>
+        <v>447.1799926757812</v>
       </c>
       <c r="BF4">
-        <v>447.1799926757812</v>
+        <v>426.9400024414062</v>
       </c>
       <c r="BG4">
-        <v>426.9400024414062</v>
+        <v>411.9599914550781</v>
       </c>
       <c r="BH4">
-        <v>411.9599914550781</v>
+        <v>416.9700012207031</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -7743,181 +7789,181 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>242.7418823242188</v>
+        <v>241.4967041015625</v>
       </c>
       <c r="C5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="D5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="E5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="F5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="G5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="H5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="I5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="J5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="K5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="L5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="M5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="N5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="O5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="P5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="Q5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="R5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="S5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="T5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="U5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="V5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="W5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="X5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="Y5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="Z5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="AA5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AB5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AC5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AD5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AE5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AF5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AG5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AH5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AI5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AJ5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AK5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AL5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AM5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AN5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AO5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AP5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AQ5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AR5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="AS5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="AT5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AU5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="AV5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="AW5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="AX5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="AY5">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="AZ5">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="BA5">
-        <v>370.6900024414062</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="BB5">
-        <v>370.7200012207031</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="BC5">
-        <v>382.8500061035156</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="BD5">
-        <v>388.9500122070312</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="BE5">
-        <v>385.4299926757812</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="BF5">
-        <v>390.4200134277344</v>
+        <v>382.9500122070312</v>
       </c>
       <c r="BG5">
-        <v>382.9500122070312</v>
+        <v>397.0400085449219</v>
       </c>
       <c r="BH5">
-        <v>397.0400085449219</v>
+        <v>403.2799987792969</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -7925,181 +7971,181 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>247.8413848876953</v>
+        <v>245.8368530273438</v>
       </c>
       <c r="C6">
-        <v>245.8368530273438</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="D6">
-        <v>252.8676147460938</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="E6">
-        <v>253.3662414550781</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="F6">
-        <v>258.5121459960938</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="G6">
-        <v>254.9718475341797</v>
+        <v>264.146728515625</v>
       </c>
       <c r="H6">
-        <v>264.146728515625</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="I6">
-        <v>265.6226806640625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="J6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="K6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="L6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="M6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="N6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="O6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="P6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="Q6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="R6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="S6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="T6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="U6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="V6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="W6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="X6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="Y6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="Z6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="AA6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AB6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AC6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AD6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AE6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AF6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AG6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AH6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AI6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AJ6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AK6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AL6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AM6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AN6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AO6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AP6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AQ6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AR6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AS6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="AT6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AU6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="AV6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="AW6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="AX6">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="AY6">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AZ6">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="BA6">
-        <v>387.7099914550781</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="BB6">
-        <v>388.8999938964844</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="BC6">
-        <v>397.7699890136719</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="BD6">
-        <v>399.4400024414062</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="BE6">
-        <v>392.4200134277344</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="BF6">
-        <v>395.9299926757812</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="BG6">
-        <v>396.4500122070312</v>
+        <v>410.8399963378906</v>
       </c>
       <c r="BH6">
-        <v>410.8399963378906</v>
+        <v>413.9200134277344</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -8107,181 +8153,181 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>51.99142837524414</v>
+        <v>50.85663604736328</v>
       </c>
       <c r="C7">
-        <v>50.85663604736328</v>
+        <v>50.97608947753906</v>
       </c>
       <c r="D7">
-        <v>50.97608947753906</v>
+        <v>49.76166152954102</v>
       </c>
       <c r="E7">
-        <v>49.76166152954102</v>
+        <v>48.86577224731445</v>
       </c>
       <c r="F7">
-        <v>48.86577224731445</v>
+        <v>48.34814834594727</v>
       </c>
       <c r="G7">
-        <v>48.34814834594727</v>
+        <v>47.72102355957031</v>
       </c>
       <c r="H7">
-        <v>47.72102355957031</v>
+        <v>48.68659591674805</v>
       </c>
       <c r="I7">
-        <v>48.68659591674805</v>
+        <v>48.58705139160156</v>
       </c>
       <c r="J7">
-        <v>48.58705139160156</v>
+        <v>51.44394302368164</v>
       </c>
       <c r="K7">
-        <v>51.44394302368164</v>
+        <v>53.34521865844727</v>
       </c>
       <c r="L7">
-        <v>53.34521865844727</v>
+        <v>52.06110763549805</v>
       </c>
       <c r="M7">
-        <v>52.06110763549805</v>
+        <v>52.64841461181641</v>
       </c>
       <c r="N7">
-        <v>52.64841461181641</v>
+        <v>54.55964660644531</v>
       </c>
       <c r="O7">
-        <v>54.55964660644531</v>
+        <v>54.32073974609375</v>
       </c>
       <c r="P7">
-        <v>54.32073974609375</v>
+        <v>53.52439498901367</v>
       </c>
       <c r="Q7">
-        <v>53.52439498901367</v>
+        <v>53.40494537353516</v>
       </c>
       <c r="R7">
-        <v>53.40494537353516</v>
+        <v>54.60941696166992</v>
       </c>
       <c r="S7">
-        <v>54.60941696166992</v>
+        <v>54.93790817260742</v>
       </c>
       <c r="T7">
-        <v>54.93790817260742</v>
+        <v>56.24192428588867</v>
       </c>
       <c r="U7">
-        <v>56.24192428588867</v>
+        <v>57.23735809326172</v>
       </c>
       <c r="V7">
-        <v>57.23735809326172</v>
+        <v>57.33689880371094</v>
       </c>
       <c r="W7">
-        <v>57.33689880371094</v>
+        <v>57.03827285766602</v>
       </c>
       <c r="X7">
-        <v>57.03827285766602</v>
+        <v>54.67909622192383</v>
       </c>
       <c r="Y7">
-        <v>54.67909622192383</v>
+        <v>53.68366622924805</v>
       </c>
       <c r="Z7">
-        <v>53.68366622924805</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="AA7">
-        <v>55.77407073974609</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="AB7">
-        <v>55.69443893432617</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="AC7">
-        <v>56.80932235717773</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="AD7">
-        <v>55.21663284301758</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="AE7">
-        <v>54.8383674621582</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="AF7">
-        <v>53.56421279907227</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="AG7">
-        <v>55.78402709960938</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="AH7">
-        <v>55.65462112426758</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="AI7">
-        <v>58.38210678100586</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="AJ7">
-        <v>58.79023361206055</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="AK7">
-        <v>58.28256225585938</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="AL7">
-        <v>57.43644714355469</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="AM7">
-        <v>58.09342956542969</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="AN7">
-        <v>58.77032470703125</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="AO7">
-        <v>59.52685165405273</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="AP7">
-        <v>59.81552886962891</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="AQ7">
-        <v>61.23899841308594</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="AR7">
+        <v>59.8354377746582</v>
+      </c>
+      <c r="AS7">
+        <v>58.1431999206543</v>
+      </c>
+      <c r="AT7">
+        <v>58.35224151611328</v>
+      </c>
+      <c r="AU7">
+        <v>58.89972686767578</v>
+      </c>
+      <c r="AV7">
+        <v>58.83004760742188</v>
+      </c>
+      <c r="AW7">
+        <v>59.90511703491211</v>
+      </c>
+      <c r="AX7">
+        <v>60.67160034179688</v>
+      </c>
+      <c r="AY7">
+        <v>60.63178253173828</v>
+      </c>
+      <c r="AZ7">
+        <v>60.33315277099609</v>
+      </c>
+      <c r="BA7">
+        <v>59.7657585144043</v>
+      </c>
+      <c r="BB7">
+        <v>60.37297058105469</v>
+      </c>
+      <c r="BC7">
         <v>61.02000045776367</v>
       </c>
-      <c r="AS7">
-        <v>59.8354377746582</v>
-      </c>
-      <c r="AT7">
-        <v>58.1431999206543</v>
-      </c>
-      <c r="AU7">
-        <v>58.35224151611328</v>
-      </c>
-      <c r="AV7">
-        <v>58.89972686767578</v>
-      </c>
-      <c r="AW7">
-        <v>58.83004760742188</v>
-      </c>
-      <c r="AX7">
-        <v>59.90511703491211</v>
-      </c>
-      <c r="AY7">
-        <v>60.67160034179688</v>
-      </c>
-      <c r="AZ7">
-        <v>60.63178253173828</v>
-      </c>
-      <c r="BA7">
-        <v>60.33315277099609</v>
-      </c>
-      <c r="BB7">
-        <v>59.7657585144043</v>
-      </c>
-      <c r="BC7">
-        <v>60.37297058105469</v>
-      </c>
       <c r="BD7">
-        <v>61.02000045776367</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="BE7">
-        <v>61.15999984741211</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="BF7">
-        <v>61.45999908447266</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="BG7">
-        <v>61.77999877929688</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="BH7">
-        <v>63.52000045776367</v>
+        <v>59.36000061035156</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -8289,181 +8335,181 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>169.440673828125</v>
+        <v>167.7496643066406</v>
       </c>
       <c r="C8">
-        <v>167.7496643066406</v>
+        <v>170.8531799316406</v>
       </c>
       <c r="D8">
-        <v>170.8531799316406</v>
+        <v>170.7437591552734</v>
       </c>
       <c r="E8">
-        <v>170.7437591552734</v>
+        <v>173.131103515625</v>
       </c>
       <c r="F8">
-        <v>173.131103515625</v>
+        <v>168.1575012207031</v>
       </c>
       <c r="G8">
-        <v>168.1575012207031</v>
+        <v>173.5787200927734</v>
       </c>
       <c r="H8">
-        <v>173.5787200927734</v>
+        <v>175.4885864257812</v>
       </c>
       <c r="I8">
-        <v>175.4885864257812</v>
+        <v>176.3937835693359</v>
       </c>
       <c r="J8">
-        <v>176.3937835693359</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="K8">
-        <v>177.8957977294922</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="L8">
-        <v>186.8184509277344</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="M8">
-        <v>188.8178405761719</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="N8">
-        <v>187.3655395507812</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="O8">
-        <v>197.2431182861328</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="P8">
-        <v>200.3864288330078</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="Q8">
-        <v>195.1243743896484</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="R8">
-        <v>200.2571258544922</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="S8">
-        <v>205.7678680419922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="T8">
-        <v>207.6976318359375</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="U8">
-        <v>211.1493225097656</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="V8">
-        <v>210.2938537597656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="W8">
-        <v>205.8872375488281</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="X8">
-        <v>205.6783599853516</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="Y8">
-        <v>206.7228088378906</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="Z8">
-        <v>204.7632141113281</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="AA8">
-        <v>205.7181396484375</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="AB8">
-        <v>209.4881286621094</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="AC8">
-        <v>210.5624237060547</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="AD8">
-        <v>205.1014099121094</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="AE8">
-        <v>204.8029937744141</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="AF8">
-        <v>201.4806365966797</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="AG8">
-        <v>204.4349517822266</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="AH8">
-        <v>202.8334503173828</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AI8">
-        <v>214.3821563720703</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AJ8">
-        <v>223.1754760742188</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AK8">
-        <v>224.3890380859375</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AL8">
-        <v>231.3819274902344</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AM8">
-        <v>232.3766479492188</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AN8">
-        <v>239.2800140380859</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AO8">
-        <v>243.4900054931641</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AP8">
-        <v>242.2899932861328</v>
+        <v>240</v>
       </c>
       <c r="AQ8">
-        <v>240</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AR8">
-        <v>242.8699951171875</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AS8">
-        <v>241.9600067138672</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="AT8">
-        <v>236.8999938964844</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AU8">
-        <v>242.2299957275391</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="AV8">
-        <v>239.8099975585938</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="AW8">
-        <v>244.0099945068359</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="AX8">
-        <v>246.5800018310547</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="AY8">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="AZ8">
-        <v>256.0899963378906</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="BA8">
-        <v>254.6600036621094</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="BB8">
-        <v>255.0899963378906</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="BC8">
-        <v>259.1400146484375</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="BD8">
-        <v>260.7799987792969</v>
+        <v>258.510009765625</v>
       </c>
       <c r="BE8">
-        <v>258.510009765625</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="BF8">
-        <v>259.4700012207031</v>
+        <v>257.0599975585938</v>
       </c>
       <c r="BG8">
-        <v>257.0599975585938</v>
+        <v>264.9299926757812</v>
       </c>
       <c r="BH8">
-        <v>264.9299926757812</v>
+        <v>264.6300048828125</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -8471,181 +8517,181 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>33.9808349609375</v>
+        <v>33.09705352783203</v>
       </c>
       <c r="C9">
-        <v>33.09705352783203</v>
+        <v>33.18642044067383</v>
       </c>
       <c r="D9">
-        <v>33.18642044067383</v>
+        <v>32.77928924560547</v>
       </c>
       <c r="E9">
-        <v>32.77928924560547</v>
+        <v>32.72963714599609</v>
       </c>
       <c r="F9">
-        <v>32.72963714599609</v>
+        <v>32.34236526489258</v>
       </c>
       <c r="G9">
-        <v>32.34236526489258</v>
+        <v>31.64725685119629</v>
       </c>
       <c r="H9">
-        <v>31.64725685119629</v>
+        <v>32.13383102416992</v>
       </c>
       <c r="I9">
-        <v>32.13383102416992</v>
+        <v>32.23313140869141</v>
       </c>
       <c r="J9">
-        <v>32.23313140869141</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="K9">
-        <v>33.76237106323242</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="L9">
-        <v>34.81496429443359</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="M9">
-        <v>33.05733489990234</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="N9">
-        <v>33.20628356933594</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="O9">
-        <v>34.42768478393555</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="P9">
-        <v>34.28866577148438</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="Q9">
-        <v>34.03048324584961</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="R9">
-        <v>34.04041290283203</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="S9">
-        <v>34.97384262084961</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="T9">
-        <v>34.59650039672852</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="U9">
-        <v>35.52000045776367</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="V9">
-        <v>36.18000030517578</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="W9">
-        <v>36.41999816894531</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="X9">
-        <v>36.15000152587891</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="Y9">
-        <v>34.7400016784668</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="Z9">
-        <v>34.93000030517578</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="AA9">
-        <v>36.70000076293945</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="AB9">
-        <v>36.33000183105469</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="AC9">
-        <v>37.31999969482422</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="AD9">
-        <v>36.86999893188477</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="AE9">
-        <v>35.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="AF9">
-        <v>34.65999984741211</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="AG9">
-        <v>36.52999877929688</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="AH9">
-        <v>37.63000106811523</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AI9">
-        <v>41.02000045776367</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AJ9">
-        <v>40.61999893188477</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AK9">
-        <v>39.97000122070312</v>
+        <v>40</v>
       </c>
       <c r="AL9">
-        <v>40</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AM9">
-        <v>40.47000122070312</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AN9">
-        <v>41.58000183105469</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AO9">
-        <v>42.36999893188477</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AP9">
-        <v>43.45000076293945</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AQ9">
-        <v>44.38999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AR9">
-        <v>43.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AS9">
-        <v>42.95999908447266</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="AT9">
-        <v>41.34999847412109</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AU9">
-        <v>41.18999862670898</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="AV9">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="AW9">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="AX9">
-        <v>43.15000152587891</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="AY9">
-        <v>44.29999923706055</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="AZ9">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="BA9">
-        <v>44.18000030517578</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="BB9">
-        <v>42.77000045776367</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="BC9">
-        <v>43.54999923706055</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="BD9">
-        <v>44.84000015258789</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="BE9">
-        <v>44.52999877929688</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="BF9">
-        <v>44.72999954223633</v>
+        <v>45.02999877929688</v>
       </c>
       <c r="BG9">
-        <v>45.02999877929688</v>
+        <v>47.40999984741211</v>
       </c>
       <c r="BH9">
-        <v>47.40999984741211</v>
+        <v>44.79000091552734</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -8653,181 +8699,181 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>199.81640625</v>
+        <v>198.7775726318359</v>
       </c>
       <c r="C10">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="D10">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="E10">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="F10">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="G10">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="H10">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="I10">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="J10">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="K10">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="L10">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="M10">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="N10">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="O10">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="P10">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="Q10">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="R10">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="S10">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="T10">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="U10">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="V10">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="W10">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="X10">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="Y10">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="Z10">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="AA10">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="AB10">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="AC10">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="AD10">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="AE10">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="AF10">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="AG10">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="AH10">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="AI10">
+        <v>217.2568969726562</v>
+      </c>
+      <c r="AJ10">
+        <v>223.8395233154297</v>
+      </c>
+      <c r="AK10">
+        <v>225.0481872558594</v>
+      </c>
+      <c r="AL10">
+        <v>224.9083404541016</v>
+      </c>
+      <c r="AM10">
+        <v>224.7584991455078</v>
+      </c>
+      <c r="AN10">
+        <v>219.4944000244141</v>
+      </c>
+      <c r="AO10">
+        <v>217.3168334960938</v>
+      </c>
+      <c r="AP10">
+        <v>216.6076354980469</v>
+      </c>
+      <c r="AQ10">
+        <v>214.4800109863281</v>
+      </c>
+      <c r="AR10">
+        <v>208.2469787597656</v>
+      </c>
+      <c r="AS10">
+        <v>212.8118743896484</v>
+      </c>
+      <c r="AT10">
+        <v>209.4256591796875</v>
+      </c>
+      <c r="AU10">
+        <v>227.7251739501953</v>
+      </c>
+      <c r="AV10">
         <v>217.3068389892578</v>
       </c>
-      <c r="AJ10">
-        <v>217.2568969726562</v>
-      </c>
-      <c r="AK10">
-        <v>223.8395233154297</v>
-      </c>
-      <c r="AL10">
-        <v>225.0481872558594</v>
-      </c>
-      <c r="AM10">
-        <v>224.9083404541016</v>
-      </c>
-      <c r="AN10">
-        <v>224.7584991455078</v>
-      </c>
-      <c r="AO10">
-        <v>219.4944000244141</v>
-      </c>
-      <c r="AP10">
-        <v>217.3168334960938</v>
-      </c>
-      <c r="AQ10">
-        <v>216.6076354980469</v>
-      </c>
-      <c r="AR10">
-        <v>214.4800109863281</v>
-      </c>
-      <c r="AS10">
-        <v>208.2469787597656</v>
-      </c>
-      <c r="AT10">
-        <v>212.8118743896484</v>
-      </c>
-      <c r="AU10">
-        <v>209.4256591796875</v>
-      </c>
-      <c r="AV10">
-        <v>227.7251739501953</v>
-      </c>
       <c r="AW10">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="AX10">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="AY10">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="AZ10">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="BA10">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="BB10">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="BC10">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="BD10">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="BE10">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="BF10">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="BG10">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="BH10">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -8835,181 +8881,181 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>315.8800048828125</v>
+        <v>319.6471252441406</v>
       </c>
       <c r="C11">
-        <v>319.6471252441406</v>
+        <v>317.2054748535156</v>
       </c>
       <c r="D11">
-        <v>317.2054748535156</v>
+        <v>326.2545166015625</v>
       </c>
       <c r="E11">
-        <v>326.2545166015625</v>
+        <v>330.7491760253906</v>
       </c>
       <c r="F11">
-        <v>330.7491760253906</v>
+        <v>328.9951477050781</v>
       </c>
       <c r="G11">
-        <v>328.9951477050781</v>
+        <v>333.4798278808594</v>
       </c>
       <c r="H11">
-        <v>333.4798278808594</v>
+        <v>341.1436157226562</v>
       </c>
       <c r="I11">
-        <v>341.1436157226562</v>
+        <v>338.0143432617188</v>
       </c>
       <c r="J11">
-        <v>338.0143432617188</v>
+        <v>342.5588073730469</v>
       </c>
       <c r="K11">
-        <v>342.5588073730469</v>
+        <v>336.7885131835938</v>
       </c>
       <c r="L11">
-        <v>336.7885131835938</v>
+        <v>336.3301086425781</v>
       </c>
       <c r="M11">
-        <v>336.3301086425781</v>
+        <v>337.7651977539062</v>
       </c>
       <c r="N11">
-        <v>337.7651977539062</v>
+        <v>340.3463745117188</v>
       </c>
       <c r="O11">
-        <v>340.3463745117188</v>
+        <v>335.6822814941406</v>
       </c>
       <c r="P11">
-        <v>335.6822814941406</v>
+        <v>328.0683288574219</v>
       </c>
       <c r="Q11">
-        <v>328.0683288574219</v>
+        <v>336.6689453125</v>
       </c>
       <c r="R11">
-        <v>336.6689453125</v>
+        <v>367.7227783203125</v>
       </c>
       <c r="S11">
-        <v>367.7227783203125</v>
+        <v>367.244384765625</v>
       </c>
       <c r="T11">
-        <v>367.244384765625</v>
+        <v>368.3705444335938</v>
       </c>
       <c r="U11">
-        <v>368.3705444335938</v>
+        <v>370.8121643066406</v>
       </c>
       <c r="V11">
-        <v>370.8121643066406</v>
+        <v>375.0875549316406</v>
       </c>
       <c r="W11">
-        <v>375.0875549316406</v>
+        <v>385.9404907226562</v>
       </c>
       <c r="X11">
-        <v>385.9404907226562</v>
+        <v>389.0199584960938</v>
       </c>
       <c r="Y11">
-        <v>389.0199584960938</v>
+        <v>395.8665161132812</v>
       </c>
       <c r="Z11">
-        <v>395.8665161132812</v>
+        <v>387.6845092773438</v>
       </c>
       <c r="AA11">
-        <v>387.6845092773438</v>
+        <v>374.7088623046875</v>
       </c>
       <c r="AB11">
-        <v>374.7088623046875</v>
+        <v>373.0844116210938</v>
       </c>
       <c r="AC11">
-        <v>373.0844116210938</v>
+        <v>372.5462646484375</v>
       </c>
       <c r="AD11">
-        <v>372.5462646484375</v>
+        <v>375.8648986816406</v>
       </c>
       <c r="AE11">
-        <v>375.8648986816406</v>
+        <v>381.1468811035156</v>
       </c>
       <c r="AF11">
-        <v>381.1468811035156</v>
+        <v>384.6847534179688</v>
       </c>
       <c r="AG11">
-        <v>384.6847534179688</v>
+        <v>383.0005187988281</v>
       </c>
       <c r="AH11">
-        <v>383.0005187988281</v>
+        <v>374.3401184082031</v>
       </c>
       <c r="AI11">
-        <v>374.3401184082031</v>
+        <v>374.3301391601562</v>
       </c>
       <c r="AJ11">
-        <v>374.3301391601562</v>
+        <v>368.8987426757812</v>
       </c>
       <c r="AK11">
-        <v>368.8987426757812</v>
+        <v>368.7392883300781</v>
       </c>
       <c r="AL11">
-        <v>368.7392883300781</v>
+        <v>369.0980224609375</v>
       </c>
       <c r="AM11">
-        <v>369.0980224609375</v>
+        <v>363.2680053710938</v>
       </c>
       <c r="AN11">
-        <v>363.2680053710938</v>
+        <v>366.6763305664062</v>
       </c>
       <c r="AO11">
-        <v>366.6763305664062</v>
+        <v>360.9857788085938</v>
       </c>
       <c r="AP11">
-        <v>360.9857788085938</v>
+        <v>363.248046875</v>
       </c>
       <c r="AQ11">
-        <v>363.248046875</v>
+        <v>362.3411254882812</v>
       </c>
       <c r="AR11">
-        <v>362.3411254882812</v>
+        <v>369.2873840332031</v>
       </c>
       <c r="AS11">
-        <v>369.2873840332031</v>
+        <v>368.4004516601562</v>
       </c>
       <c r="AT11">
-        <v>368.4004516601562</v>
+        <v>369.8853454589844</v>
       </c>
       <c r="AU11">
-        <v>369.8853454589844</v>
+        <v>368.071533203125</v>
       </c>
       <c r="AV11">
-        <v>368.071533203125</v>
+        <v>368.6396179199219</v>
       </c>
       <c r="AW11">
-        <v>368.6396179199219</v>
+        <v>364.6831359863281</v>
       </c>
       <c r="AX11">
-        <v>364.6831359863281</v>
+        <v>362.6799926757812</v>
       </c>
       <c r="AY11">
-        <v>362.6799926757812</v>
+        <v>364.9322814941406</v>
       </c>
       <c r="AZ11">
-        <v>364.9322814941406</v>
+        <v>373.0644836425781</v>
       </c>
       <c r="BA11">
-        <v>373.0644836425781</v>
+        <v>368.0914916992188</v>
       </c>
       <c r="BB11">
-        <v>368.0914916992188</v>
+        <v>364.4140625</v>
       </c>
       <c r="BC11">
-        <v>364.4140625</v>
+        <v>365.6000061035156</v>
       </c>
       <c r="BD11">
-        <v>365.6000061035156</v>
+        <v>367.5599975585938</v>
       </c>
       <c r="BE11">
-        <v>367.5599975585938</v>
+        <v>375.2000122070312</v>
       </c>
       <c r="BF11">
-        <v>375.2000122070312</v>
+        <v>378.0499877929688</v>
       </c>
       <c r="BG11">
-        <v>378.0499877929688</v>
+        <v>377.9700012207031</v>
       </c>
       <c r="BH11">
-        <v>377.9700012207031</v>
+        <v>378.9200134277344</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -9017,181 +9063,181 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>345.8554382324219</v>
+        <v>344.816162109375</v>
       </c>
       <c r="C12">
-        <v>344.816162109375</v>
+        <v>341.9679870605469</v>
       </c>
       <c r="D12">
-        <v>341.9679870605469</v>
+        <v>334.4728698730469</v>
       </c>
       <c r="E12">
-        <v>334.4728698730469</v>
+        <v>351.0520935058594</v>
       </c>
       <c r="F12">
-        <v>351.0520935058594</v>
+        <v>353.1007385253906</v>
       </c>
       <c r="G12">
-        <v>353.1007385253906</v>
+        <v>357.6578063964844</v>
       </c>
       <c r="H12">
-        <v>357.6578063964844</v>
+        <v>355.9489135742188</v>
       </c>
       <c r="I12">
-        <v>355.9489135742188</v>
+        <v>364.6632385253906</v>
       </c>
       <c r="J12">
-        <v>364.6632385253906</v>
+        <v>363.3840942382812</v>
       </c>
       <c r="K12">
-        <v>363.3840942382812</v>
+        <v>358.4772644042969</v>
       </c>
       <c r="L12">
-        <v>358.4772644042969</v>
+        <v>356.0088500976562</v>
       </c>
       <c r="M12">
-        <v>356.0088500976562</v>
+        <v>354.7996520996094</v>
       </c>
       <c r="N12">
-        <v>354.7996520996094</v>
+        <v>350.4425048828125</v>
       </c>
       <c r="O12">
-        <v>350.4425048828125</v>
+        <v>357.09814453125</v>
       </c>
       <c r="P12">
-        <v>357.09814453125</v>
+        <v>369.9697875976562</v>
       </c>
       <c r="Q12">
-        <v>369.9697875976562</v>
+        <v>353.5804443359375</v>
       </c>
       <c r="R12">
-        <v>353.5804443359375</v>
+        <v>345.8954467773438</v>
       </c>
       <c r="S12">
-        <v>345.8954467773438</v>
+        <v>351.1420288085938</v>
       </c>
       <c r="T12">
-        <v>351.1420288085938</v>
+        <v>345.9653930664062</v>
       </c>
       <c r="U12">
-        <v>345.9653930664062</v>
+        <v>341.6881713867188</v>
       </c>
       <c r="V12">
-        <v>341.6881713867188</v>
+        <v>318.1334533691406</v>
       </c>
       <c r="W12">
-        <v>318.1334533691406</v>
+        <v>318.8829650878906</v>
       </c>
       <c r="X12">
-        <v>318.8829650878906</v>
+        <v>326.3581237792969</v>
       </c>
       <c r="Y12">
-        <v>326.3581237792969</v>
+        <v>332.3842163085938</v>
       </c>
       <c r="Z12">
-        <v>332.3842163085938</v>
+        <v>335.5421752929688</v>
       </c>
       <c r="AA12">
-        <v>335.5421752929688</v>
+        <v>333.4635009765625</v>
       </c>
       <c r="AB12">
-        <v>333.4635009765625</v>
+        <v>356.4186096191406</v>
       </c>
       <c r="AC12">
-        <v>356.4186096191406</v>
+        <v>372.2283325195312</v>
       </c>
       <c r="AD12">
-        <v>372.2283325195312</v>
+        <v>375.1064758300781</v>
       </c>
       <c r="AE12">
-        <v>375.1064758300781</v>
+        <v>359.8963623046875</v>
       </c>
       <c r="AF12">
-        <v>359.8963623046875</v>
+        <v>356.3886108398438</v>
       </c>
       <c r="AG12">
-        <v>356.3886108398438</v>
+        <v>353.2406616210938</v>
       </c>
       <c r="AH12">
-        <v>353.2406616210938</v>
+        <v>355.609130859375</v>
       </c>
       <c r="AI12">
-        <v>355.609130859375</v>
+        <v>342.7774658203125</v>
       </c>
       <c r="AJ12">
-        <v>342.7774658203125</v>
+        <v>342.1478576660156</v>
       </c>
       <c r="AK12">
-        <v>342.1478576660156</v>
+        <v>343.7168579101562</v>
       </c>
       <c r="AL12">
-        <v>343.7168579101562</v>
+        <v>343.3171081542969</v>
       </c>
       <c r="AM12">
-        <v>343.3171081542969</v>
+        <v>341.2284851074219</v>
       </c>
       <c r="AN12">
-        <v>341.2284851074219</v>
+        <v>341.0585632324219</v>
       </c>
       <c r="AO12">
-        <v>341.0585632324219</v>
+        <v>341.4783325195312</v>
       </c>
       <c r="AP12">
-        <v>341.4783325195312</v>
+        <v>337.9805908203125</v>
       </c>
       <c r="AQ12">
-        <v>337.9805908203125</v>
+        <v>341.5282592773438</v>
       </c>
       <c r="AR12">
-        <v>341.5282592773438</v>
+        <v>344.3664245605469</v>
       </c>
       <c r="AS12">
-        <v>344.3664245605469</v>
+        <v>343.1172485351562</v>
       </c>
       <c r="AT12">
-        <v>343.1172485351562</v>
+        <v>338.8800048828125</v>
       </c>
       <c r="AU12">
-        <v>338.8800048828125</v>
+        <v>337.4908752441406</v>
       </c>
       <c r="AV12">
-        <v>337.4908752441406</v>
+        <v>342.6575317382812</v>
       </c>
       <c r="AW12">
-        <v>342.6575317382812</v>
+        <v>335.1923828125</v>
       </c>
       <c r="AX12">
-        <v>335.1923828125</v>
+        <v>331.8145751953125</v>
       </c>
       <c r="AY12">
-        <v>331.8145751953125</v>
+        <v>333.5634460449219</v>
       </c>
       <c r="AZ12">
-        <v>333.5634460449219</v>
+        <v>338.8599853515625</v>
       </c>
       <c r="BA12">
-        <v>338.8599853515625</v>
+        <v>335.3099975585938</v>
       </c>
       <c r="BB12">
-        <v>335.3099975585938</v>
+        <v>335.3800048828125</v>
       </c>
       <c r="BC12">
-        <v>335.3800048828125</v>
+        <v>328.3800048828125</v>
       </c>
       <c r="BD12">
-        <v>328.3800048828125</v>
+        <v>330.3900146484375</v>
       </c>
       <c r="BE12">
-        <v>330.3900146484375</v>
+        <v>335.4500122070312</v>
       </c>
       <c r="BF12">
-        <v>335.4500122070312</v>
+        <v>345.7099914550781</v>
       </c>
       <c r="BG12">
-        <v>345.7099914550781</v>
+        <v>341.4299926757812</v>
       </c>
       <c r="BH12">
-        <v>341.4299926757812</v>
+        <v>339.3599853515625</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -9199,181 +9245,181 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>63.13999938964844</v>
+        <v>62.97000122070312</v>
       </c>
       <c r="C13">
-        <v>62.97000122070312</v>
+        <v>64.76999664306641</v>
       </c>
       <c r="D13">
-        <v>64.76999664306641</v>
+        <v>65.73000335693359</v>
       </c>
       <c r="E13">
-        <v>65.73000335693359</v>
+        <v>64.54000091552734</v>
       </c>
       <c r="F13">
-        <v>64.54000091552734</v>
+        <v>64.19000244140625</v>
       </c>
       <c r="G13">
-        <v>64.19000244140625</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="H13">
-        <v>68.34999847412109</v>
+        <v>67.86000061035156</v>
       </c>
       <c r="I13">
-        <v>67.86000061035156</v>
+        <v>66.05000305175781</v>
       </c>
       <c r="J13">
-        <v>66.05000305175781</v>
+        <v>66.12000274658203</v>
       </c>
       <c r="K13">
-        <v>66.12000274658203</v>
+        <v>67.08999633789062</v>
       </c>
       <c r="L13">
-        <v>67.08999633789062</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="M13">
-        <v>67.59999847412109</v>
+        <v>67.34999847412109</v>
       </c>
       <c r="N13">
-        <v>67.34999847412109</v>
+        <v>68.29000091552734</v>
       </c>
       <c r="O13">
-        <v>68.29000091552734</v>
+        <v>68.72000122070312</v>
       </c>
       <c r="P13">
-        <v>68.72000122070312</v>
+        <v>66.61000061035156</v>
       </c>
       <c r="Q13">
-        <v>66.61000061035156</v>
+        <v>63.88999938964844</v>
       </c>
       <c r="R13">
-        <v>63.88999938964844</v>
+        <v>66.44000244140625</v>
       </c>
       <c r="S13">
-        <v>66.44000244140625</v>
+        <v>65.83999633789062</v>
       </c>
       <c r="T13">
-        <v>65.83999633789062</v>
+        <v>67.58999633789062</v>
       </c>
       <c r="U13">
-        <v>67.58999633789062</v>
+        <v>65.88999938964844</v>
       </c>
       <c r="V13">
-        <v>65.88999938964844</v>
+        <v>63.7400016784668</v>
       </c>
       <c r="W13">
-        <v>63.7400016784668</v>
+        <v>63.40999984741211</v>
       </c>
       <c r="X13">
-        <v>63.40999984741211</v>
+        <v>64.08000183105469</v>
       </c>
       <c r="Y13">
-        <v>64.08000183105469</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="Z13">
-        <v>63.90999984741211</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="AA13">
-        <v>61.81999969482422</v>
+        <v>60.84000015258789</v>
       </c>
       <c r="AB13">
-        <v>60.84000015258789</v>
+        <v>62.22000122070312</v>
       </c>
       <c r="AC13">
-        <v>62.22000122070312</v>
+        <v>63.7599983215332</v>
       </c>
       <c r="AD13">
-        <v>63.7599983215332</v>
+        <v>64.06999969482422</v>
       </c>
       <c r="AE13">
-        <v>64.06999969482422</v>
+        <v>66.98999786376953</v>
       </c>
       <c r="AF13">
-        <v>66.98999786376953</v>
+        <v>64.19999694824219</v>
       </c>
       <c r="AG13">
-        <v>64.19999694824219</v>
+        <v>65.76999664306641</v>
       </c>
       <c r="AH13">
-        <v>65.76999664306641</v>
+        <v>66.56999969482422</v>
       </c>
       <c r="AI13">
-        <v>66.56999969482422</v>
+        <v>64.87999725341797</v>
       </c>
       <c r="AJ13">
-        <v>64.87999725341797</v>
+        <v>67.06999969482422</v>
       </c>
       <c r="AK13">
-        <v>67.06999969482422</v>
+        <v>66.04000091552734</v>
       </c>
       <c r="AL13">
-        <v>66.04000091552734</v>
+        <v>67.47000122070312</v>
       </c>
       <c r="AM13">
-        <v>67.47000122070312</v>
+        <v>64.41000366210938</v>
       </c>
       <c r="AN13">
-        <v>64.41000366210938</v>
+        <v>65.22000122070312</v>
       </c>
       <c r="AO13">
-        <v>65.22000122070312</v>
+        <v>64.69999694824219</v>
       </c>
       <c r="AP13">
-        <v>64.69999694824219</v>
+        <v>64.13999938964844</v>
       </c>
       <c r="AQ13">
-        <v>64.13999938964844</v>
+        <v>65.01999664306641</v>
       </c>
       <c r="AR13">
-        <v>65.01999664306641</v>
+        <v>65.65000152587891</v>
       </c>
       <c r="AS13">
-        <v>65.65000152587891</v>
+        <v>65</v>
       </c>
       <c r="AT13">
-        <v>65</v>
+        <v>65.47000122070312</v>
       </c>
       <c r="AU13">
-        <v>65.47000122070312</v>
+        <v>65.33000183105469</v>
       </c>
       <c r="AV13">
-        <v>65.33000183105469</v>
+        <v>64.75</v>
       </c>
       <c r="AW13">
-        <v>64.75</v>
+        <v>64.33999633789062</v>
       </c>
       <c r="AX13">
-        <v>64.33999633789062</v>
+        <v>65.23000335693359</v>
       </c>
       <c r="AY13">
-        <v>65.23000335693359</v>
+        <v>67.33999633789062</v>
       </c>
       <c r="AZ13">
-        <v>67.33999633789062</v>
+        <v>68.01999664306641</v>
       </c>
       <c r="BA13">
-        <v>68.01999664306641</v>
+        <v>67.04000091552734</v>
       </c>
       <c r="BB13">
-        <v>67.04000091552734</v>
+        <v>64.58000183105469</v>
       </c>
       <c r="BC13">
-        <v>64.58000183105469</v>
+        <v>64.05999755859375</v>
       </c>
       <c r="BD13">
-        <v>64.05999755859375</v>
+        <v>65.40000152587891</v>
       </c>
       <c r="BE13">
-        <v>65.40000152587891</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="BF13">
-        <v>66.41999816894531</v>
+        <v>69.41000366210938</v>
       </c>
       <c r="BG13">
-        <v>69.41000366210938</v>
+        <v>67.66000366210938</v>
       </c>
       <c r="BH13">
-        <v>67.66000366210938</v>
+        <v>66.01000213623047</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="248">
   <si>
     <t>DELL</t>
   </si>
@@ -282,6 +282,9 @@
     <t>2026-09-17</t>
   </si>
   <si>
+    <t>2026-09-18</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -339,18 +342,18 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>HPE</t>
+  </si>
+  <si>
+    <t>Hewlett Packard Enterprise</t>
+  </si>
+  <si>
     <t>GOOGL</t>
   </si>
   <si>
     <t>Alphabet Inc. (Class A)</t>
   </si>
   <si>
-    <t>HPE</t>
-  </si>
-  <si>
-    <t>Hewlett Packard Enterprise</t>
-  </si>
-  <si>
     <t>CRM</t>
   </si>
   <si>
@@ -363,33 +366,39 @@
     <t>NetApp</t>
   </si>
   <si>
+    <t>SMCI</t>
+  </si>
+  <si>
+    <t>Supermicro</t>
+  </si>
+  <si>
+    <t>TGT</t>
+  </si>
+  <si>
+    <t>Target Corporation</t>
+  </si>
+  <si>
+    <t>Consumer Staples</t>
+  </si>
+  <si>
+    <t>INTC</t>
+  </si>
+  <si>
+    <t>Intel</t>
+  </si>
+  <si>
+    <t>INCY</t>
+  </si>
+  <si>
+    <t>Incyte</t>
+  </si>
+  <si>
     <t>ALL</t>
   </si>
   <si>
     <t>Allstate</t>
   </si>
   <si>
-    <t>TGT</t>
-  </si>
-  <si>
-    <t>Target Corporation</t>
-  </si>
-  <si>
-    <t>Consumer Staples</t>
-  </si>
-  <si>
-    <t>INCY</t>
-  </si>
-  <si>
-    <t>Incyte</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
-    <t>Intel</t>
-  </si>
-  <si>
     <t>AMZN</t>
   </si>
   <si>
@@ -399,6 +408,12 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
+    <t>HPQ</t>
+  </si>
+  <si>
+    <t>HP Inc.</t>
+  </si>
+  <si>
     <t>FTNT</t>
   </si>
   <si>
@@ -411,10 +426,16 @@
     <t>Biogen</t>
   </si>
   <si>
-    <t>SMCI</t>
-  </si>
-  <si>
-    <t>Supermicro</t>
+    <t>DLTR</t>
+  </si>
+  <si>
+    <t>Dollar Tree</t>
+  </si>
+  <si>
+    <t>RVTY</t>
+  </si>
+  <si>
+    <t>Revvity</t>
   </si>
   <si>
     <t>CVX</t>
@@ -423,10 +444,10 @@
     <t>Chevron Corporation</t>
   </si>
   <si>
-    <t>HPQ</t>
-  </si>
-  <si>
-    <t>HP Inc.</t>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
   </si>
   <si>
     <t>COF</t>
@@ -441,22 +462,16 @@
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
-    <t>DLTR</t>
-  </si>
-  <si>
-    <t>Dollar Tree</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>RVTY</t>
-  </si>
-  <si>
-    <t>Revvity</t>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
+    <t>BBY</t>
+  </si>
+  <si>
+    <t>Best Buy</t>
   </si>
   <si>
     <t>GEN</t>
@@ -465,10 +480,16 @@
     <t>Gen Digital</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
+    <t>FFIV</t>
+  </si>
+  <si>
+    <t>F5, Inc.</t>
+  </si>
+  <si>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
   </si>
   <si>
     <t>EOG</t>
@@ -483,16 +504,10 @@
     <t>News Corp (Class A)</t>
   </si>
   <si>
-    <t>WAT</t>
-  </si>
-  <si>
-    <t>Waters Corporation</t>
-  </si>
-  <si>
-    <t>FFIV</t>
-  </si>
-  <si>
-    <t>F5, Inc.</t>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>Lilly (Eli)</t>
   </si>
   <si>
     <t>AIZ</t>
@@ -501,18 +516,6 @@
     <t>Assurant</t>
   </si>
   <si>
-    <t>BBY</t>
-  </si>
-  <si>
-    <t>Best Buy</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -591,7 +594,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-18 00:25 UTC · данные на 2026-09-17 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-19 00:25 UTC · данные на 2026-09-18 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -672,7 +675,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-18 00:25 UTC</t>
+    <t>2026-09-19 00:25 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1184,9 +1187,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$20</c:f>
+              <c:f>Капитал!$A$5:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1234,16 +1237,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2026-09-17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2026-09-18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$20</c:f>
+              <c:f>Капитал!$D$5:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1290,6 +1296,9 @@
                   <c:v>10163.98</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>10163.98</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -1315,9 +1324,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$20</c:f>
+              <c:f>Капитал!$A$5:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1365,16 +1374,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2026-09-17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2026-09-18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$20</c:f>
+              <c:f>Капитал!$F$5:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1421,6 +1433,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1561,9 +1576,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$20</c:f>
+              <c:f>Капитал!$A$5:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1611,16 +1626,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2026-09-17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2026-09-18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$20</c:f>
+              <c:f>Капитал!$D$5:$D$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1667,6 +1685,9 @@
                   <c:v>10163.98</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>10163.98</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>10163.98</c:v>
                 </c:pt>
               </c:numCache>
@@ -1692,9 +1713,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$20</c:f>
+              <c:f>Капитал!$A$5:$A$21</c:f>
               <c:strCache>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1742,16 +1763,19 @@
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>2026-09-17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2026-09-18</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$20</c:f>
+              <c:f>Капитал!$F$5:$F$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="16"/>
+                <c:ptCount val="17"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1798,6 +1822,9 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="15">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2293,12 +2320,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2306,13 +2333,13 @@
         <v>74</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2331,27 +2358,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>2.67660249974473</v>
+        <v>2.589309858523897</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H9" s="7">
         <v>13</v>
@@ -2359,7 +2386,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2388,7 +2415,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2396,7 +2423,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2404,23 +2431,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C18" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C19" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2428,55 +2455,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C25" s="12">
-        <v>0.1041434245885151</v>
+        <v>0.1009259823862771</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C26" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2485,12 +2512,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2665,11 +2692,11 @@
         <v>0.20574673193473192</v>
       </c>
       <c r="L5" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
@@ -2716,11 +2743,11 @@
         <v>-0.0023453865133649322</v>
       </c>
       <c r="L6" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
@@ -2767,11 +2794,11 @@
         <v>0.001157858695424527</v>
       </c>
       <c r="L7" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
@@ -2818,11 +2845,11 @@
         <v>-0.07694846931544182</v>
       </c>
       <c r="L8" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
@@ -2869,11 +2896,11 @@
         <v>0.06333640885022687</v>
       </c>
       <c r="L9" s="11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
@@ -2920,11 +2947,11 @@
         <v>0.04063182043921025</v>
       </c>
       <c r="L10" s="11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
@@ -2971,11 +2998,11 @@
         <v>0.027097931394638883</v>
       </c>
       <c r="L11" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
@@ -3022,11 +3049,11 @@
         <v>0.020460374570953403</v>
       </c>
       <c r="L12" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
@@ -3073,11 +3100,11 @@
         <v>0.030391348943966064</v>
       </c>
       <c r="L13" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
@@ -3124,11 +3151,11 @@
         <v>-0.001824598914652231</v>
       </c>
       <c r="L14" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="11">
         <f>MAX(0,21-L14)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N14" s="20">
         <v>0.6809721702367264</v>
@@ -3175,11 +3202,11 @@
         <v>-0.013417568245354424</v>
       </c>
       <c r="L15" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" s="11">
         <f>MAX(0,21-L15)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N15" s="20">
         <v>0.8197914702434592</v>
@@ -3226,11 +3253,11 @@
         <v>0.018953362974839495</v>
       </c>
       <c r="L16" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M16" s="11">
         <f>MAX(0,21-L16)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N16" s="20">
         <v>0.776423257523575</v>
@@ -3277,11 +3304,11 @@
         <v>0.03068356896480827</v>
       </c>
       <c r="L17" s="11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M17" s="11">
         <f>MAX(0,21-L17)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N17" s="20">
         <v>0.7994794227521653</v>
@@ -3663,7 +3690,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4024,6 +4051,25 @@
         <v>13</v>
       </c>
       <c r="F20" s="10"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="10">
+        <v>3768.96</v>
+      </c>
+      <c r="C21" s="10">
+        <v>6395.02</v>
+      </c>
+      <c r="D21" s="10">
+        <f>B21+C21</f>
+        <v>10163.98</v>
+      </c>
+      <c r="E21" s="11">
+        <v>13</v>
+      </c>
+      <c r="F21" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4052,12 +4098,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4074,52 +4120,52 @@
         <v>17</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -4136,10 +4182,10 @@
         <v>42</v>
       </c>
       <c r="E5" s="10">
-        <v>403.2799987792969</v>
+        <v>412.5299987792969</v>
       </c>
       <c r="F5" s="17">
-        <v>1.050913661811838</v>
+        <v>1.083731117121839</v>
       </c>
       <c r="G5" s="20">
         <v>0.6555418499989493</v>
@@ -4151,16 +4197,16 @@
         <v>2.861941581666567</v>
       </c>
       <c r="J5" s="20">
-        <v>2.344480223395413</v>
+        <v>2.441501226766235</v>
       </c>
       <c r="K5" s="20">
         <v>0.6053625381238342</v>
       </c>
       <c r="L5" s="20">
-        <v>0.220086459678554</v>
+        <v>0.2024089254245169</v>
       </c>
       <c r="M5" s="20">
-        <v>-0.4135723315679154</v>
+        <v>-0.3539247521429589</v>
       </c>
       <c r="N5" s="20">
         <v>16.28786</v>
@@ -4175,13 +4221,13 @@
         <v>0.517</v>
       </c>
       <c r="R5" s="12">
-        <v>0.723859783852866</v>
+        <v>0.7449123815448093</v>
       </c>
       <c r="S5" s="11">
-        <v>77.54124888161878</v>
+        <v>79.91752964857486</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -4198,10 +4244,10 @@
         <v>42</v>
       </c>
       <c r="E6" s="10">
-        <v>413.9200134277344</v>
+        <v>421.9599914550781</v>
       </c>
       <c r="F6" s="17">
-        <v>1.02708127080466</v>
+        <v>1.062085137069233</v>
       </c>
       <c r="G6" s="20">
         <v>0.6866590119647646</v>
@@ -4213,16 +4259,16 @@
         <v>2.437187840999147</v>
       </c>
       <c r="J6" s="20">
-        <v>2.307933742479242</v>
+        <v>2.41324168774001</v>
       </c>
       <c r="K6" s="20">
         <v>0.7722871304671322</v>
       </c>
       <c r="L6" s="20">
-        <v>0.2804577175280851</v>
+        <v>0.2642108986471419</v>
       </c>
       <c r="M6" s="20">
-        <v>-0.6226865174124547</v>
+        <v>-0.567857869672472</v>
       </c>
       <c r="N6" s="20">
         <v>13.7380295</v>
@@ -4237,13 +4283,13 @@
         <v>0.537</v>
       </c>
       <c r="R6" s="12">
-        <v>0.7861504747971995</v>
+        <v>0.7978758027795667</v>
       </c>
       <c r="S6" s="11">
-        <v>80.53931347979024</v>
+        <v>82.58942557134458</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -4251,61 +4297,61 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E7" s="10">
-        <v>563.2899780273438</v>
+        <v>977.5</v>
       </c>
       <c r="F7" s="17">
-        <v>0.9721358964097886</v>
+        <v>0.9630148652041568</v>
       </c>
       <c r="G7" s="20">
-        <v>-0.1521673872440041</v>
+        <v>-0.495023614230421</v>
       </c>
       <c r="H7" s="20">
-        <v>-0.8490211958234019</v>
+        <v>1.812724042922127</v>
       </c>
       <c r="I7" s="20">
-        <v>2.18194679071571</v>
+        <v>3.960347878543698</v>
       </c>
       <c r="J7" s="20">
-        <v>2.9508924467175</v>
+        <v>1.800547012967832</v>
       </c>
       <c r="K7" s="20">
-        <v>1.599697301156443</v>
+        <v>0.4791386951481922</v>
       </c>
       <c r="L7" s="20">
-        <v>-2.913898944425201</v>
+        <v>-3.240137711546244</v>
       </c>
       <c r="M7" s="20">
-        <v>0.1847158110671452</v>
+        <v>-0.46505004464545</v>
       </c>
       <c r="N7" s="20">
-        <v>33.00116</v>
+        <v>22.024843</v>
       </c>
       <c r="O7" s="20">
-        <v>-256.4602</v>
+        <v>10.93157</v>
       </c>
       <c r="P7" s="12">
-        <v>0</v>
+        <v>0.66638</v>
       </c>
       <c r="Q7" s="12">
-        <v>0.577</v>
+        <v>3.457</v>
       </c>
       <c r="R7" s="12">
-        <v>2.69888619912948</v>
+        <v>1.11825313845578</v>
       </c>
       <c r="S7" s="11">
-        <v>63.28447499851127</v>
+        <v>53.81057842351695</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -4313,61 +4359,61 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="10">
-        <v>926.5499877929688</v>
+        <v>588.4000244140625</v>
       </c>
       <c r="F8" s="17">
-        <v>0.8979010563309927</v>
+        <v>0.9618277080073464</v>
       </c>
       <c r="G8" s="20">
-        <v>-0.495023614230421</v>
+        <v>-0.1521673872440041</v>
       </c>
       <c r="H8" s="20">
-        <v>1.812724042922127</v>
+        <v>-0.8490211958234019</v>
       </c>
       <c r="I8" s="20">
-        <v>3.960347878543698</v>
+        <v>2.18194679071571</v>
       </c>
       <c r="J8" s="20">
-        <v>1.575069734885173</v>
+        <v>2.923721879087933</v>
       </c>
       <c r="K8" s="20">
-        <v>0.4791386951481922</v>
+        <v>1.599697301156443</v>
       </c>
       <c r="L8" s="20">
-        <v>-3.355540730004984</v>
+        <v>-2.9898953367022</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.3468805989059708</v>
+        <v>0.2147503788552398</v>
       </c>
       <c r="N8" s="20">
-        <v>22.024843</v>
+        <v>33.00116</v>
       </c>
       <c r="O8" s="20">
-        <v>10.93157</v>
+        <v>-256.4602</v>
       </c>
       <c r="P8" s="12">
-        <v>0.66638</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="12">
-        <v>3.457</v>
+        <v>0.577</v>
       </c>
       <c r="R8" s="12">
-        <v>1.008018000554102</v>
+        <v>2.962173289129013</v>
       </c>
       <c r="S8" s="11">
-        <v>46.772333110083</v>
+        <v>66.4369442017552</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -4384,10 +4430,10 @@
         <v>42</v>
       </c>
       <c r="E9" s="10">
-        <v>264.6300048828125</v>
+        <v>274.2099914550781</v>
       </c>
       <c r="F9" s="17">
-        <v>0.8787721910309617</v>
+        <v>0.9242214458852961</v>
       </c>
       <c r="G9" s="20">
         <v>0.4728319185405508</v>
@@ -4399,16 +4445,16 @@
         <v>2.406342473145227</v>
       </c>
       <c r="J9" s="20">
-        <v>2.122891940215747</v>
+        <v>2.251151474369534</v>
       </c>
       <c r="K9" s="20">
         <v>0.688309634936399</v>
       </c>
       <c r="L9" s="20">
-        <v>0.4801287330810596</v>
+        <v>0.4343869392039937</v>
       </c>
       <c r="M9" s="20">
-        <v>-0.8589965543597157</v>
+        <v>-0.7375477763494429</v>
       </c>
       <c r="N9" s="20">
         <v>14.818389</v>
@@ -4423,13 +4469,13 @@
         <v>0.531</v>
       </c>
       <c r="R9" s="12">
-        <v>0.5515369999894433</v>
+        <v>0.6074256003440504</v>
       </c>
       <c r="S9" s="11">
-        <v>74.80114937992263</v>
+        <v>79.65375139830765</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -4437,61 +4483,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>10</v>
+        <v>105</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E10" s="10">
-        <v>378.9200134277344</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8750341800101787</v>
+        <v>0.9073626575246675</v>
       </c>
       <c r="G10" s="20">
-        <v>1.195906561845193</v>
+        <v>0.3530298731450531</v>
       </c>
       <c r="H10" s="20">
-        <v>-0.1235890761074189</v>
+        <v>-0.5362564771804156</v>
       </c>
       <c r="I10" s="20">
-        <v>-0.3802373592559733</v>
+        <v>2.205637651643404</v>
       </c>
       <c r="J10" s="20">
-        <v>0.8562439430385483</v>
+        <v>2.424458986824618</v>
       </c>
       <c r="K10" s="20">
-        <v>3.814024146500563</v>
+        <v>0</v>
       </c>
       <c r="L10" s="20">
-        <v>0.5690662211524231</v>
+        <v>-2.123525426681515</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.3891383347493648</v>
+        <v>0.003060777420367589</v>
       </c>
       <c r="N10" s="20">
-        <v>10.080602</v>
+        <v>32.005154</v>
       </c>
       <c r="O10" s="20">
-        <v>2.3630478</v>
+        <v>3.1100981</v>
       </c>
       <c r="P10" s="12">
-        <v>0.26511</v>
+        <v>0.10936</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.003</v>
+        <v>0.337</v>
       </c>
       <c r="R10" s="12">
-        <v>0.2463848523163887</v>
+        <v>1.86898133248227</v>
       </c>
       <c r="S10" s="11">
-        <v>61.69903963485483</v>
+        <v>60.02264828736805</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4499,61 +4545,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E11" s="10">
-        <v>66.01000213623047</v>
+        <v>1614.390014648438</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8553863213010248</v>
+        <v>0.9020986940932447</v>
       </c>
       <c r="G11" s="20">
-        <v>1.282244047014282</v>
+        <v>-0.4801631684214276</v>
       </c>
       <c r="H11" s="20">
-        <v>-1.356970430261629</v>
+        <v>2.05728233065155</v>
       </c>
       <c r="I11" s="20">
-        <v>-0.5801056520622042</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J11" s="20">
-        <v>1.286272228593575</v>
+        <v>1.576557425916651</v>
       </c>
       <c r="K11" s="20">
-        <v>4.1980331407876</v>
+        <v>0.08398078673057012</v>
       </c>
       <c r="L11" s="20">
-        <v>-0.02434954714148995</v>
+        <v>-3.240137711546244</v>
       </c>
       <c r="M11" s="20">
-        <v>0.1440444280304993</v>
+        <v>-0.512406102140251</v>
       </c>
       <c r="N11" s="20">
-        <v>12.502541</v>
+        <v>22.12312</v>
       </c>
       <c r="O11" s="20">
-        <v>1.4542508</v>
+        <v>15.465718</v>
       </c>
       <c r="P11" s="12">
-        <v>-0.20358999</v>
+        <v>0.9164</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.046</v>
+        <v>3.716</v>
       </c>
       <c r="R11" s="12">
-        <v>0.8892388303006635</v>
+        <v>1.14198146375697</v>
       </c>
       <c r="S11" s="11">
-        <v>50.48958326877084</v>
+        <v>52.84955340505821</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4561,61 +4607,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="10">
+        <v>379.489990234375</v>
+      </c>
+      <c r="F12" s="17">
+        <v>0.8659945306445483</v>
+      </c>
+      <c r="G12" s="20">
+        <v>1.195906561845193</v>
+      </c>
+      <c r="H12" s="20">
+        <v>-0.1235890761074189</v>
+      </c>
+      <c r="I12" s="20">
+        <v>-0.3802373592559733</v>
+      </c>
+      <c r="J12" s="20">
+        <v>0.8135315501021322</v>
+      </c>
+      <c r="K12" s="20">
+        <v>3.814024146500563</v>
+      </c>
+      <c r="L12" s="20">
+        <v>0.5747637189888012</v>
+      </c>
+      <c r="M12" s="20">
+        <v>-0.3462356016854664</v>
+      </c>
+      <c r="N12" s="20">
+        <v>10.080602</v>
+      </c>
+      <c r="O12" s="20">
+        <v>2.3630478</v>
+      </c>
+      <c r="P12" s="12">
+        <v>0.26511</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>0.003</v>
+      </c>
+      <c r="R12" s="12">
+        <v>0.2777925233619891</v>
+      </c>
+      <c r="S12" s="11">
+        <v>62.2116199685204</v>
+      </c>
+      <c r="T12" s="9" t="s">
         <v>104</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="10">
-        <v>342.8699951171875</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0.835172506044463</v>
-      </c>
-      <c r="G12" s="20">
-        <v>-0.3791628567675373</v>
-      </c>
-      <c r="H12" s="20">
-        <v>1.461933114403917</v>
-      </c>
-      <c r="I12" s="20">
-        <v>1.394253875646282</v>
-      </c>
-      <c r="J12" s="20">
-        <v>-0.003775951465358696</v>
-      </c>
-      <c r="K12" s="20">
-        <v>4.1980331407876</v>
-      </c>
-      <c r="L12" s="20">
-        <v>0.123577911699675</v>
-      </c>
-      <c r="M12" s="20">
-        <v>0.2505158529559968</v>
-      </c>
-      <c r="N12" s="20">
-        <v>16.975927</v>
-      </c>
-      <c r="O12" s="20">
-        <v>6.6508174</v>
-      </c>
-      <c r="P12" s="12">
-        <v>0.48676</v>
-      </c>
-      <c r="Q12" s="12">
-        <v>0.242</v>
-      </c>
-      <c r="R12" s="12">
-        <v>0.1041274798036558</v>
-      </c>
-      <c r="S12" s="11">
-        <v>50.06305178655397</v>
-      </c>
-      <c r="T12" s="9" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -4623,61 +4669,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" s="10">
-        <v>339.3599853515625</v>
+        <v>67.09999847412109</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8328083216241077</v>
+        <v>0.8601759839992433</v>
       </c>
       <c r="G13" s="20">
-        <v>-0.3694515340244113</v>
+        <v>1.282244047014282</v>
       </c>
       <c r="H13" s="20">
-        <v>1.461933114403917</v>
+        <v>-1.356970430261629</v>
       </c>
       <c r="I13" s="20">
-        <v>1.394253875646282</v>
+        <v>-0.5801056520622042</v>
       </c>
       <c r="J13" s="20">
-        <v>-0.03465443555860494</v>
+        <v>1.343411892432665</v>
       </c>
       <c r="K13" s="20">
         <v>4.1980331407876</v>
       </c>
       <c r="L13" s="20">
-        <v>0.1569421732261793</v>
+        <v>-0.0462211680313649</v>
       </c>
       <c r="M13" s="20">
-        <v>0.289884190734319</v>
+        <v>0.006045188029048132</v>
       </c>
       <c r="N13" s="20">
-        <v>16.83141</v>
+        <v>12.502541</v>
       </c>
       <c r="O13" s="20">
-        <v>6.5908914</v>
+        <v>1.4542508</v>
       </c>
       <c r="P13" s="12">
-        <v>0.48676</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.242</v>
+        <v>0.046</v>
       </c>
       <c r="R13" s="12">
-        <v>0.09816962643472427</v>
+        <v>0.8556415585528077</v>
       </c>
       <c r="S13" s="11">
-        <v>49.45699543810807</v>
+        <v>53.45509735265944</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -4685,61 +4731,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>2</v>
+        <v>107</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E14" s="10">
-        <v>1519.969970703125</v>
+        <v>347.3299865722656</v>
       </c>
       <c r="F14" s="17">
-        <v>0.8316214410685321</v>
+        <v>0.8487810272572711</v>
       </c>
       <c r="G14" s="20">
-        <v>-0.4801631684214276</v>
+        <v>-0.3791628567675373</v>
       </c>
       <c r="H14" s="20">
-        <v>2.05728233065155</v>
+        <v>1.461933114403917</v>
       </c>
       <c r="I14" s="20">
-        <v>4.117187201861848</v>
+        <v>1.394253875646282</v>
       </c>
       <c r="J14" s="20">
-        <v>1.328125305747322</v>
+        <v>0.06654669937216341</v>
       </c>
       <c r="K14" s="20">
-        <v>0.08398078673057012</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L14" s="20">
-        <v>-3.355540730004984</v>
+        <v>0.1067266253797308</v>
       </c>
       <c r="M14" s="20">
-        <v>-0.3751990504701193</v>
+        <v>0.1695508922153489</v>
       </c>
       <c r="N14" s="20">
-        <v>22.12312</v>
+        <v>16.975927</v>
       </c>
       <c r="O14" s="20">
-        <v>15.465718</v>
+        <v>6.6508174</v>
       </c>
       <c r="P14" s="12">
-        <v>0.9164</v>
+        <v>0.48676</v>
       </c>
       <c r="Q14" s="12">
-        <v>3.716</v>
+        <v>0.242</v>
       </c>
       <c r="R14" s="12">
-        <v>1.110571124557335</v>
+        <v>0.130231261620033</v>
       </c>
       <c r="S14" s="11">
-        <v>47.02864077974324</v>
+        <v>53.45880897505536</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -4747,61 +4793,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="E15" s="10">
-        <v>56.68000030517578</v>
+        <v>343.6799926757812</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7980632895236915</v>
+        <v>0.8443169595000172</v>
       </c>
       <c r="G15" s="20">
-        <v>0.3530298731450531</v>
+        <v>-0.3694515340244113</v>
       </c>
       <c r="H15" s="20">
-        <v>-0.5362564771804156</v>
+        <v>1.461933114403917</v>
       </c>
       <c r="I15" s="20">
-        <v>2.205637651643404</v>
+        <v>1.394253875646282</v>
       </c>
       <c r="J15" s="20">
-        <v>2.08388478101543</v>
+        <v>0.03243657637906749</v>
       </c>
       <c r="K15" s="20">
-        <v>0</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L15" s="20">
-        <v>-1.966963505523411</v>
+        <v>0.1387939093901677</v>
       </c>
       <c r="M15" s="20">
-        <v>-0.03950043967449224</v>
+        <v>0.1957620672939236</v>
       </c>
       <c r="N15" s="20">
-        <v>32.005154</v>
+        <v>16.83141</v>
       </c>
       <c r="O15" s="20">
-        <v>3.1100981</v>
+        <v>6.5908914</v>
       </c>
       <c r="P15" s="12">
-        <v>0.10936</v>
+        <v>0.48676</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.337</v>
+        <v>0.242</v>
       </c>
       <c r="R15" s="12">
-        <v>1.640165016510447</v>
+        <v>0.1234414237492858</v>
       </c>
       <c r="S15" s="11">
-        <v>53.93524889252662</v>
+        <v>53.02221561225778</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -4809,19 +4855,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E16" s="10">
-        <v>250.5399932861328</v>
+        <v>242.8500061035156</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7906584234424111</v>
+        <v>0.7571211820349885</v>
       </c>
       <c r="G16" s="20">
         <v>0.3415976968814792</v>
@@ -4833,16 +4879,16 @@
         <v>0.1958909336866145</v>
       </c>
       <c r="J16" s="20">
-        <v>1.282577727845992</v>
+        <v>1.182961504176358</v>
       </c>
       <c r="K16" s="20">
         <v>3.517269315668033</v>
       </c>
       <c r="L16" s="20">
-        <v>-1.584593559956525</v>
+        <v>-1.650209126278205</v>
       </c>
       <c r="M16" s="20">
-        <v>-1.099588396170294</v>
+        <v>-1.096031400260685</v>
       </c>
       <c r="N16" s="20">
         <v>22.684982</v>
@@ -4857,13 +4903,13 @@
         <v>0.108</v>
       </c>
       <c r="R16" s="12">
-        <v>0.2893085099491286</v>
+        <v>0.2581822585861471</v>
       </c>
       <c r="S16" s="11">
-        <v>62.37802591327755</v>
+        <v>56.91533700004462</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -4871,61 +4917,61 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E17" s="10">
-        <v>59.36000061035156</v>
+        <v>196.9199981689453</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7430174975106851</v>
+        <v>0.7366594447745334</v>
       </c>
       <c r="G17" s="20">
-        <v>0.6018835051913498</v>
+        <v>-0.4603187739276002</v>
       </c>
       <c r="H17" s="20">
-        <v>0.6139340215135211</v>
+        <v>1.359216064961746</v>
       </c>
       <c r="I17" s="20">
-        <v>2.907067021605936</v>
+        <v>0.4362761666871086</v>
       </c>
       <c r="J17" s="20">
-        <v>0.4312446123095364</v>
+        <v>1.723924603882057</v>
       </c>
       <c r="K17" s="20">
-        <v>0.9124213561380491</v>
+        <v>0</v>
       </c>
       <c r="L17" s="20">
-        <v>0.1548656291033269</v>
+        <v>-0.4480096791845573</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.03016954002676753</v>
+        <v>-0.2535162095947052</v>
       </c>
       <c r="N17" s="20">
-        <v>18.129793</v>
+        <v>28.186703</v>
       </c>
       <c r="O17" s="20">
-        <v>1.836326</v>
+        <v>26.124804</v>
       </c>
       <c r="P17" s="12">
-        <v>0.10629</v>
+        <v>1.14818</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.534</v>
+        <v>0.299</v>
       </c>
       <c r="R17" s="12">
-        <v>0.03772424029952015</v>
+        <v>0.9701281388288321</v>
       </c>
       <c r="S17" s="11">
-        <v>49.08197179589703</v>
+        <v>57.81512425854689</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -4933,61 +4979,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E18" s="10">
-        <v>191.4900054931641</v>
+        <v>59.29000091552734</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6779452139495242</v>
+        <v>0.701559228157717</v>
       </c>
       <c r="G18" s="20">
-        <v>-0.4603187739276002</v>
+        <v>0.6018835051913498</v>
       </c>
       <c r="H18" s="20">
-        <v>1.359216064961746</v>
+        <v>0.6139340215135211</v>
       </c>
       <c r="I18" s="20">
-        <v>0.4362761666871086</v>
+        <v>2.907067021605936</v>
       </c>
       <c r="J18" s="20">
-        <v>1.546273857635937</v>
+        <v>0.3404811172717484</v>
       </c>
       <c r="K18" s="20">
-        <v>0</v>
+        <v>0.9124213561380491</v>
       </c>
       <c r="L18" s="20">
-        <v>-0.4088640220953557</v>
+        <v>0.1404355287834394</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.2625416930637556</v>
+        <v>-0.1972122253072485</v>
       </c>
       <c r="N18" s="20">
-        <v>28.186703</v>
+        <v>18.129793</v>
       </c>
       <c r="O18" s="20">
-        <v>26.124804</v>
+        <v>1.836326</v>
       </c>
       <c r="P18" s="12">
-        <v>1.14818</v>
+        <v>0.10629</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.299</v>
+        <v>0.534</v>
       </c>
       <c r="R18" s="12">
-        <v>0.8941858653868795</v>
+        <v>0.02496013260861796</v>
       </c>
       <c r="S18" s="11">
-        <v>53.53304172382524</v>
+        <v>48.80748643605656</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -4995,61 +5041,61 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="E19" s="10">
-        <v>254.8500061035156</v>
+        <v>40.34999847412109</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6661245476929314</v>
+        <v>0.6889427524548952</v>
       </c>
       <c r="G19" s="20">
-        <v>1.275714742496789</v>
+        <v>0.005970682120931148</v>
       </c>
       <c r="H19" s="20">
-        <v>0.1637485141969772</v>
+        <v>-0.8151434307759278</v>
       </c>
       <c r="I19" s="20">
-        <v>-0.05524579084430264</v>
+        <v>3.899748911067756</v>
       </c>
       <c r="J19" s="20">
-        <v>0.5540854391486315</v>
+        <v>0.9751910886157077</v>
       </c>
       <c r="K19" s="20">
-        <v>1.851629787748643</v>
+        <v>3.372498295765357</v>
       </c>
       <c r="L19" s="20">
-        <v>0.48158007204799</v>
+        <v>-3.240137711546244</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.0186912467610337</v>
+        <v>-0.9316596486660019</v>
       </c>
       <c r="N19" s="20">
-        <v>5.081314</v>
+        <v>12.300613</v>
       </c>
       <c r="O19" s="20">
-        <v>2.0330794</v>
+        <v>2.5690305</v>
       </c>
       <c r="P19" s="12">
-        <v>0.46113998</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.118</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R19" s="12">
-        <v>0.2411771923059403</v>
+        <v>0.3294892246115717</v>
       </c>
       <c r="S19" s="11">
-        <v>47.68889299433403</v>
+        <v>58.80900273250104</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -5057,19 +5103,19 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E20" s="10">
-        <v>154.6799926757812</v>
+        <v>159.8300018310547</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6369924288836575</v>
+        <v>0.6873156844590108</v>
       </c>
       <c r="G20" s="20">
         <v>0.5169435305631409</v>
@@ -5081,16 +5127,16 @@
         <v>-0.03865308917984001</v>
       </c>
       <c r="J20" s="20">
-        <v>0.9671948687367055</v>
+        <v>1.180431149948533</v>
       </c>
       <c r="K20" s="20">
         <v>3.283884006002866</v>
       </c>
       <c r="L20" s="20">
-        <v>0.2706473752441712</v>
+        <v>0.2593545568069066</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.7861961176831198</v>
+        <v>-0.9483218637076097</v>
       </c>
       <c r="N20" s="20">
         <v>16.148188</v>
@@ -5105,13 +5151,13 @@
         <v>0.053</v>
       </c>
       <c r="R20" s="12">
-        <v>0.3475494720990973</v>
+        <v>0.4131112080051242</v>
       </c>
       <c r="S20" s="11">
-        <v>46.66226687311799</v>
+        <v>54.64547460756999</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -5119,61 +5165,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="E21" s="10">
-        <v>124.75</v>
+        <v>108.8000030517578</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6343377358279289</v>
+        <v>0.6732228567874444</v>
       </c>
       <c r="G21" s="20">
-        <v>0.3560597278471356</v>
+        <v>-0.7359494773385853</v>
       </c>
       <c r="H21" s="20">
-        <v>0.5036708481790161</v>
+        <v>-1.140633242548325</v>
       </c>
       <c r="I21" s="20">
-        <v>0.5191598695187023</v>
+        <v>0.5241404076306111</v>
       </c>
       <c r="J21" s="20">
-        <v>0.9181217381261554</v>
+        <v>1.791263966721708</v>
       </c>
       <c r="K21" s="20">
-        <v>1.641428449242267</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L21" s="20">
-        <v>0.2255947427853154</v>
+        <v>-2.343568280651271</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.6024994719888253</v>
+        <v>0.4406496335139055</v>
       </c>
       <c r="N21" s="20">
-        <v>15.473886</v>
+        <v>50.34258</v>
       </c>
       <c r="O21" s="20">
-        <v>3.847884</v>
+        <v>5.9300656</v>
       </c>
       <c r="P21" s="12">
-        <v>0.30667</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.377</v>
+        <v>0.254</v>
       </c>
       <c r="R21" s="12">
-        <v>0.3240288514514311</v>
+        <v>1.416167133048647</v>
       </c>
       <c r="S21" s="11">
-        <v>52.28354439180455</v>
+        <v>62.01205099819378</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -5181,61 +5227,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E22" s="10">
-        <v>101.0500030517578</v>
+        <v>127.620002746582</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6118537687214308</v>
+        <v>0.662112373894027</v>
       </c>
       <c r="G22" s="20">
-        <v>-0.7359494773385853</v>
+        <v>0.3560597278471356</v>
       </c>
       <c r="H22" s="20">
-        <v>-1.140633242548325</v>
+        <v>0.5036708481790161</v>
       </c>
       <c r="I22" s="20">
-        <v>0.5241404076306111</v>
+        <v>0.5191598695187023</v>
       </c>
       <c r="J22" s="20">
-        <v>1.512983593088108</v>
+        <v>1.018980736347699</v>
       </c>
       <c r="K22" s="20">
-        <v>4.1980331407876</v>
+        <v>1.641428449242267</v>
       </c>
       <c r="L22" s="20">
-        <v>-2.239284587221917</v>
+        <v>0.19739015541044</v>
       </c>
       <c r="M22" s="20">
-        <v>0.6388746637427194</v>
+        <v>-0.6123842989622295</v>
       </c>
       <c r="N22" s="20">
-        <v>50.34258</v>
+        <v>15.473886</v>
       </c>
       <c r="O22" s="20">
-        <v>5.9300656</v>
+        <v>3.847884</v>
       </c>
       <c r="P22" s="12">
-        <v>-0.10715</v>
+        <v>0.30667</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.254</v>
+        <v>0.377</v>
       </c>
       <c r="R22" s="12">
-        <v>1.293463456699162</v>
+        <v>0.3835646758694173</v>
       </c>
       <c r="S22" s="11">
-        <v>54.73633143599216</v>
+        <v>57.65843107444808</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -5243,61 +5289,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="E23" s="10">
-        <v>245.9600067138672</v>
+        <v>252.2100067138672</v>
       </c>
       <c r="F23" s="17">
-        <v>0.6019631473569113</v>
+        <v>0.644981752582981</v>
       </c>
       <c r="G23" s="20">
-        <v>-0.04046750433284103</v>
+        <v>1.275714742496789</v>
       </c>
       <c r="H23" s="20">
-        <v>0.1570571804969511</v>
+        <v>0.1637485141969772</v>
       </c>
       <c r="I23" s="20">
-        <v>1.023343627582307</v>
+        <v>-0.05524579084430264</v>
       </c>
       <c r="J23" s="20">
-        <v>-0.01861746216667653</v>
+        <v>0.4410209732529937</v>
       </c>
       <c r="K23" s="20">
-        <v>4.1980331407876</v>
+        <v>1.851629787748643</v>
       </c>
       <c r="L23" s="20">
-        <v>-0.3439566034803255</v>
+        <v>0.5342060994130603</v>
       </c>
       <c r="M23" s="20">
-        <v>0.05303055579237728</v>
+        <v>0.1015460409494237</v>
       </c>
       <c r="N23" s="20">
-        <v>20.658085</v>
+        <v>5.081314</v>
       </c>
       <c r="O23" s="20">
-        <v>5.0195484</v>
+        <v>2.0330794</v>
       </c>
       <c r="P23" s="12">
-        <v>0.30558002</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.196</v>
+        <v>0.118</v>
       </c>
       <c r="R23" s="12">
-        <v>0.1429368503802679</v>
+        <v>0.245688675108052</v>
       </c>
       <c r="S23" s="11">
-        <v>39.4467022217616</v>
+        <v>44.69288082538724</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -5305,61 +5351,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>8</v>
+        <v>124</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>42</v>
+        <v>126</v>
       </c>
       <c r="E24" s="10">
-        <v>44.79000091552734</v>
+        <v>251.1900024414062</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5764342161264837</v>
+        <v>0.6207206278881185</v>
       </c>
       <c r="G24" s="20">
-        <v>1.099839703019805</v>
+        <v>-0.04046750433284103</v>
       </c>
       <c r="H24" s="20">
-        <v>0.5600572175760307</v>
+        <v>0.1570571804969511</v>
       </c>
       <c r="I24" s="20">
-        <v>-0.2922173294313919</v>
+        <v>1.023343627582307</v>
       </c>
       <c r="J24" s="20">
-        <v>1.480407990773791</v>
+        <v>0.1040846024195529</v>
       </c>
       <c r="K24" s="20">
-        <v>-0.5708375986655156</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L24" s="20">
-        <v>-0.3693923024749571</v>
+        <v>-0.3769818836295213</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.4422837441235606</v>
+        <v>-0.1478647196539946</v>
       </c>
       <c r="N24" s="20">
-        <v>9.436709</v>
+        <v>20.658085</v>
       </c>
       <c r="O24" s="20">
-        <v>2.2340426</v>
+        <v>5.0195484</v>
       </c>
       <c r="P24" s="12">
-        <v>0.26659</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.092</v>
+        <v>0.196</v>
       </c>
       <c r="R24" s="12">
-        <v>0.2658811540583801</v>
+        <v>0.1968838246798759</v>
       </c>
       <c r="S24" s="11">
-        <v>58.06089547230191</v>
+        <v>45.39446648532394</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -5367,61 +5413,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D25" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E25" s="10">
-        <v>171.7700042724609</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5398387336236281</v>
+        <v>0.5913007505902222</v>
       </c>
       <c r="G25" s="20">
-        <v>-2.045758834681303</v>
+        <v>0.9932091735796537</v>
       </c>
       <c r="H25" s="20">
-        <v>1.763423185417039</v>
+        <v>-0.9910800207632466</v>
       </c>
       <c r="I25" s="20">
-        <v>0.2278103986420596</v>
+        <v>-0.385570790078564</v>
       </c>
       <c r="J25" s="20">
-        <v>1.933551989184213</v>
+        <v>2.131129485457891</v>
       </c>
       <c r="K25" s="20">
-        <v>0.4348315502669465</v>
+        <v>0.4070107848763967</v>
       </c>
       <c r="L25" s="20">
-        <v>-0.5853713061099342</v>
+        <v>-0.9006967535740653</v>
       </c>
       <c r="M25" s="20">
-        <v>0.07529337393286417</v>
+        <v>-0.3060669116528826</v>
       </c>
       <c r="N25" s="20">
-        <v>55.343975</v>
+        <v>13.5419855</v>
       </c>
       <c r="O25" s="20">
-        <v>73.826866</v>
+        <v>-347.84314</v>
       </c>
       <c r="P25" s="12">
-        <v>1.17442</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="12">
-        <v>0.256</v>
+        <v>0.125</v>
       </c>
       <c r="R25" s="12">
-        <v>1.065536275952876</v>
+        <v>0.9441784647494373</v>
       </c>
       <c r="S25" s="11">
-        <v>60.72469323234478</v>
+        <v>63.51459744839666</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -5429,61 +5475,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>127</v>
+        <v>49</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E26" s="10">
-        <v>216.0099945068359</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5049937466329726</v>
+        <v>0.556751325319207</v>
       </c>
       <c r="G26" s="20">
-        <v>0.2268704470519779</v>
+        <v>1.099839703019805</v>
       </c>
       <c r="H26" s="20">
-        <v>0.02833393151366955</v>
+        <v>0.5600572175760307</v>
       </c>
       <c r="I26" s="20">
-        <v>-0.8973367206108911</v>
+        <v>-0.2922173294313919</v>
       </c>
       <c r="J26" s="20">
-        <v>0.6115715297193677</v>
+        <v>1.451932441285735</v>
       </c>
       <c r="K26" s="20">
-        <v>3.363739906660925</v>
+        <v>-0.5708375986655156</v>
       </c>
       <c r="L26" s="20">
-        <v>-0.1233603963317929</v>
+        <v>-0.3930187064692126</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.3795164344086904</v>
+        <v>-0.5638167656386198</v>
       </c>
       <c r="N26" s="20">
-        <v>38.63879</v>
+        <v>9.436709</v>
       </c>
       <c r="O26" s="20">
-        <v>1.7016691</v>
+        <v>2.2340426</v>
       </c>
       <c r="P26" s="12">
-        <v>0.04575</v>
+        <v>0.26659</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.034</v>
+        <v>0.092</v>
       </c>
       <c r="R26" s="12">
-        <v>0.1657941731006702</v>
+        <v>0.2588469503262611</v>
       </c>
       <c r="S26" s="11">
-        <v>51.63966191247673</v>
+        <v>60.13855612358613</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -5491,61 +5537,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E27" s="10">
-        <v>36.84999847412109</v>
+        <v>172.5800018310547</v>
       </c>
       <c r="F27" s="17">
-        <v>0.4952539808894236</v>
+        <v>0.54637182013145</v>
       </c>
       <c r="G27" s="20">
-        <v>0.005970682120931148</v>
+        <v>-2.045758834681303</v>
       </c>
       <c r="H27" s="20">
-        <v>-0.8151434307759278</v>
+        <v>1.763423185417039</v>
       </c>
       <c r="I27" s="20">
-        <v>3.899748911067756</v>
+        <v>0.2278103986420596</v>
       </c>
       <c r="J27" s="20">
-        <v>0.3982040469689888</v>
+        <v>1.932793116018141</v>
       </c>
       <c r="K27" s="20">
-        <v>3.372498295765357</v>
+        <v>0.4348315502669465</v>
       </c>
       <c r="L27" s="20">
-        <v>-3.355540730004984</v>
+        <v>-0.6029321350649751</v>
       </c>
       <c r="M27" s="20">
-        <v>-1.102515623215146</v>
+        <v>0.1729733513696873</v>
       </c>
       <c r="N27" s="20">
-        <v>12.300613</v>
+        <v>55.343975</v>
       </c>
       <c r="O27" s="20">
-        <v>2.5690305</v>
+        <v>73.826866</v>
       </c>
       <c r="P27" s="12">
-        <v>0.21465999</v>
+        <v>1.17442</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.256</v>
       </c>
       <c r="R27" s="12">
-        <v>0.1694699526007828</v>
+        <v>1.069552741266452</v>
       </c>
       <c r="S27" s="11">
-        <v>51.09657212217164</v>
+        <v>61.34600954794338</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5553,61 +5599,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E28" s="10">
-        <v>211.5399932861328</v>
+        <v>219.0500030517578</v>
       </c>
       <c r="F28" s="17">
-        <v>0.4939930498965755</v>
+        <v>0.5058975121205138</v>
       </c>
       <c r="G28" s="20">
-        <v>0.5000449645463003</v>
+        <v>0.2268704470519779</v>
       </c>
       <c r="H28" s="20">
-        <v>-0.3299402274497991</v>
+        <v>0.02833393151366955</v>
       </c>
       <c r="I28" s="20">
-        <v>2.306272783126228</v>
+        <v>-0.8973367206108911</v>
       </c>
       <c r="J28" s="20">
-        <v>0.7933612633358079</v>
+        <v>0.6386128305044964</v>
       </c>
       <c r="K28" s="20">
-        <v>-0.1674365005025454</v>
+        <v>3.363739906660925</v>
       </c>
       <c r="L28" s="20">
-        <v>0.7921113334440001</v>
+        <v>-0.1391008109139891</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.4911820573686303</v>
+        <v>-0.4578189328220099</v>
       </c>
       <c r="N28" s="20">
-        <v>20.62235</v>
+        <v>38.63879</v>
       </c>
       <c r="O28" s="20">
-        <v>2.2113636</v>
+        <v>1.7016691</v>
       </c>
       <c r="P28" s="12">
-        <v>0.12231</v>
+        <v>0.04575</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.535</v>
+        <v>0.034</v>
       </c>
       <c r="R28" s="12">
-        <v>0.08774345185736498</v>
+        <v>0.2015249080421713</v>
       </c>
       <c r="S28" s="11">
-        <v>58.9632379873061</v>
+        <v>55.468011723011</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5615,61 +5661,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="E29" s="10">
-        <v>32.70000076293945</v>
+        <v>114.4000015258789</v>
       </c>
       <c r="F29" s="17">
-        <v>0.4929571211974721</v>
+        <v>0.4977021043893044</v>
       </c>
       <c r="G29" s="20">
-        <v>0.9932091735796537</v>
+        <v>0.4228371578138432</v>
       </c>
       <c r="H29" s="20">
-        <v>-0.9910800207632466</v>
+        <v>-0.1266107877394232</v>
       </c>
       <c r="I29" s="20">
-        <v>-0.385570790078564</v>
+        <v>0.4718408509917099</v>
       </c>
       <c r="J29" s="20">
-        <v>1.726676428199873</v>
+        <v>-0.2239604818921834</v>
       </c>
       <c r="K29" s="20">
-        <v>0.4070107848763967</v>
+        <v>4.1980331407876</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.7954372773962688</v>
+        <v>0.03321097442296056</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.0976079214780381</v>
+        <v>-0.5487929233785666</v>
       </c>
       <c r="N29" s="20">
-        <v>13.5419855</v>
+        <v>14.463892</v>
       </c>
       <c r="O29" s="20">
-        <v>-347.84314</v>
+        <v>6.474714</v>
       </c>
       <c r="P29" s="12">
-        <v>0</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.125</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R29" s="12">
-        <v>0.7823887385736601</v>
+        <v>0.06428508511896114</v>
       </c>
       <c r="S29" s="11">
-        <v>57.56597385475121</v>
+        <v>34.68956486478493</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -5677,61 +5723,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E30" s="10">
-        <v>203.1900024414062</v>
+        <v>146.7299957275391</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4636201602627125</v>
+        <v>0.4883507137320318</v>
       </c>
       <c r="G30" s="20">
-        <v>0.5982241598157348</v>
+        <v>-0.07531619732868289</v>
       </c>
       <c r="H30" s="20">
-        <v>-0.6609329225841165</v>
+        <v>-0.3184017151882295</v>
       </c>
       <c r="I30" s="20">
-        <v>4.117187201861848</v>
+        <v>-0.6227115884361363</v>
       </c>
       <c r="J30" s="20">
-        <v>-0.2047910416787346</v>
+        <v>1.994078345398692</v>
       </c>
       <c r="K30" s="20">
-        <v>0.6027865413284129</v>
+        <v>0.19783984508819</v>
       </c>
       <c r="L30" s="20">
-        <v>0.5947250854245805</v>
+        <v>-0.2375827286204648</v>
       </c>
       <c r="M30" s="20">
-        <v>0.04237226677362493</v>
+        <v>0.09267176514953213</v>
       </c>
       <c r="N30" s="20">
-        <v>11.482911</v>
+        <v>59.764423</v>
       </c>
       <c r="O30" s="20">
-        <v>1.2409225</v>
+        <v>1.9188677</v>
       </c>
       <c r="P30" s="12">
-        <v>0.09031</v>
+        <v>0.03211</v>
       </c>
       <c r="Q30" s="12">
-        <v>11.11</v>
+        <v>0.013</v>
       </c>
       <c r="R30" s="12">
-        <v>0.116469396289933</v>
+        <v>0.7300940216372918</v>
       </c>
       <c r="S30" s="11">
-        <v>36.31415219988843</v>
+        <v>75.04353805690388</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -5739,61 +5785,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="E31" s="10">
-        <v>63.59999847412109</v>
+        <v>211.5700073242188</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4623359647836967</v>
+        <v>0.4665220272144243</v>
       </c>
       <c r="G31" s="20">
-        <v>0.5011052908132025</v>
+        <v>0.5000449645463003</v>
       </c>
       <c r="H31" s="20">
-        <v>0.6560191381210976</v>
+        <v>-0.3299402274497991</v>
       </c>
       <c r="I31" s="20">
-        <v>0.2251020255328333</v>
+        <v>2.306272783126228</v>
       </c>
       <c r="J31" s="20">
-        <v>0.4698457022616294</v>
+        <v>0.7190619858983424</v>
       </c>
       <c r="K31" s="20">
-        <v>0.8062902881666928</v>
+        <v>-0.1674365005025454</v>
       </c>
       <c r="L31" s="20">
-        <v>0.5854092200235509</v>
+        <v>0.7863085859476283</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.3521168834405475</v>
+        <v>-0.5515954898827468</v>
       </c>
       <c r="N31" s="20">
-        <v>14.017621</v>
+        <v>20.62235</v>
       </c>
       <c r="O31" s="20">
-        <v>5.8251715</v>
+        <v>2.2113636</v>
       </c>
       <c r="P31" s="12">
-        <v>0.46598998</v>
+        <v>0.12231</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.057</v>
+        <v>0.535</v>
       </c>
       <c r="R31" s="12">
-        <v>0.08827863825792992</v>
+        <v>0.0843922138719313</v>
       </c>
       <c r="S31" s="11">
-        <v>42.73925018817186</v>
+        <v>58.99930305970489</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -5801,61 +5847,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="E32" s="10">
-        <v>112.4000015258789</v>
+        <v>347.8099975585938</v>
       </c>
       <c r="F32" s="17">
-        <v>0.459637525640187</v>
+        <v>0.4643981291062081</v>
       </c>
       <c r="G32" s="20">
-        <v>0.4228371578138432</v>
+        <v>0.116365121381956</v>
       </c>
       <c r="H32" s="20">
-        <v>-0.1266107877394232</v>
+        <v>-0.2401012663427755</v>
       </c>
       <c r="I32" s="20">
-        <v>0.4718408509917099</v>
+        <v>0.4632294407463022</v>
       </c>
       <c r="J32" s="20">
-        <v>-0.3746281810304646</v>
+        <v>1.342916524148195</v>
       </c>
       <c r="K32" s="20">
-        <v>4.1980331407876</v>
+        <v>1.700676375536956</v>
       </c>
       <c r="L32" s="20">
-        <v>0.05943715192242162</v>
+        <v>-1.682173320768879</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.4792659190985764</v>
+        <v>-0.8810007158136319</v>
       </c>
       <c r="N32" s="20">
-        <v>14.463892</v>
+        <v>32.14404</v>
       </c>
       <c r="O32" s="20">
-        <v>6.474714</v>
+        <v>4.8336897</v>
       </c>
       <c r="P32" s="12">
-        <v>0.46032003</v>
+        <v>0.15286</v>
       </c>
       <c r="Q32" s="12">
-        <v>0.07000000000000001</v>
+        <v>0.204</v>
       </c>
       <c r="R32" s="12">
-        <v>0.005007199627371284</v>
+        <v>0.6761120272071326</v>
       </c>
       <c r="S32" s="11">
-        <v>30.41797093341378</v>
+        <v>51.11115356436979</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -5863,61 +5909,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>140</v>
+        <v>9</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>32</v>
       </c>
       <c r="E33" s="10">
-        <v>341.1799926757812</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4542642581522554</v>
+        <v>0.4477193981622247</v>
       </c>
       <c r="G33" s="20">
-        <v>0.116365121381956</v>
+        <v>-1.171878848863184</v>
       </c>
       <c r="H33" s="20">
-        <v>-0.2401012663427755</v>
+        <v>2.368118728722743</v>
       </c>
       <c r="I33" s="20">
-        <v>0.4632294407463022</v>
+        <v>2.422793453764177</v>
       </c>
       <c r="J33" s="20">
-        <v>1.29269119042493</v>
+        <v>0.4184745599734765</v>
       </c>
       <c r="K33" s="20">
-        <v>1.700676375536956</v>
+        <v>-0.3055099287371252</v>
       </c>
       <c r="L33" s="20">
-        <v>-1.673163442386504</v>
+        <v>-0.1797549242559651</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.8260865100625787</v>
+        <v>-0.507707901283611</v>
       </c>
       <c r="N33" s="20">
-        <v>32.14404</v>
+        <v>27.631645</v>
       </c>
       <c r="O33" s="20">
-        <v>4.8336897</v>
+        <v>23.019087</v>
       </c>
       <c r="P33" s="12">
-        <v>0.15286</v>
+        <v>1.17211</v>
       </c>
       <c r="Q33" s="12">
-        <v>0.204</v>
+        <v>1.059</v>
       </c>
       <c r="R33" s="12">
-        <v>0.6319716667946382</v>
+        <v>0.2186328071882271</v>
       </c>
       <c r="S33" s="11">
-        <v>46.73484803783356</v>
+        <v>51.87119943924442</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -5925,61 +5971,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>143</v>
-      </c>
       <c r="D34" s="9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E34" s="10">
-        <v>145.7299957275391</v>
+        <v>202.0399932861328</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4532303251400961</v>
+        <v>0.4423966884840852</v>
       </c>
       <c r="G34" s="20">
-        <v>-0.07531619732868289</v>
+        <v>0.5982241598157348</v>
       </c>
       <c r="H34" s="20">
-        <v>-0.3184017151882295</v>
+        <v>-0.6609329225841165</v>
       </c>
       <c r="I34" s="20">
-        <v>-0.6227115884361363</v>
+        <v>4.117187201861848</v>
       </c>
       <c r="J34" s="20">
-        <v>1.941074068433888</v>
+        <v>-0.2822687497108197</v>
       </c>
       <c r="K34" s="20">
-        <v>0.19783984508819</v>
+        <v>0.6027865413284129</v>
       </c>
       <c r="L34" s="20">
-        <v>-0.2185952407681761</v>
+        <v>0.5957771241394111</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.1618076695208644</v>
+        <v>0.06683124562498005</v>
       </c>
       <c r="N34" s="20">
-        <v>59.764423</v>
+        <v>11.482911</v>
       </c>
       <c r="O34" s="20">
-        <v>1.9188677</v>
+        <v>1.2409225</v>
       </c>
       <c r="P34" s="12">
-        <v>0.03211</v>
+        <v>0.09031</v>
       </c>
       <c r="Q34" s="12">
-        <v>0.013</v>
+        <v>11.11</v>
       </c>
       <c r="R34" s="12">
-        <v>0.6703156693689796</v>
+        <v>0.1303641080671309</v>
       </c>
       <c r="S34" s="11">
-        <v>74.43373683500241</v>
+        <v>35.10657408837942</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -5987,61 +6033,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="C35" s="9" t="s">
-        <v>145</v>
-      </c>
       <c r="D35" s="9" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="E35" s="10">
-        <v>30.64999961853027</v>
+        <v>62.84000015258789</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4365584798732851</v>
+        <v>0.4405996536698572</v>
       </c>
       <c r="G35" s="20">
-        <v>0.5071505500348842</v>
+        <v>0.5011052908132025</v>
       </c>
       <c r="H35" s="20">
-        <v>0.7469802265893087</v>
+        <v>0.6560191381210976</v>
       </c>
       <c r="I35" s="20">
-        <v>-0.1877648684685418</v>
+        <v>0.2251020255328333</v>
       </c>
       <c r="J35" s="20">
-        <v>1.085097457861382</v>
+        <v>0.3559165647455765</v>
       </c>
       <c r="K35" s="20">
-        <v>-0.4688281255668335</v>
+        <v>0.8062902881666928</v>
       </c>
       <c r="L35" s="20">
-        <v>0.2659109094270264</v>
+        <v>0.5744708118481988</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.508668567455568</v>
+        <v>-0.1883827005468275</v>
       </c>
       <c r="N35" s="20">
-        <v>17.695906</v>
+        <v>14.017621</v>
       </c>
       <c r="O35" s="20">
-        <v>6.8245378</v>
+        <v>5.8251715</v>
       </c>
       <c r="P35" s="12">
-        <v>0.41944</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q35" s="12">
-        <v>0.063</v>
+        <v>0.057</v>
       </c>
       <c r="R35" s="12">
-        <v>0.4724118186748609</v>
+        <v>0.08143191414313189</v>
       </c>
       <c r="S35" s="11">
-        <v>57.59120930053963</v>
+        <v>39.32711898819483</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -6049,19 +6095,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C36" s="9" t="s">
         <v>146</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>147</v>
       </c>
       <c r="D36" s="9" t="s">
         <v>53</v>
       </c>
       <c r="E36" s="10">
-        <v>937.97998046875</v>
+        <v>951.469970703125</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4226096010620854</v>
+        <v>0.4108354989230051</v>
       </c>
       <c r="G36" s="20">
         <v>0.3658514008022524</v>
@@ -6073,16 +6119,16 @@
         <v>0.9093352353792101</v>
       </c>
       <c r="J36" s="20">
-        <v>-0.3149927963481021</v>
+        <v>-0.2678909551889405</v>
       </c>
       <c r="K36" s="20">
         <v>1.657914828732963</v>
       </c>
       <c r="L36" s="20">
-        <v>0.01282148064049671</v>
+        <v>-0.01065417727125811</v>
       </c>
       <c r="M36" s="20">
-        <v>0.3641636400947232</v>
+        <v>0.05796220244317957</v>
       </c>
       <c r="N36" s="20">
         <v>15.897128</v>
@@ -6097,13 +6143,13 @@
         <v>0.425</v>
       </c>
       <c r="R36" s="12">
-        <v>0.1730868831649932</v>
+        <v>0.1922627240709991</v>
       </c>
       <c r="S36" s="11">
-        <v>30.72063526231409</v>
+        <v>34.9632861928178</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -6111,61 +6157,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>9</v>
+        <v>147</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="E37" s="10">
-        <v>213.8999938964844</v>
+        <v>94.55999755859375</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4172954278442738</v>
+        <v>0.401747642626362</v>
       </c>
       <c r="G37" s="20">
-        <v>-1.171878848863184</v>
+        <v>0.6594637779990824</v>
       </c>
       <c r="H37" s="20">
-        <v>2.368118728722743</v>
+        <v>-0.4971404169201537</v>
       </c>
       <c r="I37" s="20">
-        <v>2.422793453764177</v>
+        <v>-0.2300784505986128</v>
       </c>
       <c r="J37" s="20">
-        <v>0.3018678144661496</v>
+        <v>1.394133108575802</v>
       </c>
       <c r="K37" s="20">
-        <v>-0.3055099287371252</v>
+        <v>-0.2864475524510079</v>
       </c>
       <c r="L37" s="20">
-        <v>-0.2033262857763942</v>
+        <v>0.06068478155890779</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.4330537134651998</v>
+        <v>-0.02391048523176309</v>
       </c>
       <c r="N37" s="20">
-        <v>27.631645</v>
+        <v>15.108153</v>
       </c>
       <c r="O37" s="20">
-        <v>23.019087</v>
+        <v>6.0021152</v>
       </c>
       <c r="P37" s="12">
-        <v>1.17211</v>
+        <v>0.43126</v>
       </c>
       <c r="Q37" s="12">
-        <v>1.059</v>
+        <v>0.036</v>
       </c>
       <c r="R37" s="12">
-        <v>0.1784142839297385</v>
+        <v>0.5635120541058161</v>
       </c>
       <c r="S37" s="11">
-        <v>46.88755014454045</v>
+        <v>64.84207171720495</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -6173,61 +6219,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E38" s="10">
-        <v>144.9299926757812</v>
+        <v>30.20999908447266</v>
       </c>
       <c r="F38" s="17">
-        <v>0.4092484779260411</v>
+        <v>0.3932082803432622</v>
       </c>
       <c r="G38" s="20">
-        <v>0.6042209697867998</v>
+        <v>0.5071505500348842</v>
       </c>
       <c r="H38" s="20">
-        <v>0.4636940000902633</v>
+        <v>0.7469802265893087</v>
       </c>
       <c r="I38" s="20">
-        <v>1.421647839457134</v>
+        <v>-0.1877648684685418</v>
       </c>
       <c r="J38" s="20">
-        <v>0.4347164752903636</v>
+        <v>0.9230729174615432</v>
       </c>
       <c r="K38" s="20">
-        <v>-0.514680868525332</v>
+        <v>-0.4688281255668335</v>
       </c>
       <c r="L38" s="20">
-        <v>0.1802405499461859</v>
+        <v>0.2394508768826273</v>
       </c>
       <c r="M38" s="20">
-        <v>0.05831510054276418</v>
+        <v>-0.4231090106731605</v>
       </c>
       <c r="N38" s="20">
-        <v>11.467704</v>
+        <v>17.695906</v>
       </c>
       <c r="O38" s="20">
-        <v>2.4302394</v>
+        <v>6.8245378</v>
       </c>
       <c r="P38" s="12">
-        <v>0.22507</v>
+        <v>0.41944</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.587</v>
+        <v>0.063</v>
       </c>
       <c r="R38" s="12">
-        <v>0.08413800754913914</v>
+        <v>0.482302622115562</v>
       </c>
       <c r="S38" s="11">
-        <v>48.13353392864501</v>
+        <v>53.97805789127119</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -6235,61 +6281,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="E39" s="10">
-        <v>30.19000053405762</v>
+        <v>434.6199951171875</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3955058451285168</v>
+        <v>0.3896642964129826</v>
       </c>
       <c r="G39" s="20">
-        <v>0.4737570391617266</v>
+        <v>-0.2429950411639331</v>
       </c>
       <c r="H39" s="20">
-        <v>-0.2868604961518937</v>
+        <v>0.6042118867300035</v>
       </c>
       <c r="I39" s="20">
-        <v>-0.7009083349924576</v>
+        <v>-0.3187981010065978</v>
       </c>
       <c r="J39" s="20">
-        <v>0.6460908200535177</v>
+        <v>1.048449083573268</v>
       </c>
       <c r="K39" s="20">
-        <v>2.017008782014688</v>
+        <v>0.3173660963957367</v>
       </c>
       <c r="L39" s="20">
-        <v>0.6247865910761435</v>
+        <v>-0.04636364134394782</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.589217554492896</v>
+        <v>0.2346559235939722</v>
       </c>
       <c r="N39" s="20">
-        <v>28.582525</v>
+        <v>32.779457</v>
       </c>
       <c r="O39" s="20">
-        <v>1.876474</v>
+        <v>6.0678544</v>
       </c>
       <c r="P39" s="12">
-        <v>0.07979</v>
+        <v>0.1983</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.108</v>
+        <v>0.109</v>
       </c>
       <c r="R39" s="12">
-        <v>0.2445185611747915</v>
+        <v>0.5401133108326583</v>
       </c>
       <c r="S39" s="11">
-        <v>55.06637281709288</v>
+        <v>63.32007478146141</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -6297,19 +6343,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D40" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E40" s="10">
-        <v>418.6400146484375</v>
+        <v>429.7200012207031</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3647940503203134</v>
+        <v>0.3803911548314809</v>
       </c>
       <c r="G40" s="20">
         <v>-1.007090388729049</v>
@@ -6321,16 +6367,16 @@
         <v>4.117187201861848</v>
       </c>
       <c r="J40" s="20">
-        <v>0.9353876006177274</v>
+        <v>1.0116879744745</v>
       </c>
       <c r="K40" s="20">
         <v>-0.5502296243021455</v>
       </c>
       <c r="L40" s="20">
-        <v>0.6430986395924994</v>
+        <v>0.6095457463997002</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.6134810313433108</v>
+        <v>-0.6794789570220128</v>
       </c>
       <c r="N40" s="20">
         <v>103.11616</v>
@@ -6345,13 +6391,13 @@
         <v>1.134</v>
       </c>
       <c r="R40" s="12">
-        <v>0.4096098468438623</v>
+        <v>0.4564311777644603</v>
       </c>
       <c r="S40" s="11">
-        <v>59.89767420130005</v>
+        <v>66.17996721498928</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -6359,61 +6405,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E41" s="10">
-        <v>423.5899963378906</v>
+        <v>145.4700012207031</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3634783352910164</v>
+        <v>0.3780495044086423</v>
       </c>
       <c r="G41" s="20">
-        <v>-0.2429950411639331</v>
+        <v>0.6042209697867998</v>
       </c>
       <c r="H41" s="20">
-        <v>0.6042118867300035</v>
+        <v>0.4636940000902633</v>
       </c>
       <c r="I41" s="20">
-        <v>-0.3187981010065978</v>
+        <v>1.421647839457134</v>
       </c>
       <c r="J41" s="20">
-        <v>0.9427973244719356</v>
+        <v>0.366837258617614</v>
       </c>
       <c r="K41" s="20">
-        <v>0.3173660963957367</v>
+        <v>-0.514680868525332</v>
       </c>
       <c r="L41" s="20">
-        <v>-0.009964680998773449</v>
+        <v>0.1741274048087001</v>
       </c>
       <c r="M41" s="20">
-        <v>0.2762262859405108</v>
+        <v>-0.07254014704879552</v>
       </c>
       <c r="N41" s="20">
-        <v>32.779457</v>
+        <v>11.467704</v>
       </c>
       <c r="O41" s="20">
-        <v>6.0678544</v>
+        <v>2.4302394</v>
       </c>
       <c r="P41" s="12">
-        <v>0.1983</v>
+        <v>0.22507</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.109</v>
+        <v>0.587</v>
       </c>
       <c r="R41" s="12">
-        <v>0.4809285674428023</v>
+        <v>0.07393429432028786</v>
       </c>
       <c r="S41" s="11">
-        <v>59.53715783994979</v>
+        <v>49.01168542358315</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -6421,61 +6467,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E42" s="10">
-        <v>283.5599975585938</v>
+        <v>30.18000030517578</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3626886008109039</v>
+        <v>0.3762441017553563</v>
       </c>
       <c r="G42" s="20">
-        <v>1.154887046419179</v>
+        <v>0.4737570391617266</v>
       </c>
       <c r="H42" s="20">
-        <v>-0.7540543836248536</v>
+        <v>-0.2868604961518937</v>
       </c>
       <c r="I42" s="20">
-        <v>-0.2666959649926476</v>
+        <v>-0.7009083349924576</v>
       </c>
       <c r="J42" s="20">
-        <v>0.6099495867240897</v>
+        <v>0.5652276110314181</v>
       </c>
       <c r="K42" s="20">
-        <v>0.5996953451739074</v>
+        <v>2.017008782014688</v>
       </c>
       <c r="L42" s="20">
-        <v>0.977367768157744</v>
+        <v>0.6231068103363985</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.1432894149108433</v>
+        <v>-0.5254924772697203</v>
       </c>
       <c r="N42" s="20">
-        <v>13.5148325</v>
+        <v>28.582525</v>
       </c>
       <c r="O42" s="20">
-        <v>2.2874217</v>
+        <v>1.876474</v>
       </c>
       <c r="P42" s="12">
-        <v>0.18341999</v>
+        <v>0.07979</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.094</v>
+        <v>0.108</v>
       </c>
       <c r="R42" s="12">
-        <v>0.3133269120670266</v>
+        <v>0.2564957477462224</v>
       </c>
       <c r="S42" s="11">
-        <v>51.70218784966599</v>
+        <v>54.94042346838992</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -6483,61 +6529,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="E43" s="10">
-        <v>92.44999694824219</v>
+        <v>1152.43994140625</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3607236851369043</v>
+        <v>0.3739747275748479</v>
       </c>
       <c r="G43" s="20">
-        <v>0.6594637779990824</v>
+        <v>-1.116529275497701</v>
       </c>
       <c r="H43" s="20">
-        <v>-0.4971404169201537</v>
+        <v>1.795145004616197</v>
       </c>
       <c r="I43" s="20">
-        <v>-0.2300784505986128</v>
+        <v>0.7292599135714521</v>
       </c>
       <c r="J43" s="20">
-        <v>1.2184990847352</v>
+        <v>0.349369197778972</v>
       </c>
       <c r="K43" s="20">
-        <v>-0.2864475524510079</v>
+        <v>0.782075918289733</v>
       </c>
       <c r="L43" s="20">
-        <v>0.1005261043608595</v>
+        <v>0.2148180397949501</v>
       </c>
       <c r="M43" s="20">
-        <v>0.09203664345080942</v>
+        <v>0.04064816440675914</v>
       </c>
       <c r="N43" s="20">
-        <v>15.108153</v>
+        <v>37.452164</v>
       </c>
       <c r="O43" s="20">
-        <v>6.0021152</v>
+        <v>29.35898</v>
       </c>
       <c r="P43" s="12">
-        <v>0.43126</v>
+        <v>1.02286</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.036</v>
+        <v>0.477</v>
       </c>
       <c r="R43" s="12">
-        <v>0.5187902826849144</v>
+        <v>0.2592756954666591</v>
       </c>
       <c r="S43" s="11">
-        <v>60.28087623970859</v>
+        <v>47.1653176323962</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6545,61 +6591,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="E44" s="10">
-        <v>132.5399932861328</v>
+        <v>283.8099975585938</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3597597139357274</v>
+        <v>0.3509916863901038</v>
       </c>
       <c r="G44" s="20">
-        <v>0.4918102935471612</v>
+        <v>1.154887046419179</v>
       </c>
       <c r="H44" s="20">
-        <v>-0.1401007530318513</v>
+        <v>-0.7540543836248536</v>
       </c>
       <c r="I44" s="20">
-        <v>0.7942683123659047</v>
+        <v>-0.2666959649926476</v>
       </c>
       <c r="J44" s="20">
-        <v>0.7739541985332267</v>
+        <v>0.5652236381958162</v>
       </c>
       <c r="K44" s="20">
-        <v>-0.09427819151258149</v>
+        <v>0.5996953451739074</v>
       </c>
       <c r="L44" s="20">
-        <v>0.3884954945912291</v>
+        <v>0.9849038368276697</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.3744931988523483</v>
+        <v>-0.1274305896922634</v>
       </c>
       <c r="N44" s="20">
-        <v>18.192053</v>
+        <v>13.5148325</v>
       </c>
       <c r="O44" s="20">
-        <v>2.5249555</v>
+        <v>2.2874217</v>
       </c>
       <c r="P44" s="12">
-        <v>0.1418</v>
+        <v>0.18341999</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.355</v>
+        <v>0.094</v>
       </c>
       <c r="R44" s="12">
-        <v>0.09396580474072702</v>
+        <v>0.3468356468898324</v>
       </c>
       <c r="S44" s="11">
-        <v>51.73931540348961</v>
+        <v>52.08842158739922</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -6665,110 +6711,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -6777,22 +6823,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -6871,57 +6917,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>34</v>
@@ -6929,113 +6975,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -7061,181 +7107,181 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>433.3439025878906</v>
+        <v>408.7745361328125</v>
       </c>
       <c r="C1">
-        <v>408.7745361328125</v>
+        <v>398.8309326171875</v>
       </c>
       <c r="D1">
-        <v>398.8309326171875</v>
+        <v>413.9259948730469</v>
       </c>
       <c r="E1">
-        <v>413.9259948730469</v>
+        <v>430.7481994628906</v>
       </c>
       <c r="F1">
-        <v>430.7481994628906</v>
+        <v>424.5484619140625</v>
       </c>
       <c r="G1">
-        <v>424.5484619140625</v>
+        <v>393.6694946289062</v>
       </c>
       <c r="H1">
-        <v>393.6694946289062</v>
+        <v>411.1206359863281</v>
       </c>
       <c r="I1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="J1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="K1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="L1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="M1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="N1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="O1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="P1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="Q1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="R1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="S1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="T1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="U1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="V1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="W1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="X1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="Y1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="Z1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="AA1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="AB1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="AC1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="AD1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="AE1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="AF1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="AG1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AH1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AI1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AJ1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AK1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AL1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AM1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AN1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AO1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AP1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AQ1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AR1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="AS1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="AT1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="AU1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="AV1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="AW1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="AX1">
-        <v>425</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="AY1">
-        <v>492.2000122070312</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="AZ1">
-        <v>516.3900146484375</v>
+        <v>524.1400146484375</v>
       </c>
       <c r="BA1">
-        <v>524.1400146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="BB1">
-        <v>533.8800048828125</v>
+        <v>535.25</v>
       </c>
       <c r="BC1">
-        <v>535.25</v>
+        <v>506.6199951171875</v>
       </c>
       <c r="BD1">
-        <v>506.6199951171875</v>
+        <v>567.2899780273438</v>
       </c>
       <c r="BE1">
-        <v>567.2899780273438</v>
+        <v>534.280029296875</v>
       </c>
       <c r="BF1">
-        <v>534.280029296875</v>
+        <v>543.510009765625</v>
       </c>
       <c r="BG1">
-        <v>543.510009765625</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="BH1">
-        <v>563.2899780273438</v>
+        <v>588.4000244140625</v>
       </c>
     </row>
     <row r="2" spans="1:60">
@@ -7243,181 +7289,181 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1048.348754882812</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="C2">
-        <v>1213.373413085938</v>
+        <v>1132.155883789062</v>
       </c>
       <c r="D2">
-        <v>1132.155883789062</v>
+        <v>1145.103881835938</v>
       </c>
       <c r="E2">
-        <v>1145.103881835938</v>
+        <v>1154.112548828125</v>
       </c>
       <c r="F2">
-        <v>1154.112548828125</v>
+        <v>1032.121337890625</v>
       </c>
       <c r="G2">
-        <v>1032.121337890625</v>
+        <v>975.4099731445312</v>
       </c>
       <c r="H2">
-        <v>975.4099731445312</v>
+        <v>984.75</v>
       </c>
       <c r="I2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="J2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="K2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="L2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="M2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="N2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="O2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="P2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="Q2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="R2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="S2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="T2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="U2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="V2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="W2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="X2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="Y2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="Z2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="AA2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="AB2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="AC2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="AD2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="AE2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="AF2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AG2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AH2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AI2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AJ2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AK2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AL2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AM2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AN2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AO2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AP2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AQ2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AR2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="AS2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="AT2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="AU2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="AV2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="AW2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="AX2">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="AY2">
-        <v>956.0800170898438</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="AZ2">
-        <v>958.1599731445312</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="BA2">
-        <v>1016.590026855469</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="BB2">
-        <v>1000.260009765625</v>
+        <v>1027.77001953125</v>
       </c>
       <c r="BC2">
-        <v>1027.77001953125</v>
+        <v>977.4099731445312</v>
       </c>
       <c r="BD2">
-        <v>977.4099731445312</v>
+        <v>975.260009765625</v>
       </c>
       <c r="BE2">
-        <v>975.260009765625</v>
+        <v>924.030029296875</v>
       </c>
       <c r="BF2">
-        <v>924.030029296875</v>
+        <v>927.5999755859375</v>
       </c>
       <c r="BG2">
-        <v>927.5999755859375</v>
+        <v>926.5499877929688</v>
       </c>
       <c r="BH2">
-        <v>926.5499877929688</v>
+        <v>977.5</v>
       </c>
     </row>
     <row r="3" spans="1:60">
@@ -7425,181 +7471,181 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1914.4599609375</v>
+        <v>2335</v>
       </c>
       <c r="C3">
-        <v>2335</v>
+        <v>2090.7099609375</v>
       </c>
       <c r="D3">
-        <v>2090.7099609375</v>
+        <v>2050.389892578125</v>
       </c>
       <c r="E3">
-        <v>2050.389892578125</v>
+        <v>2273.72998046875</v>
       </c>
       <c r="F3">
-        <v>2273.72998046875</v>
+        <v>2032.219970703125</v>
       </c>
       <c r="G3">
-        <v>2032.219970703125</v>
+        <v>1745</v>
       </c>
       <c r="H3">
-        <v>1745</v>
+        <v>1744.430053710938</v>
       </c>
       <c r="I3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="J3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="K3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="L3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="M3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="N3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="O3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="P3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="Q3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="R3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="S3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="T3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="U3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="V3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="W3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="X3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="Y3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="Z3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="AA3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="AB3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="AC3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="AD3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="AE3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="AF3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AG3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AH3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AI3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AJ3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AK3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AL3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AM3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AN3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AO3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AP3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AQ3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AR3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="AS3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AT3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="AU3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="AV3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="AW3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="AX3">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="AY3">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="AZ3">
-        <v>1554.989990234375</v>
+        <v>1740</v>
       </c>
       <c r="BA3">
-        <v>1740</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="BB3">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="BC3">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="BD3">
-        <v>1692.589965820312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="BE3">
-        <v>1633.349975585938</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="BF3">
-        <v>1551.989990234375</v>
+        <v>1530.89501953125</v>
       </c>
       <c r="BG3">
-        <v>1530.89501953125</v>
+        <v>1519.969970703125</v>
       </c>
       <c r="BH3">
-        <v>1519.969970703125</v>
+        <v>1614.390014648438</v>
       </c>
     </row>
     <row r="4" spans="1:60">
@@ -7607,181 +7653,181 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>643.6234130859375</v>
+        <v>675.1732788085938</v>
       </c>
       <c r="C4">
-        <v>675.1732788085938</v>
+        <v>586.2618408203125</v>
       </c>
       <c r="D4">
-        <v>586.2618408203125</v>
+        <v>651.6708374023438</v>
       </c>
       <c r="E4">
-        <v>651.6708374023438</v>
+        <v>638.5150146484375</v>
       </c>
       <c r="F4">
-        <v>638.5150146484375</v>
+        <v>598.177978515625</v>
       </c>
       <c r="G4">
-        <v>598.177978515625</v>
+        <v>538.8270263671875</v>
       </c>
       <c r="H4">
-        <v>538.8270263671875</v>
+        <v>577.2747192382812</v>
       </c>
       <c r="I4">
-        <v>577.2747192382812</v>
+        <v>531.92919921875</v>
       </c>
       <c r="J4">
-        <v>531.92919921875</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="K4">
-        <v>550.1234130859375</v>
+        <v>577.864501953125</v>
       </c>
       <c r="L4">
-        <v>577.864501953125</v>
+        <v>582.403076171875</v>
       </c>
       <c r="M4">
-        <v>582.403076171875</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="N4">
-        <v>555.3717041015625</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="O4">
-        <v>563.1392211914062</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="P4">
-        <v>513.6751098632812</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="Q4">
-        <v>466.6601867675781</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="R4">
-        <v>477.0668640136719</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="S4">
-        <v>487.2635803222656</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="T4">
-        <v>548.2140502929688</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="U4">
-        <v>556.4913330078125</v>
+        <v>558.120849609375</v>
       </c>
       <c r="V4">
-        <v>558.120849609375</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="W4">
-        <v>519.6331787109375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="X4">
-        <v>497.7602233886719</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="Y4">
-        <v>463.3612670898438</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="Z4">
-        <v>461.8917236328125</v>
+        <v>532.868896484375</v>
       </c>
       <c r="AA4">
-        <v>532.868896484375</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="AB4">
-        <v>544.6651611328125</v>
+        <v>527.05078125</v>
       </c>
       <c r="AC4">
-        <v>527.05078125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="AD4">
-        <v>548.3839721679688</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="AE4">
-        <v>519.0033569335938</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="AF4">
-        <v>451.3750915527344</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="AG4">
-        <v>434.1606140136719</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AH4">
-        <v>438.1993408203125</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AI4">
-        <v>437.7894592285156</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AJ4">
-        <v>453.9542846679688</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AK4">
-        <v>487.1336364746094</v>
+        <v>508.63671875</v>
       </c>
       <c r="AL4">
-        <v>508.63671875</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AM4">
-        <v>535.8380126953125</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AN4">
-        <v>496.0007934570312</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AO4">
-        <v>461.9417114257812</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AP4">
-        <v>468.8994750976562</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AQ4">
-        <v>459.2925720214844</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AR4">
-        <v>435.2402954101562</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="AS4">
-        <v>450.6053466796875</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AT4">
-        <v>468.7295227050781</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="AU4">
-        <v>461.8517456054688</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="AV4">
-        <v>459.3025817871094</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="AW4">
-        <v>450.4053955078125</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="AX4">
-        <v>450.2954406738281</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="AY4">
-        <v>448.7559509277344</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="AZ4">
-        <v>441.4283142089844</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="BA4">
-        <v>467.3099670410156</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="BB4">
-        <v>477.2999877929688</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="BC4">
-        <v>482.2799987792969</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="BD4">
-        <v>460.9299926757812</v>
+        <v>447.1799926757812</v>
       </c>
       <c r="BE4">
-        <v>447.1799926757812</v>
+        <v>426.9400024414062</v>
       </c>
       <c r="BF4">
-        <v>426.9400024414062</v>
+        <v>411.9599914550781</v>
       </c>
       <c r="BG4">
-        <v>411.9599914550781</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="BH4">
-        <v>416.9700012207031</v>
+        <v>423.8699951171875</v>
       </c>
     </row>
     <row r="5" spans="1:60">
@@ -7789,181 +7835,181 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>241.4967041015625</v>
+        <v>254.0780792236328</v>
       </c>
       <c r="C5">
-        <v>254.0780792236328</v>
+        <v>258.3714904785156</v>
       </c>
       <c r="D5">
-        <v>258.3714904785156</v>
+        <v>265.2947387695312</v>
       </c>
       <c r="E5">
-        <v>265.2947387695312</v>
+        <v>259.4373779296875</v>
       </c>
       <c r="F5">
-        <v>259.4373779296875</v>
+        <v>268.4027404785156</v>
       </c>
       <c r="G5">
-        <v>268.4027404785156</v>
+        <v>266.7291870117188</v>
       </c>
       <c r="H5">
-        <v>266.7291870117188</v>
+        <v>269.2793579101562</v>
       </c>
       <c r="I5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="J5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="K5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="L5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="M5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="N5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="O5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="P5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="Q5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="R5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="S5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="T5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="U5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="V5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="W5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="X5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="Y5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="Z5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="AA5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="AB5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="AC5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="AD5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="AE5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="AF5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="AG5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AH5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AI5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AJ5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AK5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AL5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AM5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AN5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AO5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AP5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AQ5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="AR5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="AS5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AT5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="AU5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="AV5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="AW5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="AX5">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="AY5">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="AZ5">
-        <v>370.6900024414062</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="BA5">
-        <v>370.7200012207031</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="BB5">
-        <v>382.8500061035156</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="BC5">
-        <v>388.9500122070312</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="BD5">
-        <v>385.4299926757812</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="BE5">
-        <v>390.4200134277344</v>
+        <v>382.9500122070312</v>
       </c>
       <c r="BF5">
-        <v>382.9500122070312</v>
+        <v>397.0400085449219</v>
       </c>
       <c r="BG5">
-        <v>397.0400085449219</v>
+        <v>403.2799987792969</v>
       </c>
       <c r="BH5">
-        <v>403.2799987792969</v>
+        <v>412.5299987792969</v>
       </c>
     </row>
     <row r="6" spans="1:60">
@@ -7971,181 +8017,181 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>245.8368530273438</v>
+        <v>252.8676147460938</v>
       </c>
       <c r="C6">
-        <v>252.8676147460938</v>
+        <v>253.3662414550781</v>
       </c>
       <c r="D6">
-        <v>253.3662414550781</v>
+        <v>258.5121459960938</v>
       </c>
       <c r="E6">
-        <v>258.5121459960938</v>
+        <v>254.9718475341797</v>
       </c>
       <c r="F6">
-        <v>254.9718475341797</v>
+        <v>264.146728515625</v>
       </c>
       <c r="G6">
-        <v>264.146728515625</v>
+        <v>265.6226806640625</v>
       </c>
       <c r="H6">
-        <v>265.6226806640625</v>
+        <v>268.2554626464844</v>
       </c>
       <c r="I6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="J6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="K6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="L6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="M6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="N6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="O6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="P6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="Q6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="R6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="S6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="T6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="U6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="V6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="W6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="X6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="Y6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="Z6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="AA6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="AB6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="AC6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="AD6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="AE6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="AF6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="AG6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AH6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AI6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AJ6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AK6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AL6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AM6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AN6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AO6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AP6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AQ6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AR6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="AS6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AT6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="AU6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="AV6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="AW6">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="AX6">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AY6">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="AZ6">
-        <v>387.7099914550781</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="BA6">
-        <v>388.8999938964844</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="BB6">
-        <v>397.7699890136719</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="BC6">
-        <v>399.4400024414062</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="BD6">
-        <v>392.4200134277344</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="BE6">
-        <v>395.9299926757812</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="BF6">
-        <v>396.4500122070312</v>
+        <v>410.8399963378906</v>
       </c>
       <c r="BG6">
-        <v>410.8399963378906</v>
+        <v>413.9200134277344</v>
       </c>
       <c r="BH6">
-        <v>413.9200134277344</v>
+        <v>421.9599914550781</v>
       </c>
     </row>
     <row r="7" spans="1:60">
@@ -8153,181 +8199,181 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>50.85663604736328</v>
+        <v>50.97608947753906</v>
       </c>
       <c r="C7">
-        <v>50.97608947753906</v>
+        <v>49.76166152954102</v>
       </c>
       <c r="D7">
-        <v>49.76166152954102</v>
+        <v>48.86577224731445</v>
       </c>
       <c r="E7">
-        <v>48.86577224731445</v>
+        <v>48.34814834594727</v>
       </c>
       <c r="F7">
-        <v>48.34814834594727</v>
+        <v>47.72102355957031</v>
       </c>
       <c r="G7">
-        <v>47.72102355957031</v>
+        <v>48.68659591674805</v>
       </c>
       <c r="H7">
-        <v>48.68659591674805</v>
+        <v>48.58705139160156</v>
       </c>
       <c r="I7">
-        <v>48.58705139160156</v>
+        <v>51.44394302368164</v>
       </c>
       <c r="J7">
-        <v>51.44394302368164</v>
+        <v>53.34521865844727</v>
       </c>
       <c r="K7">
-        <v>53.34521865844727</v>
+        <v>52.06110763549805</v>
       </c>
       <c r="L7">
-        <v>52.06110763549805</v>
+        <v>52.64841461181641</v>
       </c>
       <c r="M7">
-        <v>52.64841461181641</v>
+        <v>54.55964660644531</v>
       </c>
       <c r="N7">
-        <v>54.55964660644531</v>
+        <v>54.32073974609375</v>
       </c>
       <c r="O7">
-        <v>54.32073974609375</v>
+        <v>53.52439498901367</v>
       </c>
       <c r="P7">
-        <v>53.52439498901367</v>
+        <v>53.40494537353516</v>
       </c>
       <c r="Q7">
-        <v>53.40494537353516</v>
+        <v>54.60941696166992</v>
       </c>
       <c r="R7">
-        <v>54.60941696166992</v>
+        <v>54.93790817260742</v>
       </c>
       <c r="S7">
-        <v>54.93790817260742</v>
+        <v>56.24192428588867</v>
       </c>
       <c r="T7">
-        <v>56.24192428588867</v>
+        <v>57.23735809326172</v>
       </c>
       <c r="U7">
-        <v>57.23735809326172</v>
+        <v>57.33689880371094</v>
       </c>
       <c r="V7">
-        <v>57.33689880371094</v>
+        <v>57.03827285766602</v>
       </c>
       <c r="W7">
-        <v>57.03827285766602</v>
+        <v>54.67909622192383</v>
       </c>
       <c r="X7">
-        <v>54.67909622192383</v>
+        <v>53.68366622924805</v>
       </c>
       <c r="Y7">
-        <v>53.68366622924805</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="Z7">
-        <v>55.77407073974609</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="AA7">
-        <v>55.69443893432617</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="AB7">
-        <v>56.80932235717773</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="AC7">
-        <v>55.21663284301758</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="AD7">
-        <v>54.8383674621582</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="AE7">
-        <v>53.56421279907227</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="AF7">
-        <v>55.78402709960938</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="AG7">
-        <v>55.65462112426758</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="AH7">
-        <v>58.38210678100586</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="AI7">
-        <v>58.79023361206055</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="AJ7">
-        <v>58.28256225585938</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="AK7">
-        <v>57.43644714355469</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="AL7">
-        <v>58.09342956542969</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="AM7">
-        <v>58.77032470703125</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="AN7">
-        <v>59.52685165405273</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="AO7">
-        <v>59.81552886962891</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="AP7">
-        <v>61.23899841308594</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="AQ7">
+        <v>59.8354377746582</v>
+      </c>
+      <c r="AR7">
+        <v>58.1431999206543</v>
+      </c>
+      <c r="AS7">
+        <v>58.35224151611328</v>
+      </c>
+      <c r="AT7">
+        <v>58.89972686767578</v>
+      </c>
+      <c r="AU7">
+        <v>58.83004760742188</v>
+      </c>
+      <c r="AV7">
+        <v>59.90511703491211</v>
+      </c>
+      <c r="AW7">
+        <v>60.67160034179688</v>
+      </c>
+      <c r="AX7">
+        <v>60.63178253173828</v>
+      </c>
+      <c r="AY7">
+        <v>60.33315277099609</v>
+      </c>
+      <c r="AZ7">
+        <v>59.7657585144043</v>
+      </c>
+      <c r="BA7">
+        <v>60.37297058105469</v>
+      </c>
+      <c r="BB7">
         <v>61.02000045776367</v>
       </c>
-      <c r="AR7">
-        <v>59.8354377746582</v>
-      </c>
-      <c r="AS7">
-        <v>58.1431999206543</v>
-      </c>
-      <c r="AT7">
-        <v>58.35224151611328</v>
-      </c>
-      <c r="AU7">
-        <v>58.89972686767578</v>
-      </c>
-      <c r="AV7">
-        <v>58.83004760742188</v>
-      </c>
-      <c r="AW7">
-        <v>59.90511703491211</v>
-      </c>
-      <c r="AX7">
-        <v>60.67160034179688</v>
-      </c>
-      <c r="AY7">
-        <v>60.63178253173828</v>
-      </c>
-      <c r="AZ7">
-        <v>60.33315277099609</v>
-      </c>
-      <c r="BA7">
-        <v>59.7657585144043</v>
-      </c>
-      <c r="BB7">
-        <v>60.37297058105469</v>
-      </c>
       <c r="BC7">
-        <v>61.02000045776367</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="BD7">
-        <v>61.15999984741211</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="BE7">
-        <v>61.45999908447266</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="BF7">
-        <v>61.77999877929688</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="BG7">
-        <v>63.52000045776367</v>
+        <v>59.36000061035156</v>
       </c>
       <c r="BH7">
-        <v>59.36000061035156</v>
+        <v>59.29000091552734</v>
       </c>
     </row>
     <row r="8" spans="1:60">
@@ -8335,181 +8381,181 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>167.7496643066406</v>
+        <v>170.8531799316406</v>
       </c>
       <c r="C8">
-        <v>170.8531799316406</v>
+        <v>170.7437591552734</v>
       </c>
       <c r="D8">
-        <v>170.7437591552734</v>
+        <v>173.131103515625</v>
       </c>
       <c r="E8">
-        <v>173.131103515625</v>
+        <v>168.1575012207031</v>
       </c>
       <c r="F8">
-        <v>168.1575012207031</v>
+        <v>173.5787200927734</v>
       </c>
       <c r="G8">
-        <v>173.5787200927734</v>
+        <v>175.4885864257812</v>
       </c>
       <c r="H8">
-        <v>175.4885864257812</v>
+        <v>176.3937835693359</v>
       </c>
       <c r="I8">
-        <v>176.3937835693359</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="J8">
-        <v>177.8957977294922</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="K8">
-        <v>186.8184509277344</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="L8">
-        <v>188.8178405761719</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="M8">
-        <v>187.3655395507812</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="N8">
-        <v>197.2431182861328</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="O8">
-        <v>200.3864288330078</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="P8">
-        <v>195.1243743896484</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="Q8">
-        <v>200.2571258544922</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="R8">
-        <v>205.7678680419922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="S8">
-        <v>207.6976318359375</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="T8">
-        <v>211.1493225097656</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="U8">
-        <v>210.2938537597656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="V8">
-        <v>205.8872375488281</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="W8">
-        <v>205.6783599853516</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="X8">
-        <v>206.7228088378906</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="Y8">
-        <v>204.7632141113281</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="Z8">
-        <v>205.7181396484375</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="AA8">
-        <v>209.4881286621094</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="AB8">
-        <v>210.5624237060547</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="AC8">
-        <v>205.1014099121094</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="AD8">
-        <v>204.8029937744141</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="AE8">
-        <v>201.4806365966797</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="AF8">
-        <v>204.4349517822266</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="AG8">
-        <v>202.8334503173828</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AH8">
-        <v>214.3821563720703</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AI8">
-        <v>223.1754760742188</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AJ8">
-        <v>224.3890380859375</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AK8">
-        <v>231.3819274902344</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AL8">
-        <v>232.3766479492188</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AM8">
-        <v>239.2800140380859</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AN8">
-        <v>243.4900054931641</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AO8">
-        <v>242.2899932861328</v>
+        <v>240</v>
       </c>
       <c r="AP8">
-        <v>240</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AQ8">
-        <v>242.8699951171875</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AR8">
-        <v>241.9600067138672</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="AS8">
-        <v>236.8999938964844</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AT8">
-        <v>242.2299957275391</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="AU8">
-        <v>239.8099975585938</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="AV8">
-        <v>244.0099945068359</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="AW8">
-        <v>246.5800018310547</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="AX8">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="AY8">
-        <v>256.0899963378906</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="AZ8">
-        <v>254.6600036621094</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="BA8">
-        <v>255.0899963378906</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="BB8">
-        <v>259.1400146484375</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="BC8">
-        <v>260.7799987792969</v>
+        <v>258.510009765625</v>
       </c>
       <c r="BD8">
-        <v>258.510009765625</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="BE8">
-        <v>259.4700012207031</v>
+        <v>257.0599975585938</v>
       </c>
       <c r="BF8">
-        <v>257.0599975585938</v>
+        <v>264.9299926757812</v>
       </c>
       <c r="BG8">
-        <v>264.9299926757812</v>
+        <v>264.6300048828125</v>
       </c>
       <c r="BH8">
-        <v>264.6300048828125</v>
+        <v>274.2099914550781</v>
       </c>
     </row>
     <row r="9" spans="1:60">
@@ -8517,181 +8563,181 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>33.09705352783203</v>
+        <v>33.18642044067383</v>
       </c>
       <c r="C9">
-        <v>33.18642044067383</v>
+        <v>32.77928924560547</v>
       </c>
       <c r="D9">
-        <v>32.77928924560547</v>
+        <v>32.72963714599609</v>
       </c>
       <c r="E9">
-        <v>32.72963714599609</v>
+        <v>32.34236526489258</v>
       </c>
       <c r="F9">
-        <v>32.34236526489258</v>
+        <v>31.64725685119629</v>
       </c>
       <c r="G9">
-        <v>31.64725685119629</v>
+        <v>32.13383102416992</v>
       </c>
       <c r="H9">
-        <v>32.13383102416992</v>
+        <v>32.23313140869141</v>
       </c>
       <c r="I9">
-        <v>32.23313140869141</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="J9">
-        <v>33.76237106323242</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="K9">
-        <v>34.81496429443359</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="L9">
-        <v>33.05733489990234</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="M9">
-        <v>33.20628356933594</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="N9">
-        <v>34.42768478393555</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="O9">
-        <v>34.28866577148438</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="P9">
-        <v>34.03048324584961</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="Q9">
-        <v>34.04041290283203</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="R9">
-        <v>34.97384262084961</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="S9">
-        <v>34.59650039672852</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="T9">
-        <v>35.52000045776367</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="U9">
-        <v>36.18000030517578</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="V9">
-        <v>36.41999816894531</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="W9">
-        <v>36.15000152587891</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="X9">
-        <v>34.7400016784668</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="Y9">
-        <v>34.93000030517578</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="Z9">
-        <v>36.70000076293945</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="AA9">
-        <v>36.33000183105469</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="AB9">
-        <v>37.31999969482422</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="AC9">
-        <v>36.86999893188477</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="AD9">
-        <v>35.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="AE9">
-        <v>34.65999984741211</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="AF9">
-        <v>36.52999877929688</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="AG9">
-        <v>37.63000106811523</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AH9">
-        <v>41.02000045776367</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AI9">
-        <v>40.61999893188477</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AJ9">
-        <v>39.97000122070312</v>
+        <v>40</v>
       </c>
       <c r="AK9">
-        <v>40</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AL9">
-        <v>40.47000122070312</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AM9">
-        <v>41.58000183105469</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AN9">
-        <v>42.36999893188477</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AO9">
-        <v>43.45000076293945</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AP9">
-        <v>44.38999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AQ9">
-        <v>43.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AR9">
-        <v>42.95999908447266</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="AS9">
-        <v>41.34999847412109</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AT9">
-        <v>41.18999862670898</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="AU9">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="AV9">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="AW9">
-        <v>43.15000152587891</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="AX9">
-        <v>44.29999923706055</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="AY9">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="AZ9">
-        <v>44.18000030517578</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="BA9">
-        <v>42.77000045776367</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="BB9">
-        <v>43.54999923706055</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="BC9">
-        <v>44.84000015258789</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="BD9">
-        <v>44.52999877929688</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="BE9">
-        <v>44.72999954223633</v>
+        <v>45.02999877929688</v>
       </c>
       <c r="BF9">
-        <v>45.02999877929688</v>
+        <v>47.40999984741211</v>
       </c>
       <c r="BG9">
-        <v>47.40999984741211</v>
+        <v>44.79000091552734</v>
       </c>
       <c r="BH9">
-        <v>44.79000091552734</v>
+        <v>45.45999908447266</v>
       </c>
     </row>
     <row r="10" spans="1:60">
@@ -8699,181 +8745,181 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>198.7775726318359</v>
+        <v>195.5212249755859</v>
       </c>
       <c r="C10">
-        <v>195.5212249755859</v>
+        <v>192.3148040771484</v>
       </c>
       <c r="D10">
-        <v>192.3148040771484</v>
+        <v>194.7520751953125</v>
       </c>
       <c r="E10">
-        <v>194.7520751953125</v>
+        <v>199.8663482666016</v>
       </c>
       <c r="F10">
-        <v>199.8663482666016</v>
+        <v>197.3591613769531</v>
       </c>
       <c r="G10">
-        <v>197.3591613769531</v>
+        <v>194.6122436523438</v>
       </c>
       <c r="H10">
-        <v>194.6122436523438</v>
+        <v>195.3314361572266</v>
       </c>
       <c r="I10">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="J10">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="K10">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="L10">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="M10">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="N10">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="O10">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="P10">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="Q10">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="R10">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="S10">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="T10">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="U10">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="V10">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="W10">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="X10">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="Y10">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="Z10">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="AA10">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="AB10">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="AC10">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="AD10">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="AE10">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="AF10">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="AG10">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="AH10">
+        <v>217.2568969726562</v>
+      </c>
+      <c r="AI10">
+        <v>223.8395233154297</v>
+      </c>
+      <c r="AJ10">
+        <v>225.0481872558594</v>
+      </c>
+      <c r="AK10">
+        <v>224.9083404541016</v>
+      </c>
+      <c r="AL10">
+        <v>224.7584991455078</v>
+      </c>
+      <c r="AM10">
+        <v>219.4944000244141</v>
+      </c>
+      <c r="AN10">
+        <v>217.3168334960938</v>
+      </c>
+      <c r="AO10">
+        <v>216.6076354980469</v>
+      </c>
+      <c r="AP10">
+        <v>214.4800109863281</v>
+      </c>
+      <c r="AQ10">
+        <v>208.2469787597656</v>
+      </c>
+      <c r="AR10">
+        <v>212.8118743896484</v>
+      </c>
+      <c r="AS10">
+        <v>209.4256591796875</v>
+      </c>
+      <c r="AT10">
+        <v>227.7251739501953</v>
+      </c>
+      <c r="AU10">
         <v>217.3068389892578</v>
       </c>
-      <c r="AI10">
-        <v>217.2568969726562</v>
-      </c>
-      <c r="AJ10">
-        <v>223.8395233154297</v>
-      </c>
-      <c r="AK10">
-        <v>225.0481872558594</v>
-      </c>
-      <c r="AL10">
-        <v>224.9083404541016</v>
-      </c>
-      <c r="AM10">
-        <v>224.7584991455078</v>
-      </c>
-      <c r="AN10">
-        <v>219.4944000244141</v>
-      </c>
-      <c r="AO10">
-        <v>217.3168334960938</v>
-      </c>
-      <c r="AP10">
-        <v>216.6076354980469</v>
-      </c>
-      <c r="AQ10">
-        <v>214.4800109863281</v>
-      </c>
-      <c r="AR10">
-        <v>208.2469787597656</v>
-      </c>
-      <c r="AS10">
-        <v>212.8118743896484</v>
-      </c>
-      <c r="AT10">
-        <v>209.4256591796875</v>
-      </c>
-      <c r="AU10">
-        <v>227.7251739501953</v>
-      </c>
       <c r="AV10">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="AW10">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="AX10">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="AY10">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="AZ10">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="BA10">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="BB10">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="BC10">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="BD10">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="BE10">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="BF10">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="BG10">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="BH10">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
     </row>
     <row r="11" spans="1:60">
@@ -8881,181 +8927,181 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>319.6471252441406</v>
+        <v>317.2054748535156</v>
       </c>
       <c r="C11">
-        <v>317.2054748535156</v>
+        <v>326.2545166015625</v>
       </c>
       <c r="D11">
-        <v>326.2545166015625</v>
+        <v>330.7491760253906</v>
       </c>
       <c r="E11">
-        <v>330.7491760253906</v>
+        <v>328.9951477050781</v>
       </c>
       <c r="F11">
-        <v>328.9951477050781</v>
+        <v>333.4798278808594</v>
       </c>
       <c r="G11">
-        <v>333.4798278808594</v>
+        <v>341.1436157226562</v>
       </c>
       <c r="H11">
-        <v>341.1436157226562</v>
+        <v>338.0143432617188</v>
       </c>
       <c r="I11">
-        <v>338.0143432617188</v>
+        <v>342.5588073730469</v>
       </c>
       <c r="J11">
-        <v>342.5588073730469</v>
+        <v>336.7885131835938</v>
       </c>
       <c r="K11">
-        <v>336.7885131835938</v>
+        <v>336.3301086425781</v>
       </c>
       <c r="L11">
-        <v>336.3301086425781</v>
+        <v>337.7651977539062</v>
       </c>
       <c r="M11">
-        <v>337.7651977539062</v>
+        <v>340.3463745117188</v>
       </c>
       <c r="N11">
-        <v>340.3463745117188</v>
+        <v>335.6822814941406</v>
       </c>
       <c r="O11">
-        <v>335.6822814941406</v>
+        <v>328.0683288574219</v>
       </c>
       <c r="P11">
-        <v>328.0683288574219</v>
+        <v>336.6689453125</v>
       </c>
       <c r="Q11">
-        <v>336.6689453125</v>
+        <v>367.7227783203125</v>
       </c>
       <c r="R11">
-        <v>367.7227783203125</v>
+        <v>367.244384765625</v>
       </c>
       <c r="S11">
-        <v>367.244384765625</v>
+        <v>368.3705444335938</v>
       </c>
       <c r="T11">
-        <v>368.3705444335938</v>
+        <v>370.8121643066406</v>
       </c>
       <c r="U11">
-        <v>370.8121643066406</v>
+        <v>375.0875549316406</v>
       </c>
       <c r="V11">
-        <v>375.0875549316406</v>
+        <v>385.9404907226562</v>
       </c>
       <c r="W11">
-        <v>385.9404907226562</v>
+        <v>389.0199584960938</v>
       </c>
       <c r="X11">
-        <v>389.0199584960938</v>
+        <v>395.8665161132812</v>
       </c>
       <c r="Y11">
-        <v>395.8665161132812</v>
+        <v>387.6845092773438</v>
       </c>
       <c r="Z11">
-        <v>387.6845092773438</v>
+        <v>374.7088623046875</v>
       </c>
       <c r="AA11">
-        <v>374.7088623046875</v>
+        <v>373.0844116210938</v>
       </c>
       <c r="AB11">
-        <v>373.0844116210938</v>
+        <v>372.5462646484375</v>
       </c>
       <c r="AC11">
-        <v>372.5462646484375</v>
+        <v>375.8648986816406</v>
       </c>
       <c r="AD11">
-        <v>375.8648986816406</v>
+        <v>381.1468811035156</v>
       </c>
       <c r="AE11">
-        <v>381.1468811035156</v>
+        <v>384.6847534179688</v>
       </c>
       <c r="AF11">
-        <v>384.6847534179688</v>
+        <v>383.0005187988281</v>
       </c>
       <c r="AG11">
-        <v>383.0005187988281</v>
+        <v>374.3401184082031</v>
       </c>
       <c r="AH11">
-        <v>374.3401184082031</v>
+        <v>374.3301391601562</v>
       </c>
       <c r="AI11">
-        <v>374.3301391601562</v>
+        <v>368.8987426757812</v>
       </c>
       <c r="AJ11">
-        <v>368.8987426757812</v>
+        <v>368.7392883300781</v>
       </c>
       <c r="AK11">
-        <v>368.7392883300781</v>
+        <v>369.0980224609375</v>
       </c>
       <c r="AL11">
-        <v>369.0980224609375</v>
+        <v>363.2680053710938</v>
       </c>
       <c r="AM11">
-        <v>363.2680053710938</v>
+        <v>366.6763305664062</v>
       </c>
       <c r="AN11">
-        <v>366.6763305664062</v>
+        <v>360.9857788085938</v>
       </c>
       <c r="AO11">
-        <v>360.9857788085938</v>
+        <v>363.248046875</v>
       </c>
       <c r="AP11">
-        <v>363.248046875</v>
+        <v>362.3411254882812</v>
       </c>
       <c r="AQ11">
-        <v>362.3411254882812</v>
+        <v>369.2873840332031</v>
       </c>
       <c r="AR11">
-        <v>369.2873840332031</v>
+        <v>368.4004516601562</v>
       </c>
       <c r="AS11">
-        <v>368.4004516601562</v>
+        <v>369.8853454589844</v>
       </c>
       <c r="AT11">
-        <v>369.8853454589844</v>
+        <v>368.071533203125</v>
       </c>
       <c r="AU11">
-        <v>368.071533203125</v>
+        <v>368.6396179199219</v>
       </c>
       <c r="AV11">
-        <v>368.6396179199219</v>
+        <v>364.6831359863281</v>
       </c>
       <c r="AW11">
-        <v>364.6831359863281</v>
+        <v>362.6799926757812</v>
       </c>
       <c r="AX11">
-        <v>362.6799926757812</v>
+        <v>364.9322814941406</v>
       </c>
       <c r="AY11">
-        <v>364.9322814941406</v>
+        <v>373.0644836425781</v>
       </c>
       <c r="AZ11">
-        <v>373.0644836425781</v>
+        <v>368.0914916992188</v>
       </c>
       <c r="BA11">
-        <v>368.0914916992188</v>
+        <v>364.4140625</v>
       </c>
       <c r="BB11">
-        <v>364.4140625</v>
+        <v>365.6000061035156</v>
       </c>
       <c r="BC11">
-        <v>365.6000061035156</v>
+        <v>367.5599975585938</v>
       </c>
       <c r="BD11">
-        <v>367.5599975585938</v>
+        <v>375.2000122070312</v>
       </c>
       <c r="BE11">
-        <v>375.2000122070312</v>
+        <v>378.0499877929688</v>
       </c>
       <c r="BF11">
-        <v>378.0499877929688</v>
+        <v>377.9700012207031</v>
       </c>
       <c r="BG11">
-        <v>377.9700012207031</v>
+        <v>378.9200134277344</v>
       </c>
       <c r="BH11">
-        <v>378.9200134277344</v>
+        <v>379.489990234375</v>
       </c>
     </row>
     <row r="12" spans="1:60">
@@ -9063,181 +9109,181 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>344.816162109375</v>
+        <v>341.9679870605469</v>
       </c>
       <c r="C12">
-        <v>341.9679870605469</v>
+        <v>334.4728698730469</v>
       </c>
       <c r="D12">
-        <v>334.4728698730469</v>
+        <v>351.0520935058594</v>
       </c>
       <c r="E12">
-        <v>351.0520935058594</v>
+        <v>353.1007385253906</v>
       </c>
       <c r="F12">
-        <v>353.1007385253906</v>
+        <v>357.6578063964844</v>
       </c>
       <c r="G12">
-        <v>357.6578063964844</v>
+        <v>355.9489135742188</v>
       </c>
       <c r="H12">
-        <v>355.9489135742188</v>
+        <v>364.6632385253906</v>
       </c>
       <c r="I12">
-        <v>364.6632385253906</v>
+        <v>363.3840942382812</v>
       </c>
       <c r="J12">
-        <v>363.3840942382812</v>
+        <v>358.4772644042969</v>
       </c>
       <c r="K12">
-        <v>358.4772644042969</v>
+        <v>356.0088500976562</v>
       </c>
       <c r="L12">
-        <v>356.0088500976562</v>
+        <v>354.7996520996094</v>
       </c>
       <c r="M12">
-        <v>354.7996520996094</v>
+        <v>350.4425048828125</v>
       </c>
       <c r="N12">
-        <v>350.4425048828125</v>
+        <v>357.09814453125</v>
       </c>
       <c r="O12">
-        <v>357.09814453125</v>
+        <v>369.9697875976562</v>
       </c>
       <c r="P12">
-        <v>369.9697875976562</v>
+        <v>353.5804443359375</v>
       </c>
       <c r="Q12">
-        <v>353.5804443359375</v>
+        <v>345.8954467773438</v>
       </c>
       <c r="R12">
-        <v>345.8954467773438</v>
+        <v>351.1420288085938</v>
       </c>
       <c r="S12">
-        <v>351.1420288085938</v>
+        <v>345.9653930664062</v>
       </c>
       <c r="T12">
-        <v>345.9653930664062</v>
+        <v>341.6881713867188</v>
       </c>
       <c r="U12">
-        <v>341.6881713867188</v>
+        <v>318.1334533691406</v>
       </c>
       <c r="V12">
-        <v>318.1334533691406</v>
+        <v>318.8829650878906</v>
       </c>
       <c r="W12">
-        <v>318.8829650878906</v>
+        <v>326.3581237792969</v>
       </c>
       <c r="X12">
-        <v>326.3581237792969</v>
+        <v>332.3842163085938</v>
       </c>
       <c r="Y12">
-        <v>332.3842163085938</v>
+        <v>335.5421752929688</v>
       </c>
       <c r="Z12">
-        <v>335.5421752929688</v>
+        <v>333.4635009765625</v>
       </c>
       <c r="AA12">
-        <v>333.4635009765625</v>
+        <v>356.4186096191406</v>
       </c>
       <c r="AB12">
-        <v>356.4186096191406</v>
+        <v>372.2283325195312</v>
       </c>
       <c r="AC12">
-        <v>372.2283325195312</v>
+        <v>375.1064758300781</v>
       </c>
       <c r="AD12">
-        <v>375.1064758300781</v>
+        <v>359.8963623046875</v>
       </c>
       <c r="AE12">
-        <v>359.8963623046875</v>
+        <v>356.3886108398438</v>
       </c>
       <c r="AF12">
-        <v>356.3886108398438</v>
+        <v>353.2406616210938</v>
       </c>
       <c r="AG12">
-        <v>353.2406616210938</v>
+        <v>355.609130859375</v>
       </c>
       <c r="AH12">
-        <v>355.609130859375</v>
+        <v>342.7774658203125</v>
       </c>
       <c r="AI12">
-        <v>342.7774658203125</v>
+        <v>342.1478576660156</v>
       </c>
       <c r="AJ12">
-        <v>342.1478576660156</v>
+        <v>343.7168579101562</v>
       </c>
       <c r="AK12">
-        <v>343.7168579101562</v>
+        <v>343.3171081542969</v>
       </c>
       <c r="AL12">
-        <v>343.3171081542969</v>
+        <v>341.2284851074219</v>
       </c>
       <c r="AM12">
-        <v>341.2284851074219</v>
+        <v>341.0585632324219</v>
       </c>
       <c r="AN12">
-        <v>341.0585632324219</v>
+        <v>341.4783325195312</v>
       </c>
       <c r="AO12">
-        <v>341.4783325195312</v>
+        <v>337.9805908203125</v>
       </c>
       <c r="AP12">
-        <v>337.9805908203125</v>
+        <v>341.5282592773438</v>
       </c>
       <c r="AQ12">
-        <v>341.5282592773438</v>
+        <v>344.3664245605469</v>
       </c>
       <c r="AR12">
-        <v>344.3664245605469</v>
+        <v>343.1172485351562</v>
       </c>
       <c r="AS12">
-        <v>343.1172485351562</v>
+        <v>338.8800048828125</v>
       </c>
       <c r="AT12">
-        <v>338.8800048828125</v>
+        <v>337.4908752441406</v>
       </c>
       <c r="AU12">
-        <v>337.4908752441406</v>
+        <v>342.6575317382812</v>
       </c>
       <c r="AV12">
-        <v>342.6575317382812</v>
+        <v>335.1923828125</v>
       </c>
       <c r="AW12">
-        <v>335.1923828125</v>
+        <v>331.8145751953125</v>
       </c>
       <c r="AX12">
-        <v>331.8145751953125</v>
+        <v>333.5634460449219</v>
       </c>
       <c r="AY12">
-        <v>333.5634460449219</v>
+        <v>338.8599853515625</v>
       </c>
       <c r="AZ12">
-        <v>338.8599853515625</v>
+        <v>335.3099975585938</v>
       </c>
       <c r="BA12">
-        <v>335.3099975585938</v>
+        <v>335.3800048828125</v>
       </c>
       <c r="BB12">
-        <v>335.3800048828125</v>
+        <v>328.3800048828125</v>
       </c>
       <c r="BC12">
-        <v>328.3800048828125</v>
+        <v>330.3900146484375</v>
       </c>
       <c r="BD12">
-        <v>330.3900146484375</v>
+        <v>335.4500122070312</v>
       </c>
       <c r="BE12">
-        <v>335.4500122070312</v>
+        <v>345.7099914550781</v>
       </c>
       <c r="BF12">
-        <v>345.7099914550781</v>
+        <v>341.4299926757812</v>
       </c>
       <c r="BG12">
-        <v>341.4299926757812</v>
+        <v>339.3599853515625</v>
       </c>
       <c r="BH12">
-        <v>339.3599853515625</v>
+        <v>343.6799926757812</v>
       </c>
     </row>
     <row r="13" spans="1:60">
@@ -9245,181 +9291,181 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>62.97000122070312</v>
+        <v>64.76999664306641</v>
       </c>
       <c r="C13">
-        <v>64.76999664306641</v>
+        <v>65.73000335693359</v>
       </c>
       <c r="D13">
-        <v>65.73000335693359</v>
+        <v>64.54000091552734</v>
       </c>
       <c r="E13">
-        <v>64.54000091552734</v>
+        <v>64.19000244140625</v>
       </c>
       <c r="F13">
-        <v>64.19000244140625</v>
+        <v>68.34999847412109</v>
       </c>
       <c r="G13">
-        <v>68.34999847412109</v>
+        <v>67.86000061035156</v>
       </c>
       <c r="H13">
-        <v>67.86000061035156</v>
+        <v>66.05000305175781</v>
       </c>
       <c r="I13">
-        <v>66.05000305175781</v>
+        <v>66.12000274658203</v>
       </c>
       <c r="J13">
-        <v>66.12000274658203</v>
+        <v>67.08999633789062</v>
       </c>
       <c r="K13">
-        <v>67.08999633789062</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="L13">
-        <v>67.59999847412109</v>
+        <v>67.34999847412109</v>
       </c>
       <c r="M13">
-        <v>67.34999847412109</v>
+        <v>68.29000091552734</v>
       </c>
       <c r="N13">
-        <v>68.29000091552734</v>
+        <v>68.72000122070312</v>
       </c>
       <c r="O13">
-        <v>68.72000122070312</v>
+        <v>66.61000061035156</v>
       </c>
       <c r="P13">
-        <v>66.61000061035156</v>
+        <v>63.88999938964844</v>
       </c>
       <c r="Q13">
-        <v>63.88999938964844</v>
+        <v>66.44000244140625</v>
       </c>
       <c r="R13">
-        <v>66.44000244140625</v>
+        <v>65.83999633789062</v>
       </c>
       <c r="S13">
-        <v>65.83999633789062</v>
+        <v>67.58999633789062</v>
       </c>
       <c r="T13">
-        <v>67.58999633789062</v>
+        <v>65.88999938964844</v>
       </c>
       <c r="U13">
-        <v>65.88999938964844</v>
+        <v>63.7400016784668</v>
       </c>
       <c r="V13">
-        <v>63.7400016784668</v>
+        <v>63.40999984741211</v>
       </c>
       <c r="W13">
-        <v>63.40999984741211</v>
+        <v>64.08000183105469</v>
       </c>
       <c r="X13">
-        <v>64.08000183105469</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="Y13">
-        <v>63.90999984741211</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="Z13">
-        <v>61.81999969482422</v>
+        <v>60.84000015258789</v>
       </c>
       <c r="AA13">
-        <v>60.84000015258789</v>
+        <v>62.22000122070312</v>
       </c>
       <c r="AB13">
-        <v>62.22000122070312</v>
+        <v>63.7599983215332</v>
       </c>
       <c r="AC13">
-        <v>63.7599983215332</v>
+        <v>64.06999969482422</v>
       </c>
       <c r="AD13">
-        <v>64.06999969482422</v>
+        <v>66.98999786376953</v>
       </c>
       <c r="AE13">
-        <v>66.98999786376953</v>
+        <v>64.19999694824219</v>
       </c>
       <c r="AF13">
-        <v>64.19999694824219</v>
+        <v>65.76999664306641</v>
       </c>
       <c r="AG13">
-        <v>65.76999664306641</v>
+        <v>66.56999969482422</v>
       </c>
       <c r="AH13">
-        <v>66.56999969482422</v>
+        <v>64.87999725341797</v>
       </c>
       <c r="AI13">
-        <v>64.87999725341797</v>
+        <v>67.06999969482422</v>
       </c>
       <c r="AJ13">
-        <v>67.06999969482422</v>
+        <v>66.04000091552734</v>
       </c>
       <c r="AK13">
-        <v>66.04000091552734</v>
+        <v>67.47000122070312</v>
       </c>
       <c r="AL13">
-        <v>67.47000122070312</v>
+        <v>64.41000366210938</v>
       </c>
       <c r="AM13">
-        <v>64.41000366210938</v>
+        <v>65.22000122070312</v>
       </c>
       <c r="AN13">
-        <v>65.22000122070312</v>
+        <v>64.69999694824219</v>
       </c>
       <c r="AO13">
-        <v>64.69999694824219</v>
+        <v>64.13999938964844</v>
       </c>
       <c r="AP13">
-        <v>64.13999938964844</v>
+        <v>65.01999664306641</v>
       </c>
       <c r="AQ13">
-        <v>65.01999664306641</v>
+        <v>65.65000152587891</v>
       </c>
       <c r="AR13">
-        <v>65.65000152587891</v>
+        <v>65</v>
       </c>
       <c r="AS13">
-        <v>65</v>
+        <v>65.47000122070312</v>
       </c>
       <c r="AT13">
-        <v>65.47000122070312</v>
+        <v>65.33000183105469</v>
       </c>
       <c r="AU13">
-        <v>65.33000183105469</v>
+        <v>64.75</v>
       </c>
       <c r="AV13">
-        <v>64.75</v>
+        <v>64.33999633789062</v>
       </c>
       <c r="AW13">
-        <v>64.33999633789062</v>
+        <v>65.23000335693359</v>
       </c>
       <c r="AX13">
-        <v>65.23000335693359</v>
+        <v>67.33999633789062</v>
       </c>
       <c r="AY13">
-        <v>67.33999633789062</v>
+        <v>68.01999664306641</v>
       </c>
       <c r="AZ13">
-        <v>68.01999664306641</v>
+        <v>67.04000091552734</v>
       </c>
       <c r="BA13">
-        <v>67.04000091552734</v>
+        <v>64.58000183105469</v>
       </c>
       <c r="BB13">
-        <v>64.58000183105469</v>
+        <v>64.05999755859375</v>
       </c>
       <c r="BC13">
-        <v>64.05999755859375</v>
+        <v>65.40000152587891</v>
       </c>
       <c r="BD13">
-        <v>65.40000152587891</v>
+        <v>66.41999816894531</v>
       </c>
       <c r="BE13">
-        <v>66.41999816894531</v>
+        <v>69.41000366210938</v>
       </c>
       <c r="BF13">
-        <v>69.41000366210938</v>
+        <v>67.66000366210938</v>
       </c>
       <c r="BG13">
-        <v>67.66000366210938</v>
+        <v>66.01000213623047</v>
       </c>
       <c r="BH13">
-        <v>66.01000213623047</v>
+        <v>67.09999847412109</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -441,16 +441,22 @@
     <t>Fortinet</t>
   </si>
   <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
     <t>STX</t>
   </si>
   <si>
     <t>Seagate Technology</t>
   </si>
   <si>
-    <t>BMY</t>
-  </si>
-  <si>
-    <t>Bristol Myers Squibb</t>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
   </si>
   <si>
     <t>WBD</t>
@@ -459,12 +465,6 @@
     <t>Warner Bros. Discovery</t>
   </si>
   <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
-  </si>
-  <si>
     <t>WAT</t>
   </si>
   <si>
@@ -477,16 +477,22 @@
     <t>Lilly (Eli)</t>
   </si>
   <si>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
     <t>COF</t>
   </si>
   <si>
     <t>Capital One</t>
   </si>
   <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
   </si>
   <si>
     <t>A</t>
@@ -495,6 +501,12 @@
     <t>Agilent Technologies</t>
   </si>
   <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
     <t>BE</t>
   </si>
   <si>
@@ -504,22 +516,10 @@
     <t>Industrials</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>KEYS</t>
-  </si>
-  <si>
-    <t>Keysight Technologies</t>
+    <t>RVTY</t>
+  </si>
+  <si>
+    <t>Revvity</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -600,7 +600,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-28 19:27 UTC · данные на 2026-09-28 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-29 02:02 UTC · данные на 2026-09-28 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -681,7 +681,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-28 19:27 UTC</t>
+    <t>2026-09-29 02:02 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -4515,10 +4515,10 @@
         <v>36</v>
       </c>
       <c r="E5" s="10">
-        <v>1056.72998046875</v>
+        <v>1053.97998046875</v>
       </c>
       <c r="F5" s="17">
-        <v>1.209857049266151</v>
+        <v>1.2085157164277</v>
       </c>
       <c r="G5" s="20">
         <v>-0.5652307531380691</v>
@@ -4530,16 +4530,16 @@
         <v>3.949484521250298</v>
       </c>
       <c r="J5" s="20">
-        <v>2.156576916218938</v>
+        <v>2.152028444204602</v>
       </c>
       <c r="K5" s="20">
         <v>0</v>
       </c>
       <c r="L5" s="20">
-        <v>-2.838315879574414</v>
+        <v>-2.840116701519459</v>
       </c>
       <c r="M5" s="20">
-        <v>0.05981565467966299</v>
+        <v>0.06346837996923604</v>
       </c>
       <c r="N5" s="20">
         <v>24.447256</v>
@@ -4554,10 +4554,10 @@
         <v>3.457</v>
       </c>
       <c r="R5" s="12">
-        <v>1.95990296332831</v>
+        <v>1.952199955020532</v>
       </c>
       <c r="S5" s="11">
-        <v>58.78871377847319</v>
+        <v>58.35057323749435</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>114</v>
@@ -4577,10 +4577,10 @@
         <v>36</v>
       </c>
       <c r="E6" s="10">
-        <v>1710.055053710938</v>
+        <v>1712.890014648438</v>
       </c>
       <c r="F6" s="17">
-        <v>1.023692503152265</v>
+        <v>1.029211060387775</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5400051267382519</v>
@@ -4592,16 +4592,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J6" s="20">
-        <v>1.854256470224931</v>
+        <v>1.873943827100078</v>
       </c>
       <c r="K6" s="20">
         <v>0.0792978836476507</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.018570158890117</v>
+        <v>-3.017781627758584</v>
       </c>
       <c r="M6" s="20">
-        <v>-0.03681999551861631</v>
+        <v>-0.04225701670518689</v>
       </c>
       <c r="N6" s="20">
         <v>24.095963</v>
@@ -4616,10 +4616,10 @@
         <v>3.716</v>
       </c>
       <c r="R6" s="12">
-        <v>1.776829654702357</v>
+        <v>1.781433134329571</v>
       </c>
       <c r="S6" s="11">
-        <v>53.16332750710579</v>
+        <v>53.32535751730857</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>114</v>
@@ -4639,10 +4639,10 @@
         <v>36</v>
       </c>
       <c r="E7" s="10">
-        <v>62.58499908447266</v>
+        <v>62.63000106811523</v>
       </c>
       <c r="F7" s="17">
-        <v>0.9692298432562777</v>
+        <v>0.9725909310944281</v>
       </c>
       <c r="G7" s="20">
         <v>0.3308679966228206</v>
@@ -4654,16 +4654,16 @@
         <v>2.202669227673142</v>
       </c>
       <c r="J7" s="20">
-        <v>2.652702237145258</v>
+        <v>2.664679659166533</v>
       </c>
       <c r="K7" s="20">
         <v>0</v>
       </c>
       <c r="L7" s="20">
-        <v>-2.076387297304771</v>
+        <v>-2.075306633456196</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.1534776381764376</v>
+        <v>-0.1622315024229989</v>
       </c>
       <c r="N7" s="20">
         <v>32.4433</v>
@@ -4678,10 +4678,10 @@
         <v>0.337</v>
       </c>
       <c r="R7" s="12">
-        <v>1.628523977619318</v>
+        <v>1.630414027867387</v>
       </c>
       <c r="S7" s="11">
-        <v>60.56702562656024</v>
+        <v>60.67783554164512</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>114</v>
@@ -4692,58 +4692,58 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E8" s="10">
-        <v>389.6199951171875</v>
+        <v>342.75</v>
       </c>
       <c r="F8" s="17">
-        <v>0.8473924255078459</v>
+        <v>0.8491382180014263</v>
       </c>
       <c r="G8" s="20">
-        <v>0.6066625783285674</v>
+        <v>-0.3286805258697003</v>
       </c>
       <c r="H8" s="20">
-        <v>-0.6826845382770022</v>
+        <v>1.46049714331344</v>
       </c>
       <c r="I8" s="20">
-        <v>2.855442298450458</v>
+        <v>1.392272810408264</v>
       </c>
       <c r="J8" s="20">
-        <v>1.931534137371231</v>
+        <v>0.132534195576302</v>
       </c>
       <c r="K8" s="20">
-        <v>0.5895385746597579</v>
+        <v>4.134420649754185</v>
       </c>
       <c r="L8" s="20">
-        <v>0.05632757860932074</v>
+        <v>0.05523662630286615</v>
       </c>
       <c r="M8" s="20">
-        <v>-1.146325839989015</v>
+        <v>-0.04763806918211733</v>
       </c>
       <c r="N8" s="20">
-        <v>16.15269</v>
+        <v>17.273733</v>
       </c>
       <c r="O8" s="20">
-        <v>4.459058</v>
+        <v>6.7573094</v>
       </c>
       <c r="P8" s="12">
-        <v>0.27637</v>
+        <v>0.48676</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.517</v>
+        <v>0.242</v>
       </c>
       <c r="R8" s="12">
-        <v>0.5452343867345113</v>
+        <v>0.2509118514627715</v>
       </c>
       <c r="S8" s="11">
-        <v>59.40230115457515</v>
+        <v>48.86772542127657</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>114</v>
@@ -4754,58 +4754,58 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E9" s="10">
-        <v>341.5299987792969</v>
+        <v>389.5700073242188</v>
       </c>
       <c r="F9" s="17">
-        <v>0.8432562304072858</v>
+        <v>0.8488568038718871</v>
       </c>
       <c r="G9" s="20">
-        <v>-0.3286805258697003</v>
+        <v>0.6066625783285674</v>
       </c>
       <c r="H9" s="20">
-        <v>1.46049714331344</v>
+        <v>-0.6826845382770022</v>
       </c>
       <c r="I9" s="20">
-        <v>1.392272810408264</v>
+        <v>2.855442298450458</v>
       </c>
       <c r="J9" s="20">
-        <v>0.1055076982311214</v>
+        <v>1.938801096406154</v>
       </c>
       <c r="K9" s="20">
-        <v>4.134420649754185</v>
+        <v>0.5895385746597579</v>
       </c>
       <c r="L9" s="20">
-        <v>0.05365073605851149</v>
+        <v>0.05654729625472697</v>
       </c>
       <c r="M9" s="20">
-        <v>-0.01862413138117866</v>
+        <v>-1.155436995053518</v>
       </c>
       <c r="N9" s="20">
-        <v>17.273733</v>
+        <v>16.15269</v>
       </c>
       <c r="O9" s="20">
-        <v>6.7573094</v>
+        <v>4.459058</v>
       </c>
       <c r="P9" s="12">
-        <v>0.48676</v>
+        <v>0.27637</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.242</v>
+        <v>0.517</v>
       </c>
       <c r="R9" s="12">
-        <v>0.2464592942467931</v>
+        <v>0.5450361349569324</v>
       </c>
       <c r="S9" s="11">
-        <v>47.9569164197051</v>
+        <v>59.38019986852905</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>114</v>
@@ -4825,10 +4825,10 @@
         <v>59</v>
       </c>
       <c r="E10" s="10">
-        <v>338.3099975585938</v>
+        <v>339.1600036621094</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8427958803639006</v>
+        <v>0.8472556601481801</v>
       </c>
       <c r="G10" s="20">
         <v>-0.3209980775361091</v>
@@ -4840,16 +4840,16 @@
         <v>1.392272810408264</v>
       </c>
       <c r="J10" s="20">
-        <v>0.08060065993716282</v>
+        <v>0.1011824206069702</v>
       </c>
       <c r="K10" s="20">
         <v>4.134420649754185</v>
       </c>
       <c r="L10" s="20">
-        <v>0.1059438109029909</v>
+        <v>0.107497577080973</v>
       </c>
       <c r="M10" s="20">
-        <v>0.01251757179491039</v>
+        <v>-0.01008210804686011</v>
       </c>
       <c r="N10" s="20">
         <v>17.12249</v>
@@ -4864,10 +4864,10 @@
         <v>0.242</v>
       </c>
       <c r="R10" s="12">
-        <v>0.2373369246628887</v>
+        <v>0.2404458803116964</v>
       </c>
       <c r="S10" s="11">
-        <v>47.77180017862309</v>
+        <v>48.43503157637644</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>114</v>
@@ -4887,10 +4887,10 @@
         <v>36</v>
       </c>
       <c r="E11" s="10">
-        <v>42.09500122070312</v>
+        <v>41.77999877929688</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8381799897169411</v>
+        <v>0.831979250927496</v>
       </c>
       <c r="G11" s="20">
         <v>-0.01962276509782637</v>
@@ -4902,16 +4902,16 @@
         <v>3.890766583974275</v>
       </c>
       <c r="J11" s="20">
-        <v>1.287445353787207</v>
+        <v>1.264860140866668</v>
       </c>
       <c r="K11" s="20">
         <v>3.297545246029351</v>
       </c>
       <c r="L11" s="20">
-        <v>-3.018570158890117</v>
+        <v>-3.017781627758584</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.2232019703344966</v>
+        <v>-0.2166080550991883</v>
       </c>
       <c r="N11" s="20">
         <v>13.269938</v>
@@ -4926,10 +4926,10 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="R11" s="12">
-        <v>0.9160219634197087</v>
+        <v>0.9016841185744076</v>
       </c>
       <c r="S11" s="11">
-        <v>59.83336816338346</v>
+        <v>58.8399855691899</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>114</v>
@@ -4949,10 +4949,10 @@
         <v>36</v>
       </c>
       <c r="E12" s="10">
-        <v>543.5250244140625</v>
+        <v>543.4299926757812</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8127835703591179</v>
+        <v>0.8143392336076546</v>
       </c>
       <c r="G12" s="20">
         <v>-0.1018209436010066</v>
@@ -4964,16 +4964,16 @@
         <v>2.17697052724581</v>
       </c>
       <c r="J12" s="20">
-        <v>2.671855168661722</v>
+        <v>2.67886207095234</v>
       </c>
       <c r="K12" s="20">
         <v>1.562626058506958</v>
       </c>
       <c r="L12" s="20">
-        <v>-3.018570158890117</v>
+        <v>-3.017781627758584</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.7336121799167548</v>
+        <v>-0.7410336712485137</v>
       </c>
       <c r="N12" s="20">
         <v>32.783344</v>
@@ -4988,10 +4988,10 @@
         <v>0.577</v>
       </c>
       <c r="R12" s="12">
-        <v>2.178555997462185</v>
+        <v>2.178000248070538</v>
       </c>
       <c r="S12" s="11">
-        <v>54.46231358966153</v>
+        <v>54.44305844702328</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>114</v>
@@ -5011,10 +5011,10 @@
         <v>46</v>
       </c>
       <c r="E13" s="10">
-        <v>389.5150146484375</v>
+        <v>389.4400024414062</v>
       </c>
       <c r="F13" s="17">
-        <v>0.799021038858548</v>
+        <v>0.7996645417937399</v>
       </c>
       <c r="G13" s="20">
         <v>0.63544661477666</v>
@@ -5026,16 +5026,16 @@
         <v>2.432487252480616</v>
       </c>
       <c r="J13" s="20">
-        <v>1.769862998539484</v>
+        <v>1.773961275506885</v>
       </c>
       <c r="K13" s="20">
         <v>0.7528962662486143</v>
       </c>
       <c r="L13" s="20">
-        <v>0.03041539186557292</v>
+        <v>0.03037650563153634</v>
       </c>
       <c r="M13" s="20">
-        <v>-1.122081046853446</v>
+        <v>-1.129376634115772</v>
       </c>
       <c r="N13" s="20">
         <v>13.640207</v>
@@ -5050,10 +5050,10 @@
         <v>0.537</v>
       </c>
       <c r="R13" s="12">
-        <v>0.5563980261312749</v>
+        <v>0.5560982973748247</v>
       </c>
       <c r="S13" s="11">
-        <v>53.70004445072473</v>
+        <v>53.65092869600117</v>
       </c>
       <c r="T13" s="9" t="s">
         <v>114</v>
@@ -5073,10 +5073,10 @@
         <v>57</v>
       </c>
       <c r="E14" s="10">
-        <v>363.1650085449219</v>
+        <v>363.1600036621094</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7481439709710545</v>
+        <v>0.7495196647600424</v>
       </c>
       <c r="G14" s="20">
         <v>1.160842542624806</v>
@@ -5088,16 +5088,16 @@
         <v>-0.379797036716154</v>
       </c>
       <c r="J14" s="20">
-        <v>0.4367321725784516</v>
+        <v>0.4423260264844293</v>
       </c>
       <c r="K14" s="20">
         <v>3.729636424089999</v>
       </c>
       <c r="L14" s="20">
-        <v>0.5375686012483512</v>
+        <v>0.5376909604472081</v>
       </c>
       <c r="M14" s="20">
-        <v>-0.1764344952585491</v>
+        <v>-0.180307044442761</v>
       </c>
       <c r="N14" s="20">
         <v>9.756517000000001</v>
@@ -5112,10 +5112,10 @@
         <v>0.003</v>
       </c>
       <c r="R14" s="12">
-        <v>0.2827501333391973</v>
+        <v>0.2827324553858042</v>
       </c>
       <c r="S14" s="11">
-        <v>44.00694811967168</v>
+        <v>44.00018052901233</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>114</v>
@@ -5135,10 +5135,10 @@
         <v>36</v>
       </c>
       <c r="E15" s="10">
-        <v>204.2230072021484</v>
+        <v>204.4100036621094</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7430037693944536</v>
+        <v>0.7471568606718153</v>
       </c>
       <c r="G15" s="20">
         <v>-0.4407742654660424</v>
@@ -5150,16 +5150,16 @@
         <v>0.4340417055879129</v>
       </c>
       <c r="J15" s="20">
-        <v>1.784211496253286</v>
+        <v>1.799148479019377</v>
       </c>
       <c r="K15" s="20">
         <v>0</v>
       </c>
       <c r="L15" s="20">
-        <v>-0.569616032410216</v>
+        <v>-0.5699179839512446</v>
       </c>
       <c r="M15" s="20">
-        <v>-0.3755668720133269</v>
+        <v>-0.3856700896794154</v>
       </c>
       <c r="N15" s="20">
         <v>28.41031</v>
@@ -5174,10 +5174,10 @@
         <v>0.299</v>
       </c>
       <c r="R15" s="12">
-        <v>1.011848053597937</v>
+        <v>1.01369019895245</v>
       </c>
       <c r="S15" s="11">
-        <v>62.618506073638</v>
+        <v>62.75777975999041</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>114</v>
@@ -5197,10 +5197,10 @@
         <v>36</v>
       </c>
       <c r="E16" s="10">
-        <v>116.2149963378906</v>
+        <v>116.0299987792969</v>
       </c>
       <c r="F16" s="17">
-        <v>0.6890007619364713</v>
+        <v>0.6895505156335534</v>
       </c>
       <c r="G16" s="20">
         <v>-0.8300215284456212</v>
@@ -5212,16 +5212,16 @@
         <v>0.5176902230779757</v>
       </c>
       <c r="J16" s="20">
-        <v>1.978381271612087</v>
+        <v>1.978866110622099</v>
       </c>
       <c r="K16" s="20">
         <v>4.134420649754185</v>
       </c>
       <c r="L16" s="20">
-        <v>-2.656795674589432</v>
+        <v>-2.659328655657073</v>
       </c>
       <c r="M16" s="20">
-        <v>0.5152183444866391</v>
+        <v>0.5221718552133483</v>
       </c>
       <c r="N16" s="20">
         <v>59.648514</v>
@@ -5236,10 +5236,10 @@
         <v>0.254</v>
       </c>
       <c r="R16" s="12">
-        <v>1.694528019008212</v>
+        <v>1.69023871796457</v>
       </c>
       <c r="S16" s="11">
-        <v>58.71757733484527</v>
+        <v>58.52241396970124</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>114</v>
@@ -5262,7 +5262,7 @@
         <v>158.4299926757812</v>
       </c>
       <c r="F17" s="17">
-        <v>0.6708305741248314</v>
+        <v>0.6722788640418077</v>
       </c>
       <c r="G17" s="20">
         <v>0.4643687022637146</v>
@@ -5274,16 +5274,16 @@
         <v>-0.03871237626800461</v>
       </c>
       <c r="J17" s="20">
-        <v>1.041375861417352</v>
+        <v>1.047912131854923</v>
       </c>
       <c r="K17" s="20">
         <v>3.210824496173538</v>
       </c>
       <c r="L17" s="20">
-        <v>0.4238391406000225</v>
+        <v>0.4239862986276916</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.5298031013916128</v>
+        <v>-0.5363208600910532</v>
       </c>
       <c r="N17" s="20">
         <v>16.332987</v>
@@ -5298,10 +5298,10 @@
         <v>0.053</v>
       </c>
       <c r="R17" s="12">
-        <v>0.3447460983994171</v>
+        <v>0.3447460113164478</v>
       </c>
       <c r="S17" s="11">
-        <v>52.51861058331142</v>
+        <v>52.51861058025204</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>114</v>
@@ -5321,10 +5321,10 @@
         <v>46</v>
       </c>
       <c r="E18" s="10">
-        <v>253.2799987792969</v>
+        <v>253.5500030517578</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6586665806459518</v>
+        <v>0.6619889812774012</v>
       </c>
       <c r="G18" s="20">
         <v>0.4452704814464517</v>
@@ -5336,16 +5336,16 @@
         <v>2.40169945735154</v>
       </c>
       <c r="J18" s="20">
-        <v>1.486961817360241</v>
+        <v>1.502023620944271</v>
       </c>
       <c r="K18" s="20">
         <v>0.6707132300480476</v>
       </c>
       <c r="L18" s="20">
-        <v>0.303592191751834</v>
+        <v>0.3052937841421062</v>
       </c>
       <c r="M18" s="20">
-        <v>-1.000234016465102</v>
+        <v>-1.016461966304801</v>
       </c>
       <c r="N18" s="20">
         <v>14.597602</v>
@@ -5360,10 +5360,10 @@
         <v>0.531</v>
       </c>
       <c r="R18" s="12">
-        <v>0.3621886526501239</v>
+        <v>0.3636407876702044</v>
       </c>
       <c r="S18" s="11">
-        <v>52.18044228058604</v>
+        <v>52.4939899388571</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>114</v>
@@ -5383,10 +5383,10 @@
         <v>61</v>
       </c>
       <c r="E19" s="10">
-        <v>62.27830123901367</v>
+        <v>62.52999877929688</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6438252134936931</v>
+        <v>0.651133014263879</v>
       </c>
       <c r="G19" s="20">
         <v>1.236177102540873</v>
@@ -5398,16 +5398,16 @@
         <v>-0.5828068382546813</v>
       </c>
       <c r="J19" s="20">
-        <v>0.7765090107657754</v>
+        <v>0.8086146556923782</v>
       </c>
       <c r="K19" s="20">
         <v>4.134420649754185</v>
       </c>
       <c r="L19" s="20">
-        <v>0.001827206151417</v>
+        <v>-0.001475079253704801</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.3764831454316215</v>
+        <v>-0.4030550902252177</v>
       </c>
       <c r="N19" s="20">
         <v>11.559979</v>
@@ -5422,10 +5422,10 @@
         <v>0.046</v>
       </c>
       <c r="R19" s="12">
-        <v>0.9461969137191772</v>
+        <v>0.9540624618530273</v>
       </c>
       <c r="S19" s="11">
-        <v>41.34623597454802</v>
+        <v>42.30704970653467</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>114</v>
@@ -5445,10 +5445,10 @@
         <v>36</v>
       </c>
       <c r="E20" s="10">
-        <v>228.0800018310547</v>
+        <v>227.2700042724609</v>
       </c>
       <c r="F20" s="17">
-        <v>0.638561523280782</v>
+        <v>0.634220662878726</v>
       </c>
       <c r="G20" s="20">
         <v>0.4118301704600924</v>
@@ -5460,16 +5460,16 @@
         <v>0.1953152078062003</v>
       </c>
       <c r="J20" s="20">
-        <v>0.8024628040201901</v>
+        <v>0.7850496562480861</v>
       </c>
       <c r="K20" s="20">
         <v>3.439222750154254</v>
       </c>
       <c r="L20" s="20">
-        <v>-1.801014910229202</v>
+        <v>-1.805796136461388</v>
       </c>
       <c r="M20" s="20">
-        <v>-1.080219509304337</v>
+        <v>-1.065595040510507</v>
       </c>
       <c r="N20" s="20">
         <v>21.410795</v>
@@ -5484,10 +5484,10 @@
         <v>0.108</v>
       </c>
       <c r="R20" s="12">
-        <v>0.2807087065515095</v>
+        <v>0.2761603206515848</v>
       </c>
       <c r="S20" s="11">
-        <v>46.00833582155431</v>
+        <v>45.47939376335544</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>114</v>
@@ -5507,10 +5507,10 @@
         <v>127</v>
       </c>
       <c r="E21" s="10">
-        <v>246.0249938964844</v>
+        <v>246.1499938964844</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6121263867209685</v>
+        <v>0.6142383425810742</v>
       </c>
       <c r="G21" s="20">
         <v>-0.01172638762890057</v>
@@ -5522,16 +5522,16 @@
         <v>1.021835496573962</v>
       </c>
       <c r="J21" s="20">
-        <v>0.0378713451723798</v>
+        <v>0.04617228617693294</v>
       </c>
       <c r="K21" s="20">
         <v>4.134420649754185</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4431233183336993</v>
+        <v>-0.4422790846574162</v>
       </c>
       <c r="M21" s="20">
-        <v>0.07188917239300779</v>
+        <v>0.06652691662004269</v>
       </c>
       <c r="N21" s="20">
         <v>20.08608</v>
@@ -5546,10 +5546,10 @@
         <v>0.196</v>
       </c>
       <c r="R21" s="12">
-        <v>0.2341978449696593</v>
+        <v>0.2348249143099643</v>
       </c>
       <c r="S21" s="11">
-        <v>41.13582944932801</v>
+        <v>41.24381199131362</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>114</v>
@@ -5569,10 +5569,10 @@
         <v>61</v>
       </c>
       <c r="E22" s="10">
-        <v>270.4400024414062</v>
+        <v>271.8999938964844</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6077138057281105</v>
+        <v>0.6095667026960693</v>
       </c>
       <c r="G22" s="20">
         <v>-0.7382512714864492</v>
@@ -5584,16 +5584,16 @@
         <v>-0.4590192885594346</v>
       </c>
       <c r="J22" s="20">
-        <v>2.671659013794631</v>
+        <v>2.683798299504477</v>
       </c>
       <c r="K22" s="20">
         <v>-0.268593496587877</v>
       </c>
       <c r="L22" s="20">
-        <v>-0.8100559480268301</v>
+        <v>-0.8089347861230161</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.062496923740188</v>
+        <v>-0.08569890448048412</v>
       </c>
       <c r="N22" s="20">
         <v>50.27933</v>
@@ -5608,10 +5608,10 @@
         <v>0.094</v>
       </c>
       <c r="R22" s="12">
-        <v>1.298291889604014</v>
+        <v>1.31069939770121</v>
       </c>
       <c r="S22" s="11">
-        <v>73.83091183080094</v>
+        <v>74.25138551502383</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>114</v>
@@ -5622,58 +5622,58 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E23" s="10">
-        <v>125.9800033569336</v>
+        <v>56.09999847412109</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5986779441629044</v>
+        <v>0.5895029110295</v>
       </c>
       <c r="G23" s="20">
-        <v>0.3123085537627329</v>
+        <v>0.5909946933403921</v>
       </c>
       <c r="H23" s="20">
-        <v>0.5059193760536828</v>
+        <v>0.6147531683208749</v>
       </c>
       <c r="I23" s="20">
-        <v>0.5162516055283453</v>
+        <v>2.900414534129918</v>
       </c>
       <c r="J23" s="20">
-        <v>0.7715216541627893</v>
+        <v>0.06091150674024351</v>
       </c>
       <c r="K23" s="20">
-        <v>1.603465481404173</v>
+        <v>0.8900360567182717</v>
       </c>
       <c r="L23" s="20">
-        <v>0.2875881870937351</v>
+        <v>0.05235451453716362</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.3904687684846619</v>
+        <v>-0.4187142977074728</v>
       </c>
       <c r="N23" s="20">
-        <v>15.782166</v>
+        <v>16.772861</v>
       </c>
       <c r="O23" s="20">
-        <v>3.9245436</v>
+        <v>1.6988854</v>
       </c>
       <c r="P23" s="12">
-        <v>0.30667</v>
+        <v>0.10629</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.377</v>
+        <v>0.534</v>
       </c>
       <c r="R23" s="12">
-        <v>0.3951273432928331</v>
+        <v>-0.1332251289941264</v>
       </c>
       <c r="S23" s="11">
-        <v>53.53564251197643</v>
+        <v>39.51398136006124</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>114</v>
@@ -5684,58 +5684,58 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E24" s="10">
-        <v>56.16500091552734</v>
+        <v>124.8199996948242</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5902033476669435</v>
+        <v>0.5876604509647237</v>
       </c>
       <c r="G24" s="20">
-        <v>0.5909946933403921</v>
+        <v>0.3123085537627329</v>
       </c>
       <c r="H24" s="20">
-        <v>0.6147531683208749</v>
+        <v>0.5059193760536828</v>
       </c>
       <c r="I24" s="20">
-        <v>2.900414534129918</v>
+        <v>0.5162516055283453</v>
       </c>
       <c r="J24" s="20">
-        <v>0.06267905441964601</v>
+        <v>0.7171013416066088</v>
       </c>
       <c r="K24" s="20">
-        <v>0.8900360567182717</v>
+        <v>1.603465481404173</v>
       </c>
       <c r="L24" s="20">
-        <v>0.05360632121206992</v>
+        <v>0.2972086802441086</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.4175259985433694</v>
+        <v>-0.3313266312390235</v>
       </c>
       <c r="N24" s="20">
-        <v>16.772861</v>
+        <v>15.782166</v>
       </c>
       <c r="O24" s="20">
-        <v>1.6988854</v>
+        <v>3.9245436</v>
       </c>
       <c r="P24" s="12">
-        <v>0.10629</v>
+        <v>0.30667</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.534</v>
+        <v>0.377</v>
       </c>
       <c r="R24" s="12">
-        <v>-0.1322208066358832</v>
+        <v>0.3822812345120339</v>
       </c>
       <c r="S24" s="11">
-        <v>39.71509370215241</v>
+        <v>51.11266140963532</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>114</v>
@@ -5755,10 +5755,10 @@
         <v>36</v>
       </c>
       <c r="E25" s="10">
-        <v>229.6450042724609</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5856027054764036</v>
+        <v>0.58154151137038</v>
       </c>
       <c r="G25" s="20">
         <v>-1.098910330048646</v>
@@ -5770,16 +5770,16 @@
         <v>2.414157689348599</v>
       </c>
       <c r="J25" s="20">
-        <v>0.8153146239200062</v>
+        <v>0.7989918250233137</v>
       </c>
       <c r="K25" s="20">
         <v>-0.3018700633930144</v>
       </c>
       <c r="L25" s="20">
-        <v>-0.2574216305985803</v>
+        <v>-0.2531108904403336</v>
       </c>
       <c r="M25" s="20">
-        <v>-0.3800091858966296</v>
+        <v>-0.3727966714780135</v>
       </c>
       <c r="N25" s="20">
         <v>28.489874</v>
@@ -5794,10 +5794,10 @@
         <v>1.059</v>
       </c>
       <c r="R25" s="12">
-        <v>0.3739847700558896</v>
+        <v>0.3692879041816017</v>
       </c>
       <c r="S25" s="11">
-        <v>59.42871845799364</v>
+        <v>58.77557026474965</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>114</v>
@@ -5817,10 +5817,10 @@
         <v>61</v>
       </c>
       <c r="E26" s="10">
-        <v>229.3300018310547</v>
+        <v>228.6900024414062</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5548323425472482</v>
+        <v>0.5529894498470236</v>
       </c>
       <c r="G26" s="20">
         <v>0.1826167294586985</v>
@@ -5832,16 +5832,16 @@
         <v>-0.8979974000351455</v>
       </c>
       <c r="J26" s="20">
-        <v>0.8502106931837119</v>
+        <v>0.8418996128055922</v>
       </c>
       <c r="K26" s="20">
         <v>3.288974009124997</v>
       </c>
       <c r="L26" s="20">
-        <v>-0.03921277930864753</v>
+        <v>-0.03784150713372107</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.5001655952444399</v>
+        <v>-0.4930636567104923</v>
       </c>
       <c r="N26" s="20">
         <v>40.498222</v>
@@ -5856,10 +5856,10 @@
         <v>0.034</v>
       </c>
       <c r="R26" s="12">
-        <v>0.2474434638779868</v>
+        <v>0.2439621790520661</v>
       </c>
       <c r="S26" s="11">
-        <v>64.47776791287792</v>
+        <v>63.86767526487981</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>114</v>
@@ -5879,10 +5879,10 @@
         <v>36</v>
       </c>
       <c r="E27" s="10">
-        <v>371.9500122070312</v>
+        <v>371.8699951171875</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5509353815118355</v>
+        <v>0.5522508240568881</v>
       </c>
       <c r="G27" s="20">
         <v>0.08345580963657841</v>
@@ -5894,16 +5894,16 @@
         <v>0.4617856253832925</v>
       </c>
       <c r="J27" s="20">
-        <v>1.582924338066536</v>
+        <v>1.589099450015377</v>
       </c>
       <c r="K27" s="20">
         <v>1.661447378110094</v>
       </c>
       <c r="L27" s="20">
-        <v>-1.826749066100682</v>
+        <v>-1.826147220619802</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.4563644730486376</v>
+        <v>-0.4635294951542942</v>
       </c>
       <c r="N27" s="20">
         <v>33.886448</v>
@@ -5918,10 +5918,10 @@
         <v>0.204</v>
       </c>
       <c r="R27" s="12">
-        <v>0.8355211869687351</v>
+        <v>0.8351263138435636</v>
       </c>
       <c r="S27" s="11">
-        <v>62.77985356632021</v>
+        <v>62.74203964815953</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>114</v>
@@ -5941,10 +5941,10 @@
         <v>66</v>
       </c>
       <c r="E28" s="10">
-        <v>116.1050033569336</v>
+        <v>116.0199966430664</v>
       </c>
       <c r="F28" s="17">
-        <v>0.547516923596962</v>
+        <v>0.5478825115378305</v>
       </c>
       <c r="G28" s="20">
         <v>0.4073104247281907</v>
@@ -5956,16 +5956,16 @@
         <v>0.4715191624753287</v>
       </c>
       <c r="J28" s="20">
-        <v>-0.2099706958499017</v>
+        <v>-0.2093850352645275</v>
       </c>
       <c r="K28" s="20">
         <v>4.134420649754185</v>
       </c>
       <c r="L28" s="20">
-        <v>0.1214883981928092</v>
+        <v>0.1228785056741809</v>
       </c>
       <c r="M28" s="20">
-        <v>0.08125706136794154</v>
+        <v>0.0825881028226164</v>
       </c>
       <c r="N28" s="20">
         <v>13.979167</v>
@@ -5980,10 +5980,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="R28" s="12">
-        <v>0.08509348931713645</v>
+        <v>0.08429903404734951</v>
       </c>
       <c r="S28" s="11">
-        <v>42.96845385096077</v>
+        <v>42.79219288276566</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>114</v>
@@ -6003,10 +6003,10 @@
         <v>36</v>
       </c>
       <c r="E29" s="10">
-        <v>176.8558959960938</v>
+        <v>176.3300018310547</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5136304991156163</v>
+        <v>0.5095764165662345</v>
       </c>
       <c r="G29" s="20">
         <v>-1.991192966399809</v>
@@ -6018,16 +6018,16 @@
         <v>0.2259855872354321</v>
       </c>
       <c r="J29" s="20">
-        <v>1.925527408829443</v>
+        <v>1.911313265040892</v>
       </c>
       <c r="K29" s="20">
         <v>0.4226515502279323</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.7150775070228708</v>
+        <v>-0.711695549801433</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.2442544927865698</v>
+        <v>-0.2441639533628555</v>
       </c>
       <c r="N29" s="20">
         <v>61.29329</v>
@@ -6042,10 +6042,10 @@
         <v>0.256</v>
       </c>
       <c r="R29" s="12">
-        <v>1.261584436034549</v>
+        <v>1.254859446449356</v>
       </c>
       <c r="S29" s="11">
-        <v>60.54838492027917</v>
+        <v>60.11644167561602</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>114</v>
@@ -6062,52 +6062,52 @@
         <v>139</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="E30" s="10">
-        <v>927.9199829101562</v>
+        <v>63.88000106811523</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4660353783280584</v>
+        <v>0.4569664458755423</v>
       </c>
       <c r="G30" s="20">
-        <v>-2.057025624567463</v>
+        <v>0.4625864400742329</v>
       </c>
       <c r="H30" s="20">
-        <v>1.679533116257016</v>
+        <v>0.6588490782651485</v>
       </c>
       <c r="I30" s="20">
-        <v>1.336500578238815</v>
+        <v>0.2249472925442899</v>
       </c>
       <c r="J30" s="20">
-        <v>1.891627563090635</v>
+        <v>0.4698882554579958</v>
       </c>
       <c r="K30" s="20">
-        <v>-0.002885152552916025</v>
+        <v>0.7861728330537516</v>
       </c>
       <c r="L30" s="20">
-        <v>-2.633566528131504</v>
+        <v>0.6729435427886399</v>
       </c>
       <c r="M30" s="20">
-        <v>0.3099571924030959</v>
+        <v>-0.3736690535729966</v>
       </c>
       <c r="N30" s="20">
-        <v>65.76973</v>
+        <v>13.845816</v>
       </c>
       <c r="O30" s="20">
-        <v>95.9529</v>
+        <v>5.7537756</v>
       </c>
       <c r="P30" s="12">
-        <v>3.7152898</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.485</v>
+        <v>0.057</v>
       </c>
       <c r="R30" s="12">
-        <v>1.445144191226068</v>
+        <v>0.1149161833418366</v>
       </c>
       <c r="S30" s="11">
-        <v>59.95407896820135</v>
+        <v>50.28693602196861</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>114</v>
@@ -6124,52 +6124,52 @@
         <v>141</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E31" s="10">
-        <v>63.77000045776367</v>
+        <v>921.510009765625</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4539940047823754</v>
+        <v>0.4540283666719393</v>
       </c>
       <c r="G31" s="20">
-        <v>0.4625864400742329</v>
+        <v>-2.057025624567463</v>
       </c>
       <c r="H31" s="20">
-        <v>0.6588490782651485</v>
+        <v>1.679533116257016</v>
       </c>
       <c r="I31" s="20">
-        <v>0.2249472925442899</v>
+        <v>1.336500578238815</v>
       </c>
       <c r="J31" s="20">
-        <v>0.4534791032858085</v>
+        <v>1.850153369070178</v>
       </c>
       <c r="K31" s="20">
-        <v>0.7861728330537516</v>
+        <v>-0.002885152552916025</v>
       </c>
       <c r="L31" s="20">
-        <v>0.6755616529343835</v>
+        <v>-2.631270450194496</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.3512538292011881</v>
+        <v>0.3136757158255622</v>
       </c>
       <c r="N31" s="20">
-        <v>13.845816</v>
+        <v>65.76973</v>
       </c>
       <c r="O31" s="20">
-        <v>5.7537756</v>
+        <v>95.9529</v>
       </c>
       <c r="P31" s="12">
-        <v>0.46598998</v>
+        <v>3.7152898</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.057</v>
+        <v>0.485</v>
       </c>
       <c r="R31" s="12">
-        <v>0.1129963107900553</v>
+        <v>1.428253393647692</v>
       </c>
       <c r="S31" s="11">
-        <v>49.72559642745656</v>
+        <v>59.19925314731145</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>114</v>
@@ -6186,52 +6186,52 @@
         <v>143</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E32" s="10">
-        <v>30.86499977111816</v>
+        <v>401.2999877929688</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4416691599546687</v>
+        <v>0.4451083997660897</v>
       </c>
       <c r="G32" s="20">
-        <v>-0.05525750799347566</v>
+        <v>-1.18924796979833</v>
       </c>
       <c r="H32" s="20">
-        <v>-1.002892332074208</v>
+        <v>0.5645521718938252</v>
       </c>
       <c r="I32" s="20">
-        <v>-1.204760955881624</v>
+        <v>3.655490679943009</v>
       </c>
       <c r="J32" s="20">
-        <v>0.8371098194066106</v>
+        <v>0.9689918581542987</v>
       </c>
       <c r="K32" s="20">
-        <v>4.134420649754185</v>
+        <v>0.4100467900744712</v>
       </c>
       <c r="L32" s="20">
-        <v>0.5097750836511118</v>
+        <v>-2.838383011987505</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.5661943587252758</v>
+        <v>0.4211928412062529</v>
       </c>
       <c r="N32" s="20">
-        <v>495.98203</v>
+        <v>54.647465</v>
       </c>
       <c r="O32" s="20">
-        <v>2.3569846</v>
+        <v>19.836678</v>
       </c>
       <c r="P32" s="12">
-        <v>-0.08785999999999999</v>
+        <v>0.36465</v>
       </c>
       <c r="Q32" s="12">
-        <v>-0.112</v>
+        <v>1.039</v>
       </c>
       <c r="R32" s="12">
-        <v>0.1401920989684957</v>
+        <v>0.3585662742054512</v>
       </c>
       <c r="S32" s="11">
-        <v>75.46657005707851</v>
+        <v>58.84165473708767</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>114</v>
@@ -6248,52 +6248,52 @@
         <v>145</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E33" s="10">
-        <v>399.260009765625</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4340852820575317</v>
+        <v>0.4436980367291792</v>
       </c>
       <c r="G33" s="20">
-        <v>-1.18924796979833</v>
+        <v>-0.05525750799347566</v>
       </c>
       <c r="H33" s="20">
-        <v>0.5645521718938252</v>
+        <v>-1.002892332074208</v>
       </c>
       <c r="I33" s="20">
-        <v>3.655490679943009</v>
+        <v>-1.204760955881624</v>
       </c>
       <c r="J33" s="20">
-        <v>0.9298439080412395</v>
+        <v>0.8499422660647392</v>
       </c>
       <c r="K33" s="20">
-        <v>0.4100467900744712</v>
+        <v>4.134420649754185</v>
       </c>
       <c r="L33" s="20">
-        <v>-2.838770508056338</v>
+        <v>0.5101380742742394</v>
       </c>
       <c r="M33" s="20">
-        <v>0.4304993048248728</v>
+        <v>-0.5892273169792235</v>
       </c>
       <c r="N33" s="20">
-        <v>54.647465</v>
+        <v>495.98203</v>
       </c>
       <c r="O33" s="20">
-        <v>19.836678</v>
+        <v>2.3569846</v>
       </c>
       <c r="P33" s="12">
-        <v>0.36465</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q33" s="12">
-        <v>1.039</v>
+        <v>-0.112</v>
       </c>
       <c r="R33" s="12">
-        <v>0.351660105672251</v>
+        <v>0.1414850375649745</v>
       </c>
       <c r="S33" s="11">
-        <v>58.33701597271295</v>
+        <v>75.68193322667111</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>114</v>
@@ -6313,10 +6313,10 @@
         <v>61</v>
       </c>
       <c r="E34" s="10">
-        <v>442.8150024414062</v>
+        <v>442.9400024414062</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4324574127476602</v>
+        <v>0.4341556810337562</v>
       </c>
       <c r="G34" s="20">
         <v>-0.9301946228299454</v>
@@ -6328,16 +6328,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J34" s="20">
-        <v>1.150081896455197</v>
+        <v>1.158681987005308</v>
       </c>
       <c r="K34" s="20">
         <v>-0.5413605063087762</v>
       </c>
       <c r="L34" s="20">
-        <v>0.5692856352423001</v>
+        <v>0.5688221537960026</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.6763350783444144</v>
+        <v>-0.6870094532464075</v>
       </c>
       <c r="N34" s="20">
         <v>109.756966</v>
@@ -6352,10 +6352,10 @@
         <v>1.134</v>
       </c>
       <c r="R34" s="12">
-        <v>0.5313839979018902</v>
+        <v>0.5318162845197381</v>
       </c>
       <c r="S34" s="11">
-        <v>68.59537416948298</v>
+        <v>68.64760432431193</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>114</v>
@@ -6375,10 +6375,10 @@
         <v>61</v>
       </c>
       <c r="E35" s="10">
-        <v>1189.619995117188</v>
+        <v>1184.780029296875</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4209411778353496</v>
+        <v>0.4177439815420458</v>
       </c>
       <c r="G35" s="20">
         <v>-1.110237185891371</v>
@@ -6390,16 +6390,16 @@
         <v>0.7254634342718127</v>
       </c>
       <c r="J35" s="20">
-        <v>0.5077776363257624</v>
+        <v>0.4881829362998821</v>
       </c>
       <c r="K35" s="20">
         <v>0.7624758839652448</v>
       </c>
       <c r="L35" s="20">
-        <v>0.3789378606437047</v>
+        <v>0.3804182993161547</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.08483738978026956</v>
+        <v>-0.05243254735385355</v>
       </c>
       <c r="N35" s="20">
         <v>39.686787</v>
@@ -6414,10 +6414,10 @@
         <v>0.477</v>
       </c>
       <c r="R35" s="12">
-        <v>0.3588261076926391</v>
+        <v>0.353297727248485</v>
       </c>
       <c r="S35" s="11">
-        <v>57.34612121888821</v>
+        <v>56.10746417685041</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>114</v>
@@ -6428,58 +6428,58 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>43</v>
+        <v>151</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E36" s="10">
-        <v>457.5499877929688</v>
+        <v>206.3699951171875</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4066842730473901</v>
+        <v>0.4050379680416604</v>
       </c>
       <c r="G36" s="20">
-        <v>-0.8384379108839474</v>
+        <v>0.4853183280948471</v>
       </c>
       <c r="H36" s="20">
-        <v>2.151739124777599</v>
+        <v>-0.3300127972283673</v>
       </c>
       <c r="I36" s="20">
-        <v>2.646453673822382</v>
+        <v>2.301619691710589</v>
       </c>
       <c r="J36" s="20">
-        <v>0.3887841033340503</v>
+        <v>0.5649244781974105</v>
       </c>
       <c r="K36" s="20">
-        <v>-0.2156535039433402</v>
+        <v>-0.1667470345479109</v>
       </c>
       <c r="L36" s="20">
-        <v>-3.018570158890117</v>
+        <v>0.7639120797299145</v>
       </c>
       <c r="M36" s="20">
-        <v>0.4879608583279895</v>
+        <v>-0.6872709590900115</v>
       </c>
       <c r="N36" s="20">
-        <v>16.975473</v>
+        <v>19.639769</v>
       </c>
       <c r="O36" s="20">
-        <v>22.350464</v>
+        <v>2.1120868</v>
       </c>
       <c r="P36" s="12">
-        <v>1.30853</v>
+        <v>0.12231</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.438</v>
+        <v>0.535</v>
       </c>
       <c r="R36" s="12">
-        <v>0.6627305870383517</v>
+        <v>-0.005078309454742191</v>
       </c>
       <c r="S36" s="11">
-        <v>49.84296289253164</v>
+        <v>51.20657389401402</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>114</v>
@@ -6490,19 +6490,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D37" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="10">
-        <v>196.9450073242188</v>
+        <v>196.4600067138672</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4047292037353874</v>
+        <v>0.402290247644652</v>
       </c>
       <c r="G37" s="20">
         <v>0.59238818351296</v>
@@ -6514,16 +6514,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J37" s="20">
-        <v>-0.3831857575293212</v>
+        <v>-0.3923388983499679</v>
       </c>
       <c r="K37" s="20">
         <v>0.5870176226290656</v>
       </c>
       <c r="L37" s="20">
-        <v>0.5101519073990183</v>
+        <v>0.5060161277592696</v>
       </c>
       <c r="M37" s="20">
-        <v>0.09907253315335429</v>
+        <v>0.1060116948263984</v>
       </c>
       <c r="N37" s="20">
         <v>11.024229</v>
@@ -6538,10 +6538,10 @@
         <v>11.11</v>
       </c>
       <c r="R37" s="12">
-        <v>0.1271372137791889</v>
+        <v>0.124361503726621</v>
       </c>
       <c r="S37" s="11">
-        <v>35.63484053806768</v>
+        <v>35.16621525115819</v>
       </c>
       <c r="T37" s="9" t="s">
         <v>114</v>
@@ -6552,58 +6552,58 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>153</v>
+        <v>43</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E38" s="10">
-        <v>205.8549957275391</v>
+        <v>453.2300109863281</v>
       </c>
       <c r="F38" s="17">
-        <v>0.4008023788220942</v>
+        <v>0.3949353172240869</v>
       </c>
       <c r="G38" s="20">
-        <v>0.4853183280948471</v>
+        <v>-0.8384379108839474</v>
       </c>
       <c r="H38" s="20">
-        <v>-0.3300127972283673</v>
+        <v>2.151739124777599</v>
       </c>
       <c r="I38" s="20">
-        <v>2.301619691710589</v>
+        <v>2.646453673822382</v>
       </c>
       <c r="J38" s="20">
-        <v>0.5427166184456972</v>
+        <v>0.3464626300875213</v>
       </c>
       <c r="K38" s="20">
-        <v>-0.1667470345479109</v>
+        <v>-0.2156535039433402</v>
       </c>
       <c r="L38" s="20">
-        <v>0.7652147627798236</v>
+        <v>-3.017781627758584</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.6579133625530958</v>
+        <v>0.4992130368625332</v>
       </c>
       <c r="N38" s="20">
-        <v>19.639769</v>
+        <v>16.975473</v>
       </c>
       <c r="O38" s="20">
-        <v>2.1120868</v>
+        <v>22.350464</v>
       </c>
       <c r="P38" s="12">
-        <v>0.12231</v>
+        <v>1.30853</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.535</v>
+        <v>0.438</v>
       </c>
       <c r="R38" s="12">
-        <v>-0.007561224326154692</v>
+        <v>0.6470316659633728</v>
       </c>
       <c r="S38" s="11">
-        <v>50.41487690065946</v>
+        <v>48.70413616151452</v>
       </c>
       <c r="T38" s="9" t="s">
         <v>114</v>
@@ -6614,58 +6614,58 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>154</v>
+        <v>14</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E39" s="10">
-        <v>175.5899963378906</v>
+        <v>227.5500030517578</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3959957828617787</v>
+        <v>0.3937367775139732</v>
       </c>
       <c r="G39" s="20">
-        <v>-0.2374479080738863</v>
+        <v>1.23099937351617</v>
       </c>
       <c r="H39" s="20">
-        <v>0.1553448042906527</v>
+        <v>0.1667435013429619</v>
       </c>
       <c r="I39" s="20">
-        <v>-0.4072863312933673</v>
+        <v>-0.05584647993229746</v>
       </c>
       <c r="J39" s="20">
-        <v>1.542886067077079</v>
+        <v>-0.2684847993969363</v>
       </c>
       <c r="K39" s="20">
-        <v>-0.1581757976435574</v>
+        <v>1.809175167108658</v>
       </c>
       <c r="L39" s="20">
-        <v>0.4356010535850259</v>
+        <v>0.402405230693198</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.1926364607885975</v>
+        <v>-0.1204664502016454</v>
       </c>
       <c r="N39" s="20">
-        <v>34.14822</v>
+        <v>4.5574694</v>
       </c>
       <c r="O39" s="20">
-        <v>6.61701</v>
+        <v>1.8238496</v>
       </c>
       <c r="P39" s="12">
-        <v>0.20971</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.081</v>
+        <v>0.118</v>
       </c>
       <c r="R39" s="12">
-        <v>0.599502557752186</v>
+        <v>0.1331496207603819</v>
       </c>
       <c r="S39" s="11">
-        <v>77.0049965636023</v>
+        <v>27.9348560686997</v>
       </c>
       <c r="T39" s="9" t="s">
         <v>114</v>
@@ -6676,58 +6676,58 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>158</v>
+        <v>57</v>
       </c>
       <c r="E40" s="10">
-        <v>265.3800048828125</v>
+        <v>916.280029296875</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3945488872779208</v>
+        <v>0.3936655234981025</v>
       </c>
       <c r="G40" s="20">
-        <v>-3.850609330339901</v>
+        <v>0.4149604359308066</v>
       </c>
       <c r="H40" s="20">
-        <v>-0.4558428702845563</v>
+        <v>0.8229528906242468</v>
       </c>
       <c r="I40" s="20">
-        <v>4.097268549112698</v>
+        <v>0.9059327383427908</v>
       </c>
       <c r="J40" s="20">
-        <v>1.571168978170827</v>
+        <v>-0.3462979381971125</v>
       </c>
       <c r="K40" s="20">
-        <v>4.017529145995051</v>
+        <v>1.619599574400603</v>
       </c>
       <c r="L40" s="20">
-        <v>-3.018570158890117</v>
+        <v>-0.07743877165552872</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.2684176295485651</v>
+        <v>0.1361333440848979</v>
       </c>
       <c r="N40" s="20">
-        <v>384.93335</v>
+        <v>14.451568</v>
       </c>
       <c r="O40" s="20">
-        <v>52.538673</v>
+        <v>2.5837662</v>
       </c>
       <c r="P40" s="12">
-        <v>0.22213</v>
+        <v>0.16902</v>
       </c>
       <c r="Q40" s="12">
-        <v>1.655</v>
+        <v>0.425</v>
       </c>
       <c r="R40" s="12">
-        <v>0.991744175486603</v>
+        <v>0.1518708779153592</v>
       </c>
       <c r="S40" s="11">
-        <v>53.55319536339297</v>
+        <v>33.11340497456116</v>
       </c>
       <c r="T40" s="9" t="s">
         <v>114</v>
@@ -6738,58 +6738,58 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E41" s="10">
-        <v>916.4749755859375</v>
+        <v>175.2100067138672</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3927788102553957</v>
+        <v>0.3920734652803153</v>
       </c>
       <c r="G41" s="20">
-        <v>0.4149604359308066</v>
+        <v>-0.2374479080738863</v>
       </c>
       <c r="H41" s="20">
-        <v>0.8229528906242468</v>
+        <v>0.1553448042906527</v>
       </c>
       <c r="I41" s="20">
-        <v>0.9059327383427908</v>
+        <v>-0.4072863312933673</v>
       </c>
       <c r="J41" s="20">
-        <v>-0.3495608311282122</v>
+        <v>1.538382486132149</v>
       </c>
       <c r="K41" s="20">
-        <v>1.619599574400603</v>
+        <v>-0.1581757976435574</v>
       </c>
       <c r="L41" s="20">
-        <v>-0.07737643281161549</v>
+        <v>0.4379489276455764</v>
       </c>
       <c r="M41" s="20">
-        <v>0.1372385229097522</v>
+        <v>-0.2265379075588161</v>
       </c>
       <c r="N41" s="20">
-        <v>14.451568</v>
+        <v>34.14822</v>
       </c>
       <c r="O41" s="20">
-        <v>2.5837662</v>
+        <v>6.61701</v>
       </c>
       <c r="P41" s="12">
-        <v>0.16902</v>
+        <v>0.20971</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.425</v>
+        <v>0.081</v>
       </c>
       <c r="R41" s="12">
-        <v>0.1521159481405623</v>
+        <v>0.5960411169627278</v>
       </c>
       <c r="S41" s="11">
-        <v>33.14434947562151</v>
+        <v>76.76883688667752</v>
       </c>
       <c r="T41" s="9" t="s">
         <v>114</v>
@@ -6800,58 +6800,58 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>14</v>
+        <v>158</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E42" s="10">
-        <v>227.5449981689453</v>
+        <v>418.1300048828125</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3924840923347749</v>
+        <v>0.3770853258882171</v>
       </c>
       <c r="G42" s="20">
-        <v>1.23099937351617</v>
+        <v>-0.2196120997092874</v>
       </c>
       <c r="H42" s="20">
-        <v>0.1667435013429619</v>
+        <v>1.242182663983196</v>
       </c>
       <c r="I42" s="20">
-        <v>-0.05584647993229746</v>
+        <v>-0.09888920711276358</v>
       </c>
       <c r="J42" s="20">
-        <v>-0.2729983677486673</v>
+        <v>0.7708716588010035</v>
       </c>
       <c r="K42" s="20">
-        <v>1.809175167108658</v>
+        <v>-0.008935437426577335</v>
       </c>
       <c r="L42" s="20">
-        <v>0.4022560131684436</v>
+        <v>0.1143779289087324</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.1190872204790662</v>
+        <v>-0.1162090321722734</v>
       </c>
       <c r="N42" s="20">
-        <v>4.5574694</v>
+        <v>25.768177</v>
       </c>
       <c r="O42" s="20">
-        <v>1.8238496</v>
+        <v>19.177149</v>
       </c>
       <c r="P42" s="12">
-        <v>0.46113998</v>
+        <v>0.91473</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.118</v>
+        <v>0.095</v>
       </c>
       <c r="R42" s="12">
-        <v>0.133124697530389</v>
+        <v>0.214982648658705</v>
       </c>
       <c r="S42" s="11">
-        <v>27.93182429426359</v>
+        <v>58.26064928131711</v>
       </c>
       <c r="T42" s="9" t="s">
         <v>114</v>
@@ -6862,58 +6862,58 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C43" s="9" t="s">
+      <c r="D43" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="D43" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="E43" s="10">
-        <v>418.9200134277344</v>
+        <v>262.8699951171875</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3786226326188501</v>
+        <v>0.3767724079725336</v>
       </c>
       <c r="G43" s="20">
-        <v>-0.2196120997092874</v>
+        <v>-3.850609330339901</v>
       </c>
       <c r="H43" s="20">
-        <v>1.242182663983196</v>
+        <v>-0.4558428702845563</v>
       </c>
       <c r="I43" s="20">
-        <v>-0.09888920711276358</v>
+        <v>4.097268549112698</v>
       </c>
       <c r="J43" s="20">
-        <v>0.7768993099787701</v>
+        <v>1.514626221301193</v>
       </c>
       <c r="K43" s="20">
-        <v>-0.008935437426577335</v>
+        <v>4.017529145995051</v>
       </c>
       <c r="L43" s="20">
-        <v>0.1129790025485551</v>
+        <v>-3.017781627758584</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.1185471951858539</v>
+        <v>-0.2791796809534242</v>
       </c>
       <c r="N43" s="20">
-        <v>25.768177</v>
+        <v>384.93335</v>
       </c>
       <c r="O43" s="20">
-        <v>19.177149</v>
+        <v>52.538673</v>
       </c>
       <c r="P43" s="12">
-        <v>0.91473</v>
+        <v>0.22213</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.095</v>
+        <v>1.655</v>
       </c>
       <c r="R43" s="12">
-        <v>0.2172783265526801</v>
+        <v>0.9729059162390545</v>
       </c>
       <c r="S43" s="11">
-        <v>58.6262601877475</v>
+        <v>52.71776508782204</v>
       </c>
       <c r="T43" s="9" t="s">
         <v>114</v>
@@ -6930,52 +6930,52 @@
         <v>164</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="E44" s="10">
-        <v>359.5350036621094</v>
+        <v>151.0200042724609</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3661492842212424</v>
+        <v>0.369790550716444</v>
       </c>
       <c r="G44" s="20">
-        <v>-0.5841071338335053</v>
+        <v>-0.2351435193636175</v>
       </c>
       <c r="H44" s="20">
-        <v>0.2793198048091971</v>
+        <v>-0.3192964222125583</v>
       </c>
       <c r="I44" s="20">
-        <v>0.8280381860846351</v>
+        <v>-0.6222982617295744</v>
       </c>
       <c r="J44" s="20">
-        <v>0.9659447867091276</v>
+        <v>1.875230128844491</v>
       </c>
       <c r="K44" s="20">
-        <v>0.5819757185676813</v>
+        <v>0.1907239634042472</v>
       </c>
       <c r="L44" s="20">
-        <v>-0.2739840361033444</v>
+        <v>-0.1976055930026395</v>
       </c>
       <c r="M44" s="20">
-        <v>0.007651260733486431</v>
+        <v>-0.6020742594104574</v>
       </c>
       <c r="N44" s="20">
-        <v>49.005413</v>
+        <v>72.30144</v>
       </c>
       <c r="O44" s="20">
-        <v>9.385771999999999</v>
+        <v>2.3325565</v>
       </c>
       <c r="P44" s="12">
-        <v>0.20897</v>
+        <v>0.03211</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.365</v>
+        <v>0.013</v>
       </c>
       <c r="R44" s="12">
-        <v>0.2883788676541446</v>
+        <v>0.8025380420831225</v>
       </c>
       <c r="S44" s="11">
-        <v>64.26304420285817</v>
+        <v>73.51123701083746</v>
       </c>
       <c r="T44" s="9" t="s">
         <v>114</v>
@@ -7295,7 +7295,7 @@
         <v>224</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7617,7 +7617,7 @@
         <v>562.8900146484375</v>
       </c>
       <c r="BI1">
-        <v>543.5250244140625</v>
+        <v>543.4299926757812</v>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -7802,7 +7802,7 @@
         <v>1082.280029296875</v>
       </c>
       <c r="BI2">
-        <v>1056.72998046875</v>
+        <v>1053.97998046875</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -7987,7 +7987,7 @@
         <v>1777.800048828125</v>
       </c>
       <c r="BI3">
-        <v>1710.055053710938</v>
+        <v>1712.890014648438</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -8172,7 +8172,7 @@
         <v>456.8099975585938</v>
       </c>
       <c r="BI4">
-        <v>457.5499877929688</v>
+        <v>453.2300109863281</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -8357,7 +8357,7 @@
         <v>387.1799926757812</v>
       </c>
       <c r="BI5">
-        <v>389.6199951171875</v>
+        <v>389.5700073242188</v>
       </c>
     </row>
     <row r="6" spans="1:61">
@@ -8542,7 +8542,7 @@
         <v>393.5199890136719</v>
       </c>
       <c r="BI6">
-        <v>389.5150146484375</v>
+        <v>389.4400024414062</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -8727,7 +8727,7 @@
         <v>56.86000061035156</v>
       </c>
       <c r="BI7">
-        <v>56.16500091552734</v>
+        <v>56.09999847412109</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -8912,7 +8912,7 @@
         <v>255.75</v>
       </c>
       <c r="BI8">
-        <v>253.2799987792969</v>
+        <v>253.5500030517578</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -9282,7 +9282,7 @@
         <v>225.0700073242188</v>
       </c>
       <c r="BI10">
-        <v>229.6450042724609</v>
+        <v>228.8600006103516</v>
       </c>
     </row>
     <row r="11" spans="1:61">
@@ -9467,7 +9467,7 @@
         <v>363.0400085449219</v>
       </c>
       <c r="BI11">
-        <v>363.1650085449219</v>
+        <v>363.1600036621094</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -9652,7 +9652,7 @@
         <v>341.0799865722656</v>
       </c>
       <c r="BI12">
-        <v>338.3099975585938</v>
+        <v>339.1600036621094</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -9837,7 +9837,7 @@
         <v>61.81999969482422</v>
       </c>
       <c r="BI13">
-        <v>62.27830123901367</v>
+        <v>62.52999877929688</v>
       </c>
     </row>
     <row r="14" spans="1:61">
@@ -10022,7 +10022,7 @@
         <v>343.9200134277344</v>
       </c>
       <c r="BI14">
-        <v>341.5299987792969</v>
+        <v>342.75</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -10207,7 +10207,7 @@
         <v>227.6000061035156</v>
       </c>
       <c r="BI15">
-        <v>227.5449981689453</v>
+        <v>227.5500030517578</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -10577,7 +10577,7 @@
         <v>123.8899993896484</v>
       </c>
       <c r="BI17">
-        <v>125.9800033569336</v>
+        <v>124.8199996948242</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="251">
   <si>
     <t>DELL</t>
   </si>
@@ -315,6 +315,9 @@
     <t>2026-09-18</t>
   </si>
   <si>
+    <t>2026-09-29</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -477,18 +480,18 @@
     <t>Lilly (Eli)</t>
   </si>
   <si>
+    <t>COF</t>
+  </si>
+  <si>
+    <t>Capital One</t>
+  </si>
+  <si>
     <t>CVX</t>
   </si>
   <si>
     <t>Chevron Corporation</t>
   </si>
   <si>
-    <t>COF</t>
-  </si>
-  <si>
-    <t>Capital One</t>
-  </si>
-  <si>
     <t>GS</t>
   </si>
   <si>
@@ -501,25 +504,25 @@
     <t>Agilent Technologies</t>
   </si>
   <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Bloom Energy</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
     <t>AMGN</t>
   </si>
   <si>
     <t>Amgen</t>
   </si>
   <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>Bloom Energy</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>RVTY</t>
-  </si>
-  <si>
-    <t>Revvity</t>
+    <t>KEYS</t>
+  </si>
+  <si>
+    <t>Keysight Technologies</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -600,7 +603,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-29 02:02 UTC · данные на 2026-09-28 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-09-30 01:20 UTC · данные на 2026-09-29 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -681,7 +684,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-29 02:02 UTC</t>
+    <t>2026-09-30 01:20 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1199,9 +1202,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$22</c:f>
+              <c:f>Капитал!$A$5:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1255,16 +1258,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2026-09-28</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2026-09-29</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$22</c:f>
+              <c:f>Капитал!$D$5:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1317,6 +1323,9 @@
                   <c:v>10163.98</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>10217.93</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>10217.93</c:v>
                 </c:pt>
               </c:numCache>
@@ -1342,9 +1351,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$22</c:f>
+              <c:f>Капитал!$A$5:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1398,16 +1407,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2026-09-28</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2026-09-29</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$22</c:f>
+              <c:f>Капитал!$F$5:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1461,6 +1473,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>10059.63</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1600,9 +1615,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$22</c:f>
+              <c:f>Капитал!$A$5:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1656,16 +1671,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2026-09-28</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2026-09-29</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$22</c:f>
+              <c:f>Капитал!$D$5:$D$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1718,6 +1736,9 @@
                   <c:v>10163.98</c:v>
                 </c:pt>
                 <c:pt idx="17">
+                  <c:v>10217.93</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>10217.93</c:v>
                 </c:pt>
               </c:numCache>
@@ -1743,9 +1764,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$22</c:f>
+              <c:f>Капитал!$A$5:$A$23</c:f>
               <c:strCache>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1799,16 +1820,19 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>2026-09-28</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2026-09-29</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$22</c:f>
+              <c:f>Капитал!$F$5:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="18"/>
+                <c:ptCount val="19"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1862,6 +1886,9 @@
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>10059.63</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2356,12 +2383,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2369,13 +2396,13 @@
         <v>84</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2394,27 +2421,27 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>3.272450923369867</v>
+        <v>3.17650319697472</v>
       </c>
       <c r="D9" s="7">
         <v>0</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H9" s="7">
         <v>17</v>
@@ -2422,7 +2449,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2451,7 +2478,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C16" s="10">
         <v>10000</v>
@@ -2459,7 +2486,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C17" s="11">
         <v>21</v>
@@ -2467,23 +2494,23 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C18" s="11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C19" s="11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C20" s="11">
         <v>21</v>
@@ -2491,55 +2518,55 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C25" s="12">
-        <v>0.09920364827193126</v>
+        <v>0.09652235413162506</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C26" s="11">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C28" s="10">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2548,12 +2575,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="14" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2736,11 +2763,11 @@
         <v>0.22661056463806467</v>
       </c>
       <c r="L5" s="11">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M5" s="11">
         <f>MAX(0,21-L5)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N5" s="20">
         <v>2.927623067210654</v>
@@ -2787,11 +2814,11 @@
         <v>0.14092784834878958</v>
       </c>
       <c r="L6" s="11">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M6" s="11">
         <f>MAX(0,21-L6)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N6" s="20">
         <v>1.809956883354321</v>
@@ -2838,11 +2865,11 @@
         <v>0.10312250862904396</v>
       </c>
       <c r="L7" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M7" s="11">
         <f>MAX(0,21-L7)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N7" s="20">
         <v>1.655247920227722</v>
@@ -2889,11 +2916,11 @@
         <v>-0.010769129468497708</v>
       </c>
       <c r="L8" s="11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M8" s="11">
         <f>MAX(0,21-L8)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" s="20">
         <v>1.135451734784544</v>
@@ -2940,11 +2967,11 @@
         <v>0.0818569829383088</v>
       </c>
       <c r="L9" s="11">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M9" s="11">
         <f>MAX(0,21-L9)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" s="20">
         <v>1.098454348098604</v>
@@ -2991,11 +3018,11 @@
         <v>0.022428310098067856</v>
       </c>
       <c r="L10" s="11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M10" s="11">
         <f>MAX(0,21-L10)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N10" s="20">
         <v>0.9280120270881818</v>
@@ -3042,11 +3069,11 @@
         <v>-0.06625193724862595</v>
       </c>
       <c r="L11" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M11" s="11">
         <f>MAX(0,21-L11)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N11" s="20">
         <v>0.8840484909760108</v>
@@ -3093,11 +3120,11 @@
         <v>0.005454771926130383</v>
       </c>
       <c r="L12" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M12" s="11">
         <f>MAX(0,21-L12)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N12" s="20">
         <v>0.8298272742812407</v>
@@ -3144,11 +3171,11 @@
         <v>-0.031390943797511</v>
       </c>
       <c r="L13" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="11">
         <f>MAX(0,21-L13)</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N13" s="20">
         <v>0.7019116395441239</v>
@@ -3195,11 +3222,11 @@
         <v>0.08658508713616178</v>
       </c>
       <c r="L14" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M14" s="11">
         <f>MAX(0,21-L14)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N14" s="20">
         <v>0.6809721702367264</v>
@@ -3246,11 +3273,11 @@
         <v>-0.05226237580167736</v>
       </c>
       <c r="L15" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M15" s="11">
         <f>MAX(0,21-L15)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N15" s="20">
         <v>0.8197914702434592</v>
@@ -3297,11 +3324,11 @@
         <v>-0.002857562037493852</v>
       </c>
       <c r="L16" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M16" s="11">
         <f>MAX(0,21-L16)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N16" s="20">
         <v>0.776423257523575</v>
@@ -3348,11 +3375,11 @@
         <v>-0.07521653201179906</v>
       </c>
       <c r="L17" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M17" s="11">
         <f>MAX(0,21-L17)</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N17" s="20">
         <v>0.7994794227521653</v>
@@ -3399,11 +3426,11 @@
         <v>0.0019354118801651347</v>
       </c>
       <c r="L18" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" s="11">
         <f>MAX(0,21-L18)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N18" s="20">
         <v>0.8410723709429708</v>
@@ -3450,11 +3477,11 @@
         <v>-0.005460512055785145</v>
       </c>
       <c r="L19" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="11">
         <f>MAX(0,21-L19)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N19" s="20">
         <v>0.6643531276938139</v>
@@ -3501,11 +3528,11 @@
         <v>0.011180129669421552</v>
       </c>
       <c r="L20" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" s="11">
         <f>MAX(0,21-L20)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N20" s="20">
         <v>0.6369924288836575</v>
@@ -3552,11 +3579,11 @@
         <v>0.021556462933884316</v>
       </c>
       <c r="L21" s="11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21" s="11">
         <f>MAX(0,21-L21)</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="N21" s="20">
         <v>0.662112373894027</v>
@@ -4002,7 +4029,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -4403,6 +4430,25 @@
       <c r="F22" s="10">
         <v>10059.63</v>
       </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="10">
+        <v>1832.96</v>
+      </c>
+      <c r="C23" s="10">
+        <v>8384.969999999999</v>
+      </c>
+      <c r="D23" s="10">
+        <f>B23+C23</f>
+        <v>10217.93</v>
+      </c>
+      <c r="E23" s="11">
+        <v>17</v>
+      </c>
+      <c r="F23" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4431,12 +4477,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -4453,52 +4499,52 @@
         <v>21</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K4" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L4" s="15" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N4" s="15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O4" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P4" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q4" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S4" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T4" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -4518,7 +4564,7 @@
         <v>1053.97998046875</v>
       </c>
       <c r="F5" s="17">
-        <v>1.2085157164277</v>
+        <v>1.208551726646418</v>
       </c>
       <c r="G5" s="20">
         <v>-0.5652307531380691</v>
@@ -4530,16 +4576,16 @@
         <v>3.949484521250298</v>
       </c>
       <c r="J5" s="20">
-        <v>2.152028444204602</v>
+        <v>2.152233525949353</v>
       </c>
       <c r="K5" s="20">
         <v>0</v>
       </c>
       <c r="L5" s="20">
-        <v>-2.840116701519459</v>
+        <v>-2.840115994885092</v>
       </c>
       <c r="M5" s="20">
-        <v>0.06346837996923604</v>
+        <v>0.06309490585654287</v>
       </c>
       <c r="N5" s="20">
         <v>24.447256</v>
@@ -4557,10 +4603,10 @@
         <v>1.952199955020532</v>
       </c>
       <c r="S5" s="11">
-        <v>58.35057323749435</v>
+        <v>58.35057323749574</v>
       </c>
       <c r="T5" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -4580,7 +4626,7 @@
         <v>1712.890014648438</v>
       </c>
       <c r="F6" s="17">
-        <v>1.029211060387775</v>
+        <v>1.031125929043125</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5400051267382519</v>
@@ -4592,16 +4638,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J6" s="20">
-        <v>1.873943827100078</v>
+        <v>1.874173277302404</v>
       </c>
       <c r="K6" s="20">
-        <v>0.0792978836476507</v>
+        <v>0.09493727377241684</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.017781627758584</v>
+        <v>-3.017779786263553</v>
       </c>
       <c r="M6" s="20">
-        <v>-0.04225701670518689</v>
+        <v>-0.04264206308046381</v>
       </c>
       <c r="N6" s="20">
         <v>24.095963</v>
@@ -4622,7 +4668,7 @@
         <v>53.32535751730857</v>
       </c>
       <c r="T6" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -4630,10 +4676,10 @@
         <v>3</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>36</v>
@@ -4642,7 +4688,7 @@
         <v>62.63000106811523</v>
       </c>
       <c r="F7" s="17">
-        <v>0.9725909310944281</v>
+        <v>0.9725725292886965</v>
       </c>
       <c r="G7" s="20">
         <v>0.3308679966228206</v>
@@ -4654,16 +4700,16 @@
         <v>2.202669227673142</v>
       </c>
       <c r="J7" s="20">
-        <v>2.664679659166533</v>
+        <v>2.664752482451724</v>
       </c>
       <c r="K7" s="20">
         <v>0</v>
       </c>
       <c r="L7" s="20">
-        <v>-2.075306633456196</v>
+        <v>-2.075310812157834</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.1622315024229989</v>
+        <v>-0.162703875579283</v>
       </c>
       <c r="N7" s="20">
         <v>32.4433</v>
@@ -4681,10 +4727,10 @@
         <v>1.630414027867387</v>
       </c>
       <c r="S7" s="11">
-        <v>60.67783554164512</v>
+        <v>60.67783555435059</v>
       </c>
       <c r="T7" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -4692,61 +4738,61 @@
         <v>4</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E8" s="10">
-        <v>342.75</v>
+        <v>389.5700073242188</v>
       </c>
       <c r="F8" s="17">
-        <v>0.8491382180014263</v>
+        <v>0.852676197334425</v>
       </c>
       <c r="G8" s="20">
-        <v>-0.3286805258697003</v>
+        <v>0.6066625783285674</v>
       </c>
       <c r="H8" s="20">
-        <v>1.46049714331344</v>
+        <v>-0.6826845382770022</v>
       </c>
       <c r="I8" s="20">
-        <v>1.392272810408264</v>
+        <v>2.855442298450458</v>
       </c>
       <c r="J8" s="20">
-        <v>0.132534195576302</v>
+        <v>1.938855002708015</v>
       </c>
       <c r="K8" s="20">
-        <v>4.134420649754185</v>
+        <v>0.6218023213438065</v>
       </c>
       <c r="L8" s="20">
-        <v>0.05523662630286615</v>
+        <v>0.05652950002477082</v>
       </c>
       <c r="M8" s="20">
-        <v>-0.04763806918211733</v>
+        <v>-1.156278998257378</v>
       </c>
       <c r="N8" s="20">
-        <v>17.273733</v>
+        <v>16.15269</v>
       </c>
       <c r="O8" s="20">
-        <v>6.7573094</v>
+        <v>4.459058</v>
       </c>
       <c r="P8" s="12">
-        <v>0.48676</v>
+        <v>0.27637</v>
       </c>
       <c r="Q8" s="12">
-        <v>0.242</v>
+        <v>0.517</v>
       </c>
       <c r="R8" s="12">
-        <v>0.2509118514627715</v>
+        <v>0.5450361349569324</v>
       </c>
       <c r="S8" s="11">
-        <v>48.86772542127657</v>
+        <v>59.38019986855327</v>
       </c>
       <c r="T8" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -4754,61 +4800,61 @@
         <v>5</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E9" s="10">
-        <v>389.5700073242188</v>
+        <v>342.75</v>
       </c>
       <c r="F9" s="17">
-        <v>0.8488568038718871</v>
+        <v>0.8481509942326801</v>
       </c>
       <c r="G9" s="20">
-        <v>0.6066625783285674</v>
+        <v>-0.3286805258697003</v>
       </c>
       <c r="H9" s="20">
-        <v>-0.6826845382770022</v>
+        <v>1.46049714331344</v>
       </c>
       <c r="I9" s="20">
-        <v>2.855442298450458</v>
+        <v>1.392272810408264</v>
       </c>
       <c r="J9" s="20">
-        <v>1.938801096406154</v>
+        <v>0.1327881719500527</v>
       </c>
       <c r="K9" s="20">
-        <v>0.5895385746597579</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L9" s="20">
-        <v>0.05654729625472697</v>
+        <v>0.05521883844500573</v>
       </c>
       <c r="M9" s="20">
-        <v>-1.155436995053518</v>
+        <v>-0.04799982369731487</v>
       </c>
       <c r="N9" s="20">
-        <v>16.15269</v>
+        <v>17.273733</v>
       </c>
       <c r="O9" s="20">
-        <v>4.459058</v>
+        <v>6.7573094</v>
       </c>
       <c r="P9" s="12">
-        <v>0.27637</v>
+        <v>0.48676</v>
       </c>
       <c r="Q9" s="12">
-        <v>0.517</v>
+        <v>0.242</v>
       </c>
       <c r="R9" s="12">
-        <v>0.5450361349569324</v>
+        <v>0.2509119907868131</v>
       </c>
       <c r="S9" s="11">
-        <v>59.38019986852905</v>
+        <v>48.86772541391871</v>
       </c>
       <c r="T9" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -4816,61 +4862,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>11</v>
+        <v>118</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>58</v>
+        <v>119</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E10" s="10">
-        <v>339.1600036621094</v>
+        <v>41.77999877929688</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8472556601481801</v>
+        <v>0.8464277408471855</v>
       </c>
       <c r="G10" s="20">
-        <v>-0.3209980775361091</v>
+        <v>-0.01962276509782637</v>
       </c>
       <c r="H10" s="20">
-        <v>1.46049714331344</v>
+        <v>-0.81458274663997</v>
       </c>
       <c r="I10" s="20">
-        <v>1.392272810408264</v>
+        <v>3.890766583974275</v>
       </c>
       <c r="J10" s="20">
-        <v>0.1011824206069702</v>
+        <v>1.264952331308445</v>
       </c>
       <c r="K10" s="20">
-        <v>4.134420649754185</v>
+        <v>3.418039643978128</v>
       </c>
       <c r="L10" s="20">
-        <v>0.107497577080973</v>
+        <v>-3.017779786263553</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.01008210804686011</v>
+        <v>-0.2170906233041758</v>
       </c>
       <c r="N10" s="20">
-        <v>17.12249</v>
+        <v>13.269938</v>
       </c>
       <c r="O10" s="20">
-        <v>6.7015085</v>
+        <v>2.771478</v>
       </c>
       <c r="P10" s="12">
-        <v>0.48676</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.242</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R10" s="12">
-        <v>0.2404458803116964</v>
+        <v>0.9016841185744076</v>
       </c>
       <c r="S10" s="11">
-        <v>48.43503157637644</v>
+        <v>58.83998556919025</v>
       </c>
       <c r="T10" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -4878,61 +4924,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>117</v>
+        <v>11</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>118</v>
+        <v>58</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E11" s="10">
-        <v>41.77999877929688</v>
+        <v>339.1600036621094</v>
       </c>
       <c r="F11" s="17">
-        <v>0.831979250927496</v>
+        <v>0.8462702673593893</v>
       </c>
       <c r="G11" s="20">
-        <v>-0.01962276509782637</v>
+        <v>-0.3209980775361091</v>
       </c>
       <c r="H11" s="20">
-        <v>-0.81458274663997</v>
+        <v>1.46049714331344</v>
       </c>
       <c r="I11" s="20">
-        <v>3.890766583974275</v>
+        <v>1.392272810408264</v>
       </c>
       <c r="J11" s="20">
-        <v>1.264860140866668</v>
+        <v>0.101438109930742</v>
       </c>
       <c r="K11" s="20">
-        <v>3.297545246029351</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L11" s="20">
-        <v>-3.017781627758584</v>
+        <v>0.1074794553986571</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.2166080550991883</v>
+        <v>-0.01042714850685386</v>
       </c>
       <c r="N11" s="20">
-        <v>13.269938</v>
+        <v>17.12249</v>
       </c>
       <c r="O11" s="20">
-        <v>2.771478</v>
+        <v>6.7015085</v>
       </c>
       <c r="P11" s="12">
-        <v>0.21465999</v>
+        <v>0.48676</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.242</v>
       </c>
       <c r="R11" s="12">
-        <v>0.9016841185744076</v>
+        <v>0.2404458803116964</v>
       </c>
       <c r="S11" s="11">
-        <v>58.8399855691899</v>
+        <v>48.43503157654847</v>
       </c>
       <c r="T11" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -4952,7 +4998,7 @@
         <v>543.4299926757812</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8143392336076546</v>
+        <v>0.8219891143481299</v>
       </c>
       <c r="G12" s="20">
         <v>-0.1018209436010066</v>
@@ -4964,16 +5010,16 @@
         <v>2.17697052724581</v>
       </c>
       <c r="J12" s="20">
-        <v>2.67886207095234</v>
+        <v>2.678949089916177</v>
       </c>
       <c r="K12" s="20">
-        <v>1.562626058506958</v>
+        <v>1.626594358708216</v>
       </c>
       <c r="L12" s="20">
-        <v>-3.017781627758584</v>
+        <v>-3.017779786263553</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.7410336712485137</v>
+        <v>-0.7416903145301179</v>
       </c>
       <c r="N12" s="20">
         <v>32.783344</v>
@@ -4991,10 +5037,10 @@
         <v>2.178000248070538</v>
       </c>
       <c r="S12" s="11">
-        <v>54.44305844702328</v>
+        <v>54.44305844686942</v>
       </c>
       <c r="T12" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5014,7 +5060,7 @@
         <v>389.4400024414062</v>
       </c>
       <c r="F13" s="17">
-        <v>0.7996645417937399</v>
+        <v>0.8041263146778714</v>
       </c>
       <c r="G13" s="20">
         <v>0.63544661477666</v>
@@ -5026,16 +5072,16 @@
         <v>2.432487252480616</v>
       </c>
       <c r="J13" s="20">
-        <v>1.773961275506885</v>
+        <v>1.774016123245709</v>
       </c>
       <c r="K13" s="20">
-        <v>0.7528962662486143</v>
+        <v>0.7904824353884016</v>
       </c>
       <c r="L13" s="20">
-        <v>0.03037650563153634</v>
+        <v>0.03035887657132737</v>
       </c>
       <c r="M13" s="20">
-        <v>-1.129376634115772</v>
+        <v>-1.130176183999243</v>
       </c>
       <c r="N13" s="20">
         <v>13.640207</v>
@@ -5053,10 +5099,10 @@
         <v>0.5560982973748247</v>
       </c>
       <c r="S13" s="11">
-        <v>53.65092869600117</v>
+        <v>53.65092868896293</v>
       </c>
       <c r="T13" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5076,7 +5122,7 @@
         <v>363.1600036621094</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7495196647600424</v>
+        <v>0.765698064543236</v>
       </c>
       <c r="G14" s="20">
         <v>1.160842542624806</v>
@@ -5088,16 +5134,16 @@
         <v>-0.379797036716154</v>
       </c>
       <c r="J14" s="20">
-        <v>0.4423260264844293</v>
+        <v>0.4425317063762407</v>
       </c>
       <c r="K14" s="20">
-        <v>3.729636424089999</v>
+        <v>3.864208957978802</v>
       </c>
       <c r="L14" s="20">
-        <v>0.5376909604472081</v>
+        <v>0.5376700908418292</v>
       </c>
       <c r="M14" s="20">
-        <v>-0.180307044442761</v>
+        <v>-0.1806914953763021</v>
       </c>
       <c r="N14" s="20">
         <v>9.756517000000001</v>
@@ -5115,10 +5161,10 @@
         <v>0.2827324553858042</v>
       </c>
       <c r="S14" s="11">
-        <v>44.00018052901233</v>
+        <v>44.00018052953638</v>
       </c>
       <c r="T14" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -5126,10 +5172,10 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>36</v>
@@ -5138,7 +5184,7 @@
         <v>204.4100036621094</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7471568606718153</v>
+        <v>0.7471430776725437</v>
       </c>
       <c r="G15" s="20">
         <v>-0.4407742654660424</v>
@@ -5150,16 +5196,16 @@
         <v>0.4340417055879129</v>
       </c>
       <c r="J15" s="20">
-        <v>1.799148479019377</v>
+        <v>1.799262543071884</v>
       </c>
       <c r="K15" s="20">
         <v>0</v>
       </c>
       <c r="L15" s="20">
-        <v>-0.5699179839512446</v>
+        <v>-0.5699317785427325</v>
       </c>
       <c r="M15" s="20">
-        <v>-0.3856700896794154</v>
+        <v>-0.3862390969246917</v>
       </c>
       <c r="N15" s="20">
         <v>28.41031</v>
@@ -5177,10 +5223,10 @@
         <v>1.01369019895245</v>
       </c>
       <c r="S15" s="11">
-        <v>62.75777975999041</v>
+        <v>62.75777976009478</v>
       </c>
       <c r="T15" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -5188,10 +5234,10 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" s="9" t="s">
         <v>36</v>
@@ -5200,7 +5246,7 @@
         <v>116.0299987792969</v>
       </c>
       <c r="F16" s="17">
-        <v>0.6895505156335534</v>
+        <v>0.6885706028091586</v>
       </c>
       <c r="G16" s="20">
         <v>-0.8300215284456212</v>
@@ -5212,16 +5258,16 @@
         <v>0.5176902230779757</v>
       </c>
       <c r="J16" s="20">
-        <v>1.978866110622099</v>
+        <v>1.979097943411691</v>
       </c>
       <c r="K16" s="20">
-        <v>4.134420649754185</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L16" s="20">
-        <v>-2.659328655657073</v>
+        <v>-2.659329103832751</v>
       </c>
       <c r="M16" s="20">
-        <v>0.5221718552133483</v>
+        <v>0.5219715211815019</v>
       </c>
       <c r="N16" s="20">
         <v>59.648514</v>
@@ -5239,10 +5285,10 @@
         <v>1.69023871796457</v>
       </c>
       <c r="S16" s="11">
-        <v>58.52241396970124</v>
+        <v>58.52241396970126</v>
       </c>
       <c r="T16" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -5262,7 +5308,7 @@
         <v>158.4299926757812</v>
       </c>
       <c r="F17" s="17">
-        <v>0.6722788640418077</v>
+        <v>0.6863997976000916</v>
       </c>
       <c r="G17" s="20">
         <v>0.4643687022637146</v>
@@ -5274,16 +5320,16 @@
         <v>-0.03871237626800461</v>
       </c>
       <c r="J17" s="20">
-        <v>1.047912131854923</v>
+        <v>1.048069840062104</v>
       </c>
       <c r="K17" s="20">
-        <v>3.210824496173538</v>
+        <v>3.32849341059643</v>
       </c>
       <c r="L17" s="20">
-        <v>0.4239862986276916</v>
+        <v>0.4239661553274459</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.5363208600910532</v>
+        <v>-0.5368888605485839</v>
       </c>
       <c r="N17" s="20">
         <v>16.332987</v>
@@ -5298,13 +5344,13 @@
         <v>0.053</v>
       </c>
       <c r="R17" s="12">
-        <v>0.3447460113164478</v>
+        <v>0.3447460983994171</v>
       </c>
       <c r="S17" s="11">
-        <v>52.51861058025204</v>
+        <v>52.51861058334671</v>
       </c>
       <c r="T17" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -5324,7 +5370,7 @@
         <v>253.5500030517578</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6619889812774012</v>
+        <v>0.6661369568864438</v>
       </c>
       <c r="G18" s="20">
         <v>0.4452704814464517</v>
@@ -5336,16 +5382,16 @@
         <v>2.40169945735154</v>
       </c>
       <c r="J18" s="20">
-        <v>1.502023620944271</v>
+        <v>1.502090701483797</v>
       </c>
       <c r="K18" s="20">
-        <v>0.6707132300480476</v>
+        <v>0.7056217607301639</v>
       </c>
       <c r="L18" s="20">
-        <v>0.3052937841421062</v>
+        <v>0.3052743990076309</v>
       </c>
       <c r="M18" s="20">
-        <v>-1.016461966304801</v>
+        <v>-1.01721208038731</v>
       </c>
       <c r="N18" s="20">
         <v>14.597602</v>
@@ -5363,10 +5409,10 @@
         <v>0.3636407876702044</v>
       </c>
       <c r="S18" s="11">
-        <v>52.4939899388571</v>
+        <v>52.49398993264359</v>
       </c>
       <c r="T18" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -5386,7 +5432,7 @@
         <v>62.52999877929688</v>
       </c>
       <c r="F19" s="17">
-        <v>0.651133014263879</v>
+        <v>0.6501319424647862</v>
       </c>
       <c r="G19" s="20">
         <v>1.236177102540873</v>
@@ -5398,16 +5444,16 @@
         <v>-0.5828068382546813</v>
       </c>
       <c r="J19" s="20">
-        <v>0.8086146556923782</v>
+        <v>0.8088484330135332</v>
       </c>
       <c r="K19" s="20">
-        <v>4.134420649754185</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L19" s="20">
-        <v>-0.001475079253704801</v>
+        <v>-0.001492504857263614</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.4030550902252177</v>
+        <v>-0.4035144703632402</v>
       </c>
       <c r="N19" s="20">
         <v>11.559979</v>
@@ -5425,10 +5471,10 @@
         <v>0.9540624618530273</v>
       </c>
       <c r="S19" s="11">
-        <v>42.30704970653467</v>
+        <v>42.30704970653476</v>
       </c>
       <c r="T19" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -5436,10 +5482,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D20" s="9" t="s">
         <v>36</v>
@@ -5448,7 +5494,7 @@
         <v>227.2700042724609</v>
       </c>
       <c r="F20" s="17">
-        <v>0.634220662878726</v>
+        <v>0.6492077584066087</v>
       </c>
       <c r="G20" s="20">
         <v>0.4118301704600924</v>
@@ -5460,16 +5506,16 @@
         <v>0.1953152078062003</v>
       </c>
       <c r="J20" s="20">
-        <v>0.7850496562480861</v>
+        <v>0.7851580146913664</v>
       </c>
       <c r="K20" s="20">
-        <v>3.439222750154254</v>
+        <v>3.564333199677299</v>
       </c>
       <c r="L20" s="20">
-        <v>-1.805796136461388</v>
+        <v>-1.805802036700685</v>
       </c>
       <c r="M20" s="20">
-        <v>-1.065595040510507</v>
+        <v>-1.06632393967937</v>
       </c>
       <c r="N20" s="20">
         <v>21.410795</v>
@@ -5487,10 +5533,10 @@
         <v>0.2761603206515848</v>
       </c>
       <c r="S20" s="11">
-        <v>45.47939376335544</v>
+        <v>45.47939376411497</v>
       </c>
       <c r="T20" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -5498,19 +5544,19 @@
         <v>17</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E21" s="10">
         <v>246.1499938964844</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6142383425810742</v>
+        <v>0.6132540024685693</v>
       </c>
       <c r="G21" s="20">
         <v>-0.01172638762890057</v>
@@ -5522,16 +5568,16 @@
         <v>1.021835496573962</v>
       </c>
       <c r="J21" s="20">
-        <v>0.04617228617693294</v>
+        <v>0.04641212901068196</v>
       </c>
       <c r="K21" s="20">
-        <v>4.134420649754185</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4422790846574162</v>
+        <v>-0.442293694561014</v>
       </c>
       <c r="M21" s="20">
-        <v>0.06652691662004269</v>
+        <v>0.0662518251171688</v>
       </c>
       <c r="N21" s="20">
         <v>20.08608</v>
@@ -5549,10 +5595,10 @@
         <v>0.2348249143099643</v>
       </c>
       <c r="S21" s="11">
-        <v>41.24381199131362</v>
+        <v>41.24381199131338</v>
       </c>
       <c r="T21" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -5560,10 +5606,10 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D22" s="9" t="s">
         <v>61</v>
@@ -5572,7 +5618,7 @@
         <v>271.8999938964844</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6095667026960693</v>
+        <v>0.6100566751620263</v>
       </c>
       <c r="G22" s="20">
         <v>-0.7382512714864492</v>
@@ -5584,16 +5630,16 @@
         <v>-0.4590192885594346</v>
       </c>
       <c r="J22" s="20">
-        <v>2.683798299504477</v>
+        <v>2.683847913538417</v>
       </c>
       <c r="K22" s="20">
-        <v>-0.268593496587877</v>
+        <v>-0.264288895026258</v>
       </c>
       <c r="L22" s="20">
-        <v>-0.8089347861230161</v>
+        <v>-0.8089470539597733</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.08569890448048412</v>
+        <v>-0.08620800274815466</v>
       </c>
       <c r="N22" s="20">
         <v>50.27933</v>
@@ -5611,10 +5657,10 @@
         <v>1.31069939770121</v>
       </c>
       <c r="S22" s="11">
-        <v>74.25138551502383</v>
+        <v>74.25138551502386</v>
       </c>
       <c r="T22" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -5622,61 +5668,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E23" s="10">
-        <v>56.09999847412109</v>
+        <v>124.8199996948242</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5895029110295</v>
+        <v>0.5955183679171219</v>
       </c>
       <c r="G23" s="20">
-        <v>0.5909946933403921</v>
+        <v>0.3123085537627329</v>
       </c>
       <c r="H23" s="20">
-        <v>0.6147531683208749</v>
+        <v>0.5059193760536828</v>
       </c>
       <c r="I23" s="20">
-        <v>2.900414534129918</v>
+        <v>0.5162516055283453</v>
       </c>
       <c r="J23" s="20">
-        <v>0.06091150674024351</v>
+        <v>0.7173072884699651</v>
       </c>
       <c r="K23" s="20">
-        <v>0.8900360567182717</v>
+        <v>1.668764387219364</v>
       </c>
       <c r="L23" s="20">
-        <v>0.05235451453716362</v>
+        <v>0.2971893467544153</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.4187142977074728</v>
+        <v>-0.3318088286771503</v>
       </c>
       <c r="N23" s="20">
-        <v>16.772861</v>
+        <v>15.782166</v>
       </c>
       <c r="O23" s="20">
-        <v>1.6988854</v>
+        <v>3.9245436</v>
       </c>
       <c r="P23" s="12">
-        <v>0.10629</v>
+        <v>0.30667</v>
       </c>
       <c r="Q23" s="12">
-        <v>0.534</v>
+        <v>0.377</v>
       </c>
       <c r="R23" s="12">
-        <v>-0.1332251289941264</v>
+        <v>0.3822812345120339</v>
       </c>
       <c r="S23" s="11">
-        <v>39.51398136006124</v>
+        <v>51.11266140963528</v>
       </c>
       <c r="T23" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -5684,61 +5730,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E24" s="10">
-        <v>124.8199996948242</v>
+        <v>56.09999847412109</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5876604509647237</v>
+        <v>0.594570689717538</v>
       </c>
       <c r="G24" s="20">
-        <v>0.3123085537627329</v>
+        <v>0.5909946933403921</v>
       </c>
       <c r="H24" s="20">
-        <v>0.5059193760536828</v>
+        <v>0.6147531683208749</v>
       </c>
       <c r="I24" s="20">
-        <v>0.5162516055283453</v>
+        <v>2.900414534129918</v>
       </c>
       <c r="J24" s="20">
-        <v>0.7171013416066088</v>
+        <v>0.06110575945457342</v>
       </c>
       <c r="K24" s="20">
-        <v>1.603465481404173</v>
+        <v>0.9320904323641113</v>
       </c>
       <c r="L24" s="20">
-        <v>0.2972086802441086</v>
+        <v>0.05233674508921302</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.3313266312390235</v>
+        <v>-0.4191637481685332</v>
       </c>
       <c r="N24" s="20">
-        <v>15.782166</v>
+        <v>16.772861</v>
       </c>
       <c r="O24" s="20">
-        <v>3.9245436</v>
+        <v>1.6988854</v>
       </c>
       <c r="P24" s="12">
-        <v>0.30667</v>
+        <v>0.10629</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.377</v>
+        <v>0.534</v>
       </c>
       <c r="R24" s="12">
-        <v>0.3822812345120339</v>
+        <v>-0.1332251289941264</v>
       </c>
       <c r="S24" s="11">
-        <v>51.11266140963532</v>
+        <v>39.51398135968419</v>
       </c>
       <c r="T24" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -5758,7 +5804,7 @@
         <v>228.8600006103516</v>
       </c>
       <c r="F25" s="17">
-        <v>0.58154151137038</v>
+        <v>0.5819405484586296</v>
       </c>
       <c r="G25" s="20">
         <v>-1.098910330048646</v>
@@ -5770,16 +5816,16 @@
         <v>2.414157689348599</v>
       </c>
       <c r="J25" s="20">
-        <v>0.7989918250233137</v>
+        <v>0.7991813477157338</v>
       </c>
       <c r="K25" s="20">
-        <v>-0.3018700633930144</v>
+        <v>-0.2986496589983051</v>
       </c>
       <c r="L25" s="20">
-        <v>-0.2531108904403336</v>
+        <v>-0.2531267086833988</v>
       </c>
       <c r="M25" s="20">
-        <v>-0.3727966714780135</v>
+        <v>-0.3733381608812324</v>
       </c>
       <c r="N25" s="20">
         <v>28.489874</v>
@@ -5794,13 +5840,13 @@
         <v>1.059</v>
       </c>
       <c r="R25" s="12">
-        <v>0.3692879041816017</v>
+        <v>0.3692880291901632</v>
       </c>
       <c r="S25" s="11">
-        <v>58.77557026474965</v>
+        <v>58.77557027334879</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -5808,10 +5854,10 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D26" s="9" t="s">
         <v>61</v>
@@ -5820,7 +5866,7 @@
         <v>228.6900024414062</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5529894498470236</v>
+        <v>0.5674300996311124</v>
       </c>
       <c r="G26" s="20">
         <v>0.1826167294586985</v>
@@ -5832,16 +5878,16 @@
         <v>-0.8979974000351455</v>
       </c>
       <c r="J26" s="20">
-        <v>0.8418996128055922</v>
+        <v>0.8421167847182076</v>
       </c>
       <c r="K26" s="20">
-        <v>3.288974009124997</v>
+        <v>3.409189144167147</v>
       </c>
       <c r="L26" s="20">
-        <v>-0.03784150713372107</v>
+        <v>-0.03785870044141074</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.4930636567104923</v>
+        <v>-0.4936797366641485</v>
       </c>
       <c r="N26" s="20">
         <v>40.498222</v>
@@ -5859,10 +5905,10 @@
         <v>0.2439621790520661</v>
       </c>
       <c r="S26" s="11">
-        <v>63.86767526487981</v>
+        <v>63.8676752648799</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -5870,10 +5916,10 @@
         <v>23</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D27" s="9" t="s">
         <v>36</v>
@@ -5882,7 +5928,7 @@
         <v>371.8699951171875</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5522508240568881</v>
+        <v>0.5602917298008462</v>
       </c>
       <c r="G27" s="20">
         <v>0.08345580963657841</v>
@@ -5894,16 +5940,16 @@
         <v>0.4617856253832925</v>
       </c>
       <c r="J27" s="20">
-        <v>1.589099450015377</v>
+        <v>1.589188000847441</v>
       </c>
       <c r="K27" s="20">
-        <v>1.661447378110094</v>
+        <v>1.728635415352477</v>
       </c>
       <c r="L27" s="20">
-        <v>-1.826147220619802</v>
+        <v>-1.826152990863577</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.4635294951542942</v>
+        <v>-0.464127967155801</v>
       </c>
       <c r="N27" s="20">
         <v>33.886448</v>
@@ -5921,10 +5967,10 @@
         <v>0.8351263138435636</v>
       </c>
       <c r="S27" s="11">
-        <v>62.74203964815953</v>
+        <v>62.74203964815955</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -5932,10 +5978,10 @@
         <v>24</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D28" s="9" t="s">
         <v>66</v>
@@ -5944,7 +5990,7 @@
         <v>116.0199966430664</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5478825115378305</v>
+        <v>0.5469036035441049</v>
       </c>
       <c r="G28" s="20">
         <v>0.4073104247281907</v>
@@ -5956,16 +6002,16 @@
         <v>0.4715191624753287</v>
       </c>
       <c r="J28" s="20">
-        <v>-0.2093850352645275</v>
+        <v>-0.2091256425023764</v>
       </c>
       <c r="K28" s="20">
-        <v>4.134420649754185</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L28" s="20">
-        <v>0.1228785056741809</v>
+        <v>0.1228602857439374</v>
       </c>
       <c r="M28" s="20">
-        <v>0.0825881028226164</v>
+        <v>0.08231030809296014</v>
       </c>
       <c r="N28" s="20">
         <v>13.979167</v>
@@ -5983,10 +6029,10 @@
         <v>0.08429903404734951</v>
       </c>
       <c r="S28" s="11">
-        <v>42.79219288276566</v>
+        <v>42.79219288276581</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -5994,10 +6040,10 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>36</v>
@@ -6006,7 +6052,7 @@
         <v>176.3300018310547</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5095764165662345</v>
+        <v>0.5128036365010913</v>
       </c>
       <c r="G29" s="20">
         <v>-1.991192966399809</v>
@@ -6018,16 +6064,16 @@
         <v>0.2259855872354321</v>
       </c>
       <c r="J29" s="20">
-        <v>1.911313265040892</v>
+        <v>1.911476117805594</v>
       </c>
       <c r="K29" s="20">
-        <v>0.4226515502279323</v>
+        <v>0.4494778838476307</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.711695549801433</v>
+        <v>-0.7117084387680134</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.2441639533628555</v>
+        <v>-0.2446642357493879</v>
       </c>
       <c r="N29" s="20">
         <v>61.29329</v>
@@ -6045,10 +6091,10 @@
         <v>1.254859446449356</v>
       </c>
       <c r="S29" s="11">
-        <v>60.11644167561602</v>
+        <v>60.11644167561587</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -6056,10 +6102,10 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D30" s="9" t="s">
         <v>61</v>
@@ -6068,7 +6114,7 @@
         <v>63.88000106811523</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4569664458755423</v>
+        <v>0.4616272100170156</v>
       </c>
       <c r="G30" s="20">
         <v>0.4625864400742329</v>
@@ -6080,16 +6126,16 @@
         <v>0.2249472925442899</v>
       </c>
       <c r="J30" s="20">
-        <v>0.4698882554579958</v>
+        <v>0.4700919567029462</v>
       </c>
       <c r="K30" s="20">
-        <v>0.7861728330537516</v>
+        <v>0.8248431993604487</v>
       </c>
       <c r="L30" s="20">
-        <v>0.6729435427886399</v>
+        <v>0.6729218092376386</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.3736690535729966</v>
+        <v>-0.3741626307699393</v>
       </c>
       <c r="N30" s="20">
         <v>13.845816</v>
@@ -6107,10 +6153,10 @@
         <v>0.1149161833418366</v>
       </c>
       <c r="S30" s="11">
-        <v>50.28693602196861</v>
+        <v>50.28693602215542</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -6118,10 +6164,10 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>36</v>
@@ -6130,7 +6176,7 @@
         <v>921.510009765625</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4540283666719393</v>
+        <v>0.4556216055180816</v>
       </c>
       <c r="G31" s="20">
         <v>-2.057025624567463</v>
@@ -6142,16 +6188,16 @@
         <v>1.336500578238815</v>
       </c>
       <c r="J31" s="20">
-        <v>1.850153369070178</v>
+        <v>1.850355141116401</v>
       </c>
       <c r="K31" s="20">
-        <v>-0.002885152552916025</v>
+        <v>0.01007659911417913</v>
       </c>
       <c r="L31" s="20">
-        <v>-2.631270450194496</v>
+        <v>-2.631271077596059</v>
       </c>
       <c r="M31" s="20">
-        <v>0.3136757158255622</v>
+        <v>0.3133923992795318</v>
       </c>
       <c r="N31" s="20">
         <v>65.76973</v>
@@ -6169,10 +6215,10 @@
         <v>1.428253393647692</v>
       </c>
       <c r="S31" s="11">
-        <v>59.19925314731145</v>
+        <v>59.19925306598373</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -6180,10 +6226,10 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>36</v>
@@ -6192,7 +6238,7 @@
         <v>401.2999877929688</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4451083997660897</v>
+        <v>0.4483318225408142</v>
       </c>
       <c r="G32" s="20">
         <v>-1.18924796979833</v>
@@ -6204,16 +6250,16 @@
         <v>3.655490679943009</v>
       </c>
       <c r="J32" s="20">
-        <v>0.9689918581542987</v>
+        <v>0.9692343280514764</v>
       </c>
       <c r="K32" s="20">
-        <v>0.4100467900744712</v>
+        <v>0.4364624429491279</v>
       </c>
       <c r="L32" s="20">
-        <v>-2.838383011987505</v>
+        <v>-2.838382316427332</v>
       </c>
       <c r="M32" s="20">
-        <v>0.4211928412062529</v>
+        <v>0.4209523627937781</v>
       </c>
       <c r="N32" s="20">
         <v>54.647465</v>
@@ -6231,10 +6277,10 @@
         <v>0.3585662742054512</v>
       </c>
       <c r="S32" s="11">
-        <v>58.84165473708767</v>
+        <v>58.84165473709983</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -6242,10 +6288,10 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D33" s="9" t="s">
         <v>59</v>
@@ -6254,7 +6300,7 @@
         <v>30.89999961853027</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4436980367291792</v>
+        <v>0.4426676629567567</v>
       </c>
       <c r="G33" s="20">
         <v>-0.05525750799347566</v>
@@ -6266,16 +6312,16 @@
         <v>-1.204760955881624</v>
       </c>
       <c r="J33" s="20">
-        <v>0.8499422660647392</v>
+        <v>0.8501432503204055</v>
       </c>
       <c r="K33" s="20">
-        <v>4.134420649754185</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L33" s="20">
-        <v>0.5101380742742394</v>
+        <v>0.5101173806669448</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.5892273169792235</v>
+        <v>-0.5899275467854834</v>
       </c>
       <c r="N33" s="20">
         <v>495.98203</v>
@@ -6293,10 +6339,10 @@
         <v>0.1414850375649745</v>
       </c>
       <c r="S33" s="11">
-        <v>75.68193322667111</v>
+        <v>75.68193322667129</v>
       </c>
       <c r="T33" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -6304,10 +6350,10 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D34" s="9" t="s">
         <v>61</v>
@@ -6316,7 +6362,7 @@
         <v>442.9400024414062</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4341556810337562</v>
+        <v>0.4335997239490538</v>
       </c>
       <c r="G34" s="20">
         <v>-0.9301946228299454</v>
@@ -6328,16 +6374,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J34" s="20">
-        <v>1.158681987005308</v>
+        <v>1.158857186102352</v>
       </c>
       <c r="K34" s="20">
-        <v>-0.5413605063087762</v>
+        <v>-0.5459430360698566</v>
       </c>
       <c r="L34" s="20">
-        <v>0.5688221537960026</v>
+        <v>0.5688010853355797</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.6870094532464075</v>
+        <v>-0.6877263174321637</v>
       </c>
       <c r="N34" s="20">
         <v>109.756966</v>
@@ -6355,10 +6401,10 @@
         <v>0.5318162845197381</v>
       </c>
       <c r="S34" s="11">
-        <v>68.64760432431193</v>
+        <v>68.64760432431177</v>
       </c>
       <c r="T34" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -6366,10 +6412,10 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>61</v>
@@ -6378,7 +6424,7 @@
         <v>1184.780029296875</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4177439815420458</v>
+        <v>0.4223319652769435</v>
       </c>
       <c r="G35" s="20">
         <v>-1.110237185891371</v>
@@ -6390,16 +6436,16 @@
         <v>0.7254634342718127</v>
       </c>
       <c r="J35" s="20">
-        <v>0.4881829362998821</v>
+        <v>0.4884287992023069</v>
       </c>
       <c r="K35" s="20">
-        <v>0.7624758839652448</v>
+        <v>0.8003741704712637</v>
       </c>
       <c r="L35" s="20">
-        <v>0.3804182993161547</v>
+        <v>0.3803984343128673</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.05243254735385355</v>
+        <v>-0.05283726755828755</v>
       </c>
       <c r="N35" s="20">
         <v>39.686787</v>
@@ -6417,10 +6463,10 @@
         <v>0.353297727248485</v>
       </c>
       <c r="S35" s="11">
-        <v>56.10746417685041</v>
+        <v>56.10746417697418</v>
       </c>
       <c r="T35" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -6428,61 +6474,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E36" s="10">
-        <v>206.3699951171875</v>
+        <v>196.4600067138672</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4050379680416604</v>
+        <v>0.4062104593001394</v>
       </c>
       <c r="G36" s="20">
-        <v>0.4853183280948471</v>
+        <v>0.59238818351296</v>
       </c>
       <c r="H36" s="20">
-        <v>-0.3300127972283673</v>
+        <v>-0.6603051797569764</v>
       </c>
       <c r="I36" s="20">
-        <v>2.301619691710589</v>
+        <v>4.097268549112698</v>
       </c>
       <c r="J36" s="20">
-        <v>0.5649244781974105</v>
+        <v>-0.3920798867037227</v>
       </c>
       <c r="K36" s="20">
-        <v>-0.1667470345479109</v>
+        <v>0.619199233164106</v>
       </c>
       <c r="L36" s="20">
-        <v>0.7639120797299145</v>
+        <v>0.5059954604815103</v>
       </c>
       <c r="M36" s="20">
-        <v>-0.6872709590900115</v>
+        <v>0.105786131502331</v>
       </c>
       <c r="N36" s="20">
-        <v>19.639769</v>
+        <v>11.024229</v>
       </c>
       <c r="O36" s="20">
-        <v>2.1120868</v>
+        <v>1.1926677</v>
       </c>
       <c r="P36" s="12">
-        <v>0.12231</v>
+        <v>0.09031</v>
       </c>
       <c r="Q36" s="12">
-        <v>0.535</v>
+        <v>11.11</v>
       </c>
       <c r="R36" s="12">
-        <v>-0.005078309454742191</v>
+        <v>0.124361503726621</v>
       </c>
       <c r="S36" s="11">
-        <v>51.20657389401402</v>
+        <v>35.16621525115893</v>
       </c>
       <c r="T36" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -6490,61 +6536,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E37" s="10">
-        <v>196.4600067138672</v>
+        <v>206.3699951171875</v>
       </c>
       <c r="F37" s="17">
-        <v>0.402290247644652</v>
+        <v>0.4059522381644055</v>
       </c>
       <c r="G37" s="20">
-        <v>0.59238818351296</v>
+        <v>0.4853183280948471</v>
       </c>
       <c r="H37" s="20">
-        <v>-0.6603051797569764</v>
+        <v>-0.3300127972283673</v>
       </c>
       <c r="I37" s="20">
-        <v>4.097268549112698</v>
+        <v>2.301619691710589</v>
       </c>
       <c r="J37" s="20">
-        <v>-0.3923388983499679</v>
+        <v>0.5650921052231415</v>
       </c>
       <c r="K37" s="20">
-        <v>0.5870176226290656</v>
+        <v>-0.1591241325663561</v>
       </c>
       <c r="L37" s="20">
-        <v>0.5060161277592696</v>
+        <v>0.7638897651040981</v>
       </c>
       <c r="M37" s="20">
-        <v>0.1060116948263984</v>
+        <v>-0.6878888009051602</v>
       </c>
       <c r="N37" s="20">
-        <v>11.024229</v>
+        <v>19.639769</v>
       </c>
       <c r="O37" s="20">
-        <v>1.1926677</v>
+        <v>2.1120868</v>
       </c>
       <c r="P37" s="12">
-        <v>0.09031</v>
+        <v>0.12231</v>
       </c>
       <c r="Q37" s="12">
-        <v>11.11</v>
+        <v>0.535</v>
       </c>
       <c r="R37" s="12">
-        <v>0.124361503726621</v>
+        <v>-0.005078382644663759</v>
       </c>
       <c r="S37" s="11">
-        <v>35.16621525115819</v>
+        <v>51.20657389218366</v>
       </c>
       <c r="T37" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -6552,61 +6598,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E38" s="10">
-        <v>453.2300109863281</v>
+        <v>227.5500030517578</v>
       </c>
       <c r="F38" s="17">
-        <v>0.3949353172240869</v>
+        <v>0.4024313864468855</v>
       </c>
       <c r="G38" s="20">
-        <v>-0.8384379108839474</v>
+        <v>1.23099937351617</v>
       </c>
       <c r="H38" s="20">
-        <v>2.151739124777599</v>
+        <v>0.1667435013429619</v>
       </c>
       <c r="I38" s="20">
-        <v>2.646453673822382</v>
+        <v>-0.05584647993229746</v>
       </c>
       <c r="J38" s="20">
-        <v>0.3464626300875213</v>
+        <v>-0.2682271390085824</v>
       </c>
       <c r="K38" s="20">
-        <v>-0.2156535039433402</v>
+        <v>1.881176382682929</v>
       </c>
       <c r="L38" s="20">
-        <v>-3.017781627758584</v>
+        <v>0.4023852252451754</v>
       </c>
       <c r="M38" s="20">
-        <v>0.4992130368625332</v>
+        <v>-0.1207368842719567</v>
       </c>
       <c r="N38" s="20">
-        <v>16.975473</v>
+        <v>4.5574694</v>
       </c>
       <c r="O38" s="20">
-        <v>22.350464</v>
+        <v>1.8238496</v>
       </c>
       <c r="P38" s="12">
-        <v>1.30853</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.438</v>
+        <v>0.118</v>
       </c>
       <c r="R38" s="12">
-        <v>0.6470316659633728</v>
+        <v>0.1331496207603819</v>
       </c>
       <c r="S38" s="11">
-        <v>48.70413616151452</v>
+        <v>27.93485608509751</v>
       </c>
       <c r="T38" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -6614,61 +6660,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>14</v>
+        <v>155</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>64</v>
+        <v>156</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E39" s="10">
-        <v>227.5500030517578</v>
+        <v>916.280029296875</v>
       </c>
       <c r="F39" s="17">
-        <v>0.3937367775139732</v>
+        <v>0.4016294230556103</v>
       </c>
       <c r="G39" s="20">
-        <v>1.23099937351617</v>
+        <v>0.4149604359308066</v>
       </c>
       <c r="H39" s="20">
-        <v>0.1667435013429619</v>
+        <v>0.8229528906242468</v>
       </c>
       <c r="I39" s="20">
-        <v>-0.05584647993229746</v>
+        <v>0.9059327383427908</v>
       </c>
       <c r="J39" s="20">
-        <v>-0.2684847993969363</v>
+        <v>-0.3460240591209282</v>
       </c>
       <c r="K39" s="20">
-        <v>1.809175167108658</v>
+        <v>1.685424151569448</v>
       </c>
       <c r="L39" s="20">
-        <v>0.402405230693198</v>
+        <v>-0.07745571202990834</v>
       </c>
       <c r="M39" s="20">
-        <v>-0.1204664502016454</v>
+        <v>0.1359308815455718</v>
       </c>
       <c r="N39" s="20">
-        <v>4.5574694</v>
+        <v>14.451568</v>
       </c>
       <c r="O39" s="20">
-        <v>1.8238496</v>
+        <v>2.5837662</v>
       </c>
       <c r="P39" s="12">
-        <v>0.46113998</v>
+        <v>0.16902</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.118</v>
+        <v>0.425</v>
       </c>
       <c r="R39" s="12">
-        <v>0.1331496207603819</v>
+        <v>0.1518708779153592</v>
       </c>
       <c r="S39" s="11">
-        <v>27.9348560686997</v>
+        <v>33.11340495895067</v>
       </c>
       <c r="T39" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -6676,61 +6722,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>155</v>
+        <v>43</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E40" s="10">
-        <v>916.280029296875</v>
+        <v>453.2300109863281</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3936655234981025</v>
+        <v>0.3957304375489474</v>
       </c>
       <c r="G40" s="20">
-        <v>0.4149604359308066</v>
+        <v>-0.8384379108839474</v>
       </c>
       <c r="H40" s="20">
-        <v>0.8229528906242468</v>
+        <v>2.151739124777599</v>
       </c>
       <c r="I40" s="20">
-        <v>0.9059327383427908</v>
+        <v>2.646453673822382</v>
       </c>
       <c r="J40" s="20">
-        <v>-0.3462979381971125</v>
+        <v>0.3467417450804187</v>
       </c>
       <c r="K40" s="20">
-        <v>1.619599574400603</v>
+        <v>-0.2096240432525466</v>
       </c>
       <c r="L40" s="20">
-        <v>-0.07743877165552872</v>
+        <v>-3.017779786263553</v>
       </c>
       <c r="M40" s="20">
-        <v>0.1361333440848979</v>
+        <v>0.4990597875424628</v>
       </c>
       <c r="N40" s="20">
-        <v>14.451568</v>
+        <v>16.975473</v>
       </c>
       <c r="O40" s="20">
-        <v>2.5837662</v>
+        <v>22.350464</v>
       </c>
       <c r="P40" s="12">
-        <v>0.16902</v>
+        <v>1.30853</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.425</v>
+        <v>0.438</v>
       </c>
       <c r="R40" s="12">
-        <v>0.1518708779153592</v>
+        <v>0.6470316659633728</v>
       </c>
       <c r="S40" s="11">
-        <v>33.11340497456116</v>
+        <v>48.70413616150016</v>
       </c>
       <c r="T40" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -6738,10 +6784,10 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>61</v>
@@ -6750,7 +6796,7 @@
         <v>175.2100067138672</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3920734652803153</v>
+        <v>0.3930162745520817</v>
       </c>
       <c r="G41" s="20">
         <v>-0.2374479080738863</v>
@@ -6762,16 +6808,16 @@
         <v>-0.4072863312933673</v>
       </c>
       <c r="J41" s="20">
-        <v>1.538382486132149</v>
+        <v>1.53851837986278</v>
       </c>
       <c r="K41" s="20">
-        <v>-0.1581757976435574</v>
+        <v>-0.1502736327553743</v>
       </c>
       <c r="L41" s="20">
-        <v>0.4379489276455764</v>
+        <v>0.4379286951569987</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.2265379075588161</v>
+        <v>-0.2271004661174427</v>
       </c>
       <c r="N41" s="20">
         <v>34.14822</v>
@@ -6789,10 +6835,10 @@
         <v>0.5960411169627278</v>
       </c>
       <c r="S41" s="11">
-        <v>76.76883688667752</v>
+        <v>76.76883688666288</v>
       </c>
       <c r="T41" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -6800,61 +6846,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>61</v>
+        <v>161</v>
       </c>
       <c r="E42" s="10">
-        <v>418.1300048828125</v>
+        <v>262.8699951171875</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3770853258882171</v>
+        <v>0.3897912908289492</v>
       </c>
       <c r="G42" s="20">
-        <v>-0.2196120997092874</v>
+        <v>-3.850609330339901</v>
       </c>
       <c r="H42" s="20">
-        <v>1.242182663983196</v>
+        <v>-0.4558428702845563</v>
       </c>
       <c r="I42" s="20">
-        <v>-0.09888920711276358</v>
+        <v>4.097268549112698</v>
       </c>
       <c r="J42" s="20">
-        <v>0.7708716588010035</v>
+        <v>1.514835964631135</v>
       </c>
       <c r="K42" s="20">
-        <v>-0.008935437426577335</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L42" s="20">
-        <v>0.1143779289087324</v>
+        <v>-3.017779786263553</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.1162090321722734</v>
+        <v>-0.2796512063931901</v>
       </c>
       <c r="N42" s="20">
-        <v>25.768177</v>
+        <v>384.93335</v>
       </c>
       <c r="O42" s="20">
-        <v>19.177149</v>
+        <v>52.538673</v>
       </c>
       <c r="P42" s="12">
-        <v>0.91473</v>
+        <v>0.22213</v>
       </c>
       <c r="Q42" s="12">
-        <v>0.095</v>
+        <v>1.655</v>
       </c>
       <c r="R42" s="12">
-        <v>0.214982648658705</v>
+        <v>0.9729059162390545</v>
       </c>
       <c r="S42" s="11">
-        <v>58.26064928131711</v>
+        <v>52.71776508782204</v>
       </c>
       <c r="T42" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -6862,61 +6908,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>162</v>
+        <v>61</v>
       </c>
       <c r="E43" s="10">
-        <v>262.8699951171875</v>
+        <v>418.1300048828125</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3767724079725336</v>
+        <v>0.3786346422075749</v>
       </c>
       <c r="G43" s="20">
-        <v>-3.850609330339901</v>
+        <v>-0.2196120997092874</v>
       </c>
       <c r="H43" s="20">
-        <v>-0.4558428702845563</v>
+        <v>1.242182663983196</v>
       </c>
       <c r="I43" s="20">
-        <v>4.097268549112698</v>
+        <v>-0.09888920711276358</v>
       </c>
       <c r="J43" s="20">
-        <v>1.514626221301193</v>
+        <v>0.7710514738671556</v>
       </c>
       <c r="K43" s="20">
-        <v>4.017529145995051</v>
+        <v>0.003829187482897866</v>
       </c>
       <c r="L43" s="20">
-        <v>-3.017781627758584</v>
+        <v>0.1143597632771644</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.2791796809534242</v>
+        <v>-0.1166501978189085</v>
       </c>
       <c r="N43" s="20">
-        <v>384.93335</v>
+        <v>25.768177</v>
       </c>
       <c r="O43" s="20">
-        <v>52.538673</v>
+        <v>19.177149</v>
       </c>
       <c r="P43" s="12">
-        <v>0.22213</v>
+        <v>0.91473</v>
       </c>
       <c r="Q43" s="12">
-        <v>1.655</v>
+        <v>0.095</v>
       </c>
       <c r="R43" s="12">
-        <v>0.9729059162390545</v>
+        <v>0.2149827563991888</v>
       </c>
       <c r="S43" s="11">
-        <v>52.71776508782204</v>
+        <v>58.26064927610839</v>
       </c>
       <c r="T43" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -6924,61 +6970,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E44" s="10">
-        <v>151.0200042724609</v>
+        <v>359.739990234375</v>
       </c>
       <c r="F44" s="17">
-        <v>0.369790550716444</v>
+        <v>0.3723854701971951</v>
       </c>
       <c r="G44" s="20">
-        <v>-0.2351435193636175</v>
+        <v>-0.5841071338335053</v>
       </c>
       <c r="H44" s="20">
-        <v>-0.3192964222125583</v>
+        <v>0.2793198048091971</v>
       </c>
       <c r="I44" s="20">
-        <v>-0.6222982617295744</v>
+        <v>0.8280381860846351</v>
       </c>
       <c r="J44" s="20">
-        <v>1.875230128844491</v>
+        <v>0.9769890779368873</v>
       </c>
       <c r="K44" s="20">
-        <v>0.1907239634042472</v>
+        <v>0.613993056804705</v>
       </c>
       <c r="L44" s="20">
-        <v>-0.1976055930026395</v>
+        <v>-0.2733111740760106</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.6020742594104574</v>
+        <v>-0.004343160547240599</v>
       </c>
       <c r="N44" s="20">
-        <v>72.30144</v>
+        <v>49.005413</v>
       </c>
       <c r="O44" s="20">
-        <v>2.3325565</v>
+        <v>9.385771999999999</v>
       </c>
       <c r="P44" s="12">
-        <v>0.03211</v>
+        <v>0.20897</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.013</v>
+        <v>0.365</v>
       </c>
       <c r="R44" s="12">
-        <v>0.8025380420831225</v>
+        <v>0.2891134285874886</v>
       </c>
       <c r="S44" s="11">
-        <v>73.51123701083746</v>
+        <v>64.41720015945053</v>
       </c>
       <c r="T44" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -7044,110 +7090,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B6" s="12">
         <v>0.18</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B7" s="12">
         <v>0.16</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B8" s="12">
         <v>0.1</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B9" s="12">
         <v>0.3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B10" s="12">
         <v>0.12</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B11" s="12">
         <v>0.06</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B12" s="12">
         <v>0.08</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B13" s="12">
         <f>SUM(B6:B12)</f>
@@ -7156,22 +7202,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B19" s="14"/>
       <c r="C19" s="14"/>
@@ -7250,57 +7296,57 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>38</v>
@@ -7308,113 +7354,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B19" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="21" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B23" s="21"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="21" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B24" s="21"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="21" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B25" s="21"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="21" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" s="21"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="21" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" s="21"/>
     </row>
@@ -7432,3151 +7478,3100 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI17"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:60">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>411.1206359863281</v>
+        <v>416.5915832519531</v>
       </c>
       <c r="C1">
-        <v>416.5915832519531</v>
+        <v>431.2573547363281</v>
       </c>
       <c r="D1">
-        <v>431.2573547363281</v>
+        <v>449.4772644042969</v>
       </c>
       <c r="E1">
-        <v>449.4772644042969</v>
+        <v>434.2524108886719</v>
       </c>
       <c r="F1">
-        <v>434.2524108886719</v>
+        <v>426.4053649902344</v>
       </c>
       <c r="G1">
-        <v>426.4053649902344</v>
+        <v>456.7851867675781</v>
       </c>
       <c r="H1">
-        <v>456.7851867675781</v>
+        <v>411.9991760253906</v>
       </c>
       <c r="I1">
-        <v>411.9991760253906</v>
+        <v>390.7343444824219</v>
       </c>
       <c r="J1">
-        <v>390.7343444824219</v>
+        <v>395.6861267089844</v>
       </c>
       <c r="K1">
-        <v>395.6861267089844</v>
+        <v>381.25</v>
       </c>
       <c r="L1">
-        <v>381.25</v>
+        <v>404.1499938964844</v>
       </c>
       <c r="M1">
-        <v>404.1499938964844</v>
+        <v>441.7999877929688</v>
       </c>
       <c r="N1">
-        <v>441.7999877929688</v>
+        <v>439.3399963378906</v>
       </c>
       <c r="O1">
-        <v>439.3399963378906</v>
+        <v>437.5</v>
       </c>
       <c r="P1">
-        <v>437.5</v>
+        <v>426.9100036621094</v>
       </c>
       <c r="Q1">
-        <v>426.9100036621094</v>
+        <v>392.1000061035156</v>
       </c>
       <c r="R1">
-        <v>392.1000061035156</v>
+        <v>369.6400146484375</v>
       </c>
       <c r="S1">
-        <v>369.6400146484375</v>
+        <v>404.8099975585938</v>
       </c>
       <c r="T1">
-        <v>404.8099975585938</v>
+        <v>405.3699951171875</v>
       </c>
       <c r="U1">
-        <v>405.3699951171875</v>
+        <v>429.0199890136719</v>
       </c>
       <c r="V1">
-        <v>429.0199890136719</v>
+        <v>467.2699890136719</v>
       </c>
       <c r="W1">
-        <v>467.2699890136719</v>
+        <v>462.7000122070312</v>
       </c>
       <c r="X1">
-        <v>462.7000122070312</v>
+        <v>437.6499938964844</v>
       </c>
       <c r="Y1">
-        <v>437.6499938964844</v>
+        <v>453.7699890136719</v>
       </c>
       <c r="Z1">
-        <v>453.7699890136719</v>
+        <v>457.8800048828125</v>
       </c>
       <c r="AA1">
-        <v>457.8800048828125</v>
+        <v>440.9700012207031</v>
       </c>
       <c r="AB1">
-        <v>440.9700012207031</v>
+        <v>484.5</v>
       </c>
       <c r="AC1">
-        <v>484.5</v>
+        <v>494.510009765625</v>
       </c>
       <c r="AD1">
-        <v>494.510009765625</v>
+        <v>490.8099975585938</v>
       </c>
       <c r="AE1">
-        <v>490.8099975585938</v>
+        <v>479.8099975585938</v>
       </c>
       <c r="AF1">
-        <v>479.8099975585938</v>
+        <v>468.6499938964844</v>
       </c>
       <c r="AG1">
-        <v>468.6499938964844</v>
+        <v>437.5499877929688</v>
       </c>
       <c r="AH1">
-        <v>437.5499877929688</v>
+        <v>434.7799987792969</v>
       </c>
       <c r="AI1">
-        <v>434.7799987792969</v>
+        <v>442.0799865722656</v>
       </c>
       <c r="AJ1">
-        <v>442.0799865722656</v>
+        <v>433.1900024414062</v>
       </c>
       <c r="AK1">
-        <v>433.1900024414062</v>
+        <v>451.5</v>
       </c>
       <c r="AL1">
-        <v>451.5</v>
+        <v>463.8200073242188</v>
       </c>
       <c r="AM1">
-        <v>463.8200073242188</v>
+        <v>472.260009765625</v>
       </c>
       <c r="AN1">
-        <v>472.260009765625</v>
+        <v>456.239990234375</v>
       </c>
       <c r="AO1">
-        <v>456.239990234375</v>
+        <v>456.010009765625</v>
       </c>
       <c r="AP1">
-        <v>456.010009765625</v>
+        <v>425</v>
       </c>
       <c r="AQ1">
-        <v>425</v>
+        <v>492.2000122070312</v>
       </c>
       <c r="AR1">
-        <v>492.2000122070312</v>
+        <v>516.3900146484375</v>
       </c>
       <c r="AS1">
-        <v>516.3900146484375</v>
+        <v>524.1400146484375</v>
       </c>
       <c r="AT1">
-        <v>524.1400146484375</v>
+        <v>533.8800048828125</v>
       </c>
       <c r="AU1">
-        <v>533.8800048828125</v>
+        <v>535.25</v>
       </c>
       <c r="AV1">
-        <v>535.25</v>
+        <v>506.6199951171875</v>
       </c>
       <c r="AW1">
-        <v>506.6199951171875</v>
+        <v>567.2899780273438</v>
       </c>
       <c r="AX1">
-        <v>567.2899780273438</v>
+        <v>534.280029296875</v>
       </c>
       <c r="AY1">
-        <v>534.280029296875</v>
+        <v>543.510009765625</v>
       </c>
       <c r="AZ1">
-        <v>543.510009765625</v>
+        <v>563.2899780273438</v>
       </c>
       <c r="BA1">
-        <v>563.2899780273438</v>
+        <v>588.4000244140625</v>
       </c>
       <c r="BB1">
-        <v>588.4000244140625</v>
+        <v>568.0599975585938</v>
       </c>
       <c r="BC1">
-        <v>568.0599975585938</v>
+        <v>575.3099975585938</v>
       </c>
       <c r="BD1">
-        <v>575.3099975585938</v>
+        <v>548.9199829101562</v>
       </c>
       <c r="BE1">
-        <v>548.9199829101562</v>
+        <v>549.8300170898438</v>
       </c>
       <c r="BF1">
-        <v>549.8300170898438</v>
+        <v>536.02001953125</v>
       </c>
       <c r="BG1">
-        <v>536.02001953125</v>
+        <v>562.8900146484375</v>
       </c>
       <c r="BH1">
-        <v>562.8900146484375</v>
-      </c>
-      <c r="BI1">
         <v>543.4299926757812</v>
       </c>
     </row>
-    <row r="2" spans="1:61">
+    <row r="2" spans="1:60">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>984.75</v>
+        <v>938.3800048828125</v>
       </c>
       <c r="C2">
-        <v>938.3800048828125</v>
+        <v>948.7999877929688</v>
       </c>
       <c r="D2">
-        <v>948.7999877929688</v>
+        <v>991.6400146484375</v>
       </c>
       <c r="E2">
-        <v>991.6400146484375</v>
+        <v>979.2999877929688</v>
       </c>
       <c r="F2">
-        <v>979.2999877929688</v>
+        <v>937</v>
       </c>
       <c r="G2">
-        <v>937</v>
+        <v>983.1199951171875</v>
       </c>
       <c r="H2">
-        <v>983.1199951171875</v>
+        <v>904.280029296875</v>
       </c>
       <c r="I2">
-        <v>904.280029296875</v>
+        <v>853.2000122070312</v>
       </c>
       <c r="J2">
-        <v>853.2000122070312</v>
+        <v>848.9500122070312</v>
       </c>
       <c r="K2">
-        <v>848.9500122070312</v>
+        <v>865.4600219726562</v>
       </c>
       <c r="L2">
-        <v>865.4600219726562</v>
+        <v>970.8200073242188</v>
       </c>
       <c r="M2">
-        <v>970.8200073242188</v>
+        <v>959.47998046875</v>
       </c>
       <c r="N2">
-        <v>959.47998046875</v>
+        <v>990.2100219726562</v>
       </c>
       <c r="O2">
-        <v>990.2100219726562</v>
+        <v>920.9500122070312</v>
       </c>
       <c r="P2">
-        <v>920.9500122070312</v>
+        <v>900.2000122070312</v>
       </c>
       <c r="Q2">
-        <v>900.2000122070312</v>
+        <v>820.530029296875</v>
       </c>
       <c r="R2">
-        <v>820.530029296875</v>
+        <v>739</v>
       </c>
       <c r="S2">
-        <v>739</v>
+        <v>874.6599731445312</v>
       </c>
       <c r="T2">
-        <v>874.6599731445312</v>
+        <v>823.030029296875</v>
       </c>
       <c r="U2">
-        <v>823.030029296875</v>
+        <v>829.5</v>
       </c>
       <c r="V2">
-        <v>829.5</v>
+        <v>892.6699829101562</v>
       </c>
       <c r="W2">
-        <v>892.6699829101562</v>
+        <v>893.1900024414062</v>
       </c>
       <c r="X2">
-        <v>893.1900024414062</v>
+        <v>881.469970703125</v>
       </c>
       <c r="Y2">
-        <v>881.469970703125</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="Z2">
-        <v>877.5700073242188</v>
+        <v>861</v>
       </c>
       <c r="AA2">
-        <v>861</v>
+        <v>868.52001953125</v>
       </c>
       <c r="AB2">
-        <v>868.52001953125</v>
+        <v>911.2899780273438</v>
       </c>
       <c r="AC2">
-        <v>911.2899780273438</v>
+        <v>949.8300170898438</v>
       </c>
       <c r="AD2">
-        <v>949.8300170898438</v>
+        <v>971.6599731445312</v>
       </c>
       <c r="AE2">
-        <v>971.6599731445312</v>
+        <v>1011.75</v>
       </c>
       <c r="AF2">
-        <v>1011.75</v>
+        <v>940.760009765625</v>
       </c>
       <c r="AG2">
-        <v>940.760009765625</v>
+        <v>937.1099853515625</v>
       </c>
       <c r="AH2">
-        <v>937.1099853515625</v>
+        <v>974.3300170898438</v>
       </c>
       <c r="AI2">
-        <v>974.3300170898438</v>
+        <v>966.780029296875</v>
       </c>
       <c r="AJ2">
-        <v>966.780029296875</v>
+        <v>910.4299926757812</v>
       </c>
       <c r="AK2">
-        <v>910.4299926757812</v>
+        <v>932.969970703125</v>
       </c>
       <c r="AL2">
-        <v>932.969970703125</v>
+        <v>938.4000244140625</v>
       </c>
       <c r="AM2">
-        <v>938.4000244140625</v>
+        <v>935.3900146484375</v>
       </c>
       <c r="AN2">
-        <v>935.3900146484375</v>
+        <v>932.8599853515625</v>
       </c>
       <c r="AO2">
-        <v>932.8599853515625</v>
+        <v>958.72998046875</v>
       </c>
       <c r="AP2">
-        <v>958.72998046875</v>
+        <v>933.4400024414062</v>
       </c>
       <c r="AQ2">
-        <v>933.4400024414062</v>
+        <v>956.0800170898438</v>
       </c>
       <c r="AR2">
-        <v>956.0800170898438</v>
+        <v>958.1599731445312</v>
       </c>
       <c r="AS2">
-        <v>958.1599731445312</v>
+        <v>1016.590026855469</v>
       </c>
       <c r="AT2">
-        <v>1016.590026855469</v>
+        <v>1000.260009765625</v>
       </c>
       <c r="AU2">
-        <v>1000.260009765625</v>
+        <v>1027.77001953125</v>
       </c>
       <c r="AV2">
-        <v>1027.77001953125</v>
+        <v>977.4099731445312</v>
       </c>
       <c r="AW2">
-        <v>977.4099731445312</v>
+        <v>975.260009765625</v>
       </c>
       <c r="AX2">
-        <v>975.260009765625</v>
+        <v>924.030029296875</v>
       </c>
       <c r="AY2">
-        <v>924.030029296875</v>
+        <v>927.5999755859375</v>
       </c>
       <c r="AZ2">
-        <v>927.5999755859375</v>
+        <v>926.5499877929688</v>
       </c>
       <c r="BA2">
-        <v>926.5499877929688</v>
+        <v>977.5</v>
       </c>
       <c r="BB2">
-        <v>977.5</v>
+        <v>1015.799987792969</v>
       </c>
       <c r="BC2">
-        <v>1015.799987792969</v>
+        <v>1043.9599609375</v>
       </c>
       <c r="BD2">
-        <v>1043.9599609375</v>
+        <v>1096.160034179688</v>
       </c>
       <c r="BE2">
-        <v>1096.160034179688</v>
+        <v>1071.880004882812</v>
       </c>
       <c r="BF2">
-        <v>1071.880004882812</v>
+        <v>1080.530029296875</v>
       </c>
       <c r="BG2">
-        <v>1080.530029296875</v>
+        <v>1082.280029296875</v>
       </c>
       <c r="BH2">
-        <v>1082.280029296875</v>
-      </c>
-      <c r="BI2">
         <v>1053.97998046875</v>
       </c>
     </row>
-    <row r="3" spans="1:61">
+    <row r="3" spans="1:60">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1744.430053710938</v>
+        <v>1617.699951171875</v>
       </c>
       <c r="C3">
-        <v>1617.699951171875</v>
+        <v>1727.180053710938</v>
       </c>
       <c r="D3">
-        <v>1727.180053710938</v>
+        <v>1858.27001953125</v>
       </c>
       <c r="E3">
-        <v>1858.27001953125</v>
+        <v>1915.920043945312</v>
       </c>
       <c r="F3">
-        <v>1915.920043945312</v>
+        <v>1673.969970703125</v>
       </c>
       <c r="G3">
-        <v>1673.969970703125</v>
+        <v>1757.819946289062</v>
       </c>
       <c r="H3">
-        <v>1757.819946289062</v>
+        <v>1615</v>
       </c>
       <c r="I3">
-        <v>1615</v>
+        <v>1411.079956054688</v>
       </c>
       <c r="J3">
-        <v>1411.079956054688</v>
+        <v>1354.819946289062</v>
       </c>
       <c r="K3">
-        <v>1354.819946289062</v>
+        <v>1390.949951171875</v>
       </c>
       <c r="L3">
-        <v>1390.949951171875</v>
+        <v>1589.400024414062</v>
       </c>
       <c r="M3">
-        <v>1589.400024414062</v>
+        <v>1599.27001953125</v>
       </c>
       <c r="N3">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="O3">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="P3">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="Q3">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="R3">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="S3">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="T3">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="U3">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="V3">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="W3">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="X3">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="Y3">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="Z3">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="AA3">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="AB3">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="AC3">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="AD3">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="AE3">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="AF3">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="AG3">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="AH3">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="AI3">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="AJ3">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="AK3">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="AL3">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AM3">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="AN3">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="AO3">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="AP3">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="AQ3">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="AR3">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="AS3">
-        <v>1554.989990234375</v>
+        <v>1740</v>
       </c>
       <c r="AT3">
-        <v>1740</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="AU3">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="AV3">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="AW3">
-        <v>1692.589965820312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="AX3">
-        <v>1633.349975585938</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="AY3">
-        <v>1551.989990234375</v>
+        <v>1530.89501953125</v>
       </c>
       <c r="AZ3">
-        <v>1530.89501953125</v>
+        <v>1519.969970703125</v>
       </c>
       <c r="BA3">
-        <v>1519.969970703125</v>
+        <v>1614.390014648438</v>
       </c>
       <c r="BB3">
-        <v>1614.390014648438</v>
+        <v>1791.819946289062</v>
       </c>
       <c r="BC3">
-        <v>1791.819946289062</v>
+        <v>1766.640014648438</v>
       </c>
       <c r="BD3">
-        <v>1766.640014648438</v>
+        <v>1887.0400390625</v>
       </c>
       <c r="BE3">
-        <v>1887.0400390625</v>
+        <v>1816.569946289062</v>
       </c>
       <c r="BF3">
-        <v>1816.569946289062</v>
+        <v>1753.619995117188</v>
       </c>
       <c r="BG3">
-        <v>1753.619995117188</v>
+        <v>1777.800048828125</v>
       </c>
       <c r="BH3">
-        <v>1777.800048828125</v>
-      </c>
-      <c r="BI3">
         <v>1712.890014648438</v>
       </c>
     </row>
-    <row r="4" spans="1:61">
+    <row r="4" spans="1:60">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>577.2747192382812</v>
+        <v>531.92919921875</v>
       </c>
       <c r="C4">
-        <v>531.92919921875</v>
+        <v>550.1234130859375</v>
       </c>
       <c r="D4">
-        <v>550.1234130859375</v>
+        <v>577.864501953125</v>
       </c>
       <c r="E4">
-        <v>577.864501953125</v>
+        <v>582.403076171875</v>
       </c>
       <c r="F4">
-        <v>582.403076171875</v>
+        <v>555.3717041015625</v>
       </c>
       <c r="G4">
-        <v>555.3717041015625</v>
+        <v>563.1392211914062</v>
       </c>
       <c r="H4">
-        <v>563.1392211914062</v>
+        <v>513.6751098632812</v>
       </c>
       <c r="I4">
-        <v>513.6751098632812</v>
+        <v>466.6601867675781</v>
       </c>
       <c r="J4">
-        <v>466.6601867675781</v>
+        <v>477.0668640136719</v>
       </c>
       <c r="K4">
-        <v>477.0668640136719</v>
+        <v>487.2635803222656</v>
       </c>
       <c r="L4">
-        <v>487.2635803222656</v>
+        <v>548.2140502929688</v>
       </c>
       <c r="M4">
-        <v>548.2140502929688</v>
+        <v>556.4913330078125</v>
       </c>
       <c r="N4">
-        <v>556.4913330078125</v>
+        <v>558.120849609375</v>
       </c>
       <c r="O4">
-        <v>558.120849609375</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="P4">
-        <v>519.6331787109375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="Q4">
-        <v>497.7602233886719</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="R4">
-        <v>463.3612670898438</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="S4">
-        <v>461.8917236328125</v>
+        <v>532.868896484375</v>
       </c>
       <c r="T4">
-        <v>532.868896484375</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="U4">
-        <v>544.6651611328125</v>
+        <v>527.05078125</v>
       </c>
       <c r="V4">
-        <v>527.05078125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="W4">
-        <v>548.3839721679688</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="X4">
-        <v>519.0033569335938</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="Y4">
-        <v>451.3750915527344</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="Z4">
-        <v>434.1606140136719</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="AA4">
-        <v>438.1993408203125</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="AB4">
-        <v>437.7894592285156</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="AC4">
-        <v>453.9542846679688</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="AD4">
-        <v>487.1336364746094</v>
+        <v>508.63671875</v>
       </c>
       <c r="AE4">
-        <v>508.63671875</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="AF4">
-        <v>535.8380126953125</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="AG4">
-        <v>496.0007934570312</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="AH4">
-        <v>461.9417114257812</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="AI4">
-        <v>468.8994750976562</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="AJ4">
-        <v>459.2925720214844</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="AK4">
-        <v>435.2402954101562</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="AL4">
-        <v>450.6053466796875</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AM4">
-        <v>468.7295227050781</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="AN4">
-        <v>461.8517456054688</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="AO4">
-        <v>459.3025817871094</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="AP4">
-        <v>450.4053955078125</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="AQ4">
-        <v>450.2954406738281</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="AR4">
-        <v>448.7559509277344</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="AS4">
-        <v>441.4283142089844</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="AT4">
-        <v>467.3099670410156</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="AU4">
-        <v>477.2999877929688</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="AV4">
-        <v>482.2799987792969</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="AW4">
-        <v>460.9299926757812</v>
+        <v>447.1799926757812</v>
       </c>
       <c r="AX4">
-        <v>447.1799926757812</v>
+        <v>426.9400024414062</v>
       </c>
       <c r="AY4">
-        <v>426.9400024414062</v>
+        <v>411.9599914550781</v>
       </c>
       <c r="AZ4">
-        <v>411.9599914550781</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="BA4">
-        <v>416.9700012207031</v>
+        <v>423.8699951171875</v>
       </c>
       <c r="BB4">
-        <v>423.8699951171875</v>
+        <v>441.3599853515625</v>
       </c>
       <c r="BC4">
-        <v>441.3599853515625</v>
+        <v>448.1700134277344</v>
       </c>
       <c r="BD4">
-        <v>448.1700134277344</v>
+        <v>464.6000061035156</v>
       </c>
       <c r="BE4">
-        <v>464.6000061035156</v>
+        <v>473.6900024414062</v>
       </c>
       <c r="BF4">
-        <v>473.6900024414062</v>
+        <v>450.3099975585938</v>
       </c>
       <c r="BG4">
-        <v>450.3099975585938</v>
+        <v>456.8099975585938</v>
       </c>
       <c r="BH4">
-        <v>456.8099975585938</v>
-      </c>
-      <c r="BI4">
         <v>453.2300109863281</v>
       </c>
     </row>
-    <row r="5" spans="1:61">
+    <row r="5" spans="1:60">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>269.2793579101562</v>
+        <v>265.1951293945312</v>
       </c>
       <c r="C5">
-        <v>265.1951293945312</v>
+        <v>281.7909851074219</v>
       </c>
       <c r="D5">
-        <v>281.7909851074219</v>
+        <v>280.1672668457031</v>
       </c>
       <c r="E5">
-        <v>280.1672668457031</v>
+        <v>279.6094055175781</v>
       </c>
       <c r="F5">
-        <v>279.6094055175781</v>
+        <v>294.6513061523438</v>
       </c>
       <c r="G5">
-        <v>294.6513061523438</v>
+        <v>300.2695617675781</v>
       </c>
       <c r="H5">
-        <v>300.2695617675781</v>
+        <v>291.5333251953125</v>
       </c>
       <c r="I5">
-        <v>291.5333251953125</v>
+        <v>299.1040954589844</v>
       </c>
       <c r="J5">
-        <v>299.1040954589844</v>
+        <v>308.4579162597656</v>
       </c>
       <c r="K5">
-        <v>308.4579162597656</v>
+        <v>312.1038208007812</v>
       </c>
       <c r="L5">
-        <v>312.1038208007812</v>
+        <v>313.5880737304688</v>
       </c>
       <c r="M5">
-        <v>313.5880737304688</v>
+        <v>309.7230529785156</v>
       </c>
       <c r="N5">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="O5">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="P5">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="Q5">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="R5">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="S5">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="T5">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="U5">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="V5">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="W5">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="X5">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="Y5">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="Z5">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="AA5">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="AB5">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="AC5">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="AD5">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="AE5">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="AF5">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="AG5">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="AH5">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="AI5">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="AJ5">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="AK5">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="AL5">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AM5">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="AN5">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="AO5">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="AP5">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="AQ5">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="AR5">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="AS5">
-        <v>370.6900024414062</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="AT5">
-        <v>370.7200012207031</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="AU5">
-        <v>382.8500061035156</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="AV5">
-        <v>388.9500122070312</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="AW5">
-        <v>385.4299926757812</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="AX5">
-        <v>390.4200134277344</v>
+        <v>382.9500122070312</v>
       </c>
       <c r="AY5">
-        <v>382.9500122070312</v>
+        <v>397.0400085449219</v>
       </c>
       <c r="AZ5">
-        <v>397.0400085449219</v>
+        <v>403.2799987792969</v>
       </c>
       <c r="BA5">
-        <v>403.2799987792969</v>
+        <v>412.5299987792969</v>
       </c>
       <c r="BB5">
-        <v>412.5299987792969</v>
+        <v>413.2799987792969</v>
       </c>
       <c r="BC5">
-        <v>413.2799987792969</v>
+        <v>393.2699890136719</v>
       </c>
       <c r="BD5">
-        <v>393.2699890136719</v>
+        <v>377.1400146484375</v>
       </c>
       <c r="BE5">
-        <v>377.1400146484375</v>
+        <v>375.8399963378906</v>
       </c>
       <c r="BF5">
-        <v>375.8399963378906</v>
+        <v>382.8599853515625</v>
       </c>
       <c r="BG5">
-        <v>382.8599853515625</v>
+        <v>387.1799926757812</v>
       </c>
       <c r="BH5">
-        <v>387.1799926757812</v>
-      </c>
-      <c r="BI5">
         <v>389.5700073242188</v>
       </c>
     </row>
-    <row r="6" spans="1:61">
+    <row r="6" spans="1:60">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>268.2554626464844</v>
+        <v>265.6027221679688</v>
       </c>
       <c r="C6">
-        <v>265.6027221679688</v>
+        <v>279.9135437011719</v>
       </c>
       <c r="D6">
-        <v>279.9135437011719</v>
+        <v>282.5263977050781</v>
       </c>
       <c r="E6">
-        <v>282.5263977050781</v>
+        <v>282.9651794433594</v>
       </c>
       <c r="F6">
-        <v>282.9651794433594</v>
+        <v>296.0693359375</v>
       </c>
       <c r="G6">
-        <v>296.0693359375</v>
+        <v>302.5715026855469</v>
       </c>
       <c r="H6">
-        <v>302.5715026855469</v>
+        <v>298.363037109375</v>
       </c>
       <c r="I6">
-        <v>298.363037109375</v>
+        <v>305.0148315429688</v>
       </c>
       <c r="J6">
-        <v>305.0148315429688</v>
+        <v>311.7463989257812</v>
       </c>
       <c r="K6">
-        <v>311.7463989257812</v>
+        <v>314.4490051269531</v>
       </c>
       <c r="L6">
-        <v>314.4490051269531</v>
+        <v>318.8868408203125</v>
       </c>
       <c r="M6">
-        <v>318.8868408203125</v>
+        <v>314.9576110839844</v>
       </c>
       <c r="N6">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="O6">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="P6">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="Q6">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="R6">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="S6">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="T6">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="U6">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="V6">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="W6">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="X6">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="Y6">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="Z6">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="AA6">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="AB6">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="AC6">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="AD6">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="AE6">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="AF6">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="AG6">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="AH6">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="AI6">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="AJ6">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="AK6">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="AL6">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AM6">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="AN6">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="AO6">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="AP6">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="AQ6">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AR6">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="AS6">
-        <v>387.7099914550781</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="AT6">
-        <v>388.8999938964844</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="AU6">
-        <v>397.7699890136719</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="AV6">
-        <v>399.4400024414062</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="AW6">
-        <v>392.4200134277344</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="AX6">
-        <v>395.9299926757812</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="AY6">
-        <v>396.4500122070312</v>
+        <v>410.8399963378906</v>
       </c>
       <c r="AZ6">
-        <v>410.8399963378906</v>
+        <v>413.9200134277344</v>
       </c>
       <c r="BA6">
-        <v>413.9200134277344</v>
+        <v>421.9599914550781</v>
       </c>
       <c r="BB6">
-        <v>421.9599914550781</v>
+        <v>424.8900146484375</v>
       </c>
       <c r="BC6">
-        <v>424.8900146484375</v>
+        <v>402.3800048828125</v>
       </c>
       <c r="BD6">
-        <v>402.3800048828125</v>
+        <v>389.6799926757812</v>
       </c>
       <c r="BE6">
-        <v>389.6799926757812</v>
+        <v>388.3800048828125</v>
       </c>
       <c r="BF6">
-        <v>388.3800048828125</v>
+        <v>390.9500122070312</v>
       </c>
       <c r="BG6">
-        <v>390.9500122070312</v>
+        <v>393.5199890136719</v>
       </c>
       <c r="BH6">
-        <v>393.5199890136719</v>
-      </c>
-      <c r="BI6">
         <v>389.4400024414062</v>
       </c>
     </row>
-    <row r="7" spans="1:61">
+    <row r="7" spans="1:60">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>48.58705139160156</v>
+        <v>51.44394302368164</v>
       </c>
       <c r="C7">
-        <v>51.44394302368164</v>
+        <v>53.34521865844727</v>
       </c>
       <c r="D7">
-        <v>53.34521865844727</v>
+        <v>52.06110763549805</v>
       </c>
       <c r="E7">
-        <v>52.06110763549805</v>
+        <v>52.64841461181641</v>
       </c>
       <c r="F7">
-        <v>52.64841461181641</v>
+        <v>54.55964660644531</v>
       </c>
       <c r="G7">
-        <v>54.55964660644531</v>
+        <v>54.32073974609375</v>
       </c>
       <c r="H7">
-        <v>54.32073974609375</v>
+        <v>53.52439498901367</v>
       </c>
       <c r="I7">
-        <v>53.52439498901367</v>
+        <v>53.40494537353516</v>
       </c>
       <c r="J7">
-        <v>53.40494537353516</v>
+        <v>54.60941696166992</v>
       </c>
       <c r="K7">
-        <v>54.60941696166992</v>
+        <v>54.93790817260742</v>
       </c>
       <c r="L7">
-        <v>54.93790817260742</v>
+        <v>56.24192428588867</v>
       </c>
       <c r="M7">
-        <v>56.24192428588867</v>
+        <v>57.23735809326172</v>
       </c>
       <c r="N7">
-        <v>57.23735809326172</v>
+        <v>57.33689880371094</v>
       </c>
       <c r="O7">
-        <v>57.33689880371094</v>
+        <v>57.03827285766602</v>
       </c>
       <c r="P7">
-        <v>57.03827285766602</v>
+        <v>54.67909622192383</v>
       </c>
       <c r="Q7">
-        <v>54.67909622192383</v>
+        <v>53.68366622924805</v>
       </c>
       <c r="R7">
-        <v>53.68366622924805</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="S7">
-        <v>55.77407073974609</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="T7">
-        <v>55.69443893432617</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="U7">
-        <v>56.80932235717773</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="V7">
-        <v>55.21663284301758</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="W7">
-        <v>54.8383674621582</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="X7">
-        <v>53.56421279907227</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="Y7">
-        <v>55.78402709960938</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="Z7">
-        <v>55.65462112426758</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="AA7">
-        <v>58.38210678100586</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="AB7">
-        <v>58.79023361206055</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="AC7">
-        <v>58.28256225585938</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="AD7">
-        <v>57.43644714355469</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="AE7">
-        <v>58.09342956542969</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="AF7">
-        <v>58.77032470703125</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="AG7">
-        <v>59.52685165405273</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="AH7">
-        <v>59.81552886962891</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="AI7">
-        <v>61.23899841308594</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="AJ7">
+        <v>59.8354377746582</v>
+      </c>
+      <c r="AK7">
+        <v>58.1431999206543</v>
+      </c>
+      <c r="AL7">
+        <v>58.35224151611328</v>
+      </c>
+      <c r="AM7">
+        <v>58.89972686767578</v>
+      </c>
+      <c r="AN7">
+        <v>58.83004760742188</v>
+      </c>
+      <c r="AO7">
+        <v>59.90511703491211</v>
+      </c>
+      <c r="AP7">
+        <v>60.67160034179688</v>
+      </c>
+      <c r="AQ7">
+        <v>60.63178253173828</v>
+      </c>
+      <c r="AR7">
+        <v>60.33315277099609</v>
+      </c>
+      <c r="AS7">
+        <v>59.7657585144043</v>
+      </c>
+      <c r="AT7">
+        <v>60.37297058105469</v>
+      </c>
+      <c r="AU7">
         <v>61.02000045776367</v>
       </c>
-      <c r="AK7">
-        <v>59.8354377746582</v>
-      </c>
-      <c r="AL7">
-        <v>58.1431999206543</v>
-      </c>
-      <c r="AM7">
-        <v>58.35224151611328</v>
-      </c>
-      <c r="AN7">
-        <v>58.89972686767578</v>
-      </c>
-      <c r="AO7">
-        <v>58.83004760742188</v>
-      </c>
-      <c r="AP7">
-        <v>59.90511703491211</v>
-      </c>
-      <c r="AQ7">
-        <v>60.67160034179688</v>
-      </c>
-      <c r="AR7">
-        <v>60.63178253173828</v>
-      </c>
-      <c r="AS7">
-        <v>60.33315277099609</v>
-      </c>
-      <c r="AT7">
-        <v>59.7657585144043</v>
-      </c>
-      <c r="AU7">
-        <v>60.37297058105469</v>
-      </c>
       <c r="AV7">
-        <v>61.02000045776367</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="AW7">
-        <v>61.15999984741211</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="AX7">
-        <v>61.45999908447266</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="AY7">
-        <v>61.77999877929688</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="AZ7">
-        <v>63.52000045776367</v>
+        <v>59.36000061035156</v>
       </c>
       <c r="BA7">
-        <v>59.36000061035156</v>
+        <v>59.29000091552734</v>
       </c>
       <c r="BB7">
-        <v>59.29000091552734</v>
+        <v>58.84000015258789</v>
       </c>
       <c r="BC7">
-        <v>58.84000015258789</v>
+        <v>57.25</v>
       </c>
       <c r="BD7">
-        <v>57.25</v>
+        <v>56.31000137329102</v>
       </c>
       <c r="BE7">
-        <v>56.31000137329102</v>
+        <v>57.36000061035156</v>
       </c>
       <c r="BF7">
-        <v>57.36000061035156</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="BG7">
-        <v>58.04999923706055</v>
+        <v>56.86000061035156</v>
       </c>
       <c r="BH7">
-        <v>56.86000061035156</v>
-      </c>
-      <c r="BI7">
         <v>56.09999847412109</v>
       </c>
     </row>
-    <row r="8" spans="1:61">
+    <row r="8" spans="1:60">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>176.3937835693359</v>
+        <v>177.8957977294922</v>
       </c>
       <c r="C8">
-        <v>177.8957977294922</v>
+        <v>186.8184509277344</v>
       </c>
       <c r="D8">
-        <v>186.8184509277344</v>
+        <v>188.8178405761719</v>
       </c>
       <c r="E8">
-        <v>188.8178405761719</v>
+        <v>187.3655395507812</v>
       </c>
       <c r="F8">
-        <v>187.3655395507812</v>
+        <v>197.2431182861328</v>
       </c>
       <c r="G8">
-        <v>197.2431182861328</v>
+        <v>200.3864288330078</v>
       </c>
       <c r="H8">
-        <v>200.3864288330078</v>
+        <v>195.1243743896484</v>
       </c>
       <c r="I8">
-        <v>195.1243743896484</v>
+        <v>200.2571258544922</v>
       </c>
       <c r="J8">
-        <v>200.2571258544922</v>
+        <v>205.7678680419922</v>
       </c>
       <c r="K8">
-        <v>205.7678680419922</v>
+        <v>207.6976318359375</v>
       </c>
       <c r="L8">
-        <v>207.6976318359375</v>
+        <v>211.1493225097656</v>
       </c>
       <c r="M8">
-        <v>211.1493225097656</v>
+        <v>210.2938537597656</v>
       </c>
       <c r="N8">
-        <v>210.2938537597656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="O8">
-        <v>205.8872375488281</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="P8">
-        <v>205.6783599853516</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="Q8">
-        <v>206.7228088378906</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="R8">
-        <v>204.7632141113281</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="S8">
-        <v>205.7181396484375</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="T8">
-        <v>209.4881286621094</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="U8">
-        <v>210.5624237060547</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="V8">
-        <v>205.1014099121094</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="W8">
-        <v>204.8029937744141</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="X8">
-        <v>201.4806365966797</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="Y8">
-        <v>204.4349517822266</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="Z8">
-        <v>202.8334503173828</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="AA8">
-        <v>214.3821563720703</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="AB8">
-        <v>223.1754760742188</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="AC8">
-        <v>224.3890380859375</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="AD8">
-        <v>231.3819274902344</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="AE8">
-        <v>232.3766479492188</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="AF8">
-        <v>239.2800140380859</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="AG8">
-        <v>243.4900054931641</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="AH8">
-        <v>242.2899932861328</v>
+        <v>240</v>
       </c>
       <c r="AI8">
-        <v>240</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="AJ8">
-        <v>242.8699951171875</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="AK8">
-        <v>241.9600067138672</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="AL8">
-        <v>236.8999938964844</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AM8">
-        <v>242.2299957275391</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="AN8">
-        <v>239.8099975585938</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="AO8">
-        <v>244.0099945068359</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="AP8">
-        <v>246.5800018310547</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="AQ8">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="AR8">
-        <v>256.0899963378906</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="AS8">
-        <v>254.6600036621094</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="AT8">
-        <v>255.0899963378906</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="AU8">
-        <v>259.1400146484375</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="AV8">
-        <v>260.7799987792969</v>
+        <v>258.510009765625</v>
       </c>
       <c r="AW8">
-        <v>258.510009765625</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="AX8">
-        <v>259.4700012207031</v>
+        <v>257.0599975585938</v>
       </c>
       <c r="AY8">
-        <v>257.0599975585938</v>
+        <v>264.9299926757812</v>
       </c>
       <c r="AZ8">
-        <v>264.9299926757812</v>
+        <v>264.6300048828125</v>
       </c>
       <c r="BA8">
-        <v>264.6300048828125</v>
+        <v>274.2099914550781</v>
       </c>
       <c r="BB8">
-        <v>274.2099914550781</v>
+        <v>273.1300048828125</v>
       </c>
       <c r="BC8">
-        <v>273.1300048828125</v>
+        <v>261.75</v>
       </c>
       <c r="BD8">
-        <v>261.75</v>
+        <v>256.7799987792969</v>
       </c>
       <c r="BE8">
-        <v>256.7799987792969</v>
+        <v>256.4800109863281</v>
       </c>
       <c r="BF8">
-        <v>256.4800109863281</v>
+        <v>255.8699951171875</v>
       </c>
       <c r="BG8">
-        <v>255.8699951171875</v>
+        <v>255.75</v>
       </c>
       <c r="BH8">
-        <v>255.75</v>
-      </c>
-      <c r="BI8">
         <v>253.5500030517578</v>
       </c>
     </row>
-    <row r="9" spans="1:61">
+    <row r="9" spans="1:60">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>32.23313140869141</v>
+        <v>33.76237106323242</v>
       </c>
       <c r="C9">
-        <v>33.76237106323242</v>
+        <v>34.81496429443359</v>
       </c>
       <c r="D9">
-        <v>34.81496429443359</v>
+        <v>33.05733489990234</v>
       </c>
       <c r="E9">
-        <v>33.05733489990234</v>
+        <v>33.20628356933594</v>
       </c>
       <c r="F9">
-        <v>33.20628356933594</v>
+        <v>34.42768478393555</v>
       </c>
       <c r="G9">
-        <v>34.42768478393555</v>
+        <v>34.28866577148438</v>
       </c>
       <c r="H9">
-        <v>34.28866577148438</v>
+        <v>34.03048324584961</v>
       </c>
       <c r="I9">
-        <v>34.03048324584961</v>
+        <v>34.04041290283203</v>
       </c>
       <c r="J9">
-        <v>34.04041290283203</v>
+        <v>34.97384262084961</v>
       </c>
       <c r="K9">
-        <v>34.97384262084961</v>
+        <v>34.59650039672852</v>
       </c>
       <c r="L9">
-        <v>34.59650039672852</v>
+        <v>35.52000045776367</v>
       </c>
       <c r="M9">
-        <v>35.52000045776367</v>
+        <v>36.18000030517578</v>
       </c>
       <c r="N9">
-        <v>36.18000030517578</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="O9">
-        <v>36.41999816894531</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="P9">
-        <v>36.15000152587891</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="Q9">
-        <v>34.7400016784668</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="R9">
-        <v>34.93000030517578</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="S9">
-        <v>36.70000076293945</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="T9">
-        <v>36.33000183105469</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="U9">
-        <v>37.31999969482422</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="V9">
-        <v>36.86999893188477</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="W9">
-        <v>35.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="X9">
-        <v>34.65999984741211</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="Y9">
-        <v>36.52999877929688</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="Z9">
-        <v>37.63000106811523</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="AA9">
-        <v>41.02000045776367</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="AB9">
-        <v>40.61999893188477</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="AC9">
-        <v>39.97000122070312</v>
+        <v>40</v>
       </c>
       <c r="AD9">
-        <v>40</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="AE9">
-        <v>40.47000122070312</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="AF9">
-        <v>41.58000183105469</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="AG9">
-        <v>42.36999893188477</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="AH9">
-        <v>43.45000076293945</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="AI9">
-        <v>44.38999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="AJ9">
-        <v>43.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="AK9">
-        <v>42.95999908447266</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="AL9">
-        <v>41.34999847412109</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AM9">
-        <v>41.18999862670898</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="AN9">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="AO9">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="AP9">
-        <v>43.15000152587891</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="AQ9">
-        <v>44.29999923706055</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="AR9">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="AS9">
-        <v>44.18000030517578</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="AT9">
-        <v>42.77000045776367</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="AU9">
-        <v>43.54999923706055</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="AV9">
-        <v>44.84000015258789</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="AW9">
-        <v>44.52999877929688</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="AX9">
-        <v>44.72999954223633</v>
+        <v>45.02999877929688</v>
       </c>
       <c r="AY9">
-        <v>45.02999877929688</v>
+        <v>47.40999984741211</v>
       </c>
       <c r="AZ9">
-        <v>47.40999984741211</v>
+        <v>44.79000091552734</v>
       </c>
       <c r="BA9">
-        <v>44.79000091552734</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="BB9">
-        <v>45.45999908447266</v>
+        <v>44.86999893188477</v>
       </c>
       <c r="BC9">
-        <v>44.86999893188477</v>
+        <v>43.81000137329102</v>
       </c>
       <c r="BD9">
-        <v>43.81000137329102</v>
+        <v>42.29999923706055</v>
       </c>
       <c r="BE9">
-        <v>42.29999923706055</v>
+        <v>43.70000076293945</v>
       </c>
       <c r="BF9">
-        <v>43.70000076293945</v>
+        <v>43.68000030517578</v>
       </c>
       <c r="BG9">
-        <v>43.68000030517578</v>
+        <v>42.7400016784668</v>
       </c>
       <c r="BH9">
-        <v>42.7400016784668</v>
-      </c>
-      <c r="BI9">
         <v>42.33000183105469</v>
       </c>
     </row>
-    <row r="10" spans="1:61">
+    <row r="10" spans="1:60">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>195.3314361572266</v>
+        <v>196.7098846435547</v>
       </c>
       <c r="C10">
-        <v>196.7098846435547</v>
+        <v>203.891845703125</v>
       </c>
       <c r="D10">
-        <v>203.891845703125</v>
+        <v>202.5533447265625</v>
       </c>
       <c r="E10">
-        <v>202.5533447265625</v>
+        <v>210.7242126464844</v>
       </c>
       <c r="F10">
-        <v>210.7242126464844</v>
+        <v>203.3025054931641</v>
       </c>
       <c r="G10">
-        <v>203.3025054931641</v>
+        <v>211.5632781982422</v>
       </c>
       <c r="H10">
-        <v>211.5632781982422</v>
+        <v>212.2624816894531</v>
       </c>
       <c r="I10">
-        <v>212.2624816894531</v>
+        <v>207.1681823730469</v>
       </c>
       <c r="J10">
-        <v>207.1681823730469</v>
+        <v>202.5833129882812</v>
       </c>
       <c r="K10">
-        <v>202.5833129882812</v>
+        <v>203.0527954101562</v>
       </c>
       <c r="L10">
-        <v>203.0527954101562</v>
+        <v>207.0583038330078</v>
       </c>
       <c r="M10">
-        <v>207.0583038330078</v>
+        <v>211.8229827880859</v>
       </c>
       <c r="N10">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="O10">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="P10">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="Q10">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="R10">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="S10">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="T10">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="U10">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="V10">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="W10">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="X10">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="Y10">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="Z10">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="AA10">
+        <v>217.2568969726562</v>
+      </c>
+      <c r="AB10">
+        <v>223.8395233154297</v>
+      </c>
+      <c r="AC10">
+        <v>225.0481872558594</v>
+      </c>
+      <c r="AD10">
+        <v>224.9083404541016</v>
+      </c>
+      <c r="AE10">
+        <v>224.7584991455078</v>
+      </c>
+      <c r="AF10">
+        <v>219.4944000244141</v>
+      </c>
+      <c r="AG10">
+        <v>217.3168334960938</v>
+      </c>
+      <c r="AH10">
+        <v>216.6076354980469</v>
+      </c>
+      <c r="AI10">
+        <v>214.4800109863281</v>
+      </c>
+      <c r="AJ10">
+        <v>208.2469787597656</v>
+      </c>
+      <c r="AK10">
+        <v>212.8118743896484</v>
+      </c>
+      <c r="AL10">
+        <v>209.4256591796875</v>
+      </c>
+      <c r="AM10">
+        <v>227.7251739501953</v>
+      </c>
+      <c r="AN10">
         <v>217.3068389892578</v>
       </c>
-      <c r="AB10">
-        <v>217.2568969726562</v>
-      </c>
-      <c r="AC10">
-        <v>223.8395233154297</v>
-      </c>
-      <c r="AD10">
-        <v>225.0481872558594</v>
-      </c>
-      <c r="AE10">
-        <v>224.9083404541016</v>
-      </c>
-      <c r="AF10">
-        <v>224.7584991455078</v>
-      </c>
-      <c r="AG10">
-        <v>219.4944000244141</v>
-      </c>
-      <c r="AH10">
-        <v>217.3168334960938</v>
-      </c>
-      <c r="AI10">
-        <v>216.6076354980469</v>
-      </c>
-      <c r="AJ10">
-        <v>214.4800109863281</v>
-      </c>
-      <c r="AK10">
-        <v>208.2469787597656</v>
-      </c>
-      <c r="AL10">
-        <v>212.8118743896484</v>
-      </c>
-      <c r="AM10">
-        <v>209.4256591796875</v>
-      </c>
-      <c r="AN10">
-        <v>227.7251739501953</v>
-      </c>
       <c r="AO10">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="AP10">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="AQ10">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="AR10">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="AS10">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="AT10">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="AU10">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="AV10">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="AW10">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="AX10">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="AY10">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="AZ10">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="BA10">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="BB10">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="BC10">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="BD10">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="BE10">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="BF10">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="BG10">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="BH10">
-        <v>225.0700073242188</v>
-      </c>
-      <c r="BI10">
         <v>228.8600006103516</v>
       </c>
     </row>
-    <row r="11" spans="1:61">
+    <row r="11" spans="1:60">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>338.0143432617188</v>
+        <v>342.5588073730469</v>
       </c>
       <c r="C11">
-        <v>342.5588073730469</v>
+        <v>336.7885131835938</v>
       </c>
       <c r="D11">
-        <v>336.7885131835938</v>
+        <v>336.3301086425781</v>
       </c>
       <c r="E11">
-        <v>336.3301086425781</v>
+        <v>337.7651977539062</v>
       </c>
       <c r="F11">
-        <v>337.7651977539062</v>
+        <v>340.3463745117188</v>
       </c>
       <c r="G11">
-        <v>340.3463745117188</v>
+        <v>335.6822814941406</v>
       </c>
       <c r="H11">
-        <v>335.6822814941406</v>
+        <v>328.0683288574219</v>
       </c>
       <c r="I11">
-        <v>328.0683288574219</v>
+        <v>336.6689453125</v>
       </c>
       <c r="J11">
-        <v>336.6689453125</v>
+        <v>367.7227783203125</v>
       </c>
       <c r="K11">
-        <v>367.7227783203125</v>
+        <v>367.244384765625</v>
       </c>
       <c r="L11">
-        <v>367.244384765625</v>
+        <v>368.3705444335938</v>
       </c>
       <c r="M11">
-        <v>368.3705444335938</v>
+        <v>370.8121643066406</v>
       </c>
       <c r="N11">
-        <v>370.8121643066406</v>
+        <v>375.0875549316406</v>
       </c>
       <c r="O11">
-        <v>375.0875549316406</v>
+        <v>385.9404907226562</v>
       </c>
       <c r="P11">
-        <v>385.9404907226562</v>
+        <v>389.0199584960938</v>
       </c>
       <c r="Q11">
-        <v>389.0199584960938</v>
+        <v>395.8665161132812</v>
       </c>
       <c r="R11">
-        <v>395.8665161132812</v>
+        <v>387.6845092773438</v>
       </c>
       <c r="S11">
-        <v>387.6845092773438</v>
+        <v>374.7088623046875</v>
       </c>
       <c r="T11">
-        <v>374.7088623046875</v>
+        <v>373.0844116210938</v>
       </c>
       <c r="U11">
-        <v>373.0844116210938</v>
+        <v>372.5462646484375</v>
       </c>
       <c r="V11">
-        <v>372.5462646484375</v>
+        <v>375.8648986816406</v>
       </c>
       <c r="W11">
-        <v>375.8648986816406</v>
+        <v>381.1468811035156</v>
       </c>
       <c r="X11">
-        <v>381.1468811035156</v>
+        <v>384.6847534179688</v>
       </c>
       <c r="Y11">
-        <v>384.6847534179688</v>
+        <v>383.0005187988281</v>
       </c>
       <c r="Z11">
-        <v>383.0005187988281</v>
+        <v>374.3401184082031</v>
       </c>
       <c r="AA11">
-        <v>374.3401184082031</v>
+        <v>374.3301391601562</v>
       </c>
       <c r="AB11">
-        <v>374.3301391601562</v>
+        <v>368.8987426757812</v>
       </c>
       <c r="AC11">
-        <v>368.8987426757812</v>
+        <v>368.7392883300781</v>
       </c>
       <c r="AD11">
-        <v>368.7392883300781</v>
+        <v>369.0980224609375</v>
       </c>
       <c r="AE11">
-        <v>369.0980224609375</v>
+        <v>363.2680053710938</v>
       </c>
       <c r="AF11">
-        <v>363.2680053710938</v>
+        <v>366.6763305664062</v>
       </c>
       <c r="AG11">
-        <v>366.6763305664062</v>
+        <v>360.9857788085938</v>
       </c>
       <c r="AH11">
-        <v>360.9857788085938</v>
+        <v>363.248046875</v>
       </c>
       <c r="AI11">
-        <v>363.248046875</v>
+        <v>362.3411254882812</v>
       </c>
       <c r="AJ11">
-        <v>362.3411254882812</v>
+        <v>369.2873840332031</v>
       </c>
       <c r="AK11">
-        <v>369.2873840332031</v>
+        <v>368.4004516601562</v>
       </c>
       <c r="AL11">
-        <v>368.4004516601562</v>
+        <v>369.8853454589844</v>
       </c>
       <c r="AM11">
-        <v>369.8853454589844</v>
+        <v>368.071533203125</v>
       </c>
       <c r="AN11">
-        <v>368.071533203125</v>
+        <v>368.6396179199219</v>
       </c>
       <c r="AO11">
-        <v>368.6396179199219</v>
+        <v>364.6831359863281</v>
       </c>
       <c r="AP11">
-        <v>364.6831359863281</v>
+        <v>362.6799926757812</v>
       </c>
       <c r="AQ11">
-        <v>362.6799926757812</v>
+        <v>364.9322814941406</v>
       </c>
       <c r="AR11">
-        <v>364.9322814941406</v>
+        <v>373.0644836425781</v>
       </c>
       <c r="AS11">
-        <v>373.0644836425781</v>
+        <v>368.0914916992188</v>
       </c>
       <c r="AT11">
-        <v>368.0914916992188</v>
+        <v>364.4140625</v>
       </c>
       <c r="AU11">
-        <v>364.4140625</v>
+        <v>365.6000061035156</v>
       </c>
       <c r="AV11">
-        <v>365.6000061035156</v>
+        <v>367.5599975585938</v>
       </c>
       <c r="AW11">
-        <v>367.5599975585938</v>
+        <v>375.2000122070312</v>
       </c>
       <c r="AX11">
-        <v>375.2000122070312</v>
+        <v>378.0499877929688</v>
       </c>
       <c r="AY11">
-        <v>378.0499877929688</v>
+        <v>377.9700012207031</v>
       </c>
       <c r="AZ11">
-        <v>377.9700012207031</v>
+        <v>378.9200134277344</v>
       </c>
       <c r="BA11">
-        <v>378.9200134277344</v>
+        <v>379.489990234375</v>
       </c>
       <c r="BB11">
-        <v>379.489990234375</v>
+        <v>374.6199951171875</v>
       </c>
       <c r="BC11">
-        <v>374.6199951171875</v>
+        <v>371.1300048828125</v>
       </c>
       <c r="BD11">
-        <v>371.1300048828125</v>
+        <v>362.010009765625</v>
       </c>
       <c r="BE11">
-        <v>362.010009765625</v>
+        <v>360.3900146484375</v>
       </c>
       <c r="BF11">
-        <v>360.3900146484375</v>
+        <v>362.3900146484375</v>
       </c>
       <c r="BG11">
-        <v>362.3900146484375</v>
+        <v>363.0400085449219</v>
       </c>
       <c r="BH11">
-        <v>363.0400085449219</v>
-      </c>
-      <c r="BI11">
         <v>363.1600036621094</v>
       </c>
     </row>
-    <row r="12" spans="1:61">
+    <row r="12" spans="1:60">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>364.6632385253906</v>
+        <v>363.3840942382812</v>
       </c>
       <c r="C12">
-        <v>363.3840942382812</v>
+        <v>358.4772644042969</v>
       </c>
       <c r="D12">
-        <v>358.4772644042969</v>
+        <v>356.0088500976562</v>
       </c>
       <c r="E12">
-        <v>356.0088500976562</v>
+        <v>354.7996520996094</v>
       </c>
       <c r="F12">
-        <v>354.7996520996094</v>
+        <v>350.4425048828125</v>
       </c>
       <c r="G12">
-        <v>350.4425048828125</v>
+        <v>357.09814453125</v>
       </c>
       <c r="H12">
-        <v>357.09814453125</v>
+        <v>369.9697875976562</v>
       </c>
       <c r="I12">
-        <v>369.9697875976562</v>
+        <v>353.5804443359375</v>
       </c>
       <c r="J12">
-        <v>353.5804443359375</v>
+        <v>345.8954467773438</v>
       </c>
       <c r="K12">
-        <v>345.8954467773438</v>
+        <v>351.1420288085938</v>
       </c>
       <c r="L12">
-        <v>351.1420288085938</v>
+        <v>345.9653930664062</v>
       </c>
       <c r="M12">
-        <v>345.9653930664062</v>
+        <v>341.6881713867188</v>
       </c>
       <c r="N12">
-        <v>341.6881713867188</v>
+        <v>318.1334533691406</v>
       </c>
       <c r="O12">
-        <v>318.1334533691406</v>
+        <v>318.8829650878906</v>
       </c>
       <c r="P12">
-        <v>318.8829650878906</v>
+        <v>326.3581237792969</v>
       </c>
       <c r="Q12">
-        <v>326.3581237792969</v>
+        <v>332.3842163085938</v>
       </c>
       <c r="R12">
-        <v>332.3842163085938</v>
+        <v>335.5421752929688</v>
       </c>
       <c r="S12">
-        <v>335.5421752929688</v>
+        <v>333.4635009765625</v>
       </c>
       <c r="T12">
-        <v>333.4635009765625</v>
+        <v>356.4186096191406</v>
       </c>
       <c r="U12">
-        <v>356.4186096191406</v>
+        <v>372.2283325195312</v>
       </c>
       <c r="V12">
-        <v>372.2283325195312</v>
+        <v>375.1064758300781</v>
       </c>
       <c r="W12">
-        <v>375.1064758300781</v>
+        <v>359.8963623046875</v>
       </c>
       <c r="X12">
-        <v>359.8963623046875</v>
+        <v>356.3886108398438</v>
       </c>
       <c r="Y12">
-        <v>356.3886108398438</v>
+        <v>353.2406616210938</v>
       </c>
       <c r="Z12">
-        <v>353.2406616210938</v>
+        <v>355.609130859375</v>
       </c>
       <c r="AA12">
-        <v>355.609130859375</v>
+        <v>342.7774658203125</v>
       </c>
       <c r="AB12">
-        <v>342.7774658203125</v>
+        <v>342.1478576660156</v>
       </c>
       <c r="AC12">
-        <v>342.1478576660156</v>
+        <v>343.7168579101562</v>
       </c>
       <c r="AD12">
-        <v>343.7168579101562</v>
+        <v>343.3171081542969</v>
       </c>
       <c r="AE12">
-        <v>343.3171081542969</v>
+        <v>341.2284851074219</v>
       </c>
       <c r="AF12">
-        <v>341.2284851074219</v>
+        <v>341.0585632324219</v>
       </c>
       <c r="AG12">
-        <v>341.0585632324219</v>
+        <v>341.4783325195312</v>
       </c>
       <c r="AH12">
-        <v>341.4783325195312</v>
+        <v>337.9805908203125</v>
       </c>
       <c r="AI12">
-        <v>337.9805908203125</v>
+        <v>341.5282592773438</v>
       </c>
       <c r="AJ12">
-        <v>341.5282592773438</v>
+        <v>344.3664245605469</v>
       </c>
       <c r="AK12">
-        <v>344.3664245605469</v>
+        <v>343.1172485351562</v>
       </c>
       <c r="AL12">
-        <v>343.1172485351562</v>
+        <v>338.8800048828125</v>
       </c>
       <c r="AM12">
-        <v>338.8800048828125</v>
+        <v>337.4908752441406</v>
       </c>
       <c r="AN12">
-        <v>337.4908752441406</v>
+        <v>342.6575317382812</v>
       </c>
       <c r="AO12">
-        <v>342.6575317382812</v>
+        <v>335.1923828125</v>
       </c>
       <c r="AP12">
-        <v>335.1923828125</v>
+        <v>331.8145751953125</v>
       </c>
       <c r="AQ12">
-        <v>331.8145751953125</v>
+        <v>333.5634460449219</v>
       </c>
       <c r="AR12">
-        <v>333.5634460449219</v>
+        <v>338.8599853515625</v>
       </c>
       <c r="AS12">
-        <v>338.8599853515625</v>
+        <v>335.3099975585938</v>
       </c>
       <c r="AT12">
-        <v>335.3099975585938</v>
+        <v>335.3800048828125</v>
       </c>
       <c r="AU12">
-        <v>335.3800048828125</v>
+        <v>328.3800048828125</v>
       </c>
       <c r="AV12">
-        <v>328.3800048828125</v>
+        <v>330.3900146484375</v>
       </c>
       <c r="AW12">
-        <v>330.3900146484375</v>
+        <v>335.4500122070312</v>
       </c>
       <c r="AX12">
-        <v>335.4500122070312</v>
+        <v>345.7099914550781</v>
       </c>
       <c r="AY12">
-        <v>345.7099914550781</v>
+        <v>341.4299926757812</v>
       </c>
       <c r="AZ12">
-        <v>341.4299926757812</v>
+        <v>339.3599853515625</v>
       </c>
       <c r="BA12">
-        <v>339.3599853515625</v>
+        <v>343.6799926757812</v>
       </c>
       <c r="BB12">
-        <v>343.6799926757812</v>
+        <v>344.4100036621094</v>
       </c>
       <c r="BC12">
-        <v>344.4100036621094</v>
+        <v>350.8699951171875</v>
       </c>
       <c r="BD12">
-        <v>350.8699951171875</v>
+        <v>347.4100036621094</v>
       </c>
       <c r="BE12">
-        <v>347.4100036621094</v>
+        <v>334.9800109863281</v>
       </c>
       <c r="BF12">
-        <v>334.9800109863281</v>
+        <v>339.010009765625</v>
       </c>
       <c r="BG12">
-        <v>339.010009765625</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="BH12">
-        <v>341.0799865722656</v>
-      </c>
-      <c r="BI12">
         <v>339.1600036621094</v>
       </c>
     </row>
-    <row r="13" spans="1:61">
+    <row r="13" spans="1:60">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>66.05000305175781</v>
+        <v>66.12000274658203</v>
       </c>
       <c r="C13">
-        <v>66.12000274658203</v>
+        <v>67.08999633789062</v>
       </c>
       <c r="D13">
-        <v>67.08999633789062</v>
+        <v>67.59999847412109</v>
       </c>
       <c r="E13">
-        <v>67.59999847412109</v>
+        <v>67.34999847412109</v>
       </c>
       <c r="F13">
-        <v>67.34999847412109</v>
+        <v>68.29000091552734</v>
       </c>
       <c r="G13">
-        <v>68.29000091552734</v>
+        <v>68.72000122070312</v>
       </c>
       <c r="H13">
-        <v>68.72000122070312</v>
+        <v>66.61000061035156</v>
       </c>
       <c r="I13">
-        <v>66.61000061035156</v>
+        <v>63.88999938964844</v>
       </c>
       <c r="J13">
-        <v>63.88999938964844</v>
+        <v>66.44000244140625</v>
       </c>
       <c r="K13">
-        <v>66.44000244140625</v>
+        <v>65.83999633789062</v>
       </c>
       <c r="L13">
-        <v>65.83999633789062</v>
+        <v>67.58999633789062</v>
       </c>
       <c r="M13">
-        <v>67.58999633789062</v>
+        <v>65.88999938964844</v>
       </c>
       <c r="N13">
-        <v>65.88999938964844</v>
+        <v>63.7400016784668</v>
       </c>
       <c r="O13">
-        <v>63.7400016784668</v>
+        <v>63.40999984741211</v>
       </c>
       <c r="P13">
-        <v>63.40999984741211</v>
+        <v>64.08000183105469</v>
       </c>
       <c r="Q13">
-        <v>64.08000183105469</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="R13">
-        <v>63.90999984741211</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="S13">
+        <v>60.84000015258789</v>
+      </c>
+      <c r="T13">
+        <v>62.22000122070312</v>
+      </c>
+      <c r="U13">
+        <v>63.7599983215332</v>
+      </c>
+      <c r="V13">
+        <v>64.06999969482422</v>
+      </c>
+      <c r="W13">
+        <v>66.98999786376953</v>
+      </c>
+      <c r="X13">
+        <v>64.19999694824219</v>
+      </c>
+      <c r="Y13">
+        <v>65.76999664306641</v>
+      </c>
+      <c r="Z13">
+        <v>66.56999969482422</v>
+      </c>
+      <c r="AA13">
+        <v>64.87999725341797</v>
+      </c>
+      <c r="AB13">
+        <v>67.06999969482422</v>
+      </c>
+      <c r="AC13">
+        <v>66.04000091552734</v>
+      </c>
+      <c r="AD13">
+        <v>67.47000122070312</v>
+      </c>
+      <c r="AE13">
+        <v>64.41000366210938</v>
+      </c>
+      <c r="AF13">
+        <v>65.22000122070312</v>
+      </c>
+      <c r="AG13">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="AH13">
+        <v>64.13999938964844</v>
+      </c>
+      <c r="AI13">
+        <v>65.01999664306641</v>
+      </c>
+      <c r="AJ13">
+        <v>65.65000152587891</v>
+      </c>
+      <c r="AK13">
+        <v>65</v>
+      </c>
+      <c r="AL13">
+        <v>65.47000122070312</v>
+      </c>
+      <c r="AM13">
+        <v>65.33000183105469</v>
+      </c>
+      <c r="AN13">
+        <v>64.75</v>
+      </c>
+      <c r="AO13">
+        <v>64.33999633789062</v>
+      </c>
+      <c r="AP13">
+        <v>65.23000335693359</v>
+      </c>
+      <c r="AQ13">
+        <v>67.33999633789062</v>
+      </c>
+      <c r="AR13">
+        <v>68.01999664306641</v>
+      </c>
+      <c r="AS13">
+        <v>67.04000091552734</v>
+      </c>
+      <c r="AT13">
+        <v>64.58000183105469</v>
+      </c>
+      <c r="AU13">
+        <v>64.05999755859375</v>
+      </c>
+      <c r="AV13">
+        <v>65.40000152587891</v>
+      </c>
+      <c r="AW13">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="AX13">
+        <v>69.41000366210938</v>
+      </c>
+      <c r="AY13">
+        <v>67.66000366210938</v>
+      </c>
+      <c r="AZ13">
+        <v>66.01000213623047</v>
+      </c>
+      <c r="BA13">
+        <v>67.09999847412109</v>
+      </c>
+      <c r="BB13">
+        <v>65.11000061035156</v>
+      </c>
+      <c r="BC13">
+        <v>64.98999786376953</v>
+      </c>
+      <c r="BD13">
+        <v>63.29999923706055</v>
+      </c>
+      <c r="BE13">
+        <v>62.08000183105469</v>
+      </c>
+      <c r="BF13">
+        <v>61.91999816894531</v>
+      </c>
+      <c r="BG13">
         <v>61.81999969482422</v>
       </c>
-      <c r="T13">
-        <v>60.84000015258789</v>
-      </c>
-      <c r="U13">
-        <v>62.22000122070312</v>
-      </c>
-      <c r="V13">
-        <v>63.7599983215332</v>
-      </c>
-      <c r="W13">
-        <v>64.06999969482422</v>
-      </c>
-      <c r="X13">
-        <v>66.98999786376953</v>
-      </c>
-      <c r="Y13">
-        <v>64.19999694824219</v>
-      </c>
-      <c r="Z13">
-        <v>65.76999664306641</v>
-      </c>
-      <c r="AA13">
-        <v>66.56999969482422</v>
-      </c>
-      <c r="AB13">
-        <v>64.87999725341797</v>
-      </c>
-      <c r="AC13">
-        <v>67.06999969482422</v>
-      </c>
-      <c r="AD13">
-        <v>66.04000091552734</v>
-      </c>
-      <c r="AE13">
-        <v>67.47000122070312</v>
-      </c>
-      <c r="AF13">
-        <v>64.41000366210938</v>
-      </c>
-      <c r="AG13">
-        <v>65.22000122070312</v>
-      </c>
-      <c r="AH13">
-        <v>64.69999694824219</v>
-      </c>
-      <c r="AI13">
-        <v>64.13999938964844</v>
-      </c>
-      <c r="AJ13">
-        <v>65.01999664306641</v>
-      </c>
-      <c r="AK13">
-        <v>65.65000152587891</v>
-      </c>
-      <c r="AL13">
-        <v>65</v>
-      </c>
-      <c r="AM13">
-        <v>65.47000122070312</v>
-      </c>
-      <c r="AN13">
-        <v>65.33000183105469</v>
-      </c>
-      <c r="AO13">
-        <v>64.75</v>
-      </c>
-      <c r="AP13">
-        <v>64.33999633789062</v>
-      </c>
-      <c r="AQ13">
-        <v>65.23000335693359</v>
-      </c>
-      <c r="AR13">
-        <v>67.33999633789062</v>
-      </c>
-      <c r="AS13">
-        <v>68.01999664306641</v>
-      </c>
-      <c r="AT13">
-        <v>67.04000091552734</v>
-      </c>
-      <c r="AU13">
-        <v>64.58000183105469</v>
-      </c>
-      <c r="AV13">
-        <v>64.05999755859375</v>
-      </c>
-      <c r="AW13">
-        <v>65.40000152587891</v>
-      </c>
-      <c r="AX13">
-        <v>66.41999816894531</v>
-      </c>
-      <c r="AY13">
-        <v>69.41000366210938</v>
-      </c>
-      <c r="AZ13">
-        <v>67.66000366210938</v>
-      </c>
-      <c r="BA13">
-        <v>66.01000213623047</v>
-      </c>
-      <c r="BB13">
-        <v>67.09999847412109</v>
-      </c>
-      <c r="BC13">
-        <v>65.11000061035156</v>
-      </c>
-      <c r="BD13">
-        <v>64.98999786376953</v>
-      </c>
-      <c r="BE13">
-        <v>63.29999923706055</v>
-      </c>
-      <c r="BF13">
-        <v>62.08000183105469</v>
-      </c>
-      <c r="BG13">
-        <v>61.91999816894531</v>
-      </c>
       <c r="BH13">
-        <v>61.81999969482422</v>
-      </c>
-      <c r="BI13">
         <v>62.52999877929688</v>
       </c>
     </row>
-    <row r="14" spans="1:61">
+    <row r="14" spans="1:60">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>366.2245788574219</v>
+        <v>366.7942199707031</v>
       </c>
       <c r="C14">
-        <v>366.7942199707031</v>
+        <v>361.6875305175781</v>
       </c>
       <c r="D14">
-        <v>361.6875305175781</v>
+        <v>358.6594848632812</v>
       </c>
       <c r="E14">
-        <v>358.6594848632812</v>
+        <v>356.9505615234375</v>
       </c>
       <c r="F14">
-        <v>356.9505615234375</v>
+        <v>352.2835693359375</v>
       </c>
       <c r="G14">
-        <v>352.2835693359375</v>
+        <v>359.2790832519531</v>
       </c>
       <c r="H14">
-        <v>359.2790832519531</v>
+        <v>370.6817626953125</v>
       </c>
       <c r="I14">
-        <v>370.6817626953125</v>
+        <v>354.2322998046875</v>
       </c>
       <c r="J14">
-        <v>354.2322998046875</v>
+        <v>346.5472412109375</v>
       </c>
       <c r="K14">
-        <v>346.5472412109375</v>
+        <v>351.7638854980469</v>
       </c>
       <c r="L14">
-        <v>351.7638854980469</v>
+        <v>346.927001953125</v>
       </c>
       <c r="M14">
-        <v>346.927001953125</v>
+        <v>341.8702392578125</v>
       </c>
       <c r="N14">
-        <v>341.8702392578125</v>
+        <v>317.4859313964844</v>
       </c>
       <c r="O14">
-        <v>317.4859313964844</v>
+        <v>319.5346069335938</v>
       </c>
       <c r="P14">
-        <v>319.5346069335938</v>
+        <v>326.3502197265625</v>
       </c>
       <c r="Q14">
-        <v>326.3502197265625</v>
+        <v>333.4956359863281</v>
       </c>
       <c r="R14">
-        <v>333.4956359863281</v>
+        <v>336.4937133789062</v>
       </c>
       <c r="S14">
-        <v>336.4937133789062</v>
+        <v>333.4456787109375</v>
       </c>
       <c r="T14">
-        <v>333.4456787109375</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="U14">
-        <v>355.9012451171875</v>
+        <v>373.2700805664062</v>
       </c>
       <c r="V14">
-        <v>373.2700805664062</v>
+        <v>377.4074096679688</v>
       </c>
       <c r="W14">
-        <v>377.4074096679688</v>
+        <v>362.1971740722656</v>
       </c>
       <c r="X14">
-        <v>362.1971740722656</v>
+        <v>357.5202026367188</v>
       </c>
       <c r="Y14">
-        <v>357.5202026367188</v>
+        <v>354.0723876953125</v>
       </c>
       <c r="Z14">
-        <v>354.0723876953125</v>
+        <v>357.2903442382812</v>
       </c>
       <c r="AA14">
-        <v>357.2903442382812</v>
+        <v>343.5791320800781</v>
       </c>
       <c r="AB14">
-        <v>343.5791320800781</v>
+        <v>343.3193359375</v>
       </c>
       <c r="AC14">
-        <v>343.3193359375</v>
+        <v>346.1375122070312</v>
       </c>
       <c r="AD14">
-        <v>346.1375122070312</v>
+        <v>345.6777954101562</v>
       </c>
       <c r="AE14">
-        <v>345.6777954101562</v>
+        <v>343.7790222167969</v>
       </c>
       <c r="AF14">
-        <v>343.7790222167969</v>
+        <v>343.9789123535156</v>
       </c>
       <c r="AG14">
-        <v>343.9789123535156</v>
+        <v>344.4985656738281</v>
       </c>
       <c r="AH14">
-        <v>344.4985656738281</v>
+        <v>340.451171875</v>
       </c>
       <c r="AI14">
-        <v>340.451171875</v>
+        <v>344.5985107421875</v>
       </c>
       <c r="AJ14">
-        <v>344.5985107421875</v>
+        <v>347.83642578125</v>
       </c>
       <c r="AK14">
-        <v>347.83642578125</v>
+        <v>346.7371215820312</v>
       </c>
       <c r="AL14">
-        <v>346.7371215820312</v>
+        <v>341.7803039550781</v>
       </c>
       <c r="AM14">
-        <v>341.7803039550781</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="AN14">
-        <v>340.4311828613281</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="AO14">
-        <v>346.3673706054688</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="AP14">
-        <v>339.1320190429688</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="AQ14">
-        <v>334.8047790527344</v>
+        <v>336.9034423828125</v>
       </c>
       <c r="AR14">
-        <v>336.9034423828125</v>
+        <v>342.260009765625</v>
       </c>
       <c r="AS14">
-        <v>342.260009765625</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="AT14">
-        <v>338.4599914550781</v>
+        <v>338.3599853515625</v>
       </c>
       <c r="AU14">
-        <v>338.3599853515625</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="AV14">
-        <v>330.6499938964844</v>
+        <v>332.6000061035156</v>
       </c>
       <c r="AW14">
-        <v>332.6000061035156</v>
+        <v>338.5</v>
       </c>
       <c r="AX14">
-        <v>338.5</v>
+        <v>349.3900146484375</v>
       </c>
       <c r="AY14">
-        <v>349.3900146484375</v>
+        <v>344.9800109863281</v>
       </c>
       <c r="AZ14">
-        <v>344.9800109863281</v>
+        <v>342.8699951171875</v>
       </c>
       <c r="BA14">
-        <v>342.8699951171875</v>
+        <v>347.3299865722656</v>
       </c>
       <c r="BB14">
-        <v>347.3299865722656</v>
+        <v>349.5400085449219</v>
       </c>
       <c r="BC14">
-        <v>349.5400085449219</v>
+        <v>354.9700012207031</v>
       </c>
       <c r="BD14">
-        <v>354.9700012207031</v>
+        <v>351.1600036621094</v>
       </c>
       <c r="BE14">
-        <v>351.1600036621094</v>
+        <v>337.8299865722656</v>
       </c>
       <c r="BF14">
-        <v>337.8299865722656</v>
+        <v>342.3599853515625</v>
       </c>
       <c r="BG14">
-        <v>342.3599853515625</v>
+        <v>343.9200134277344</v>
       </c>
       <c r="BH14">
-        <v>343.9200134277344</v>
-      </c>
-      <c r="BI14">
         <v>342.75</v>
       </c>
     </row>
-    <row r="15" spans="1:61">
+    <row r="15" spans="1:60">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>247.3405914306641</v>
+        <v>250.4178009033203</v>
       </c>
       <c r="C15">
-        <v>250.4178009033203</v>
+        <v>250.1289978027344</v>
       </c>
       <c r="D15">
-        <v>250.1289978027344</v>
+        <v>247.6094818115234</v>
       </c>
       <c r="E15">
-        <v>247.6094818115234</v>
+        <v>250.5671691894531</v>
       </c>
       <c r="F15">
-        <v>250.5671691894531</v>
+        <v>255.3871307373047</v>
       </c>
       <c r="G15">
-        <v>255.3871307373047</v>
+        <v>249.3124084472656</v>
       </c>
       <c r="H15">
-        <v>249.3124084472656</v>
+        <v>238.4874420166016</v>
       </c>
       <c r="I15">
-        <v>238.4874420166016</v>
+        <v>240.8575897216797</v>
       </c>
       <c r="J15">
-        <v>240.8575897216797</v>
+        <v>248.8642578125</v>
       </c>
       <c r="K15">
-        <v>248.8642578125</v>
+        <v>252.6783905029297</v>
       </c>
       <c r="L15">
-        <v>252.6783905029297</v>
+        <v>250.6966400146484</v>
       </c>
       <c r="M15">
-        <v>250.6966400146484</v>
+        <v>250.7862701416016</v>
       </c>
       <c r="N15">
-        <v>250.7862701416016</v>
+        <v>253.4651184082031</v>
       </c>
       <c r="O15">
-        <v>253.4651184082031</v>
+        <v>258.8925170898438</v>
       </c>
       <c r="P15">
-        <v>258.8925170898438</v>
+        <v>260.1871337890625</v>
       </c>
       <c r="Q15">
-        <v>260.1871337890625</v>
+        <v>271.2909240722656</v>
       </c>
       <c r="R15">
-        <v>271.2909240722656</v>
+        <v>273.2527770996094</v>
       </c>
       <c r="S15">
-        <v>273.2527770996094</v>
+        <v>264.2801208496094</v>
       </c>
       <c r="T15">
-        <v>264.2801208496094</v>
+        <v>262.9854736328125</v>
       </c>
       <c r="U15">
-        <v>262.9854736328125</v>
+        <v>261.5912780761719</v>
       </c>
       <c r="V15">
-        <v>261.5912780761719</v>
+        <v>261.4718017578125</v>
       </c>
       <c r="W15">
-        <v>261.4718017578125</v>
+        <v>263.4933776855469</v>
       </c>
       <c r="X15">
-        <v>263.4933776855469</v>
+        <v>273.9697570800781</v>
       </c>
       <c r="Y15">
-        <v>273.9697570800781</v>
+        <v>265.8934020996094</v>
       </c>
       <c r="Z15">
-        <v>265.8934020996094</v>
+        <v>268.5523376464844</v>
       </c>
       <c r="AA15">
-        <v>268.5523376464844</v>
+        <v>261.1431579589844</v>
       </c>
       <c r="AB15">
-        <v>261.1431579589844</v>
+        <v>254.7796325683594</v>
       </c>
       <c r="AC15">
-        <v>254.7796325683594</v>
+        <v>259.4004211425781</v>
       </c>
       <c r="AD15">
-        <v>259.4004211425781</v>
+        <v>260.3265686035156</v>
       </c>
       <c r="AE15">
-        <v>260.3265686035156</v>
+        <v>257.0302734375</v>
       </c>
       <c r="AF15">
-        <v>257.0302734375</v>
+        <v>260.067626953125</v>
       </c>
       <c r="AG15">
-        <v>260.067626953125</v>
+        <v>258.6634826660156</v>
       </c>
       <c r="AH15">
-        <v>258.6634826660156</v>
+        <v>253.4850311279297</v>
       </c>
       <c r="AI15">
-        <v>253.4850311279297</v>
+        <v>252.7779693603516</v>
       </c>
       <c r="AJ15">
-        <v>252.7779693603516</v>
+        <v>259.1116027832031</v>
       </c>
       <c r="AK15">
-        <v>259.1116027832031</v>
+        <v>256.55224609375</v>
       </c>
       <c r="AL15">
+        <v>260.7248840332031</v>
+      </c>
+      <c r="AM15">
         <v>256.55224609375</v>
       </c>
-      <c r="AM15">
-        <v>260.7248840332031</v>
-      </c>
       <c r="AN15">
-        <v>256.55224609375</v>
+        <v>259.4999694824219</v>
       </c>
       <c r="AO15">
-        <v>259.4999694824219</v>
+        <v>257.7999877929688</v>
       </c>
       <c r="AP15">
-        <v>257.7999877929688</v>
+        <v>257.8699951171875</v>
       </c>
       <c r="AQ15">
-        <v>257.8699951171875</v>
+        <v>259.3399963378906</v>
       </c>
       <c r="AR15">
-        <v>259.3399963378906</v>
+        <v>263.1099853515625</v>
       </c>
       <c r="AS15">
-        <v>263.1099853515625</v>
+        <v>259.5700073242188</v>
       </c>
       <c r="AT15">
-        <v>259.5700073242188</v>
+        <v>253.4600067138672</v>
       </c>
       <c r="AU15">
-        <v>253.4600067138672</v>
+        <v>253.5800018310547</v>
       </c>
       <c r="AV15">
-        <v>253.5800018310547</v>
+        <v>251.7899932861328</v>
       </c>
       <c r="AW15">
-        <v>251.7899932861328</v>
+        <v>253.7100067138672</v>
       </c>
       <c r="AX15">
-        <v>253.7100067138672</v>
+        <v>258.4800109863281</v>
       </c>
       <c r="AY15">
-        <v>258.4800109863281</v>
+        <v>257.2099914550781</v>
       </c>
       <c r="AZ15">
-        <v>257.2099914550781</v>
+        <v>254.8500061035156</v>
       </c>
       <c r="BA15">
-        <v>254.8500061035156</v>
+        <v>252.2100067138672</v>
       </c>
       <c r="BB15">
-        <v>252.2100067138672</v>
+        <v>249.8300018310547</v>
       </c>
       <c r="BC15">
-        <v>249.8300018310547</v>
+        <v>242.8600006103516</v>
       </c>
       <c r="BD15">
-        <v>242.8600006103516</v>
+        <v>229.5</v>
       </c>
       <c r="BE15">
-        <v>229.5</v>
+        <v>225.6600036621094</v>
       </c>
       <c r="BF15">
-        <v>225.6600036621094</v>
+        <v>227.1699981689453</v>
       </c>
       <c r="BG15">
-        <v>227.1699981689453</v>
+        <v>227.6000061035156</v>
       </c>
       <c r="BH15">
-        <v>227.6000061035156</v>
-      </c>
-      <c r="BI15">
         <v>227.5500030517578</v>
       </c>
     </row>
-    <row r="16" spans="1:61">
+    <row r="16" spans="1:60">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>125.1394882202148</v>
+        <v>126.5784454345703</v>
       </c>
       <c r="C16">
-        <v>126.5784454345703</v>
+        <v>131.4113464355469</v>
       </c>
       <c r="D16">
-        <v>131.4113464355469</v>
+        <v>131.2624969482422</v>
       </c>
       <c r="E16">
-        <v>131.2624969482422</v>
+        <v>134.1106262207031</v>
       </c>
       <c r="F16">
-        <v>134.1106262207031</v>
+        <v>133.7434539794922</v>
       </c>
       <c r="G16">
-        <v>133.7434539794922</v>
+        <v>132.9793090820312</v>
       </c>
       <c r="H16">
-        <v>132.9793090820312</v>
+        <v>137.2366333007812</v>
       </c>
       <c r="I16">
-        <v>137.2366333007812</v>
+        <v>139.1420135498047</v>
       </c>
       <c r="J16">
-        <v>139.1420135498047</v>
+        <v>138.5366668701172</v>
       </c>
       <c r="K16">
-        <v>138.5366668701172</v>
+        <v>138.5267333984375</v>
       </c>
       <c r="L16">
-        <v>138.5267333984375</v>
+        <v>137.4251861572266</v>
       </c>
       <c r="M16">
-        <v>137.4251861572266</v>
+        <v>136.8694610595703</v>
       </c>
       <c r="N16">
-        <v>136.8694610595703</v>
+        <v>133.4556579589844</v>
       </c>
       <c r="O16">
-        <v>133.4556579589844</v>
+        <v>135.7381439208984</v>
       </c>
       <c r="P16">
-        <v>135.7381439208984</v>
+        <v>139.2710113525391</v>
       </c>
       <c r="Q16">
-        <v>139.2710113525391</v>
+        <v>143.1016235351562</v>
       </c>
       <c r="R16">
-        <v>143.1016235351562</v>
+        <v>144.7886657714844</v>
       </c>
       <c r="S16">
-        <v>144.7886657714844</v>
+        <v>143.4092559814453</v>
       </c>
       <c r="T16">
-        <v>143.4092559814453</v>
+        <v>143.3894195556641</v>
       </c>
       <c r="U16">
-        <v>143.3894195556641</v>
+        <v>148.21240234375</v>
       </c>
       <c r="V16">
-        <v>148.21240234375</v>
+        <v>146.9818420410156</v>
       </c>
       <c r="W16">
-        <v>146.9818420410156</v>
+        <v>146.574951171875</v>
       </c>
       <c r="X16">
-        <v>146.574951171875</v>
+        <v>145.9596862792969</v>
       </c>
       <c r="Y16">
-        <v>145.9596862792969</v>
+        <v>148.5597229003906</v>
       </c>
       <c r="Z16">
-        <v>148.5597229003906</v>
+        <v>150.862060546875</v>
       </c>
       <c r="AA16">
-        <v>150.862060546875</v>
+        <v>151.1299896240234</v>
       </c>
       <c r="AB16">
-        <v>151.1299896240234</v>
+        <v>154</v>
       </c>
       <c r="AC16">
-        <v>154</v>
+        <v>155.5099945068359</v>
       </c>
       <c r="AD16">
-        <v>155.5099945068359</v>
+        <v>154.4799957275391</v>
       </c>
       <c r="AE16">
-        <v>154.4799957275391</v>
+        <v>151.0099945068359</v>
       </c>
       <c r="AF16">
-        <v>151.0099945068359</v>
+        <v>152.4799957275391</v>
       </c>
       <c r="AG16">
-        <v>152.4799957275391</v>
+        <v>159</v>
       </c>
       <c r="AH16">
-        <v>159</v>
+        <v>158.25</v>
       </c>
       <c r="AI16">
-        <v>158.25</v>
+        <v>165.4400024414062</v>
       </c>
       <c r="AJ16">
-        <v>165.4400024414062</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="AK16">
-        <v>169.8899993896484</v>
+        <v>163.4700012207031</v>
       </c>
       <c r="AL16">
-        <v>163.4700012207031</v>
+        <v>164.0399932861328</v>
       </c>
       <c r="AM16">
-        <v>164.0399932861328</v>
+        <v>165.9299926757812</v>
       </c>
       <c r="AN16">
-        <v>165.9299926757812</v>
+        <v>163.1799926757812</v>
       </c>
       <c r="AO16">
-        <v>163.1799926757812</v>
+        <v>160.8800048828125</v>
       </c>
       <c r="AP16">
-        <v>160.8800048828125</v>
+        <v>163.75</v>
       </c>
       <c r="AQ16">
-        <v>163.75</v>
+        <v>163.3600006103516</v>
       </c>
       <c r="AR16">
-        <v>163.3600006103516</v>
+        <v>164.0099945068359</v>
       </c>
       <c r="AS16">
-        <v>164.0099945068359</v>
+        <v>164.4400024414062</v>
       </c>
       <c r="AT16">
-        <v>164.4400024414062</v>
+        <v>162.7100067138672</v>
       </c>
       <c r="AU16">
-        <v>162.7100067138672</v>
+        <v>157.5200042724609</v>
       </c>
       <c r="AV16">
-        <v>157.5200042724609</v>
+        <v>155.7299957275391</v>
       </c>
       <c r="AW16">
-        <v>155.7299957275391</v>
+        <v>155.8300018310547</v>
       </c>
       <c r="AX16">
-        <v>155.8300018310547</v>
+        <v>158.6999969482422</v>
       </c>
       <c r="AY16">
-        <v>158.6999969482422</v>
+        <v>154.3999938964844</v>
       </c>
       <c r="AZ16">
-        <v>154.3999938964844</v>
+        <v>154.6799926757812</v>
       </c>
       <c r="BA16">
-        <v>154.6799926757812</v>
+        <v>159.8300018310547</v>
       </c>
       <c r="BB16">
-        <v>159.8300018310547</v>
+        <v>158.1900024414062</v>
       </c>
       <c r="BC16">
-        <v>158.1900024414062</v>
+        <v>157.7100067138672</v>
       </c>
       <c r="BD16">
-        <v>157.7100067138672</v>
+        <v>159.0200042724609</v>
       </c>
       <c r="BE16">
-        <v>159.0200042724609</v>
+        <v>156.2599945068359</v>
       </c>
       <c r="BF16">
-        <v>156.2599945068359</v>
+        <v>156.1499938964844</v>
       </c>
       <c r="BG16">
-        <v>156.1499938964844</v>
+        <v>157.4499969482422</v>
       </c>
       <c r="BH16">
-        <v>157.4499969482422</v>
-      </c>
-      <c r="BI16">
         <v>158.4299926757812</v>
       </c>
     </row>
-    <row r="17" spans="1:61">
+    <row r="17" spans="1:60">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>115.620002746582</v>
+        <v>118.0500030517578</v>
       </c>
       <c r="C17">
-        <v>118.0500030517578</v>
+        <v>117.2600021362305</v>
       </c>
       <c r="D17">
-        <v>117.2600021362305</v>
+        <v>118.5199966430664</v>
       </c>
       <c r="E17">
-        <v>118.5199966430664</v>
+        <v>116.7099990844727</v>
       </c>
       <c r="F17">
-        <v>116.7099990844727</v>
+        <v>114.2300033569336</v>
       </c>
       <c r="G17">
-        <v>114.2300033569336</v>
+        <v>114.879997253418</v>
       </c>
       <c r="H17">
-        <v>114.879997253418</v>
+        <v>115.0899963378906</v>
       </c>
       <c r="I17">
-        <v>115.0899963378906</v>
+        <v>116.6500015258789</v>
       </c>
       <c r="J17">
-        <v>116.6500015258789</v>
+        <v>117.25</v>
       </c>
       <c r="K17">
-        <v>117.25</v>
+        <v>115.6500015258789</v>
       </c>
       <c r="L17">
-        <v>115.6500015258789</v>
+        <v>117.3899993896484</v>
       </c>
       <c r="M17">
-        <v>117.3899993896484</v>
+        <v>115.7900009155273</v>
       </c>
       <c r="N17">
-        <v>115.7900009155273</v>
+        <v>116.6900024414062</v>
       </c>
       <c r="O17">
-        <v>116.6900024414062</v>
+        <v>117.6699981689453</v>
       </c>
       <c r="P17">
-        <v>117.6699981689453</v>
+        <v>118.870002746582</v>
       </c>
       <c r="Q17">
-        <v>118.870002746582</v>
+        <v>129.9299926757812</v>
       </c>
       <c r="R17">
-        <v>129.9299926757812</v>
+        <v>127.0999984741211</v>
       </c>
       <c r="S17">
-        <v>127.0999984741211</v>
+        <v>122.9899978637695</v>
       </c>
       <c r="T17">
-        <v>122.9899978637695</v>
+        <v>119.5199966430664</v>
       </c>
       <c r="U17">
-        <v>119.5199966430664</v>
+        <v>118.4300003051758</v>
       </c>
       <c r="V17">
-        <v>118.4300003051758</v>
+        <v>120.5999984741211</v>
       </c>
       <c r="W17">
-        <v>120.5999984741211</v>
+        <v>119.8000030517578</v>
       </c>
       <c r="X17">
-        <v>119.8000030517578</v>
+        <v>118.379997253418</v>
       </c>
       <c r="Y17">
-        <v>118.379997253418</v>
+        <v>120.5599975585938</v>
       </c>
       <c r="Z17">
-        <v>120.5599975585938</v>
+        <v>121.5500030517578</v>
       </c>
       <c r="AA17">
-        <v>121.5500030517578</v>
+        <v>121.0699996948242</v>
       </c>
       <c r="AB17">
-        <v>121.0699996948242</v>
+        <v>120.7699966430664</v>
       </c>
       <c r="AC17">
-        <v>120.7699966430664</v>
+        <v>120.5199966430664</v>
       </c>
       <c r="AD17">
-        <v>120.5199966430664</v>
+        <v>120.1600036621094</v>
       </c>
       <c r="AE17">
-        <v>120.1600036621094</v>
+        <v>123.5</v>
       </c>
       <c r="AF17">
-        <v>123.5</v>
+        <v>123.4700012207031</v>
       </c>
       <c r="AG17">
-        <v>123.4700012207031</v>
+        <v>128.4700012207031</v>
       </c>
       <c r="AH17">
-        <v>128.4700012207031</v>
+        <v>127.2200012207031</v>
       </c>
       <c r="AI17">
-        <v>127.2200012207031</v>
+        <v>127.8099975585938</v>
       </c>
       <c r="AJ17">
-        <v>127.8099975585938</v>
+        <v>127.9800033569336</v>
       </c>
       <c r="AK17">
-        <v>127.9800033569336</v>
+        <v>129.7200012207031</v>
       </c>
       <c r="AL17">
-        <v>129.7200012207031</v>
+        <v>128.1199951171875</v>
       </c>
       <c r="AM17">
-        <v>128.1199951171875</v>
+        <v>127.7399978637695</v>
       </c>
       <c r="AN17">
-        <v>127.7399978637695</v>
+        <v>124.370002746582</v>
       </c>
       <c r="AO17">
-        <v>124.370002746582</v>
+        <v>123.2200012207031</v>
       </c>
       <c r="AP17">
-        <v>123.2200012207031</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="AQ17">
-        <v>125.0100021362305</v>
+        <v>128.8300018310547</v>
       </c>
       <c r="AR17">
-        <v>128.8300018310547</v>
+        <v>128</v>
       </c>
       <c r="AS17">
-        <v>128</v>
+        <v>126.75</v>
       </c>
       <c r="AT17">
-        <v>126.75</v>
+        <v>124.4000015258789</v>
       </c>
       <c r="AU17">
-        <v>124.4000015258789</v>
+        <v>126.0100021362305</v>
       </c>
       <c r="AV17">
-        <v>126.0100021362305</v>
+        <v>123.2799987792969</v>
       </c>
       <c r="AW17">
-        <v>123.2799987792969</v>
+        <v>121.4700012207031</v>
       </c>
       <c r="AX17">
-        <v>121.4700012207031</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="AY17">
-        <v>122.1900024414062</v>
+        <v>121.7399978637695</v>
       </c>
       <c r="AZ17">
-        <v>121.7399978637695</v>
+        <v>124.75</v>
       </c>
       <c r="BA17">
-        <v>124.75</v>
+        <v>127.620002746582</v>
       </c>
       <c r="BB17">
-        <v>127.620002746582</v>
+        <v>125.3099975585938</v>
       </c>
       <c r="BC17">
-        <v>125.3099975585938</v>
+        <v>124.6500015258789</v>
       </c>
       <c r="BD17">
-        <v>124.6500015258789</v>
+        <v>126.9300003051758</v>
       </c>
       <c r="BE17">
-        <v>126.9300003051758</v>
+        <v>124.6399993896484</v>
       </c>
       <c r="BF17">
-        <v>124.6399993896484</v>
+        <v>124.4400024414062</v>
       </c>
       <c r="BG17">
-        <v>124.4400024414062</v>
+        <v>123.8899993896484</v>
       </c>
       <c r="BH17">
-        <v>123.8899993896484</v>
-      </c>
-      <c r="BI17">
         <v>124.8199996948242</v>
       </c>
     </row>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -381,18 +381,18 @@
     <t>Hewlett Packard Enterprise</t>
   </si>
   <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
     <t>SMCI</t>
   </si>
   <si>
     <t>Supermicro</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
     <t>INTC</t>
   </si>
   <si>
@@ -405,6 +405,12 @@
     <t>Salesforce</t>
   </si>
   <si>
+    <t>ILMN</t>
+  </si>
+  <si>
+    <t>Illumina, Inc.</t>
+  </si>
+  <si>
     <t>AMZN</t>
   </si>
   <si>
@@ -414,10 +420,10 @@
     <t>Consumer Discretionary</t>
   </si>
   <si>
-    <t>ILMN</t>
-  </si>
-  <si>
-    <t>Illumina, Inc.</t>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
   </si>
   <si>
     <t>BIIB</t>
@@ -426,10 +432,13 @@
     <t>Biogen</t>
   </si>
   <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Bloom Energy</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>DLTR</t>
@@ -450,6 +459,12 @@
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
+    <t>WBD</t>
+  </si>
+  <si>
+    <t>Warner Bros. Discovery</t>
+  </si>
+  <si>
     <t>STX</t>
   </si>
   <si>
@@ -462,10 +477,10 @@
     <t>Teradyne</t>
   </si>
   <si>
-    <t>WBD</t>
-  </si>
-  <si>
-    <t>Warner Bros. Discovery</t>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>Lilly (Eli)</t>
   </si>
   <si>
     <t>WAT</t>
@@ -474,10 +489,10 @@
     <t>Waters Corporation</t>
   </si>
   <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>Lilly (Eli)</t>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
   </si>
   <si>
     <t>COF</t>
@@ -492,10 +507,16 @@
     <t>Chevron Corporation</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>RVTY</t>
+  </si>
+  <si>
+    <t>Revvity</t>
   </si>
   <si>
     <t>A</t>
@@ -504,27 +525,6 @@
     <t>Agilent Technologies</t>
   </si>
   <si>
-    <t>BE</t>
-  </si>
-  <si>
-    <t>Bloom Energy</t>
-  </si>
-  <si>
-    <t>Industrials</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>KEYS</t>
-  </si>
-  <si>
-    <t>Keysight Technologies</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -603,7 +603,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-09-30 01:20 UTC · данные на 2026-09-29 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-01 01:20 UTC · данные на 2026-09-29 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -684,7 +684,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-09-30 01:20 UTC</t>
+    <t>2026-10-01 01:20 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -4561,10 +4561,10 @@
         <v>36</v>
       </c>
       <c r="E5" s="10">
-        <v>1053.97998046875</v>
+        <v>1065.079956054688</v>
       </c>
       <c r="F5" s="17">
-        <v>1.208551726646418</v>
+        <v>1.204436360353394</v>
       </c>
       <c r="G5" s="20">
         <v>-0.5652307531380691</v>
@@ -4576,16 +4576,16 @@
         <v>3.949484521250298</v>
       </c>
       <c r="J5" s="20">
-        <v>2.152233525949353</v>
+        <v>2.19799394423147</v>
       </c>
       <c r="K5" s="20">
         <v>0</v>
       </c>
       <c r="L5" s="20">
-        <v>-2.840115994885092</v>
+        <v>-2.857585512270284</v>
       </c>
       <c r="M5" s="20">
-        <v>0.06309490585654287</v>
+        <v>-0.1406735538857623</v>
       </c>
       <c r="N5" s="20">
         <v>24.447256</v>
@@ -4600,10 +4600,10 @@
         <v>3.457</v>
       </c>
       <c r="R5" s="12">
-        <v>1.952199955020532</v>
+        <v>2.31026679009629</v>
       </c>
       <c r="S5" s="11">
-        <v>58.35057323749574</v>
+        <v>59.65751472336584</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>115</v>
@@ -4623,10 +4623,10 @@
         <v>36</v>
       </c>
       <c r="E6" s="10">
-        <v>1712.890014648438</v>
+        <v>1729.760009765625</v>
       </c>
       <c r="F6" s="17">
-        <v>1.031125929043125</v>
+        <v>0.9984108770060762</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5400051267382519</v>
@@ -4638,16 +4638,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J6" s="20">
-        <v>1.874173277302404</v>
+        <v>1.823650412693357</v>
       </c>
       <c r="K6" s="20">
         <v>0.09493727377241684</v>
       </c>
       <c r="L6" s="20">
-        <v>-3.017779786263553</v>
+        <v>-2.985297298849611</v>
       </c>
       <c r="M6" s="20">
-        <v>-0.04264206308046381</v>
+        <v>-0.2864813368200971</v>
       </c>
       <c r="N6" s="20">
         <v>24.095963</v>
@@ -4662,10 +4662,10 @@
         <v>3.716</v>
       </c>
       <c r="R6" s="12">
-        <v>1.781433134329571</v>
+        <v>2.021414864219433</v>
       </c>
       <c r="S6" s="11">
-        <v>53.32535751730857</v>
+        <v>54.21951952094359</v>
       </c>
       <c r="T6" s="9" t="s">
         <v>115</v>
@@ -4685,10 +4685,10 @@
         <v>36</v>
       </c>
       <c r="E7" s="10">
-        <v>62.63000106811523</v>
+        <v>61.4900016784668</v>
       </c>
       <c r="F7" s="17">
-        <v>0.9725725292886965</v>
+        <v>0.9248925295105955</v>
       </c>
       <c r="G7" s="20">
         <v>0.3308679966228206</v>
@@ -4700,16 +4700,16 @@
         <v>2.202669227673142</v>
       </c>
       <c r="J7" s="20">
-        <v>2.664752482451724</v>
+        <v>2.548722423528928</v>
       </c>
       <c r="K7" s="20">
         <v>0</v>
       </c>
       <c r="L7" s="20">
-        <v>-2.075310812157834</v>
+        <v>-2.070565856618932</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.162703875579283</v>
+        <v>-0.2556298688320858</v>
       </c>
       <c r="N7" s="20">
         <v>32.4433</v>
@@ -4724,10 +4724,10 @@
         <v>0.337</v>
       </c>
       <c r="R7" s="12">
-        <v>1.630414027867387</v>
+        <v>1.734448527840111</v>
       </c>
       <c r="S7" s="11">
-        <v>60.67783555435059</v>
+        <v>57.79328944211449</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>115</v>
@@ -4747,10 +4747,10 @@
         <v>46</v>
       </c>
       <c r="E8" s="10">
-        <v>389.5700073242188</v>
+        <v>387.7200012207031</v>
       </c>
       <c r="F8" s="17">
-        <v>0.852676197334425</v>
+        <v>0.8582650273023472</v>
       </c>
       <c r="G8" s="20">
         <v>0.6066625783285674</v>
@@ -4762,16 +4762,16 @@
         <v>2.855442298450458</v>
       </c>
       <c r="J8" s="20">
-        <v>1.938855002708015</v>
+        <v>1.958104606146084</v>
       </c>
       <c r="K8" s="20">
         <v>0.6218023213438065</v>
       </c>
       <c r="L8" s="20">
-        <v>0.05652950002477082</v>
+        <v>0.04294879532932066</v>
       </c>
       <c r="M8" s="20">
-        <v>-1.156278998257378</v>
+        <v>-1.14841910802952</v>
       </c>
       <c r="N8" s="20">
         <v>16.15269</v>
@@ -4786,10 +4786,10 @@
         <v>0.517</v>
       </c>
       <c r="R8" s="12">
-        <v>0.5450361349569324</v>
+        <v>0.562582877019681</v>
       </c>
       <c r="S8" s="11">
-        <v>59.38019986855327</v>
+        <v>58.11915852427872</v>
       </c>
       <c r="T8" s="9" t="s">
         <v>115</v>
@@ -4809,10 +4809,10 @@
         <v>59</v>
       </c>
       <c r="E9" s="10">
-        <v>342.75</v>
+        <v>340.9200134277344</v>
       </c>
       <c r="F9" s="17">
-        <v>0.8481509942326801</v>
+        <v>0.843527635465728</v>
       </c>
       <c r="G9" s="20">
         <v>-0.3286805258697003</v>
@@ -4824,16 +4824,16 @@
         <v>1.392272810408264</v>
       </c>
       <c r="J9" s="20">
-        <v>0.1327881719500527</v>
+        <v>0.1192952438720594</v>
       </c>
       <c r="K9" s="20">
         <v>4.125808907685986</v>
       </c>
       <c r="L9" s="20">
-        <v>0.05521883844500573</v>
+        <v>0.06077980325553421</v>
       </c>
       <c r="M9" s="20">
-        <v>-0.04799982369731487</v>
+        <v>-0.05936405159963884</v>
       </c>
       <c r="N9" s="20">
         <v>17.273733</v>
@@ -4848,10 +4848,10 @@
         <v>0.242</v>
       </c>
       <c r="R9" s="12">
-        <v>0.2509119907868131</v>
+        <v>0.2480544791639319</v>
       </c>
       <c r="S9" s="11">
-        <v>48.86772541391871</v>
+        <v>47.41311441825979</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>115</v>
@@ -4862,58 +4862,58 @@
         <v>6</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>118</v>
+        <v>11</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>119</v>
+        <v>58</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E10" s="10">
-        <v>41.77999877929688</v>
+        <v>337.3200073242188</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8464277408471855</v>
+        <v>0.8433340346352719</v>
       </c>
       <c r="G10" s="20">
-        <v>-0.01962276509782637</v>
+        <v>-0.3209980775361091</v>
       </c>
       <c r="H10" s="20">
-        <v>-0.81458274663997</v>
+        <v>1.46049714331344</v>
       </c>
       <c r="I10" s="20">
-        <v>3.890766583974275</v>
+        <v>1.392272810408264</v>
       </c>
       <c r="J10" s="20">
-        <v>1.264952331308445</v>
+        <v>0.09100496218309335</v>
       </c>
       <c r="K10" s="20">
-        <v>3.418039643978128</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L10" s="20">
-        <v>-3.017779786263553</v>
+        <v>0.125703593065829</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.2170906233041758</v>
+        <v>-0.02167385675501864</v>
       </c>
       <c r="N10" s="20">
-        <v>13.269938</v>
+        <v>17.12249</v>
       </c>
       <c r="O10" s="20">
-        <v>2.771478</v>
+        <v>6.7015085</v>
       </c>
       <c r="P10" s="12">
-        <v>0.21465999</v>
+        <v>0.48676</v>
       </c>
       <c r="Q10" s="12">
-        <v>0.9320000000000001</v>
+        <v>0.242</v>
       </c>
       <c r="R10" s="12">
-        <v>0.9016841185744076</v>
+        <v>0.2365165708046646</v>
       </c>
       <c r="S10" s="11">
-        <v>58.83998556919025</v>
+        <v>46.91658518376647</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>115</v>
@@ -4924,58 +4924,58 @@
         <v>7</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E11" s="10">
-        <v>339.1600036621094</v>
+        <v>392.0299987792969</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8462702673593893</v>
+        <v>0.8208963944652438</v>
       </c>
       <c r="G11" s="20">
-        <v>-0.3209980775361091</v>
+        <v>0.63544661477666</v>
       </c>
       <c r="H11" s="20">
-        <v>1.46049714331344</v>
+        <v>-0.5748310520290635</v>
       </c>
       <c r="I11" s="20">
-        <v>1.392272810408264</v>
+        <v>2.432487252480616</v>
       </c>
       <c r="J11" s="20">
-        <v>0.101438109930742</v>
+        <v>1.858594596424158</v>
       </c>
       <c r="K11" s="20">
-        <v>4.125808907685986</v>
+        <v>0.7904824353884016</v>
       </c>
       <c r="L11" s="20">
-        <v>0.1074794553986571</v>
+        <v>0.02201799348917184</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.01042714850685386</v>
+        <v>-1.231463798764657</v>
       </c>
       <c r="N11" s="20">
-        <v>17.12249</v>
+        <v>13.640207</v>
       </c>
       <c r="O11" s="20">
-        <v>6.7015085</v>
+        <v>5.837709</v>
       </c>
       <c r="P11" s="12">
-        <v>0.48676</v>
+        <v>0.42099</v>
       </c>
       <c r="Q11" s="12">
-        <v>0.242</v>
+        <v>0.537</v>
       </c>
       <c r="R11" s="12">
-        <v>0.2404458803116964</v>
+        <v>0.6095762101198507</v>
       </c>
       <c r="S11" s="11">
-        <v>48.43503157654847</v>
+        <v>55.17538403875515</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>115</v>
@@ -4986,58 +4986,58 @@
         <v>8</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>35</v>
+        <v>119</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>36</v>
       </c>
       <c r="E12" s="10">
-        <v>543.4299926757812</v>
+        <v>209.1799926757812</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8219891143481299</v>
+        <v>0.8040434138060629</v>
       </c>
       <c r="G12" s="20">
-        <v>-0.1018209436010066</v>
+        <v>-0.4407742654660424</v>
       </c>
       <c r="H12" s="20">
-        <v>-0.8490887888117886</v>
+        <v>1.36710860701193</v>
       </c>
       <c r="I12" s="20">
-        <v>2.17697052724581</v>
+        <v>0.4340417055879129</v>
       </c>
       <c r="J12" s="20">
-        <v>2.678949089916177</v>
+        <v>1.964493007860773</v>
       </c>
       <c r="K12" s="20">
-        <v>1.626594358708216</v>
+        <v>0</v>
       </c>
       <c r="L12" s="20">
-        <v>-3.017779786263553</v>
+        <v>-0.4859537739633528</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.7416903145301179</v>
+        <v>-0.4429331458488497</v>
       </c>
       <c r="N12" s="20">
-        <v>32.783344</v>
+        <v>28.41031</v>
       </c>
       <c r="O12" s="20">
-        <v>-252.41704</v>
+        <v>26.369299</v>
       </c>
       <c r="P12" s="12">
-        <v>0</v>
+        <v>1.14818</v>
       </c>
       <c r="Q12" s="12">
-        <v>0.577</v>
+        <v>0.299</v>
       </c>
       <c r="R12" s="12">
-        <v>2.178000248070538</v>
+        <v>1.084305319997294</v>
       </c>
       <c r="S12" s="11">
-        <v>54.44305844686942</v>
+        <v>66.21556311151514</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>115</v>
@@ -5048,58 +5048,58 @@
         <v>9</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E13" s="10">
-        <v>389.4400024414062</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8041263146778714</v>
+        <v>0.7914298208133268</v>
       </c>
       <c r="G13" s="20">
-        <v>0.63544661477666</v>
+        <v>-0.01962276509782637</v>
       </c>
       <c r="H13" s="20">
-        <v>-0.5748310520290635</v>
+        <v>-0.81458274663997</v>
       </c>
       <c r="I13" s="20">
-        <v>2.432487252480616</v>
+        <v>3.890766583974275</v>
       </c>
       <c r="J13" s="20">
-        <v>1.774016123245709</v>
+        <v>1.101899074582801</v>
       </c>
       <c r="K13" s="20">
-        <v>0.7904824353884016</v>
+        <v>3.418039643978128</v>
       </c>
       <c r="L13" s="20">
-        <v>0.03035887657132737</v>
+        <v>-2.985297298849611</v>
       </c>
       <c r="M13" s="20">
-        <v>-1.130176183999243</v>
+        <v>-0.3174767765667028</v>
       </c>
       <c r="N13" s="20">
-        <v>13.640207</v>
+        <v>13.269938</v>
       </c>
       <c r="O13" s="20">
-        <v>5.837709</v>
+        <v>2.771478</v>
       </c>
       <c r="P13" s="12">
-        <v>0.42099</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q13" s="12">
-        <v>0.537</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R13" s="12">
-        <v>0.5560982973748247</v>
+        <v>0.9477683522309686</v>
       </c>
       <c r="S13" s="11">
-        <v>53.65092868896293</v>
+        <v>56.40673166815571</v>
       </c>
       <c r="T13" s="9" t="s">
         <v>115</v>
@@ -5110,58 +5110,58 @@
         <v>10</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E14" s="10">
-        <v>363.1600036621094</v>
+        <v>539.5900268554688</v>
       </c>
       <c r="F14" s="17">
-        <v>0.765698064543236</v>
+        <v>0.7829011641383317</v>
       </c>
       <c r="G14" s="20">
-        <v>1.160842542624806</v>
+        <v>-0.1018209436010066</v>
       </c>
       <c r="H14" s="20">
-        <v>-0.1221460134271735</v>
+        <v>-0.8490887888117886</v>
       </c>
       <c r="I14" s="20">
-        <v>-0.379797036716154</v>
+        <v>2.17697052724581</v>
       </c>
       <c r="J14" s="20">
-        <v>0.4425317063762407</v>
+        <v>2.585945072309453</v>
       </c>
       <c r="K14" s="20">
-        <v>3.864208957978802</v>
+        <v>1.626594358708216</v>
       </c>
       <c r="L14" s="20">
-        <v>0.5376700908418292</v>
+        <v>-2.985297298849611</v>
       </c>
       <c r="M14" s="20">
-        <v>-0.1806914953763021</v>
+        <v>-0.9058864916878377</v>
       </c>
       <c r="N14" s="20">
-        <v>9.756517000000001</v>
+        <v>32.783344</v>
       </c>
       <c r="O14" s="20">
-        <v>2.286463</v>
+        <v>-252.41704</v>
       </c>
       <c r="P14" s="12">
-        <v>0.26511</v>
+        <v>0</v>
       </c>
       <c r="Q14" s="12">
-        <v>0.003</v>
+        <v>0.577</v>
       </c>
       <c r="R14" s="12">
-        <v>0.2827324553858042</v>
+        <v>2.292566454540003</v>
       </c>
       <c r="S14" s="11">
-        <v>44.00018052953638</v>
+        <v>53.61814981192158</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>115</v>
@@ -5172,58 +5172,58 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>121</v>
+        <v>56</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="E15" s="10">
-        <v>204.4100036621094</v>
+        <v>363.2099914550781</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7471430776725437</v>
+        <v>0.7661399499463161</v>
       </c>
       <c r="G15" s="20">
-        <v>-0.4407742654660424</v>
+        <v>1.160842542624806</v>
       </c>
       <c r="H15" s="20">
-        <v>1.36710860701193</v>
+        <v>-0.1221460134271735</v>
       </c>
       <c r="I15" s="20">
-        <v>0.4340417055879129</v>
+        <v>-0.379797036716154</v>
       </c>
       <c r="J15" s="20">
-        <v>1.799262543071884</v>
+        <v>0.4471303323635836</v>
       </c>
       <c r="K15" s="20">
-        <v>0</v>
+        <v>3.864208957978802</v>
       </c>
       <c r="L15" s="20">
-        <v>-0.5699317785427325</v>
+        <v>0.5360538911827746</v>
       </c>
       <c r="M15" s="20">
-        <v>-0.3862390969246917</v>
+        <v>-0.1912006255460467</v>
       </c>
       <c r="N15" s="20">
-        <v>28.41031</v>
+        <v>9.756517000000001</v>
       </c>
       <c r="O15" s="20">
-        <v>26.369299</v>
+        <v>2.286463</v>
       </c>
       <c r="P15" s="12">
-        <v>1.14818</v>
+        <v>0.26511</v>
       </c>
       <c r="Q15" s="12">
-        <v>0.299</v>
+        <v>0.003</v>
       </c>
       <c r="R15" s="12">
-        <v>1.01369019895245</v>
+        <v>0.2541136285061665</v>
       </c>
       <c r="S15" s="11">
-        <v>62.75777976009478</v>
+        <v>44.07288790747463</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>115</v>
@@ -5234,58 +5234,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>123</v>
+        <v>65</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="E16" s="10">
-        <v>116.0299987792969</v>
+        <v>156.4299926757812</v>
       </c>
       <c r="F16" s="17">
-        <v>0.6885706028091586</v>
+        <v>0.6857408060184229</v>
       </c>
       <c r="G16" s="20">
-        <v>-0.8300215284456212</v>
+        <v>0.4643687022637146</v>
       </c>
       <c r="H16" s="20">
-        <v>-1.15511857368005</v>
+        <v>-0.5602647059158709</v>
       </c>
       <c r="I16" s="20">
-        <v>0.5176902230779757</v>
+        <v>-0.03871237626800461</v>
       </c>
       <c r="J16" s="20">
-        <v>1.979097943411691</v>
+        <v>1.001759588514815</v>
       </c>
       <c r="K16" s="20">
-        <v>4.125808907685986</v>
+        <v>3.32849341059643</v>
       </c>
       <c r="L16" s="20">
-        <v>-2.659329103832751</v>
+        <v>0.4656348777355975</v>
       </c>
       <c r="M16" s="20">
-        <v>0.5219715211815019</v>
+        <v>-0.4027143538232261</v>
       </c>
       <c r="N16" s="20">
-        <v>59.648514</v>
+        <v>16.332987</v>
       </c>
       <c r="O16" s="20">
-        <v>7.085662</v>
+        <v>4.008707</v>
       </c>
       <c r="P16" s="12">
-        <v>-0.10715</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q16" s="12">
-        <v>0.254</v>
+        <v>0.053</v>
       </c>
       <c r="R16" s="12">
-        <v>1.69023871796457</v>
+        <v>0.3396192502099078</v>
       </c>
       <c r="S16" s="11">
-        <v>58.52241396970126</v>
+        <v>48.68209180836577</v>
       </c>
       <c r="T16" s="9" t="s">
         <v>115</v>
@@ -5296,58 +5296,58 @@
         <v>13</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E17" s="10">
-        <v>158.4299926757812</v>
+        <v>252.25</v>
       </c>
       <c r="F17" s="17">
-        <v>0.6863997976000916</v>
+        <v>0.6708407473163873</v>
       </c>
       <c r="G17" s="20">
-        <v>0.4643687022637146</v>
+        <v>0.4452704814464517</v>
       </c>
       <c r="H17" s="20">
-        <v>-0.5602647059158709</v>
+        <v>-0.7901437171956464</v>
       </c>
       <c r="I17" s="20">
-        <v>-0.03871237626800461</v>
+        <v>2.40169945735154</v>
       </c>
       <c r="J17" s="20">
-        <v>1.048069840062104</v>
+        <v>1.528110631619969</v>
       </c>
       <c r="K17" s="20">
-        <v>3.32849341059643</v>
+        <v>0.7056217607301639</v>
       </c>
       <c r="L17" s="20">
-        <v>0.4239661553274459</v>
+        <v>0.2912608365601688</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.5368888605485839</v>
+        <v>-1.045479266188063</v>
       </c>
       <c r="N17" s="20">
-        <v>16.332987</v>
+        <v>14.597602</v>
       </c>
       <c r="O17" s="20">
-        <v>4.008707</v>
+        <v>3.2390637</v>
       </c>
       <c r="P17" s="12">
-        <v>0.26408002</v>
+        <v>0.23452999</v>
       </c>
       <c r="Q17" s="12">
-        <v>0.053</v>
+        <v>0.531</v>
       </c>
       <c r="R17" s="12">
-        <v>0.3447460983994171</v>
+        <v>0.3821216365587718</v>
       </c>
       <c r="S17" s="11">
-        <v>52.51861058334671</v>
+        <v>50.90785892675171</v>
       </c>
       <c r="T17" s="9" t="s">
         <v>115</v>
@@ -5358,58 +5358,58 @@
         <v>14</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E18" s="10">
-        <v>253.5500030517578</v>
+        <v>62.20999908447266</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6661369568864438</v>
+        <v>0.650836149598322</v>
       </c>
       <c r="G18" s="20">
-        <v>0.4452704814464517</v>
+        <v>1.236177102540873</v>
       </c>
       <c r="H18" s="20">
-        <v>-0.7901437171956464</v>
+        <v>-1.371750894206162</v>
       </c>
       <c r="I18" s="20">
-        <v>2.40169945735154</v>
+        <v>-0.5828068382546813</v>
       </c>
       <c r="J18" s="20">
-        <v>1.502090701483797</v>
+        <v>0.7932651612414429</v>
       </c>
       <c r="K18" s="20">
-        <v>0.7056217607301639</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L18" s="20">
-        <v>0.3052743990076309</v>
+        <v>0.01625442835937477</v>
       </c>
       <c r="M18" s="20">
-        <v>-1.01721208038731</v>
+        <v>-0.3495848119611839</v>
       </c>
       <c r="N18" s="20">
-        <v>14.597602</v>
+        <v>11.559979</v>
       </c>
       <c r="O18" s="20">
-        <v>3.2390637</v>
+        <v>1.3535349</v>
       </c>
       <c r="P18" s="12">
-        <v>0.23452999</v>
+        <v>-0.20358999</v>
       </c>
       <c r="Q18" s="12">
-        <v>0.531</v>
+        <v>0.046</v>
       </c>
       <c r="R18" s="12">
-        <v>0.3636407876702044</v>
+        <v>0.9562893263208481</v>
       </c>
       <c r="S18" s="11">
-        <v>52.49398993264359</v>
+        <v>41.37898465258728</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>115</v>
@@ -5420,58 +5420,58 @@
         <v>15</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>60</v>
+        <v>123</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E19" s="10">
-        <v>62.52999877929688</v>
+        <v>115.9300003051758</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6501319424647862</v>
+        <v>0.6336921470744762</v>
       </c>
       <c r="G19" s="20">
-        <v>1.236177102540873</v>
+        <v>-0.8300215284456212</v>
       </c>
       <c r="H19" s="20">
-        <v>-1.371750894206162</v>
+        <v>-1.15511857368005</v>
       </c>
       <c r="I19" s="20">
-        <v>-0.5828068382546813</v>
+        <v>0.5176902230779757</v>
       </c>
       <c r="J19" s="20">
-        <v>0.8088484330135332</v>
+        <v>1.868069409305132</v>
       </c>
       <c r="K19" s="20">
         <v>4.125808907685986</v>
       </c>
       <c r="L19" s="20">
-        <v>-0.001492504857263614</v>
+        <v>-2.671577674883161</v>
       </c>
       <c r="M19" s="20">
-        <v>-0.4035144703632402</v>
+        <v>0.2615342556853729</v>
       </c>
       <c r="N19" s="20">
-        <v>11.559979</v>
+        <v>59.648514</v>
       </c>
       <c r="O19" s="20">
-        <v>1.3535349</v>
+        <v>7.085662</v>
       </c>
       <c r="P19" s="12">
-        <v>-0.20358999</v>
+        <v>-0.10715</v>
       </c>
       <c r="Q19" s="12">
-        <v>0.046</v>
+        <v>0.254</v>
       </c>
       <c r="R19" s="12">
-        <v>0.9540624618530273</v>
+        <v>1.814518188160435</v>
       </c>
       <c r="S19" s="11">
-        <v>42.30704970653476</v>
+        <v>58.40940185859423</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>115</v>
@@ -5491,10 +5491,10 @@
         <v>36</v>
       </c>
       <c r="E20" s="10">
-        <v>227.2700042724609</v>
+        <v>225.3099975585938</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6492077584066087</v>
+        <v>0.6289722699452422</v>
       </c>
       <c r="G20" s="20">
         <v>0.4118301704600924</v>
@@ -5506,16 +5506,16 @@
         <v>0.1953152078062003</v>
       </c>
       <c r="J20" s="20">
-        <v>0.7851580146913664</v>
+        <v>0.7194684262759553</v>
       </c>
       <c r="K20" s="20">
         <v>3.564333199677299</v>
       </c>
       <c r="L20" s="20">
-        <v>-1.805802036700685</v>
+        <v>-1.823173151150118</v>
       </c>
       <c r="M20" s="20">
-        <v>-1.06632393967937</v>
+        <v>-1.059903253051583</v>
       </c>
       <c r="N20" s="20">
         <v>21.410795</v>
@@ -5530,10 +5530,10 @@
         <v>0.108</v>
       </c>
       <c r="R20" s="12">
-        <v>0.2761603206515848</v>
+        <v>0.2260437892590945</v>
       </c>
       <c r="S20" s="11">
-        <v>45.47939376411497</v>
+        <v>44.15650065010893</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>115</v>
@@ -5550,52 +5550,52 @@
         <v>127</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>128</v>
+        <v>61</v>
       </c>
       <c r="E21" s="10">
-        <v>246.1499938964844</v>
+        <v>272</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6132540024685693</v>
+        <v>0.626905401747914</v>
       </c>
       <c r="G21" s="20">
-        <v>-0.01172638762890057</v>
+        <v>-0.7382512714864492</v>
       </c>
       <c r="H21" s="20">
-        <v>0.1587373163946222</v>
+        <v>0.4427349355287207</v>
       </c>
       <c r="I21" s="20">
-        <v>1.021835496573962</v>
+        <v>-0.4590192885594346</v>
       </c>
       <c r="J21" s="20">
-        <v>0.04641212901068196</v>
+        <v>2.717171302221459</v>
       </c>
       <c r="K21" s="20">
-        <v>4.125808907685986</v>
+        <v>-0.264288895026258</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.442293694561014</v>
+        <v>-0.8039940222115048</v>
       </c>
       <c r="M21" s="20">
-        <v>0.0662518251171688</v>
+        <v>-0.004276401797169482</v>
       </c>
       <c r="N21" s="20">
-        <v>20.08608</v>
+        <v>50.27933</v>
       </c>
       <c r="O21" s="20">
-        <v>4.8805614</v>
+        <v>14.365522</v>
       </c>
       <c r="P21" s="12">
-        <v>0.30558002</v>
+        <v>0.32339</v>
       </c>
       <c r="Q21" s="12">
-        <v>0.196</v>
+        <v>0.094</v>
       </c>
       <c r="R21" s="12">
-        <v>0.2348249143099643</v>
+        <v>1.251469294733476</v>
       </c>
       <c r="S21" s="11">
-        <v>41.24381199131338</v>
+        <v>74.28186801109125</v>
       </c>
       <c r="T21" s="9" t="s">
         <v>115</v>
@@ -5606,58 +5606,58 @@
         <v>18</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="C22" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="D22" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D22" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="E22" s="10">
-        <v>271.8999938964844</v>
+        <v>246.6699981689453</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6100566751620263</v>
+        <v>0.6209026142441407</v>
       </c>
       <c r="G22" s="20">
-        <v>-0.7382512714864492</v>
+        <v>-0.01172638762890057</v>
       </c>
       <c r="H22" s="20">
-        <v>0.4427349355287207</v>
+        <v>0.1587373163946222</v>
       </c>
       <c r="I22" s="20">
-        <v>-0.4590192885594346</v>
+        <v>1.021835496573962</v>
       </c>
       <c r="J22" s="20">
-        <v>2.683847913538417</v>
+        <v>0.09158269404707803</v>
       </c>
       <c r="K22" s="20">
-        <v>-0.264288895026258</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L22" s="20">
-        <v>-0.8089470539597733</v>
+        <v>-0.4514642984274641</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.08620800274815466</v>
+        <v>-0.0006521936748348639</v>
       </c>
       <c r="N22" s="20">
-        <v>50.27933</v>
+        <v>20.08608</v>
       </c>
       <c r="O22" s="20">
-        <v>14.365522</v>
+        <v>4.8805614</v>
       </c>
       <c r="P22" s="12">
-        <v>0.32339</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q22" s="12">
-        <v>0.094</v>
+        <v>0.196</v>
       </c>
       <c r="R22" s="12">
-        <v>1.31069939770121</v>
+        <v>0.2275192929337493</v>
       </c>
       <c r="S22" s="11">
-        <v>74.25138551502386</v>
+        <v>41.92676510431599</v>
       </c>
       <c r="T22" s="9" t="s">
         <v>115</v>
@@ -5677,10 +5677,10 @@
         <v>61</v>
       </c>
       <c r="E23" s="10">
-        <v>124.8199996948242</v>
+        <v>123.1999969482422</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5955183679171219</v>
+        <v>0.5785494723389598</v>
       </c>
       <c r="G23" s="20">
         <v>0.3123085537627329</v>
@@ -5692,16 +5692,16 @@
         <v>0.5162516055283453</v>
       </c>
       <c r="J23" s="20">
-        <v>0.7173072884699651</v>
+        <v>0.6386031770597075</v>
       </c>
       <c r="K23" s="20">
         <v>1.668764387219364</v>
       </c>
       <c r="L23" s="20">
-        <v>0.2971893467544153</v>
+        <v>0.2862810231114462</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.3318088286771503</v>
+        <v>-0.2405983628834838</v>
       </c>
       <c r="N23" s="20">
         <v>15.782166</v>
@@ -5716,10 +5716,10 @@
         <v>0.377</v>
       </c>
       <c r="R23" s="12">
-        <v>0.3822812345120339</v>
+        <v>0.36388790491408</v>
       </c>
       <c r="S23" s="11">
-        <v>51.11266140963528</v>
+        <v>47.39552496670595</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>115</v>
@@ -5730,58 +5730,58 @@
         <v>20</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>6</v>
+        <v>131</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E24" s="10">
-        <v>56.09999847412109</v>
+        <v>375.9700012207031</v>
       </c>
       <c r="F24" s="17">
-        <v>0.594570689717538</v>
+        <v>0.5668525766492716</v>
       </c>
       <c r="G24" s="20">
-        <v>0.5909946933403921</v>
+        <v>0.08345580963657841</v>
       </c>
       <c r="H24" s="20">
-        <v>0.6147531683208749</v>
+        <v>-0.2400131984019881</v>
       </c>
       <c r="I24" s="20">
-        <v>2.900414534129918</v>
+        <v>0.4617856253832925</v>
       </c>
       <c r="J24" s="20">
-        <v>0.06110575945457342</v>
+        <v>1.628671178377844</v>
       </c>
       <c r="K24" s="20">
-        <v>0.9320904323641113</v>
+        <v>1.728635415352477</v>
       </c>
       <c r="L24" s="20">
-        <v>0.05233674508921302</v>
+        <v>-1.84023166816157</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.4191637481685332</v>
+        <v>-0.5196202893159986</v>
       </c>
       <c r="N24" s="20">
-        <v>16.772861</v>
+        <v>33.886448</v>
       </c>
       <c r="O24" s="20">
-        <v>1.6988854</v>
+        <v>5.1050563</v>
       </c>
       <c r="P24" s="12">
-        <v>0.10629</v>
+        <v>0.15286</v>
       </c>
       <c r="Q24" s="12">
-        <v>0.534</v>
+        <v>0.204</v>
       </c>
       <c r="R24" s="12">
-        <v>-0.1332251289941264</v>
+        <v>0.8864525612830245</v>
       </c>
       <c r="S24" s="11">
-        <v>39.51398135968419</v>
+        <v>64.71987507210254</v>
       </c>
       <c r="T24" s="9" t="s">
         <v>115</v>
@@ -5792,58 +5792,58 @@
         <v>21</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E25" s="10">
-        <v>228.8600006103516</v>
+        <v>54.93999862670898</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5819405484586296</v>
+        <v>0.5635254660625055</v>
       </c>
       <c r="G25" s="20">
-        <v>-1.098910330048646</v>
+        <v>0.5909946933403921</v>
       </c>
       <c r="H25" s="20">
-        <v>2.371667806806906</v>
+        <v>0.6147531683208749</v>
       </c>
       <c r="I25" s="20">
-        <v>2.414157689348599</v>
+        <v>2.900414534129918</v>
       </c>
       <c r="J25" s="20">
-        <v>0.7991813477157338</v>
+        <v>-0.04447012705801937</v>
       </c>
       <c r="K25" s="20">
-        <v>-0.2986496589983051</v>
+        <v>0.9320904323641113</v>
       </c>
       <c r="L25" s="20">
-        <v>-0.2531267086833988</v>
+        <v>0.02209116526051533</v>
       </c>
       <c r="M25" s="20">
-        <v>-0.3733381608812324</v>
+        <v>-0.388635284562691</v>
       </c>
       <c r="N25" s="20">
-        <v>28.489874</v>
+        <v>16.772861</v>
       </c>
       <c r="O25" s="20">
-        <v>23.73405</v>
+        <v>1.6988854</v>
       </c>
       <c r="P25" s="12">
-        <v>1.17211</v>
+        <v>0.10629</v>
       </c>
       <c r="Q25" s="12">
-        <v>1.059</v>
+        <v>0.534</v>
       </c>
       <c r="R25" s="12">
-        <v>0.3692880291901632</v>
+        <v>-0.1629373059864707</v>
       </c>
       <c r="S25" s="11">
-        <v>58.77557027334879</v>
+        <v>36.00957779935527</v>
       </c>
       <c r="T25" s="9" t="s">
         <v>115</v>
@@ -5854,58 +5854,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E26" s="10">
-        <v>228.6900024414062</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="F26" s="17">
-        <v>0.5674300996311124</v>
+        <v>0.5593540356038559</v>
       </c>
       <c r="G26" s="20">
-        <v>0.1826167294586985</v>
+        <v>-1.098910330048646</v>
       </c>
       <c r="H26" s="20">
-        <v>0.02741872860098578</v>
+        <v>2.371667806806906</v>
       </c>
       <c r="I26" s="20">
-        <v>-0.8979974000351455</v>
+        <v>2.414157689348599</v>
       </c>
       <c r="J26" s="20">
-        <v>0.8421167847182076</v>
+        <v>0.7133741676287647</v>
       </c>
       <c r="K26" s="20">
-        <v>3.409189144167147</v>
+        <v>-0.2986496589983051</v>
       </c>
       <c r="L26" s="20">
-        <v>-0.03785870044141074</v>
+        <v>-0.2665392677529459</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.4936797366641485</v>
+        <v>-0.3238332269376096</v>
       </c>
       <c r="N26" s="20">
-        <v>40.498222</v>
+        <v>28.489874</v>
       </c>
       <c r="O26" s="20">
-        <v>1.7835593</v>
+        <v>23.73405</v>
       </c>
       <c r="P26" s="12">
-        <v>0.04575</v>
+        <v>1.17211</v>
       </c>
       <c r="Q26" s="12">
-        <v>0.034</v>
+        <v>1.059</v>
       </c>
       <c r="R26" s="12">
-        <v>0.2439621790520661</v>
+        <v>0.3787573860671793</v>
       </c>
       <c r="S26" s="11">
-        <v>63.8676752648799</v>
+        <v>56.70904523604791</v>
       </c>
       <c r="T26" s="9" t="s">
         <v>115</v>
@@ -5922,52 +5922,52 @@
         <v>134</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="E27" s="10">
-        <v>371.8699951171875</v>
+        <v>227.0700073242188</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5602917298008462</v>
+        <v>0.5586229362639302</v>
       </c>
       <c r="G27" s="20">
-        <v>0.08345580963657841</v>
+        <v>0.1826167294586985</v>
       </c>
       <c r="H27" s="20">
-        <v>-0.2400131984019881</v>
+        <v>0.02741872860098578</v>
       </c>
       <c r="I27" s="20">
-        <v>0.4617856253832925</v>
+        <v>-0.8979974000351455</v>
       </c>
       <c r="J27" s="20">
-        <v>1.589188000847441</v>
+        <v>0.7882121432853492</v>
       </c>
       <c r="K27" s="20">
-        <v>1.728635415352477</v>
+        <v>3.409189144167147</v>
       </c>
       <c r="L27" s="20">
-        <v>-1.826152990863577</v>
+        <v>0.005808360481315007</v>
       </c>
       <c r="M27" s="20">
-        <v>-0.464127967155801</v>
+        <v>-0.4343771690727498</v>
       </c>
       <c r="N27" s="20">
-        <v>33.886448</v>
+        <v>40.498222</v>
       </c>
       <c r="O27" s="20">
-        <v>5.1050563</v>
+        <v>1.7835593</v>
       </c>
       <c r="P27" s="12">
-        <v>0.15286</v>
+        <v>0.04575</v>
       </c>
       <c r="Q27" s="12">
-        <v>0.204</v>
+        <v>0.034</v>
       </c>
       <c r="R27" s="12">
-        <v>0.8351263138435636</v>
+        <v>0.2105880389060464</v>
       </c>
       <c r="S27" s="11">
-        <v>62.74203964815955</v>
+        <v>61.01124101302132</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>115</v>
@@ -5984,52 +5984,52 @@
         <v>136</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="E28" s="10">
-        <v>116.0199966430664</v>
+        <v>291.25</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5469036035441049</v>
+        <v>0.5494213258453997</v>
       </c>
       <c r="G28" s="20">
-        <v>0.4073104247281907</v>
+        <v>-3.850609330339901</v>
       </c>
       <c r="H28" s="20">
-        <v>-0.1242500444886299</v>
+        <v>-0.4558428702845563</v>
       </c>
       <c r="I28" s="20">
-        <v>0.4715191624753287</v>
+        <v>4.097268549112698</v>
       </c>
       <c r="J28" s="20">
-        <v>-0.2091256425023764</v>
+        <v>2.089363066892072</v>
       </c>
       <c r="K28" s="20">
         <v>4.125808907685986</v>
       </c>
       <c r="L28" s="20">
-        <v>0.1228602857439374</v>
+        <v>-2.985297298849611</v>
       </c>
       <c r="M28" s="20">
-        <v>0.08231030809296014</v>
+        <v>-0.4631142677265263</v>
       </c>
       <c r="N28" s="20">
-        <v>13.979167</v>
+        <v>384.93335</v>
       </c>
       <c r="O28" s="20">
-        <v>6.2500687</v>
+        <v>52.538673</v>
       </c>
       <c r="P28" s="12">
-        <v>0.46032003</v>
+        <v>0.22213</v>
       </c>
       <c r="Q28" s="12">
-        <v>0.07000000000000001</v>
+        <v>1.655</v>
       </c>
       <c r="R28" s="12">
-        <v>0.08429903404734951</v>
+        <v>1.43703451421582</v>
       </c>
       <c r="S28" s="11">
-        <v>42.79219288276581</v>
+        <v>60.26546600801933</v>
       </c>
       <c r="T28" s="9" t="s">
         <v>115</v>
@@ -6040,58 +6040,58 @@
         <v>25</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="E29" s="10">
-        <v>176.3300018310547</v>
+        <v>113.3000030517578</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5128036365010913</v>
+        <v>0.5353926705160622</v>
       </c>
       <c r="G29" s="20">
-        <v>-1.991192966399809</v>
+        <v>0.4073104247281907</v>
       </c>
       <c r="H29" s="20">
-        <v>1.771970471950948</v>
+        <v>-0.1242500444886299</v>
       </c>
       <c r="I29" s="20">
-        <v>0.2259855872354321</v>
+        <v>0.4715191624753287</v>
       </c>
       <c r="J29" s="20">
-        <v>1.911476117805594</v>
+        <v>-0.3010998195063742</v>
       </c>
       <c r="K29" s="20">
-        <v>0.4494778838476307</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L29" s="20">
-        <v>-0.7117084387680134</v>
+        <v>0.1096211336541071</v>
       </c>
       <c r="M29" s="20">
-        <v>-0.2446642357493879</v>
+        <v>0.2932561730747906</v>
       </c>
       <c r="N29" s="20">
-        <v>61.29329</v>
+        <v>13.979167</v>
       </c>
       <c r="O29" s="20">
-        <v>82.05298000000001</v>
+        <v>6.2500687</v>
       </c>
       <c r="P29" s="12">
-        <v>1.17442</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q29" s="12">
-        <v>0.256</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R29" s="12">
-        <v>1.254859446449356</v>
+        <v>0.07149617307282563</v>
       </c>
       <c r="S29" s="11">
-        <v>60.11644167561587</v>
+        <v>38.67354790400834</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>115</v>
@@ -6102,58 +6102,58 @@
         <v>26</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E30" s="10">
-        <v>63.88000106811523</v>
+        <v>175.9600067138672</v>
       </c>
       <c r="F30" s="17">
-        <v>0.4616272100170156</v>
+        <v>0.4941979190187143</v>
       </c>
       <c r="G30" s="20">
-        <v>0.4625864400742329</v>
+        <v>-1.991192966399809</v>
       </c>
       <c r="H30" s="20">
-        <v>0.6588490782651485</v>
+        <v>1.771970471950948</v>
       </c>
       <c r="I30" s="20">
-        <v>0.2249472925442899</v>
+        <v>0.2259855872354321</v>
       </c>
       <c r="J30" s="20">
-        <v>0.4700919567029462</v>
+        <v>1.86860497929311</v>
       </c>
       <c r="K30" s="20">
-        <v>0.8248431993604487</v>
+        <v>0.4494778838476307</v>
       </c>
       <c r="L30" s="20">
-        <v>0.6729218092376386</v>
+        <v>-0.6795161609375023</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.3741626307699393</v>
+        <v>-0.3406131432301697</v>
       </c>
       <c r="N30" s="20">
-        <v>13.845816</v>
+        <v>61.29329</v>
       </c>
       <c r="O30" s="20">
-        <v>5.7537756</v>
+        <v>82.05298000000001</v>
       </c>
       <c r="P30" s="12">
-        <v>0.46598998</v>
+        <v>1.17442</v>
       </c>
       <c r="Q30" s="12">
-        <v>0.057</v>
+        <v>0.256</v>
       </c>
       <c r="R30" s="12">
-        <v>0.1149161833418366</v>
+        <v>1.22593295282554</v>
       </c>
       <c r="S30" s="11">
-        <v>50.28693602215542</v>
+        <v>59.6218467606099</v>
       </c>
       <c r="T30" s="9" t="s">
         <v>115</v>
@@ -6164,58 +6164,58 @@
         <v>27</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="E31" s="10">
-        <v>921.510009765625</v>
+        <v>62.86000061035156</v>
       </c>
       <c r="F31" s="17">
-        <v>0.4556216055180816</v>
+        <v>0.4580620506425523</v>
       </c>
       <c r="G31" s="20">
-        <v>-2.057025624567463</v>
+        <v>0.4625864400742329</v>
       </c>
       <c r="H31" s="20">
-        <v>1.679533116257016</v>
+        <v>0.6588490782651485</v>
       </c>
       <c r="I31" s="20">
-        <v>1.336500578238815</v>
+        <v>0.2249472925442899</v>
       </c>
       <c r="J31" s="20">
-        <v>1.850355141116401</v>
+        <v>0.3867401570805634</v>
       </c>
       <c r="K31" s="20">
-        <v>0.01007659911417913</v>
+        <v>0.8248431993604487</v>
       </c>
       <c r="L31" s="20">
-        <v>-2.631271077596059</v>
+        <v>0.6877957040923544</v>
       </c>
       <c r="M31" s="20">
-        <v>0.3133923992795318</v>
+        <v>-0.1173132955078318</v>
       </c>
       <c r="N31" s="20">
-        <v>65.76973</v>
+        <v>13.845816</v>
       </c>
       <c r="O31" s="20">
-        <v>95.9529</v>
+        <v>5.7537756</v>
       </c>
       <c r="P31" s="12">
-        <v>3.7152898</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q31" s="12">
-        <v>0.485</v>
+        <v>0.057</v>
       </c>
       <c r="R31" s="12">
-        <v>1.428253393647692</v>
+        <v>0.07525604454087897</v>
       </c>
       <c r="S31" s="11">
-        <v>59.19925306598373</v>
+        <v>45.24247197719519</v>
       </c>
       <c r="T31" s="9" t="s">
         <v>115</v>
@@ -6226,58 +6226,58 @@
         <v>28</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="E32" s="10">
-        <v>401.2999877929688</v>
+        <v>30.85000038146973</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4483318225408142</v>
+        <v>0.4535045757239861</v>
       </c>
       <c r="G32" s="20">
-        <v>-1.18924796979833</v>
+        <v>-0.05525750799347566</v>
       </c>
       <c r="H32" s="20">
-        <v>0.5645521718938252</v>
+        <v>-1.002892332074208</v>
       </c>
       <c r="I32" s="20">
-        <v>3.655490679943009</v>
+        <v>-1.204760955881624</v>
       </c>
       <c r="J32" s="20">
-        <v>0.9692343280514764</v>
+        <v>0.8784380221141332</v>
       </c>
       <c r="K32" s="20">
-        <v>0.4364624429491279</v>
+        <v>4.125808907685986</v>
       </c>
       <c r="L32" s="20">
-        <v>-2.838382316427332</v>
+        <v>0.5157706289458311</v>
       </c>
       <c r="M32" s="20">
-        <v>0.4209523627937781</v>
+        <v>-0.5648114676307594</v>
       </c>
       <c r="N32" s="20">
-        <v>54.647465</v>
+        <v>495.98203</v>
       </c>
       <c r="O32" s="20">
-        <v>19.836678</v>
+        <v>2.3569846</v>
       </c>
       <c r="P32" s="12">
-        <v>0.36465</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q32" s="12">
-        <v>1.039</v>
+        <v>-0.112</v>
       </c>
       <c r="R32" s="12">
-        <v>0.3585662742054512</v>
+        <v>0.1387966115800352</v>
       </c>
       <c r="S32" s="11">
-        <v>58.84165473709983</v>
+        <v>74.67346692769081</v>
       </c>
       <c r="T32" s="9" t="s">
         <v>115</v>
@@ -6288,58 +6288,58 @@
         <v>29</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="E33" s="10">
-        <v>30.89999961853027</v>
+        <v>913.4500122070312</v>
       </c>
       <c r="F33" s="17">
-        <v>0.4426676629567567</v>
+        <v>0.4485393428361564</v>
       </c>
       <c r="G33" s="20">
-        <v>-0.05525750799347566</v>
+        <v>-2.057025624567463</v>
       </c>
       <c r="H33" s="20">
-        <v>-1.002892332074208</v>
+        <v>1.679533116257016</v>
       </c>
       <c r="I33" s="20">
-        <v>-1.204760955881624</v>
+        <v>1.336500578238815</v>
       </c>
       <c r="J33" s="20">
-        <v>0.8501432503204055</v>
+        <v>1.828400854523204</v>
       </c>
       <c r="K33" s="20">
-        <v>4.125808907685986</v>
+        <v>0.01007659911417913</v>
       </c>
       <c r="L33" s="20">
-        <v>0.5101173806669448</v>
+        <v>-2.58772927104221</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.5899275467854834</v>
+        <v>0.2745363355645698</v>
       </c>
       <c r="N33" s="20">
-        <v>495.98203</v>
+        <v>65.76973</v>
       </c>
       <c r="O33" s="20">
-        <v>2.3569846</v>
+        <v>95.9529</v>
       </c>
       <c r="P33" s="12">
-        <v>-0.08785999999999999</v>
+        <v>3.7152898</v>
       </c>
       <c r="Q33" s="12">
-        <v>-0.112</v>
+        <v>0.485</v>
       </c>
       <c r="R33" s="12">
-        <v>0.1414850375649745</v>
+        <v>1.52416779092974</v>
       </c>
       <c r="S33" s="11">
-        <v>75.68193322667129</v>
+        <v>57.72584798532598</v>
       </c>
       <c r="T33" s="9" t="s">
         <v>115</v>
@@ -6350,58 +6350,58 @@
         <v>30</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="E34" s="10">
-        <v>442.9400024414062</v>
+        <v>403.0199890136719</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4335997239490538</v>
+        <v>0.4436727013513844</v>
       </c>
       <c r="G34" s="20">
-        <v>-0.9301946228299454</v>
+        <v>-1.18924796979833</v>
       </c>
       <c r="H34" s="20">
-        <v>-0.4371628130044394</v>
+        <v>0.5645521718938252</v>
       </c>
       <c r="I34" s="20">
-        <v>4.097268549112698</v>
+        <v>3.655490679943009</v>
       </c>
       <c r="J34" s="20">
-        <v>1.158857186102352</v>
+        <v>0.9677779031833783</v>
       </c>
       <c r="K34" s="20">
-        <v>-0.5459430360698566</v>
+        <v>0.4364624429491279</v>
       </c>
       <c r="L34" s="20">
-        <v>0.5688010853355797</v>
+        <v>-2.842917558422142</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.6877263174321637</v>
+        <v>0.3715763726773813</v>
       </c>
       <c r="N34" s="20">
-        <v>109.756966</v>
+        <v>54.647465</v>
       </c>
       <c r="O34" s="20">
-        <v>2.8025289</v>
+        <v>19.836678</v>
       </c>
       <c r="P34" s="12">
-        <v>0.019199999</v>
+        <v>0.36465</v>
       </c>
       <c r="Q34" s="12">
-        <v>1.134</v>
+        <v>1.039</v>
       </c>
       <c r="R34" s="12">
-        <v>0.5318162845197381</v>
+        <v>0.4594792177568496</v>
       </c>
       <c r="S34" s="11">
-        <v>68.64760432431177</v>
+        <v>59.28939458736772</v>
       </c>
       <c r="T34" s="9" t="s">
         <v>115</v>
@@ -6412,19 +6412,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D35" s="9" t="s">
         <v>61</v>
       </c>
       <c r="E35" s="10">
-        <v>1184.780029296875</v>
+        <v>1184.630004882812</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4223319652769435</v>
+        <v>0.4299879524013854</v>
       </c>
       <c r="G35" s="20">
         <v>-1.110237185891371</v>
@@ -6436,16 +6436,16 @@
         <v>0.7254634342718127</v>
       </c>
       <c r="J35" s="20">
-        <v>0.4884287992023069</v>
+        <v>0.519321255412373</v>
       </c>
       <c r="K35" s="20">
         <v>0.8003741704712637</v>
       </c>
       <c r="L35" s="20">
-        <v>0.3803984343128673</v>
+        <v>0.3788573344954649</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.05283726755828755</v>
+        <v>-0.07182831442745968</v>
       </c>
       <c r="N35" s="20">
         <v>39.686787</v>
@@ -6460,10 +6460,10 @@
         <v>0.477</v>
       </c>
       <c r="R35" s="12">
-        <v>0.353297727248485</v>
+        <v>0.3403220201712167</v>
       </c>
       <c r="S35" s="11">
-        <v>56.10746417697418</v>
+        <v>56.05312703493652</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>115</v>
@@ -6474,58 +6474,58 @@
         <v>32</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E36" s="10">
-        <v>196.4600067138672</v>
+        <v>443.260009765625</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4062104593001394</v>
+        <v>0.4222504556274702</v>
       </c>
       <c r="G36" s="20">
-        <v>0.59238818351296</v>
+        <v>-0.9301946228299454</v>
       </c>
       <c r="H36" s="20">
-        <v>-0.6603051797569764</v>
+        <v>-0.4371628130044394</v>
       </c>
       <c r="I36" s="20">
         <v>4.097268549112698</v>
       </c>
       <c r="J36" s="20">
-        <v>-0.3920798867037227</v>
+        <v>1.121263198418043</v>
       </c>
       <c r="K36" s="20">
-        <v>0.619199233164106</v>
+        <v>-0.5459430360698566</v>
       </c>
       <c r="L36" s="20">
-        <v>0.5059954604815103</v>
+        <v>0.5621376615554001</v>
       </c>
       <c r="M36" s="20">
-        <v>0.105786131502331</v>
+        <v>-0.6836171498006661</v>
       </c>
       <c r="N36" s="20">
-        <v>11.024229</v>
+        <v>109.756966</v>
       </c>
       <c r="O36" s="20">
-        <v>1.1926677</v>
+        <v>2.8025289</v>
       </c>
       <c r="P36" s="12">
-        <v>0.09031</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q36" s="12">
-        <v>11.11</v>
+        <v>1.134</v>
       </c>
       <c r="R36" s="12">
-        <v>0.124361503726621</v>
+        <v>0.5109248292026711</v>
       </c>
       <c r="S36" s="11">
-        <v>35.16621525115893</v>
+        <v>68.79070649323441</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>115</v>
@@ -6536,58 +6536,58 @@
         <v>33</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>153</v>
+        <v>3</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>154</v>
+        <v>43</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E37" s="10">
-        <v>206.3699951171875</v>
+        <v>453.4800109863281</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4059522381644055</v>
+        <v>0.4137571807358134</v>
       </c>
       <c r="G37" s="20">
-        <v>0.4853183280948471</v>
+        <v>-0.8384379108839474</v>
       </c>
       <c r="H37" s="20">
-        <v>-0.3300127972283673</v>
+        <v>2.151739124777599</v>
       </c>
       <c r="I37" s="20">
-        <v>2.301619691710589</v>
+        <v>2.646453673822382</v>
       </c>
       <c r="J37" s="20">
-        <v>0.5650921052231415</v>
+        <v>0.4175693362755825</v>
       </c>
       <c r="K37" s="20">
-        <v>-0.1591241325663561</v>
+        <v>-0.2096240432525466</v>
       </c>
       <c r="L37" s="20">
-        <v>0.7638897651040981</v>
+        <v>-2.985297298849611</v>
       </c>
       <c r="M37" s="20">
-        <v>-0.6878888009051602</v>
+        <v>0.4344287448359685</v>
       </c>
       <c r="N37" s="20">
-        <v>19.639769</v>
+        <v>16.975473</v>
       </c>
       <c r="O37" s="20">
-        <v>2.1120868</v>
+        <v>22.350464</v>
       </c>
       <c r="P37" s="12">
-        <v>0.12231</v>
+        <v>1.30853</v>
       </c>
       <c r="Q37" s="12">
-        <v>0.535</v>
+        <v>0.438</v>
       </c>
       <c r="R37" s="12">
-        <v>-0.005078382644663759</v>
+        <v>0.8029318871666784</v>
       </c>
       <c r="S37" s="11">
-        <v>51.20657389218366</v>
+        <v>48.77699690554417</v>
       </c>
       <c r="T37" s="9" t="s">
         <v>115</v>
@@ -6598,58 +6598,58 @@
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>14</v>
+        <v>154</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>64</v>
+        <v>155</v>
       </c>
       <c r="D38" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E38" s="10">
-        <v>227.5500030517578</v>
+        <v>916.239990234375</v>
       </c>
       <c r="F38" s="17">
-        <v>0.4024313864468855</v>
+        <v>0.4113760891941076</v>
       </c>
       <c r="G38" s="20">
-        <v>1.23099937351617</v>
+        <v>0.4149604359308066</v>
       </c>
       <c r="H38" s="20">
-        <v>0.1667435013429619</v>
+        <v>0.8229528906242468</v>
       </c>
       <c r="I38" s="20">
-        <v>-0.05584647993229746</v>
+        <v>0.9059327383427908</v>
       </c>
       <c r="J38" s="20">
-        <v>-0.2682271390085824</v>
+        <v>-0.3262868106260743</v>
       </c>
       <c r="K38" s="20">
-        <v>1.881176382682929</v>
+        <v>1.685424151569448</v>
       </c>
       <c r="L38" s="20">
-        <v>0.4023852252451754</v>
+        <v>-0.0364785476111247</v>
       </c>
       <c r="M38" s="20">
-        <v>-0.1207368842719567</v>
+        <v>0.1530166531069971</v>
       </c>
       <c r="N38" s="20">
-        <v>4.5574694</v>
+        <v>14.451568</v>
       </c>
       <c r="O38" s="20">
-        <v>1.8238496</v>
+        <v>2.5837662</v>
       </c>
       <c r="P38" s="12">
-        <v>0.46113998</v>
+        <v>0.16902</v>
       </c>
       <c r="Q38" s="12">
-        <v>0.118</v>
+        <v>0.425</v>
       </c>
       <c r="R38" s="12">
-        <v>0.1331496207603819</v>
+        <v>0.1451030683657764</v>
       </c>
       <c r="S38" s="11">
-        <v>27.93485608509751</v>
+        <v>33.10656833392984</v>
       </c>
       <c r="T38" s="9" t="s">
         <v>115</v>
@@ -6660,58 +6660,58 @@
         <v>35</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D39" s="9" t="s">
         <v>57</v>
       </c>
       <c r="E39" s="10">
-        <v>916.280029296875</v>
+        <v>196.4600067138672</v>
       </c>
       <c r="F39" s="17">
-        <v>0.4016294230556103</v>
+        <v>0.4108525826571053</v>
       </c>
       <c r="G39" s="20">
-        <v>0.4149604359308066</v>
+        <v>0.59238818351296</v>
       </c>
       <c r="H39" s="20">
-        <v>0.8229528906242468</v>
+        <v>-0.6603051797569764</v>
       </c>
       <c r="I39" s="20">
-        <v>0.9059327383427908</v>
+        <v>4.097268549112698</v>
       </c>
       <c r="J39" s="20">
-        <v>-0.3460240591209282</v>
+        <v>-0.3818791779226705</v>
       </c>
       <c r="K39" s="20">
-        <v>1.685424151569448</v>
+        <v>0.619199233164106</v>
       </c>
       <c r="L39" s="20">
-        <v>-0.07745571202990834</v>
+        <v>0.5013363353587109</v>
       </c>
       <c r="M39" s="20">
-        <v>0.1359308815455718</v>
+        <v>0.1290543593775588</v>
       </c>
       <c r="N39" s="20">
-        <v>14.451568</v>
+        <v>11.024229</v>
       </c>
       <c r="O39" s="20">
-        <v>2.5837662</v>
+        <v>1.1926677</v>
       </c>
       <c r="P39" s="12">
-        <v>0.16902</v>
+        <v>0.09031</v>
       </c>
       <c r="Q39" s="12">
-        <v>0.425</v>
+        <v>11.11</v>
       </c>
       <c r="R39" s="12">
-        <v>0.1518708779153592</v>
+        <v>0.1115481164973846</v>
       </c>
       <c r="S39" s="11">
-        <v>33.11340495895067</v>
+        <v>35.16621525115872</v>
       </c>
       <c r="T39" s="9" t="s">
         <v>115</v>
@@ -6722,58 +6722,58 @@
         <v>36</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>3</v>
+        <v>158</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>43</v>
+        <v>159</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E40" s="10">
-        <v>453.2300109863281</v>
+        <v>204.3800048828125</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3957304375489474</v>
+        <v>0.4080676006141685</v>
       </c>
       <c r="G40" s="20">
-        <v>-0.8384379108839474</v>
+        <v>0.4853183280948471</v>
       </c>
       <c r="H40" s="20">
-        <v>2.151739124777599</v>
+        <v>-0.3300127972283673</v>
       </c>
       <c r="I40" s="20">
-        <v>2.646453673822382</v>
+        <v>2.301619691710589</v>
       </c>
       <c r="J40" s="20">
-        <v>0.3467417450804187</v>
+        <v>0.5442178148284251</v>
       </c>
       <c r="K40" s="20">
-        <v>-0.2096240432525466</v>
+        <v>-0.1591241325663561</v>
       </c>
       <c r="L40" s="20">
-        <v>-3.017779786263553</v>
+        <v>0.7528680905195144</v>
       </c>
       <c r="M40" s="20">
-        <v>0.4990597875424628</v>
+        <v>-0.574901925364497</v>
       </c>
       <c r="N40" s="20">
-        <v>16.975473</v>
+        <v>19.639769</v>
       </c>
       <c r="O40" s="20">
-        <v>22.350464</v>
+        <v>2.1120868</v>
       </c>
       <c r="P40" s="12">
-        <v>1.30853</v>
+        <v>0.12231</v>
       </c>
       <c r="Q40" s="12">
-        <v>0.438</v>
+        <v>0.535</v>
       </c>
       <c r="R40" s="12">
-        <v>0.6470316659633728</v>
+        <v>-0.0126146936932281</v>
       </c>
       <c r="S40" s="11">
-        <v>48.70413616150016</v>
+        <v>48.01631904750207</v>
       </c>
       <c r="T40" s="9" t="s">
         <v>115</v>
@@ -6784,58 +6784,58 @@
         <v>37</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="D41" s="9" t="s">
         <v>61</v>
       </c>
       <c r="E41" s="10">
-        <v>175.2100067138672</v>
+        <v>423.6400146484375</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3930162745520817</v>
+        <v>0.4041721765744405</v>
       </c>
       <c r="G41" s="20">
-        <v>-0.2374479080738863</v>
+        <v>-0.2196120997092874</v>
       </c>
       <c r="H41" s="20">
-        <v>0.1553448042906527</v>
+        <v>1.242182663983196</v>
       </c>
       <c r="I41" s="20">
-        <v>-0.4072863312933673</v>
+        <v>-0.09888920711276358</v>
       </c>
       <c r="J41" s="20">
-        <v>1.53851837986278</v>
+        <v>0.8572611527945363</v>
       </c>
       <c r="K41" s="20">
-        <v>-0.1502736327553743</v>
+        <v>0.003829187482897866</v>
       </c>
       <c r="L41" s="20">
-        <v>0.4379286951569987</v>
+        <v>0.1238796578777723</v>
       </c>
       <c r="M41" s="20">
-        <v>-0.2271004661174427</v>
+        <v>-0.1278572351612215</v>
       </c>
       <c r="N41" s="20">
-        <v>34.14822</v>
+        <v>25.768177</v>
       </c>
       <c r="O41" s="20">
-        <v>6.61701</v>
+        <v>19.177149</v>
       </c>
       <c r="P41" s="12">
-        <v>0.20971</v>
+        <v>0.91473</v>
       </c>
       <c r="Q41" s="12">
-        <v>0.081</v>
+        <v>0.095</v>
       </c>
       <c r="R41" s="12">
-        <v>0.5960411169627278</v>
+        <v>0.230182197080671</v>
       </c>
       <c r="S41" s="11">
-        <v>76.76883688666288</v>
+        <v>60.85862849109794</v>
       </c>
       <c r="T41" s="9" t="s">
         <v>115</v>
@@ -6846,58 +6846,58 @@
         <v>38</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>161</v>
+        <v>61</v>
       </c>
       <c r="E42" s="10">
-        <v>262.8699951171875</v>
+        <v>152.7700042724609</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3897912908289492</v>
+        <v>0.4000967053555931</v>
       </c>
       <c r="G42" s="20">
-        <v>-3.850609330339901</v>
+        <v>-0.2351435193636175</v>
       </c>
       <c r="H42" s="20">
-        <v>-0.4558428702845563</v>
+        <v>-0.3192964222125583</v>
       </c>
       <c r="I42" s="20">
-        <v>4.097268549112698</v>
+        <v>-0.6222982617295744</v>
       </c>
       <c r="J42" s="20">
-        <v>1.514835964631135</v>
+        <v>1.952981222687295</v>
       </c>
       <c r="K42" s="20">
-        <v>4.125808907685986</v>
+        <v>0.2099937713151807</v>
       </c>
       <c r="L42" s="20">
-        <v>-3.017779786263553</v>
+        <v>-0.2028868736290599</v>
       </c>
       <c r="M42" s="20">
-        <v>-0.2796512063931901</v>
+        <v>-0.5397576797281944</v>
       </c>
       <c r="N42" s="20">
-        <v>384.93335</v>
+        <v>72.30144</v>
       </c>
       <c r="O42" s="20">
-        <v>52.538673</v>
+        <v>2.3325565</v>
       </c>
       <c r="P42" s="12">
-        <v>0.22213</v>
+        <v>0.03211</v>
       </c>
       <c r="Q42" s="12">
-        <v>1.655</v>
+        <v>0.013</v>
       </c>
       <c r="R42" s="12">
-        <v>0.9729059162390545</v>
+        <v>0.8044988040521823</v>
       </c>
       <c r="S42" s="11">
-        <v>52.71776508782204</v>
+        <v>74.82190785255371</v>
       </c>
       <c r="T42" s="9" t="s">
         <v>115</v>
@@ -6908,58 +6908,58 @@
         <v>39</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>162</v>
+        <v>14</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>163</v>
+        <v>64</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E43" s="10">
-        <v>418.1300048828125</v>
+        <v>225.4199981689453</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3786346422075749</v>
+        <v>0.4000016436444572</v>
       </c>
       <c r="G43" s="20">
-        <v>-0.2196120997092874</v>
+        <v>1.23099937351617</v>
       </c>
       <c r="H43" s="20">
-        <v>1.242182663983196</v>
+        <v>0.1667435013429619</v>
       </c>
       <c r="I43" s="20">
-        <v>-0.09888920711276358</v>
+        <v>-0.05584647993229746</v>
       </c>
       <c r="J43" s="20">
-        <v>0.7710514738671556</v>
+        <v>-0.299929212240946</v>
       </c>
       <c r="K43" s="20">
-        <v>0.003829187482897866</v>
+        <v>1.881176382682929</v>
       </c>
       <c r="L43" s="20">
-        <v>0.1143597632771644</v>
+        <v>0.3935880109954843</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.1166501978189085</v>
+        <v>-0.02562798399367761</v>
       </c>
       <c r="N43" s="20">
-        <v>25.768177</v>
+        <v>4.5574694</v>
       </c>
       <c r="O43" s="20">
-        <v>19.177149</v>
+        <v>1.8238496</v>
       </c>
       <c r="P43" s="12">
-        <v>0.91473</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q43" s="12">
-        <v>0.095</v>
+        <v>0.118</v>
       </c>
       <c r="R43" s="12">
-        <v>0.2149827563991888</v>
+        <v>0.09784639480564694</v>
       </c>
       <c r="S43" s="11">
-        <v>58.26064927610839</v>
+        <v>26.61103062050894</v>
       </c>
       <c r="T43" s="9" t="s">
         <v>115</v>
@@ -6976,52 +6976,52 @@
         <v>165</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="E44" s="10">
-        <v>359.739990234375</v>
+        <v>175.0299987792969</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3723854701971951</v>
+        <v>0.3853008363421832</v>
       </c>
       <c r="G44" s="20">
-        <v>-0.5841071338335053</v>
+        <v>-0.2374479080738863</v>
       </c>
       <c r="H44" s="20">
-        <v>0.2793198048091971</v>
+        <v>0.1553448042906527</v>
       </c>
       <c r="I44" s="20">
-        <v>0.8280381860846351</v>
+        <v>-0.4072863312933673</v>
       </c>
       <c r="J44" s="20">
-        <v>0.9769890779368873</v>
+        <v>1.496539466448083</v>
       </c>
       <c r="K44" s="20">
-        <v>0.613993056804705</v>
+        <v>-0.1502736327553743</v>
       </c>
       <c r="L44" s="20">
-        <v>-0.2733111740760106</v>
+        <v>0.4301254809532029</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.004343160547240599</v>
+        <v>-0.1602701077832147</v>
       </c>
       <c r="N44" s="20">
-        <v>49.005413</v>
+        <v>34.14822</v>
       </c>
       <c r="O44" s="20">
-        <v>9.385771999999999</v>
+        <v>6.61701</v>
       </c>
       <c r="P44" s="12">
-        <v>0.20897</v>
+        <v>0.20971</v>
       </c>
       <c r="Q44" s="12">
-        <v>0.365</v>
+        <v>0.081</v>
       </c>
       <c r="R44" s="12">
-        <v>0.2891134285874886</v>
+        <v>0.5692063745470108</v>
       </c>
       <c r="S44" s="11">
-        <v>64.41720015945053</v>
+        <v>76.36871496674689</v>
       </c>
       <c r="T44" s="9" t="s">
         <v>115</v>
@@ -7341,7 +7341,7 @@
         <v>225</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7478,10 +7478,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BI17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:60">
+    <row r="1" spans="1:61">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7662,8 +7662,11 @@
       <c r="BH1">
         <v>543.4299926757812</v>
       </c>
-    </row>
-    <row r="2" spans="1:60">
+      <c r="BI1">
+        <v>539.5900268554688</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -7844,8 +7847,11 @@
       <c r="BH2">
         <v>1053.97998046875</v>
       </c>
-    </row>
-    <row r="3" spans="1:60">
+      <c r="BI2">
+        <v>1065.079956054688</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8026,8 +8032,11 @@
       <c r="BH3">
         <v>1712.890014648438</v>
       </c>
-    </row>
-    <row r="4" spans="1:60">
+      <c r="BI3">
+        <v>1729.760009765625</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -8208,8 +8217,11 @@
       <c r="BH4">
         <v>453.2300109863281</v>
       </c>
-    </row>
-    <row r="5" spans="1:60">
+      <c r="BI4">
+        <v>453.4800109863281</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -8390,8 +8402,11 @@
       <c r="BH5">
         <v>389.5700073242188</v>
       </c>
-    </row>
-    <row r="6" spans="1:60">
+      <c r="BI5">
+        <v>387.7200012207031</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -8572,8 +8587,11 @@
       <c r="BH6">
         <v>389.4400024414062</v>
       </c>
-    </row>
-    <row r="7" spans="1:60">
+      <c r="BI6">
+        <v>392.0299987792969</v>
+      </c>
+    </row>
+    <row r="7" spans="1:61">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -8754,8 +8772,11 @@
       <c r="BH7">
         <v>56.09999847412109</v>
       </c>
-    </row>
-    <row r="8" spans="1:60">
+      <c r="BI7">
+        <v>54.93999862670898</v>
+      </c>
+    </row>
+    <row r="8" spans="1:61">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -8936,8 +8957,11 @@
       <c r="BH8">
         <v>253.5500030517578</v>
       </c>
-    </row>
-    <row r="9" spans="1:60">
+      <c r="BI8">
+        <v>252.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -9118,8 +9142,11 @@
       <c r="BH9">
         <v>42.33000183105469</v>
       </c>
-    </row>
-    <row r="10" spans="1:60">
+      <c r="BI9">
+        <v>42.18999862670898</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -9300,8 +9327,11 @@
       <c r="BH10">
         <v>228.8600006103516</v>
       </c>
-    </row>
-    <row r="11" spans="1:60">
+      <c r="BI10">
+        <v>227.2100067138672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -9482,8 +9512,11 @@
       <c r="BH11">
         <v>363.1600036621094</v>
       </c>
-    </row>
-    <row r="12" spans="1:60">
+      <c r="BI11">
+        <v>363.2099914550781</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -9664,8 +9697,11 @@
       <c r="BH12">
         <v>339.1600036621094</v>
       </c>
-    </row>
-    <row r="13" spans="1:60">
+      <c r="BI12">
+        <v>337.3200073242188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -9846,8 +9882,11 @@
       <c r="BH13">
         <v>62.52999877929688</v>
       </c>
-    </row>
-    <row r="14" spans="1:60">
+      <c r="BI13">
+        <v>62.20999908447266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:61">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -10028,8 +10067,11 @@
       <c r="BH14">
         <v>342.75</v>
       </c>
-    </row>
-    <row r="15" spans="1:60">
+      <c r="BI14">
+        <v>340.9200134277344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:61">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -10210,8 +10252,11 @@
       <c r="BH15">
         <v>227.5500030517578</v>
       </c>
-    </row>
-    <row r="16" spans="1:60">
+      <c r="BI15">
+        <v>225.4199981689453</v>
+      </c>
+    </row>
+    <row r="16" spans="1:61">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -10392,8 +10437,11 @@
       <c r="BH16">
         <v>158.4299926757812</v>
       </c>
-    </row>
-    <row r="17" spans="1:60">
+      <c r="BI16">
+        <v>156.4299926757812</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -10573,6 +10621,9 @@
       </c>
       <c r="BH17">
         <v>124.8199996948242</v>
+      </c>
+      <c r="BI17">
+        <v>123.1999969482422</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -600,7 +600,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-10-02 01:43 UTC · данные на 2026-10-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-03 01:15 UTC · данные на 2026-10-01 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -681,7 +681,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-10-02 01:43 UTC</t>
+    <t>2026-10-03 01:15 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -4754,7 +4754,7 @@
         <v>1097.390014648438</v>
       </c>
       <c r="F5" s="17">
-        <v>1.285486808019755</v>
+        <v>1.285486805459509</v>
       </c>
       <c r="G5" s="20">
         <v>-0.5652307531380691</v>
@@ -4766,16 +4766,16 @@
         <v>3.949484521250298</v>
       </c>
       <c r="J5" s="20">
-        <v>2.48393739314099</v>
+        <v>2.483937385166392</v>
       </c>
       <c r="K5" s="20">
         <v>0</v>
       </c>
       <c r="L5" s="20">
-        <v>-2.794696396170142</v>
+        <v>-2.79469639389148</v>
       </c>
       <c r="M5" s="20">
-        <v>-0.368573400041603</v>
+        <v>-0.3685734000085525</v>
       </c>
       <c r="N5" s="20">
         <v>24.447256</v>
@@ -4793,7 +4793,7 @@
         <v>1.983712963688992</v>
       </c>
       <c r="S5" s="11">
-        <v>63.52153926643471</v>
+        <v>63.52153926655919</v>
       </c>
       <c r="T5" s="9" t="s">
         <v>121</v>
@@ -4816,7 +4816,7 @@
         <v>1787.68994140625</v>
       </c>
       <c r="F6" s="17">
-        <v>1.085461078478544</v>
+        <v>1.08546107774469</v>
       </c>
       <c r="G6" s="20">
         <v>-0.5400051267382519</v>
@@ -4828,16 +4828,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J6" s="20">
-        <v>2.170862005413911</v>
+        <v>2.170862002469971</v>
       </c>
       <c r="K6" s="20">
         <v>0.09339231842057676</v>
       </c>
       <c r="L6" s="20">
-        <v>-2.979224572392682</v>
+        <v>-2.979224569881017</v>
       </c>
       <c r="M6" s="20">
-        <v>-0.5026344029312562</v>
+        <v>-0.5026344029484163</v>
       </c>
       <c r="N6" s="20">
         <v>24.095963</v>
@@ -4878,7 +4878,7 @@
         <v>64.58000183105469</v>
       </c>
       <c r="F7" s="17">
-        <v>1.001733184344769</v>
+        <v>1.001733181017572</v>
       </c>
       <c r="G7" s="20">
         <v>0.3308679966228206</v>
@@ -4890,16 +4890,16 @@
         <v>2.202669227673142</v>
       </c>
       <c r="J7" s="20">
-        <v>2.823883111196433</v>
+        <v>2.823883101153019</v>
       </c>
       <c r="K7" s="20">
         <v>0</v>
       </c>
       <c r="L7" s="20">
-        <v>-2.065975589387055</v>
+        <v>-2.065975588028546</v>
       </c>
       <c r="M7" s="20">
-        <v>-0.4456779448332291</v>
+        <v>-0.4456779447884763</v>
       </c>
       <c r="N7" s="20">
         <v>32.4433</v>
@@ -4917,7 +4917,7 @@
         <v>1.707788463053347</v>
       </c>
       <c r="S7" s="11">
-        <v>63.01389754872083</v>
+        <v>63.01389754872125</v>
       </c>
       <c r="T7" s="9" t="s">
         <v>121</v>
@@ -4940,7 +4940,7 @@
         <v>408.4599914550781</v>
       </c>
       <c r="F8" s="17">
-        <v>0.9781275114323849</v>
+        <v>0.9781275085965883</v>
       </c>
       <c r="G8" s="20">
         <v>0.6066625783285674</v>
@@ -4952,16 +4952,16 @@
         <v>2.855442298450458</v>
       </c>
       <c r="J8" s="20">
-        <v>2.391495645687474</v>
+        <v>2.391495636466272</v>
       </c>
       <c r="K8" s="20">
         <v>0.6194862069932039</v>
       </c>
       <c r="L8" s="20">
-        <v>0.0883169387750089</v>
+        <v>0.08831693741330324</v>
       </c>
       <c r="M8" s="20">
-        <v>-1.305906390742624</v>
+        <v>-1.305906390589295</v>
       </c>
       <c r="N8" s="20">
         <v>16.15269</v>
@@ -5002,7 +5002,7 @@
         <v>420.1499938964844</v>
       </c>
       <c r="F9" s="17">
-        <v>0.9656747719148259</v>
+        <v>0.9656747691895257</v>
       </c>
       <c r="G9" s="20">
         <v>0.63544661477666</v>
@@ -5014,16 +5014,16 @@
         <v>2.432487252480616</v>
       </c>
       <c r="J9" s="20">
-        <v>2.396892440402444</v>
+        <v>2.396892431519611</v>
       </c>
       <c r="K9" s="20">
         <v>0.7879194282358235</v>
       </c>
       <c r="L9" s="20">
-        <v>-0.01322631425197463</v>
+        <v>-0.01322631548546208</v>
       </c>
       <c r="M9" s="20">
-        <v>-1.410073254028723</v>
+        <v>-1.410073253859235</v>
       </c>
       <c r="N9" s="20">
         <v>13.640207</v>
@@ -5041,7 +5041,7 @@
         <v>0.7757319079127687</v>
       </c>
       <c r="S9" s="11">
-        <v>68.22267862046635</v>
+        <v>68.22267862051785</v>
       </c>
       <c r="T9" s="9" t="s">
         <v>121</v>
@@ -5064,7 +5064,7 @@
         <v>215.0500030517578</v>
       </c>
       <c r="F10" s="17">
-        <v>0.8935350913976876</v>
+        <v>0.8935351291843813</v>
       </c>
       <c r="G10" s="20">
         <v>-0.4407742654660424</v>
@@ -5076,16 +5076,16 @@
         <v>0.4340417055879129</v>
       </c>
       <c r="J10" s="20">
-        <v>2.185833396767238</v>
+        <v>2.18583350770885</v>
       </c>
       <c r="K10" s="20">
         <v>0</v>
       </c>
       <c r="L10" s="20">
-        <v>-0.497088857853933</v>
+        <v>-0.4970888584764495</v>
       </c>
       <c r="M10" s="20">
-        <v>-0.2801998378222837</v>
+        <v>-0.2801998377328109</v>
       </c>
       <c r="N10" s="20">
         <v>28.41031</v>
@@ -5100,10 +5100,10 @@
         <v>0.299</v>
       </c>
       <c r="R10" s="12">
-        <v>1.124735473127145</v>
+        <v>1.12473563328948</v>
       </c>
       <c r="S10" s="11">
-        <v>70.13029100919474</v>
+        <v>70.130291009312</v>
       </c>
       <c r="T10" s="9" t="s">
         <v>121</v>
@@ -5126,7 +5126,7 @@
         <v>334.9299926757812</v>
       </c>
       <c r="F11" s="17">
-        <v>0.8276442614933179</v>
+        <v>0.8276442728913612</v>
       </c>
       <c r="G11" s="20">
         <v>-0.3209980775361091</v>
@@ -5138,16 +5138,16 @@
         <v>1.392272810408264</v>
       </c>
       <c r="J11" s="20">
-        <v>0.04098232086480564</v>
+        <v>0.04098235918876483</v>
       </c>
       <c r="K11" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L11" s="20">
-        <v>0.1047993079355826</v>
+        <v>0.1047993065530647</v>
       </c>
       <c r="M11" s="20">
-        <v>-0.01227076923426584</v>
+        <v>-0.01227076943668289</v>
       </c>
       <c r="N11" s="20">
         <v>17.12249</v>
@@ -5165,7 +5165,7 @@
         <v>0.1371622507241324</v>
       </c>
       <c r="S11" s="11">
-        <v>45.17125526720505</v>
+        <v>45.17125526719685</v>
       </c>
       <c r="T11" s="9" t="s">
         <v>121</v>
@@ -5188,7 +5188,7 @@
         <v>338.239990234375</v>
       </c>
       <c r="F12" s="17">
-        <v>0.8254534949808605</v>
+        <v>0.8254534944590238</v>
       </c>
       <c r="G12" s="20">
         <v>-0.3286805258697003</v>
@@ -5200,16 +5200,16 @@
         <v>1.392272810408264</v>
       </c>
       <c r="J12" s="20">
-        <v>0.05889042149936171</v>
+        <v>0.05889042007146154</v>
       </c>
       <c r="K12" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L12" s="20">
-        <v>0.04236630920973218</v>
+        <v>0.04236630790604818</v>
       </c>
       <c r="M12" s="20">
-        <v>-0.04270047022460094</v>
+        <v>-0.042700470415171</v>
       </c>
       <c r="N12" s="20">
         <v>17.273733</v>
@@ -5227,7 +5227,7 @@
         <v>0.1387724584582675</v>
       </c>
       <c r="S12" s="11">
-        <v>45.42895605791418</v>
+        <v>45.42895605791296</v>
       </c>
       <c r="T12" s="9" t="s">
         <v>121</v>
@@ -5250,7 +5250,7 @@
         <v>41.91999816894531</v>
       </c>
       <c r="F13" s="17">
-        <v>0.8154608077916036</v>
+        <v>0.815460809177788</v>
       </c>
       <c r="G13" s="20">
         <v>-0.01962276509782637</v>
@@ -5262,16 +5262,16 @@
         <v>3.890766583974275</v>
       </c>
       <c r="J13" s="20">
-        <v>1.256350728126966</v>
+        <v>1.256350732244048</v>
       </c>
       <c r="K13" s="20">
         <v>3.411630748024409</v>
       </c>
       <c r="L13" s="20">
-        <v>-2.979224572392682</v>
+        <v>-2.979224569881017</v>
       </c>
       <c r="M13" s="20">
-        <v>-0.591224341040976</v>
+        <v>-0.5912243410364808</v>
       </c>
       <c r="N13" s="20">
         <v>13.269938</v>
@@ -5312,7 +5312,7 @@
         <v>541.739990234375</v>
       </c>
       <c r="F14" s="17">
-        <v>0.7962785804127523</v>
+        <v>0.7962785779927749</v>
       </c>
       <c r="G14" s="20">
         <v>-0.1018209436010066</v>
@@ -5324,16 +5324,16 @@
         <v>2.17697052724581</v>
       </c>
       <c r="J14" s="20">
-        <v>2.695448949789352</v>
+        <v>2.695448941223713</v>
       </c>
       <c r="K14" s="20">
         <v>1.622807555753254</v>
       </c>
       <c r="L14" s="20">
-        <v>-2.979224572392682</v>
+        <v>-2.979224569881017</v>
       </c>
       <c r="M14" s="20">
-        <v>-1.148182669217457</v>
+        <v>-1.148182669229773</v>
       </c>
       <c r="N14" s="20">
         <v>32.783344</v>
@@ -5351,7 +5351,7 @@
         <v>2.213568150082671</v>
       </c>
       <c r="S14" s="11">
-        <v>54.03869553907989</v>
+        <v>54.0386955390799</v>
       </c>
       <c r="T14" s="9" t="s">
         <v>121</v>
@@ -5374,7 +5374,7 @@
         <v>264.2300109863281</v>
       </c>
       <c r="F15" s="17">
-        <v>0.7644548025127714</v>
+        <v>0.7644548019186523</v>
       </c>
       <c r="G15" s="20">
         <v>0.4452704814464517</v>
@@ -5386,16 +5386,16 @@
         <v>2.40169945735154</v>
       </c>
       <c r="J15" s="20">
-        <v>1.915666431479693</v>
+        <v>1.915666430046824</v>
       </c>
       <c r="K15" s="20">
         <v>0.7031829619933945</v>
       </c>
       <c r="L15" s="20">
-        <v>0.3280242064398979</v>
+        <v>0.3280242047755149</v>
       </c>
       <c r="M15" s="20">
-        <v>-1.35255215501187</v>
+        <v>-1.352552155816811</v>
       </c>
       <c r="N15" s="20">
         <v>14.597602</v>
@@ -5413,7 +5413,7 @@
         <v>0.5233484325939939</v>
       </c>
       <c r="S15" s="11">
-        <v>62.72541706055569</v>
+        <v>62.72541707729614</v>
       </c>
       <c r="T15" s="9" t="s">
         <v>121</v>
@@ -5436,7 +5436,7 @@
         <v>361.6400146484375</v>
       </c>
       <c r="F16" s="17">
-        <v>0.7535570045459029</v>
+        <v>0.7535570032185959</v>
       </c>
       <c r="G16" s="20">
         <v>1.160842542624806</v>
@@ -5448,16 +5448,16 @@
         <v>-0.379797036716154</v>
       </c>
       <c r="J16" s="20">
-        <v>0.4281959295638111</v>
+        <v>0.4281959255698076</v>
       </c>
       <c r="K16" s="20">
         <v>3.857147015323562</v>
       </c>
       <c r="L16" s="20">
-        <v>0.5145706798535327</v>
+        <v>0.5145706779535983</v>
       </c>
       <c r="M16" s="20">
-        <v>-0.2507781100722728</v>
+        <v>-0.2507781102611458</v>
       </c>
       <c r="N16" s="20">
         <v>9.756517000000001</v>
@@ -5498,7 +5498,7 @@
         <v>120</v>
       </c>
       <c r="F17" s="17">
-        <v>0.7178515643551848</v>
+        <v>0.7178515626346031</v>
       </c>
       <c r="G17" s="20">
         <v>-0.8300215284456212</v>
@@ -5510,16 +5510,16 @@
         <v>0.5176902230779757</v>
       </c>
       <c r="J17" s="20">
-        <v>2.234405112252195</v>
+        <v>2.234405106137475</v>
       </c>
       <c r="K17" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L17" s="20">
-        <v>-2.481750997246986</v>
+        <v>-2.481750995363479</v>
       </c>
       <c r="M17" s="20">
-        <v>-0.2003397895804699</v>
+        <v>-0.2003397895701755</v>
       </c>
       <c r="N17" s="20">
         <v>59.648514</v>
@@ -5560,7 +5560,7 @@
         <v>156.6999969482422</v>
       </c>
       <c r="F18" s="17">
-        <v>0.7020475725239862</v>
+        <v>0.7020475634535434</v>
       </c>
       <c r="G18" s="20">
         <v>0.4643687022637146</v>
@@ -5572,16 +5572,16 @@
         <v>-0.03871237626800461</v>
       </c>
       <c r="J18" s="20">
-        <v>1.052444307841311</v>
+        <v>1.052444278055609</v>
       </c>
       <c r="K18" s="20">
         <v>3.322215581191908</v>
       </c>
       <c r="L18" s="20">
-        <v>0.5136728617938997</v>
+        <v>0.513672859895099</v>
       </c>
       <c r="M18" s="20">
-        <v>-0.4155592139149851</v>
+        <v>-0.4155592141750382</v>
       </c>
       <c r="N18" s="20">
         <v>16.332987</v>
@@ -5596,10 +5596,10 @@
         <v>0.053</v>
       </c>
       <c r="R18" s="12">
-        <v>0.3233260271893192</v>
+        <v>0.323326112451183</v>
       </c>
       <c r="S18" s="11">
-        <v>49.22291097140219</v>
+        <v>49.2229109732122</v>
       </c>
       <c r="T18" s="9" t="s">
         <v>121</v>
@@ -5622,7 +5622,7 @@
         <v>236.6900024414062</v>
       </c>
       <c r="F19" s="17">
-        <v>0.6847242694846301</v>
+        <v>0.6847242687126274</v>
       </c>
       <c r="G19" s="20">
         <v>0.4118301704600924</v>
@@ -5634,16 +5634,16 @@
         <v>0.1953152078062003</v>
       </c>
       <c r="J19" s="20">
-        <v>1.012631722932007</v>
+        <v>1.012631720144824</v>
       </c>
       <c r="K19" s="20">
         <v>3.557710177558904</v>
       </c>
       <c r="L19" s="20">
-        <v>-1.80664429698869</v>
+        <v>-1.806644295957637</v>
       </c>
       <c r="M19" s="20">
-        <v>-1.464827728712908</v>
+        <v>-1.464827728684295</v>
       </c>
       <c r="N19" s="20">
         <v>21.410795</v>
@@ -5661,7 +5661,7 @@
         <v>0.2796010923994163</v>
       </c>
       <c r="S19" s="11">
-        <v>53.09756456171621</v>
+        <v>53.09756456171831</v>
       </c>
       <c r="T19" s="9" t="s">
         <v>121</v>
@@ -5684,7 +5684,7 @@
         <v>57.84000015258789</v>
       </c>
       <c r="F20" s="17">
-        <v>0.6616465574362155</v>
+        <v>0.6616465151129166</v>
       </c>
       <c r="G20" s="20">
         <v>0.5909946933403921</v>
@@ -5696,16 +5696,16 @@
         <v>2.900414534129918</v>
       </c>
       <c r="J20" s="20">
-        <v>0.3502260376541535</v>
+        <v>0.3502258974504746</v>
       </c>
       <c r="K20" s="20">
         <v>0.9293201571802452</v>
       </c>
       <c r="L20" s="20">
-        <v>0.1183836662686155</v>
+        <v>0.1183836648689447</v>
       </c>
       <c r="M20" s="20">
-        <v>-0.7102962230422424</v>
+        <v>-0.7102962252699278</v>
       </c>
       <c r="N20" s="20">
         <v>16.772861</v>
@@ -5723,7 +5723,7 @@
         <v>-0.06196697287300468</v>
       </c>
       <c r="S20" s="11">
-        <v>49.00085616387121</v>
+        <v>49.00085617630703</v>
       </c>
       <c r="T20" s="9" t="s">
         <v>121</v>
@@ -5746,7 +5746,7 @@
         <v>248.2299957275391</v>
       </c>
       <c r="F21" s="17">
-        <v>0.6248209607391152</v>
+        <v>0.6248209600504624</v>
       </c>
       <c r="G21" s="20">
         <v>-0.01172638762890057</v>
@@ -5758,16 +5758,16 @@
         <v>1.021835496573962</v>
       </c>
       <c r="J21" s="20">
-        <v>0.1156628152337254</v>
+        <v>0.1156628131284615</v>
       </c>
       <c r="K21" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L21" s="20">
-        <v>-0.4537346920669745</v>
+        <v>-0.4537346927442339</v>
       </c>
       <c r="M21" s="20">
-        <v>-0.03800838870403797</v>
+        <v>-0.03800838890951242</v>
       </c>
       <c r="N21" s="20">
         <v>20.08608</v>
@@ -5808,7 +5808,7 @@
         <v>60.9900016784668</v>
       </c>
       <c r="F22" s="17">
-        <v>0.6128426228027249</v>
+        <v>0.6128426213481737</v>
       </c>
       <c r="G22" s="20">
         <v>1.236177102540873</v>
@@ -5820,16 +5820,16 @@
         <v>-0.5828068382546813</v>
       </c>
       <c r="J22" s="20">
-        <v>0.6342669720142113</v>
+        <v>0.6342669674886959</v>
       </c>
       <c r="K22" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L22" s="20">
-        <v>0.004471254674813079</v>
+        <v>0.004471253418978988</v>
       </c>
       <c r="M22" s="20">
-        <v>-0.2171611740366948</v>
+        <v>-0.2171611743060273</v>
       </c>
       <c r="N22" s="20">
         <v>11.559979</v>
@@ -5870,7 +5870,7 @@
         <v>230.8600006103516</v>
       </c>
       <c r="F23" s="17">
-        <v>0.5890849734606489</v>
+        <v>0.5890849891517805</v>
       </c>
       <c r="G23" s="20">
         <v>-1.098910330048646</v>
@@ -5882,16 +5882,16 @@
         <v>2.414157689348599</v>
       </c>
       <c r="J23" s="20">
-        <v>0.8339069483269244</v>
+        <v>0.8339070006761288</v>
       </c>
       <c r="K23" s="20">
         <v>-0.299618531145536</v>
       </c>
       <c r="L23" s="20">
-        <v>-0.2322942481516655</v>
+        <v>-0.2322942491085369</v>
       </c>
       <c r="M23" s="20">
-        <v>-0.4284248878259105</v>
+        <v>-0.4284248872786271</v>
       </c>
       <c r="N23" s="20">
         <v>28.489874</v>
@@ -5906,10 +5906,10 @@
         <v>1.059</v>
       </c>
       <c r="R23" s="12">
-        <v>0.3165728959678238</v>
+        <v>0.3165730105352706</v>
       </c>
       <c r="S23" s="11">
-        <v>60.21556912334641</v>
+        <v>60.21556911417232</v>
       </c>
       <c r="T23" s="9" t="s">
         <v>121</v>
@@ -5932,7 +5932,7 @@
         <v>265.7200012207031</v>
       </c>
       <c r="F24" s="17">
-        <v>0.5799417315151679</v>
+        <v>0.5799417288299482</v>
       </c>
       <c r="G24" s="20">
         <v>-0.7382512714864492</v>
@@ -5944,16 +5944,16 @@
         <v>-0.4590192885594346</v>
       </c>
       <c r="J24" s="20">
-        <v>2.594064455729839</v>
+        <v>2.594064446804781</v>
       </c>
       <c r="K24" s="20">
         <v>-0.265308060151669</v>
       </c>
       <c r="L24" s="20">
-        <v>-0.8075716469285997</v>
+        <v>-0.8075716471590709</v>
       </c>
       <c r="M24" s="20">
-        <v>-0.125459639136982</v>
+        <v>-0.1254596390604076</v>
       </c>
       <c r="N24" s="20">
         <v>50.27933</v>
@@ -5994,7 +5994,7 @@
         <v>114.4300003051758</v>
       </c>
       <c r="F25" s="17">
-        <v>0.5689208109667999</v>
+        <v>0.5689208107871169</v>
       </c>
       <c r="G25" s="20">
         <v>0.4073104247281907</v>
@@ -6006,16 +6006,16 @@
         <v>0.4715191624753287</v>
       </c>
       <c r="J25" s="20">
-        <v>-0.2030740583953191</v>
+        <v>-0.203074058646881</v>
       </c>
       <c r="K25" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L25" s="20">
-        <v>0.1033991309948696</v>
+        <v>0.1033991296141197</v>
       </c>
       <c r="M25" s="20">
-        <v>0.3516899595408978</v>
+        <v>0.3516899592737782</v>
       </c>
       <c r="N25" s="20">
         <v>13.979167</v>
@@ -6056,7 +6056,7 @@
         <v>375.4500122070312</v>
       </c>
       <c r="F26" s="17">
-        <v>0.561619443805634</v>
+        <v>0.5616194419195365</v>
       </c>
       <c r="G26" s="20">
         <v>0.08345580963657841</v>
@@ -6068,16 +6068,16 @@
         <v>0.4617856253832925</v>
       </c>
       <c r="J26" s="20">
-        <v>1.589539223310789</v>
+        <v>1.589539216802767</v>
       </c>
       <c r="K26" s="20">
         <v>1.724699257492616</v>
       </c>
       <c r="L26" s="20">
-        <v>-1.810870409335119</v>
+        <v>-1.810870408298729</v>
       </c>
       <c r="M26" s="20">
-        <v>-0.4544063256900623</v>
+        <v>-0.4544063256384905</v>
       </c>
       <c r="N26" s="20">
         <v>33.886448</v>
@@ -6118,7 +6118,7 @@
         <v>415.7900085449219</v>
       </c>
       <c r="F27" s="17">
-        <v>0.5611223540533053</v>
+        <v>0.5611223527027128</v>
       </c>
       <c r="G27" s="20">
         <v>-1.18924796979833</v>
@@ -6130,16 +6130,16 @@
         <v>3.655490679943009</v>
       </c>
       <c r="J27" s="20">
-        <v>1.345352954417839</v>
+        <v>1.345352949501701</v>
       </c>
       <c r="K27" s="20">
         <v>0.4344176058747699</v>
       </c>
       <c r="L27" s="20">
-        <v>-2.642298436708754</v>
+        <v>-2.642298434622524</v>
       </c>
       <c r="M27" s="20">
-        <v>0.2763935036486616</v>
+        <v>0.2763935036371011</v>
       </c>
       <c r="N27" s="20">
         <v>54.647465</v>
@@ -6157,7 +6157,7 @@
         <v>0.3328212869389235</v>
       </c>
       <c r="S27" s="11">
-        <v>62.48592231347849</v>
+        <v>62.4859223134785</v>
       </c>
       <c r="T27" s="9" t="s">
         <v>121</v>
@@ -6180,7 +6180,7 @@
         <v>222.8200073242188</v>
       </c>
       <c r="F28" s="17">
-        <v>0.5422090109042741</v>
+        <v>0.5422090087965805</v>
       </c>
       <c r="G28" s="20">
         <v>0.1826167294586985</v>
@@ -6192,16 +6192,16 @@
         <v>-0.8979974000351455</v>
       </c>
       <c r="J28" s="20">
-        <v>0.6949044763941202</v>
+        <v>0.6949044696446123</v>
       </c>
       <c r="K28" s="20">
         <v>3.402793202465384</v>
       </c>
       <c r="L28" s="20">
-        <v>0.02518119391725908</v>
+        <v>0.02518119263527464</v>
       </c>
       <c r="M28" s="20">
-        <v>-0.2945831977506554</v>
+        <v>-0.2945831978246836</v>
       </c>
       <c r="N28" s="20">
         <v>40.498222</v>
@@ -6242,7 +6242,7 @@
         <v>945.5700073242188</v>
       </c>
       <c r="F29" s="17">
-        <v>0.5182066164956924</v>
+        <v>0.5182066144980955</v>
       </c>
       <c r="G29" s="20">
         <v>-2.057025624567463</v>
@@ -6254,16 +6254,16 @@
         <v>1.336500578238815</v>
       </c>
       <c r="J29" s="20">
-        <v>2.089653613368173</v>
+        <v>2.089653606331009</v>
       </c>
       <c r="K29" s="20">
         <v>0.008655852178147645</v>
       </c>
       <c r="L29" s="20">
-        <v>-2.499528413404004</v>
+        <v>-2.499528411498049</v>
       </c>
       <c r="M29" s="20">
-        <v>0.1016598878155299</v>
+        <v>0.101659887805467</v>
       </c>
       <c r="N29" s="20">
         <v>65.76973</v>
@@ -6281,7 +6281,7 @@
         <v>1.238142217971629</v>
       </c>
       <c r="S29" s="11">
-        <v>62.00954285142532</v>
+        <v>62.0095428514892</v>
       </c>
       <c r="T29" s="9" t="s">
         <v>121</v>
@@ -6304,7 +6304,7 @@
         <v>178.7200012207031</v>
       </c>
       <c r="F30" s="17">
-        <v>0.5180490299646927</v>
+        <v>0.5180490271318313</v>
       </c>
       <c r="G30" s="20">
         <v>-1.991192966399809</v>
@@ -6316,16 +6316,16 @@
         <v>0.2259855872354321</v>
       </c>
       <c r="J30" s="20">
-        <v>1.982907476200258</v>
+        <v>1.982907466830991</v>
       </c>
       <c r="K30" s="20">
         <v>0.4474139964027498</v>
       </c>
       <c r="L30" s="20">
-        <v>-0.6600050397023072</v>
+        <v>-0.6600050401191101</v>
       </c>
       <c r="M30" s="20">
-        <v>-0.4826461295663204</v>
+        <v>-0.4826461295297345</v>
       </c>
       <c r="N30" s="20">
         <v>61.29329</v>
@@ -6366,7 +6366,7 @@
         <v>117.1399993896484</v>
       </c>
       <c r="F31" s="17">
-        <v>0.485760718097929</v>
+        <v>0.4857607167993843</v>
       </c>
       <c r="G31" s="20">
         <v>0.3123085537627329</v>
@@ -6378,16 +6378,16 @@
         <v>0.5162516055283453</v>
       </c>
       <c r="J31" s="20">
-        <v>0.3076361805561017</v>
+        <v>0.3076361766132128</v>
       </c>
       <c r="K31" s="20">
         <v>1.664915861063909</v>
       </c>
       <c r="L31" s="20">
-        <v>0.2254188255887091</v>
+        <v>0.2254188240538856</v>
       </c>
       <c r="M31" s="20">
-        <v>-0.107912116632611</v>
+        <v>-0.1079121169274689</v>
       </c>
       <c r="N31" s="20">
         <v>15.782166</v>
@@ -6428,7 +6428,7 @@
         <v>373.8800048828125</v>
       </c>
       <c r="F32" s="17">
-        <v>0.4695113119870993</v>
+        <v>0.4695113094454156</v>
       </c>
       <c r="G32" s="20">
         <v>-0.5841071338335053</v>
@@ -6440,16 +6440,16 @@
         <v>0.8280381860846351</v>
       </c>
       <c r="J32" s="20">
-        <v>1.337786552883619</v>
+        <v>1.337786544579946</v>
       </c>
       <c r="K32" s="20">
         <v>0.611688372676416</v>
       </c>
       <c r="L32" s="20">
-        <v>-0.234943768834207</v>
+        <v>-0.2349437697877328</v>
       </c>
       <c r="M32" s="20">
-        <v>-0.168579196962601</v>
+        <v>-0.168579196879728</v>
       </c>
       <c r="N32" s="20">
         <v>49.005413</v>
@@ -6490,7 +6490,7 @@
         <v>277.5799865722656</v>
       </c>
       <c r="F33" s="17">
-        <v>0.465036716452301</v>
+        <v>0.4650367154680411</v>
       </c>
       <c r="G33" s="20">
         <v>-3.850609330339901</v>
@@ -6502,16 +6502,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J33" s="20">
-        <v>1.822087483969626</v>
+        <v>1.822087480196372</v>
       </c>
       <c r="K33" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L33" s="20">
-        <v>-2.979224572392682</v>
+        <v>-2.979224569881017</v>
       </c>
       <c r="M33" s="20">
-        <v>-0.5179308610198697</v>
+        <v>-0.5179308610571686</v>
       </c>
       <c r="N33" s="20">
         <v>384.93335</v>
@@ -6552,7 +6552,7 @@
         <v>30.95000076293945</v>
       </c>
       <c r="F34" s="17">
-        <v>0.4585150168952701</v>
+        <v>0.4585150146228578</v>
       </c>
       <c r="G34" s="20">
         <v>-0.05525750799347566</v>
@@ -6564,16 +6564,16 @@
         <v>-1.204760955881624</v>
       </c>
       <c r="J34" s="20">
-        <v>0.9112741339007516</v>
+        <v>0.9112741266718484</v>
       </c>
       <c r="K34" s="20">
         <v>4.12430081901671</v>
       </c>
       <c r="L34" s="20">
-        <v>0.4991361139523723</v>
+        <v>0.4991361120719272</v>
       </c>
       <c r="M34" s="20">
-        <v>-0.610578352940521</v>
+        <v>-0.6105783528269535</v>
       </c>
       <c r="N34" s="20">
         <v>495.98203</v>
@@ -6614,7 +6614,7 @@
         <v>207.1000061035156</v>
       </c>
       <c r="F35" s="17">
-        <v>0.4525859177884882</v>
+        <v>0.4525859145748181</v>
       </c>
       <c r="G35" s="20">
         <v>0.4853183280948471</v>
@@ -6626,16 +6626,16 @@
         <v>2.301619691710589</v>
       </c>
       <c r="J35" s="20">
-        <v>0.7199281874606166</v>
+        <v>0.7199281771566947</v>
       </c>
       <c r="K35" s="20">
         <v>-0.1602972246855913</v>
       </c>
       <c r="L35" s="20">
-        <v>0.7897186859703635</v>
+        <v>0.7897186837230011</v>
       </c>
       <c r="M35" s="20">
-        <v>-0.703215166465504</v>
+        <v>-0.7032151663111512</v>
       </c>
       <c r="N35" s="20">
         <v>19.639769</v>
@@ -6653,7 +6653,7 @@
         <v>0.06793386106959676</v>
       </c>
       <c r="S35" s="11">
-        <v>52.67986446308661</v>
+        <v>52.67986446217586</v>
       </c>
       <c r="T35" s="9" t="s">
         <v>121</v>
@@ -6676,7 +6676,7 @@
         <v>462.5599975585938</v>
       </c>
       <c r="F36" s="17">
-        <v>0.4502108907863499</v>
+        <v>0.4502108918820704</v>
       </c>
       <c r="G36" s="20">
         <v>-0.8384379108839474</v>
@@ -6688,16 +6688,16 @@
         <v>2.646453673822382</v>
       </c>
       <c r="J36" s="20">
-        <v>0.5433867357202309</v>
+        <v>0.5433867389287584</v>
       </c>
       <c r="K36" s="20">
         <v>-0.2107232199341534</v>
       </c>
       <c r="L36" s="20">
-        <v>-2.900885218031489</v>
+        <v>-2.900885215618743</v>
       </c>
       <c r="M36" s="20">
-        <v>0.3566245769590605</v>
+        <v>0.3566245768140288</v>
       </c>
       <c r="N36" s="20">
         <v>16.975473</v>
@@ -6715,7 +6715,7 @@
         <v>0.5545262813291512</v>
       </c>
       <c r="S36" s="11">
-        <v>51.64766058406301</v>
+        <v>51.64766058406312</v>
       </c>
       <c r="T36" s="9" t="s">
         <v>121</v>
@@ -6738,7 +6738,7 @@
         <v>61.45999908447266</v>
       </c>
       <c r="F37" s="17">
-        <v>0.4353874964789385</v>
+        <v>0.4353875121117406</v>
       </c>
       <c r="G37" s="20">
         <v>0.4625864400742329</v>
@@ -6750,16 +6750,16 @@
         <v>0.2249472925442899</v>
       </c>
       <c r="J37" s="20">
-        <v>0.2543371964562657</v>
+        <v>0.2543372490533102</v>
       </c>
       <c r="K37" s="20">
         <v>0.8222298992296905</v>
       </c>
       <c r="L37" s="20">
-        <v>0.6778738936539114</v>
+        <v>0.6778738915477748</v>
       </c>
       <c r="M37" s="20">
-        <v>0.1071271878130815</v>
+        <v>0.107127187563794</v>
       </c>
       <c r="N37" s="20">
         <v>13.845816</v>
@@ -6777,7 +6777,7 @@
         <v>0.01724677002681863</v>
       </c>
       <c r="S37" s="11">
-        <v>39.1392914222837</v>
+        <v>39.13929142198131</v>
       </c>
       <c r="T37" s="9" t="s">
         <v>121</v>
@@ -6800,7 +6800,7 @@
         <v>194.4799957275391</v>
       </c>
       <c r="F38" s="17">
-        <v>0.4105079546784793</v>
+        <v>0.4105079551624213</v>
       </c>
       <c r="G38" s="20">
         <v>0.59238818351296</v>
@@ -6812,16 +6812,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J38" s="20">
-        <v>-0.4128970723718264</v>
+        <v>-0.412897070261743</v>
       </c>
       <c r="K38" s="20">
         <v>0.6168869288876079</v>
       </c>
       <c r="L38" s="20">
-        <v>0.6369704150015569</v>
+        <v>0.636970412947069</v>
       </c>
       <c r="M38" s="20">
-        <v>0.1428065105116808</v>
+        <v>0.1428065101890085</v>
       </c>
       <c r="N38" s="20">
         <v>11.024229</v>
@@ -6839,7 +6839,7 @@
         <v>0.06235521795490739</v>
       </c>
       <c r="S38" s="11">
-        <v>34.60049096737299</v>
+        <v>34.60049096718133</v>
       </c>
       <c r="T38" s="9" t="s">
         <v>121</v>
@@ -6862,7 +6862,7 @@
         <v>43.34000015258789</v>
       </c>
       <c r="F39" s="17">
-        <v>0.4048436512849039</v>
+        <v>0.4048436685894283</v>
       </c>
       <c r="G39" s="20">
         <v>1.059148550569024</v>
@@ -6874,16 +6874,16 @@
         <v>-0.2925442957684757</v>
       </c>
       <c r="J39" s="20">
-        <v>1.136910667816565</v>
+        <v>1.136910725616407</v>
       </c>
       <c r="K39" s="20">
         <v>-0.5673441760219223</v>
       </c>
       <c r="L39" s="20">
-        <v>-0.5697136394268014</v>
+        <v>-0.5697136399576148</v>
       </c>
       <c r="M39" s="20">
-        <v>-1.064805934208756</v>
+        <v>-1.064805934253499</v>
       </c>
       <c r="N39" s="20">
         <v>9.016878</v>
@@ -6901,7 +6901,7 @@
         <v>0.06256777056741436</v>
       </c>
       <c r="S39" s="11">
-        <v>51.77883738066112</v>
+        <v>51.77883738066085</v>
       </c>
       <c r="T39" s="9" t="s">
         <v>121</v>
@@ -6924,7 +6924,7 @@
         <v>224.4100036621094</v>
       </c>
       <c r="F40" s="17">
-        <v>0.3933804681189832</v>
+        <v>0.3933804569988119</v>
       </c>
       <c r="G40" s="20">
         <v>1.23099937351617</v>
@@ -6936,16 +6936,16 @@
         <v>-0.05584647993229746</v>
       </c>
       <c r="J40" s="20">
-        <v>-0.310491483102157</v>
+        <v>-0.3104915195875511</v>
       </c>
       <c r="K40" s="20">
         <v>1.877016954480541</v>
       </c>
       <c r="L40" s="20">
-        <v>0.3697879761811656</v>
+        <v>0.3697879744640478</v>
       </c>
       <c r="M40" s="20">
-        <v>-0.04469499391824128</v>
+        <v>-0.04469499481231631</v>
       </c>
       <c r="N40" s="20">
         <v>4.5574694</v>
@@ -6963,7 +6963,7 @@
         <v>0.1099024161447113</v>
       </c>
       <c r="S40" s="11">
-        <v>28.83412545259858</v>
+        <v>28.83412546568528</v>
       </c>
       <c r="T40" s="9" t="s">
         <v>121</v>
@@ -6986,7 +6986,7 @@
         <v>896.6699829101562</v>
       </c>
       <c r="F41" s="17">
-        <v>0.3864458599589694</v>
+        <v>0.3864458481765602</v>
       </c>
       <c r="G41" s="20">
         <v>0.4149604359308066</v>
@@ -6998,16 +6998,16 @@
         <v>0.9059327383427908</v>
       </c>
       <c r="J41" s="20">
-        <v>-0.4270063878948185</v>
+        <v>-0.4270064268168616</v>
       </c>
       <c r="K41" s="20">
         <v>1.681551240939723</v>
       </c>
       <c r="L41" s="20">
-        <v>-0.04700108600208337</v>
+        <v>-0.04700108719292357</v>
       </c>
       <c r="M41" s="20">
-        <v>0.2327884721633677</v>
+        <v>0.2327884717340447</v>
       </c>
       <c r="N41" s="20">
         <v>14.451568</v>
@@ -7025,7 +7025,7 @@
         <v>0.05210667104380784</v>
       </c>
       <c r="S41" s="11">
-        <v>29.81898770434628</v>
+        <v>29.8189877049967</v>
       </c>
       <c r="T41" s="9" t="s">
         <v>121</v>
@@ -7048,7 +7048,7 @@
         <v>1149.849975585938</v>
       </c>
       <c r="F42" s="17">
-        <v>0.3857632300277744</v>
+        <v>0.385763233223959</v>
       </c>
       <c r="G42" s="20">
         <v>-1.110237185891371</v>
@@ -7060,16 +7060,16 @@
         <v>0.7254634342718127</v>
       </c>
       <c r="J42" s="20">
-        <v>0.2952040451130705</v>
+        <v>0.2952040561672602</v>
       </c>
       <c r="K42" s="20">
         <v>0.7977966850370883</v>
       </c>
       <c r="L42" s="20">
-        <v>0.3922093669114455</v>
+        <v>0.3922093651660162</v>
       </c>
       <c r="M42" s="20">
-        <v>0.2096543983640639</v>
+        <v>0.2096543981722334</v>
       </c>
       <c r="N42" s="20">
         <v>39.686787</v>
@@ -7084,10 +7084,10 @@
         <v>0.477</v>
       </c>
       <c r="R42" s="12">
-        <v>0.2084397581701849</v>
+        <v>0.2084396806546296</v>
       </c>
       <c r="S42" s="11">
-        <v>44.99906431885702</v>
+        <v>44.99906432160219</v>
       </c>
       <c r="T42" s="9" t="s">
         <v>121</v>
@@ -7110,7 +7110,7 @@
         <v>425.5299987792969</v>
       </c>
       <c r="F43" s="17">
-        <v>0.3709529256385218</v>
+        <v>0.3709529237346074</v>
       </c>
       <c r="G43" s="20">
         <v>-0.9301946228299454</v>
@@ -7122,16 +7122,16 @@
         <v>4.097268549112698</v>
       </c>
       <c r="J43" s="20">
-        <v>0.8320847960975849</v>
+        <v>0.8320847901525288</v>
       </c>
       <c r="K43" s="20">
         <v>-0.5465499511771544</v>
       </c>
       <c r="L43" s="20">
-        <v>0.5082491235382414</v>
+        <v>0.5082491216462892</v>
       </c>
       <c r="M43" s="20">
-        <v>-0.1990904897869874</v>
+        <v>-0.1990904898729935</v>
       </c>
       <c r="N43" s="20">
         <v>109.756966</v>
@@ -7172,7 +7172,7 @@
         <v>89.98000335693359</v>
       </c>
       <c r="F44" s="17">
-        <v>0.3631776423937694</v>
+        <v>0.3631776406040229</v>
       </c>
       <c r="G44" s="20">
         <v>0.1395143880902008</v>
@@ -7184,16 +7184,16 @@
         <v>0.0309319074885313</v>
       </c>
       <c r="J44" s="20">
-        <v>0.2000980621530313</v>
+        <v>0.2000980564388269</v>
       </c>
       <c r="K44" s="20">
         <v>0.04556560127761066</v>
       </c>
       <c r="L44" s="20">
-        <v>0.2999511255260598</v>
+        <v>0.2999511238971247</v>
       </c>
       <c r="M44" s="20">
-        <v>-0.1627297656754051</v>
+        <v>-0.1627297653972689</v>
       </c>
       <c r="N44" s="20">
         <v>15.618794</v>
@@ -7211,7 +7211,7 @@
         <v>0.02257362158566534</v>
       </c>
       <c r="S44" s="11">
-        <v>51.16020198221448</v>
+        <v>51.16020197751875</v>
       </c>
       <c r="T44" s="9" t="s">
         <v>121</v>
@@ -7531,7 +7531,7 @@
         <v>224</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:2">

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -472,6 +472,18 @@
     <t>EOG Resources</t>
   </si>
   <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
+  </si>
+  <si>
+    <t>GS</t>
+  </si>
+  <si>
+    <t>Goldman Sachs</t>
+  </si>
+  <si>
     <t>WBD</t>
   </si>
   <si>
@@ -493,40 +505,37 @@
     <t>Hasbro</t>
   </si>
   <si>
-    <t>GS</t>
-  </si>
-  <si>
-    <t>Goldman Sachs</t>
-  </si>
-  <si>
-    <t>TER</t>
-  </si>
-  <si>
-    <t>Teradyne</t>
-  </si>
-  <si>
     <t>BMY</t>
   </si>
   <si>
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>Lilly (Eli)</t>
+  </si>
+  <si>
+    <t>PTC</t>
+  </si>
+  <si>
+    <t>PTC Inc.</t>
+  </si>
+  <si>
     <t>WSM</t>
   </si>
   <si>
     <t>Williams-Sonoma, Inc.</t>
   </si>
   <si>
-    <t>PTC</t>
-  </si>
-  <si>
-    <t>PTC Inc.</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>Lilly (Eli)</t>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Bloom Energy</t>
+  </si>
+  <si>
+    <t>Industrials</t>
   </si>
   <si>
     <t>COP</t>
@@ -535,12 +544,6 @@
     <t>ConocoPhillips</t>
   </si>
   <si>
-    <t>FFIV</t>
-  </si>
-  <si>
-    <t>F5, Inc.</t>
-  </si>
-  <si>
     <t>CPAY</t>
   </si>
   <si>
@@ -625,7 +628,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-10-08 18:06 UTC · данные на 2026-10-08 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-09 02:13 UTC · данные на 2026-10-08 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -706,7 +709,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-10-08 18:06 UTC</t>
+    <t>2026-10-09 02:13 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -739,7 +742,7 @@
     <t>Запросов AV использовано</t>
   </si>
   <si>
-    <t>4</t>
+    <t>2</t>
   </si>
   <si>
     <t>Источник цен</t>
@@ -755,9 +758,6 @@
   </si>
   <si>
     <t>Версия состояния</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
   <si>
     <t>Регламент данных</t>
@@ -2549,12 +2549,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2562,13 +2562,13 @@
         <v>96</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2587,16 +2587,16 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="9" spans="2:8">
@@ -2615,7 +2615,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C16" s="11">
         <v>10000</v>
@@ -2652,7 +2652,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C17" s="12">
         <v>21</v>
@@ -2660,7 +2660,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C18" s="12">
         <v>0</v>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C19" s="12">
         <v>2</v>
@@ -2676,7 +2676,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C20" s="12">
         <v>21</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="13">
         <v>22</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C22" s="14">
         <v>0.283009</v>
@@ -2700,7 +2700,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C23" s="14">
         <v>0</v>
@@ -2708,15 +2708,15 @@
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C25" s="15">
         <v>0.0933751524086011</v>
@@ -2724,7 +2724,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C26" s="12">
         <v>24</v>
@@ -2732,7 +2732,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="16" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C28" s="11">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2741,12 +2741,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -5098,10 +5098,10 @@
         <v>47</v>
       </c>
       <c r="E5" s="11">
-        <v>443.2049865722656</v>
+        <v>443.7999877929688</v>
       </c>
       <c r="F5" s="20">
-        <v>1.126911877044903</v>
+        <v>1.127712912232116</v>
       </c>
       <c r="G5" s="13">
         <v>0.5608233001069692</v>
@@ -5113,16 +5113,16 @@
         <v>2.889457700830385</v>
       </c>
       <c r="J5" s="13">
-        <v>2.709088306870372</v>
+        <v>2.718489321034547</v>
       </c>
       <c r="K5" s="13">
         <v>0.6753553581795787</v>
       </c>
       <c r="L5" s="13">
-        <v>0.1281405243273873</v>
+        <v>0.1240996057671344</v>
       </c>
       <c r="M5" s="13">
-        <v>-0.6980283411820921</v>
+        <v>-0.7202385155373949</v>
       </c>
       <c r="N5" s="13">
         <v>16.950356</v>
@@ -5137,10 +5137,10 @@
         <v>0.517</v>
       </c>
       <c r="R5" s="15">
-        <v>0.9014533090698369</v>
+        <v>0.9040060038144437</v>
       </c>
       <c r="S5" s="12">
-        <v>76.99208653977058</v>
+        <v>77.12540496146083</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>128</v>
@@ -5160,10 +5160,10 @@
         <v>47</v>
       </c>
       <c r="E6" s="11">
-        <v>462.239990234375</v>
+        <v>463.3399963378906</v>
       </c>
       <c r="F6" s="20">
-        <v>1.123760071015307</v>
+        <v>1.125348453306782</v>
       </c>
       <c r="G6" s="13">
         <v>0.5719283241998815</v>
@@ -5175,16 +5175,16 @@
         <v>2.458659489905401</v>
       </c>
       <c r="J6" s="13">
-        <v>2.683233387245641</v>
+        <v>2.693754004535606</v>
       </c>
       <c r="K6" s="13">
         <v>0.8531255981518465</v>
       </c>
       <c r="L6" s="13">
-        <v>-0.03830471840012115</v>
+        <v>-0.04529802816877315</v>
       </c>
       <c r="M6" s="13">
-        <v>-0.4841444601580566</v>
+        <v>-0.4984970140254921</v>
       </c>
       <c r="N6" s="13">
         <v>14.638821</v>
@@ -5199,10 +5199,10 @@
         <v>0.537</v>
       </c>
       <c r="R6" s="15">
-        <v>1.081579378639483</v>
+        <v>1.08653297432534</v>
       </c>
       <c r="S6" s="12">
-        <v>79.42855288872435</v>
+        <v>79.63829186385152</v>
       </c>
       <c r="T6" s="10" t="s">
         <v>128</v>
@@ -5222,10 +5222,10 @@
         <v>39</v>
       </c>
       <c r="E7" s="11">
-        <v>1037.930053710938</v>
+        <v>1035.839965820312</v>
       </c>
       <c r="F7" s="20">
-        <v>1.081154337379512</v>
+        <v>1.071807264719382</v>
       </c>
       <c r="G7" s="13">
         <v>-0.1593145350616495</v>
@@ -5237,16 +5237,16 @@
         <v>3.98239266248428</v>
       </c>
       <c r="J7" s="13">
-        <v>2.07695522636725</v>
+        <v>2.04425685194996</v>
       </c>
       <c r="K7" s="13">
         <v>-0.356699646103866</v>
       </c>
       <c r="L7" s="13">
-        <v>-2.678520638841762</v>
+        <v>-2.678434811341815</v>
       </c>
       <c r="M7" s="13">
-        <v>-0.6499715245040546</v>
+        <v>-0.6442553993158138</v>
       </c>
       <c r="N7" s="13">
         <v>14.451332</v>
@@ -5261,10 +5261,10 @@
         <v>3.793</v>
       </c>
       <c r="R7" s="15">
-        <v>1.462787753379528</v>
+        <v>1.457828418362574</v>
       </c>
       <c r="S7" s="12">
-        <v>51.50795945124582</v>
+        <v>51.21364013790259</v>
       </c>
       <c r="T7" s="10" t="s">
         <v>128</v>
@@ -5284,10 +5284,10 @@
         <v>39</v>
       </c>
       <c r="E8" s="11">
-        <v>70.91000366210938</v>
+        <v>71</v>
       </c>
       <c r="F8" s="20">
-        <v>1.059639876397163</v>
+        <v>1.058753234202569</v>
       </c>
       <c r="G8" s="13">
         <v>0.247981045924682</v>
@@ -5299,16 +5299,16 @@
         <v>2.23427577606005</v>
       </c>
       <c r="J8" s="13">
-        <v>2.916158493292498</v>
+        <v>2.916199247860426</v>
       </c>
       <c r="K8" s="13">
         <v>0</v>
       </c>
       <c r="L8" s="13">
-        <v>-1.921358810013353</v>
+        <v>-1.917026891451921</v>
       </c>
       <c r="M8" s="13">
-        <v>-0.1220189511391702</v>
+        <v>-0.1351737838304993</v>
       </c>
       <c r="N8" s="13">
         <v>35.737114</v>
@@ -5323,10 +5323,10 @@
         <v>0.337</v>
       </c>
       <c r="R8" s="15">
-        <v>1.871419449868764</v>
+        <v>1.87506374858108</v>
       </c>
       <c r="S8" s="12">
-        <v>68.20196991276492</v>
+        <v>68.44738355772868</v>
       </c>
       <c r="T8" s="10" t="s">
         <v>128</v>
@@ -5346,10 +5346,10 @@
         <v>39</v>
       </c>
       <c r="E9" s="11">
-        <v>231.0899963378906</v>
+        <v>231.0500030517578</v>
       </c>
       <c r="F9" s="20">
-        <v>1.012833102047801</v>
+        <v>1.007006446090841</v>
       </c>
       <c r="G9" s="13">
         <v>-0.5898873289196422</v>
@@ -5361,16 +5361,16 @@
         <v>0.4384441196585954</v>
       </c>
       <c r="J9" s="13">
-        <v>2.489916868351201</v>
+        <v>2.478547964452967</v>
       </c>
       <c r="K9" s="13">
         <v>0</v>
       </c>
       <c r="L9" s="13">
-        <v>-0.240797394576804</v>
+        <v>-0.2400201918325052</v>
       </c>
       <c r="M9" s="13">
-        <v>0.03504516935671753</v>
+        <v>0.01300244139031714</v>
       </c>
       <c r="N9" s="13">
         <v>31.95904</v>
@@ -5385,10 +5385,10 @@
         <v>0.299</v>
       </c>
       <c r="R9" s="15">
-        <v>1.422827255233634</v>
+        <v>1.422407951822822</v>
       </c>
       <c r="S9" s="12">
-        <v>71.85316483276445</v>
+        <v>71.80565526193517</v>
       </c>
       <c r="T9" s="10" t="s">
         <v>128</v>
@@ -5408,10 +5408,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="11">
-        <v>279.9800109863281</v>
+        <v>281.6000061035156</v>
       </c>
       <c r="F10" s="20">
-        <v>0.9163606290213278</v>
+        <v>0.9211219155867839</v>
       </c>
       <c r="G10" s="13">
         <v>0.417875360797194</v>
@@ -5423,16 +5423,16 @@
         <v>2.427643605051808</v>
       </c>
       <c r="J10" s="13">
-        <v>2.301691607930444</v>
+        <v>2.320625169638272</v>
       </c>
       <c r="K10" s="13">
         <v>0.7636918045855513</v>
       </c>
       <c r="L10" s="13">
-        <v>0.4333614601781883</v>
+        <v>0.4171103243560632</v>
       </c>
       <c r="M10" s="13">
-        <v>-1.050489381020943</v>
+        <v>-1.049785803490504</v>
       </c>
       <c r="N10" s="13">
         <v>15.101597</v>
@@ -5447,10 +5447,10 @@
         <v>0.531</v>
       </c>
       <c r="R10" s="15">
-        <v>0.7601630087355984</v>
+        <v>0.7703475053700561</v>
       </c>
       <c r="S10" s="12">
-        <v>73.92908305723738</v>
+        <v>74.77639453117079</v>
       </c>
       <c r="T10" s="10" t="s">
         <v>128</v>
@@ -5470,10 +5470,10 @@
         <v>39</v>
       </c>
       <c r="E11" s="11">
-        <v>573.7150268554688</v>
+        <v>574.5499877929688</v>
       </c>
       <c r="F11" s="20">
-        <v>0.8826458820669609</v>
+        <v>0.8816137741469884</v>
       </c>
       <c r="G11" s="13">
         <v>-0.1020507268082084</v>
@@ -5485,16 +5485,16 @@
         <v>2.197120840076886</v>
       </c>
       <c r="J11" s="13">
-        <v>2.830284202424679</v>
+        <v>2.828440300671322</v>
       </c>
       <c r="K11" s="13">
         <v>1.734295367890928</v>
       </c>
       <c r="L11" s="13">
-        <v>-2.866217698538444</v>
+        <v>-2.861345181659439</v>
       </c>
       <c r="M11" s="13">
-        <v>-0.8630624167549702</v>
+        <v>-0.8727035218387911</v>
       </c>
       <c r="N11" s="13">
         <v>32.68565</v>
@@ -5509,10 +5509,10 @@
         <v>0.577</v>
       </c>
       <c r="R11" s="15">
-        <v>2.17668433435097</v>
+        <v>2.181307548326189</v>
       </c>
       <c r="S11" s="12">
-        <v>59.14697390008392</v>
+        <v>59.38682312033914</v>
       </c>
       <c r="T11" s="10" t="s">
         <v>128</v>
@@ -5532,10 +5532,10 @@
         <v>39</v>
       </c>
       <c r="E12" s="11">
-        <v>42.28499984741211</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="F12" s="20">
-        <v>0.8376793415246946</v>
+        <v>0.8532442011057501</v>
       </c>
       <c r="G12" s="13">
         <v>-0.03145316484583764</v>
@@ -5547,16 +5547,16 @@
         <v>3.922713545802811</v>
       </c>
       <c r="J12" s="13">
-        <v>1.206701133379654</v>
+        <v>1.262462935746718</v>
       </c>
       <c r="K12" s="13">
         <v>3.622281157226033</v>
       </c>
       <c r="L12" s="13">
-        <v>-2.992110817092736</v>
+        <v>-2.999055024122038</v>
       </c>
       <c r="M12" s="13">
-        <v>-0.4559534741577778</v>
+        <v>-0.465291332999098</v>
       </c>
       <c r="N12" s="13">
         <v>13.40184</v>
@@ -5571,10 +5571,10 @@
         <v>0.9320000000000001</v>
       </c>
       <c r="R12" s="15">
-        <v>0.8210594788042387</v>
+        <v>0.8419466719435005</v>
       </c>
       <c r="S12" s="12">
-        <v>55.38382441683361</v>
+        <v>56.95908507336836</v>
       </c>
       <c r="T12" s="10" t="s">
         <v>128</v>
@@ -5594,10 +5594,10 @@
         <v>60</v>
       </c>
       <c r="E13" s="11">
-        <v>346.6524963378906</v>
+        <v>348.2900085449219</v>
       </c>
       <c r="F13" s="20">
-        <v>0.824283567454185</v>
+        <v>0.8261176667085641</v>
       </c>
       <c r="G13" s="13">
         <v>-0.3240370018595447</v>
@@ -5609,16 +5609,16 @@
         <v>1.414981871477047</v>
       </c>
       <c r="J13" s="13">
-        <v>0.0992094811426309</v>
+        <v>0.1159907731032845</v>
       </c>
       <c r="K13" s="13">
         <v>4.053505670818017</v>
       </c>
       <c r="L13" s="13">
-        <v>0.06291375589264916</v>
+        <v>0.06678960586246752</v>
       </c>
       <c r="M13" s="13">
-        <v>-0.155146271805352</v>
+        <v>-0.1980567634554271</v>
       </c>
       <c r="N13" s="13">
         <v>17.243977</v>
@@ -5633,10 +5633,10 @@
         <v>0.242</v>
       </c>
       <c r="R13" s="15">
-        <v>0.08977526419049542</v>
+        <v>0.09492312932022817</v>
       </c>
       <c r="S13" s="12">
-        <v>51.95176420269681</v>
+        <v>53.50378125436893</v>
       </c>
       <c r="T13" s="10" t="s">
         <v>128</v>
@@ -5656,10 +5656,10 @@
         <v>58</v>
       </c>
       <c r="E14" s="11">
-        <v>370.8900146484375</v>
+        <v>370.2699890136719</v>
       </c>
       <c r="F14" s="20">
-        <v>0.7846868061424669</v>
+        <v>0.7790209439562005</v>
       </c>
       <c r="G14" s="13">
         <v>1.157023636953287</v>
@@ -5671,16 +5671,16 @@
         <v>-0.3751061753896214</v>
       </c>
       <c r="J14" s="13">
-        <v>0.5447321134776782</v>
+        <v>0.5191456956755395</v>
       </c>
       <c r="K14" s="13">
         <v>4.053505670818017</v>
       </c>
       <c r="L14" s="13">
-        <v>0.4959737662258626</v>
+        <v>0.5008624057058816</v>
       </c>
       <c r="M14" s="13">
-        <v>-0.5813885901299511</v>
+        <v>-0.5599292803102754</v>
       </c>
       <c r="N14" s="13">
         <v>9.679829</v>
@@ -5695,10 +5695,10 @@
         <v>0.003</v>
       </c>
       <c r="R14" s="15">
-        <v>0.2324437725829185</v>
+        <v>0.2303834670955007</v>
       </c>
       <c r="S14" s="12">
-        <v>57.14961116612521</v>
+        <v>56.51228695836431</v>
       </c>
       <c r="T14" s="10" t="s">
         <v>128</v>
@@ -5718,10 +5718,10 @@
         <v>47</v>
       </c>
       <c r="E15" s="11">
-        <v>60.04999923706055</v>
+        <v>60.27999877929688</v>
       </c>
       <c r="F15" s="20">
-        <v>0.7441359258024959</v>
+        <v>0.7454221460725009</v>
       </c>
       <c r="G15" s="13">
         <v>0.5635956445072656</v>
@@ -5733,16 +5733,16 @@
         <v>2.934384420890633</v>
       </c>
       <c r="J15" s="13">
-        <v>0.4886938387981778</v>
+        <v>0.4995545769744096</v>
       </c>
       <c r="K15" s="13">
         <v>1.002364811955726</v>
       </c>
       <c r="L15" s="13">
-        <v>0.1496014330995104</v>
+        <v>0.1392993734211786</v>
       </c>
       <c r="M15" s="13">
-        <v>-0.3118992068559348</v>
+        <v>-0.3288226768829935</v>
       </c>
       <c r="N15" s="13">
         <v>17.132744</v>
@@ -5757,10 +5757,10 @@
         <v>0.534</v>
       </c>
       <c r="R15" s="15">
-        <v>0.03543804528361316</v>
+        <v>0.03940391171916713</v>
       </c>
       <c r="S15" s="12">
-        <v>57.90549112143525</v>
+        <v>58.69068548720703</v>
       </c>
       <c r="T15" s="10" t="s">
         <v>128</v>
@@ -5780,10 +5780,10 @@
         <v>39</v>
       </c>
       <c r="E16" s="11">
-        <v>1605.800048828125</v>
+        <v>1609.4599609375</v>
       </c>
       <c r="F16" s="20">
-        <v>0.7178719256684057</v>
+        <v>0.7202703102859981</v>
       </c>
       <c r="G16" s="13">
         <v>-0.4890899962055227</v>
@@ -5795,16 +5795,16 @@
         <v>4.091481883216078</v>
       </c>
       <c r="J16" s="13">
-        <v>1.089887021683769</v>
+        <v>1.089079387619618</v>
       </c>
       <c r="K16" s="13">
         <v>0.1200976950563219</v>
       </c>
       <c r="L16" s="13">
-        <v>-2.992110817092736</v>
+        <v>-2.999055024122038</v>
       </c>
       <c r="M16" s="13">
-        <v>-1.176140313473963</v>
+        <v>-1.137923722741519</v>
       </c>
       <c r="N16" s="13">
         <v>23.309256</v>
@@ -5819,10 +5819,10 @@
         <v>3.716</v>
       </c>
       <c r="R16" s="15">
-        <v>0.8856935249209028</v>
+        <v>0.8899913654717637</v>
       </c>
       <c r="S16" s="12">
-        <v>45.26683003625369</v>
+        <v>45.48004943392557</v>
       </c>
       <c r="T16" s="10" t="s">
         <v>128</v>
@@ -5842,10 +5842,10 @@
         <v>62</v>
       </c>
       <c r="E17" s="11">
-        <v>64.76000213623047</v>
+        <v>64.54000091552734</v>
       </c>
       <c r="F17" s="20">
-        <v>0.6764182981145851</v>
+        <v>0.668113784940833</v>
       </c>
       <c r="G17" s="13">
         <v>1.227866124214571</v>
@@ -5857,16 +5857,16 @@
         <v>-0.5838568810772288</v>
       </c>
       <c r="J17" s="13">
-        <v>0.8264599931699078</v>
+        <v>0.7892535230002062</v>
       </c>
       <c r="K17" s="13">
         <v>4.053505670818017</v>
       </c>
       <c r="L17" s="13">
-        <v>-0.04162960647816023</v>
+        <v>-0.0421166991608405</v>
       </c>
       <c r="M17" s="13">
-        <v>0.00655919047767789</v>
+        <v>0.04264235845416636</v>
       </c>
       <c r="N17" s="13">
         <v>11.778764</v>
@@ -5881,10 +5881,10 @@
         <v>0.046</v>
       </c>
       <c r="R17" s="15">
-        <v>0.7246339135025759</v>
+        <v>0.7187750260146104</v>
       </c>
       <c r="S17" s="12">
-        <v>52.28921488728933</v>
+        <v>51.41288776445112</v>
       </c>
       <c r="T17" s="10" t="s">
         <v>128</v>
@@ -5895,58 +5895,58 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>14</v>
+        <v>136</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="E18" s="11">
-        <v>155.9024963378906</v>
+        <v>227.8000030517578</v>
       </c>
       <c r="F18" s="20">
-        <v>0.6482332712377955</v>
+        <v>0.6462033973464348</v>
       </c>
       <c r="G18" s="13">
-        <v>0.458736225579167</v>
+        <v>0.4025852595515658</v>
       </c>
       <c r="H18" s="13">
-        <v>-0.5571550118778178</v>
+        <v>0.5365165526684268</v>
       </c>
       <c r="I18" s="13">
-        <v>-0.03073722755982558</v>
+        <v>0.2045922725886486</v>
       </c>
       <c r="J18" s="13">
-        <v>0.8493110121013773</v>
+        <v>0.7178584830955589</v>
       </c>
       <c r="K18" s="13">
-        <v>3.527909301438286</v>
+        <v>3.776458433251364</v>
       </c>
       <c r="L18" s="13">
-        <v>0.448087065236268</v>
+        <v>-1.799770499647731</v>
       </c>
       <c r="M18" s="13">
-        <v>-0.5893546053400598</v>
+        <v>-1.163876899982847</v>
       </c>
       <c r="N18" s="13">
-        <v>16.182571</v>
+        <v>21.511457</v>
       </c>
       <c r="O18" s="13">
-        <v>3.97179</v>
+        <v>5.03281</v>
       </c>
       <c r="P18" s="15">
-        <v>0.26408002</v>
+        <v>0.19381</v>
       </c>
       <c r="Q18" s="15">
-        <v>0.053</v>
+        <v>0.108</v>
       </c>
       <c r="R18" s="15">
-        <v>0.2785891055655501</v>
+        <v>0.339126427964294</v>
       </c>
       <c r="S18" s="12">
-        <v>49.62566718671048</v>
+        <v>46.92373858554119</v>
       </c>
       <c r="T18" s="10" t="s">
         <v>128</v>
@@ -5957,58 +5957,58 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D19" s="10" t="s">
         <v>67</v>
       </c>
       <c r="E19" s="11">
-        <v>118.9700012207031</v>
+        <v>154.7599945068359</v>
       </c>
       <c r="F19" s="20">
-        <v>0.6271049699935198</v>
+        <v>0.6351783368835885</v>
       </c>
       <c r="G19" s="13">
-        <v>0.4086985785071914</v>
+        <v>0.458736225579167</v>
       </c>
       <c r="H19" s="13">
-        <v>-0.1224082745840677</v>
+        <v>-0.5571550118778178</v>
       </c>
       <c r="I19" s="13">
-        <v>0.4870648270709046</v>
+        <v>-0.03073722755982558</v>
       </c>
       <c r="J19" s="13">
-        <v>0.006835483505656072</v>
+        <v>0.7839620645895177</v>
       </c>
       <c r="K19" s="13">
-        <v>4.053505670818017</v>
+        <v>3.527909301438286</v>
       </c>
       <c r="L19" s="13">
-        <v>0.1002719285057883</v>
+        <v>0.4694765001912884</v>
       </c>
       <c r="M19" s="13">
-        <v>0.3741303228547428</v>
+        <v>-0.5235248078144396</v>
       </c>
       <c r="N19" s="13">
-        <v>13.728274</v>
+        <v>16.182571</v>
       </c>
       <c r="O19" s="13">
-        <v>6.145417</v>
+        <v>3.97179</v>
       </c>
       <c r="P19" s="15">
-        <v>0.46032003</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q19" s="15">
-        <v>0.07000000000000001</v>
+        <v>0.053</v>
       </c>
       <c r="R19" s="15">
-        <v>0.1595516860627542</v>
+        <v>0.2692192081707758</v>
       </c>
       <c r="S19" s="12">
-        <v>52.81024937591118</v>
+        <v>47.53762363271841</v>
       </c>
       <c r="T19" s="10" t="s">
         <v>128</v>
@@ -6028,10 +6028,10 @@
         <v>70</v>
       </c>
       <c r="E20" s="11">
-        <v>254.0800018310547</v>
+        <v>254.0599975585938</v>
       </c>
       <c r="F20" s="20">
-        <v>0.6253866478950925</v>
+        <v>0.6224856656184191</v>
       </c>
       <c r="G20" s="13">
         <v>-0.0192271310826416</v>
@@ -6043,16 +6043,16 @@
         <v>1.040595857895933</v>
       </c>
       <c r="J20" s="13">
-        <v>0.1107302985019277</v>
+        <v>0.09705436971668062</v>
       </c>
       <c r="K20" s="13">
         <v>4.053505670818017</v>
       </c>
       <c r="L20" s="13">
-        <v>-0.4862998574222859</v>
+        <v>-0.485033532316027</v>
       </c>
       <c r="M20" s="13">
-        <v>0.1093385317909413</v>
+        <v>0.1234112424475061</v>
       </c>
       <c r="N20" s="13">
         <v>20.234915</v>
@@ -6067,10 +6067,10 @@
         <v>0.196</v>
       </c>
       <c r="R20" s="15">
-        <v>0.08743851259684421</v>
+        <v>0.08735289619203579</v>
       </c>
       <c r="S20" s="12">
-        <v>50.83863675738066</v>
+        <v>50.81595861705996</v>
       </c>
       <c r="T20" s="10" t="s">
         <v>128</v>
@@ -6081,58 +6081,58 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>137</v>
+        <v>73</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="E21" s="11">
-        <v>223.8600006103516</v>
+        <v>118.620002746582</v>
       </c>
       <c r="F21" s="20">
-        <v>0.6213510994666637</v>
+        <v>0.6208912052021749</v>
       </c>
       <c r="G21" s="13">
-        <v>0.4025852595515658</v>
+        <v>0.4086985785071914</v>
       </c>
       <c r="H21" s="13">
-        <v>0.5365165526684268</v>
+        <v>-0.1224082745840677</v>
       </c>
       <c r="I21" s="13">
-        <v>0.2045922725886486</v>
+        <v>0.4870648270709046</v>
       </c>
       <c r="J21" s="13">
-        <v>0.6140536163607105</v>
+        <v>-0.02383868978615962</v>
       </c>
       <c r="K21" s="13">
-        <v>3.776458433251364</v>
+        <v>4.053505670818017</v>
       </c>
       <c r="L21" s="13">
-        <v>-1.802717279636437</v>
+        <v>0.1068383138981024</v>
       </c>
       <c r="M21" s="13">
-        <v>-1.083052288232777</v>
+        <v>0.4065616237630048</v>
       </c>
       <c r="N21" s="13">
-        <v>21.511457</v>
+        <v>13.728274</v>
       </c>
       <c r="O21" s="13">
-        <v>5.03281</v>
+        <v>6.145417</v>
       </c>
       <c r="P21" s="15">
-        <v>0.19381</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q21" s="15">
-        <v>0.108</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R21" s="15">
-        <v>0.3159649344851529</v>
+        <v>0.1561403948412503</v>
       </c>
       <c r="S21" s="12">
-        <v>43.41693106245736</v>
+        <v>52.15191617419707</v>
       </c>
       <c r="T21" s="10" t="s">
         <v>128</v>
@@ -6152,10 +6152,10 @@
         <v>39</v>
       </c>
       <c r="E22" s="11">
-        <v>189.0149993896484</v>
+        <v>189.1000061035156</v>
       </c>
       <c r="F22" s="20">
-        <v>0.5870645694630445</v>
+        <v>0.5811464276333514</v>
       </c>
       <c r="G22" s="13">
         <v>-2.064128721767363</v>
@@ -6167,16 +6167,16 @@
         <v>0.2289594453101543</v>
       </c>
       <c r="J22" s="13">
-        <v>2.248650754176033</v>
+        <v>2.233270392636907</v>
       </c>
       <c r="K22" s="13">
         <v>0.4937444031461815</v>
       </c>
       <c r="L22" s="13">
-        <v>-0.5775174853734575</v>
+        <v>-0.5759124468957545</v>
       </c>
       <c r="M22" s="13">
-        <v>-0.5801176664599497</v>
+        <v>-0.5976218624176669</v>
       </c>
       <c r="N22" s="13">
         <v>64.166664</v>
@@ -6191,10 +6191,10 @@
         <v>0.256</v>
       </c>
       <c r="R22" s="15">
-        <v>1.343354708753127</v>
+        <v>1.344408598041593</v>
       </c>
       <c r="S22" s="12">
-        <v>68.4660259558279</v>
+        <v>68.60804561252328</v>
       </c>
       <c r="T22" s="10" t="s">
         <v>128</v>
@@ -6214,10 +6214,10 @@
         <v>39</v>
       </c>
       <c r="E23" s="11">
-        <v>382.5950012207031</v>
+        <v>382.1400146484375</v>
       </c>
       <c r="F23" s="20">
-        <v>0.548805044618753</v>
+        <v>0.5410159618184333</v>
       </c>
       <c r="G23" s="13">
         <v>0.06680461853698441</v>
@@ -6229,16 +6229,16 @@
         <v>0.4710104351601621</v>
       </c>
       <c r="J23" s="13">
-        <v>1.556757266127551</v>
+        <v>1.528470891858554</v>
       </c>
       <c r="K23" s="13">
         <v>1.841835389602547</v>
       </c>
       <c r="L23" s="13">
-        <v>-1.792697950964816</v>
+        <v>-1.790787518088742</v>
       </c>
       <c r="M23" s="13">
-        <v>-0.6586296958225855</v>
+        <v>-0.6513521519748963</v>
       </c>
       <c r="N23" s="13">
         <v>34.482567</v>
@@ -6253,10 +6253,10 @@
         <v>0.204</v>
       </c>
       <c r="R23" s="15">
-        <v>0.7151342119455102</v>
+        <v>0.7130945537336184</v>
       </c>
       <c r="S23" s="12">
-        <v>65.28781396335785</v>
+        <v>64.81260092614816</v>
       </c>
       <c r="T23" s="10" t="s">
         <v>128</v>
@@ -6267,58 +6267,58 @@
         <v>20</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="E24" s="11">
-        <v>219.2299957275391</v>
+        <v>230.4799957275391</v>
       </c>
       <c r="F24" s="20">
-        <v>0.5442958745080955</v>
+        <v>0.5383255408931984</v>
       </c>
       <c r="G24" s="13">
-        <v>0.1955997684952965</v>
+        <v>-1.14885078933395</v>
       </c>
       <c r="H24" s="13">
-        <v>0.02741996157637986</v>
+        <v>2.367995217071406</v>
       </c>
       <c r="I24" s="13">
-        <v>-0.9032146122193362</v>
+        <v>2.42193339916702</v>
       </c>
       <c r="J24" s="13">
-        <v>0.5821605073865312</v>
+        <v>0.6098673909894227</v>
       </c>
       <c r="K24" s="13">
-        <v>3.612953706363291</v>
+        <v>-0.2946995315456368</v>
       </c>
       <c r="L24" s="13">
-        <v>0.419736847397063</v>
+        <v>-0.1518582617912941</v>
       </c>
       <c r="M24" s="13">
-        <v>-0.4795578034340398</v>
+        <v>-0.1804833684836323</v>
       </c>
       <c r="N24" s="13">
-        <v>39.546764</v>
+        <v>29.576487</v>
       </c>
       <c r="O24" s="13">
-        <v>1.7230625</v>
+        <v>24.670464</v>
       </c>
       <c r="P24" s="15">
-        <v>0.04575</v>
+        <v>1.17211</v>
       </c>
       <c r="Q24" s="15">
-        <v>0.034</v>
+        <v>1.059</v>
       </c>
       <c r="R24" s="15">
-        <v>0.2378182766192465</v>
+        <v>0.2560861155369871</v>
       </c>
       <c r="S24" s="12">
-        <v>47.70281023360193</v>
+        <v>54.53071535924345</v>
       </c>
       <c r="T24" s="10" t="s">
         <v>128</v>
@@ -6329,58 +6329,58 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E25" s="11">
-        <v>230.5</v>
+        <v>218.4299926757812</v>
       </c>
       <c r="F25" s="20">
-        <v>0.5421585312726607</v>
+        <v>0.5358253083789183</v>
       </c>
       <c r="G25" s="13">
-        <v>-1.14885078933395</v>
+        <v>0.1955997684952965</v>
       </c>
       <c r="H25" s="13">
-        <v>2.367995217071406</v>
+        <v>0.02741996157637986</v>
       </c>
       <c r="I25" s="13">
-        <v>2.42193339916702</v>
+        <v>-0.9032146122193362</v>
       </c>
       <c r="J25" s="13">
-        <v>0.6246229780312107</v>
+        <v>0.5437017813137784</v>
       </c>
       <c r="K25" s="13">
-        <v>-0.2946995315456368</v>
+        <v>3.612953706363291</v>
       </c>
       <c r="L25" s="13">
-        <v>-0.1526667892008814</v>
+        <v>0.4139977959485823</v>
       </c>
       <c r="M25" s="13">
-        <v>-0.1872980445898669</v>
+        <v>-0.4369153686895714</v>
       </c>
       <c r="N25" s="13">
-        <v>29.576487</v>
+        <v>39.546764</v>
       </c>
       <c r="O25" s="13">
-        <v>24.670464</v>
+        <v>1.7230625</v>
       </c>
       <c r="P25" s="15">
-        <v>1.17211</v>
+        <v>0.04575</v>
       </c>
       <c r="Q25" s="15">
-        <v>1.059</v>
+        <v>0.034</v>
       </c>
       <c r="R25" s="15">
-        <v>0.256195240693345</v>
+        <v>0.233301292547196</v>
       </c>
       <c r="S25" s="12">
-        <v>54.55465622969638</v>
+        <v>46.59996992197073</v>
       </c>
       <c r="T25" s="10" t="s">
         <v>128</v>
@@ -6400,10 +6400,10 @@
         <v>47</v>
       </c>
       <c r="E26" s="11">
-        <v>45.72000122070312</v>
+        <v>45.47000122070312</v>
       </c>
       <c r="F26" s="20">
-        <v>0.5047906651418537</v>
+        <v>0.4886561825698539</v>
       </c>
       <c r="G26" s="13">
         <v>1.022935901394866</v>
@@ -6415,16 +6415,16 @@
         <v>-0.2905175108276593</v>
       </c>
       <c r="J26" s="13">
-        <v>1.392694472669962</v>
+        <v>1.334820209245315</v>
       </c>
       <c r="K26" s="13">
         <v>-0.5772664253287171</v>
       </c>
       <c r="L26" s="13">
-        <v>-0.5119163774772003</v>
+        <v>-0.4966368718888502</v>
       </c>
       <c r="M26" s="13">
-        <v>-0.7225648298095313</v>
+        <v>-0.7186770033083624</v>
       </c>
       <c r="N26" s="13">
         <v>9.21519</v>
@@ -6439,10 +6439,10 @@
         <v>0.092</v>
       </c>
       <c r="R26" s="15">
-        <v>0.1893756256882073</v>
+        <v>0.1828720408569933</v>
       </c>
       <c r="S26" s="12">
-        <v>61.07061192205893</v>
+        <v>60.20923179513572</v>
       </c>
       <c r="T26" s="10" t="s">
         <v>128</v>
@@ -6462,10 +6462,10 @@
         <v>58</v>
       </c>
       <c r="E27" s="11">
-        <v>231.1000061035156</v>
+        <v>230.6300048828125</v>
       </c>
       <c r="F27" s="20">
-        <v>0.4639787525580581</v>
+        <v>0.4608149419893603</v>
       </c>
       <c r="G27" s="13">
         <v>1.22714929116337</v>
@@ -6477,16 +6477,16 @@
         <v>-0.05114060494765273</v>
       </c>
       <c r="J27" s="13">
-        <v>-0.2108098818284226</v>
+        <v>-0.2352417460934689</v>
       </c>
       <c r="K27" s="13">
         <v>2.002596748589814</v>
       </c>
       <c r="L27" s="13">
-        <v>0.4358479295533649</v>
+        <v>0.4428861871262617</v>
       </c>
       <c r="M27" s="13">
-        <v>0.225467029855959</v>
+        <v>0.2722601955614881</v>
       </c>
       <c r="N27" s="13">
         <v>4.4801764</v>
@@ -6501,10 +6501,10 @@
         <v>0.118</v>
       </c>
       <c r="R27" s="15">
-        <v>0.08747118756420025</v>
+        <v>0.08525953558611366</v>
       </c>
       <c r="S27" s="12">
-        <v>42.1236652002238</v>
+        <v>41.43376434064626</v>
       </c>
       <c r="T27" s="10" t="s">
         <v>128</v>
@@ -6515,58 +6515,58 @@
         <v>24</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="E28" s="11">
-        <v>211.4799957275391</v>
+        <v>264.5700073242188</v>
       </c>
       <c r="F28" s="20">
-        <v>0.4638644283027667</v>
+        <v>0.4596195497498691</v>
       </c>
       <c r="G28" s="13">
-        <v>0.4665617585959619</v>
+        <v>-0.7324636747785005</v>
       </c>
       <c r="H28" s="13">
-        <v>-0.3277583774658664</v>
+        <v>0.4425436300243135</v>
       </c>
       <c r="I28" s="13">
-        <v>2.32574166424169</v>
+        <v>-0.4598095680642147</v>
       </c>
       <c r="J28" s="13">
-        <v>0.7742733470841192</v>
+        <v>2.444368495799374</v>
       </c>
       <c r="K28" s="13">
-        <v>-0.1476550120624028</v>
+        <v>-0.2584870752549896</v>
       </c>
       <c r="L28" s="13">
-        <v>0.7779018217059723</v>
+        <v>-1.128067097759947</v>
       </c>
       <c r="M28" s="13">
-        <v>-0.7685878281780325</v>
+        <v>-0.8496385828885779</v>
       </c>
       <c r="N28" s="13">
-        <v>19.874039</v>
+        <v>49.463768</v>
       </c>
       <c r="O28" s="13">
-        <v>2.1352272</v>
+        <v>14.527268</v>
       </c>
       <c r="P28" s="15">
-        <v>0.12231</v>
+        <v>0.32339</v>
       </c>
       <c r="Q28" s="15">
-        <v>0.535</v>
+        <v>0.094</v>
       </c>
       <c r="R28" s="15">
-        <v>0.1309072224708232</v>
+        <v>1.139322481130713</v>
       </c>
       <c r="S28" s="12">
-        <v>59.12198056983122</v>
+        <v>57.65826271220038</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>128</v>
@@ -6577,58 +6577,58 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="E29" s="11">
-        <v>196.5099945068359</v>
+        <v>211.5500030517578</v>
       </c>
       <c r="F29" s="20">
-        <v>0.4462074139990458</v>
+        <v>0.4593294622910945</v>
       </c>
       <c r="G29" s="13">
-        <v>0.5925785231780542</v>
+        <v>0.4665617585959619</v>
       </c>
       <c r="H29" s="13">
-        <v>-0.6549127127071878</v>
+        <v>-0.3277583774658664</v>
       </c>
       <c r="I29" s="13">
-        <v>4.091481883216078</v>
+        <v>2.32574166424169</v>
       </c>
       <c r="J29" s="13">
-        <v>-0.4086412004168099</v>
+        <v>0.7615493822204353</v>
       </c>
       <c r="K29" s="13">
-        <v>0.6726119902787721</v>
+        <v>-0.1476550120624028</v>
       </c>
       <c r="L29" s="13">
-        <v>0.7486189592426963</v>
+        <v>0.7766785772343523</v>
       </c>
       <c r="M29" s="13">
-        <v>0.4017863659445858</v>
+        <v>-0.7766426017314065</v>
       </c>
       <c r="N29" s="13">
-        <v>10.7283745</v>
+        <v>19.874039</v>
       </c>
       <c r="O29" s="13">
-        <v>1.1600213</v>
+        <v>2.1352272</v>
       </c>
       <c r="P29" s="15">
-        <v>0.09031</v>
+        <v>0.12231</v>
       </c>
       <c r="Q29" s="15">
-        <v>11.11</v>
+        <v>0.535</v>
       </c>
       <c r="R29" s="15">
-        <v>0.01705152424513101</v>
+        <v>0.131281592577615</v>
       </c>
       <c r="S29" s="12">
-        <v>39.21064532304133</v>
+        <v>59.21366848787304</v>
       </c>
       <c r="T29" s="10" t="s">
         <v>128</v>
@@ -6639,58 +6639,58 @@
         <v>26</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E30" s="11">
-        <v>261.7749938964844</v>
+        <v>199.3999938964844</v>
       </c>
       <c r="F30" s="20">
-        <v>0.4397782834834033</v>
+        <v>0.4506743847128026</v>
       </c>
       <c r="G30" s="13">
-        <v>-0.7324636747785005</v>
+        <v>0.5925785231780542</v>
       </c>
       <c r="H30" s="13">
-        <v>0.4425436300243135</v>
+        <v>-0.6549127127071878</v>
       </c>
       <c r="I30" s="13">
-        <v>-0.4598095680642147</v>
+        <v>4.091481883216078</v>
       </c>
       <c r="J30" s="13">
-        <v>2.37825060402861</v>
+        <v>-0.3349737855053637</v>
       </c>
       <c r="K30" s="13">
-        <v>-0.2584870752549896</v>
+        <v>0.6726119902787721</v>
       </c>
       <c r="L30" s="13">
-        <v>-1.143856153226578</v>
+        <v>0.7287476633246349</v>
       </c>
       <c r="M30" s="13">
-        <v>-0.837870525479061</v>
+        <v>0.196274165887166</v>
       </c>
       <c r="N30" s="13">
-        <v>49.463768</v>
+        <v>10.7283745</v>
       </c>
       <c r="O30" s="13">
-        <v>14.527268</v>
+        <v>1.1600213</v>
       </c>
       <c r="P30" s="15">
-        <v>0.32339</v>
+        <v>0.09031</v>
       </c>
       <c r="Q30" s="15">
-        <v>0.094</v>
+        <v>11.11</v>
       </c>
       <c r="R30" s="15">
-        <v>1.116721903228899</v>
+        <v>0.0320090041809864</v>
       </c>
       <c r="S30" s="12">
-        <v>56.15996545988147</v>
+        <v>45.43908074289359</v>
       </c>
       <c r="T30" s="10" t="s">
         <v>128</v>
@@ -6710,10 +6710,10 @@
         <v>47</v>
       </c>
       <c r="E31" s="11">
-        <v>148.3300018310547</v>
+        <v>148.5099945068359</v>
       </c>
       <c r="F31" s="20">
-        <v>0.409767684196624</v>
+        <v>0.4072590657901985</v>
       </c>
       <c r="G31" s="13">
         <v>0.5519570047327462</v>
@@ -6725,16 +6725,16 @@
         <v>1.424012467219417</v>
       </c>
       <c r="J31" s="13">
-        <v>0.5763687522998078</v>
+        <v>0.5704782980746558</v>
       </c>
       <c r="K31" s="13">
         <v>-0.5174610050911331</v>
       </c>
       <c r="L31" s="13">
-        <v>0.1433041746113113</v>
+        <v>0.1409445701295148</v>
       </c>
       <c r="M31" s="13">
-        <v>-0.3235789579078677</v>
+        <v>-0.3310777812825189</v>
       </c>
       <c r="N31" s="13">
         <v>11.002335</v>
@@ -6749,10 +6749,10 @@
         <v>0.587</v>
       </c>
       <c r="R31" s="15">
-        <v>0.1025848765169544</v>
+        <v>0.103922820289289</v>
       </c>
       <c r="S31" s="12">
-        <v>59.37033576424934</v>
+        <v>59.6438353402292</v>
       </c>
       <c r="T31" s="10" t="s">
         <v>128</v>
@@ -6769,52 +6769,52 @@
         <v>149</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="E32" s="11">
-        <v>30.95</v>
+        <v>398.7200012207031</v>
       </c>
       <c r="F32" s="20">
-        <v>0.4064536841008188</v>
+        <v>0.4072477544669877</v>
       </c>
       <c r="G32" s="13">
-        <v>-0.04195459747446569</v>
+        <v>-1.391940526482032</v>
       </c>
       <c r="H32" s="13">
-        <v>-0.9999951229141718</v>
+        <v>0.5647588783596147</v>
       </c>
       <c r="I32" s="13">
-        <v>-1.209667697995005</v>
+        <v>3.683586308362309</v>
       </c>
       <c r="J32" s="13">
-        <v>0.8987137592412817</v>
+        <v>0.9799027982747487</v>
       </c>
       <c r="K32" s="13">
-        <v>4.053505670818017</v>
+        <v>0.4800275636421485</v>
       </c>
       <c r="L32" s="13">
-        <v>0.4995913201646023</v>
+        <v>-2.766357767093798</v>
       </c>
       <c r="M32" s="13">
-        <v>-1.137984829605401</v>
+        <v>0.1685539595766212</v>
       </c>
       <c r="N32" s="13">
-        <v>497.26776</v>
+        <v>61.766163</v>
       </c>
       <c r="O32" s="13">
-        <v>2.3630948</v>
+        <v>22.35921</v>
       </c>
       <c r="P32" s="15">
-        <v>-0.08785999999999999</v>
+        <v>0.36465</v>
       </c>
       <c r="Q32" s="15">
-        <v>-0.112</v>
+        <v>1.039</v>
       </c>
       <c r="R32" s="15">
-        <v>0.1308001461454147</v>
+        <v>0.09558724753143433</v>
       </c>
       <c r="S32" s="12">
-        <v>75.22299401348948</v>
+        <v>51.41189311208314</v>
       </c>
       <c r="T32" s="10" t="s">
         <v>128</v>
@@ -6825,58 +6825,58 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>152</v>
-      </c>
       <c r="D33" s="10" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="E33" s="11">
-        <v>375.0625</v>
+        <v>882.5900268554688</v>
       </c>
       <c r="F33" s="20">
-        <v>0.4034064539856614</v>
+        <v>0.400460233108476</v>
       </c>
       <c r="G33" s="13">
-        <v>-0.6593896211068547</v>
+        <v>0.4259345004319178</v>
       </c>
       <c r="H33" s="13">
-        <v>0.2797819680903868</v>
+        <v>0.821956331355851</v>
       </c>
       <c r="I33" s="13">
-        <v>0.8358553199308463</v>
+        <v>0.9122660713367897</v>
       </c>
       <c r="J33" s="13">
-        <v>1.17427516594485</v>
+        <v>-0.6139020096540911</v>
       </c>
       <c r="K33" s="13">
-        <v>0.6671252544771589</v>
+        <v>1.796295482449158</v>
       </c>
       <c r="L33" s="13">
-        <v>-0.3015885152806337</v>
+        <v>0.3402285785877152</v>
       </c>
       <c r="M33" s="13">
-        <v>-0.2562041313315935</v>
+        <v>0.6156729145897639</v>
       </c>
       <c r="N33" s="13">
-        <v>52.048717</v>
+        <v>13.928394</v>
       </c>
       <c r="O33" s="13">
-        <v>9.968641</v>
+        <v>2.492922</v>
       </c>
       <c r="P33" s="15">
-        <v>0.20897</v>
+        <v>0.16902</v>
       </c>
       <c r="Q33" s="15">
-        <v>0.365</v>
+        <v>0.425</v>
       </c>
       <c r="R33" s="15">
-        <v>0.1613999416750818</v>
+        <v>-0.01427272154665127</v>
       </c>
       <c r="S33" s="12">
-        <v>63.33302107836657</v>
+        <v>29.19030823305391</v>
       </c>
       <c r="T33" s="10" t="s">
         <v>128</v>
@@ -6887,58 +6887,58 @@
         <v>30</v>
       </c>
       <c r="B34" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="D34" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="D34" s="10" t="s">
-        <v>70</v>
-      </c>
       <c r="E34" s="11">
-        <v>92.26999664306641</v>
+        <v>30.95</v>
       </c>
       <c r="F34" s="20">
-        <v>0.3969181344711442</v>
+        <v>0.3994941649302248</v>
       </c>
       <c r="G34" s="13">
-        <v>0.1201293344453046</v>
+        <v>-0.04195459747446569</v>
       </c>
       <c r="H34" s="13">
-        <v>1.649629327208398</v>
+        <v>-0.9999951229141718</v>
       </c>
       <c r="I34" s="13">
-        <v>0.0292607103332167</v>
+        <v>-1.209667697995005</v>
       </c>
       <c r="J34" s="13">
-        <v>0.292779780902158</v>
+        <v>0.8847876819141055</v>
       </c>
       <c r="K34" s="13">
-        <v>0.06961972568148038</v>
+        <v>4.053505670818017</v>
       </c>
       <c r="L34" s="13">
-        <v>0.2752149919100464</v>
+        <v>0.4998712617332146</v>
       </c>
       <c r="M34" s="13">
-        <v>-0.053413874783799</v>
+        <v>-1.172965985437374</v>
       </c>
       <c r="N34" s="13">
-        <v>16.017889</v>
+        <v>497.26776</v>
       </c>
       <c r="O34" s="13">
-        <v>17.936699</v>
+        <v>2.3630948</v>
       </c>
       <c r="P34" s="15">
-        <v>1.5956</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q34" s="15">
-        <v>0.162</v>
+        <v>-0.112</v>
       </c>
       <c r="R34" s="15">
-        <v>0.007132026006196224</v>
+        <v>0.1308001461454147</v>
       </c>
       <c r="S34" s="12">
-        <v>57.43324950129764</v>
+        <v>75.22299401348948</v>
       </c>
       <c r="T34" s="10" t="s">
         <v>128</v>
@@ -6955,52 +6955,52 @@
         <v>156</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="E35" s="11">
-        <v>880.0399780273438</v>
+        <v>374.6700134277344</v>
       </c>
       <c r="F35" s="20">
-        <v>0.3960176791560469</v>
+        <v>0.397025821417776</v>
       </c>
       <c r="G35" s="13">
-        <v>0.4259345004319178</v>
+        <v>-0.6593896211068547</v>
       </c>
       <c r="H35" s="13">
-        <v>0.821956331355851</v>
+        <v>0.2797819680903868</v>
       </c>
       <c r="I35" s="13">
-        <v>0.9122660713367897</v>
+        <v>0.8358553199308463</v>
       </c>
       <c r="J35" s="13">
-        <v>-0.6188918863425265</v>
+        <v>1.151377895469973</v>
       </c>
       <c r="K35" s="13">
-        <v>1.796295482449158</v>
+        <v>0.6671252544771589</v>
       </c>
       <c r="L35" s="13">
-        <v>0.3390873191437165</v>
+        <v>-0.3019227454567416</v>
       </c>
       <c r="M35" s="13">
-        <v>0.5797089723490312</v>
+        <v>-0.2498466015172903</v>
       </c>
       <c r="N35" s="13">
-        <v>13.928394</v>
+        <v>52.048717</v>
       </c>
       <c r="O35" s="13">
-        <v>2.492922</v>
+        <v>9.968641</v>
       </c>
       <c r="P35" s="15">
-        <v>0.16902</v>
+        <v>0.20897</v>
       </c>
       <c r="Q35" s="15">
-        <v>0.425</v>
+        <v>0.365</v>
       </c>
       <c r="R35" s="15">
-        <v>-0.01712076266969298</v>
+        <v>0.1601845872151251</v>
       </c>
       <c r="S35" s="12">
-        <v>28.72352340188237</v>
+        <v>63.02739839436715</v>
       </c>
       <c r="T35" s="10" t="s">
         <v>128</v>
@@ -7011,58 +7011,58 @@
         <v>32</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>68</v>
+        <v>158</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E36" s="11">
-        <v>113.2600021362305</v>
+        <v>92.5</v>
       </c>
       <c r="F36" s="20">
-        <v>0.3949002642296038</v>
+        <v>0.3961591448833117</v>
       </c>
       <c r="G36" s="13">
-        <v>0.3552290711584428</v>
+        <v>0.1201293344453046</v>
       </c>
       <c r="H36" s="13">
-        <v>0.5065218152404674</v>
+        <v>1.649629327208398</v>
       </c>
       <c r="I36" s="13">
-        <v>0.5184131913684406</v>
+        <v>0.0292607103332167</v>
       </c>
       <c r="J36" s="13">
-        <v>0.02555694705479609</v>
+        <v>0.2945925471051071</v>
       </c>
       <c r="K36" s="13">
-        <v>1.778737927883995</v>
+        <v>0.06961972568148038</v>
       </c>
       <c r="L36" s="13">
-        <v>0.2115183102491379</v>
+        <v>0.2720803177073305</v>
       </c>
       <c r="M36" s="13">
-        <v>-0.4466564028962663</v>
+        <v>-0.06734811224072718</v>
       </c>
       <c r="N36" s="13">
-        <v>14.687899</v>
+        <v>16.017889</v>
       </c>
       <c r="O36" s="13">
-        <v>3.652433</v>
+        <v>17.936699</v>
       </c>
       <c r="P36" s="15">
-        <v>0.30667</v>
+        <v>1.5956</v>
       </c>
       <c r="Q36" s="15">
-        <v>0.377</v>
+        <v>0.162</v>
       </c>
       <c r="R36" s="15">
-        <v>0.1681105941178596</v>
+        <v>0.009642525142256941</v>
       </c>
       <c r="S36" s="12">
-        <v>31.99446289313337</v>
+        <v>58.0654644178495</v>
       </c>
       <c r="T36" s="10" t="s">
         <v>128</v>
@@ -7073,58 +7073,58 @@
         <v>33</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>157</v>
+        <v>15</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>158</v>
+        <v>68</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="E37" s="11">
-        <v>395.3250122070312</v>
+        <v>112.75</v>
       </c>
       <c r="F37" s="20">
-        <v>0.3929121734456331</v>
+        <v>0.3865192906519103</v>
       </c>
       <c r="G37" s="13">
-        <v>-1.391940526482032</v>
+        <v>0.3552290711584428</v>
       </c>
       <c r="H37" s="13">
-        <v>0.5647588783596147</v>
+        <v>0.5065218152404674</v>
       </c>
       <c r="I37" s="13">
-        <v>3.683586308362309</v>
+        <v>0.5184131913684406</v>
       </c>
       <c r="J37" s="13">
-        <v>0.9390385072663382</v>
+        <v>-0.01477502541237469</v>
       </c>
       <c r="K37" s="13">
-        <v>0.4800275636421485</v>
+        <v>1.778737927883995</v>
       </c>
       <c r="L37" s="13">
-        <v>-2.782745128137709</v>
+        <v>0.2105966326513896</v>
       </c>
       <c r="M37" s="13">
-        <v>0.1548908088741609</v>
+        <v>-0.3994824176672329</v>
       </c>
       <c r="N37" s="13">
-        <v>61.766163</v>
+        <v>14.687899</v>
       </c>
       <c r="O37" s="13">
-        <v>22.35921</v>
+        <v>3.652433</v>
       </c>
       <c r="P37" s="15">
-        <v>0.36465</v>
+        <v>0.30667</v>
       </c>
       <c r="Q37" s="15">
-        <v>1.039</v>
+        <v>0.377</v>
       </c>
       <c r="R37" s="15">
-        <v>0.08625862930937189</v>
+        <v>0.1628506710460147</v>
       </c>
       <c r="S37" s="12">
-        <v>50.44219261882302</v>
+        <v>31.25989917026152</v>
       </c>
       <c r="T37" s="10" t="s">
         <v>128</v>
@@ -7144,10 +7144,10 @@
         <v>62</v>
       </c>
       <c r="E38" s="11">
-        <v>59.51499938964844</v>
+        <v>59.58000183105469</v>
       </c>
       <c r="F38" s="20">
-        <v>0.385687986274687</v>
+        <v>0.3855126187727344</v>
       </c>
       <c r="G38" s="13">
         <v>0.4714651609000165</v>
@@ -7159,16 +7159,16 @@
         <v>0.2370544747896051</v>
       </c>
       <c r="J38" s="13">
-        <v>0.05976132889074035</v>
+        <v>0.05357730276752234</v>
       </c>
       <c r="K38" s="13">
         <v>0.8893380544424937</v>
       </c>
       <c r="L38" s="13">
-        <v>0.7628095803699949</v>
+        <v>0.7632032746541464</v>
       </c>
       <c r="M38" s="13">
-        <v>0.01782523150599347</v>
+        <v>0.0385279649805409</v>
       </c>
       <c r="N38" s="13">
         <v>13.469164</v>
@@ -7183,10 +7183,10 @@
         <v>0.057</v>
       </c>
       <c r="R38" s="15">
-        <v>0.02253502959954301</v>
+        <v>0.02365184509192364</v>
       </c>
       <c r="S38" s="12">
-        <v>37.2443375265683</v>
+        <v>37.48811874033412</v>
       </c>
       <c r="T38" s="10" t="s">
         <v>128</v>
@@ -7203,52 +7203,52 @@
         <v>162</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E39" s="11">
-        <v>240.6699981689453</v>
+        <v>1169.599975585938</v>
       </c>
       <c r="F39" s="20">
-        <v>0.3811234192682533</v>
+        <v>0.3789750176534584</v>
       </c>
       <c r="G39" s="13">
-        <v>-0.03177896967545183</v>
+        <v>-1.034305093517767</v>
       </c>
       <c r="H39" s="13">
-        <v>0.2705322751456885</v>
+        <v>1.799298489421478</v>
       </c>
       <c r="I39" s="13">
-        <v>-0.2798112141847907</v>
+        <v>0.7264515483695176</v>
       </c>
       <c r="J39" s="13">
-        <v>0.5904353559896601</v>
+        <v>0.2953454382755975</v>
       </c>
       <c r="K39" s="13">
-        <v>1.445144391145912</v>
+        <v>0.8635503961749117</v>
       </c>
       <c r="L39" s="13">
-        <v>0.45730489610186</v>
+        <v>0.3662197451843187</v>
       </c>
       <c r="M39" s="13">
-        <v>-0.08058295369394486</v>
+        <v>-0.1198230299057454</v>
       </c>
       <c r="N39" s="13">
-        <v>23.80123</v>
+        <v>38.3121</v>
       </c>
       <c r="O39" s="13">
-        <v>14.628464</v>
+        <v>30.073418</v>
       </c>
       <c r="P39" s="15">
-        <v>0.54960996</v>
+        <v>1.02286</v>
       </c>
       <c r="Q39" s="15">
-        <v>0.067</v>
+        <v>0.477</v>
       </c>
       <c r="R39" s="15">
-        <v>0.2672401776034905</v>
+        <v>0.2283338880134231</v>
       </c>
       <c r="S39" s="12">
-        <v>61.08125959019548</v>
+        <v>51.60207446186203</v>
       </c>
       <c r="T39" s="10" t="s">
         <v>128</v>
@@ -7268,10 +7268,10 @@
         <v>39</v>
       </c>
       <c r="E40" s="11">
-        <v>193.6799926757812</v>
+        <v>193.7299957275391</v>
       </c>
       <c r="F40" s="20">
-        <v>0.3771214450008533</v>
+        <v>0.3747153835151923</v>
       </c>
       <c r="G40" s="13">
         <v>0.332252133810496</v>
@@ -7283,16 +7283,16 @@
         <v>-0.9006491143990446</v>
       </c>
       <c r="J40" s="13">
-        <v>1.401258770279991</v>
+        <v>1.398906388607742</v>
       </c>
       <c r="K40" s="13">
         <v>-0.578912446069201</v>
       </c>
       <c r="L40" s="13">
-        <v>-2.992110817092736</v>
+        <v>-2.999055024122038</v>
       </c>
       <c r="M40" s="13">
-        <v>0.2981423822045641</v>
+        <v>0.2820962001767124</v>
       </c>
       <c r="N40" s="13">
         <v>13.969932</v>
@@ -7307,10 +7307,10 @@
         <v>-0.068</v>
       </c>
       <c r="R40" s="15">
-        <v>0.3914791959092985</v>
+        <v>0.3918384390365399</v>
       </c>
       <c r="S40" s="12">
-        <v>80.82399880885332</v>
+        <v>80.83774450653536</v>
       </c>
       <c r="T40" s="10" t="s">
         <v>128</v>
@@ -7327,52 +7327,52 @@
         <v>166</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E41" s="11">
-        <v>1153.859985351562</v>
+        <v>239</v>
       </c>
       <c r="F41" s="20">
-        <v>0.3642438305781039</v>
+        <v>0.3692855712693026</v>
       </c>
       <c r="G41" s="13">
-        <v>-1.034305093517767</v>
+        <v>-0.03177896967545183</v>
       </c>
       <c r="H41" s="13">
-        <v>1.799298489421478</v>
+        <v>0.2705322751456885</v>
       </c>
       <c r="I41" s="13">
-        <v>0.7264515483695176</v>
+        <v>-0.2798112141847907</v>
       </c>
       <c r="J41" s="13">
-        <v>0.2212321200888481</v>
+        <v>0.5291723752649697</v>
       </c>
       <c r="K41" s="13">
-        <v>0.8635503961749117</v>
+        <v>1.445144391145912</v>
       </c>
       <c r="L41" s="13">
-        <v>0.3361093917690012</v>
+        <v>0.4547517377304682</v>
       </c>
       <c r="M41" s="13">
-        <v>-0.003455160085877609</v>
+        <v>0.003094992815304676</v>
       </c>
       <c r="N41" s="13">
-        <v>38.3121</v>
+        <v>23.80123</v>
       </c>
       <c r="O41" s="13">
-        <v>30.073418</v>
+        <v>14.628464</v>
       </c>
       <c r="P41" s="15">
-        <v>1.02286</v>
+        <v>0.54960996</v>
       </c>
       <c r="Q41" s="15">
-        <v>0.477</v>
+        <v>0.067</v>
       </c>
       <c r="R41" s="15">
-        <v>0.2118034812030114</v>
+        <v>0.2584468556592814</v>
       </c>
       <c r="S41" s="12">
-        <v>47.46940808987857</v>
+        <v>58.73854878142804</v>
       </c>
       <c r="T41" s="10" t="s">
         <v>128</v>
@@ -7389,52 +7389,52 @@
         <v>168</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>47</v>
+        <v>169</v>
       </c>
       <c r="E42" s="11">
-        <v>134.3099975585938</v>
+        <v>272.8200073242188</v>
       </c>
       <c r="F42" s="20">
-        <v>0.352463045555982</v>
+        <v>0.3622630724537931</v>
       </c>
       <c r="G42" s="13">
-        <v>0.4724324774271865</v>
+        <v>-3.873896380635145</v>
       </c>
       <c r="H42" s="13">
-        <v>-0.1379046355837053</v>
+        <v>-0.4529156336272934</v>
       </c>
       <c r="I42" s="13">
-        <v>0.7991585696769221</v>
+        <v>4.091481883216078</v>
       </c>
       <c r="J42" s="13">
-        <v>0.8051835875752253</v>
+        <v>1.576287060011471</v>
       </c>
       <c r="K42" s="13">
-        <v>-0.0521858091143329</v>
+        <v>4.053505670818017</v>
       </c>
       <c r="L42" s="13">
-        <v>0.3477325025547811</v>
+        <v>-2.999055024122038</v>
       </c>
       <c r="M42" s="13">
-        <v>-0.5822830623418187</v>
+        <v>-0.7060095378425373</v>
       </c>
       <c r="N42" s="13">
-        <v>16.788078</v>
+        <v>356.9753</v>
       </c>
       <c r="O42" s="13">
-        <v>2.3300917</v>
+        <v>52.620564</v>
       </c>
       <c r="P42" s="15">
-        <v>0.1418</v>
+        <v>0.22213</v>
       </c>
       <c r="Q42" s="15">
-        <v>0.355</v>
+        <v>1.655</v>
       </c>
       <c r="R42" s="15">
-        <v>0.1031880524704087</v>
+        <v>0.7037407044599535</v>
       </c>
       <c r="S42" s="12">
-        <v>60.24825520026894</v>
+        <v>51.54221590217757</v>
       </c>
       <c r="T42" s="10" t="s">
         <v>128</v>
@@ -7445,58 +7445,58 @@
         <v>39</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E43" s="11">
-        <v>463.7900085449219</v>
+        <v>134.1900024414062</v>
       </c>
       <c r="F43" s="20">
-        <v>0.3520140973763233</v>
+        <v>0.3461509643256707</v>
       </c>
       <c r="G43" s="13">
-        <v>-0.2822274966466811</v>
+        <v>0.4724324774271865</v>
       </c>
       <c r="H43" s="13">
-        <v>0.6042682609127178</v>
+        <v>-0.1379046355837053</v>
       </c>
       <c r="I43" s="13">
-        <v>-0.3184536913372166</v>
+        <v>0.7991585696769221</v>
       </c>
       <c r="J43" s="13">
-        <v>1.173032544483859</v>
+        <v>0.7834957886641423</v>
       </c>
       <c r="K43" s="13">
-        <v>0.3686468268694003</v>
+        <v>-0.0521858091143329</v>
       </c>
       <c r="L43" s="13">
-        <v>-0.07070178422311099</v>
+        <v>0.3509343564527889</v>
       </c>
       <c r="M43" s="13">
-        <v>-0.6740972669460797</v>
+        <v>-0.5822562222276545</v>
       </c>
       <c r="N43" s="13">
-        <v>36.207336</v>
+        <v>16.788078</v>
       </c>
       <c r="O43" s="13">
-        <v>6.691722</v>
+        <v>2.3300917</v>
       </c>
       <c r="P43" s="15">
-        <v>0.1983</v>
+        <v>0.1418</v>
       </c>
       <c r="Q43" s="15">
-        <v>0.109</v>
+        <v>0.355</v>
       </c>
       <c r="R43" s="15">
-        <v>0.5743576303010682</v>
+        <v>0.1022024431930482</v>
       </c>
       <c r="S43" s="12">
-        <v>65.32212392327753</v>
+        <v>60.05927987967636</v>
       </c>
       <c r="T43" s="10" t="s">
         <v>128</v>
@@ -7507,19 +7507,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>58</v>
       </c>
       <c r="E44" s="11">
-        <v>400.2699890136719</v>
+        <v>402.0799865722656</v>
       </c>
       <c r="F44" s="20">
-        <v>0.3427661902514897</v>
+        <v>0.343719735046792</v>
       </c>
       <c r="G44" s="13">
         <v>0.2852659683235538</v>
@@ -7531,16 +7531,16 @@
         <v>-0.1283007250327522</v>
       </c>
       <c r="J44" s="13">
-        <v>0.6195075423350427</v>
+        <v>0.6354480201420043</v>
       </c>
       <c r="K44" s="13">
         <v>-0.2870181014233783</v>
       </c>
       <c r="L44" s="13">
-        <v>0.8346986050625392</v>
+        <v>0.8374181138136499</v>
       </c>
       <c r="M44" s="13">
-        <v>-0.1245784276987621</v>
+        <v>-0.1744755410969229</v>
       </c>
       <c r="N44" s="13">
         <v>23.98784</v>
@@ -7555,10 +7555,10 @@
         <v>0.215</v>
       </c>
       <c r="R44" s="15">
-        <v>0.3056397542188756</v>
+        <v>0.3115437810817498</v>
       </c>
       <c r="S44" s="12">
-        <v>50.36249298955109</v>
+        <v>52.06802818086921</v>
       </c>
       <c r="T44" s="10" t="s">
         <v>128</v>
@@ -7627,110 +7627,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B6" s="15">
         <v>0.18</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B7" s="15">
         <v>0.16</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B8" s="15">
         <v>0.1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B9" s="15">
         <v>0.3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B10" s="15">
         <v>0.12</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B11" s="15">
         <v>0.06</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B12" s="15">
         <v>0.08</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B13" s="15">
         <f>SUM(B6:B12)</f>
@@ -7739,22 +7739,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -7833,25 +7833,25 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B5" s="10" t="s">
         <v>89</v>
@@ -7859,31 +7859,31 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>41</v>
@@ -7891,42 +7891,42 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -8200,7 +8200,7 @@
         <v>1088</v>
       </c>
       <c r="BI1">
-        <v>1037.930053710938</v>
+        <v>1035.839965820312</v>
       </c>
     </row>
     <row r="2" spans="1:61">
@@ -8385,7 +8385,7 @@
         <v>1692.420043945312</v>
       </c>
       <c r="BI2">
-        <v>1605.800048828125</v>
+        <v>1609.4599609375</v>
       </c>
     </row>
     <row r="3" spans="1:61">
@@ -8570,7 +8570,7 @@
         <v>405.4200134277344</v>
       </c>
       <c r="BI3">
-        <v>393.3999938964844</v>
+        <v>393.3099975585938</v>
       </c>
     </row>
     <row r="4" spans="1:61">
@@ -8755,7 +8755,7 @@
         <v>424.1000061035156</v>
       </c>
       <c r="BI4">
-        <v>443.2049865722656</v>
+        <v>443.7999877929688</v>
       </c>
     </row>
     <row r="5" spans="1:61">
@@ -8940,7 +8940,7 @@
         <v>442.260009765625</v>
       </c>
       <c r="BI5">
-        <v>462.239990234375</v>
+        <v>463.3399963378906</v>
       </c>
     </row>
     <row r="6" spans="1:61">
@@ -9125,7 +9125,7 @@
         <v>58.20999908447266</v>
       </c>
       <c r="BI6">
-        <v>60.04999923706055</v>
+        <v>60.27999877929688</v>
       </c>
     </row>
     <row r="7" spans="1:61">
@@ -9310,7 +9310,7 @@
         <v>271.6199951171875</v>
       </c>
       <c r="BI7">
-        <v>279.9800109863281</v>
+        <v>281.6000061035156</v>
       </c>
     </row>
     <row r="8" spans="1:61">
@@ -9495,7 +9495,7 @@
         <v>43.81000137329102</v>
       </c>
       <c r="BI8">
-        <v>45.72000122070312</v>
+        <v>45.47000122070312</v>
       </c>
     </row>
     <row r="9" spans="1:61">
@@ -9680,7 +9680,7 @@
         <v>237.4700012207031</v>
       </c>
       <c r="BI9">
-        <v>230.5</v>
+        <v>230.4799957275391</v>
       </c>
     </row>
     <row r="10" spans="1:61">
@@ -9865,7 +9865,7 @@
         <v>360.6099853515625</v>
       </c>
       <c r="BI10">
-        <v>370.8900146484375</v>
+        <v>370.2699890136719</v>
       </c>
     </row>
     <row r="11" spans="1:61">
@@ -10050,7 +10050,7 @@
         <v>347.3699951171875</v>
       </c>
       <c r="BI11">
-        <v>343.6000061035156</v>
+        <v>344.8599853515625</v>
       </c>
     </row>
     <row r="12" spans="1:61">
@@ -10235,7 +10235,7 @@
         <v>64.98999786376953</v>
       </c>
       <c r="BI12">
-        <v>64.76000213623047</v>
+        <v>64.54000091552734</v>
       </c>
     </row>
     <row r="13" spans="1:61">
@@ -10420,7 +10420,7 @@
         <v>350.5</v>
       </c>
       <c r="BI13">
-        <v>346.6524963378906</v>
+        <v>348.2900085449219</v>
       </c>
     </row>
     <row r="14" spans="1:61">
@@ -10605,7 +10605,7 @@
         <v>223.9499969482422</v>
       </c>
       <c r="BI14">
-        <v>231.1000061035156</v>
+        <v>230.6300048828125</v>
       </c>
     </row>
     <row r="15" spans="1:61">
@@ -10790,7 +10790,7 @@
         <v>150.9199981689453</v>
       </c>
       <c r="BI15">
-        <v>155.9024963378906</v>
+        <v>154.7599945068359</v>
       </c>
     </row>
     <row r="16" spans="1:61">
@@ -10975,7 +10975,7 @@
         <v>113.4400024414062</v>
       </c>
       <c r="BI16">
-        <v>113.2600021362305</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="17" spans="1:61">
@@ -11160,7 +11160,7 @@
         <v>259.9200134277344</v>
       </c>
       <c r="BI17">
-        <v>254.0800018310547</v>
+        <v>254.0599975585938</v>
       </c>
     </row>
     <row r="18" spans="1:61">
@@ -11345,7 +11345,7 @@
         <v>267.760009765625</v>
       </c>
       <c r="BI18">
-        <v>261.7749938964844</v>
+        <v>264.5700073242188</v>
       </c>
     </row>
     <row r="19" spans="1:61">
@@ -11530,7 +11530,7 @@
         <v>116.3000030517578</v>
       </c>
       <c r="BI19">
-        <v>118.9700012207031</v>
+        <v>118.620002746582</v>
       </c>
     </row>
     <row r="20" spans="1:61">
@@ -11715,7 +11715,7 @@
         <v>222.1499938964844</v>
       </c>
       <c r="BI20">
-        <v>219.2299957275391</v>
+        <v>218.4299926757812</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -17,7 +17,7 @@
     <sheet name="_данные" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$P$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Позиции!$A$4:$Q$25</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Сделки!$A$4:$O$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Скрин!$A$4:$T$44</definedName>
   </definedNames>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="262">
   <si>
     <t>SNDK</t>
   </si>
@@ -94,7 +94,7 @@
     <t>Открытые позиции</t>
   </si>
   <si>
-    <t>Позиции удерживаются, пока сохраняется инвестиционный сигнал; автоматического выхода по сроку нет. Жёлтая колонка «Тек. цена» — единственное, что нужно править вручную; остальное пересчитается формулами.</t>
+    <t>Позиции удерживаются, пока сохраняется инвестиционный сигнал; автоматического выхода по сроку нет. Размер распределяется по рейтингу: «Вес ×» — коэффициент целевого веса позиции; жёлтая колонка «Тек. цена» предназначена для ручного ввода.</t>
   </si>
   <si>
     <t>Тикер</t>
@@ -145,6 +145,9 @@
     <t>Динамика</t>
   </si>
   <si>
+    <t>Вес ×</t>
+  </si>
+  <si>
     <t>Sandisk</t>
   </si>
   <si>
@@ -631,7 +634,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-10-13 03:04 UTC · данные на 2026-10-12 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-14 01:17 UTC · данные на 2026-10-12 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -715,7 +718,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-10-13 03:04 UTC</t>
+    <t>2026-10-14 01:17 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -2611,26 +2614,26 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="2:8">
       <c r="B5" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2649,16 +2652,16 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="2:8">
@@ -2677,12 +2680,12 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="2:8">
       <c r="B13" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C13" s="11">
         <v>159.906297033976</v>
@@ -2690,7 +2693,7 @@
     </row>
     <row r="14" spans="2:8">
       <c r="B14" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="11">
         <v>10274.38</v>
@@ -2698,7 +2701,7 @@
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C15" s="11">
         <v>10434.28629703398</v>
@@ -2706,7 +2709,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="10" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C16" s="11">
         <v>10000</v>
@@ -2714,7 +2717,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C17" s="12">
         <v>21</v>
@@ -2722,7 +2725,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C18" s="12">
         <v>0</v>
@@ -2730,7 +2733,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C19" s="12">
         <v>0</v>
@@ -2738,15 +2741,15 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C21" s="13">
         <v>22</v>
@@ -2754,7 +2757,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C22" s="14">
         <v>0.210302</v>
@@ -2762,7 +2765,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C23" s="14">
         <v>0</v>
@@ -2770,15 +2773,15 @@
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C25" s="15">
         <v>0.09028103209030917</v>
@@ -2786,7 +2789,7 @@
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C26" s="12">
         <v>26</v>
@@ -2794,7 +2797,7 @@
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="16" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C28" s="11">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2803,12 +2806,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="17" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -2821,7 +2824,7 @@
     </row>
     <row r="33" spans="2:3">
       <c r="B33" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C33" s="11">
         <v>2673.14</v>
@@ -2829,7 +2832,7 @@
     </row>
     <row r="34" spans="2:3">
       <c r="B34" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" s="11">
         <v>1858.2</v>
@@ -2837,7 +2840,7 @@
     </row>
     <row r="35" spans="2:3">
       <c r="B35" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C35" s="11">
         <v>1791.37</v>
@@ -2845,7 +2848,7 @@
     </row>
     <row r="36" spans="2:3">
       <c r="B36" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C36" s="11">
         <v>1465.71</v>
@@ -2853,7 +2856,7 @@
     </row>
     <row r="37" spans="2:3">
       <c r="B37" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C37" s="11">
         <v>1001.2</v>
@@ -2861,7 +2864,7 @@
     </row>
     <row r="38" spans="2:3">
       <c r="B38" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C38" s="11">
         <v>983.12</v>
@@ -2869,7 +2872,7 @@
     </row>
     <row r="39" spans="2:3">
       <c r="B39" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="11">
         <v>501.64</v>
@@ -2883,7 +2886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:Q26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -2899,19 +2902,20 @@
     <col min="12" max="12" width="12.7109375" customWidth="1"/>
     <col min="13" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="16" width="14.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="30" customHeight="1">
+    <row r="4" spans="1:17" ht="30" customHeight="1">
       <c r="A4" s="18" t="s">
         <v>23</v>
       </c>
@@ -2960,19 +2964,22 @@
       <c r="P4" s="18" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" s="11">
         <v>1550.1948</v>
@@ -3002,27 +3009,30 @@
         <v>22</v>
       </c>
       <c r="M5" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N5" s="13">
         <v>1.655247920227722</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6" s="10" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" s="11">
         <v>462.5311</v>
@@ -3052,27 +3062,30 @@
         <v>21</v>
       </c>
       <c r="M6" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N6" s="13">
         <v>1.135451734784544</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" s="10" t="s">
         <v>2</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E7" s="11">
         <v>360.14</v>
@@ -3102,27 +3115,30 @@
         <v>20</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N7" s="13">
         <v>1.098454348098604</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q7" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" s="11">
         <v>380.9704</v>
@@ -3152,27 +3168,30 @@
         <v>19</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N8" s="13">
         <v>0.9280120270881818</v>
       </c>
       <c r="O8" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q8" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="10" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E9" s="11">
         <v>60.1501</v>
@@ -3202,27 +3221,30 @@
         <v>16</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N9" s="13">
         <v>0.8840484909760108</v>
       </c>
       <c r="O9" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>53</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>52</v>
       </c>
       <c r="E10" s="11">
         <v>251.9059</v>
@@ -3252,27 +3274,30 @@
         <v>16</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N10" s="13">
         <v>0.8298272742812407</v>
       </c>
       <c r="O10" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q10" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E11" s="11">
         <v>43.7018</v>
@@ -3302,27 +3327,30 @@
         <v>16</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N11" s="13">
         <v>0.7019116395441239</v>
       </c>
       <c r="O11" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E12" s="11">
         <v>211.3456</v>
@@ -3352,27 +3380,30 @@
         <v>12</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N12" s="13">
         <v>0.6809721702367264</v>
       </c>
       <c r="O12" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q12" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="19" t="s">
         <v>57</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>56</v>
       </c>
       <c r="E13" s="11">
         <v>383.1915</v>
@@ -3402,27 +3433,30 @@
         <v>12</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N13" s="13">
         <v>0.8197914702434592</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" s="11">
         <v>339.2795</v>
@@ -3452,27 +3486,30 @@
         <v>12</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N14" s="13">
         <v>0.776423257523575</v>
       </c>
       <c r="O14" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="11">
         <v>67.3437</v>
@@ -3502,27 +3539,30 @@
         <v>12</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N15" s="13">
         <v>0.7994794227521653</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <v>44</v>
+      </c>
+      <c r="Q15" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16" s="11">
         <v>340.8704</v>
@@ -3552,27 +3592,30 @@
         <v>8</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N16" s="13">
         <v>0.8410723709429708</v>
       </c>
       <c r="O16" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
       <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>65</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>64</v>
       </c>
       <c r="E17" s="11">
         <v>228.7943</v>
@@ -3602,27 +3645,30 @@
         <v>8</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N17" s="13">
         <v>0.6643531276938139</v>
       </c>
       <c r="O17" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q17" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
       <c r="A18" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="11">
         <v>156.6783</v>
@@ -3652,27 +3698,30 @@
         <v>8</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N18" s="13">
         <v>0.6369924288836575</v>
       </c>
       <c r="O18" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q18" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
       <c r="A19" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="11">
         <v>123.3216</v>
@@ -3702,27 +3751,30 @@
         <v>8</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N19" s="13">
         <v>0.662112373894027</v>
       </c>
       <c r="O19" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q19" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
       <c r="A20" s="10" t="s">
         <v>15</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="11">
         <v>251.7358</v>
@@ -3752,27 +3804,30 @@
         <v>6</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N20" s="13">
         <v>0.6121263867209685</v>
       </c>
       <c r="O20" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q20" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
       <c r="A21" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="19" t="s">
         <v>72</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D21" s="19" t="s">
-        <v>71</v>
       </c>
       <c r="E21" s="11">
         <v>273.3566</v>
@@ -3802,27 +3857,30 @@
         <v>6</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N21" s="13">
         <v>0.6100566751620263</v>
       </c>
       <c r="O21" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q21" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
       <c r="A22" s="10" t="s">
         <v>17</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E22" s="11">
         <v>113.3066</v>
@@ -3852,27 +3910,30 @@
         <v>5</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N22" s="13">
         <v>0.5689208109667999</v>
       </c>
       <c r="O22" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q22" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
       <c r="A23" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D23" s="19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="11">
         <v>224.6423</v>
@@ -3902,27 +3963,30 @@
         <v>4</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N23" s="13">
         <v>0.5555859964967851</v>
       </c>
       <c r="O23" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q23" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
       <c r="A24" s="10" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E24" s="11">
         <v>198.7093</v>
@@ -3952,27 +4016,30 @@
         <v>1</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N24" s="13">
         <v>0.4462074139990458</v>
       </c>
       <c r="O24" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q24" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
       <c r="A25" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E25" s="11">
         <v>72.88639999999999</v>
@@ -4002,18 +4069,21 @@
         <v>0</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N25" s="13">
         <v>1.053611276486443</v>
       </c>
       <c r="O25" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15">
+        <v>44</v>
+      </c>
+      <c r="Q25" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="F26" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G26" s="11">
         <f>SUM(G5:G25)</f>
@@ -4033,7 +4103,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P25"/>
+  <autoFilter ref="A4:Q25"/>
   <conditionalFormatting sqref="K5:K25">
     <cfRule type="colorScale" priority="1">
       <colorScale>
@@ -4414,17 +4484,17 @@
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="30" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>23</v>
@@ -4433,7 +4503,7 @@
         <v>25</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" s="18" t="s">
         <v>27</v>
@@ -4442,7 +4512,7 @@
         <v>35</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" s="18" t="s">
         <v>28</v>
@@ -4451,7 +4521,7 @@
         <v>29</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>32</v>
@@ -4460,13 +4530,13 @@
         <v>33</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N4" s="18" t="s">
         <v>36</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -4474,19 +4544,19 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E5" s="11">
         <v>926.2029</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" s="11">
         <v>1053.643</v>
@@ -4515,7 +4585,7 @@
         <v>1.809956883354321</v>
       </c>
       <c r="O5" s="23" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -4523,19 +4593,19 @@
         <v>1</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E6" s="11">
         <v>443.1115</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G6" s="11">
         <v>568.5155999999999</v>
@@ -4564,7 +4634,7 @@
         <v>2.927623067210654</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -4599,37 +4669,37 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="30" customHeight="1">
       <c r="A4" s="18" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B5" s="11">
         <v>10000</v>
@@ -4650,7 +4720,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="19" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B6" s="11">
         <v>9523.809999999999</v>
@@ -4671,7 +4741,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="19" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" s="11">
         <v>9047.190000000001</v>
@@ -4692,7 +4762,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="11">
         <v>8569.639999999999</v>
@@ -4713,7 +4783,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="11">
         <v>8092.69</v>
@@ -4734,7 +4804,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="11">
         <v>7616.77</v>
@@ -4755,7 +4825,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="11">
         <v>7139.55</v>
@@ -4776,7 +4846,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B12" s="11">
         <v>7139.55</v>
@@ -4795,7 +4865,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="19" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B13" s="11">
         <v>7139.55</v>
@@ -4814,7 +4884,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="11">
         <v>5714.88</v>
@@ -4835,7 +4905,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="19" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B15" s="11">
         <v>5714.88</v>
@@ -4854,7 +4924,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="19" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B16" s="11">
         <v>5714.88</v>
@@ -4873,7 +4943,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" s="11">
         <v>5714.88</v>
@@ -4892,7 +4962,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="19" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B18" s="11">
         <v>3768.96</v>
@@ -4913,7 +4983,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19" s="11">
         <v>3768.96</v>
@@ -4932,7 +5002,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B20" s="11">
         <v>3768.96</v>
@@ -4951,7 +5021,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B21" s="11">
         <v>3768.96</v>
@@ -4970,7 +5040,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B22" s="11">
         <v>1832.96</v>
@@ -4991,7 +5061,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B23" s="11">
         <v>1832.96</v>
@@ -5010,7 +5080,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="11">
         <v>859.8200000000001</v>
@@ -5031,7 +5101,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="19" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B25" s="11">
         <v>369.86</v>
@@ -5052,7 +5122,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B26" s="11">
         <v>0</v>
@@ -5073,7 +5143,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="11">
         <v>0</v>
@@ -5094,7 +5164,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B28" s="11">
         <v>610.96</v>
@@ -5115,7 +5185,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B29" s="11">
         <v>657.4299999999999</v>
@@ -5136,7 +5206,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" s="11">
         <v>159.91</v>
@@ -5182,17 +5252,17 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B4" s="18" t="s">
         <v>23</v>
@@ -5204,52 +5274,52 @@
         <v>25</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S4" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -5260,16 +5330,16 @@
         <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" s="11">
         <v>458.8099975585938</v>
       </c>
       <c r="F5" s="20">
-        <v>1.085664978718589</v>
+        <v>1.085693637696603</v>
       </c>
       <c r="G5" s="13">
         <v>0.5120832578157225</v>
@@ -5281,16 +5351,16 @@
         <v>2.358223271893585</v>
       </c>
       <c r="J5" s="13">
-        <v>2.605988236380184</v>
+        <v>2.605986620980146</v>
       </c>
       <c r="K5" s="13">
         <v>0.8619880398903373</v>
       </c>
       <c r="L5" s="13">
-        <v>-0.08336799457753447</v>
+        <v>-0.08338966141520089</v>
       </c>
       <c r="M5" s="13">
-        <v>-0.3886315554559648</v>
+        <v>-0.3882510103523907</v>
       </c>
       <c r="N5" s="13">
         <v>15.755887</v>
@@ -5308,10 +5378,10 @@
         <v>1.049900786089409</v>
       </c>
       <c r="S5" s="12">
-        <v>74.49539614847626</v>
+        <v>74.49539614851619</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -5322,16 +5392,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" s="11">
         <v>436</v>
       </c>
       <c r="F6" s="20">
-        <v>1.078766031499238</v>
+        <v>1.078791303344421</v>
       </c>
       <c r="G6" s="13">
         <v>0.5257662583602529</v>
@@ -5343,16 +5413,16 @@
         <v>2.788833462425317</v>
       </c>
       <c r="J6" s="13">
-        <v>2.592982122839505</v>
+        <v>2.592987870138397</v>
       </c>
       <c r="K6" s="13">
         <v>0.6828504886879644</v>
       </c>
       <c r="L6" s="13">
-        <v>0.09728168509131846</v>
+        <v>0.09725876316050838</v>
       </c>
       <c r="M6" s="13">
-        <v>-0.6461414565724128</v>
+        <v>-0.6458299194303707</v>
       </c>
       <c r="N6" s="13">
         <v>18.08045</v>
@@ -5370,10 +5440,10 @@
         <v>0.8166079942791562</v>
       </c>
       <c r="S6" s="12">
-        <v>70.45073668034189</v>
+        <v>70.45073668034195</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -5381,19 +5451,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E7" s="11">
         <v>239.1799926757812</v>
       </c>
       <c r="F7" s="20">
-        <v>0.9564768536065485</v>
+        <v>0.9565102773976096</v>
       </c>
       <c r="G7" s="13">
         <v>-0.6400146282615523</v>
@@ -5405,16 +5475,16 @@
         <v>0.4239293519712278</v>
       </c>
       <c r="J7" s="13">
-        <v>2.538073915541093</v>
+        <v>2.538065434056157</v>
       </c>
       <c r="K7" s="13">
         <v>0.5556849430813415</v>
       </c>
       <c r="L7" s="13">
-        <v>-0.2563698115640022</v>
+        <v>-0.2563902764432996</v>
       </c>
       <c r="M7" s="13">
-        <v>-0.02583609273826026</v>
+        <v>-0.02537114112201089</v>
       </c>
       <c r="N7" s="13">
         <v>33.448517</v>
@@ -5432,10 +5502,10 @@
         <v>1.443572980130468</v>
       </c>
       <c r="S7" s="12">
-        <v>75.63453577060713</v>
+        <v>75.63453584428217</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5443,19 +5513,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" s="11">
         <v>989.0399780273438</v>
       </c>
       <c r="F8" s="20">
-        <v>0.9377735635520826</v>
+        <v>0.9377756854861626</v>
       </c>
       <c r="G8" s="13">
         <v>-0.1172294581697382</v>
@@ -5467,16 +5537,16 @@
         <v>4.12785569855674</v>
       </c>
       <c r="J8" s="13">
-        <v>1.607536947772798</v>
+        <v>1.607558418334735</v>
       </c>
       <c r="K8" s="13">
         <v>-0.3571425169035899</v>
       </c>
       <c r="L8" s="13">
-        <v>-2.653531115308783</v>
+        <v>-2.653534925518545</v>
       </c>
       <c r="M8" s="13">
-        <v>-0.9782895282190311</v>
+        <v>-0.9783406609929741</v>
       </c>
       <c r="N8" s="13">
         <v>13.84367</v>
@@ -5494,10 +5564,10 @@
         <v>1.318998661144475</v>
       </c>
       <c r="S8" s="12">
-        <v>44.65640077520665</v>
+        <v>44.65640077520689</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5508,16 +5578,16 @@
         <v>20</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E9" s="11">
         <v>70.33000183105469</v>
       </c>
       <c r="F9" s="20">
-        <v>0.9363369136679693</v>
+        <v>0.9363640257707037</v>
       </c>
       <c r="G9" s="13">
         <v>0.2210528163067884</v>
@@ -5529,16 +5599,16 @@
         <v>2.11370107259597</v>
       </c>
       <c r="J9" s="13">
-        <v>2.826534552097618</v>
+        <v>2.826530447715288</v>
       </c>
       <c r="K9" s="13">
         <v>0.3826292223210245</v>
       </c>
       <c r="L9" s="13">
-        <v>-1.935572265305158</v>
+        <v>-1.935581063651249</v>
       </c>
       <c r="M9" s="13">
-        <v>-0.08813769238466007</v>
+        <v>-0.08777680090717965</v>
       </c>
       <c r="N9" s="13">
         <v>37.86598</v>
@@ -5556,10 +5626,10 @@
         <v>1.850228779373882</v>
       </c>
       <c r="S9" s="12">
-        <v>63.1780122898009</v>
+        <v>63.17801228970154</v>
       </c>
       <c r="T9" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5570,16 +5640,16 @@
         <v>5</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="11">
         <v>281.4700012207031</v>
       </c>
       <c r="F10" s="20">
-        <v>0.8749995009995929</v>
+        <v>0.8750213495426987</v>
       </c>
       <c r="G10" s="13">
         <v>0.4033582074212857</v>
@@ -5591,16 +5661,16 @@
         <v>2.328125318139155</v>
       </c>
       <c r="J10" s="13">
-        <v>2.153499225132459</v>
+        <v>2.153504015857766</v>
       </c>
       <c r="K10" s="13">
         <v>0.7718663706126003</v>
       </c>
       <c r="L10" s="13">
-        <v>0.4091535559188778</v>
+        <v>0.4091284672073267</v>
       </c>
       <c r="M10" s="13">
-        <v>-0.8467680892443864</v>
+        <v>-0.8464941311417989</v>
       </c>
       <c r="N10" s="13">
         <v>15.896</v>
@@ -5618,10 +5688,10 @@
         <v>0.7769217142407425</v>
       </c>
       <c r="S10" s="12">
-        <v>71.6520349509448</v>
+        <v>71.65203495089884</v>
       </c>
       <c r="T10" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5629,19 +5699,19 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" s="11">
         <v>576.760009765625</v>
       </c>
       <c r="F11" s="20">
-        <v>0.8459790624533218</v>
+        <v>0.8459944330838874</v>
       </c>
       <c r="G11" s="13">
         <v>-0.1075886523285822</v>
@@ -5653,16 +5723,16 @@
         <v>2.119917693224531</v>
       </c>
       <c r="J11" s="13">
-        <v>2.679728080946291</v>
+        <v>2.679734804539066</v>
       </c>
       <c r="K11" s="13">
         <v>1.749935284430495</v>
       </c>
       <c r="L11" s="13">
-        <v>-2.817310696293543</v>
+        <v>-2.817313368617926</v>
       </c>
       <c r="M11" s="13">
-        <v>-0.704499946341189</v>
+        <v>-0.7043310226887378</v>
       </c>
       <c r="N11" s="13">
         <v>33.41277</v>
@@ -5680,10 +5750,10 @@
         <v>2.053378176100111</v>
       </c>
       <c r="S11" s="12">
-        <v>58.78827562228673</v>
+        <v>58.78827562228676</v>
       </c>
       <c r="T11" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5694,16 +5764,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E12" s="11">
         <v>371.6799926757812</v>
       </c>
       <c r="F12" s="20">
-        <v>0.8407437389780993</v>
+        <v>0.8407676470610254</v>
       </c>
       <c r="G12" s="13">
         <v>1.187286552445482</v>
@@ -5715,16 +5785,16 @@
         <v>-0.3892490054509348</v>
       </c>
       <c r="J12" s="13">
-        <v>0.5549810262260452</v>
+        <v>0.5550039803922299</v>
       </c>
       <c r="K12" s="13">
         <v>4.065553522685905</v>
       </c>
       <c r="L12" s="13">
-        <v>1.0060120350558</v>
+        <v>1.005982799572517</v>
       </c>
       <c r="M12" s="13">
-        <v>-0.3697938460681786</v>
+        <v>-0.3695591465423338</v>
       </c>
       <c r="N12" s="13">
         <v>9.904647000000001</v>
@@ -5742,10 +5812,10 @@
         <v>0.2429390004958811</v>
       </c>
       <c r="S12" s="12">
-        <v>57.69523119256868</v>
+        <v>57.69523121020872</v>
       </c>
       <c r="T12" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5756,16 +5826,16 @@
         <v>11</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="11">
         <v>352.7200012207031</v>
       </c>
       <c r="F13" s="20">
-        <v>0.8323522967121189</v>
+        <v>0.832380707519863</v>
       </c>
       <c r="G13" s="13">
         <v>-0.3285343560247656</v>
@@ -5777,16 +5847,16 @@
         <v>1.329512425464752</v>
       </c>
       <c r="J13" s="13">
-        <v>0.1709527599131569</v>
+        <v>0.1709850369707459</v>
       </c>
       <c r="K13" s="13">
         <v>4.065553522685905</v>
       </c>
       <c r="L13" s="13">
-        <v>0.1351820442138687</v>
+        <v>0.1351588589641257</v>
       </c>
       <c r="M13" s="13">
-        <v>-0.278356783950331</v>
+        <v>-0.2781052988821814</v>
       </c>
       <c r="N13" s="13">
         <v>17.644756</v>
@@ -5804,10 +5874,10 @@
         <v>0.09911777141138889</v>
       </c>
       <c r="S13" s="12">
-        <v>57.28955266000223</v>
+        <v>57.28955266000194</v>
       </c>
       <c r="T13" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5818,16 +5888,16 @@
         <v>4</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E14" s="11">
         <v>61.13000106811523</v>
       </c>
       <c r="F14" s="20">
-        <v>0.7778006585332977</v>
+        <v>0.7778336252776394</v>
       </c>
       <c r="G14" s="13">
         <v>0.5555932315613028</v>
@@ -5839,16 +5909,16 @@
         <v>3.077929577016555</v>
       </c>
       <c r="J14" s="13">
-        <v>0.5290531478456938</v>
+        <v>0.5290788692858239</v>
       </c>
       <c r="K14" s="13">
         <v>0.9675907321114892</v>
       </c>
       <c r="L14" s="13">
-        <v>0.1153480423268218</v>
+        <v>0.1153249948770452</v>
       </c>
       <c r="M14" s="13">
-        <v>-0.1273606016655193</v>
+        <v>-0.1270276871744041</v>
       </c>
       <c r="N14" s="13">
         <v>17.076704</v>
@@ -5866,10 +5936,10 @@
         <v>0.06259313932283361</v>
       </c>
       <c r="S14" s="12">
-        <v>61.47408057653433</v>
+        <v>61.47408057679643</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -5880,16 +5950,16 @@
         <v>10</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="11">
         <v>67.01999664306641</v>
       </c>
       <c r="F15" s="20">
-        <v>0.7398711165186228</v>
+        <v>0.739903413331194</v>
       </c>
       <c r="G15" s="13">
         <v>1.255811942784209</v>
@@ -5901,16 +5971,16 @@
         <v>-0.5870526183679002</v>
       </c>
       <c r="J15" s="13">
-        <v>1.0224975848524</v>
+        <v>1.022521270947599</v>
       </c>
       <c r="K15" s="13">
         <v>4.065553522685905</v>
       </c>
       <c r="L15" s="13">
-        <v>0.02854903731338743</v>
+        <v>0.02852659291386957</v>
       </c>
       <c r="M15" s="13">
-        <v>-0.06121153944994118</v>
+        <v>-0.06087981885015764</v>
       </c>
       <c r="N15" s="13">
         <v>12.221939</v>
@@ -5928,10 +5998,10 @@
         <v>0.7886307568636042</v>
       </c>
       <c r="S15" s="12">
-        <v>59.97532048433934</v>
+        <v>59.97532048433954</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -5939,19 +6009,19 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E16" s="11">
         <v>233.9199981689453</v>
       </c>
       <c r="F16" s="20">
-        <v>0.69769004639359</v>
+        <v>0.6976935935408983</v>
       </c>
       <c r="G16" s="13">
         <v>0.445387850826149</v>
@@ -5963,16 +6033,16 @@
         <v>0.1720715631623876</v>
       </c>
       <c r="J16" s="13">
-        <v>0.8032648560068737</v>
+        <v>0.8032675264038369</v>
       </c>
       <c r="K16" s="13">
         <v>3.807805548551582</v>
       </c>
       <c r="L16" s="13">
-        <v>-1.79638149583805</v>
+        <v>-1.796391261234738</v>
       </c>
       <c r="M16" s="13">
-        <v>-0.9469545191352288</v>
+        <v>-0.9469128697349707</v>
       </c>
       <c r="N16" s="13">
         <v>20.963404</v>
@@ -5990,10 +6060,10 @@
         <v>0.3594278623200486</v>
       </c>
       <c r="S16" s="12">
-        <v>52.38320949327242</v>
+        <v>52.38320948857223</v>
       </c>
       <c r="T16" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -6001,19 +6071,19 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E17" s="11">
         <v>39.97999954223633</v>
       </c>
       <c r="F17" s="20">
-        <v>0.6471435880736945</v>
+        <v>0.6471419624260647</v>
       </c>
       <c r="G17" s="13">
         <v>-0.01436423851863369</v>
@@ -6025,16 +6095,16 @@
         <v>3.797605429884786</v>
       </c>
       <c r="J17" s="13">
-        <v>0.6940526159196395</v>
+        <v>0.6940462614974199</v>
       </c>
       <c r="K17" s="13">
         <v>3.652442425440882</v>
       </c>
       <c r="L17" s="13">
-        <v>-2.914608927309175</v>
+        <v>-2.914610923638212</v>
       </c>
       <c r="M17" s="13">
-        <v>-0.8985264561787664</v>
+        <v>-0.8985214504440362</v>
       </c>
       <c r="N17" s="13">
         <v>13.120689</v>
@@ -6052,10 +6122,10 @@
         <v>0.5394686407125744</v>
       </c>
       <c r="S17" s="12">
-        <v>48.05305385006023</v>
+        <v>48.05305385006031</v>
       </c>
       <c r="T17" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -6066,16 +6136,16 @@
         <v>13</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E18" s="11">
         <v>153.6199951171875</v>
       </c>
       <c r="F18" s="20">
-        <v>0.638800571378175</v>
+        <v>0.6388147124101484</v>
       </c>
       <c r="G18" s="13">
         <v>0.4755572880593366</v>
@@ -6087,16 +6157,16 @@
         <v>-0.05791369034948607</v>
       </c>
       <c r="J18" s="13">
-        <v>0.7376069923162509</v>
+        <v>0.7376299794250959</v>
       </c>
       <c r="K18" s="13">
         <v>3.55734471307419</v>
       </c>
       <c r="L18" s="13">
-        <v>0.4391509123489496</v>
+        <v>0.4391256152258671</v>
       </c>
       <c r="M18" s="13">
-        <v>-0.3282006709075356</v>
+        <v>-0.3280911368237265</v>
       </c>
       <c r="N18" s="13">
         <v>15.954309</v>
@@ -6111,13 +6181,13 @@
         <v>0.053</v>
       </c>
       <c r="R18" s="15">
-        <v>0.3255994279230887</v>
+        <v>0.3255993406526994</v>
       </c>
       <c r="S18" s="12">
-        <v>45.50790736854233</v>
+        <v>45.50790736452572</v>
       </c>
       <c r="T18" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -6128,16 +6198,16 @@
         <v>18</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E19" s="11">
         <v>229.4100036621094</v>
       </c>
       <c r="F19" s="20">
-        <v>0.6286861913466527</v>
+        <v>0.6287037042026858</v>
       </c>
       <c r="G19" s="13">
         <v>0.1972144638373766</v>
@@ -6149,16 +6219,16 @@
         <v>-0.878827185566031</v>
       </c>
       <c r="J19" s="13">
-        <v>0.9068715021885962</v>
+        <v>0.9068898126213472</v>
       </c>
       <c r="K19" s="13">
         <v>3.643043232939523</v>
       </c>
       <c r="L19" s="13">
-        <v>0.4999730486562222</v>
+        <v>0.4999473289614175</v>
       </c>
       <c r="M19" s="13">
-        <v>-0.7814254749574097</v>
+        <v>-0.7812559386087082</v>
       </c>
       <c r="N19" s="13">
         <v>40.090588</v>
@@ -6176,10 +6246,10 @@
         <v>0.3007314736822435</v>
       </c>
       <c r="S19" s="12">
-        <v>60.46120476963799</v>
+        <v>60.46120476963803</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -6190,16 +6260,16 @@
         <v>15</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" s="11">
         <v>259.5299987792969</v>
       </c>
       <c r="F20" s="20">
-        <v>0.6274879429464142</v>
+        <v>0.6275196101113768</v>
       </c>
       <c r="G20" s="13">
         <v>-0.02977335660029285</v>
@@ -6211,16 +6281,16 @@
         <v>0.9707254877878508</v>
       </c>
       <c r="J20" s="13">
-        <v>0.1653764895017485</v>
+        <v>0.1654028307288406</v>
       </c>
       <c r="K20" s="13">
         <v>4.065553522685905</v>
       </c>
       <c r="L20" s="13">
-        <v>-0.5335577582532481</v>
+        <v>-0.5335762973240302</v>
       </c>
       <c r="M20" s="13">
-        <v>0.0587484519384483</v>
+        <v>0.05905941620197114</v>
       </c>
       <c r="N20" s="13">
         <v>21.112629</v>
@@ -6238,10 +6308,10 @@
         <v>0.08187085514034953</v>
       </c>
       <c r="S20" s="12">
-        <v>55.57687470546151</v>
+        <v>55.57687470546165</v>
       </c>
       <c r="T20" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -6252,16 +6322,16 @@
         <v>17</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E21" s="11">
         <v>117.6100006103516</v>
       </c>
       <c r="F21" s="20">
-        <v>0.6015319929714389</v>
+        <v>0.6015708208717453</v>
       </c>
       <c r="G21" s="13">
         <v>0.3844623079993796</v>
@@ -6273,16 +6343,16 @@
         <v>0.4303409832118458</v>
       </c>
       <c r="J21" s="13">
-        <v>-0.1181337482570213</v>
+        <v>-0.1181014898345606</v>
       </c>
       <c r="K21" s="13">
         <v>4.065553522685905</v>
       </c>
       <c r="L21" s="13">
-        <v>0.0934525566037277</v>
+        <v>0.09342966127641296</v>
       </c>
       <c r="M21" s="13">
-        <v>0.6357971798297802</v>
+        <v>0.636178730994867</v>
       </c>
       <c r="N21" s="13">
         <v>14.45067</v>
@@ -6300,10 +6370,10 @@
         <v>0.1515715634312869</v>
       </c>
       <c r="S21" s="12">
-        <v>49.82271004354786</v>
+        <v>49.82271004354774</v>
       </c>
       <c r="T21" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -6314,16 +6384,16 @@
         <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E22" s="11">
         <v>1487.329956054688</v>
       </c>
       <c r="F22" s="20">
-        <v>0.5855374186333148</v>
+        <v>0.5855431106407357</v>
       </c>
       <c r="G22" s="13">
         <v>-0.3715766681671279</v>
@@ -6335,16 +6405,16 @@
         <v>4.09736352358056</v>
       </c>
       <c r="J22" s="13">
-        <v>0.470624991669029</v>
+        <v>0.4706676696181682</v>
       </c>
       <c r="K22" s="13">
         <v>0.1233220880188241</v>
       </c>
       <c r="L22" s="13">
-        <v>-2.914608927309175</v>
+        <v>-2.914610923638212</v>
       </c>
       <c r="M22" s="13">
-        <v>-0.8444096384372709</v>
+        <v>-0.8444970334070023</v>
       </c>
       <c r="N22" s="13">
         <v>21.445498</v>
@@ -6365,7 +6435,7 @@
         <v>38.56381407509831</v>
       </c>
       <c r="T22" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -6373,19 +6443,19 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23" s="11">
         <v>192.9400024414062</v>
       </c>
       <c r="F23" s="20">
-        <v>0.5741257978280695</v>
+        <v>0.5741517902117206</v>
       </c>
       <c r="G23" s="13">
         <v>-2.114609254291167</v>
@@ -6397,16 +6467,16 @@
         <v>0.220221171989416</v>
       </c>
       <c r="J23" s="13">
-        <v>2.232871523848216</v>
+        <v>2.232875261442047</v>
       </c>
       <c r="K23" s="13">
         <v>0.4998426817497377</v>
       </c>
       <c r="L23" s="13">
-        <v>-0.6093692367710628</v>
+        <v>-0.6093872491292204</v>
       </c>
       <c r="M23" s="13">
-        <v>-0.5486809408163533</v>
+        <v>-0.5483565427289621</v>
       </c>
       <c r="N23" s="13">
         <v>68.81625</v>
@@ -6427,7 +6497,7 @@
         <v>69.56377323296238</v>
       </c>
       <c r="T23" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -6435,19 +6505,19 @@
         <v>20</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E24" s="11">
         <v>388.1199951171875</v>
       </c>
       <c r="F24" s="20">
-        <v>0.5480118645011236</v>
+        <v>0.5480296687934385</v>
       </c>
       <c r="G24" s="13">
         <v>0.05829011904393756</v>
@@ -6459,16 +6529,16 @@
         <v>0.4382083912057649</v>
       </c>
       <c r="J24" s="13">
-        <v>1.599748433626592</v>
+        <v>1.599742985343705</v>
       </c>
       <c r="K24" s="13">
         <v>1.8583024450344</v>
       </c>
       <c r="L24" s="13">
-        <v>-1.785396833194811</v>
+        <v>-1.785406674909236</v>
       </c>
       <c r="M24" s="13">
-        <v>-0.7989487719759455</v>
+        <v>-0.7986984059753659</v>
       </c>
       <c r="N24" s="13">
         <v>35.48854</v>
@@ -6486,10 +6556,10 @@
         <v>0.7166615126887068</v>
       </c>
       <c r="S24" s="12">
-        <v>68.13516668419383</v>
+        <v>68.13516668419412</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -6500,16 +6570,16 @@
         <v>6</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E25" s="11">
         <v>46.84000015258789</v>
       </c>
       <c r="F25" s="20">
-        <v>0.5462024417427693</v>
+        <v>0.5462298704441475</v>
       </c>
       <c r="G25" s="13">
         <v>0.9861002278279252</v>
@@ -6521,16 +6591,16 @@
         <v>-0.2947421241753646</v>
       </c>
       <c r="J25" s="13">
-        <v>1.483847611979077</v>
+        <v>1.483863809330682</v>
       </c>
       <c r="K25" s="13">
         <v>-0.5794057748769046</v>
       </c>
       <c r="L25" s="13">
-        <v>-0.5150851212139512</v>
+        <v>-0.5151037886263952</v>
       </c>
       <c r="M25" s="13">
-        <v>-0.4542765188896552</v>
+        <v>-0.4539803996316135</v>
       </c>
       <c r="N25" s="13">
         <v>9.699789000000001</v>
@@ -6548,10 +6618,10 @@
         <v>0.2024664476819262</v>
       </c>
       <c r="S25" s="12">
-        <v>65.0228042256123</v>
+        <v>65.02280422534588</v>
       </c>
       <c r="T25" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -6562,16 +6632,16 @@
         <v>12</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E26" s="11">
         <v>232.6000061035156</v>
       </c>
       <c r="F26" s="20">
-        <v>0.4973040134956361</v>
+        <v>0.4973358805009261</v>
       </c>
       <c r="G26" s="13">
         <v>1.256899045882137</v>
@@ -6583,16 +6653,16 @@
         <v>-0.06592248185956601</v>
       </c>
       <c r="J26" s="13">
-        <v>-0.194501476273947</v>
+        <v>-0.1944686334570076</v>
       </c>
       <c r="K26" s="13">
         <v>2.020300292263706</v>
       </c>
       <c r="L26" s="13">
-        <v>0.4611583052647147</v>
+        <v>0.4611328552416769</v>
       </c>
       <c r="M26" s="13">
-        <v>0.4862870130294497</v>
+        <v>0.4865812775493311</v>
       </c>
       <c r="N26" s="13">
         <v>4.590436</v>
@@ -6610,10 +6680,10 @@
         <v>0.09162912947589863</v>
       </c>
       <c r="S26" s="12">
-        <v>45.07745554447872</v>
+        <v>45.07745554447878</v>
       </c>
       <c r="T26" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -6621,19 +6691,19 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E27" s="11">
         <v>282.6600036621094</v>
       </c>
       <c r="F27" s="20">
-        <v>0.4896499994980856</v>
+        <v>0.4896502677651764</v>
       </c>
       <c r="G27" s="13">
         <v>-0.8805891848256409</v>
@@ -6645,16 +6715,16 @@
         <v>2.246420289880714</v>
       </c>
       <c r="J27" s="13">
-        <v>2.274101635714309</v>
+        <v>2.274102618645411</v>
       </c>
       <c r="K27" s="13">
         <v>-0.02374762994361796</v>
       </c>
       <c r="L27" s="13">
-        <v>-2.648687062928873</v>
+        <v>-2.648690906793479</v>
       </c>
       <c r="M27" s="13">
-        <v>-1.284876201104153</v>
+        <v>-1.284873650858694</v>
       </c>
       <c r="N27" s="13">
         <v>40.037346</v>
@@ -6672,10 +6742,10 @@
         <v>1.275112753720819</v>
       </c>
       <c r="S27" s="12">
-        <v>55.95509928104708</v>
+        <v>55.95509928104715</v>
       </c>
       <c r="T27" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -6686,16 +6756,16 @@
         <v>16</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E28" s="11">
         <v>276.6700134277344</v>
       </c>
       <c r="F28" s="20">
-        <v>0.4849478650414937</v>
+        <v>0.4849551548480557</v>
       </c>
       <c r="G28" s="13">
         <v>-0.7248874185708422</v>
@@ -6707,16 +6777,16 @@
         <v>-0.4530813424943169</v>
       </c>
       <c r="J28" s="13">
-        <v>2.597412311560211</v>
+        <v>2.59740885948642</v>
       </c>
       <c r="K28" s="13">
         <v>-0.2581745488010443</v>
       </c>
       <c r="L28" s="13">
-        <v>-1.188653150194887</v>
+        <v>-1.188667137883478</v>
       </c>
       <c r="M28" s="13">
-        <v>-1.088494007778788</v>
+        <v>-1.088379449153606</v>
       </c>
       <c r="N28" s="13">
         <v>51.89739</v>
@@ -6734,10 +6804,10 @@
         <v>1.179190417634238</v>
       </c>
       <c r="S28" s="12">
-        <v>61.94913440562174</v>
+        <v>61.94913440562173</v>
       </c>
       <c r="T28" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -6745,19 +6815,19 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E29" s="11">
         <v>215</v>
       </c>
       <c r="F29" s="20">
-        <v>0.4670117078999237</v>
+        <v>0.4670350759472273</v>
       </c>
       <c r="G29" s="13">
         <v>0.4630268796884387</v>
@@ -6769,16 +6839,16 @@
         <v>2.233294390227442</v>
       </c>
       <c r="J29" s="13">
-        <v>0.7959757120383317</v>
+        <v>0.7959970623679594</v>
       </c>
       <c r="K29" s="13">
         <v>-0.1464900261378365</v>
       </c>
       <c r="L29" s="13">
-        <v>0.7534841921231115</v>
+        <v>0.7534567111182474</v>
       </c>
       <c r="M29" s="13">
-        <v>-0.6694876144393433</v>
+        <v>-0.6692549668305044</v>
       </c>
       <c r="N29" s="13">
         <v>20.40231</v>
@@ -6796,10 +6866,10 @@
         <v>0.141217834444429</v>
       </c>
       <c r="S29" s="12">
-        <v>63.81150708646095</v>
+        <v>63.81150708617674</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -6810,16 +6880,16 @@
         <v>7</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E30" s="11">
         <v>226.3200073242188</v>
       </c>
       <c r="F30" s="20">
-        <v>0.4597533303443286</v>
+        <v>0.4597703297647296</v>
       </c>
       <c r="G30" s="13">
         <v>-1.1019019214601</v>
@@ -6831,16 +6901,16 @@
         <v>2.390890545007346</v>
       </c>
       <c r="J30" s="13">
-        <v>0.3806040867899689</v>
+        <v>0.3806274011474164</v>
       </c>
       <c r="K30" s="13">
         <v>-0.2946655314533796</v>
       </c>
       <c r="L30" s="13">
-        <v>-0.1437563338861892</v>
+        <v>-0.1437775811660089</v>
       </c>
       <c r="M30" s="13">
-        <v>-0.378479770259575</v>
+        <v>-0.3783387708851265</v>
       </c>
       <c r="N30" s="13">
         <v>28.986094</v>
@@ -6858,10 +6928,10 @@
         <v>0.1982321357508277</v>
       </c>
       <c r="S30" s="12">
-        <v>49.40904749569918</v>
+        <v>49.4090474956845</v>
       </c>
       <c r="T30" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -6872,16 +6942,16 @@
         <v>19</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E31" s="11">
         <v>201.1399993896484</v>
       </c>
       <c r="F31" s="20">
-        <v>0.453550833150787</v>
+        <v>0.4535810840919642</v>
       </c>
       <c r="G31" s="13">
         <v>0.573799013559786</v>
@@ -6893,16 +6963,16 @@
         <v>4.09736352358056</v>
       </c>
       <c r="J31" s="13">
-        <v>-0.3362566626083723</v>
+        <v>-0.3362273364853589</v>
       </c>
       <c r="K31" s="13">
         <v>0.6800860203052117</v>
       </c>
       <c r="L31" s="13">
-        <v>0.7185253716142624</v>
+        <v>0.7184981334915115</v>
       </c>
       <c r="M31" s="13">
-        <v>0.2701147574421553</v>
+        <v>0.2704033498376333</v>
       </c>
       <c r="N31" s="13">
         <v>12.797688</v>
@@ -6920,10 +6990,10 @@
         <v>0.0261541061582351</v>
       </c>
       <c r="S31" s="12">
-        <v>49.1103672203525</v>
+        <v>49.11036722035263</v>
       </c>
       <c r="T31" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -6931,19 +7001,19 @@
         <v>28</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E32" s="11">
         <v>94.73000335693359</v>
       </c>
       <c r="F32" s="20">
-        <v>0.4304199243168543</v>
+        <v>0.4304532172388581</v>
       </c>
       <c r="G32" s="13">
         <v>0.09120761566025611</v>
@@ -6955,16 +7025,16 @@
         <v>0.0273109313630392</v>
       </c>
       <c r="J32" s="13">
-        <v>0.4462933714250963</v>
+        <v>0.4463133577666956</v>
       </c>
       <c r="K32" s="13">
         <v>0.07245586977617496</v>
       </c>
       <c r="L32" s="13">
-        <v>0.2470968185257646</v>
+        <v>0.2470728557298551</v>
       </c>
       <c r="M32" s="13">
-        <v>-0.1312882555792421</v>
+        <v>-0.1309290707382601</v>
       </c>
       <c r="N32" s="13">
         <v>16.694096</v>
@@ -6982,10 +7052,10 @@
         <v>0.04035537369362263</v>
       </c>
       <c r="S32" s="12">
-        <v>63.93102421462042</v>
+        <v>63.93102419667103</v>
       </c>
       <c r="T32" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -6993,19 +7063,19 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E33" s="11">
         <v>150.5099945068359</v>
       </c>
       <c r="F33" s="20">
-        <v>0.4126218325768846</v>
+        <v>0.4126547753912954</v>
       </c>
       <c r="G33" s="13">
         <v>0.5258568789706033</v>
@@ -7017,16 +7087,16 @@
         <v>1.396975994830035</v>
       </c>
       <c r="J33" s="13">
-        <v>0.5785776767507351</v>
+        <v>0.5786032497754163</v>
       </c>
       <c r="K33" s="13">
         <v>-0.5191403641328964</v>
       </c>
       <c r="L33" s="13">
-        <v>0.1119842680637263</v>
+        <v>0.1119612439843206</v>
       </c>
       <c r="M33" s="13">
-        <v>-0.1787419676124397</v>
+        <v>-0.1784088132153056</v>
       </c>
       <c r="N33" s="13">
         <v>11.529961</v>
@@ -7044,10 +7114,10 @@
         <v>0.1156854457104213</v>
       </c>
       <c r="S33" s="12">
-        <v>62.57628203594637</v>
+        <v>62.57628203594309</v>
       </c>
       <c r="T33" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -7055,19 +7125,19 @@
         <v>30</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="11">
         <v>893.9500122070312</v>
       </c>
       <c r="F34" s="20">
-        <v>0.4035934984669988</v>
+        <v>0.4036206365483563</v>
       </c>
       <c r="G34" s="13">
         <v>0.4370619936694824</v>
@@ -7079,16 +7149,16 @@
         <v>0.8896007492696106</v>
       </c>
       <c r="J34" s="13">
-        <v>-0.6144670790881682</v>
+        <v>-0.6144243533410796</v>
       </c>
       <c r="K34" s="13">
         <v>1.812412269880705</v>
       </c>
       <c r="L34" s="13">
-        <v>0.4226740520934945</v>
+        <v>0.4226488694460888</v>
       </c>
       <c r="M34" s="13">
-        <v>0.5723320137312273</v>
+        <v>0.5725299051821682</v>
       </c>
       <c r="N34" s="13">
         <v>13.827336</v>
@@ -7106,10 +7176,10 @@
         <v>0.01290691566887481</v>
       </c>
       <c r="S34" s="12">
-        <v>34.55781914973589</v>
+        <v>34.55781915000817</v>
       </c>
       <c r="T34" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -7117,19 +7187,19 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E35" s="11">
         <v>30.95</v>
       </c>
       <c r="F35" s="20">
-        <v>0.4017920647625202</v>
+        <v>0.4018143441367035</v>
       </c>
       <c r="G35" s="13">
         <v>-0.01541387474592746</v>
@@ -7141,16 +7211,16 @@
         <v>-1.185161562431872</v>
       </c>
       <c r="J35" s="13">
-        <v>0.8539374274117441</v>
+        <v>0.8539599034963703</v>
       </c>
       <c r="K35" s="13">
         <v>4.065553522685905</v>
       </c>
       <c r="L35" s="13">
-        <v>0.4646125273660214</v>
+        <v>0.4645870533442115</v>
       </c>
       <c r="M35" s="13">
-        <v>-1.107437984010593</v>
+        <v>-1.107224671634293</v>
       </c>
       <c r="N35" s="13">
         <v>497.26776</v>
@@ -7168,10 +7238,10 @@
         <v>0.1308001461454147</v>
       </c>
       <c r="S35" s="12">
-        <v>75.2229940134896</v>
+        <v>75.22299401348944</v>
       </c>
       <c r="T35" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -7179,19 +7249,19 @@
         <v>32</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E36" s="11">
         <v>1182.619995117188</v>
       </c>
       <c r="F36" s="20">
-        <v>0.3887805185355094</v>
+        <v>0.3888064547873435</v>
       </c>
       <c r="G36" s="13">
         <v>-1.067825127575939</v>
@@ -7203,16 +7273,16 @@
         <v>0.7243252315067988</v>
       </c>
       <c r="J36" s="13">
-        <v>0.3708803209756428</v>
+        <v>0.3709060453153052</v>
       </c>
       <c r="K36" s="13">
         <v>0.8724930197447975</v>
       </c>
       <c r="L36" s="13">
-        <v>0.3373257217823686</v>
+        <v>0.3373011321064223</v>
       </c>
       <c r="M36" s="13">
-        <v>-0.1993808926548141</v>
+        <v>-0.1991347135236622</v>
       </c>
       <c r="N36" s="13">
         <v>39.5861</v>
@@ -7230,10 +7300,10 @@
         <v>0.2762663501477425</v>
       </c>
       <c r="S36" s="12">
-        <v>55.1493026910259</v>
+        <v>55.14930268724262</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -7241,19 +7311,19 @@
         <v>33</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E37" s="11">
         <v>137.5599975585938</v>
       </c>
       <c r="F37" s="20">
-        <v>0.3882735109121323</v>
+        <v>0.3883036491457548</v>
       </c>
       <c r="G37" s="13">
         <v>0.4503326028677878</v>
@@ -7265,16 +7335,16 @@
         <v>0.7716117421870532</v>
       </c>
       <c r="J37" s="13">
-        <v>0.8973741036071611</v>
+        <v>0.8973941032917306</v>
       </c>
       <c r="K37" s="13">
         <v>-0.05028652641804361</v>
       </c>
       <c r="L37" s="13">
-        <v>0.3041744035286977</v>
+        <v>0.3041500441769475</v>
       </c>
       <c r="M37" s="13">
-        <v>-0.3658419594566631</v>
+        <v>-0.3655219608397052</v>
       </c>
       <c r="N37" s="13">
         <v>17.76159</v>
@@ -7292,10 +7362,10 @@
         <v>0.1285116901271193</v>
       </c>
       <c r="S37" s="12">
-        <v>65.32149315245815</v>
+        <v>65.32149315234878</v>
       </c>
       <c r="T37" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -7306,16 +7376,16 @@
         <v>14</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E38" s="11">
         <v>111.3600006103516</v>
       </c>
       <c r="F38" s="20">
-        <v>0.3806692236085101</v>
+        <v>0.3806737295530273</v>
       </c>
       <c r="G38" s="13">
         <v>0.3787913962730532</v>
@@ -7327,16 +7397,16 @@
         <v>0.5122250580763105</v>
       </c>
       <c r="J38" s="13">
-        <v>-0.0923574974510399</v>
+        <v>-0.09232601847091108</v>
       </c>
       <c r="K38" s="13">
         <v>1.794719672231089</v>
       </c>
       <c r="L38" s="13">
-        <v>0.1810594146059152</v>
+        <v>0.1810359106156512</v>
       </c>
       <c r="M38" s="13">
-        <v>-0.2300740145997751</v>
+        <v>-0.2301181084760948</v>
       </c>
       <c r="N38" s="13">
         <v>14.368154</v>
@@ -7354,10 +7424,10 @@
         <v>0.1654630774844636</v>
       </c>
       <c r="S38" s="12">
-        <v>29.21590779509792</v>
+        <v>29.21590779509789</v>
       </c>
       <c r="T38" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -7365,19 +7435,19 @@
         <v>35</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E39" s="11">
         <v>377.7000122070312</v>
       </c>
       <c r="F39" s="20">
-        <v>0.3759805370315437</v>
+        <v>0.3760079950482088</v>
       </c>
       <c r="G39" s="13">
         <v>-0.6206010111104859</v>
@@ -7389,16 +7459,16 @@
         <v>0.807718544723493</v>
       </c>
       <c r="J39" s="13">
-        <v>1.138302255601297</v>
+        <v>1.138330405196894</v>
       </c>
       <c r="K39" s="13">
         <v>0.6745570835397064</v>
       </c>
       <c r="L39" s="13">
-        <v>-0.3090719046865988</v>
+        <v>-0.3090920034094998</v>
       </c>
       <c r="M39" s="13">
-        <v>-0.5223257359287339</v>
+        <v>-0.5220729976617323</v>
       </c>
       <c r="N39" s="13">
         <v>51.792965</v>
@@ -7416,10 +7486,10 @@
         <v>0.1407086131999338</v>
       </c>
       <c r="S39" s="12">
-        <v>62.5328796857528</v>
+        <v>62.53287968575284</v>
       </c>
       <c r="T39" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -7427,19 +7497,19 @@
         <v>36</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E40" s="11">
         <v>473.489990234375</v>
       </c>
       <c r="F40" s="20">
-        <v>0.3585554265328762</v>
+        <v>0.3585806010535155</v>
       </c>
       <c r="G40" s="13">
         <v>-0.3132621056075221</v>
@@ -7451,16 +7521,16 @@
         <v>-0.318020136024011</v>
       </c>
       <c r="J40" s="13">
-        <v>1.192597215437437</v>
+        <v>1.192613053882506</v>
       </c>
       <c r="K40" s="13">
         <v>0.3737829234962159</v>
       </c>
       <c r="L40" s="13">
-        <v>-0.08184634453511662</v>
+        <v>-0.08186802194469514</v>
       </c>
       <c r="M40" s="13">
-        <v>-0.5970893971102791</v>
+        <v>-0.5968178517141163</v>
       </c>
       <c r="N40" s="13">
         <v>38.233463</v>
@@ -7478,10 +7548,10 @@
         <v>0.5885194034948549</v>
       </c>
       <c r="S40" s="12">
-        <v>65.80478696021379</v>
+        <v>65.80478696021385</v>
       </c>
       <c r="T40" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -7489,19 +7559,19 @@
         <v>37</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E41" s="11">
         <v>433.5</v>
       </c>
       <c r="F41" s="20">
-        <v>0.3560845270345497</v>
+        <v>0.3561196072079962</v>
       </c>
       <c r="G41" s="13">
         <v>0.2970607495888827</v>
@@ -7513,16 +7583,16 @@
         <v>0.1591049640981598</v>
       </c>
       <c r="J41" s="13">
-        <v>1.65569471359508</v>
+        <v>1.655703558536159</v>
       </c>
       <c r="K41" s="13">
         <v>-0.1492544945205892</v>
       </c>
       <c r="L41" s="13">
-        <v>-0.3900369463308139</v>
+        <v>-0.3900564825358691</v>
       </c>
       <c r="M41" s="13">
-        <v>0.0005697543448602849</v>
+        <v>0.0009897401376892656</v>
       </c>
       <c r="N41" s="13">
         <v>40.81947</v>
@@ -7540,10 +7610,10 @@
         <v>1.192013146281626</v>
       </c>
       <c r="S41" s="12">
-        <v>66.65373747213368</v>
+        <v>66.65373747216645</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -7551,19 +7621,19 @@
         <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E42" s="11">
         <v>238.8600006103516</v>
       </c>
       <c r="F42" s="20">
-        <v>0.347330122095405</v>
+        <v>0.3473601259576903</v>
       </c>
       <c r="G42" s="13">
         <v>-0.05761153498665986</v>
@@ -7575,16 +7645,16 @@
         <v>-0.2889821613467594</v>
       </c>
       <c r="J42" s="13">
-        <v>0.4789218752297259</v>
+        <v>0.4789441544119799</v>
       </c>
       <c r="K42" s="13">
         <v>1.458560316888363</v>
       </c>
       <c r="L42" s="13">
-        <v>0.4343585058363938</v>
+        <v>0.434333242009338</v>
       </c>
       <c r="M42" s="13">
-        <v>-0.01903157503579672</v>
+        <v>-0.0187211258203917</v>
       </c>
       <c r="N42" s="13">
         <v>24.797949</v>
@@ -7602,10 +7672,10 @@
         <v>0.2433466079890823</v>
       </c>
       <c r="S42" s="12">
-        <v>57.16584925015388</v>
+        <v>57.1658492505596</v>
       </c>
       <c r="T42" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -7613,19 +7683,19 @@
         <v>39</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E43" s="11">
         <v>295.8500061035156</v>
       </c>
       <c r="F43" s="20">
-        <v>0.3385871286651107</v>
+        <v>0.3386021939481863</v>
       </c>
       <c r="G43" s="13">
         <v>-0.6750434006171774</v>
@@ -7637,16 +7707,16 @@
         <v>-0.01179628325654914</v>
       </c>
       <c r="J43" s="13">
-        <v>1.728642713571406</v>
+        <v>1.728632051179333</v>
       </c>
       <c r="K43" s="13">
         <v>-0.3162283848388505</v>
       </c>
       <c r="L43" s="13">
-        <v>-0.8834670463414569</v>
+        <v>-0.8834831543603313</v>
       </c>
       <c r="M43" s="13">
-        <v>-0.8828360364772404</v>
+        <v>-0.8825956554543628</v>
       </c>
       <c r="N43" s="13">
         <v>48.545902</v>
@@ -7664,10 +7734,10 @@
         <v>0.8671505951505651</v>
       </c>
       <c r="S43" s="12">
-        <v>68.99665210559198</v>
+        <v>68.99665210559164</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -7675,19 +7745,19 @@
         <v>40</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E44" s="11">
         <v>29.3799991607666</v>
       </c>
       <c r="F44" s="20">
-        <v>0.3384104561867246</v>
+        <v>0.3384334006939357</v>
       </c>
       <c r="G44" s="13">
         <v>0.4636006651738224</v>
@@ -7699,16 +7769,16 @@
         <v>-0.682866398151852</v>
       </c>
       <c r="J44" s="13">
-        <v>0.3032441061962322</v>
+        <v>0.3032675745021816</v>
       </c>
       <c r="K44" s="13">
         <v>2.197779162436428</v>
       </c>
       <c r="L44" s="13">
-        <v>0.5475953097490143</v>
+        <v>0.5475692591907755</v>
       </c>
       <c r="M44" s="13">
-        <v>-0.2307952248757424</v>
+        <v>-0.2305768867642359</v>
       </c>
       <c r="N44" s="13">
         <v>28.271847</v>
@@ -7726,10 +7796,10 @@
         <v>0.1819909676981719</v>
       </c>
       <c r="S44" s="12">
-        <v>53.29358553864772</v>
+        <v>53.29358553864782</v>
       </c>
       <c r="T44" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -7795,110 +7865,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B6" s="15">
         <v>0.18</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B7" s="15">
         <v>0.16</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B8" s="15">
         <v>0.1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B9" s="15">
         <v>0.3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B10" s="15">
         <v>0.12</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B11" s="15">
         <v>0.06</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B12" s="15">
         <v>0.08</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B13" s="15">
         <f>SUM(B6:B12)</f>
@@ -7907,22 +7977,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -8001,171 +8071,171 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="10" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B23" s="26"/>
     </row>
     <row r="24" spans="1:2" ht="32" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B24" s="26"/>
     </row>
     <row r="25" spans="1:2" ht="32" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B25" s="26"/>
     </row>
     <row r="26" spans="1:2" ht="32" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B26" s="26"/>
     </row>
     <row r="27" spans="1:2" ht="32" customHeight="1">
       <c r="A27" s="26" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B27" s="26"/>
     </row>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="264">
   <si>
     <t>SNDK</t>
   </si>
@@ -379,6 +379,9 @@
     <t>2026-10-14</t>
   </si>
   <si>
+    <t>2026-10-15</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -436,22 +439,58 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>NTAP</t>
+  </si>
+  <si>
+    <t>NetApp</t>
+  </si>
+  <si>
+    <t>Micron Technology</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
     <t>Dell Technologies</t>
   </si>
   <si>
-    <t>NTAP</t>
-  </si>
-  <si>
-    <t>NetApp</t>
-  </si>
-  <si>
-    <t>Micron Technology</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
+    <t>CVX</t>
+  </si>
+  <si>
+    <t>Chevron Corporation</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
+    <t>COP</t>
+  </si>
+  <si>
+    <t>ConocoPhillips</t>
+  </si>
+  <si>
+    <t>EOG</t>
+  </si>
+  <si>
+    <t>EOG Resources</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
   </si>
   <si>
     <t>TWLO</t>
@@ -460,40 +499,10 @@
     <t>Twilio</t>
   </si>
   <si>
-    <t>CVX</t>
-  </si>
-  <si>
-    <t>Chevron Corporation</t>
-  </si>
-  <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
-  </si>
-  <si>
-    <t>COP</t>
-  </si>
-  <si>
-    <t>ConocoPhillips</t>
-  </si>
-  <si>
-    <t>EOG</t>
-  </si>
-  <si>
-    <t>EOG Resources</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>Lilly (Eli)</t>
   </si>
   <si>
     <t>SMCI</t>
@@ -502,12 +511,6 @@
     <t>Supermicro</t>
   </si>
   <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>Lilly (Eli)</t>
-  </si>
-  <si>
     <t>WBD</t>
   </si>
   <si>
@@ -517,36 +520,30 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>XOM</t>
+  </si>
+  <si>
+    <t>ExxonMobil</t>
+  </si>
+  <si>
+    <t>DVN</t>
+  </si>
+  <si>
+    <t>Devon Energy</t>
+  </si>
+  <si>
+    <t>HUM</t>
+  </si>
+  <si>
+    <t>Humana</t>
+  </si>
+  <si>
     <t>VEEV</t>
   </si>
   <si>
     <t>Veeva Systems</t>
   </si>
   <si>
-    <t>XOM</t>
-  </si>
-  <si>
-    <t>ExxonMobil</t>
-  </si>
-  <si>
-    <t>DVN</t>
-  </si>
-  <si>
-    <t>Devon Energy</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>News Corp (Class A)</t>
-  </si>
-  <si>
     <t>MA</t>
   </si>
   <si>
@@ -559,6 +556,12 @@
     <t>Altria</t>
   </si>
   <si>
+    <t>FANG</t>
+  </si>
+  <si>
+    <t>Diamondback Energy</t>
+  </si>
+  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -637,7 +640,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-10-15 00:36 UTC · данные на 2026-10-14 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-16 00:28 UTC · данные на 2026-10-15 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -721,7 +724,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-10-15 00:36 UTC</t>
+    <t>2026-10-16 00:28 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -745,13 +748,10 @@
     <t>Проверка Alpha Vantage</t>
   </si>
   <si>
-    <t>unverified</t>
-  </si>
-  <si>
     <t>Комментарий проверки</t>
   </si>
   <si>
-    <t>GLOBAL_QUOTE unavailable</t>
+    <t>price confirmed; OVERVIEW unavailable</t>
   </si>
   <si>
     <t>Запросов AV использовано</t>
@@ -1271,9 +1271,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$31</c:f>
+              <c:f>Капитал!$A$5:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1354,16 +1354,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>2026-10-14</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2026-10-15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$31</c:f>
+              <c:f>Капитал!$D$5:$D$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1443,6 +1446,9 @@
                   <c:v>10434.289999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>10495.47</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>10495.47</c:v>
                 </c:pt>
               </c:numCache>
@@ -1468,9 +1474,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$31</c:f>
+              <c:f>Капитал!$A$5:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1551,16 +1557,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>2026-10-14</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2026-10-15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$31</c:f>
+              <c:f>Капитал!$F$5:$F$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1641,6 +1650,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>10105.32</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1780,9 +1792,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$31</c:f>
+              <c:f>Капитал!$A$5:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1863,16 +1875,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>2026-10-14</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2026-10-15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$31</c:f>
+              <c:f>Капитал!$D$5:$D$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1952,6 +1967,9 @@
                   <c:v>10434.289999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
+                  <c:v>10495.47</c:v>
+                </c:pt>
+                <c:pt idx="27">
                   <c:v>10495.47</c:v>
                 </c:pt>
               </c:numCache>
@@ -1977,9 +1995,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$31</c:f>
+              <c:f>Капитал!$A$5:$A$32</c:f>
               <c:strCache>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -2060,16 +2078,19 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>2026-10-14</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2026-10-15</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$31</c:f>
+              <c:f>Капитал!$F$5:$F$32</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="27"/>
+                <c:ptCount val="28"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -2150,6 +2171,9 @@
                 </c:pt>
                 <c:pt idx="26">
                   <c:v>10105.32</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2644,12 +2668,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2657,13 +2681,13 @@
         <v>102</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2682,21 +2706,21 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>5.290293206657666</v>
+        <v>5.180756315998459</v>
       </c>
       <c r="D9" s="7">
         <v>2</v>
@@ -2710,7 +2734,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2739,7 +2763,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C16" s="11">
         <v>10000</v>
@@ -2747,7 +2771,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C17" s="12">
         <v>21</v>
@@ -2755,7 +2779,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C18" s="12">
         <v>0</v>
@@ -2763,23 +2787,23 @@
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C19" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C21" s="13">
         <v>22</v>
@@ -2787,7 +2811,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="14">
         <v>0.210302</v>
@@ -2795,7 +2819,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C23" s="14">
         <v>0</v>
@@ -2803,31 +2827,31 @@
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C25" s="15">
-        <v>0.08942778785792493</v>
+        <v>0.08793639336079187</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="10" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C26" s="12">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="16" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" s="11">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2836,12 +2860,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -3036,7 +3060,7 @@
         <v>-0.040553020332949496</v>
       </c>
       <c r="L5" s="12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>43</v>
@@ -3089,7 +3113,7 @@
         <v>-0.21280961652164793</v>
       </c>
       <c r="L6" s="12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>43</v>
@@ -3142,7 +3166,7 @@
         <v>0.2766700980837115</v>
       </c>
       <c r="L7" s="12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>43</v>
@@ -3195,7 +3219,7 @@
         <v>0.2728545399606051</v>
       </c>
       <c r="L8" s="12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>43</v>
@@ -3248,7 +3272,7 @@
         <v>0.020946648866053245</v>
       </c>
       <c r="L9" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>43</v>
@@ -3301,7 +3325,7 @@
         <v>0.11736163397839519</v>
       </c>
       <c r="L10" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>43</v>
@@ -3354,7 +3378,7 @@
         <v>0.08393600265324602</v>
       </c>
       <c r="L11" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>43</v>
@@ -3407,7 +3431,7 @@
         <v>0.047100001233349814</v>
       </c>
       <c r="L12" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>43</v>
@@ -3460,7 +3484,7 @@
         <v>-0.014017790330537929</v>
       </c>
       <c r="L13" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>43</v>
@@ -3513,7 +3537,7 @@
         <v>0.02856195966946232</v>
       </c>
       <c r="L14" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>43</v>
@@ -3566,7 +3590,7 @@
         <v>0.04182047541522759</v>
       </c>
       <c r="L15" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>43</v>
@@ -3619,7 +3643,7 @@
         <v>0.01986011942148753</v>
       </c>
       <c r="L16" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M16" s="10" t="s">
         <v>43</v>
@@ -3672,7 +3696,7 @@
         <v>0.032237099772727276</v>
       </c>
       <c r="L17" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>43</v>
@@ -3725,7 +3749,7 @@
         <v>-0.008733283223140464</v>
       </c>
       <c r="L18" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>43</v>
@@ -3778,7 +3802,7 @@
         <v>-0.0952924704752066</v>
       </c>
       <c r="L19" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M19" s="10" t="s">
         <v>43</v>
@@ -3831,7 +3855,7 @@
         <v>0.00931226503894612</v>
       </c>
       <c r="L20" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M20" s="10" t="s">
         <v>43</v>
@@ -3884,7 +3908,7 @@
         <v>-0.005840516102513467</v>
       </c>
       <c r="L21" s="12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M21" s="10" t="s">
         <v>43</v>
@@ -3937,7 +3961,7 @@
         <v>0.07460630451465418</v>
       </c>
       <c r="L22" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M22" s="10" t="s">
         <v>43</v>
@@ -3990,7 +4014,7 @@
         <v>0.03644791326447835</v>
       </c>
       <c r="L23" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M23" s="10" t="s">
         <v>43</v>
@@ -4043,7 +4067,7 @@
         <v>-0.02193802573981816</v>
       </c>
       <c r="L24" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M24" s="10" t="s">
         <v>43</v>
@@ -4096,7 +4120,7 @@
         <v>-0.035074011517124914</v>
       </c>
       <c r="L25" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>43</v>
@@ -4687,7 +4711,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5275,6 +5299,25 @@
       <c r="F31" s="11">
         <v>10105.32</v>
       </c>
+    </row>
+    <row r="32" spans="1:6">
+      <c r="A32" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" s="11">
+        <v>159.91</v>
+      </c>
+      <c r="C32" s="11">
+        <v>10335.56</v>
+      </c>
+      <c r="D32" s="11">
+        <f>B32+C32</f>
+        <v>10495.47</v>
+      </c>
+      <c r="E32" s="12">
+        <v>21</v>
+      </c>
+      <c r="F32" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5303,12 +5346,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5325,52 +5368,52 @@
         <v>25</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="S4" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -5390,7 +5433,7 @@
         <v>484.9200134277344</v>
       </c>
       <c r="F5" s="20">
-        <v>1.137069287147647</v>
+        <v>1.143604366996855</v>
       </c>
       <c r="G5" s="13">
         <v>0.5120832578157225</v>
@@ -5402,16 +5445,16 @@
         <v>2.358223271893585</v>
       </c>
       <c r="J5" s="13">
-        <v>2.762897055033057</v>
+        <v>2.785637453087448</v>
       </c>
       <c r="K5" s="13">
-        <v>0.8456909715515779</v>
+        <v>0.8322577472718413</v>
       </c>
       <c r="L5" s="13">
-        <v>-0.1329713480481546</v>
+        <v>-0.1279325713710688</v>
       </c>
       <c r="M5" s="13">
-        <v>-0.2728376524299093</v>
+        <v>-0.2600548931069835</v>
       </c>
       <c r="N5" s="13">
         <v>15.755887</v>
@@ -5429,10 +5472,10 @@
         <v>1.188510822240728</v>
       </c>
       <c r="S5" s="12">
-        <v>80.00121277065431</v>
+        <v>80.00121278466597</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -5452,7 +5495,7 @@
         <v>459.7799987792969</v>
       </c>
       <c r="F6" s="20">
-        <v>1.128804213485436</v>
+        <v>1.134211724033697</v>
       </c>
       <c r="G6" s="13">
         <v>0.5257662583602529</v>
@@ -5464,16 +5507,16 @@
         <v>2.788833462425317</v>
       </c>
       <c r="J6" s="13">
-        <v>2.738531587657905</v>
+        <v>2.755020669378902</v>
       </c>
       <c r="K6" s="13">
-        <v>0.6699501589677099</v>
+        <v>0.6587310680489812</v>
       </c>
       <c r="L6" s="13">
-        <v>0.02338870261419407</v>
+        <v>0.02707969585094485</v>
       </c>
       <c r="M6" s="13">
-        <v>-0.4917044433757058</v>
+        <v>-0.4718842265256571</v>
       </c>
       <c r="N6" s="13">
         <v>18.08045</v>
@@ -5488,13 +5531,13 @@
         <v>0.517</v>
       </c>
       <c r="R6" s="15">
-        <v>0.973403322063314</v>
+        <v>0.9734034513047376</v>
       </c>
       <c r="S6" s="12">
-        <v>76.52079183778889</v>
+        <v>76.52079183018837</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -5511,10 +5554,10 @@
         <v>48</v>
       </c>
       <c r="E7" s="11">
-        <v>292.7300109863281</v>
+        <v>297.2900085449219</v>
       </c>
       <c r="F7" s="20">
-        <v>0.9898014269092068</v>
+        <v>1.008427519545958</v>
       </c>
       <c r="G7" s="13">
         <v>0.4033582074212857</v>
@@ -5526,16 +5569,16 @@
         <v>2.328125318139155</v>
       </c>
       <c r="J7" s="13">
-        <v>2.504605882745575</v>
+        <v>2.525506257180785</v>
       </c>
       <c r="K7" s="13">
-        <v>0.7572781553442616</v>
+        <v>0.7449588314899703</v>
       </c>
       <c r="L7" s="13">
-        <v>0.3485827993420503</v>
+        <v>0.3505139366089186</v>
       </c>
       <c r="M7" s="13">
-        <v>-0.6610835910882649</v>
+        <v>-0.4896032044296331</v>
       </c>
       <c r="N7" s="13">
         <v>15.896</v>
@@ -5550,13 +5593,13 @@
         <v>0.531</v>
       </c>
       <c r="R7" s="15">
-        <v>0.8670962284262103</v>
+        <v>0.8647031541042864</v>
       </c>
       <c r="S7" s="12">
-        <v>77.23505216070144</v>
+        <v>79.03573507405349</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5576,7 +5619,7 @@
         <v>70.16000366210938</v>
       </c>
       <c r="F8" s="20">
-        <v>0.8837035548309201</v>
+        <v>0.8974445030180477</v>
       </c>
       <c r="G8" s="13">
         <v>1.255811942784209</v>
@@ -5588,16 +5631,16 @@
         <v>-0.5870526183679002</v>
       </c>
       <c r="J8" s="13">
-        <v>1.502528733831972</v>
+        <v>1.558174597985955</v>
       </c>
       <c r="K8" s="13">
-        <v>4.044575143915362</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L8" s="13">
-        <v>0.01184934511840388</v>
+        <v>0.01563980465027959</v>
       </c>
       <c r="M8" s="13">
-        <v>-0.01943053191756738</v>
+        <v>-0.04799092386195003</v>
       </c>
       <c r="N8" s="13">
         <v>12.221939</v>
@@ -5615,10 +5658,10 @@
         <v>0.8659576199291157</v>
       </c>
       <c r="S8" s="12">
-        <v>68.08093597350663</v>
+        <v>68.08093597350666</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5626,61 +5669,61 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E9" s="11">
-        <v>68.80999755859375</v>
+        <v>377.8200073242188</v>
       </c>
       <c r="F9" s="20">
-        <v>0.880701318879478</v>
+        <v>0.8818249596899992</v>
       </c>
       <c r="G9" s="13">
-        <v>0.2210528163067884</v>
+        <v>1.187286552445482</v>
       </c>
       <c r="H9" s="13">
-        <v>-0.5344576345348465</v>
+        <v>-0.1198805307813126</v>
       </c>
       <c r="I9" s="13">
-        <v>2.11370107259597</v>
+        <v>-0.3892490054509348</v>
       </c>
       <c r="J9" s="13">
-        <v>2.699358535192657</v>
+        <v>0.7371472278044641</v>
       </c>
       <c r="K9" s="13">
-        <v>0.3754215749151163</v>
+        <v>3.994299457555074</v>
       </c>
       <c r="L9" s="13">
-        <v>-1.944566610942048</v>
+        <v>0.9926924723957937</v>
       </c>
       <c r="M9" s="13">
-        <v>-0.2891153335106698</v>
+        <v>-0.4225310733972489</v>
       </c>
       <c r="N9" s="13">
-        <v>37.86598</v>
+        <v>9.904647000000001</v>
       </c>
       <c r="O9" s="13">
-        <v>3.6796231</v>
+        <v>2.3224251</v>
       </c>
       <c r="P9" s="15">
-        <v>0.10936</v>
+        <v>0.26511</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.337</v>
+        <v>0.003</v>
       </c>
       <c r="R9" s="15">
-        <v>1.827375218148993</v>
+        <v>0.2718294193672723</v>
       </c>
       <c r="S9" s="12">
-        <v>59.56407878444165</v>
+        <v>63.94899117709577</v>
       </c>
       <c r="T9" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5688,61 +5731,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>8</v>
+        <v>137</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E10" s="11">
-        <v>377.8200073242188</v>
+        <v>222.1999969482422</v>
       </c>
       <c r="F10" s="20">
-        <v>0.8779142040493122</v>
+        <v>0.8487173035719388</v>
       </c>
       <c r="G10" s="13">
-        <v>1.187286552445482</v>
+        <v>-0.6400146282615523</v>
       </c>
       <c r="H10" s="13">
-        <v>-0.1198805307813126</v>
+        <v>1.366445373608231</v>
       </c>
       <c r="I10" s="13">
-        <v>-0.3892490054509348</v>
+        <v>0.4239293519712278</v>
       </c>
       <c r="J10" s="13">
-        <v>0.7005368444243097</v>
+        <v>2.227392860297685</v>
       </c>
       <c r="K10" s="13">
-        <v>4.044575143915362</v>
+        <v>0.535548548847568</v>
       </c>
       <c r="L10" s="13">
-        <v>0.9973971818561659</v>
+        <v>-0.432215872556926</v>
       </c>
       <c r="M10" s="13">
-        <v>-0.4130686428659688</v>
+        <v>-0.04568737391274738</v>
       </c>
       <c r="N10" s="13">
-        <v>9.904647000000001</v>
+        <v>33.448517</v>
       </c>
       <c r="O10" s="13">
-        <v>2.3224251</v>
+        <v>31.089407</v>
       </c>
       <c r="P10" s="15">
-        <v>0.26511</v>
+        <v>1.14818</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.003</v>
+        <v>0.299</v>
       </c>
       <c r="R10" s="15">
-        <v>0.2718294193672723</v>
+        <v>1.226428808465815</v>
       </c>
       <c r="S10" s="12">
-        <v>63.94899117685328</v>
+        <v>57.00448767884139</v>
       </c>
       <c r="T10" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5750,61 +5793,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>94</v>
+        <v>11</v>
       </c>
       <c r="C11" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="11">
+        <v>347.6400146484375</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0.8335946736879928</v>
+      </c>
+      <c r="G11" s="13">
+        <v>-0.3285343560247656</v>
+      </c>
+      <c r="H11" s="13">
+        <v>1.459641297606501</v>
+      </c>
+      <c r="I11" s="13">
+        <v>1.329512425464752</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0.1234071019879688</v>
+      </c>
+      <c r="K11" s="13">
+        <v>4.037113416620117</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0.1382840507197841</v>
+      </c>
+      <c r="M11" s="13">
+        <v>-0.04419720031320588</v>
+      </c>
+      <c r="N11" s="13">
+        <v>17.644756</v>
+      </c>
+      <c r="O11" s="13">
+        <v>6.909384</v>
+      </c>
+      <c r="P11" s="15">
+        <v>0.48676</v>
+      </c>
+      <c r="Q11" s="15">
+        <v>0.242</v>
+      </c>
+      <c r="R11" s="15">
+        <v>0.03248472636154864</v>
+      </c>
+      <c r="S11" s="12">
+        <v>51.27427440341948</v>
+      </c>
+      <c r="T11" s="10" t="s">
         <v>136</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="11">
-        <v>572.469970703125</v>
-      </c>
-      <c r="F11" s="20">
-        <v>0.8439177225573126</v>
-      </c>
-      <c r="G11" s="13">
-        <v>-0.1075886523285822</v>
-      </c>
-      <c r="H11" s="13">
-        <v>-0.8447423148789104</v>
-      </c>
-      <c r="I11" s="13">
-        <v>2.119917693224531</v>
-      </c>
-      <c r="J11" s="13">
-        <v>2.661087470585215</v>
-      </c>
-      <c r="K11" s="13">
-        <v>1.716801295655566</v>
-      </c>
-      <c r="L11" s="13">
-        <v>-2.808354765764111</v>
-      </c>
-      <c r="M11" s="13">
-        <v>-0.6173803709219485</v>
-      </c>
-      <c r="N11" s="13">
-        <v>33.41277</v>
-      </c>
-      <c r="O11" s="13">
-        <v>-262.80716</v>
-      </c>
-      <c r="P11" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="15">
-        <v>0.577</v>
-      </c>
-      <c r="R11" s="15">
-        <v>2.117393305780042</v>
-      </c>
-      <c r="S11" s="12">
-        <v>57.44466942747432</v>
-      </c>
-      <c r="T11" s="10" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5812,61 +5855,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>137</v>
+        <v>4</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>138</v>
+        <v>52</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E12" s="11">
-        <v>222.1999969482422</v>
+        <v>61.40999984741211</v>
       </c>
       <c r="F12" s="20">
-        <v>0.8332002236473779</v>
+        <v>0.8303882255887448</v>
       </c>
       <c r="G12" s="13">
-        <v>-0.6400146282615523</v>
+        <v>0.5555932315613028</v>
       </c>
       <c r="H12" s="13">
-        <v>1.366445373608231</v>
+        <v>0.615262828357206</v>
       </c>
       <c r="I12" s="13">
-        <v>0.4239293519712278</v>
+        <v>3.077929577016555</v>
       </c>
       <c r="J12" s="13">
-        <v>2.170467938072191</v>
+        <v>0.6897836443150713</v>
       </c>
       <c r="K12" s="13">
-        <v>0.5451958784297789</v>
+        <v>0.9345527958260584</v>
       </c>
       <c r="L12" s="13">
-        <v>-0.4399002978775566</v>
+        <v>0.1327018018753043</v>
       </c>
       <c r="M12" s="13">
-        <v>-0.03489009000699678</v>
+        <v>-0.03621379046581302</v>
       </c>
       <c r="N12" s="13">
-        <v>33.448517</v>
+        <v>17.076704</v>
       </c>
       <c r="O12" s="13">
-        <v>31.089407</v>
+        <v>1.7959902</v>
       </c>
       <c r="P12" s="15">
-        <v>1.14818</v>
+        <v>0.10629</v>
       </c>
       <c r="Q12" s="15">
-        <v>0.299</v>
+        <v>0.534</v>
       </c>
       <c r="R12" s="15">
-        <v>1.226428808465815</v>
+        <v>0.1100974115596502</v>
       </c>
       <c r="S12" s="12">
-        <v>57.00448766666207</v>
+        <v>61.82698456128156</v>
       </c>
       <c r="T12" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -5874,61 +5917,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E13" s="11">
-        <v>347.6400146484375</v>
+        <v>914.1300048828125</v>
       </c>
       <c r="F13" s="20">
-        <v>0.8263717859910835</v>
+        <v>0.8227437804748921</v>
       </c>
       <c r="G13" s="13">
-        <v>-0.3285343560247656</v>
+        <v>-0.1172294581697382</v>
       </c>
       <c r="H13" s="13">
-        <v>1.459641297606501</v>
+        <v>2.151002143997514</v>
       </c>
       <c r="I13" s="13">
-        <v>1.329512425464752</v>
+        <v>4.12785569855674</v>
       </c>
       <c r="J13" s="13">
-        <v>0.09645953826214881</v>
+        <v>1.169969808953976</v>
       </c>
       <c r="K13" s="13">
-        <v>4.044575143915362</v>
+        <v>-0.3486877085504021</v>
       </c>
       <c r="L13" s="13">
-        <v>0.1355599447537723</v>
+        <v>-2.422008617716169</v>
       </c>
       <c r="M13" s="13">
-        <v>-0.0425794440211075</v>
+        <v>-0.9616091318375725</v>
       </c>
       <c r="N13" s="13">
-        <v>17.644756</v>
+        <v>13.84367</v>
       </c>
       <c r="O13" s="13">
-        <v>6.909384</v>
+        <v>11.533936</v>
       </c>
       <c r="P13" s="15">
-        <v>0.48676</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="Q13" s="15">
-        <v>0.242</v>
+        <v>3.793</v>
       </c>
       <c r="R13" s="15">
-        <v>0.03248472636154864</v>
+        <v>1.004283947628566</v>
       </c>
       <c r="S13" s="12">
-        <v>51.27427440347203</v>
+        <v>36.26124679880706</v>
       </c>
       <c r="T13" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -5936,61 +5979,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E14" s="11">
-        <v>61.40999984741211</v>
+        <v>63.11000061035156</v>
       </c>
       <c r="F14" s="20">
-        <v>0.8226575260308396</v>
+        <v>0.7417345846425372</v>
       </c>
       <c r="G14" s="13">
-        <v>0.5555932315613028</v>
+        <v>0.2210528163067884</v>
       </c>
       <c r="H14" s="13">
-        <v>0.615262828357206</v>
+        <v>-0.5344576345348465</v>
       </c>
       <c r="I14" s="13">
-        <v>3.077929577016555</v>
+        <v>2.11370107259597</v>
       </c>
       <c r="J14" s="13">
-        <v>0.6536393619034754</v>
+        <v>2.330621670522358</v>
       </c>
       <c r="K14" s="13">
-        <v>0.9492912653895988</v>
+        <v>0.3679132074995579</v>
       </c>
       <c r="L14" s="13">
-        <v>0.1299291599921857</v>
+        <v>-2.06572026997574</v>
       </c>
       <c r="M14" s="13">
-        <v>-0.01733469882911143</v>
+        <v>-0.5413084735602033</v>
       </c>
       <c r="N14" s="13">
-        <v>17.076704</v>
+        <v>37.86598</v>
       </c>
       <c r="O14" s="13">
-        <v>1.7959902</v>
+        <v>3.6796231</v>
       </c>
       <c r="P14" s="15">
-        <v>0.10629</v>
+        <v>0.10936</v>
       </c>
       <c r="Q14" s="15">
-        <v>0.534</v>
+        <v>0.337</v>
       </c>
       <c r="R14" s="15">
-        <v>0.1100974115596502</v>
+        <v>1.577365282101474</v>
       </c>
       <c r="S14" s="12">
-        <v>61.82698456085182</v>
+        <v>48.38639197874727</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -5998,61 +6041,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D15" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E15" s="11">
-        <v>914.1300048828125</v>
+        <v>235.9499969482422</v>
       </c>
       <c r="F15" s="20">
-        <v>0.816510827906392</v>
+        <v>0.7369781494044974</v>
       </c>
       <c r="G15" s="13">
-        <v>-0.1172294581697382</v>
+        <v>0.445387850826149</v>
       </c>
       <c r="H15" s="13">
-        <v>2.151002143997514</v>
+        <v>0.5371012848843359</v>
       </c>
       <c r="I15" s="13">
-        <v>4.12785569855674</v>
+        <v>0.1720715631623876</v>
       </c>
       <c r="J15" s="13">
-        <v>1.154478326382756</v>
+        <v>0.8444998961780219</v>
       </c>
       <c r="K15" s="13">
-        <v>-0.3503228918664129</v>
+        <v>3.685807583381099</v>
       </c>
       <c r="L15" s="13">
-        <v>-2.446993671946273</v>
+        <v>-1.780884631767303</v>
       </c>
       <c r="M15" s="13">
-        <v>-0.9602364136551541</v>
+        <v>-0.4391103324380299</v>
       </c>
       <c r="N15" s="13">
-        <v>13.84367</v>
+        <v>20.963404</v>
       </c>
       <c r="O15" s="13">
-        <v>11.533936</v>
+        <v>4.913579</v>
       </c>
       <c r="P15" s="15">
-        <v>0.8826000000000001</v>
+        <v>0.19381</v>
       </c>
       <c r="Q15" s="15">
-        <v>3.793</v>
+        <v>0.108</v>
       </c>
       <c r="R15" s="15">
-        <v>1.004283947628566</v>
+        <v>0.3343194829716822</v>
       </c>
       <c r="S15" s="12">
-        <v>36.2612467304262</v>
+        <v>53.6771808177494</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -6060,61 +6103,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D16" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E16" s="11">
-        <v>235.9499969482422</v>
+        <v>507.9299926757812</v>
       </c>
       <c r="F16" s="20">
-        <v>0.7292953543370435</v>
+        <v>0.6647884886059343</v>
       </c>
       <c r="G16" s="13">
-        <v>0.445387850826149</v>
+        <v>-0.1075886523285822</v>
       </c>
       <c r="H16" s="13">
-        <v>0.5371012848843359</v>
+        <v>-0.8447423148789104</v>
       </c>
       <c r="I16" s="13">
-        <v>0.1720715631623876</v>
+        <v>2.119917693224531</v>
       </c>
       <c r="J16" s="13">
-        <v>0.8048705658058123</v>
+        <v>2.115454346998049</v>
       </c>
       <c r="K16" s="13">
-        <v>3.735651000708519</v>
+        <v>1.69239307699997</v>
       </c>
       <c r="L16" s="13">
-        <v>-1.800295312388473</v>
+        <v>-2.949498962581992</v>
       </c>
       <c r="M16" s="13">
-        <v>-0.4467423974106675</v>
+        <v>-0.6679011062654987</v>
       </c>
       <c r="N16" s="13">
-        <v>20.963404</v>
+        <v>33.41277</v>
       </c>
       <c r="O16" s="13">
-        <v>4.913579</v>
+        <v>-262.80716</v>
       </c>
       <c r="P16" s="15">
-        <v>0.19381</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="15">
-        <v>0.108</v>
+        <v>0.577</v>
       </c>
       <c r="R16" s="15">
-        <v>0.3343194829716822</v>
+        <v>1.878742764702428</v>
       </c>
       <c r="S16" s="12">
-        <v>53.67718082266041</v>
+        <v>41.92176235596323</v>
       </c>
       <c r="T16" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -6122,61 +6165,61 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E17" s="11">
-        <v>155.3099975585938</v>
+        <v>47.36999893188477</v>
       </c>
       <c r="F17" s="20">
-        <v>0.6359270654675769</v>
+        <v>0.6481137457849795</v>
       </c>
       <c r="G17" s="13">
-        <v>0.4755572880593366</v>
+        <v>0.9861002278279252</v>
       </c>
       <c r="H17" s="13">
-        <v>-0.5579052235604326</v>
+        <v>0.5612515707924636</v>
       </c>
       <c r="I17" s="13">
-        <v>-0.05791369034948607</v>
+        <v>-0.2947421241753646</v>
       </c>
       <c r="J17" s="13">
-        <v>0.7563326414799662</v>
+        <v>1.738567162804421</v>
       </c>
       <c r="K17" s="13">
-        <v>3.489939309040333</v>
+        <v>-0.5639893290676546</v>
       </c>
       <c r="L17" s="13">
-        <v>0.414309937651701</v>
+        <v>-0.5154522265252964</v>
       </c>
       <c r="M17" s="13">
-        <v>-0.3146018420802212</v>
+        <v>-0.158432873687435</v>
       </c>
       <c r="N17" s="13">
-        <v>15.954309</v>
+        <v>9.699789000000001</v>
       </c>
       <c r="O17" s="13">
-        <v>3.911704</v>
+        <v>2.2914796</v>
       </c>
       <c r="P17" s="15">
-        <v>0.26408002</v>
+        <v>0.26659</v>
       </c>
       <c r="Q17" s="15">
-        <v>0.053</v>
+        <v>0.092</v>
       </c>
       <c r="R17" s="15">
-        <v>0.285755006502739</v>
+        <v>0.3120957736347147</v>
       </c>
       <c r="S17" s="12">
-        <v>49.77755513641856</v>
+        <v>64.70245176621867</v>
       </c>
       <c r="T17" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -6184,61 +6227,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E18" s="11">
-        <v>232.8300018310547</v>
+        <v>155.3099975585938</v>
       </c>
       <c r="F18" s="20">
-        <v>0.6346585487926786</v>
+        <v>0.6417892365552625</v>
       </c>
       <c r="G18" s="13">
-        <v>0.1972144638373766</v>
+        <v>0.4755572880593366</v>
       </c>
       <c r="H18" s="13">
-        <v>0.0272457680026615</v>
+        <v>-0.5579052235604326</v>
       </c>
       <c r="I18" s="13">
-        <v>-0.878827185566031</v>
+        <v>-0.05791369034948607</v>
       </c>
       <c r="J18" s="13">
-        <v>0.8940266411106603</v>
+        <v>0.7919848434204225</v>
       </c>
       <c r="K18" s="13">
-        <v>3.574012845924591</v>
+        <v>3.44319157817136</v>
       </c>
       <c r="L18" s="13">
-        <v>0.5497016585832664</v>
+        <v>0.4146312903387912</v>
       </c>
       <c r="M18" s="13">
-        <v>-0.5923536547627128</v>
+        <v>-0.3051398789727215</v>
       </c>
       <c r="N18" s="13">
-        <v>40.090588</v>
+        <v>15.954309</v>
       </c>
       <c r="O18" s="13">
-        <v>1.7687485</v>
+        <v>3.911704</v>
       </c>
       <c r="P18" s="15">
-        <v>0.04575</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q18" s="15">
-        <v>0.034</v>
+        <v>0.053</v>
       </c>
       <c r="R18" s="15">
-        <v>0.2896311647804755</v>
+        <v>0.285755006502739</v>
       </c>
       <c r="S18" s="12">
-        <v>63.69891901044485</v>
+        <v>49.77755513642406</v>
       </c>
       <c r="T18" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -6246,61 +6289,61 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E19" s="11">
-        <v>47.36999893188477</v>
+        <v>232.8300018310547</v>
       </c>
       <c r="F19" s="20">
-        <v>0.63220720557369</v>
+        <v>0.6410855620214339</v>
       </c>
       <c r="G19" s="13">
-        <v>0.9861002278279252</v>
+        <v>0.1972144638373766</v>
       </c>
       <c r="H19" s="13">
-        <v>0.5612515707924636</v>
+        <v>0.0272457680026615</v>
       </c>
       <c r="I19" s="13">
-        <v>-0.2947421241753646</v>
+        <v>-0.878827185566031</v>
       </c>
       <c r="J19" s="13">
-        <v>1.683793290209685</v>
+        <v>0.9356240407770618</v>
       </c>
       <c r="K19" s="13">
-        <v>-0.568371677850101</v>
+        <v>3.526205884589703</v>
       </c>
       <c r="L19" s="13">
-        <v>-0.5238603660494731</v>
+        <v>0.5488559694418522</v>
       </c>
       <c r="M19" s="13">
-        <v>-0.1389829762814919</v>
+        <v>-0.595661529293887</v>
       </c>
       <c r="N19" s="13">
-        <v>9.699789000000001</v>
+        <v>40.090588</v>
       </c>
       <c r="O19" s="13">
-        <v>2.2914796</v>
+        <v>1.7687485</v>
       </c>
       <c r="P19" s="15">
-        <v>0.26659</v>
+        <v>0.04575</v>
       </c>
       <c r="Q19" s="15">
-        <v>0.092</v>
+        <v>0.034</v>
       </c>
       <c r="R19" s="15">
-        <v>0.3120957736347147</v>
+        <v>0.2896311647804755</v>
       </c>
       <c r="S19" s="12">
-        <v>64.70245176599263</v>
+        <v>63.69891901044474</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -6320,7 +6363,7 @@
         <v>121.7600021362305</v>
       </c>
       <c r="F20" s="20">
-        <v>0.6150781333238232</v>
+        <v>0.6207711653919917</v>
       </c>
       <c r="G20" s="13">
         <v>0.3844623079993796</v>
@@ -6332,16 +6375,16 @@
         <v>0.4303409832118458</v>
       </c>
       <c r="J20" s="13">
-        <v>0.05774445246831652</v>
+        <v>0.0846708712803828</v>
       </c>
       <c r="K20" s="13">
-        <v>4.044575143915362</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L20" s="13">
-        <v>-0.01149619958408073</v>
+        <v>-0.007504507458442592</v>
       </c>
       <c r="M20" s="13">
-        <v>0.2557598168112371</v>
+        <v>0.234147468966735</v>
       </c>
       <c r="N20" s="13">
         <v>14.45067</v>
@@ -6359,10 +6402,10 @@
         <v>0.2016184736603308</v>
       </c>
       <c r="S20" s="12">
-        <v>57.94718888596616</v>
+        <v>57.94718888596617</v>
       </c>
       <c r="T20" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -6370,61 +6413,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="E21" s="11">
-        <v>1482.329956054688</v>
+        <v>254.0800018310547</v>
       </c>
       <c r="F21" s="20">
-        <v>0.594236097403286</v>
+        <v>0.5950055868451747</v>
       </c>
       <c r="G21" s="13">
-        <v>-0.3715766681671279</v>
+        <v>-0.02977335660029285</v>
       </c>
       <c r="H21" s="13">
-        <v>2.057050157474414</v>
+        <v>0.160055113268548</v>
       </c>
       <c r="I21" s="13">
-        <v>4.09736352358056</v>
+        <v>0.9707254877878508</v>
       </c>
       <c r="J21" s="13">
-        <v>0.5505882159170882</v>
+        <v>0.04440619398056514</v>
       </c>
       <c r="K21" s="13">
-        <v>0.1210313246008135</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L21" s="13">
-        <v>-2.893114900796578</v>
+        <v>-0.5380224524188785</v>
       </c>
       <c r="M21" s="13">
-        <v>-1.048222619500283</v>
+        <v>0.1523662886002977</v>
       </c>
       <c r="N21" s="13">
-        <v>21.445498</v>
+        <v>21.112629</v>
       </c>
       <c r="O21" s="13">
-        <v>14.977796</v>
+        <v>5.1299944</v>
       </c>
       <c r="P21" s="15">
-        <v>0.9164</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q21" s="15">
-        <v>3.716</v>
+        <v>0.196</v>
       </c>
       <c r="R21" s="15">
-        <v>0.5694999487205437</v>
+        <v>0.02245473573865064</v>
       </c>
       <c r="S21" s="12">
-        <v>38.30278467269132</v>
+        <v>49.33534011995932</v>
       </c>
       <c r="T21" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -6432,61 +6475,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E22" s="11">
-        <v>254.0800018310547</v>
+        <v>1403.339965820312</v>
       </c>
       <c r="F22" s="20">
-        <v>0.5887322555501705</v>
+        <v>0.558057235297111</v>
       </c>
       <c r="G22" s="13">
-        <v>-0.02977335660029285</v>
+        <v>-0.3715766681671279</v>
       </c>
       <c r="H22" s="13">
-        <v>0.160055113268548</v>
+        <v>2.057050157474414</v>
       </c>
       <c r="I22" s="13">
-        <v>0.9707254877878508</v>
+        <v>4.09736352358056</v>
       </c>
       <c r="J22" s="13">
-        <v>0.0208912173251452</v>
+        <v>0.3978093361686088</v>
       </c>
       <c r="K22" s="13">
-        <v>4.044575143915362</v>
+        <v>0.1167279835627633</v>
       </c>
       <c r="L22" s="13">
-        <v>-0.5466268330357708</v>
+        <v>-2.949498962581992</v>
       </c>
       <c r="M22" s="13">
-        <v>0.157391504390368</v>
+        <v>-0.8787945388745357</v>
       </c>
       <c r="N22" s="13">
-        <v>21.112629</v>
+        <v>21.445498</v>
       </c>
       <c r="O22" s="13">
-        <v>5.1299944</v>
+        <v>14.977796</v>
       </c>
       <c r="P22" s="15">
-        <v>0.30558002</v>
+        <v>0.9164</v>
       </c>
       <c r="Q22" s="15">
-        <v>0.196</v>
+        <v>3.716</v>
       </c>
       <c r="R22" s="15">
-        <v>0.02245473573865064</v>
+        <v>0.5737451351614038</v>
       </c>
       <c r="S22" s="12">
-        <v>49.33534011995933</v>
+        <v>34.34738914248405</v>
       </c>
       <c r="T22" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -6494,61 +6537,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E23" s="11">
-        <v>236.1699981689453</v>
+        <v>222.0399932861328</v>
       </c>
       <c r="F23" s="20">
-        <v>0.5451401842944362</v>
+        <v>0.5481076026540469</v>
       </c>
       <c r="G23" s="13">
-        <v>1.256899045882137</v>
+        <v>0.4630268796884387</v>
       </c>
       <c r="H23" s="13">
-        <v>0.1687273867194284</v>
+        <v>-0.3282907644621123</v>
       </c>
       <c r="I23" s="13">
-        <v>-0.06592248185956601</v>
+        <v>2.233294390227442</v>
       </c>
       <c r="J23" s="13">
-        <v>-0.03109008758434979</v>
+        <v>1.057651638229864</v>
       </c>
       <c r="K23" s="13">
-        <v>1.982039744277515</v>
+        <v>-0.144633187612409</v>
       </c>
       <c r="L23" s="13">
-        <v>0.4602894047106454</v>
+        <v>0.7341297764532626</v>
       </c>
       <c r="M23" s="13">
-        <v>0.5294889378233001</v>
+        <v>-0.625343099266802</v>
       </c>
       <c r="N23" s="13">
-        <v>4.590436</v>
+        <v>20.40231</v>
       </c>
       <c r="O23" s="13">
-        <v>1.838514</v>
+        <v>2.1898758</v>
       </c>
       <c r="P23" s="15">
-        <v>0.46113998</v>
+        <v>0.12231</v>
       </c>
       <c r="Q23" s="15">
-        <v>0.118</v>
+        <v>0.535</v>
       </c>
       <c r="R23" s="15">
-        <v>0.0924357250811636</v>
+        <v>0.2223742950496221</v>
       </c>
       <c r="S23" s="12">
-        <v>50.06648475223956</v>
+        <v>71.31825715055166</v>
       </c>
       <c r="T23" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -6556,61 +6599,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E24" s="11">
-        <v>281.5899963378906</v>
+        <v>236.1699981689453</v>
       </c>
       <c r="F24" s="20">
-        <v>0.5383161844918004</v>
+        <v>0.54688789690373</v>
       </c>
       <c r="G24" s="13">
-        <v>-0.8805891848256409</v>
+        <v>1.256899045882137</v>
       </c>
       <c r="H24" s="13">
-        <v>0.03652855326022123</v>
+        <v>0.1687273867194284</v>
       </c>
       <c r="I24" s="13">
-        <v>2.246420289880714</v>
+        <v>-0.06592248185956601</v>
       </c>
       <c r="J24" s="13">
-        <v>2.400080728518379</v>
+        <v>-0.009314915661564302</v>
       </c>
       <c r="K24" s="13">
-        <v>-0.02324971289088063</v>
+        <v>1.954289824345583</v>
       </c>
       <c r="L24" s="13">
-        <v>-2.669570420116886</v>
+        <v>0.4602144262118926</v>
       </c>
       <c r="M24" s="13">
-        <v>-1.134054844386073</v>
+        <v>0.5113595645009885</v>
       </c>
       <c r="N24" s="13">
-        <v>40.037346</v>
+        <v>4.590436</v>
       </c>
       <c r="O24" s="13">
-        <v>4.951591</v>
+        <v>1.838514</v>
       </c>
       <c r="P24" s="15">
-        <v>0.13497</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q24" s="15">
-        <v>0.22</v>
+        <v>0.118</v>
       </c>
       <c r="R24" s="15">
-        <v>1.270887067241053</v>
+        <v>0.09243564797535408</v>
       </c>
       <c r="S24" s="12">
-        <v>55.42219710924207</v>
+        <v>50.0664847517501</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -6618,61 +6661,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E25" s="11">
-        <v>222.0399932861328</v>
+        <v>184.0500030517578</v>
       </c>
       <c r="F25" s="20">
-        <v>0.5364713329740858</v>
+        <v>0.5300148814832472</v>
       </c>
       <c r="G25" s="13">
-        <v>0.4630268796884387</v>
+        <v>-2.114609254291167</v>
       </c>
       <c r="H25" s="13">
-        <v>-0.3282907644621123</v>
+        <v>1.770921230679228</v>
       </c>
       <c r="I25" s="13">
-        <v>2.233294390227442</v>
+        <v>0.220221171989416</v>
       </c>
       <c r="J25" s="13">
-        <v>1.014093784940011</v>
+        <v>2.050910296744923</v>
       </c>
       <c r="K25" s="13">
-        <v>-0.1436647141057532</v>
+        <v>0.4814553556330344</v>
       </c>
       <c r="L25" s="13">
-        <v>0.7365863637093412</v>
+        <v>-0.6502105175938252</v>
       </c>
       <c r="M25" s="13">
-        <v>-0.6107496711314129</v>
+        <v>-0.3595008436971591</v>
       </c>
       <c r="N25" s="13">
-        <v>20.40231</v>
+        <v>68.81625</v>
       </c>
       <c r="O25" s="13">
-        <v>2.1898758</v>
+        <v>92.12393</v>
       </c>
       <c r="P25" s="15">
-        <v>0.12231</v>
+        <v>1.17442</v>
       </c>
       <c r="Q25" s="15">
-        <v>0.535</v>
+        <v>0.256</v>
       </c>
       <c r="R25" s="15">
-        <v>0.2223741923669302</v>
+        <v>1.311024666779198</v>
       </c>
       <c r="S25" s="12">
-        <v>71.31825715496656</v>
+        <v>56.14718236618351</v>
       </c>
       <c r="T25" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -6680,61 +6723,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E26" s="11">
-        <v>184.0500030517578</v>
+        <v>376.8800048828125</v>
       </c>
       <c r="F26" s="20">
-        <v>0.5189228234076575</v>
+        <v>0.5230637675122519</v>
       </c>
       <c r="G26" s="13">
-        <v>-2.114609254291167</v>
+        <v>0.05829011904393756</v>
       </c>
       <c r="H26" s="13">
-        <v>1.770921230679228</v>
+        <v>-0.2386394236856432</v>
       </c>
       <c r="I26" s="13">
-        <v>0.220221171989416</v>
+        <v>0.4382083912057649</v>
       </c>
       <c r="J26" s="13">
-        <v>2.012538976092558</v>
+        <v>1.444707029718736</v>
       </c>
       <c r="K26" s="13">
-        <v>0.4904124769761658</v>
+        <v>1.797366006406391</v>
       </c>
       <c r="L26" s="13">
-        <v>-0.6597903385365431</v>
+        <v>-1.796953766701602</v>
       </c>
       <c r="M26" s="13">
-        <v>-0.3605099335033192</v>
+        <v>-0.4293223616102758</v>
       </c>
       <c r="N26" s="13">
-        <v>68.81625</v>
+        <v>35.48854</v>
       </c>
       <c r="O26" s="13">
-        <v>92.12393</v>
+        <v>5.341519</v>
       </c>
       <c r="P26" s="15">
-        <v>1.17442</v>
+        <v>0.15286</v>
       </c>
       <c r="Q26" s="15">
-        <v>0.256</v>
+        <v>0.204</v>
       </c>
       <c r="R26" s="15">
-        <v>1.311024666779198</v>
+        <v>0.6411775208348187</v>
       </c>
       <c r="S26" s="12">
-        <v>56.14718236618354</v>
+        <v>55.99241757454548</v>
       </c>
       <c r="T26" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -6742,61 +6785,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E27" s="11">
-        <v>376.8800048828125</v>
+        <v>142.3399963378906</v>
       </c>
       <c r="F27" s="20">
-        <v>0.5101348007888404</v>
+        <v>0.4948522192547213</v>
       </c>
       <c r="G27" s="13">
-        <v>0.05829011904393756</v>
+        <v>0.4503326028677878</v>
       </c>
       <c r="H27" s="13">
-        <v>-0.2386394236856432</v>
+        <v>-0.1381780449371671</v>
       </c>
       <c r="I27" s="13">
-        <v>0.4382083912057649</v>
+        <v>0.7716117421870532</v>
       </c>
       <c r="J27" s="13">
-        <v>1.396175629344713</v>
+        <v>1.225168296832862</v>
       </c>
       <c r="K27" s="13">
-        <v>1.823113639070499</v>
+        <v>-0.05144293395568774</v>
       </c>
       <c r="L27" s="13">
-        <v>-1.816504163452039</v>
+        <v>0.2882442862019671</v>
       </c>
       <c r="M27" s="13">
-        <v>-0.4329003456836654</v>
+        <v>-0.2491541304691666</v>
       </c>
       <c r="N27" s="13">
-        <v>35.48854</v>
+        <v>17.76159</v>
       </c>
       <c r="O27" s="13">
-        <v>5.341519</v>
+        <v>2.4652097</v>
       </c>
       <c r="P27" s="15">
-        <v>0.15286</v>
+        <v>0.1418</v>
       </c>
       <c r="Q27" s="15">
-        <v>0.204</v>
+        <v>0.355</v>
       </c>
       <c r="R27" s="15">
-        <v>0.6411775208348187</v>
+        <v>0.2138771476263022</v>
       </c>
       <c r="S27" s="12">
-        <v>55.99241757454562</v>
+        <v>71.29538722149405</v>
       </c>
       <c r="T27" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -6804,61 +6847,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D28" s="10" t="s">
         <v>48</v>
       </c>
       <c r="E28" s="11">
-        <v>142.3399963378906</v>
+        <v>154.1900024414062</v>
       </c>
       <c r="F28" s="20">
-        <v>0.4832800584621187</v>
+        <v>0.4912680759628336</v>
       </c>
       <c r="G28" s="13">
-        <v>0.4503326028677878</v>
+        <v>0.5258568789706033</v>
       </c>
       <c r="H28" s="13">
-        <v>-0.1381780449371671</v>
+        <v>0.4660864804691944</v>
       </c>
       <c r="I28" s="13">
-        <v>0.7716117421870532</v>
+        <v>1.396975994830035</v>
       </c>
       <c r="J28" s="13">
-        <v>1.178800937387167</v>
+        <v>0.8399506512951906</v>
       </c>
       <c r="K28" s="13">
-        <v>-0.04928538882923147</v>
+        <v>-0.5056115264895936</v>
       </c>
       <c r="L28" s="13">
-        <v>0.2868240378319618</v>
+        <v>0.1106169185921604</v>
       </c>
       <c r="M28" s="13">
-        <v>-0.2220996738675207</v>
+        <v>-0.1950803241910638</v>
       </c>
       <c r="N28" s="13">
-        <v>17.76159</v>
+        <v>11.529961</v>
       </c>
       <c r="O28" s="13">
-        <v>2.4652097</v>
+        <v>2.443433</v>
       </c>
       <c r="P28" s="15">
-        <v>0.1418</v>
+        <v>0.22507</v>
       </c>
       <c r="Q28" s="15">
-        <v>0.355</v>
+        <v>0.587</v>
       </c>
       <c r="R28" s="15">
-        <v>0.2138771476263022</v>
+        <v>0.1824185236671019</v>
       </c>
       <c r="S28" s="12">
-        <v>71.2953872215198</v>
+        <v>67.66312279253869</v>
       </c>
       <c r="T28" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -6866,61 +6909,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>152</v>
+        <v>16</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>153</v>
+        <v>73</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E29" s="11">
-        <v>154.1900024414062</v>
+        <v>271.760009765625</v>
       </c>
       <c r="F29" s="20">
-        <v>0.4807071296793239</v>
+        <v>0.4876514246202027</v>
       </c>
       <c r="G29" s="13">
-        <v>0.5258568789706033</v>
+        <v>-0.7248874185708422</v>
       </c>
       <c r="H29" s="13">
-        <v>0.4660864804691944</v>
+        <v>0.4430731040983454</v>
       </c>
       <c r="I29" s="13">
-        <v>1.396975994830035</v>
+        <v>-0.4530813424943169</v>
       </c>
       <c r="J29" s="13">
-        <v>0.8006618665795479</v>
+        <v>2.592394613188554</v>
       </c>
       <c r="K29" s="13">
-        <v>-0.5092489970734293</v>
+        <v>-0.2528195740414762</v>
       </c>
       <c r="L29" s="13">
-        <v>0.1076522555193374</v>
+        <v>-1.163536009350817</v>
       </c>
       <c r="M29" s="13">
-        <v>-0.1720795068709055</v>
+        <v>-1.062753461923618</v>
       </c>
       <c r="N29" s="13">
-        <v>11.529961</v>
+        <v>51.89739</v>
       </c>
       <c r="O29" s="13">
-        <v>2.443433</v>
+        <v>14.800214</v>
       </c>
       <c r="P29" s="15">
-        <v>0.22507</v>
+        <v>0.32339</v>
       </c>
       <c r="Q29" s="15">
-        <v>0.587</v>
+        <v>0.094</v>
       </c>
       <c r="R29" s="15">
-        <v>0.182418385308472</v>
+        <v>1.05474082150804</v>
       </c>
       <c r="S29" s="12">
-        <v>67.6631227940432</v>
+        <v>58.88132724219482</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -6928,61 +6971,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E30" s="11">
-        <v>271.760009765625</v>
+        <v>95.45999908447266</v>
       </c>
       <c r="F30" s="20">
-        <v>0.475490935170159</v>
+        <v>0.4627199685805627</v>
       </c>
       <c r="G30" s="13">
-        <v>-0.7248874185708422</v>
+        <v>0.09120761566025611</v>
       </c>
       <c r="H30" s="13">
-        <v>0.4430731040983454</v>
+        <v>1.652287474348924</v>
       </c>
       <c r="I30" s="13">
-        <v>-0.4530813424943169</v>
+        <v>0.0273109313630392</v>
       </c>
       <c r="J30" s="13">
-        <v>2.560158142110547</v>
+        <v>0.4720630108032512</v>
       </c>
       <c r="K30" s="13">
-        <v>-0.2532315170129796</v>
+        <v>0.06745497588219804</v>
       </c>
       <c r="L30" s="13">
-        <v>-1.177579035752629</v>
+        <v>0.6161377183359579</v>
       </c>
       <c r="M30" s="13">
-        <v>-1.082722629248023</v>
+        <v>-0.09345318396764679</v>
       </c>
       <c r="N30" s="13">
-        <v>51.89739</v>
+        <v>16.694096</v>
       </c>
       <c r="O30" s="13">
-        <v>14.800214</v>
+        <v>18.69391</v>
       </c>
       <c r="P30" s="15">
-        <v>0.32339</v>
+        <v>1.5956</v>
       </c>
       <c r="Q30" s="15">
-        <v>0.094</v>
+        <v>0.162</v>
       </c>
       <c r="R30" s="15">
-        <v>1.05474082150804</v>
+        <v>0.03230029322725958</v>
       </c>
       <c r="S30" s="12">
-        <v>58.88132724219485</v>
+        <v>64.58742501238767</v>
       </c>
       <c r="T30" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -6990,61 +7033,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E31" s="11">
-        <v>95.45999908447266</v>
+        <v>271.1199951171875</v>
       </c>
       <c r="F31" s="20">
-        <v>0.4552544264463766</v>
+        <v>0.4471372258957333</v>
       </c>
       <c r="G31" s="13">
-        <v>0.09120761566025611</v>
+        <v>-0.8805891848256409</v>
       </c>
       <c r="H31" s="13">
-        <v>1.652287474348924</v>
+        <v>0.03652855326022123</v>
       </c>
       <c r="I31" s="13">
-        <v>0.0273109313630392</v>
+        <v>2.246420289880714</v>
       </c>
       <c r="J31" s="13">
-        <v>0.4397089695665124</v>
+        <v>2.096390508368464</v>
       </c>
       <c r="K31" s="13">
-        <v>0.0711296123856411</v>
+        <v>-0.02573527777452323</v>
       </c>
       <c r="L31" s="13">
-        <v>0.6175684013531559</v>
+        <v>-2.630324415505271</v>
       </c>
       <c r="M31" s="13">
-        <v>-0.07202977302526614</v>
+        <v>-1.160659657407979</v>
       </c>
       <c r="N31" s="13">
-        <v>16.694096</v>
+        <v>40.037346</v>
       </c>
       <c r="O31" s="13">
-        <v>18.69391</v>
+        <v>4.951591</v>
       </c>
       <c r="P31" s="15">
-        <v>1.5956</v>
+        <v>0.13497</v>
       </c>
       <c r="Q31" s="15">
-        <v>0.162</v>
+        <v>0.22</v>
       </c>
       <c r="R31" s="15">
-        <v>0.03230029322725958</v>
+        <v>1.022227047855257</v>
       </c>
       <c r="S31" s="12">
-        <v>64.58742501246988</v>
+        <v>50.36741809631073</v>
       </c>
       <c r="T31" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -7052,61 +7095,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E32" s="11">
-        <v>35.77999877929688</v>
+        <v>1208.739990234375</v>
       </c>
       <c r="F32" s="20">
-        <v>0.4401218774166582</v>
+        <v>0.4457402747961864</v>
       </c>
       <c r="G32" s="13">
-        <v>-0.01436423851863369</v>
+        <v>-1.067825127575939</v>
       </c>
       <c r="H32" s="13">
-        <v>-0.8111350979836002</v>
+        <v>1.801901173699206</v>
       </c>
       <c r="I32" s="13">
-        <v>3.797605429884786</v>
+        <v>0.7243252315067988</v>
       </c>
       <c r="J32" s="13">
-        <v>0.06016855391795665</v>
+        <v>0.6080065705360135</v>
       </c>
       <c r="K32" s="13">
-        <v>3.58323381448609</v>
+        <v>0.842433694510219</v>
       </c>
       <c r="L32" s="13">
-        <v>-2.893114900796578</v>
+        <v>0.3305573712931109</v>
       </c>
       <c r="M32" s="13">
-        <v>-1.021540210337669</v>
+        <v>-0.3264421245289307</v>
       </c>
       <c r="N32" s="13">
-        <v>13.120689</v>
+        <v>39.5861</v>
       </c>
       <c r="O32" s="13">
-        <v>2.6814659</v>
+        <v>31.03179</v>
       </c>
       <c r="P32" s="15">
-        <v>0.21465999</v>
+        <v>1.02286</v>
       </c>
       <c r="Q32" s="15">
-        <v>0.9320000000000001</v>
+        <v>0.477</v>
       </c>
       <c r="R32" s="15">
-        <v>0.3111028794044097</v>
+        <v>0.339796252696557</v>
       </c>
       <c r="S32" s="12">
-        <v>37.68367454999319</v>
+        <v>60.43546764048855</v>
       </c>
       <c r="T32" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -7114,61 +7157,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E33" s="11">
-        <v>1208.739990234375</v>
+        <v>35.77999877929688</v>
       </c>
       <c r="F33" s="20">
-        <v>0.4370908009912824</v>
+        <v>0.4384088602597463</v>
       </c>
       <c r="G33" s="13">
-        <v>-1.067825127575939</v>
+        <v>-0.01436423851863369</v>
       </c>
       <c r="H33" s="13">
-        <v>1.801901173699206</v>
+        <v>-0.8111350979836002</v>
       </c>
       <c r="I33" s="13">
-        <v>0.7243252315067988</v>
+        <v>3.797605429884786</v>
       </c>
       <c r="J33" s="13">
-        <v>0.5720946684500957</v>
+        <v>0.08533625270185578</v>
       </c>
       <c r="K33" s="13">
-        <v>0.8559967599438418</v>
+        <v>3.535310679487199</v>
       </c>
       <c r="L33" s="13">
-        <v>0.3295050220346879</v>
+        <v>-2.949498962581992</v>
       </c>
       <c r="M33" s="13">
-        <v>-0.3194462504746564</v>
+        <v>-1.023159046401292</v>
       </c>
       <c r="N33" s="13">
-        <v>39.5861</v>
+        <v>13.120689</v>
       </c>
       <c r="O33" s="13">
-        <v>31.03179</v>
+        <v>2.6814659</v>
       </c>
       <c r="P33" s="15">
-        <v>1.02286</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q33" s="15">
-        <v>0.477</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R33" s="15">
-        <v>0.339796252696557</v>
+        <v>0.3111028794044097</v>
       </c>
       <c r="S33" s="12">
-        <v>60.43546764052299</v>
+        <v>37.68367454999314</v>
       </c>
       <c r="T33" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -7188,7 +7231,7 @@
         <v>221.3000030517578</v>
       </c>
       <c r="F34" s="20">
-        <v>0.4142566566814465</v>
+        <v>0.4243984586823153</v>
       </c>
       <c r="G34" s="13">
         <v>-1.1019019214601</v>
@@ -7200,16 +7243,16 @@
         <v>2.390890545007346</v>
       </c>
       <c r="J34" s="13">
-        <v>0.231187293958861</v>
+        <v>0.258180308540127</v>
       </c>
       <c r="K34" s="13">
-        <v>-0.2890305714282119</v>
+        <v>-0.2881676012905774</v>
       </c>
       <c r="L34" s="13">
-        <v>-0.1828728415177966</v>
+        <v>-0.1774039267954655</v>
       </c>
       <c r="M34" s="13">
-        <v>-0.3659902772429932</v>
+        <v>-0.3458376981600805</v>
       </c>
       <c r="N34" s="13">
         <v>28.986094</v>
@@ -7227,10 +7270,10 @@
         <v>0.1153307952322089</v>
       </c>
       <c r="S34" s="12">
-        <v>43.9793505854711</v>
+        <v>43.97935058533494</v>
       </c>
       <c r="T34" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -7238,61 +7281,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="E35" s="11">
-        <v>194.3500061035156</v>
+        <v>30.95</v>
       </c>
       <c r="F35" s="20">
-        <v>0.4112791282584083</v>
+        <v>0.4215045175391142</v>
       </c>
       <c r="G35" s="13">
-        <v>0.573799013559786</v>
+        <v>-0.01541387474592746</v>
       </c>
       <c r="H35" s="13">
-        <v>-0.6557710512148275</v>
+        <v>-1.00154153379357</v>
       </c>
       <c r="I35" s="13">
-        <v>4.09736352358056</v>
+        <v>-1.185161562431872</v>
       </c>
       <c r="J35" s="13">
-        <v>-0.5568254049112498</v>
+        <v>0.910656118902156</v>
       </c>
       <c r="K35" s="13">
-        <v>0.6672381093907983</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L35" s="13">
-        <v>0.6878072536899908</v>
+        <v>0.4629239467103094</v>
       </c>
       <c r="M35" s="13">
-        <v>0.6111616847380363</v>
+        <v>-1.029800822801748</v>
       </c>
       <c r="N35" s="13">
-        <v>12.797688</v>
+        <v>497.26776</v>
       </c>
       <c r="O35" s="13">
-        <v>1.1870677</v>
+        <v>2.3630948</v>
       </c>
       <c r="P35" s="15">
-        <v>0.09031</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q35" s="15">
-        <v>11.11</v>
+        <v>-0.112</v>
       </c>
       <c r="R35" s="15">
-        <v>-0.03501068146755337</v>
+        <v>0.1308001461454147</v>
       </c>
       <c r="S35" s="12">
-        <v>38.08737904426127</v>
+        <v>75.22299401348903</v>
       </c>
       <c r="T35" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -7300,61 +7343,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>160</v>
+        <v>19</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="E36" s="11">
-        <v>30.95</v>
+        <v>194.3500061035156</v>
       </c>
       <c r="F36" s="20">
-        <v>0.4069185318219268</v>
+        <v>0.4137428543891978</v>
       </c>
       <c r="G36" s="13">
-        <v>-0.01541387474592746</v>
+        <v>0.573799013559786</v>
       </c>
       <c r="H36" s="13">
-        <v>-1.00154153379357</v>
+        <v>-0.6557710512148275</v>
       </c>
       <c r="I36" s="13">
-        <v>-1.185161562431872</v>
+        <v>4.09736352358056</v>
       </c>
       <c r="J36" s="13">
-        <v>0.869259898596953</v>
+        <v>-0.5431764848141137</v>
       </c>
       <c r="K36" s="13">
-        <v>4.044575143915362</v>
+        <v>0.6560531871967765</v>
       </c>
       <c r="L36" s="13">
-        <v>0.4630224836468843</v>
+        <v>0.6857711298223538</v>
       </c>
       <c r="M36" s="13">
-        <v>-1.068156311767379</v>
+        <v>0.6090792872004047</v>
       </c>
       <c r="N36" s="13">
-        <v>497.26776</v>
+        <v>12.797688</v>
       </c>
       <c r="O36" s="13">
-        <v>2.3630948</v>
+        <v>1.1870677</v>
       </c>
       <c r="P36" s="15">
-        <v>-0.08785999999999999</v>
+        <v>0.09031</v>
       </c>
       <c r="Q36" s="15">
-        <v>-0.112</v>
+        <v>11.11</v>
       </c>
       <c r="R36" s="15">
-        <v>0.1308001461454147</v>
+        <v>-0.03501068146755337</v>
       </c>
       <c r="S36" s="12">
-        <v>75.22299401349004</v>
+        <v>38.08737904424933</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -7362,61 +7405,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E37" s="11">
-        <v>301.6300048828125</v>
+        <v>177.0099945068359</v>
       </c>
       <c r="F37" s="20">
-        <v>0.4005030458714431</v>
+        <v>0.404486204762235</v>
       </c>
       <c r="G37" s="13">
-        <v>-0.6750434006171774</v>
+        <v>0.3069913706549089</v>
       </c>
       <c r="H37" s="13">
-        <v>0.6516504181860266</v>
+        <v>-0.5480761301982536</v>
       </c>
       <c r="I37" s="13">
-        <v>-0.01179628325654914</v>
+        <v>1.025934986624751</v>
       </c>
       <c r="J37" s="13">
-        <v>1.906688753190626</v>
+        <v>1.088646310071552</v>
       </c>
       <c r="K37" s="13">
-        <v>-0.310184558128122</v>
+        <v>0.09209147972248062</v>
       </c>
       <c r="L37" s="13">
-        <v>-0.8983284335905188</v>
+        <v>0.706020135818737</v>
       </c>
       <c r="M37" s="13">
-        <v>-0.7744794195994562</v>
+        <v>-0.5709954815461327</v>
       </c>
       <c r="N37" s="13">
-        <v>48.545902</v>
+        <v>21.7426</v>
       </c>
       <c r="O37" s="13">
-        <v>6.605916</v>
+        <v>2.6781864</v>
       </c>
       <c r="P37" s="15">
-        <v>0.14425</v>
+        <v>0.12584</v>
       </c>
       <c r="Q37" s="15">
-        <v>0.176</v>
+        <v>0.441</v>
       </c>
       <c r="R37" s="15">
-        <v>0.8959709084547447</v>
+        <v>0.203713807215314</v>
       </c>
       <c r="S37" s="12">
-        <v>71.85823662423283</v>
+        <v>74.92349295561721</v>
       </c>
       <c r="T37" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -7424,61 +7467,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D38" s="10" t="s">
         <v>48</v>
       </c>
       <c r="E38" s="11">
-        <v>177.0099945068359</v>
+        <v>49.91999816894531</v>
       </c>
       <c r="F38" s="20">
-        <v>0.3899292716102917</v>
+        <v>0.3955166201400885</v>
       </c>
       <c r="G38" s="13">
-        <v>0.3069913706549089</v>
+        <v>0.3190129943001489</v>
       </c>
       <c r="H38" s="13">
-        <v>-0.5480761301982536</v>
+        <v>-0.04431119898918571</v>
       </c>
       <c r="I38" s="13">
-        <v>1.025934986624751</v>
+        <v>1.24285337166309</v>
       </c>
       <c r="J38" s="13">
-        <v>1.044248612990179</v>
+        <v>0.7969238953376877</v>
       </c>
       <c r="K38" s="13">
-        <v>0.09608046849322725</v>
+        <v>-0.01502375436570473</v>
       </c>
       <c r="L38" s="13">
-        <v>0.7082323184941979</v>
+        <v>0.04804998572963944</v>
       </c>
       <c r="M38" s="13">
-        <v>-0.5941084020529939</v>
+        <v>-0.240732267289722</v>
       </c>
       <c r="N38" s="13">
-        <v>21.7426</v>
+        <v>10.65342</v>
       </c>
       <c r="O38" s="13">
-        <v>2.6781864</v>
+        <v>1.3292934</v>
       </c>
       <c r="P38" s="15">
-        <v>0.12584</v>
+        <v>0.11522</v>
       </c>
       <c r="Q38" s="15">
-        <v>0.441</v>
+        <v>0.642</v>
       </c>
       <c r="R38" s="15">
-        <v>0.203713807215314</v>
+        <v>0.1187412046852947</v>
       </c>
       <c r="S38" s="12">
-        <v>74.9234929516121</v>
+        <v>59.96046600045739</v>
       </c>
       <c r="T38" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -7486,61 +7529,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E39" s="11">
-        <v>49.91999816894531</v>
+        <v>427.3999938964844</v>
       </c>
       <c r="F39" s="20">
-        <v>0.3850631458073874</v>
+        <v>0.3879338692574937</v>
       </c>
       <c r="G39" s="13">
-        <v>0.3190129943001489</v>
+        <v>0.2970607495888827</v>
       </c>
       <c r="H39" s="13">
-        <v>-0.04431119898918571</v>
+        <v>-1.054613391281616</v>
       </c>
       <c r="I39" s="13">
-        <v>1.24285337166309</v>
+        <v>0.1591049640981598</v>
       </c>
       <c r="J39" s="13">
-        <v>0.7593109324500283</v>
+        <v>1.733020161420015</v>
       </c>
       <c r="K39" s="13">
-        <v>-0.0124015145832345</v>
+        <v>-0.1473110684646137</v>
       </c>
       <c r="L39" s="13">
-        <v>0.0445413226396831</v>
+        <v>-0.4257336278185164</v>
       </c>
       <c r="M39" s="13">
-        <v>-0.2316539479760001</v>
+        <v>0.1325734748199665</v>
       </c>
       <c r="N39" s="13">
-        <v>10.65342</v>
+        <v>40.81947</v>
       </c>
       <c r="O39" s="13">
-        <v>1.3292934</v>
+        <v>2.6991706</v>
       </c>
       <c r="P39" s="15">
-        <v>0.11522</v>
+        <v>0.06893000000000001</v>
       </c>
       <c r="Q39" s="15">
-        <v>0.642</v>
+        <v>0.262</v>
       </c>
       <c r="R39" s="15">
-        <v>0.1187412046852947</v>
+        <v>1.159642837344081</v>
       </c>
       <c r="S39" s="12">
-        <v>59.96046600596216</v>
+        <v>62.00128646866262</v>
       </c>
       <c r="T39" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -7560,7 +7603,7 @@
         <v>111.5699996948242</v>
       </c>
       <c r="F40" s="20">
-        <v>0.3795989567361757</v>
+        <v>0.3847476415627792</v>
       </c>
       <c r="G40" s="13">
         <v>0.3787913962730532</v>
@@ -7572,16 +7615,16 @@
         <v>0.5122250580763105</v>
       </c>
       <c r="J40" s="13">
-        <v>-0.07709043403359279</v>
+        <v>-0.05830769128455526</v>
       </c>
       <c r="K40" s="13">
-        <v>1.760736498801533</v>
+        <v>1.735774746805685</v>
       </c>
       <c r="L40" s="13">
-        <v>0.1355161803004448</v>
+        <v>0.1382406635047936</v>
       </c>
       <c r="M40" s="13">
-        <v>-0.2155716524459457</v>
+        <v>-0.1862491118317821</v>
       </c>
       <c r="N40" s="13">
         <v>14.368154</v>
@@ -7599,10 +7642,10 @@
         <v>0.1490216421018755</v>
       </c>
       <c r="S40" s="12">
-        <v>34.99391983401445</v>
+        <v>34.99391983401442</v>
       </c>
       <c r="T40" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -7610,61 +7653,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>63</v>
       </c>
       <c r="E41" s="11">
-        <v>427.3999938964844</v>
+        <v>297.3500061035156</v>
       </c>
       <c r="F41" s="20">
-        <v>0.3710288853806689</v>
+        <v>0.3838247184468957</v>
       </c>
       <c r="G41" s="13">
-        <v>0.2970607495888827</v>
+        <v>-0.6750434006171774</v>
       </c>
       <c r="H41" s="13">
-        <v>-1.054613391281616</v>
+        <v>0.6516504181860266</v>
       </c>
       <c r="I41" s="13">
-        <v>0.1591049640981598</v>
+        <v>-0.01179628325654914</v>
       </c>
       <c r="J41" s="13">
-        <v>1.671217486723745</v>
+        <v>1.790528600503205</v>
       </c>
       <c r="K41" s="13">
-        <v>-0.1463767636826648</v>
+        <v>-0.3090550719377735</v>
       </c>
       <c r="L41" s="13">
-        <v>-0.4333616920377246</v>
+        <v>-0.8280026110745325</v>
       </c>
       <c r="M41" s="13">
-        <v>0.1573407974621526</v>
+        <v>-0.6017965360009805</v>
       </c>
       <c r="N41" s="13">
-        <v>40.81947</v>
+        <v>48.545902</v>
       </c>
       <c r="O41" s="13">
-        <v>2.6991706</v>
+        <v>6.605916</v>
       </c>
       <c r="P41" s="15">
-        <v>0.06893000000000001</v>
+        <v>0.14425</v>
       </c>
       <c r="Q41" s="15">
-        <v>0.262</v>
+        <v>0.176</v>
       </c>
       <c r="R41" s="15">
-        <v>1.159642837344081</v>
+        <v>0.777346088938947</v>
       </c>
       <c r="S41" s="12">
-        <v>62.00128646867507</v>
+        <v>66.93181933307791</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -7672,61 +7715,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E42" s="11">
-        <v>29.6299991607666</v>
+        <v>603.239990234375</v>
       </c>
       <c r="F42" s="20">
-        <v>0.3606769430479269</v>
+        <v>0.3672650752951226</v>
       </c>
       <c r="G42" s="13">
-        <v>0.4636006651738224</v>
+        <v>-1.341725686078395</v>
       </c>
       <c r="H42" s="13">
-        <v>-0.286561597971879</v>
+        <v>2.889093849209865</v>
       </c>
       <c r="I42" s="13">
-        <v>-0.682866398151852</v>
+        <v>-0.1842355355782666</v>
       </c>
       <c r="J42" s="13">
-        <v>0.3849832541795246</v>
+        <v>0.5675987956162279</v>
       </c>
       <c r="K42" s="13">
-        <v>2.156153327115236</v>
+        <v>-0.3219089000283558</v>
       </c>
       <c r="L42" s="13">
-        <v>0.5451745226208672</v>
+        <v>1.024002403499752</v>
       </c>
       <c r="M42" s="13">
-        <v>-0.194731600720164</v>
+        <v>-0.3518309802246099</v>
       </c>
       <c r="N42" s="13">
-        <v>28.271847</v>
+        <v>32.40594</v>
       </c>
       <c r="O42" s="13">
-        <v>1.8560776</v>
+        <v>92.11069500000001</v>
       </c>
       <c r="P42" s="15">
-        <v>0.07979</v>
+        <v>2.41202</v>
       </c>
       <c r="Q42" s="15">
-        <v>0.108</v>
+        <v>0.141</v>
       </c>
       <c r="R42" s="15">
-        <v>0.1877624929638697</v>
+        <v>0.1638726102948753</v>
       </c>
       <c r="S42" s="12">
-        <v>56.19412514270516</v>
+        <v>70.36768024122347</v>
       </c>
       <c r="T42" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -7734,61 +7777,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E43" s="11">
-        <v>603.239990234375</v>
+        <v>73.12999725341797</v>
       </c>
       <c r="F43" s="20">
-        <v>0.3587782241164886</v>
+        <v>0.3670164460944886</v>
       </c>
       <c r="G43" s="13">
-        <v>-1.341725686078395</v>
+        <v>0.4281951431088404</v>
       </c>
       <c r="H43" s="13">
-        <v>2.889093849209865</v>
+        <v>1.839920832819933</v>
       </c>
       <c r="I43" s="13">
-        <v>-0.1842355355782666</v>
+        <v>-0.6395167842697658</v>
       </c>
       <c r="J43" s="13">
-        <v>0.5329248653487405</v>
+        <v>0.5657338531163074</v>
       </c>
       <c r="K43" s="13">
-        <v>-0.3232023960972974</v>
+        <v>-0.6807449342237767</v>
       </c>
       <c r="L43" s="13">
-        <v>1.028979343070787</v>
+        <v>0.3739159694915301</v>
       </c>
       <c r="M43" s="13">
-        <v>-0.3296818420293212</v>
+        <v>-0.6370007060855774</v>
       </c>
       <c r="N43" s="13">
-        <v>32.40594</v>
+        <v>15.090527</v>
       </c>
       <c r="O43" s="13">
-        <v>92.11069500000001</v>
+        <v>-44.856068</v>
       </c>
       <c r="P43" s="15">
-        <v>2.41202</v>
+        <v>0</v>
       </c>
       <c r="Q43" s="15">
-        <v>0.141</v>
+        <v>0.012</v>
       </c>
       <c r="R43" s="15">
-        <v>0.1638726102948753</v>
+        <v>0.1705850852388084</v>
       </c>
       <c r="S43" s="12">
-        <v>70.36768018331439</v>
+        <v>72.05984684714561</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -7796,61 +7839,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E44" s="11">
-        <v>73.12999725341797</v>
+        <v>197.5099945068359</v>
       </c>
       <c r="F44" s="20">
-        <v>0.3564147107025588</v>
+        <v>0.3661560894885361</v>
       </c>
       <c r="G44" s="13">
-        <v>0.4281951431088404</v>
+        <v>0.578054316350588</v>
       </c>
       <c r="H44" s="13">
-        <v>1.839920832819933</v>
+        <v>-0.04848410617494222</v>
       </c>
       <c r="I44" s="13">
-        <v>-0.6395167842697658</v>
+        <v>1.554104829957849</v>
       </c>
       <c r="J44" s="13">
-        <v>0.5287718416355411</v>
+        <v>0.3933033463599815</v>
       </c>
       <c r="K44" s="13">
-        <v>-0.6866170394034443</v>
+        <v>-0.1724831484753372</v>
       </c>
       <c r="L44" s="13">
-        <v>0.3732406097559057</v>
+        <v>0.008771521503207765</v>
       </c>
       <c r="M44" s="13">
-        <v>-0.6216001778606073</v>
+        <v>0.2079246144561197</v>
       </c>
       <c r="N44" s="13">
-        <v>15.090527</v>
+        <v>36.59619</v>
       </c>
       <c r="O44" s="13">
-        <v>-44.856068</v>
+        <v>1.4223108</v>
       </c>
       <c r="P44" s="15">
-        <v>0</v>
+        <v>0.034930002</v>
       </c>
       <c r="Q44" s="15">
-        <v>0.012</v>
+        <v>0.525</v>
       </c>
       <c r="R44" s="15">
-        <v>0.1705850137611253</v>
+        <v>0.07435304624468642</v>
       </c>
       <c r="S44" s="12">
-        <v>72.05984697550703</v>
+        <v>58.19270011730175</v>
       </c>
       <c r="T44" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
@@ -7916,110 +7959,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B6" s="15">
         <v>0.18</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B7" s="15">
         <v>0.16</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B8" s="15">
         <v>0.1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B9" s="15">
         <v>0.3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B10" s="15">
         <v>0.12</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B11" s="15">
         <v>0.06</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B12" s="15">
         <v>0.08</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B13" s="15">
         <f>SUM(B6:B12)</f>
@@ -8028,22 +8071,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -8122,49 +8165,49 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="10" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>137</v>
@@ -8172,10 +8215,10 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>239</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -8304,3880 +8347,3829 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI21"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:60">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>1599.27001953125</v>
+        <v>1610.329956054688</v>
       </c>
       <c r="C1">
-        <v>1610.329956054688</v>
+        <v>1436.56005859375</v>
       </c>
       <c r="D1">
-        <v>1436.56005859375</v>
+        <v>1278.22998046875</v>
       </c>
       <c r="E1">
-        <v>1278.22998046875</v>
+        <v>1096.099975585938</v>
       </c>
       <c r="F1">
-        <v>1096.099975585938</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="G1">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="H1">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="I1">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="J1">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="K1">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="L1">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="M1">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="N1">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="O1">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="P1">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="Q1">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="R1">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="S1">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="T1">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="U1">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="V1">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="W1">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="X1">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="Y1">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="Z1">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="AA1">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="AB1">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="AC1">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="AD1">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="AE1">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="AF1">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="AG1">
-        <v>1554.989990234375</v>
+        <v>1740</v>
       </c>
       <c r="AH1">
-        <v>1740</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="AI1">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="AJ1">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="AK1">
-        <v>1692.589965820312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="AL1">
-        <v>1633.349975585938</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="AM1">
-        <v>1551.989990234375</v>
+        <v>1530.89501953125</v>
       </c>
       <c r="AN1">
-        <v>1530.89501953125</v>
+        <v>1519.969970703125</v>
       </c>
       <c r="AO1">
-        <v>1519.969970703125</v>
+        <v>1614.390014648438</v>
       </c>
       <c r="AP1">
-        <v>1614.390014648438</v>
+        <v>1791.819946289062</v>
       </c>
       <c r="AQ1">
-        <v>1791.819946289062</v>
+        <v>1766.640014648438</v>
       </c>
       <c r="AR1">
-        <v>1766.640014648438</v>
+        <v>1887.0400390625</v>
       </c>
       <c r="AS1">
-        <v>1887.0400390625</v>
+        <v>1816.569946289062</v>
       </c>
       <c r="AT1">
-        <v>1816.569946289062</v>
+        <v>1753.619995117188</v>
       </c>
       <c r="AU1">
-        <v>1753.619995117188</v>
+        <v>1777.800048828125</v>
       </c>
       <c r="AV1">
-        <v>1777.800048828125</v>
+        <v>1712.890014648438</v>
       </c>
       <c r="AW1">
-        <v>1712.890014648438</v>
+        <v>1729.760009765625</v>
       </c>
       <c r="AX1">
-        <v>1729.760009765625</v>
+        <v>1739.890014648438</v>
       </c>
       <c r="AY1">
-        <v>1739.890014648438</v>
+        <v>1787.68994140625</v>
       </c>
       <c r="AZ1">
-        <v>1787.68994140625</v>
+        <v>1719.989990234375</v>
       </c>
       <c r="BA1">
-        <v>1719.989990234375</v>
+        <v>1704.160034179688</v>
       </c>
       <c r="BB1">
-        <v>1704.160034179688</v>
+        <v>1660.4599609375</v>
       </c>
       <c r="BC1">
-        <v>1660.4599609375</v>
+        <v>1692.420043945312</v>
       </c>
       <c r="BD1">
-        <v>1692.420043945312</v>
+        <v>1609.4599609375</v>
       </c>
       <c r="BE1">
-        <v>1609.4599609375</v>
+        <v>1581.819946289062</v>
       </c>
       <c r="BF1">
-        <v>1581.819946289062</v>
+        <v>1487.329956054688</v>
       </c>
       <c r="BG1">
-        <v>1487.329956054688</v>
+        <v>1482.329956054688</v>
       </c>
       <c r="BH1">
-        <v>1482.329956054688</v>
-      </c>
-    </row>
-    <row r="2" spans="1:61">
+        <v>1403.339965820312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:60">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>556.4913330078125</v>
+        <v>558.120849609375</v>
       </c>
       <c r="C2">
-        <v>558.120849609375</v>
+        <v>519.6331787109375</v>
       </c>
       <c r="D2">
-        <v>519.6331787109375</v>
+        <v>497.7602233886719</v>
       </c>
       <c r="E2">
-        <v>497.7602233886719</v>
+        <v>463.3612670898438</v>
       </c>
       <c r="F2">
-        <v>463.3612670898438</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="G2">
-        <v>461.8917236328125</v>
+        <v>532.868896484375</v>
       </c>
       <c r="H2">
-        <v>532.868896484375</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="I2">
-        <v>544.6651611328125</v>
+        <v>527.05078125</v>
       </c>
       <c r="J2">
-        <v>527.05078125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="K2">
-        <v>548.3839721679688</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="L2">
-        <v>519.0033569335938</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="M2">
-        <v>451.3750915527344</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="N2">
-        <v>434.1606140136719</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="O2">
-        <v>438.1993408203125</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="P2">
-        <v>437.7894592285156</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="Q2">
-        <v>453.9542846679688</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="R2">
-        <v>487.1336364746094</v>
+        <v>508.63671875</v>
       </c>
       <c r="S2">
-        <v>508.63671875</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="T2">
-        <v>535.8380126953125</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="U2">
-        <v>496.0007934570312</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="V2">
-        <v>461.9417114257812</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="W2">
-        <v>468.8994750976562</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="X2">
-        <v>459.2925720214844</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="Y2">
-        <v>435.2402954101562</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="Z2">
-        <v>450.6053466796875</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="AA2">
-        <v>468.7295227050781</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="AB2">
-        <v>461.8517456054688</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="AC2">
-        <v>459.3025817871094</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="AD2">
-        <v>450.4053955078125</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="AE2">
-        <v>450.2954406738281</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="AF2">
-        <v>448.7559509277344</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="AG2">
-        <v>441.4283142089844</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="AH2">
-        <v>467.3099670410156</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="AI2">
-        <v>477.2999877929688</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="AJ2">
-        <v>482.2799987792969</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="AK2">
-        <v>460.9299926757812</v>
+        <v>447.1799926757812</v>
       </c>
       <c r="AL2">
-        <v>447.1799926757812</v>
+        <v>426.9400024414062</v>
       </c>
       <c r="AM2">
-        <v>426.9400024414062</v>
+        <v>411.9599914550781</v>
       </c>
       <c r="AN2">
-        <v>411.9599914550781</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="AO2">
-        <v>416.9700012207031</v>
+        <v>423.8699951171875</v>
       </c>
       <c r="AP2">
-        <v>423.8699951171875</v>
+        <v>441.3599853515625</v>
       </c>
       <c r="AQ2">
-        <v>441.3599853515625</v>
+        <v>448.1700134277344</v>
       </c>
       <c r="AR2">
-        <v>448.1700134277344</v>
+        <v>464.6000061035156</v>
       </c>
       <c r="AS2">
-        <v>464.6000061035156</v>
+        <v>473.6900024414062</v>
       </c>
       <c r="AT2">
-        <v>473.6900024414062</v>
+        <v>450.3099975585938</v>
       </c>
       <c r="AU2">
-        <v>450.3099975585938</v>
+        <v>456.8099975585938</v>
       </c>
       <c r="AV2">
-        <v>456.8099975585938</v>
+        <v>453.2300109863281</v>
       </c>
       <c r="AW2">
-        <v>453.2300109863281</v>
+        <v>453.4800109863281</v>
       </c>
       <c r="AX2">
-        <v>453.4800109863281</v>
+        <v>454.4599914550781</v>
       </c>
       <c r="AY2">
-        <v>454.4599914550781</v>
+        <v>462.5599975585938</v>
       </c>
       <c r="AZ2">
-        <v>462.5599975585938</v>
+        <v>415.2900085449219</v>
       </c>
       <c r="BA2">
-        <v>415.2900085449219</v>
+        <v>441.6400146484375</v>
       </c>
       <c r="BB2">
-        <v>441.6400146484375</v>
+        <v>411.0400085449219</v>
       </c>
       <c r="BC2">
-        <v>411.0400085449219</v>
+        <v>405.4200134277344</v>
       </c>
       <c r="BD2">
-        <v>405.4200134277344</v>
+        <v>393.3099975585938</v>
       </c>
       <c r="BE2">
-        <v>393.3099975585938</v>
+        <v>397.2799987792969</v>
       </c>
       <c r="BF2">
-        <v>397.2799987792969</v>
+        <v>386.9400024414062</v>
       </c>
       <c r="BG2">
-        <v>386.9400024414062</v>
+        <v>380.7099914550781</v>
       </c>
       <c r="BH2">
-        <v>380.7099914550781</v>
-      </c>
-      <c r="BI2">
         <v>364.1000061035156</v>
       </c>
     </row>
-    <row r="3" spans="1:61">
+    <row r="3" spans="1:60">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>309.7230529785156</v>
+        <v>304.0848388671875</v>
       </c>
       <c r="C3">
-        <v>304.0848388671875</v>
+        <v>301.33544921875</v>
       </c>
       <c r="D3">
-        <v>301.33544921875</v>
+        <v>303.756103515625</v>
       </c>
       <c r="E3">
-        <v>303.756103515625</v>
+        <v>297.7294006347656</v>
       </c>
       <c r="F3">
-        <v>297.7294006347656</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="G3">
-        <v>300.1600036621094</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="H3">
-        <v>310.5099792480469</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="I3">
-        <v>312.8999938964844</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="J3">
-        <v>307.5400085449219</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="K3">
-        <v>308.7300109863281</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="L3">
-        <v>302.3900146484375</v>
+        <v>302.989990234375</v>
       </c>
       <c r="M3">
-        <v>302.989990234375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="N3">
-        <v>298.3099975585938</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="O3">
-        <v>314.9500122070312</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="P3">
-        <v>323.9200134277344</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="Q3">
-        <v>330.2099914550781</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="R3">
-        <v>342.9200134277344</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="S3">
-        <v>341.6700134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="T3">
-        <v>347.1900024414062</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="U3">
-        <v>350.0499877929688</v>
+        <v>346.260009765625</v>
       </c>
       <c r="V3">
-        <v>346.260009765625</v>
+        <v>341.510009765625</v>
       </c>
       <c r="W3">
-        <v>341.510009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="X3">
-        <v>348.8599853515625</v>
+        <v>346</v>
       </c>
       <c r="Y3">
-        <v>346</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="Z3">
-        <v>340.4100036621094</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="AA3">
-        <v>348.0299987792969</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="AB3">
-        <v>346.5899963378906</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="AC3">
-        <v>352.3599853515625</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="AD3">
-        <v>358.9200134277344</v>
+        <v>361.989990234375</v>
       </c>
       <c r="AE3">
-        <v>361.989990234375</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="AF3">
-        <v>366.0899963378906</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="AG3">
-        <v>370.6900024414062</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="AH3">
-        <v>370.7200012207031</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="AI3">
-        <v>382.8500061035156</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="AJ3">
-        <v>388.9500122070312</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="AK3">
-        <v>385.4299926757812</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="AL3">
-        <v>390.4200134277344</v>
+        <v>382.9500122070312</v>
       </c>
       <c r="AM3">
-        <v>382.9500122070312</v>
+        <v>397.0400085449219</v>
       </c>
       <c r="AN3">
-        <v>397.0400085449219</v>
+        <v>403.2799987792969</v>
       </c>
       <c r="AO3">
-        <v>403.2799987792969</v>
+        <v>412.5299987792969</v>
       </c>
       <c r="AP3">
-        <v>412.5299987792969</v>
+        <v>413.2799987792969</v>
       </c>
       <c r="AQ3">
-        <v>413.2799987792969</v>
+        <v>393.2699890136719</v>
       </c>
       <c r="AR3">
-        <v>393.2699890136719</v>
+        <v>377.1400146484375</v>
       </c>
       <c r="AS3">
-        <v>377.1400146484375</v>
+        <v>375.8399963378906</v>
       </c>
       <c r="AT3">
-        <v>375.8399963378906</v>
+        <v>382.8599853515625</v>
       </c>
       <c r="AU3">
-        <v>382.8599853515625</v>
+        <v>387.1799926757812</v>
       </c>
       <c r="AV3">
-        <v>387.1799926757812</v>
+        <v>389.5700073242188</v>
       </c>
       <c r="AW3">
-        <v>389.5700073242188</v>
+        <v>387.7200012207031</v>
       </c>
       <c r="AX3">
-        <v>387.7200012207031</v>
+        <v>387.6099853515625</v>
       </c>
       <c r="AY3">
-        <v>387.6099853515625</v>
+        <v>408.4599914550781</v>
       </c>
       <c r="AZ3">
-        <v>408.4599914550781</v>
+        <v>406.2999877929688</v>
       </c>
       <c r="BA3">
-        <v>406.2999877929688</v>
+        <v>419.3299865722656</v>
       </c>
       <c r="BB3">
-        <v>419.3299865722656</v>
+        <v>419.2200012207031</v>
       </c>
       <c r="BC3">
-        <v>419.2200012207031</v>
+        <v>424.1000061035156</v>
       </c>
       <c r="BD3">
-        <v>424.1000061035156</v>
+        <v>443.7999877929688</v>
       </c>
       <c r="BE3">
-        <v>443.7999877929688</v>
+        <v>433.75</v>
       </c>
       <c r="BF3">
-        <v>433.75</v>
+        <v>436</v>
       </c>
       <c r="BG3">
-        <v>436</v>
+        <v>456.4599914550781</v>
       </c>
       <c r="BH3">
-        <v>456.4599914550781</v>
-      </c>
-      <c r="BI3">
         <v>459.7799987792969</v>
       </c>
     </row>
-    <row r="4" spans="1:61">
+    <row r="4" spans="1:60">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>314.9576110839844</v>
+        <v>311.4172973632812</v>
       </c>
       <c r="C4">
-        <v>311.4172973632812</v>
+        <v>308.3955688476562</v>
       </c>
       <c r="D4">
-        <v>308.3955688476562</v>
+        <v>311.4970703125</v>
       </c>
       <c r="E4">
-        <v>311.4970703125</v>
+        <v>305.2142639160156</v>
       </c>
       <c r="F4">
-        <v>305.2142639160156</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="G4">
-        <v>307.8769836425781</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="H4">
-        <v>313.2223510742188</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="I4">
-        <v>315.6058349609375</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="J4">
-        <v>306.1915893554688</v>
+        <v>311.75634765625</v>
       </c>
       <c r="K4">
-        <v>311.75634765625</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="L4">
-        <v>296.9369506835938</v>
+        <v>298.432861328125</v>
       </c>
       <c r="M4">
-        <v>298.432861328125</v>
+        <v>297.3857421875</v>
       </c>
       <c r="N4">
-        <v>297.3857421875</v>
+        <v>319.4453125</v>
       </c>
       <c r="O4">
-        <v>319.4453125</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="P4">
-        <v>335.5013732910156</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="Q4">
-        <v>347.2990417480469</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="R4">
-        <v>355.3968811035156</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="S4">
-        <v>354.4494934082031</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="T4">
-        <v>357.2019348144531</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="U4">
-        <v>365.2099914550781</v>
+        <v>360.75</v>
       </c>
       <c r="V4">
-        <v>360.75</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="W4">
-        <v>358.2300109863281</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="X4">
-        <v>360.7200012207031</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="Y4">
-        <v>362.5199890136719</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="Z4">
-        <v>354.8800048828125</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="AA4">
-        <v>362.2699890136719</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="AB4">
-        <v>363.5400085449219</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="AC4">
-        <v>368.8299865722656</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="AD4">
-        <v>373.3200073242188</v>
+        <v>383</v>
       </c>
       <c r="AE4">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AF4">
-        <v>387</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="AG4">
-        <v>387.7099914550781</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="AH4">
-        <v>388.8999938964844</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="AI4">
-        <v>397.7699890136719</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="AJ4">
-        <v>399.4400024414062</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="AK4">
-        <v>392.4200134277344</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="AL4">
-        <v>395.9299926757812</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="AM4">
-        <v>396.4500122070312</v>
+        <v>410.8399963378906</v>
       </c>
       <c r="AN4">
-        <v>410.8399963378906</v>
+        <v>413.9200134277344</v>
       </c>
       <c r="AO4">
-        <v>413.9200134277344</v>
+        <v>421.9599914550781</v>
       </c>
       <c r="AP4">
-        <v>421.9599914550781</v>
+        <v>424.8900146484375</v>
       </c>
       <c r="AQ4">
-        <v>424.8900146484375</v>
+        <v>402.3800048828125</v>
       </c>
       <c r="AR4">
-        <v>402.3800048828125</v>
+        <v>389.6799926757812</v>
       </c>
       <c r="AS4">
-        <v>389.6799926757812</v>
+        <v>388.3800048828125</v>
       </c>
       <c r="AT4">
-        <v>388.3800048828125</v>
+        <v>390.9500122070312</v>
       </c>
       <c r="AU4">
-        <v>390.9500122070312</v>
+        <v>393.5199890136719</v>
       </c>
       <c r="AV4">
-        <v>393.5199890136719</v>
+        <v>389.4400024414062</v>
       </c>
       <c r="AW4">
-        <v>389.4400024414062</v>
+        <v>392.0299987792969</v>
       </c>
       <c r="AX4">
-        <v>392.0299987792969</v>
+        <v>395.4200134277344</v>
       </c>
       <c r="AY4">
-        <v>395.4200134277344</v>
+        <v>420.1499938964844</v>
       </c>
       <c r="AZ4">
-        <v>420.1499938964844</v>
+        <v>422.3299865722656</v>
       </c>
       <c r="BA4">
-        <v>422.3299865722656</v>
+        <v>433.4700012207031</v>
       </c>
       <c r="BB4">
-        <v>433.4700012207031</v>
+        <v>432.3599853515625</v>
       </c>
       <c r="BC4">
-        <v>432.3599853515625</v>
+        <v>442.260009765625</v>
       </c>
       <c r="BD4">
-        <v>442.260009765625</v>
+        <v>463.3399963378906</v>
       </c>
       <c r="BE4">
-        <v>463.3399963378906</v>
+        <v>455.0299987792969</v>
       </c>
       <c r="BF4">
-        <v>455.0299987792969</v>
+        <v>458.8099975585938</v>
       </c>
       <c r="BG4">
-        <v>458.8099975585938</v>
+        <v>476.9800109863281</v>
       </c>
       <c r="BH4">
-        <v>476.9800109863281</v>
-      </c>
-      <c r="BI4">
         <v>484.9200134277344</v>
       </c>
     </row>
-    <row r="5" spans="1:61">
+    <row r="5" spans="1:60">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>57.23735809326172</v>
+        <v>57.33689880371094</v>
       </c>
       <c r="C5">
-        <v>57.33689880371094</v>
+        <v>57.03827285766602</v>
       </c>
       <c r="D5">
-        <v>57.03827285766602</v>
+        <v>54.67909622192383</v>
       </c>
       <c r="E5">
-        <v>54.67909622192383</v>
+        <v>53.68366622924805</v>
       </c>
       <c r="F5">
-        <v>53.68366622924805</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="G5">
-        <v>55.77407073974609</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="H5">
-        <v>55.69443893432617</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="I5">
-        <v>56.80932235717773</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="J5">
-        <v>55.21663284301758</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="K5">
-        <v>54.8383674621582</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="L5">
-        <v>53.56421279907227</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="M5">
-        <v>55.78402709960938</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="N5">
-        <v>55.65462112426758</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="O5">
-        <v>58.38210678100586</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="P5">
-        <v>58.79023361206055</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="Q5">
-        <v>58.28256225585938</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="R5">
-        <v>57.43644714355469</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="S5">
-        <v>58.09342956542969</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="T5">
-        <v>58.77032470703125</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="U5">
-        <v>59.52685165405273</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="V5">
-        <v>59.81552886962891</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="W5">
-        <v>61.23899841308594</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="X5">
+        <v>59.8354377746582</v>
+      </c>
+      <c r="Y5">
+        <v>58.1431999206543</v>
+      </c>
+      <c r="Z5">
+        <v>58.35224151611328</v>
+      </c>
+      <c r="AA5">
+        <v>58.89972686767578</v>
+      </c>
+      <c r="AB5">
+        <v>58.83004760742188</v>
+      </c>
+      <c r="AC5">
+        <v>59.90511703491211</v>
+      </c>
+      <c r="AD5">
+        <v>60.67160034179688</v>
+      </c>
+      <c r="AE5">
+        <v>60.63178253173828</v>
+      </c>
+      <c r="AF5">
+        <v>60.33315277099609</v>
+      </c>
+      <c r="AG5">
+        <v>59.7657585144043</v>
+      </c>
+      <c r="AH5">
+        <v>60.37297058105469</v>
+      </c>
+      <c r="AI5">
         <v>61.02000045776367</v>
       </c>
-      <c r="Y5">
-        <v>59.8354377746582</v>
-      </c>
-      <c r="Z5">
-        <v>58.1431999206543</v>
-      </c>
-      <c r="AA5">
-        <v>58.35224151611328</v>
-      </c>
-      <c r="AB5">
-        <v>58.89972686767578</v>
-      </c>
-      <c r="AC5">
-        <v>58.83004760742188</v>
-      </c>
-      <c r="AD5">
-        <v>59.90511703491211</v>
-      </c>
-      <c r="AE5">
-        <v>60.67160034179688</v>
-      </c>
-      <c r="AF5">
-        <v>60.63178253173828</v>
-      </c>
-      <c r="AG5">
-        <v>60.33315277099609</v>
-      </c>
-      <c r="AH5">
-        <v>59.7657585144043</v>
-      </c>
-      <c r="AI5">
-        <v>60.37297058105469</v>
-      </c>
       <c r="AJ5">
-        <v>61.02000045776367</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="AK5">
-        <v>61.15999984741211</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="AL5">
-        <v>61.45999908447266</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="AM5">
-        <v>61.77999877929688</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="AN5">
-        <v>63.52000045776367</v>
+        <v>59.36000061035156</v>
       </c>
       <c r="AO5">
-        <v>59.36000061035156</v>
+        <v>59.29000091552734</v>
       </c>
       <c r="AP5">
-        <v>59.29000091552734</v>
+        <v>58.84000015258789</v>
       </c>
       <c r="AQ5">
-        <v>58.84000015258789</v>
+        <v>57.25</v>
       </c>
       <c r="AR5">
-        <v>57.25</v>
+        <v>56.31000137329102</v>
       </c>
       <c r="AS5">
-        <v>56.31000137329102</v>
+        <v>57.36000061035156</v>
       </c>
       <c r="AT5">
-        <v>57.36000061035156</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="AU5">
-        <v>58.04999923706055</v>
+        <v>56.86000061035156</v>
       </c>
       <c r="AV5">
-        <v>56.86000061035156</v>
+        <v>56.09999847412109</v>
       </c>
       <c r="AW5">
-        <v>56.09999847412109</v>
+        <v>54.93999862670898</v>
       </c>
       <c r="AX5">
-        <v>54.93999862670898</v>
+        <v>55.31999969482422</v>
       </c>
       <c r="AY5">
-        <v>55.31999969482422</v>
+        <v>57.84000015258789</v>
       </c>
       <c r="AZ5">
-        <v>57.84000015258789</v>
+        <v>58.08000183105469</v>
       </c>
       <c r="BA5">
-        <v>58.08000183105469</v>
+        <v>58.31000137329102</v>
       </c>
       <c r="BB5">
-        <v>58.31000137329102</v>
+        <v>58.33000183105469</v>
       </c>
       <c r="BC5">
-        <v>58.33000183105469</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="BD5">
-        <v>58.20999908447266</v>
+        <v>60.27999877929688</v>
       </c>
       <c r="BE5">
-        <v>60.27999877929688</v>
+        <v>60.11000061035156</v>
       </c>
       <c r="BF5">
-        <v>60.11000061035156</v>
+        <v>61.13000106811523</v>
       </c>
       <c r="BG5">
-        <v>61.13000106811523</v>
+        <v>61.65000152587891</v>
       </c>
       <c r="BH5">
-        <v>61.65000152587891</v>
-      </c>
-      <c r="BI5">
         <v>61.40999984741211</v>
       </c>
     </row>
-    <row r="6" spans="1:61">
+    <row r="6" spans="1:60">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>210.2938537597656</v>
+        <v>205.8872375488281</v>
       </c>
       <c r="C6">
-        <v>205.8872375488281</v>
+        <v>205.6783599853516</v>
       </c>
       <c r="D6">
-        <v>205.6783599853516</v>
+        <v>206.7228088378906</v>
       </c>
       <c r="E6">
-        <v>206.7228088378906</v>
+        <v>204.7632141113281</v>
       </c>
       <c r="F6">
-        <v>204.7632141113281</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="G6">
-        <v>205.7181396484375</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="H6">
-        <v>209.4881286621094</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="I6">
-        <v>210.5624237060547</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="J6">
-        <v>205.1014099121094</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="K6">
-        <v>204.8029937744141</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="L6">
-        <v>201.4806365966797</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="M6">
-        <v>204.4349517822266</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="N6">
-        <v>202.8334503173828</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="O6">
-        <v>214.3821563720703</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="P6">
-        <v>223.1754760742188</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="Q6">
-        <v>224.3890380859375</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="R6">
-        <v>231.3819274902344</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="S6">
-        <v>232.3766479492188</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="T6">
-        <v>239.2800140380859</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="U6">
-        <v>243.4900054931641</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="V6">
-        <v>242.2899932861328</v>
+        <v>240</v>
       </c>
       <c r="W6">
-        <v>240</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="X6">
-        <v>242.8699951171875</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="Y6">
-        <v>241.9600067138672</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="Z6">
-        <v>236.8999938964844</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="AA6">
-        <v>242.2299957275391</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="AB6">
-        <v>239.8099975585938</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="AC6">
-        <v>244.0099945068359</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="AD6">
-        <v>246.5800018310547</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="AE6">
-        <v>252.0200042724609</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="AF6">
-        <v>256.0899963378906</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="AG6">
-        <v>254.6600036621094</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="AH6">
-        <v>255.0899963378906</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="AI6">
-        <v>259.1400146484375</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="AJ6">
-        <v>260.7799987792969</v>
+        <v>258.510009765625</v>
       </c>
       <c r="AK6">
-        <v>258.510009765625</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="AL6">
-        <v>259.4700012207031</v>
+        <v>257.0599975585938</v>
       </c>
       <c r="AM6">
-        <v>257.0599975585938</v>
+        <v>264.9299926757812</v>
       </c>
       <c r="AN6">
-        <v>264.9299926757812</v>
+        <v>264.6300048828125</v>
       </c>
       <c r="AO6">
-        <v>264.6300048828125</v>
+        <v>274.2099914550781</v>
       </c>
       <c r="AP6">
-        <v>274.2099914550781</v>
+        <v>273.1300048828125</v>
       </c>
       <c r="AQ6">
-        <v>273.1300048828125</v>
+        <v>261.75</v>
       </c>
       <c r="AR6">
-        <v>261.75</v>
+        <v>256.7799987792969</v>
       </c>
       <c r="AS6">
-        <v>256.7799987792969</v>
+        <v>256.4800109863281</v>
       </c>
       <c r="AT6">
-        <v>256.4800109863281</v>
+        <v>255.8699951171875</v>
       </c>
       <c r="AU6">
-        <v>255.8699951171875</v>
+        <v>255.75</v>
       </c>
       <c r="AV6">
-        <v>255.75</v>
+        <v>253.5500030517578</v>
       </c>
       <c r="AW6">
-        <v>253.5500030517578</v>
+        <v>252.25</v>
       </c>
       <c r="AX6">
-        <v>252.25</v>
+        <v>255.3099975585938</v>
       </c>
       <c r="AY6">
-        <v>255.3099975585938</v>
+        <v>264.2300109863281</v>
       </c>
       <c r="AZ6">
-        <v>264.2300109863281</v>
+        <v>264.5799865722656</v>
       </c>
       <c r="BA6">
-        <v>264.5799865722656</v>
+        <v>269.7200012207031</v>
       </c>
       <c r="BB6">
-        <v>269.7200012207031</v>
+        <v>269.7900085449219</v>
       </c>
       <c r="BC6">
-        <v>269.7900085449219</v>
+        <v>271.6199951171875</v>
       </c>
       <c r="BD6">
-        <v>271.6199951171875</v>
+        <v>281.6000061035156</v>
       </c>
       <c r="BE6">
-        <v>281.6000061035156</v>
+        <v>278.1799926757812</v>
       </c>
       <c r="BF6">
-        <v>278.1799926757812</v>
+        <v>281.4700012207031</v>
       </c>
       <c r="BG6">
-        <v>281.4700012207031</v>
+        <v>292.7300109863281</v>
       </c>
       <c r="BH6">
-        <v>292.7300109863281</v>
-      </c>
-    </row>
-    <row r="7" spans="1:61">
+        <v>297.2900085449219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:60">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>36.18000030517578</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="C7">
-        <v>36.41999816894531</v>
+        <v>36.15000152587891</v>
       </c>
       <c r="D7">
-        <v>36.15000152587891</v>
+        <v>34.7400016784668</v>
       </c>
       <c r="E7">
-        <v>34.7400016784668</v>
+        <v>34.93000030517578</v>
       </c>
       <c r="F7">
-        <v>34.93000030517578</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="G7">
-        <v>36.70000076293945</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="H7">
-        <v>36.33000183105469</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="I7">
-        <v>37.31999969482422</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="J7">
-        <v>36.86999893188477</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="K7">
-        <v>35.79999923706055</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="L7">
-        <v>34.65999984741211</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="M7">
-        <v>36.52999877929688</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="N7">
-        <v>37.63000106811523</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="O7">
-        <v>41.02000045776367</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="P7">
-        <v>40.61999893188477</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="Q7">
-        <v>39.97000122070312</v>
+        <v>40</v>
       </c>
       <c r="R7">
-        <v>40</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="S7">
-        <v>40.47000122070312</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="T7">
-        <v>41.58000183105469</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="U7">
-        <v>42.36999893188477</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="V7">
-        <v>43.45000076293945</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="W7">
-        <v>44.38999938964844</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="X7">
-        <v>43.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="Y7">
-        <v>42.95999908447266</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="Z7">
-        <v>41.34999847412109</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="AA7">
-        <v>41.18999862670898</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="AB7">
-        <v>42.38000106811523</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="AC7">
-        <v>42.54000091552734</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="AD7">
-        <v>43.15000152587891</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="AE7">
-        <v>44.29999923706055</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="AF7">
-        <v>44.70000076293945</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="AG7">
-        <v>44.18000030517578</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="AH7">
-        <v>42.77000045776367</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="AI7">
-        <v>43.54999923706055</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="AJ7">
-        <v>44.84000015258789</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="AK7">
-        <v>44.52999877929688</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="AL7">
-        <v>44.72999954223633</v>
+        <v>45.02999877929688</v>
       </c>
       <c r="AM7">
-        <v>45.02999877929688</v>
+        <v>47.40999984741211</v>
       </c>
       <c r="AN7">
-        <v>47.40999984741211</v>
+        <v>44.79000091552734</v>
       </c>
       <c r="AO7">
-        <v>44.79000091552734</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="AP7">
-        <v>45.45999908447266</v>
+        <v>44.86999893188477</v>
       </c>
       <c r="AQ7">
-        <v>44.86999893188477</v>
+        <v>43.81000137329102</v>
       </c>
       <c r="AR7">
+        <v>42.29999923706055</v>
+      </c>
+      <c r="AS7">
+        <v>43.70000076293945</v>
+      </c>
+      <c r="AT7">
+        <v>43.68000030517578</v>
+      </c>
+      <c r="AU7">
+        <v>42.7400016784668</v>
+      </c>
+      <c r="AV7">
+        <v>42.33000183105469</v>
+      </c>
+      <c r="AW7">
+        <v>42.18999862670898</v>
+      </c>
+      <c r="AX7">
+        <v>41.54000091552734</v>
+      </c>
+      <c r="AY7">
+        <v>43.34000015258789</v>
+      </c>
+      <c r="AZ7">
+        <v>43.68000030517578</v>
+      </c>
+      <c r="BA7">
+        <v>43.84999847412109</v>
+      </c>
+      <c r="BB7">
+        <v>44.09999847412109</v>
+      </c>
+      <c r="BC7">
         <v>43.81000137329102</v>
       </c>
-      <c r="AS7">
-        <v>42.29999923706055</v>
-      </c>
-      <c r="AT7">
-        <v>43.70000076293945</v>
-      </c>
-      <c r="AU7">
-        <v>43.68000030517578</v>
-      </c>
-      <c r="AV7">
-        <v>42.7400016784668</v>
-      </c>
-      <c r="AW7">
-        <v>42.33000183105469</v>
-      </c>
-      <c r="AX7">
-        <v>42.18999862670898</v>
-      </c>
-      <c r="AY7">
-        <v>41.54000091552734</v>
-      </c>
-      <c r="AZ7">
-        <v>43.34000015258789</v>
-      </c>
-      <c r="BA7">
-        <v>43.68000030517578</v>
-      </c>
-      <c r="BB7">
-        <v>43.84999847412109</v>
-      </c>
-      <c r="BC7">
-        <v>44.09999847412109</v>
-      </c>
       <c r="BD7">
-        <v>43.81000137329102</v>
+        <v>45.47000122070312</v>
       </c>
       <c r="BE7">
-        <v>45.47000122070312</v>
+        <v>45.88000106811523</v>
       </c>
       <c r="BF7">
-        <v>45.88000106811523</v>
+        <v>46.84000015258789</v>
       </c>
       <c r="BG7">
-        <v>46.84000015258789</v>
+        <v>48.0099983215332</v>
       </c>
       <c r="BH7">
-        <v>48.0099983215332</v>
-      </c>
-      <c r="BI7">
         <v>47.36999893188477</v>
       </c>
     </row>
-    <row r="8" spans="1:61">
+    <row r="8" spans="1:60">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>211.8229827880859</v>
+        <v>208.5266571044922</v>
       </c>
       <c r="C8">
-        <v>208.5266571044922</v>
+        <v>206.6088104248047</v>
       </c>
       <c r="D8">
-        <v>206.6088104248047</v>
+        <v>196.2903594970703</v>
       </c>
       <c r="E8">
-        <v>196.2903594970703</v>
+        <v>196.789794921875</v>
       </c>
       <c r="F8">
-        <v>196.789794921875</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="G8">
-        <v>189.7976226806641</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="H8">
-        <v>194.8219909667969</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="I8">
-        <v>200.5256195068359</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="J8">
-        <v>206.4090423583984</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="K8">
-        <v>211.7031097412109</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="L8">
-        <v>218.9749755859375</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="M8">
-        <v>218.7452392578125</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="N8">
-        <v>223.7096862792969</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="O8">
+        <v>217.2568969726562</v>
+      </c>
+      <c r="P8">
+        <v>223.8395233154297</v>
+      </c>
+      <c r="Q8">
+        <v>225.0481872558594</v>
+      </c>
+      <c r="R8">
+        <v>224.9083404541016</v>
+      </c>
+      <c r="S8">
+        <v>224.7584991455078</v>
+      </c>
+      <c r="T8">
+        <v>219.4944000244141</v>
+      </c>
+      <c r="U8">
+        <v>217.3168334960938</v>
+      </c>
+      <c r="V8">
+        <v>216.6076354980469</v>
+      </c>
+      <c r="W8">
+        <v>214.4800109863281</v>
+      </c>
+      <c r="X8">
+        <v>208.2469787597656</v>
+      </c>
+      <c r="Y8">
+        <v>212.8118743896484</v>
+      </c>
+      <c r="Z8">
+        <v>209.4256591796875</v>
+      </c>
+      <c r="AA8">
+        <v>227.7251739501953</v>
+      </c>
+      <c r="AB8">
         <v>217.3068389892578</v>
       </c>
-      <c r="P8">
-        <v>217.2568969726562</v>
-      </c>
-      <c r="Q8">
-        <v>223.8395233154297</v>
-      </c>
-      <c r="R8">
-        <v>225.0481872558594</v>
-      </c>
-      <c r="S8">
-        <v>224.9083404541016</v>
-      </c>
-      <c r="T8">
-        <v>224.7584991455078</v>
-      </c>
-      <c r="U8">
-        <v>219.4944000244141</v>
-      </c>
-      <c r="V8">
-        <v>217.3168334960938</v>
-      </c>
-      <c r="W8">
-        <v>216.6076354980469</v>
-      </c>
-      <c r="X8">
-        <v>214.4800109863281</v>
-      </c>
-      <c r="Y8">
-        <v>208.2469787597656</v>
-      </c>
-      <c r="Z8">
-        <v>212.8118743896484</v>
-      </c>
-      <c r="AA8">
-        <v>209.4256591796875</v>
-      </c>
-      <c r="AB8">
-        <v>227.7251739501953</v>
-      </c>
       <c r="AC8">
-        <v>217.3068389892578</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="AD8">
-        <v>220.5332336425781</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="AE8">
-        <v>217.1969757080078</v>
+        <v>224.1591796875</v>
       </c>
       <c r="AF8">
-        <v>224.1591796875</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="AG8">
-        <v>228.1946563720703</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="AH8">
-        <v>230.1025238037109</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="AI8">
-        <v>225.4776916503906</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="AJ8">
-        <v>223.4199981689453</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="AK8">
-        <v>218.3600006103516</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="AL8">
-        <v>218.2899932861328</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="AM8">
-        <v>210.9600067138672</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="AN8">
-        <v>212.1699981689453</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="AO8">
-        <v>213.8999938964844</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="AP8">
-        <v>219.3399963378906</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="AQ8">
-        <v>222.2700042724609</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="AR8">
-        <v>227.3800048828125</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="AS8">
-        <v>228.8699951171875</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="AT8">
-        <v>225.5099945068359</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="AU8">
-        <v>224.5800018310547</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="AV8">
-        <v>225.0700073242188</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="AW8">
-        <v>228.8600006103516</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="AX8">
-        <v>227.2100067138672</v>
+        <v>228.3800048828125</v>
       </c>
       <c r="AY8">
-        <v>228.3800048828125</v>
+        <v>230.8600006103516</v>
       </c>
       <c r="AZ8">
-        <v>230.8600006103516</v>
+        <v>233.9499969482422</v>
       </c>
       <c r="BA8">
-        <v>233.9499969482422</v>
+        <v>238.8999938964844</v>
       </c>
       <c r="BB8">
-        <v>238.8999938964844</v>
+        <v>239.2400054931641</v>
       </c>
       <c r="BC8">
-        <v>239.2400054931641</v>
+        <v>237.4700012207031</v>
       </c>
       <c r="BD8">
-        <v>237.4700012207031</v>
+        <v>230.4799957275391</v>
       </c>
       <c r="BE8">
-        <v>230.4799957275391</v>
+        <v>229.2799987792969</v>
       </c>
       <c r="BF8">
-        <v>229.2799987792969</v>
+        <v>226.3200073242188</v>
       </c>
       <c r="BG8">
-        <v>226.3200073242188</v>
+        <v>228.5200042724609</v>
       </c>
       <c r="BH8">
-        <v>228.5200042724609</v>
-      </c>
-      <c r="BI8">
         <v>221.3000030517578</v>
       </c>
     </row>
-    <row r="9" spans="1:61">
+    <row r="9" spans="1:60">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>370.8121643066406</v>
+        <v>375.0875549316406</v>
       </c>
       <c r="C9">
-        <v>375.0875549316406</v>
+        <v>385.9404907226562</v>
       </c>
       <c r="D9">
-        <v>385.9404907226562</v>
+        <v>389.0199584960938</v>
       </c>
       <c r="E9">
-        <v>389.0199584960938</v>
+        <v>395.8665161132812</v>
       </c>
       <c r="F9">
-        <v>395.8665161132812</v>
+        <v>387.6845092773438</v>
       </c>
       <c r="G9">
-        <v>387.6845092773438</v>
+        <v>374.7088623046875</v>
       </c>
       <c r="H9">
-        <v>374.7088623046875</v>
+        <v>373.0844116210938</v>
       </c>
       <c r="I9">
-        <v>373.0844116210938</v>
+        <v>372.5462646484375</v>
       </c>
       <c r="J9">
-        <v>372.5462646484375</v>
+        <v>375.8648986816406</v>
       </c>
       <c r="K9">
-        <v>375.8648986816406</v>
+        <v>381.1468811035156</v>
       </c>
       <c r="L9">
-        <v>381.1468811035156</v>
+        <v>384.6847534179688</v>
       </c>
       <c r="M9">
-        <v>384.6847534179688</v>
+        <v>383.0005187988281</v>
       </c>
       <c r="N9">
-        <v>383.0005187988281</v>
+        <v>374.3401184082031</v>
       </c>
       <c r="O9">
-        <v>374.3401184082031</v>
+        <v>374.3301391601562</v>
       </c>
       <c r="P9">
-        <v>374.3301391601562</v>
+        <v>368.8987426757812</v>
       </c>
       <c r="Q9">
-        <v>368.8987426757812</v>
+        <v>368.7392883300781</v>
       </c>
       <c r="R9">
-        <v>368.7392883300781</v>
+        <v>369.0980224609375</v>
       </c>
       <c r="S9">
-        <v>369.0980224609375</v>
+        <v>363.2680053710938</v>
       </c>
       <c r="T9">
-        <v>363.2680053710938</v>
+        <v>366.6763305664062</v>
       </c>
       <c r="U9">
-        <v>366.6763305664062</v>
+        <v>360.9857788085938</v>
       </c>
       <c r="V9">
-        <v>360.9857788085938</v>
+        <v>363.248046875</v>
       </c>
       <c r="W9">
-        <v>363.248046875</v>
+        <v>362.3411254882812</v>
       </c>
       <c r="X9">
-        <v>362.3411254882812</v>
+        <v>369.2873840332031</v>
       </c>
       <c r="Y9">
-        <v>369.2873840332031</v>
+        <v>368.4004516601562</v>
       </c>
       <c r="Z9">
-        <v>368.4004516601562</v>
+        <v>369.8853454589844</v>
       </c>
       <c r="AA9">
-        <v>369.8853454589844</v>
+        <v>368.071533203125</v>
       </c>
       <c r="AB9">
-        <v>368.071533203125</v>
+        <v>368.6396179199219</v>
       </c>
       <c r="AC9">
-        <v>368.6396179199219</v>
+        <v>364.6831359863281</v>
       </c>
       <c r="AD9">
-        <v>364.6831359863281</v>
+        <v>362.6799926757812</v>
       </c>
       <c r="AE9">
-        <v>362.6799926757812</v>
+        <v>364.9322814941406</v>
       </c>
       <c r="AF9">
-        <v>364.9322814941406</v>
+        <v>373.0644836425781</v>
       </c>
       <c r="AG9">
-        <v>373.0644836425781</v>
+        <v>368.0914916992188</v>
       </c>
       <c r="AH9">
-        <v>368.0914916992188</v>
+        <v>364.4140625</v>
       </c>
       <c r="AI9">
-        <v>364.4140625</v>
+        <v>365.6000061035156</v>
       </c>
       <c r="AJ9">
-        <v>365.6000061035156</v>
+        <v>367.5599975585938</v>
       </c>
       <c r="AK9">
-        <v>367.5599975585938</v>
+        <v>375.2000122070312</v>
       </c>
       <c r="AL9">
-        <v>375.2000122070312</v>
+        <v>378.0499877929688</v>
       </c>
       <c r="AM9">
-        <v>378.0499877929688</v>
+        <v>377.9700012207031</v>
       </c>
       <c r="AN9">
-        <v>377.9700012207031</v>
+        <v>378.9200134277344</v>
       </c>
       <c r="AO9">
-        <v>378.9200134277344</v>
+        <v>379.489990234375</v>
       </c>
       <c r="AP9">
-        <v>379.489990234375</v>
+        <v>374.6199951171875</v>
       </c>
       <c r="AQ9">
-        <v>374.6199951171875</v>
+        <v>371.1300048828125</v>
       </c>
       <c r="AR9">
-        <v>371.1300048828125</v>
+        <v>362.010009765625</v>
       </c>
       <c r="AS9">
-        <v>362.010009765625</v>
+        <v>360.3900146484375</v>
       </c>
       <c r="AT9">
-        <v>360.3900146484375</v>
+        <v>362.3900146484375</v>
       </c>
       <c r="AU9">
-        <v>362.3900146484375</v>
+        <v>363.0400085449219</v>
       </c>
       <c r="AV9">
-        <v>363.0400085449219</v>
+        <v>363.1600036621094</v>
       </c>
       <c r="AW9">
-        <v>363.1600036621094</v>
+        <v>363.2099914550781</v>
       </c>
       <c r="AX9">
-        <v>363.2099914550781</v>
+        <v>356.510009765625</v>
       </c>
       <c r="AY9">
-        <v>356.510009765625</v>
+        <v>361.6400146484375</v>
       </c>
       <c r="AZ9">
-        <v>361.6400146484375</v>
+        <v>360.3800048828125</v>
       </c>
       <c r="BA9">
-        <v>360.3800048828125</v>
+        <v>360.7000122070312</v>
       </c>
       <c r="BB9">
-        <v>360.7000122070312</v>
+        <v>360.6400146484375</v>
       </c>
       <c r="BC9">
-        <v>360.6400146484375</v>
+        <v>360.6099853515625</v>
       </c>
       <c r="BD9">
-        <v>360.6099853515625</v>
+        <v>370.2699890136719</v>
       </c>
       <c r="BE9">
-        <v>370.2699890136719</v>
+        <v>368.75</v>
       </c>
       <c r="BF9">
-        <v>368.75</v>
+        <v>371.6799926757812</v>
       </c>
       <c r="BG9">
-        <v>371.6799926757812</v>
+        <v>373.2799987792969</v>
       </c>
       <c r="BH9">
-        <v>373.2799987792969</v>
-      </c>
-      <c r="BI9">
         <v>377.8200073242188</v>
       </c>
     </row>
-    <row r="10" spans="1:61">
+    <row r="10" spans="1:60">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>341.6881713867188</v>
+        <v>318.1334533691406</v>
       </c>
       <c r="C10">
-        <v>318.1334533691406</v>
+        <v>318.8829650878906</v>
       </c>
       <c r="D10">
-        <v>318.8829650878906</v>
+        <v>326.3581237792969</v>
       </c>
       <c r="E10">
-        <v>326.3581237792969</v>
+        <v>332.3842163085938</v>
       </c>
       <c r="F10">
-        <v>332.3842163085938</v>
+        <v>335.5421752929688</v>
       </c>
       <c r="G10">
-        <v>335.5421752929688</v>
+        <v>333.4635009765625</v>
       </c>
       <c r="H10">
-        <v>333.4635009765625</v>
+        <v>356.4186096191406</v>
       </c>
       <c r="I10">
-        <v>356.4186096191406</v>
+        <v>372.2283325195312</v>
       </c>
       <c r="J10">
-        <v>372.2283325195312</v>
+        <v>375.1064758300781</v>
       </c>
       <c r="K10">
-        <v>375.1064758300781</v>
+        <v>359.8963623046875</v>
       </c>
       <c r="L10">
-        <v>359.8963623046875</v>
+        <v>356.3886108398438</v>
       </c>
       <c r="M10">
-        <v>356.3886108398438</v>
+        <v>353.2406616210938</v>
       </c>
       <c r="N10">
-        <v>353.2406616210938</v>
+        <v>355.609130859375</v>
       </c>
       <c r="O10">
-        <v>355.609130859375</v>
+        <v>342.7774658203125</v>
       </c>
       <c r="P10">
-        <v>342.7774658203125</v>
+        <v>342.1478576660156</v>
       </c>
       <c r="Q10">
-        <v>342.1478576660156</v>
+        <v>343.7168579101562</v>
       </c>
       <c r="R10">
-        <v>343.7168579101562</v>
+        <v>343.3171081542969</v>
       </c>
       <c r="S10">
-        <v>343.3171081542969</v>
+        <v>341.2284851074219</v>
       </c>
       <c r="T10">
-        <v>341.2284851074219</v>
+        <v>341.0585632324219</v>
       </c>
       <c r="U10">
-        <v>341.0585632324219</v>
+        <v>341.4783325195312</v>
       </c>
       <c r="V10">
-        <v>341.4783325195312</v>
+        <v>337.9805908203125</v>
       </c>
       <c r="W10">
-        <v>337.9805908203125</v>
+        <v>341.5282592773438</v>
       </c>
       <c r="X10">
-        <v>341.5282592773438</v>
+        <v>344.3664245605469</v>
       </c>
       <c r="Y10">
-        <v>344.3664245605469</v>
+        <v>343.1172485351562</v>
       </c>
       <c r="Z10">
-        <v>343.1172485351562</v>
+        <v>338.8800048828125</v>
       </c>
       <c r="AA10">
-        <v>338.8800048828125</v>
+        <v>337.4908752441406</v>
       </c>
       <c r="AB10">
-        <v>337.4908752441406</v>
+        <v>342.6575317382812</v>
       </c>
       <c r="AC10">
-        <v>342.6575317382812</v>
+        <v>335.1923828125</v>
       </c>
       <c r="AD10">
-        <v>335.1923828125</v>
+        <v>331.8145751953125</v>
       </c>
       <c r="AE10">
-        <v>331.8145751953125</v>
+        <v>333.5634460449219</v>
       </c>
       <c r="AF10">
-        <v>333.5634460449219</v>
+        <v>338.8599853515625</v>
       </c>
       <c r="AG10">
-        <v>338.8599853515625</v>
+        <v>335.3099975585938</v>
       </c>
       <c r="AH10">
-        <v>335.3099975585938</v>
+        <v>335.3800048828125</v>
       </c>
       <c r="AI10">
-        <v>335.3800048828125</v>
+        <v>328.3800048828125</v>
       </c>
       <c r="AJ10">
-        <v>328.3800048828125</v>
+        <v>330.3900146484375</v>
       </c>
       <c r="AK10">
-        <v>330.3900146484375</v>
+        <v>335.4500122070312</v>
       </c>
       <c r="AL10">
-        <v>335.4500122070312</v>
+        <v>345.7099914550781</v>
       </c>
       <c r="AM10">
-        <v>345.7099914550781</v>
+        <v>341.4299926757812</v>
       </c>
       <c r="AN10">
-        <v>341.4299926757812</v>
+        <v>339.3599853515625</v>
       </c>
       <c r="AO10">
-        <v>339.3599853515625</v>
+        <v>343.6799926757812</v>
       </c>
       <c r="AP10">
-        <v>343.6799926757812</v>
+        <v>344.4100036621094</v>
       </c>
       <c r="AQ10">
-        <v>344.4100036621094</v>
+        <v>350.8699951171875</v>
       </c>
       <c r="AR10">
-        <v>350.8699951171875</v>
+        <v>347.4100036621094</v>
       </c>
       <c r="AS10">
-        <v>347.4100036621094</v>
+        <v>334.9800109863281</v>
       </c>
       <c r="AT10">
-        <v>334.9800109863281</v>
+        <v>339.010009765625</v>
       </c>
       <c r="AU10">
-        <v>339.010009765625</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="AV10">
-        <v>341.0799865722656</v>
+        <v>339.1600036621094</v>
       </c>
       <c r="AW10">
-        <v>339.1600036621094</v>
+        <v>337.3200073242188</v>
       </c>
       <c r="AX10">
-        <v>337.3200073242188</v>
+        <v>340.739990234375</v>
       </c>
       <c r="AY10">
-        <v>340.739990234375</v>
+        <v>334.9299926757812</v>
       </c>
       <c r="AZ10">
-        <v>334.9299926757812</v>
+        <v>340.3500061035156</v>
       </c>
       <c r="BA10">
-        <v>340.3500061035156</v>
+        <v>343.8299865722656</v>
       </c>
       <c r="BB10">
-        <v>343.8299865722656</v>
+        <v>344.5899963378906</v>
       </c>
       <c r="BC10">
-        <v>344.5899963378906</v>
+        <v>347.3699951171875</v>
       </c>
       <c r="BD10">
-        <v>347.3699951171875</v>
+        <v>344.8599853515625</v>
       </c>
       <c r="BE10">
-        <v>344.8599853515625</v>
+        <v>347.8599853515625</v>
       </c>
       <c r="BF10">
-        <v>347.8599853515625</v>
+        <v>348.9700012207031</v>
       </c>
       <c r="BG10">
-        <v>348.9700012207031</v>
+        <v>349.5199890136719</v>
       </c>
       <c r="BH10">
-        <v>349.5199890136719</v>
-      </c>
-    </row>
-    <row r="11" spans="1:61">
+        <v>343.6499938964844</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>65.88999938964844</v>
+        <v>63.7400016784668</v>
       </c>
       <c r="C11">
-        <v>63.7400016784668</v>
+        <v>63.40999984741211</v>
       </c>
       <c r="D11">
-        <v>63.40999984741211</v>
+        <v>64.08000183105469</v>
       </c>
       <c r="E11">
-        <v>64.08000183105469</v>
+        <v>63.90999984741211</v>
       </c>
       <c r="F11">
-        <v>63.90999984741211</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="G11">
+        <v>60.84000015258789</v>
+      </c>
+      <c r="H11">
+        <v>62.22000122070312</v>
+      </c>
+      <c r="I11">
+        <v>63.7599983215332</v>
+      </c>
+      <c r="J11">
+        <v>64.06999969482422</v>
+      </c>
+      <c r="K11">
+        <v>66.98999786376953</v>
+      </c>
+      <c r="L11">
+        <v>64.19999694824219</v>
+      </c>
+      <c r="M11">
+        <v>65.76999664306641</v>
+      </c>
+      <c r="N11">
+        <v>66.56999969482422</v>
+      </c>
+      <c r="O11">
+        <v>64.87999725341797</v>
+      </c>
+      <c r="P11">
+        <v>67.06999969482422</v>
+      </c>
+      <c r="Q11">
+        <v>66.04000091552734</v>
+      </c>
+      <c r="R11">
+        <v>67.47000122070312</v>
+      </c>
+      <c r="S11">
+        <v>64.41000366210938</v>
+      </c>
+      <c r="T11">
+        <v>65.22000122070312</v>
+      </c>
+      <c r="U11">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="V11">
+        <v>64.13999938964844</v>
+      </c>
+      <c r="W11">
+        <v>65.01999664306641</v>
+      </c>
+      <c r="X11">
+        <v>65.65000152587891</v>
+      </c>
+      <c r="Y11">
+        <v>65</v>
+      </c>
+      <c r="Z11">
+        <v>65.47000122070312</v>
+      </c>
+      <c r="AA11">
+        <v>65.33000183105469</v>
+      </c>
+      <c r="AB11">
+        <v>64.75</v>
+      </c>
+      <c r="AC11">
+        <v>64.33999633789062</v>
+      </c>
+      <c r="AD11">
+        <v>65.23000335693359</v>
+      </c>
+      <c r="AE11">
+        <v>67.33999633789062</v>
+      </c>
+      <c r="AF11">
+        <v>68.01999664306641</v>
+      </c>
+      <c r="AG11">
+        <v>67.04000091552734</v>
+      </c>
+      <c r="AH11">
+        <v>64.58000183105469</v>
+      </c>
+      <c r="AI11">
+        <v>64.05999755859375</v>
+      </c>
+      <c r="AJ11">
+        <v>65.40000152587891</v>
+      </c>
+      <c r="AK11">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="AL11">
+        <v>69.41000366210938</v>
+      </c>
+      <c r="AM11">
+        <v>67.66000366210938</v>
+      </c>
+      <c r="AN11">
+        <v>66.01000213623047</v>
+      </c>
+      <c r="AO11">
+        <v>67.09999847412109</v>
+      </c>
+      <c r="AP11">
+        <v>65.11000061035156</v>
+      </c>
+      <c r="AQ11">
+        <v>64.98999786376953</v>
+      </c>
+      <c r="AR11">
+        <v>63.29999923706055</v>
+      </c>
+      <c r="AS11">
+        <v>62.08000183105469</v>
+      </c>
+      <c r="AT11">
+        <v>61.91999816894531</v>
+      </c>
+      <c r="AU11">
         <v>61.81999969482422</v>
       </c>
-      <c r="H11">
-        <v>60.84000015258789</v>
-      </c>
-      <c r="I11">
-        <v>62.22000122070312</v>
-      </c>
-      <c r="J11">
-        <v>63.7599983215332</v>
-      </c>
-      <c r="K11">
-        <v>64.06999969482422</v>
-      </c>
-      <c r="L11">
-        <v>66.98999786376953</v>
-      </c>
-      <c r="M11">
-        <v>64.19999694824219</v>
-      </c>
-      <c r="N11">
-        <v>65.76999664306641</v>
-      </c>
-      <c r="O11">
-        <v>66.56999969482422</v>
-      </c>
-      <c r="P11">
-        <v>64.87999725341797</v>
-      </c>
-      <c r="Q11">
-        <v>67.06999969482422</v>
-      </c>
-      <c r="R11">
-        <v>66.04000091552734</v>
-      </c>
-      <c r="S11">
-        <v>67.47000122070312</v>
-      </c>
-      <c r="T11">
-        <v>64.41000366210938</v>
-      </c>
-      <c r="U11">
-        <v>65.22000122070312</v>
-      </c>
-      <c r="V11">
-        <v>64.69999694824219</v>
-      </c>
-      <c r="W11">
-        <v>64.13999938964844</v>
-      </c>
-      <c r="X11">
-        <v>65.01999664306641</v>
-      </c>
-      <c r="Y11">
-        <v>65.65000152587891</v>
-      </c>
-      <c r="Z11">
-        <v>65</v>
-      </c>
-      <c r="AA11">
-        <v>65.47000122070312</v>
-      </c>
-      <c r="AB11">
-        <v>65.33000183105469</v>
-      </c>
-      <c r="AC11">
-        <v>64.75</v>
-      </c>
-      <c r="AD11">
-        <v>64.33999633789062</v>
-      </c>
-      <c r="AE11">
-        <v>65.23000335693359</v>
-      </c>
-      <c r="AF11">
-        <v>67.33999633789062</v>
-      </c>
-      <c r="AG11">
-        <v>68.01999664306641</v>
-      </c>
-      <c r="AH11">
-        <v>67.04000091552734</v>
-      </c>
-      <c r="AI11">
-        <v>64.58000183105469</v>
-      </c>
-      <c r="AJ11">
-        <v>64.05999755859375</v>
-      </c>
-      <c r="AK11">
-        <v>65.40000152587891</v>
-      </c>
-      <c r="AL11">
-        <v>66.41999816894531</v>
-      </c>
-      <c r="AM11">
-        <v>69.41000366210938</v>
-      </c>
-      <c r="AN11">
-        <v>67.66000366210938</v>
-      </c>
-      <c r="AO11">
-        <v>66.01000213623047</v>
-      </c>
-      <c r="AP11">
-        <v>67.09999847412109</v>
-      </c>
-      <c r="AQ11">
-        <v>65.11000061035156</v>
-      </c>
-      <c r="AR11">
+      <c r="AV11">
+        <v>62.52999877929688</v>
+      </c>
+      <c r="AW11">
+        <v>62.20999908447266</v>
+      </c>
+      <c r="AX11">
+        <v>62.11999893188477</v>
+      </c>
+      <c r="AY11">
+        <v>60.9900016784668</v>
+      </c>
+      <c r="AZ11">
+        <v>62.9900016784668</v>
+      </c>
+      <c r="BA11">
+        <v>64.30000305175781</v>
+      </c>
+      <c r="BB11">
+        <v>64.61000061035156</v>
+      </c>
+      <c r="BC11">
         <v>64.98999786376953</v>
       </c>
-      <c r="AS11">
-        <v>63.29999923706055</v>
-      </c>
-      <c r="AT11">
-        <v>62.08000183105469</v>
-      </c>
-      <c r="AU11">
-        <v>61.91999816894531</v>
-      </c>
-      <c r="AV11">
-        <v>61.81999969482422</v>
-      </c>
-      <c r="AW11">
-        <v>62.52999877929688</v>
-      </c>
-      <c r="AX11">
-        <v>62.20999908447266</v>
-      </c>
-      <c r="AY11">
-        <v>62.11999893188477</v>
-      </c>
-      <c r="AZ11">
-        <v>60.9900016784668</v>
-      </c>
-      <c r="BA11">
-        <v>62.9900016784668</v>
-      </c>
-      <c r="BB11">
-        <v>64.30000305175781</v>
-      </c>
-      <c r="BC11">
-        <v>64.61000061035156</v>
-      </c>
       <c r="BD11">
-        <v>64.98999786376953</v>
+        <v>64.54000091552734</v>
       </c>
       <c r="BE11">
-        <v>64.54000091552734</v>
+        <v>65.36000061035156</v>
       </c>
       <c r="BF11">
-        <v>65.36000061035156</v>
+        <v>67.01999664306641</v>
       </c>
       <c r="BG11">
-        <v>67.01999664306641</v>
+        <v>68.86000061035156</v>
       </c>
       <c r="BH11">
-        <v>68.86000061035156</v>
-      </c>
-      <c r="BI11">
         <v>70.16000366210938</v>
       </c>
     </row>
-    <row r="12" spans="1:61">
+    <row r="12" spans="1:60">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>341.8702392578125</v>
+        <v>317.4859313964844</v>
       </c>
       <c r="C12">
-        <v>317.4859313964844</v>
+        <v>319.5346069335938</v>
       </c>
       <c r="D12">
-        <v>319.5346069335938</v>
+        <v>326.3502197265625</v>
       </c>
       <c r="E12">
-        <v>326.3502197265625</v>
+        <v>333.4956359863281</v>
       </c>
       <c r="F12">
-        <v>333.4956359863281</v>
+        <v>336.4937133789062</v>
       </c>
       <c r="G12">
-        <v>336.4937133789062</v>
+        <v>333.4456787109375</v>
       </c>
       <c r="H12">
-        <v>333.4456787109375</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="I12">
-        <v>355.9012451171875</v>
+        <v>373.2700805664062</v>
       </c>
       <c r="J12">
-        <v>373.2700805664062</v>
+        <v>377.4074096679688</v>
       </c>
       <c r="K12">
-        <v>377.4074096679688</v>
+        <v>362.1971740722656</v>
       </c>
       <c r="L12">
-        <v>362.1971740722656</v>
+        <v>357.5202026367188</v>
       </c>
       <c r="M12">
-        <v>357.5202026367188</v>
+        <v>354.0723876953125</v>
       </c>
       <c r="N12">
-        <v>354.0723876953125</v>
+        <v>357.2903442382812</v>
       </c>
       <c r="O12">
-        <v>357.2903442382812</v>
+        <v>343.5791320800781</v>
       </c>
       <c r="P12">
-        <v>343.5791320800781</v>
+        <v>343.3193359375</v>
       </c>
       <c r="Q12">
-        <v>343.3193359375</v>
+        <v>346.1375122070312</v>
       </c>
       <c r="R12">
-        <v>346.1375122070312</v>
+        <v>345.6777954101562</v>
       </c>
       <c r="S12">
-        <v>345.6777954101562</v>
+        <v>343.7790222167969</v>
       </c>
       <c r="T12">
-        <v>343.7790222167969</v>
+        <v>343.9789123535156</v>
       </c>
       <c r="U12">
-        <v>343.9789123535156</v>
+        <v>344.4985656738281</v>
       </c>
       <c r="V12">
-        <v>344.4985656738281</v>
+        <v>340.451171875</v>
       </c>
       <c r="W12">
-        <v>340.451171875</v>
+        <v>344.5985107421875</v>
       </c>
       <c r="X12">
-        <v>344.5985107421875</v>
+        <v>347.83642578125</v>
       </c>
       <c r="Y12">
-        <v>347.83642578125</v>
+        <v>346.7371215820312</v>
       </c>
       <c r="Z12">
-        <v>346.7371215820312</v>
+        <v>341.7803039550781</v>
       </c>
       <c r="AA12">
-        <v>341.7803039550781</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="AB12">
-        <v>340.4311828613281</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="AC12">
-        <v>346.3673706054688</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="AD12">
-        <v>339.1320190429688</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="AE12">
-        <v>334.8047790527344</v>
+        <v>336.9034423828125</v>
       </c>
       <c r="AF12">
-        <v>336.9034423828125</v>
+        <v>342.260009765625</v>
       </c>
       <c r="AG12">
-        <v>342.260009765625</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="AH12">
-        <v>338.4599914550781</v>
+        <v>338.3599853515625</v>
       </c>
       <c r="AI12">
-        <v>338.3599853515625</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="AJ12">
-        <v>330.6499938964844</v>
+        <v>332.6000061035156</v>
       </c>
       <c r="AK12">
-        <v>332.6000061035156</v>
+        <v>338.5</v>
       </c>
       <c r="AL12">
-        <v>338.5</v>
+        <v>349.3900146484375</v>
       </c>
       <c r="AM12">
-        <v>349.3900146484375</v>
+        <v>344.9800109863281</v>
       </c>
       <c r="AN12">
-        <v>344.9800109863281</v>
+        <v>342.8699951171875</v>
       </c>
       <c r="AO12">
-        <v>342.8699951171875</v>
+        <v>347.3299865722656</v>
       </c>
       <c r="AP12">
-        <v>347.3299865722656</v>
+        <v>349.5400085449219</v>
       </c>
       <c r="AQ12">
-        <v>349.5400085449219</v>
+        <v>354.9700012207031</v>
       </c>
       <c r="AR12">
-        <v>354.9700012207031</v>
+        <v>351.1600036621094</v>
       </c>
       <c r="AS12">
-        <v>351.1600036621094</v>
+        <v>337.8299865722656</v>
       </c>
       <c r="AT12">
-        <v>337.8299865722656</v>
+        <v>342.3599853515625</v>
       </c>
       <c r="AU12">
-        <v>342.3599853515625</v>
+        <v>343.9200134277344</v>
       </c>
       <c r="AV12">
-        <v>343.9200134277344</v>
+        <v>342.75</v>
       </c>
       <c r="AW12">
-        <v>342.75</v>
+        <v>340.9200134277344</v>
       </c>
       <c r="AX12">
-        <v>340.9200134277344</v>
+        <v>344.0799865722656</v>
       </c>
       <c r="AY12">
-        <v>344.0799865722656</v>
+        <v>338.239990234375</v>
       </c>
       <c r="AZ12">
-        <v>338.239990234375</v>
+        <v>343.5</v>
       </c>
       <c r="BA12">
-        <v>343.5</v>
+        <v>346.4700012207031</v>
       </c>
       <c r="BB12">
-        <v>346.4700012207031</v>
+        <v>347.6799926757812</v>
       </c>
       <c r="BC12">
-        <v>347.6799926757812</v>
+        <v>350.5</v>
       </c>
       <c r="BD12">
-        <v>350.5</v>
+        <v>348.2900085449219</v>
       </c>
       <c r="BE12">
-        <v>348.2900085449219</v>
+        <v>351.6600036621094</v>
       </c>
       <c r="BF12">
-        <v>351.6600036621094</v>
+        <v>352.7200012207031</v>
       </c>
       <c r="BG12">
-        <v>352.7200012207031</v>
+        <v>353.7799987792969</v>
       </c>
       <c r="BH12">
-        <v>353.7799987792969</v>
-      </c>
-      <c r="BI12">
         <v>347.6400146484375</v>
       </c>
     </row>
-    <row r="13" spans="1:61">
+    <row r="13" spans="1:60">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>250.7862701416016</v>
+        <v>253.4651184082031</v>
       </c>
       <c r="C13">
-        <v>253.4651184082031</v>
+        <v>258.8925170898438</v>
       </c>
       <c r="D13">
-        <v>258.8925170898438</v>
+        <v>260.1871337890625</v>
       </c>
       <c r="E13">
-        <v>260.1871337890625</v>
+        <v>271.2909240722656</v>
       </c>
       <c r="F13">
-        <v>271.2909240722656</v>
+        <v>273.2527770996094</v>
       </c>
       <c r="G13">
-        <v>273.2527770996094</v>
+        <v>264.2801208496094</v>
       </c>
       <c r="H13">
-        <v>264.2801208496094</v>
+        <v>262.9854736328125</v>
       </c>
       <c r="I13">
-        <v>262.9854736328125</v>
+        <v>261.5912780761719</v>
       </c>
       <c r="J13">
-        <v>261.5912780761719</v>
+        <v>261.4718017578125</v>
       </c>
       <c r="K13">
-        <v>261.4718017578125</v>
+        <v>263.4933776855469</v>
       </c>
       <c r="L13">
-        <v>263.4933776855469</v>
+        <v>273.9697570800781</v>
       </c>
       <c r="M13">
-        <v>273.9697570800781</v>
+        <v>265.8934020996094</v>
       </c>
       <c r="N13">
-        <v>265.8934020996094</v>
+        <v>268.5523376464844</v>
       </c>
       <c r="O13">
-        <v>268.5523376464844</v>
+        <v>261.1431579589844</v>
       </c>
       <c r="P13">
-        <v>261.1431579589844</v>
+        <v>254.7796325683594</v>
       </c>
       <c r="Q13">
-        <v>254.7796325683594</v>
+        <v>259.4004211425781</v>
       </c>
       <c r="R13">
-        <v>259.4004211425781</v>
+        <v>260.3265686035156</v>
       </c>
       <c r="S13">
-        <v>260.3265686035156</v>
+        <v>257.0302734375</v>
       </c>
       <c r="T13">
-        <v>257.0302734375</v>
+        <v>260.067626953125</v>
       </c>
       <c r="U13">
-        <v>260.067626953125</v>
+        <v>258.6634826660156</v>
       </c>
       <c r="V13">
-        <v>258.6634826660156</v>
+        <v>253.4850311279297</v>
       </c>
       <c r="W13">
-        <v>253.4850311279297</v>
+        <v>252.7779693603516</v>
       </c>
       <c r="X13">
-        <v>252.7779693603516</v>
+        <v>259.1116027832031</v>
       </c>
       <c r="Y13">
-        <v>259.1116027832031</v>
+        <v>256.55224609375</v>
       </c>
       <c r="Z13">
+        <v>260.7248840332031</v>
+      </c>
+      <c r="AA13">
         <v>256.55224609375</v>
       </c>
-      <c r="AA13">
-        <v>260.7248840332031</v>
-      </c>
       <c r="AB13">
-        <v>256.55224609375</v>
+        <v>259.4999694824219</v>
       </c>
       <c r="AC13">
-        <v>259.4999694824219</v>
+        <v>257.7999877929688</v>
       </c>
       <c r="AD13">
-        <v>257.7999877929688</v>
+        <v>257.8699951171875</v>
       </c>
       <c r="AE13">
-        <v>257.8699951171875</v>
+        <v>259.3399963378906</v>
       </c>
       <c r="AF13">
-        <v>259.3399963378906</v>
+        <v>263.1099853515625</v>
       </c>
       <c r="AG13">
-        <v>263.1099853515625</v>
+        <v>259.5700073242188</v>
       </c>
       <c r="AH13">
-        <v>259.5700073242188</v>
+        <v>253.4600067138672</v>
       </c>
       <c r="AI13">
-        <v>253.4600067138672</v>
+        <v>253.5800018310547</v>
       </c>
       <c r="AJ13">
-        <v>253.5800018310547</v>
+        <v>251.7899932861328</v>
       </c>
       <c r="AK13">
-        <v>251.7899932861328</v>
+        <v>253.7100067138672</v>
       </c>
       <c r="AL13">
-        <v>253.7100067138672</v>
+        <v>258.4800109863281</v>
       </c>
       <c r="AM13">
-        <v>258.4800109863281</v>
+        <v>257.2099914550781</v>
       </c>
       <c r="AN13">
-        <v>257.2099914550781</v>
+        <v>254.8500061035156</v>
       </c>
       <c r="AO13">
-        <v>254.8500061035156</v>
+        <v>252.2100067138672</v>
       </c>
       <c r="AP13">
-        <v>252.2100067138672</v>
+        <v>249.8300018310547</v>
       </c>
       <c r="AQ13">
-        <v>249.8300018310547</v>
+        <v>242.8600006103516</v>
       </c>
       <c r="AR13">
-        <v>242.8600006103516</v>
+        <v>229.5</v>
       </c>
       <c r="AS13">
-        <v>229.5</v>
+        <v>225.6600036621094</v>
       </c>
       <c r="AT13">
-        <v>225.6600036621094</v>
+        <v>227.1699981689453</v>
       </c>
       <c r="AU13">
-        <v>227.1699981689453</v>
+        <v>227.6000061035156</v>
       </c>
       <c r="AV13">
-        <v>227.6000061035156</v>
+        <v>227.5500030517578</v>
       </c>
       <c r="AW13">
-        <v>227.5500030517578</v>
+        <v>225.4199981689453</v>
       </c>
       <c r="AX13">
-        <v>225.4199981689453</v>
+        <v>221.8600006103516</v>
       </c>
       <c r="AY13">
-        <v>221.8600006103516</v>
+        <v>224.4100036621094</v>
       </c>
       <c r="AZ13">
-        <v>224.4100036621094</v>
+        <v>223.7400054931641</v>
       </c>
       <c r="BA13">
-        <v>223.7400054931641</v>
+        <v>224.7100067138672</v>
       </c>
       <c r="BB13">
-        <v>224.7100067138672</v>
+        <v>224.2700042724609</v>
       </c>
       <c r="BC13">
-        <v>224.2700042724609</v>
+        <v>223.9499969482422</v>
       </c>
       <c r="BD13">
-        <v>223.9499969482422</v>
+        <v>230.6300048828125</v>
       </c>
       <c r="BE13">
-        <v>230.6300048828125</v>
+        <v>229.4299926757812</v>
       </c>
       <c r="BF13">
-        <v>229.4299926757812</v>
+        <v>232.6000061035156</v>
       </c>
       <c r="BG13">
-        <v>232.6000061035156</v>
+        <v>236.3999938964844</v>
       </c>
       <c r="BH13">
-        <v>236.3999938964844</v>
-      </c>
-      <c r="BI13">
         <v>236.1699981689453</v>
       </c>
     </row>
-    <row r="14" spans="1:61">
+    <row r="14" spans="1:60">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>136.8694610595703</v>
+        <v>133.4556579589844</v>
       </c>
       <c r="C14">
-        <v>133.4556579589844</v>
+        <v>135.7381439208984</v>
       </c>
       <c r="D14">
-        <v>135.7381439208984</v>
+        <v>139.2710113525391</v>
       </c>
       <c r="E14">
-        <v>139.2710113525391</v>
+        <v>143.1016235351562</v>
       </c>
       <c r="F14">
-        <v>143.1016235351562</v>
+        <v>144.7886657714844</v>
       </c>
       <c r="G14">
-        <v>144.7886657714844</v>
+        <v>143.4092559814453</v>
       </c>
       <c r="H14">
-        <v>143.4092559814453</v>
+        <v>143.3894195556641</v>
       </c>
       <c r="I14">
-        <v>143.3894195556641</v>
+        <v>148.21240234375</v>
       </c>
       <c r="J14">
-        <v>148.21240234375</v>
+        <v>146.9818420410156</v>
       </c>
       <c r="K14">
-        <v>146.9818420410156</v>
+        <v>146.574951171875</v>
       </c>
       <c r="L14">
-        <v>146.574951171875</v>
+        <v>145.9596862792969</v>
       </c>
       <c r="M14">
-        <v>145.9596862792969</v>
+        <v>148.5597229003906</v>
       </c>
       <c r="N14">
-        <v>148.5597229003906</v>
+        <v>150.862060546875</v>
       </c>
       <c r="O14">
-        <v>150.862060546875</v>
+        <v>151.1299896240234</v>
       </c>
       <c r="P14">
-        <v>151.1299896240234</v>
+        <v>154</v>
       </c>
       <c r="Q14">
-        <v>154</v>
+        <v>155.5099945068359</v>
       </c>
       <c r="R14">
-        <v>155.5099945068359</v>
+        <v>154.4799957275391</v>
       </c>
       <c r="S14">
-        <v>154.4799957275391</v>
+        <v>151.0099945068359</v>
       </c>
       <c r="T14">
-        <v>151.0099945068359</v>
+        <v>152.4799957275391</v>
       </c>
       <c r="U14">
-        <v>152.4799957275391</v>
+        <v>159</v>
       </c>
       <c r="V14">
-        <v>159</v>
+        <v>158.25</v>
       </c>
       <c r="W14">
-        <v>158.25</v>
+        <v>165.4400024414062</v>
       </c>
       <c r="X14">
-        <v>165.4400024414062</v>
+        <v>169.8899993896484</v>
       </c>
       <c r="Y14">
-        <v>169.8899993896484</v>
+        <v>163.4700012207031</v>
       </c>
       <c r="Z14">
-        <v>163.4700012207031</v>
+        <v>164.0399932861328</v>
       </c>
       <c r="AA14">
-        <v>164.0399932861328</v>
+        <v>165.9299926757812</v>
       </c>
       <c r="AB14">
-        <v>165.9299926757812</v>
+        <v>163.1799926757812</v>
       </c>
       <c r="AC14">
-        <v>163.1799926757812</v>
+        <v>160.8800048828125</v>
       </c>
       <c r="AD14">
-        <v>160.8800048828125</v>
+        <v>163.75</v>
       </c>
       <c r="AE14">
-        <v>163.75</v>
+        <v>163.3600006103516</v>
       </c>
       <c r="AF14">
-        <v>163.3600006103516</v>
+        <v>164.0099945068359</v>
       </c>
       <c r="AG14">
-        <v>164.0099945068359</v>
+        <v>164.4400024414062</v>
       </c>
       <c r="AH14">
-        <v>164.4400024414062</v>
+        <v>162.7100067138672</v>
       </c>
       <c r="AI14">
-        <v>162.7100067138672</v>
+        <v>157.5200042724609</v>
       </c>
       <c r="AJ14">
-        <v>157.5200042724609</v>
+        <v>155.7299957275391</v>
       </c>
       <c r="AK14">
-        <v>155.7299957275391</v>
+        <v>155.8300018310547</v>
       </c>
       <c r="AL14">
-        <v>155.8300018310547</v>
+        <v>158.6999969482422</v>
       </c>
       <c r="AM14">
-        <v>158.6999969482422</v>
+        <v>154.3999938964844</v>
       </c>
       <c r="AN14">
-        <v>154.3999938964844</v>
+        <v>154.6799926757812</v>
       </c>
       <c r="AO14">
-        <v>154.6799926757812</v>
+        <v>159.8300018310547</v>
       </c>
       <c r="AP14">
-        <v>159.8300018310547</v>
+        <v>158.1900024414062</v>
       </c>
       <c r="AQ14">
-        <v>158.1900024414062</v>
+        <v>157.7100067138672</v>
       </c>
       <c r="AR14">
-        <v>157.7100067138672</v>
+        <v>159.0200042724609</v>
       </c>
       <c r="AS14">
-        <v>159.0200042724609</v>
+        <v>156.2599945068359</v>
       </c>
       <c r="AT14">
-        <v>156.2599945068359</v>
+        <v>156.1499938964844</v>
       </c>
       <c r="AU14">
-        <v>156.1499938964844</v>
+        <v>157.4499969482422</v>
       </c>
       <c r="AV14">
-        <v>157.4499969482422</v>
+        <v>158.4299926757812</v>
       </c>
       <c r="AW14">
-        <v>158.4299926757812</v>
+        <v>156.4299926757812</v>
       </c>
       <c r="AX14">
-        <v>156.4299926757812</v>
+        <v>156.6900024414062</v>
       </c>
       <c r="AY14">
-        <v>156.6900024414062</v>
+        <v>156.6999969482422</v>
       </c>
       <c r="AZ14">
-        <v>156.6999969482422</v>
+        <v>156</v>
       </c>
       <c r="BA14">
-        <v>156</v>
+        <v>152.9900054931641</v>
       </c>
       <c r="BB14">
-        <v>152.9900054931641</v>
+        <v>154.3300018310547</v>
       </c>
       <c r="BC14">
-        <v>154.3300018310547</v>
+        <v>150.9199981689453</v>
       </c>
       <c r="BD14">
-        <v>150.9199981689453</v>
+        <v>154.7599945068359</v>
       </c>
       <c r="BE14">
-        <v>154.7599945068359</v>
+        <v>153.6399993896484</v>
       </c>
       <c r="BF14">
-        <v>153.6399993896484</v>
+        <v>153.6199951171875</v>
       </c>
       <c r="BG14">
-        <v>153.6199951171875</v>
+        <v>151.9900054931641</v>
       </c>
       <c r="BH14">
-        <v>151.9900054931641</v>
-      </c>
-      <c r="BI14">
         <v>155.3099975585938</v>
       </c>
     </row>
-    <row r="15" spans="1:61">
+    <row r="15" spans="1:60">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>115.7900009155273</v>
+        <v>116.6900024414062</v>
       </c>
       <c r="C15">
-        <v>116.6900024414062</v>
+        <v>117.6699981689453</v>
       </c>
       <c r="D15">
-        <v>117.6699981689453</v>
+        <v>118.870002746582</v>
       </c>
       <c r="E15">
-        <v>118.870002746582</v>
+        <v>129.9299926757812</v>
       </c>
       <c r="F15">
-        <v>129.9299926757812</v>
+        <v>127.0999984741211</v>
       </c>
       <c r="G15">
-        <v>127.0999984741211</v>
+        <v>122.9899978637695</v>
       </c>
       <c r="H15">
-        <v>122.9899978637695</v>
+        <v>119.5199966430664</v>
       </c>
       <c r="I15">
-        <v>119.5199966430664</v>
+        <v>118.4300003051758</v>
       </c>
       <c r="J15">
-        <v>118.4300003051758</v>
+        <v>120.5999984741211</v>
       </c>
       <c r="K15">
-        <v>120.5999984741211</v>
+        <v>119.8000030517578</v>
       </c>
       <c r="L15">
-        <v>119.8000030517578</v>
+        <v>118.379997253418</v>
       </c>
       <c r="M15">
-        <v>118.379997253418</v>
+        <v>120.5599975585938</v>
       </c>
       <c r="N15">
-        <v>120.5599975585938</v>
+        <v>121.5500030517578</v>
       </c>
       <c r="O15">
-        <v>121.5500030517578</v>
+        <v>121.0699996948242</v>
       </c>
       <c r="P15">
-        <v>121.0699996948242</v>
+        <v>120.7699966430664</v>
       </c>
       <c r="Q15">
-        <v>120.7699966430664</v>
+        <v>120.5199966430664</v>
       </c>
       <c r="R15">
-        <v>120.5199966430664</v>
+        <v>120.1600036621094</v>
       </c>
       <c r="S15">
-        <v>120.1600036621094</v>
+        <v>123.5</v>
       </c>
       <c r="T15">
-        <v>123.5</v>
+        <v>123.4700012207031</v>
       </c>
       <c r="U15">
-        <v>123.4700012207031</v>
+        <v>128.4700012207031</v>
       </c>
       <c r="V15">
-        <v>128.4700012207031</v>
+        <v>127.2200012207031</v>
       </c>
       <c r="W15">
-        <v>127.2200012207031</v>
+        <v>127.8099975585938</v>
       </c>
       <c r="X15">
-        <v>127.8099975585938</v>
+        <v>127.9800033569336</v>
       </c>
       <c r="Y15">
-        <v>127.9800033569336</v>
+        <v>129.7200012207031</v>
       </c>
       <c r="Z15">
-        <v>129.7200012207031</v>
+        <v>128.1199951171875</v>
       </c>
       <c r="AA15">
-        <v>128.1199951171875</v>
+        <v>127.7399978637695</v>
       </c>
       <c r="AB15">
-        <v>127.7399978637695</v>
+        <v>124.370002746582</v>
       </c>
       <c r="AC15">
-        <v>124.370002746582</v>
+        <v>123.2200012207031</v>
       </c>
       <c r="AD15">
-        <v>123.2200012207031</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="AE15">
-        <v>125.0100021362305</v>
+        <v>128.8300018310547</v>
       </c>
       <c r="AF15">
-        <v>128.8300018310547</v>
+        <v>128</v>
       </c>
       <c r="AG15">
-        <v>128</v>
+        <v>126.75</v>
       </c>
       <c r="AH15">
-        <v>126.75</v>
+        <v>124.4000015258789</v>
       </c>
       <c r="AI15">
-        <v>124.4000015258789</v>
+        <v>126.0100021362305</v>
       </c>
       <c r="AJ15">
-        <v>126.0100021362305</v>
+        <v>123.2799987792969</v>
       </c>
       <c r="AK15">
-        <v>123.2799987792969</v>
+        <v>121.4700012207031</v>
       </c>
       <c r="AL15">
-        <v>121.4700012207031</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="AM15">
-        <v>122.1900024414062</v>
+        <v>121.7399978637695</v>
       </c>
       <c r="AN15">
-        <v>121.7399978637695</v>
+        <v>124.75</v>
       </c>
       <c r="AO15">
-        <v>124.75</v>
+        <v>127.620002746582</v>
       </c>
       <c r="AP15">
-        <v>127.620002746582</v>
+        <v>125.3099975585938</v>
       </c>
       <c r="AQ15">
-        <v>125.3099975585938</v>
+        <v>124.6500015258789</v>
       </c>
       <c r="AR15">
-        <v>124.6500015258789</v>
+        <v>126.9300003051758</v>
       </c>
       <c r="AS15">
-        <v>126.9300003051758</v>
+        <v>124.6399993896484</v>
       </c>
       <c r="AT15">
-        <v>124.6399993896484</v>
+        <v>124.4400024414062</v>
       </c>
       <c r="AU15">
-        <v>124.4400024414062</v>
+        <v>123.8899993896484</v>
       </c>
       <c r="AV15">
-        <v>123.8899993896484</v>
+        <v>124.8199996948242</v>
       </c>
       <c r="AW15">
-        <v>124.8199996948242</v>
+        <v>123.1999969482422</v>
       </c>
       <c r="AX15">
-        <v>123.1999969482422</v>
+        <v>121.3499984741211</v>
       </c>
       <c r="AY15">
-        <v>121.3499984741211</v>
+        <v>117.1399993896484</v>
       </c>
       <c r="AZ15">
-        <v>117.1399993896484</v>
+        <v>115.3000030517578</v>
       </c>
       <c r="BA15">
-        <v>115.3000030517578</v>
+        <v>114.129997253418</v>
       </c>
       <c r="BB15">
-        <v>114.129997253418</v>
+        <v>112.7300033569336</v>
       </c>
       <c r="BC15">
-        <v>112.7300033569336</v>
+        <v>113.4400024414062</v>
       </c>
       <c r="BD15">
-        <v>113.4400024414062</v>
+        <v>112.75</v>
       </c>
       <c r="BE15">
-        <v>112.75</v>
+        <v>112.7900009155273</v>
       </c>
       <c r="BF15">
-        <v>112.7900009155273</v>
+        <v>111.3600006103516</v>
       </c>
       <c r="BG15">
-        <v>111.3600006103516</v>
+        <v>108.620002746582</v>
       </c>
       <c r="BH15">
-        <v>108.620002746582</v>
-      </c>
-      <c r="BI15">
         <v>111.5699996948242</v>
       </c>
     </row>
-    <row r="16" spans="1:61">
+    <row r="16" spans="1:60">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>244.8500061035156</v>
+        <v>233.6600036621094</v>
       </c>
       <c r="C16">
-        <v>233.6600036621094</v>
+        <v>232.1100006103516</v>
       </c>
       <c r="D16">
-        <v>232.1100006103516</v>
+        <v>231.3899993896484</v>
       </c>
       <c r="E16">
-        <v>231.3899993896484</v>
+        <v>230.8600006103516</v>
       </c>
       <c r="F16">
-        <v>230.8600006103516</v>
+        <v>226.6499938964844</v>
       </c>
       <c r="G16">
-        <v>226.6499938964844</v>
+        <v>235.5</v>
       </c>
       <c r="H16">
-        <v>235.5</v>
+        <v>271.5799865722656</v>
       </c>
       <c r="I16">
-        <v>271.5799865722656</v>
+        <v>284.0199890136719</v>
       </c>
       <c r="J16">
-        <v>284.0199890136719</v>
+        <v>277.4200134277344</v>
       </c>
       <c r="K16">
-        <v>277.4200134277344</v>
+        <v>272.6499938964844</v>
       </c>
       <c r="L16">
-        <v>272.6499938964844</v>
+        <v>272.260009765625</v>
       </c>
       <c r="M16">
-        <v>272.260009765625</v>
+        <v>274.4800109863281</v>
       </c>
       <c r="N16">
-        <v>274.4800109863281</v>
+        <v>278.0899963378906</v>
       </c>
       <c r="O16">
-        <v>278.0899963378906</v>
+        <v>272.2699890136719</v>
       </c>
       <c r="P16">
-        <v>272.2699890136719</v>
+        <v>267.2799987792969</v>
       </c>
       <c r="Q16">
-        <v>267.2799987792969</v>
+        <v>265.1300048828125</v>
       </c>
       <c r="R16">
-        <v>265.1300048828125</v>
+        <v>262.6499938964844</v>
       </c>
       <c r="S16">
-        <v>262.6499938964844</v>
+        <v>261.3099975585938</v>
       </c>
       <c r="T16">
-        <v>261.3099975585938</v>
+        <v>259.4500122070312</v>
       </c>
       <c r="U16">
-        <v>259.4500122070312</v>
+        <v>265.8399963378906</v>
       </c>
       <c r="V16">
-        <v>265.8399963378906</v>
+        <v>260.1099853515625</v>
       </c>
       <c r="W16">
-        <v>260.1099853515625</v>
+        <v>258.6300048828125</v>
       </c>
       <c r="X16">
-        <v>258.6300048828125</v>
+        <v>262.0700073242188</v>
       </c>
       <c r="Y16">
-        <v>262.0700073242188</v>
+        <v>261.0599975585938</v>
       </c>
       <c r="Z16">
-        <v>261.0599975585938</v>
+        <v>260.2799987792969</v>
       </c>
       <c r="AA16">
-        <v>260.2799987792969</v>
+        <v>256.260009765625</v>
       </c>
       <c r="AB16">
-        <v>256.260009765625</v>
+        <v>266.4299926757812</v>
       </c>
       <c r="AC16">
-        <v>266.4299926757812</v>
+        <v>259.7699890136719</v>
       </c>
       <c r="AD16">
-        <v>259.7699890136719</v>
+        <v>254.9199981689453</v>
       </c>
       <c r="AE16">
-        <v>254.9199981689453</v>
+        <v>254.9799957275391</v>
       </c>
       <c r="AF16">
+        <v>258.8999938964844</v>
+      </c>
+      <c r="AG16">
+        <v>258.510009765625</v>
+      </c>
+      <c r="AH16">
+        <v>256.9700012207031</v>
+      </c>
+      <c r="AI16">
+        <v>252.3999938964844</v>
+      </c>
+      <c r="AJ16">
+        <v>251.8899993896484</v>
+      </c>
+      <c r="AK16">
+        <v>256.7799987792969</v>
+      </c>
+      <c r="AL16">
+        <v>253.5399932861328</v>
+      </c>
+      <c r="AM16">
+        <v>248.4199981689453</v>
+      </c>
+      <c r="AN16">
+        <v>245.9600067138672</v>
+      </c>
+      <c r="AO16">
+        <v>251.1900024414062</v>
+      </c>
+      <c r="AP16">
+        <v>253.7100067138672</v>
+      </c>
+      <c r="AQ16">
+        <v>258.4500122070312</v>
+      </c>
+      <c r="AR16">
         <v>254.9799957275391</v>
       </c>
-      <c r="AG16">
-        <v>258.8999938964844</v>
-      </c>
-      <c r="AH16">
-        <v>258.510009765625</v>
-      </c>
-      <c r="AI16">
-        <v>256.9700012207031</v>
-      </c>
-      <c r="AJ16">
-        <v>252.3999938964844</v>
-      </c>
-      <c r="AK16">
-        <v>251.8899993896484</v>
-      </c>
-      <c r="AL16">
-        <v>256.7799987792969</v>
-      </c>
-      <c r="AM16">
-        <v>253.5399932861328</v>
-      </c>
-      <c r="AN16">
-        <v>248.4199981689453</v>
-      </c>
-      <c r="AO16">
-        <v>245.9600067138672</v>
-      </c>
-      <c r="AP16">
-        <v>251.1900024414062</v>
-      </c>
-      <c r="AQ16">
-        <v>253.7100067138672</v>
-      </c>
-      <c r="AR16">
-        <v>258.4500122070312</v>
-      </c>
       <c r="AS16">
-        <v>254.9799957275391</v>
+        <v>249.2700042724609</v>
       </c>
       <c r="AT16">
-        <v>249.2700042724609</v>
+        <v>249.3800048828125</v>
       </c>
       <c r="AU16">
-        <v>249.3800048828125</v>
+        <v>249.6699981689453</v>
       </c>
       <c r="AV16">
-        <v>249.6699981689453</v>
+        <v>246.1499938964844</v>
       </c>
       <c r="AW16">
-        <v>246.1499938964844</v>
+        <v>246.6699981689453</v>
       </c>
       <c r="AX16">
-        <v>246.6699981689453</v>
+        <v>249.1499938964844</v>
       </c>
       <c r="AY16">
-        <v>249.1499938964844</v>
+        <v>248.2299957275391</v>
       </c>
       <c r="AZ16">
-        <v>248.2299957275391</v>
+        <v>251.5200042724609</v>
       </c>
       <c r="BA16">
-        <v>251.5200042724609</v>
+        <v>251.3999938964844</v>
       </c>
       <c r="BB16">
-        <v>251.3999938964844</v>
+        <v>256.2900085449219</v>
       </c>
       <c r="BC16">
-        <v>256.2900085449219</v>
+        <v>259.9200134277344</v>
       </c>
       <c r="BD16">
-        <v>259.9200134277344</v>
+        <v>254.0599975585938</v>
       </c>
       <c r="BE16">
-        <v>254.0599975585938</v>
+        <v>262.4299926757812</v>
       </c>
       <c r="BF16">
-        <v>262.4299926757812</v>
+        <v>259.5299987792969</v>
       </c>
       <c r="BG16">
-        <v>259.5299987792969</v>
+        <v>258.5799865722656</v>
       </c>
       <c r="BH16">
-        <v>258.5799865722656</v>
-      </c>
-      <c r="BI16">
         <v>254.0800018310547</v>
       </c>
     </row>
-    <row r="17" spans="1:61">
+    <row r="17" spans="1:60">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>190.8699951171875</v>
+        <v>196.8600006103516</v>
       </c>
       <c r="C17">
-        <v>196.8600006103516</v>
+        <v>194.0899963378906</v>
       </c>
       <c r="D17">
-        <v>194.0899963378906</v>
+        <v>189.4700012207031</v>
       </c>
       <c r="E17">
-        <v>189.4700012207031</v>
+        <v>192.9799957275391</v>
       </c>
       <c r="F17">
-        <v>192.9799957275391</v>
+        <v>194.8200073242188</v>
       </c>
       <c r="G17">
-        <v>194.8200073242188</v>
+        <v>205.0899963378906</v>
       </c>
       <c r="H17">
-        <v>205.0899963378906</v>
+        <v>205.1000061035156</v>
       </c>
       <c r="I17">
-        <v>205.1000061035156</v>
+        <v>198.1600036621094</v>
       </c>
       <c r="J17">
-        <v>198.1600036621094</v>
+        <v>203.0099945068359</v>
       </c>
       <c r="K17">
-        <v>203.0099945068359</v>
+        <v>199.8699951171875</v>
       </c>
       <c r="L17">
-        <v>199.8699951171875</v>
+        <v>193.7200012207031</v>
       </c>
       <c r="M17">
-        <v>193.7200012207031</v>
+        <v>187.9600067138672</v>
       </c>
       <c r="N17">
-        <v>187.9600067138672</v>
+        <v>191.7899932861328</v>
       </c>
       <c r="O17">
-        <v>191.7899932861328</v>
+        <v>192.8399963378906</v>
       </c>
       <c r="P17">
-        <v>192.8399963378906</v>
+        <v>192.9100036621094</v>
       </c>
       <c r="Q17">
-        <v>192.9100036621094</v>
+        <v>192.6399993896484</v>
       </c>
       <c r="R17">
-        <v>192.6399993896484</v>
+        <v>190.8899993896484</v>
       </c>
       <c r="S17">
-        <v>190.8899993896484</v>
+        <v>193.1399993896484</v>
       </c>
       <c r="T17">
-        <v>193.1399993896484</v>
+        <v>188.2899932861328</v>
       </c>
       <c r="U17">
-        <v>188.2899932861328</v>
+        <v>205</v>
       </c>
       <c r="V17">
+        <v>213.2400054931641</v>
+      </c>
+      <c r="W17">
+        <v>219.3999938964844</v>
+      </c>
+      <c r="X17">
+        <v>223.2200012207031</v>
+      </c>
+      <c r="Y17">
+        <v>224.9900054931641</v>
+      </c>
+      <c r="Z17">
+        <v>224.8399963378906</v>
+      </c>
+      <c r="AA17">
+        <v>227.6900024414062</v>
+      </c>
+      <c r="AB17">
+        <v>215.5899963378906</v>
+      </c>
+      <c r="AC17">
+        <v>213.6300048828125</v>
+      </c>
+      <c r="AD17">
+        <v>207.1300048828125</v>
+      </c>
+      <c r="AE17">
+        <v>213.25</v>
+      </c>
+      <c r="AF17">
+        <v>221.6600036621094</v>
+      </c>
+      <c r="AG17">
+        <v>218.2200012207031</v>
+      </c>
+      <c r="AH17">
+        <v>211.0599975585938</v>
+      </c>
+      <c r="AI17">
         <v>205</v>
       </c>
-      <c r="W17">
-        <v>213.2400054931641</v>
-      </c>
-      <c r="X17">
-        <v>219.3999938964844</v>
-      </c>
-      <c r="Y17">
-        <v>223.2200012207031</v>
-      </c>
-      <c r="Z17">
-        <v>224.9900054931641</v>
-      </c>
-      <c r="AA17">
-        <v>224.8399963378906</v>
-      </c>
-      <c r="AB17">
-        <v>227.6900024414062</v>
-      </c>
-      <c r="AC17">
-        <v>215.5899963378906</v>
-      </c>
-      <c r="AD17">
-        <v>213.6300048828125</v>
-      </c>
-      <c r="AE17">
-        <v>207.1300048828125</v>
-      </c>
-      <c r="AF17">
-        <v>213.25</v>
-      </c>
-      <c r="AG17">
-        <v>221.6600036621094</v>
-      </c>
-      <c r="AH17">
-        <v>218.2200012207031</v>
-      </c>
-      <c r="AI17">
-        <v>211.0599975585938</v>
-      </c>
       <c r="AJ17">
-        <v>205</v>
+        <v>201.2700042724609</v>
       </c>
       <c r="AK17">
-        <v>201.2700042724609</v>
+        <v>206.4499969482422</v>
       </c>
       <c r="AL17">
-        <v>206.4499969482422</v>
+        <v>208.2100067138672</v>
       </c>
       <c r="AM17">
-        <v>208.2100067138672</v>
+        <v>222.2899932861328</v>
       </c>
       <c r="AN17">
-        <v>222.2899932861328</v>
+        <v>228.9299926757812</v>
       </c>
       <c r="AO17">
-        <v>228.9299926757812</v>
+        <v>245.1799926757812</v>
       </c>
       <c r="AP17">
-        <v>245.1799926757812</v>
+        <v>239.6199951171875</v>
       </c>
       <c r="AQ17">
-        <v>239.6199951171875</v>
+        <v>238.8200073242188</v>
       </c>
       <c r="AR17">
-        <v>238.8200073242188</v>
+        <v>247.4600067138672</v>
       </c>
       <c r="AS17">
-        <v>247.4600067138672</v>
+        <v>255.3800048828125</v>
       </c>
       <c r="AT17">
-        <v>255.3800048828125</v>
+        <v>273.8999938964844</v>
       </c>
       <c r="AU17">
-        <v>273.8999938964844</v>
+        <v>270</v>
       </c>
       <c r="AV17">
-        <v>270</v>
+        <v>271.8999938964844</v>
       </c>
       <c r="AW17">
-        <v>271.8999938964844</v>
+        <v>272</v>
       </c>
       <c r="AX17">
-        <v>272</v>
+        <v>273.6799926757812</v>
       </c>
       <c r="AY17">
-        <v>273.6799926757812</v>
+        <v>265.7200012207031</v>
       </c>
       <c r="AZ17">
-        <v>265.7200012207031</v>
+        <v>273.0400085449219</v>
       </c>
       <c r="BA17">
-        <v>273.0400085449219</v>
+        <v>293.6900024414062</v>
       </c>
       <c r="BB17">
-        <v>293.6900024414062</v>
+        <v>273.5400085449219</v>
       </c>
       <c r="BC17">
-        <v>273.5400085449219</v>
+        <v>267.760009765625</v>
       </c>
       <c r="BD17">
-        <v>267.760009765625</v>
+        <v>264.5700073242188</v>
       </c>
       <c r="BE17">
-        <v>264.5700073242188</v>
+        <v>278.1700134277344</v>
       </c>
       <c r="BF17">
-        <v>278.1700134277344</v>
+        <v>276.6700134277344</v>
       </c>
       <c r="BG17">
-        <v>276.6700134277344</v>
+        <v>271.1799926757812</v>
       </c>
       <c r="BH17">
-        <v>271.1799926757812</v>
-      </c>
-      <c r="BI17">
         <v>271.760009765625</v>
       </c>
     </row>
-    <row r="18" spans="1:61">
+    <row r="18" spans="1:60">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>122.1500015258789</v>
+        <v>117.6500015258789</v>
       </c>
       <c r="C18">
-        <v>117.6500015258789</v>
+        <v>120.4499969482422</v>
       </c>
       <c r="D18">
-        <v>120.4499969482422</v>
+        <v>125.5400009155273</v>
       </c>
       <c r="E18">
-        <v>125.5400009155273</v>
+        <v>126.7600021362305</v>
       </c>
       <c r="F18">
-        <v>126.7600021362305</v>
+        <v>128.9499969482422</v>
       </c>
       <c r="G18">
-        <v>128.9499969482422</v>
+        <v>128.5700073242188</v>
       </c>
       <c r="H18">
-        <v>128.5700073242188</v>
+        <v>127.2099990844727</v>
       </c>
       <c r="I18">
-        <v>127.2099990844727</v>
+        <v>129.3500061035156</v>
       </c>
       <c r="J18">
-        <v>129.3500061035156</v>
+        <v>130.7100067138672</v>
       </c>
       <c r="K18">
-        <v>130.7100067138672</v>
+        <v>128.7599945068359</v>
       </c>
       <c r="L18">
-        <v>128.7599945068359</v>
+        <v>129.6799926757812</v>
       </c>
       <c r="M18">
-        <v>129.6799926757812</v>
+        <v>130.8999938964844</v>
       </c>
       <c r="N18">
-        <v>130.8999938964844</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="O18">
-        <v>129.3699951171875</v>
+        <v>128.0599975585938</v>
       </c>
       <c r="P18">
-        <v>128.0599975585938</v>
+        <v>128.6100006103516</v>
       </c>
       <c r="Q18">
-        <v>128.6100006103516</v>
+        <v>129.5299987792969</v>
       </c>
       <c r="R18">
-        <v>129.5299987792969</v>
+        <v>129.3899993896484</v>
       </c>
       <c r="S18">
-        <v>129.3899993896484</v>
+        <v>129.5399932861328</v>
       </c>
       <c r="T18">
-        <v>129.5399932861328</v>
+        <v>130.4799957275391</v>
       </c>
       <c r="U18">
-        <v>130.4799957275391</v>
+        <v>131.8399963378906</v>
       </c>
       <c r="V18">
-        <v>131.8399963378906</v>
+        <v>128.4499969482422</v>
       </c>
       <c r="W18">
-        <v>128.4499969482422</v>
+        <v>131.4799957275391</v>
       </c>
       <c r="X18">
-        <v>131.4799957275391</v>
+        <v>136.75</v>
       </c>
       <c r="Y18">
-        <v>136.75</v>
+        <v>134.4799957275391</v>
       </c>
       <c r="Z18">
-        <v>134.4799957275391</v>
+        <v>132.1799926757812</v>
       </c>
       <c r="AA18">
-        <v>132.1799926757812</v>
+        <v>127</v>
       </c>
       <c r="AB18">
-        <v>127</v>
+        <v>128.2599945068359</v>
       </c>
       <c r="AC18">
-        <v>128.2599945068359</v>
+        <v>126.5899963378906</v>
       </c>
       <c r="AD18">
-        <v>126.5899963378906</v>
+        <v>131.7100067138672</v>
       </c>
       <c r="AE18">
-        <v>131.7100067138672</v>
+        <v>131.9100036621094</v>
       </c>
       <c r="AF18">
-        <v>131.9100036621094</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="AG18">
-        <v>131.0399932861328</v>
+        <v>131.4199981689453</v>
       </c>
       <c r="AH18">
-        <v>131.4199981689453</v>
+        <v>124.0400009155273</v>
       </c>
       <c r="AI18">
-        <v>124.0400009155273</v>
+        <v>118.3899993896484</v>
       </c>
       <c r="AJ18">
-        <v>118.3899993896484</v>
+        <v>118.6600036621094</v>
       </c>
       <c r="AK18">
-        <v>118.6600036621094</v>
+        <v>118.1699981689453</v>
       </c>
       <c r="AL18">
-        <v>118.1699981689453</v>
+        <v>119.1699981689453</v>
       </c>
       <c r="AM18">
-        <v>119.1699981689453</v>
+        <v>112.7900009155273</v>
       </c>
       <c r="AN18">
-        <v>112.7900009155273</v>
+        <v>112.4000015258789</v>
       </c>
       <c r="AO18">
-        <v>112.4000015258789</v>
+        <v>114.4000015258789</v>
       </c>
       <c r="AP18">
-        <v>114.4000015258789</v>
+        <v>111.9599990844727</v>
       </c>
       <c r="AQ18">
-        <v>111.9599990844727</v>
+        <v>112.3300018310547</v>
       </c>
       <c r="AR18">
-        <v>112.3300018310547</v>
+        <v>115.0400009155273</v>
       </c>
       <c r="AS18">
-        <v>115.0400009155273</v>
+        <v>113.1600036621094</v>
       </c>
       <c r="AT18">
-        <v>113.1600036621094</v>
+        <v>113.5</v>
       </c>
       <c r="AU18">
-        <v>113.5</v>
+        <v>114.0699996948242</v>
       </c>
       <c r="AV18">
-        <v>114.0699996948242</v>
+        <v>116.0199966430664</v>
       </c>
       <c r="AW18">
-        <v>116.0199966430664</v>
+        <v>113.3000030517578</v>
       </c>
       <c r="AX18">
-        <v>113.3000030517578</v>
+        <v>114.0199966430664</v>
       </c>
       <c r="AY18">
-        <v>114.0199966430664</v>
+        <v>114.4300003051758</v>
       </c>
       <c r="AZ18">
-        <v>114.4300003051758</v>
+        <v>112.1600036621094</v>
       </c>
       <c r="BA18">
-        <v>112.1600036621094</v>
+        <v>113.1900024414062</v>
       </c>
       <c r="BB18">
-        <v>113.1900024414062</v>
+        <v>116.1900024414062</v>
       </c>
       <c r="BC18">
-        <v>116.1900024414062</v>
+        <v>116.3000030517578</v>
       </c>
       <c r="BD18">
-        <v>116.3000030517578</v>
+        <v>118.620002746582</v>
       </c>
       <c r="BE18">
-        <v>118.620002746582</v>
+        <v>118.6399993896484</v>
       </c>
       <c r="BF18">
-        <v>118.6399993896484</v>
+        <v>117.6100006103516</v>
       </c>
       <c r="BG18">
-        <v>117.6100006103516</v>
+        <v>116.2799987792969</v>
       </c>
       <c r="BH18">
-        <v>116.2799987792969</v>
-      </c>
-      <c r="BI18">
         <v>121.7600021362305</v>
       </c>
     </row>
-    <row r="19" spans="1:61">
+    <row r="19" spans="1:60">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>197.7400054931641</v>
+        <v>200.6199951171875</v>
       </c>
       <c r="C19">
-        <v>200.6199951171875</v>
+        <v>202.1900024414062</v>
       </c>
       <c r="D19">
-        <v>202.1900024414062</v>
+        <v>200.1399993896484</v>
       </c>
       <c r="E19">
-        <v>200.1399993896484</v>
+        <v>205.6100006103516</v>
       </c>
       <c r="F19">
-        <v>205.6100006103516</v>
+        <v>209.2299957275391</v>
       </c>
       <c r="G19">
-        <v>209.2299957275391</v>
+        <v>207.9299926757812</v>
       </c>
       <c r="H19">
-        <v>207.9299926757812</v>
+        <v>202.9499969482422</v>
       </c>
       <c r="I19">
-        <v>202.9499969482422</v>
+        <v>201.8200073242188</v>
       </c>
       <c r="J19">
-        <v>201.8200073242188</v>
+        <v>208.4499969482422</v>
       </c>
       <c r="K19">
-        <v>208.4499969482422</v>
+        <v>206.6300048828125</v>
       </c>
       <c r="L19">
-        <v>206.6300048828125</v>
+        <v>206.2799987792969</v>
       </c>
       <c r="M19">
-        <v>206.2799987792969</v>
+        <v>207.9400024414062</v>
       </c>
       <c r="N19">
-        <v>207.9400024414062</v>
+        <v>207.1300048828125</v>
       </c>
       <c r="O19">
-        <v>207.1300048828125</v>
+        <v>203.8899993896484</v>
       </c>
       <c r="P19">
-        <v>203.8899993896484</v>
+        <v>208.8699951171875</v>
       </c>
       <c r="Q19">
-        <v>208.8699951171875</v>
+        <v>210.6499938964844</v>
       </c>
       <c r="R19">
-        <v>210.6499938964844</v>
+        <v>209.8300018310547</v>
       </c>
       <c r="S19">
-        <v>209.8300018310547</v>
+        <v>209.1499938964844</v>
       </c>
       <c r="T19">
-        <v>209.1499938964844</v>
+        <v>212.5500030517578</v>
       </c>
       <c r="U19">
-        <v>212.5500030517578</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="V19">
-        <v>221.5599975585938</v>
+        <v>214.3500061035156</v>
       </c>
       <c r="W19">
-        <v>214.3500061035156</v>
+        <v>216.7799987792969</v>
       </c>
       <c r="X19">
-        <v>216.7799987792969</v>
+        <v>218.1199951171875</v>
       </c>
       <c r="Y19">
-        <v>218.1199951171875</v>
+        <v>220.7700042724609</v>
       </c>
       <c r="Z19">
-        <v>220.7700042724609</v>
+        <v>221.0700073242188</v>
       </c>
       <c r="AA19">
-        <v>221.0700073242188</v>
+        <v>221.5</v>
       </c>
       <c r="AB19">
-        <v>221.5</v>
+        <v>218.5</v>
       </c>
       <c r="AC19">
-        <v>218.5</v>
+        <v>216.6499938964844</v>
       </c>
       <c r="AD19">
-        <v>216.6499938964844</v>
+        <v>216.0399932861328</v>
       </c>
       <c r="AE19">
-        <v>216.0399932861328</v>
+        <v>222.6699981689453</v>
       </c>
       <c r="AF19">
-        <v>222.6699981689453</v>
+        <v>224.5099945068359</v>
       </c>
       <c r="AG19">
-        <v>224.5099945068359</v>
+        <v>220.8300018310547</v>
       </c>
       <c r="AH19">
-        <v>220.8300018310547</v>
+        <v>212.5</v>
       </c>
       <c r="AI19">
-        <v>212.5</v>
+        <v>210.7299957275391</v>
       </c>
       <c r="AJ19">
-        <v>210.7299957275391</v>
+        <v>215.4299926757812</v>
       </c>
       <c r="AK19">
-        <v>215.4299926757812</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="AL19">
-        <v>217.1499938964844</v>
+        <v>217.3600006103516</v>
       </c>
       <c r="AM19">
-        <v>217.3600006103516</v>
+        <v>216.1699981689453</v>
       </c>
       <c r="AN19">
-        <v>216.1699981689453</v>
+        <v>216.0099945068359</v>
       </c>
       <c r="AO19">
-        <v>216.0099945068359</v>
+        <v>219.0500030517578</v>
       </c>
       <c r="AP19">
-        <v>219.0500030517578</v>
+        <v>215.5</v>
       </c>
       <c r="AQ19">
-        <v>215.5</v>
+        <v>219.0700073242188</v>
       </c>
       <c r="AR19">
-        <v>219.0700073242188</v>
+        <v>225.3600006103516</v>
       </c>
       <c r="AS19">
-        <v>225.3600006103516</v>
+        <v>227.5299987792969</v>
       </c>
       <c r="AT19">
-        <v>227.5299987792969</v>
+        <v>226.3600006103516</v>
       </c>
       <c r="AU19">
-        <v>226.3600006103516</v>
+        <v>227.6000061035156</v>
       </c>
       <c r="AV19">
-        <v>227.6000061035156</v>
+        <v>228.6900024414062</v>
       </c>
       <c r="AW19">
-        <v>228.6900024414062</v>
+        <v>227.0700073242188</v>
       </c>
       <c r="AX19">
-        <v>227.0700073242188</v>
+        <v>225.8800048828125</v>
       </c>
       <c r="AY19">
-        <v>225.8800048828125</v>
+        <v>222.8200073242188</v>
       </c>
       <c r="AZ19">
-        <v>222.8200073242188</v>
+        <v>219.8800048828125</v>
       </c>
       <c r="BA19">
-        <v>219.8800048828125</v>
+        <v>223.5899963378906</v>
       </c>
       <c r="BB19">
-        <v>223.5899963378906</v>
+        <v>222.8899993896484</v>
       </c>
       <c r="BC19">
-        <v>222.8899993896484</v>
+        <v>222.1499938964844</v>
       </c>
       <c r="BD19">
-        <v>222.1499938964844</v>
+        <v>218.4299926757812</v>
       </c>
       <c r="BE19">
-        <v>218.4299926757812</v>
+        <v>225.7100067138672</v>
       </c>
       <c r="BF19">
-        <v>225.7100067138672</v>
+        <v>229.4100036621094</v>
       </c>
       <c r="BG19">
-        <v>229.4100036621094</v>
+        <v>228.8999938964844</v>
       </c>
       <c r="BH19">
-        <v>228.8999938964844</v>
-      </c>
-      <c r="BI19">
         <v>232.8300018310547</v>
       </c>
     </row>
-    <row r="20" spans="1:61">
+    <row r="20" spans="1:60">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>200.6514282226562</v>
+        <v>199.2563629150391</v>
       </c>
       <c r="C20">
-        <v>199.2563629150391</v>
+        <v>202.126220703125</v>
       </c>
       <c r="D20">
-        <v>202.126220703125</v>
+        <v>206.3214111328125</v>
       </c>
       <c r="E20">
-        <v>206.3214111328125</v>
+        <v>211.6625518798828</v>
       </c>
       <c r="F20">
-        <v>211.6625518798828</v>
+        <v>207.9755706787109</v>
       </c>
       <c r="G20">
-        <v>207.9755706787109</v>
+        <v>209.4005279541016</v>
       </c>
       <c r="H20">
-        <v>209.4005279541016</v>
+        <v>208.2745056152344</v>
       </c>
       <c r="I20">
-        <v>208.2745056152344</v>
+        <v>216.9139862060547</v>
       </c>
       <c r="J20">
-        <v>216.9139862060547</v>
+        <v>221.1291198730469</v>
       </c>
       <c r="K20">
-        <v>221.1291198730469</v>
+        <v>220.85009765625</v>
       </c>
       <c r="L20">
-        <v>220.85009765625</v>
+        <v>219.225830078125</v>
       </c>
       <c r="M20">
-        <v>219.225830078125</v>
+        <v>216.9937133789062</v>
       </c>
       <c r="N20">
-        <v>216.9937133789062</v>
+        <v>218.199462890625</v>
       </c>
       <c r="O20">
-        <v>218.199462890625</v>
+        <v>218.3788146972656</v>
       </c>
       <c r="P20">
-        <v>218.3788146972656</v>
+        <v>221.6572570800781</v>
       </c>
       <c r="Q20">
-        <v>221.6572570800781</v>
+        <v>223.0423583984375</v>
       </c>
       <c r="R20">
-        <v>223.0423583984375</v>
+        <v>226.5399932861328</v>
       </c>
       <c r="S20">
-        <v>226.5399932861328</v>
+        <v>221.4499969482422</v>
       </c>
       <c r="T20">
-        <v>221.4499969482422</v>
+        <v>221.4700012207031</v>
       </c>
       <c r="U20">
-        <v>221.4700012207031</v>
+        <v>220.7299957275391</v>
       </c>
       <c r="V20">
-        <v>220.7299957275391</v>
+        <v>212.4799957275391</v>
       </c>
       <c r="W20">
-        <v>212.4799957275391</v>
+        <v>217.9100036621094</v>
       </c>
       <c r="X20">
-        <v>217.9100036621094</v>
+        <v>216.2700042724609</v>
       </c>
       <c r="Y20">
-        <v>216.2700042724609</v>
+        <v>216.2400054931641</v>
       </c>
       <c r="Z20">
-        <v>216.2400054931641</v>
+        <v>217.2100067138672</v>
       </c>
       <c r="AA20">
-        <v>217.2100067138672</v>
+        <v>216.6699981689453</v>
       </c>
       <c r="AB20">
-        <v>216.6699981689453</v>
+        <v>215.6699981689453</v>
       </c>
       <c r="AC20">
-        <v>215.6699981689453</v>
+        <v>214.5099945068359</v>
       </c>
       <c r="AD20">
-        <v>214.5099945068359</v>
+        <v>211.3399963378906</v>
       </c>
       <c r="AE20">
-        <v>211.3399963378906</v>
+        <v>216.6000061035156</v>
       </c>
       <c r="AF20">
-        <v>216.6000061035156</v>
+        <v>220.5</v>
       </c>
       <c r="AG20">
-        <v>220.5</v>
+        <v>219.6000061035156</v>
       </c>
       <c r="AH20">
-        <v>219.6000061035156</v>
+        <v>213.9600067138672</v>
       </c>
       <c r="AI20">
-        <v>213.9600067138672</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="AJ20">
-        <v>210.8600006103516</v>
+        <v>207.1100006103516</v>
       </c>
       <c r="AK20">
-        <v>207.1100006103516</v>
+        <v>208.3000030517578</v>
       </c>
       <c r="AL20">
-        <v>208.3000030517578</v>
+        <v>206.6799926757812</v>
       </c>
       <c r="AM20">
-        <v>206.6799926757812</v>
+        <v>206.8500061035156</v>
       </c>
       <c r="AN20">
-        <v>206.8500061035156</v>
+        <v>203.1900024414062</v>
       </c>
       <c r="AO20">
-        <v>203.1900024414062</v>
+        <v>202.0399932861328</v>
       </c>
       <c r="AP20">
-        <v>202.0399932861328</v>
+        <v>202.4299926757812</v>
       </c>
       <c r="AQ20">
-        <v>202.4299926757812</v>
+        <v>204.9199981689453</v>
       </c>
       <c r="AR20">
-        <v>204.9199981689453</v>
+        <v>200.5500030517578</v>
       </c>
       <c r="AS20">
-        <v>200.5500030517578</v>
+        <v>196.1000061035156</v>
       </c>
       <c r="AT20">
-        <v>196.1000061035156</v>
+        <v>196.6100006103516</v>
       </c>
       <c r="AU20">
-        <v>196.6100006103516</v>
+        <v>200.1999969482422</v>
       </c>
       <c r="AV20">
-        <v>200.1999969482422</v>
+        <v>196.4600067138672</v>
       </c>
       <c r="AW20">
         <v>196.4600067138672</v>
       </c>
       <c r="AX20">
-        <v>196.4600067138672</v>
+        <v>193.0700073242188</v>
       </c>
       <c r="AY20">
-        <v>193.0700073242188</v>
+        <v>194.4799957275391</v>
       </c>
       <c r="AZ20">
-        <v>194.4799957275391</v>
+        <v>194.7200012207031</v>
       </c>
       <c r="BA20">
-        <v>194.7200012207031</v>
+        <v>195.1399993896484</v>
       </c>
       <c r="BB20">
-        <v>195.1399993896484</v>
+        <v>195.8200073242188</v>
       </c>
       <c r="BC20">
-        <v>195.8200073242188</v>
+        <v>195.9100036621094</v>
       </c>
       <c r="BD20">
-        <v>195.9100036621094</v>
+        <v>199.3999938964844</v>
       </c>
       <c r="BE20">
-        <v>199.3999938964844</v>
+        <v>199.2599945068359</v>
       </c>
       <c r="BF20">
-        <v>199.2599945068359</v>
+        <v>201.1399993896484</v>
       </c>
       <c r="BG20">
-        <v>201.1399993896484</v>
+        <v>198.0700073242188</v>
       </c>
       <c r="BH20">
-        <v>198.0700073242188</v>
-      </c>
-      <c r="BI20">
         <v>194.3500061035156</v>
       </c>
     </row>
-    <row r="21" spans="1:61">
+    <row r="21" spans="1:60">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>48.00857162475586</v>
+        <v>47.51980590820312</v>
       </c>
       <c r="C21">
-        <v>47.51980590820312</v>
+        <v>47.56967926025391</v>
       </c>
       <c r="D21">
-        <v>47.56967926025391</v>
+        <v>48.06841659545898</v>
       </c>
       <c r="E21">
-        <v>48.06841659545898</v>
+        <v>45.47497940063477</v>
       </c>
       <c r="F21">
-        <v>45.47497940063477</v>
+        <v>44.32787704467773</v>
       </c>
       <c r="G21">
-        <v>44.32787704467773</v>
+        <v>47.02106857299805</v>
       </c>
       <c r="H21">
-        <v>47.02106857299805</v>
+        <v>47.77915191650391</v>
       </c>
       <c r="I21">
-        <v>47.77915191650391</v>
+        <v>50.11325073242188</v>
       </c>
       <c r="J21">
-        <v>50.11325073242188</v>
+        <v>52.2578239440918</v>
       </c>
       <c r="K21">
-        <v>52.2578239440918</v>
+        <v>53.08573150634766</v>
       </c>
       <c r="L21">
+        <v>52.29772186279297</v>
+      </c>
+      <c r="M21">
         <v>53.08573150634766</v>
       </c>
-      <c r="M21">
+      <c r="N21">
+        <v>54.54204559326172</v>
+      </c>
+      <c r="O21">
+        <v>54.24280166625977</v>
+      </c>
+      <c r="P21">
+        <v>58.64167785644531</v>
+      </c>
+      <c r="Q21">
+        <v>59.6690788269043</v>
+      </c>
+      <c r="R21">
+        <v>58.5618782043457</v>
+      </c>
+      <c r="S21">
+        <v>57.46465301513672</v>
+      </c>
+      <c r="T21">
+        <v>55.54949569702148</v>
+      </c>
+      <c r="U21">
+        <v>52.99595642089844</v>
+      </c>
+      <c r="V21">
+        <v>52.75656127929688</v>
+      </c>
+      <c r="W21">
+        <v>53.31515121459961</v>
+      </c>
+      <c r="X21">
         <v>52.29772186279297</v>
       </c>
-      <c r="N21">
-        <v>53.08573150634766</v>
-      </c>
-      <c r="O21">
-        <v>54.54204559326172</v>
-      </c>
-      <c r="P21">
-        <v>54.24280166625977</v>
-      </c>
-      <c r="Q21">
-        <v>58.64167785644531</v>
-      </c>
-      <c r="R21">
-        <v>59.6690788269043</v>
-      </c>
-      <c r="S21">
-        <v>58.5618782043457</v>
-      </c>
-      <c r="T21">
-        <v>57.46465301513672</v>
-      </c>
-      <c r="U21">
-        <v>55.54949569702148</v>
-      </c>
-      <c r="V21">
-        <v>52.99595642089844</v>
-      </c>
-      <c r="W21">
-        <v>52.75656127929688</v>
-      </c>
-      <c r="X21">
-        <v>53.31515121459961</v>
-      </c>
       <c r="Y21">
-        <v>52.29772186279297</v>
+        <v>53.30517196655273</v>
       </c>
       <c r="Z21">
-        <v>53.30517196655273</v>
+        <v>55.09065628051758</v>
       </c>
       <c r="AA21">
-        <v>55.09065628051758</v>
+        <v>54.27272796630859</v>
       </c>
       <c r="AB21">
-        <v>54.27272796630859</v>
+        <v>52.17802429199219</v>
       </c>
       <c r="AC21">
-        <v>52.17802429199219</v>
+        <v>52.10820388793945</v>
       </c>
       <c r="AD21">
-        <v>52.10820388793945</v>
+        <v>50.74165725708008</v>
       </c>
       <c r="AE21">
-        <v>50.74165725708008</v>
+        <v>51.69923782348633</v>
       </c>
       <c r="AF21">
-        <v>51.69923782348633</v>
+        <v>54.30265045166016</v>
       </c>
       <c r="AG21">
-        <v>54.30265045166016</v>
+        <v>51.86880493164062</v>
       </c>
       <c r="AH21">
-        <v>51.86880493164062</v>
+        <v>55.88863754272461</v>
       </c>
       <c r="AI21">
-        <v>55.88863754272461</v>
+        <v>58.75139999389648</v>
       </c>
       <c r="AJ21">
-        <v>58.75139999389648</v>
+        <v>55.08068466186523</v>
       </c>
       <c r="AK21">
-        <v>55.08068466186523</v>
+        <v>61.933349609375</v>
       </c>
       <c r="AL21">
-        <v>61.933349609375</v>
+        <v>55.27020263671875</v>
       </c>
       <c r="AM21">
-        <v>55.27020263671875</v>
+        <v>55.73901748657227</v>
       </c>
       <c r="AN21">
-        <v>55.73901748657227</v>
+        <v>56.5369987487793</v>
       </c>
       <c r="AO21">
-        <v>56.5369987487793</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="AP21">
-        <v>61.04000091552734</v>
+        <v>60.7599983215332</v>
       </c>
       <c r="AQ21">
-        <v>60.7599983215332</v>
+        <v>61.75</v>
       </c>
       <c r="AR21">
-        <v>61.75</v>
+        <v>61.02999877929688</v>
       </c>
       <c r="AS21">
-        <v>61.02999877929688</v>
+        <v>62.33000183105469</v>
       </c>
       <c r="AT21">
-        <v>62.33000183105469</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="AU21">
-        <v>63.52000045776367</v>
+        <v>62.93999862670898</v>
       </c>
       <c r="AV21">
-        <v>62.93999862670898</v>
+        <v>62.63000106811523</v>
       </c>
       <c r="AW21">
-        <v>62.63000106811523</v>
+        <v>61.4900016784668</v>
       </c>
       <c r="AX21">
-        <v>61.4900016784668</v>
+        <v>63.88999938964844</v>
       </c>
       <c r="AY21">
-        <v>63.88999938964844</v>
+        <v>64.58000183105469</v>
       </c>
       <c r="AZ21">
-        <v>64.58000183105469</v>
+        <v>69.33000183105469</v>
       </c>
       <c r="BA21">
-        <v>69.33000183105469</v>
+        <v>68.36000061035156</v>
       </c>
       <c r="BB21">
-        <v>68.36000061035156</v>
+        <v>70.48000335693359</v>
       </c>
       <c r="BC21">
-        <v>70.48000335693359</v>
+        <v>72.08999633789062</v>
       </c>
       <c r="BD21">
-        <v>72.08999633789062</v>
+        <v>71</v>
       </c>
       <c r="BE21">
-        <v>71</v>
+        <v>73.45999908447266</v>
       </c>
       <c r="BF21">
-        <v>73.45999908447266</v>
+        <v>70.33000183105469</v>
       </c>
       <c r="BG21">
-        <v>70.33000183105469</v>
+        <v>68.80999755859375</v>
       </c>
       <c r="BH21">
-        <v>68.80999755859375</v>
+        <v>63.11000061035156</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -439,21 +439,21 @@
     <t>проходит</t>
   </si>
   <si>
+    <t>Micron Technology</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Salesforce</t>
+  </si>
+  <si>
     <t>NTAP</t>
   </si>
   <si>
     <t>NetApp</t>
   </si>
   <si>
-    <t>Micron Technology</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>Salesforce</t>
-  </si>
-  <si>
     <t>Dell Technologies</t>
   </si>
   <si>
@@ -463,16 +463,34 @@
     <t>Chevron Corporation</t>
   </si>
   <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>Lilly (Eli)</t>
+  </si>
+  <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
+  </si>
+  <si>
     <t>FTNT</t>
   </si>
   <si>
     <t>Fortinet</t>
   </si>
   <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
+    <t>TWLO</t>
+  </si>
+  <si>
+    <t>Twilio</t>
   </si>
   <si>
     <t>COP</t>
@@ -487,22 +505,19 @@
     <t>EOG Resources</t>
   </si>
   <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
-  </si>
-  <si>
-    <t>TWLO</t>
-  </si>
-  <si>
-    <t>Twilio</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>Lilly (Eli)</t>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>Veeva Systems</t>
+  </si>
+  <si>
+    <t>WBD</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
   <si>
     <t>SMCI</t>
@@ -511,37 +526,28 @@
     <t>Supermicro</t>
   </si>
   <si>
-    <t>WBD</t>
-  </si>
-  <si>
-    <t>nan</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>XOM</t>
-  </si>
-  <si>
-    <t>ExxonMobil</t>
-  </si>
-  <si>
-    <t>DVN</t>
-  </si>
-  <si>
-    <t>Devon Energy</t>
-  </si>
-  <si>
-    <t>HUM</t>
-  </si>
-  <si>
-    <t>Humana</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>Veeva Systems</t>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>Williams-Sonoma, Inc.</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Gartner</t>
+  </si>
+  <si>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
+  </si>
+  <si>
+    <t>SJM</t>
+  </si>
+  <si>
+    <t>J.M. Smucker Company (The)</t>
   </si>
   <si>
     <t>MA</t>
@@ -550,16 +556,10 @@
     <t>Mastercard</t>
   </si>
   <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
-    <t>FANG</t>
-  </si>
-  <si>
-    <t>Diamondback Energy</t>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
   </si>
   <si>
     <t>Факторы и самообучение</t>
@@ -640,7 +640,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-10-16 00:28 UTC · данные на 2026-10-15 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-17 00:36 UTC · данные на 2026-10-15 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -724,7 +724,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-10-16 00:28 UTC</t>
+    <t>2026-10-17 00:36 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -5430,10 +5430,10 @@
         <v>48</v>
       </c>
       <c r="E5" s="11">
-        <v>484.9200134277344</v>
+        <v>476.9200134277344</v>
       </c>
       <c r="F5" s="20">
-        <v>1.143604366996855</v>
+        <v>1.092971894934843</v>
       </c>
       <c r="G5" s="13">
         <v>0.5120832578157225</v>
@@ -5445,16 +5445,16 @@
         <v>2.358223271893585</v>
       </c>
       <c r="J5" s="13">
-        <v>2.785637453087448</v>
+        <v>2.654628830364357</v>
       </c>
       <c r="K5" s="13">
         <v>0.8322577472718413</v>
       </c>
       <c r="L5" s="13">
-        <v>-0.1279325713710688</v>
+        <v>-0.1227695717993949</v>
       </c>
       <c r="M5" s="13">
-        <v>-0.2600548931069835</v>
+        <v>-0.4055507083492996</v>
       </c>
       <c r="N5" s="13">
         <v>15.755887</v>
@@ -5469,10 +5469,10 @@
         <v>0.537</v>
       </c>
       <c r="R5" s="15">
-        <v>1.188510822240728</v>
+        <v>1.121866293373595</v>
       </c>
       <c r="S5" s="12">
-        <v>80.00121278466597</v>
+        <v>74.4226965709481</v>
       </c>
       <c r="T5" s="10" t="s">
         <v>136</v>
@@ -5492,10 +5492,10 @@
         <v>48</v>
       </c>
       <c r="E6" s="11">
-        <v>459.7799987792969</v>
+        <v>444.0599975585938</v>
       </c>
       <c r="F6" s="20">
-        <v>1.134211724033697</v>
+        <v>1.082783279249571</v>
       </c>
       <c r="G6" s="13">
         <v>0.5257662583602529</v>
@@ -5507,16 +5507,16 @@
         <v>2.788833462425317</v>
       </c>
       <c r="J6" s="13">
-        <v>2.755020669378902</v>
+        <v>2.541719572839457</v>
       </c>
       <c r="K6" s="13">
         <v>0.6587310680489812</v>
       </c>
       <c r="L6" s="13">
-        <v>0.02707969585094485</v>
+        <v>-0.01405736006428712</v>
       </c>
       <c r="M6" s="13">
-        <v>-0.4718842265256571</v>
+        <v>-0.2840078823678914</v>
       </c>
       <c r="N6" s="13">
         <v>18.08045</v>
@@ -5531,10 +5531,10 @@
         <v>0.517</v>
       </c>
       <c r="R6" s="15">
-        <v>0.9734034513047376</v>
+        <v>0.8527924104432805</v>
       </c>
       <c r="S6" s="12">
-        <v>76.52079183018837</v>
+        <v>66.20489565484002</v>
       </c>
       <c r="T6" s="10" t="s">
         <v>136</v>
@@ -5554,10 +5554,10 @@
         <v>48</v>
       </c>
       <c r="E7" s="11">
-        <v>297.2900085449219</v>
+        <v>289.2000122070312</v>
       </c>
       <c r="F7" s="20">
-        <v>1.008427519545958</v>
+        <v>0.9411141700809874</v>
       </c>
       <c r="G7" s="13">
         <v>0.4033582074212857</v>
@@ -5569,16 +5569,16 @@
         <v>2.328125318139155</v>
       </c>
       <c r="J7" s="13">
-        <v>2.525506257180785</v>
+        <v>2.266476440868649</v>
       </c>
       <c r="K7" s="13">
         <v>0.7449588314899703</v>
       </c>
       <c r="L7" s="13">
-        <v>0.3505139366089186</v>
+        <v>0.3175682163354259</v>
       </c>
       <c r="M7" s="13">
-        <v>-0.4896032044296331</v>
+        <v>-0.3349489713661307</v>
       </c>
       <c r="N7" s="13">
         <v>15.896</v>
@@ -5593,10 +5593,10 @@
         <v>0.531</v>
       </c>
       <c r="R7" s="15">
-        <v>0.8647031541042864</v>
+        <v>0.7929694413985626</v>
       </c>
       <c r="S7" s="12">
-        <v>79.03573507405349</v>
+        <v>68.65950380818738</v>
       </c>
       <c r="T7" s="10" t="s">
         <v>136</v>
@@ -5616,10 +5616,10 @@
         <v>63</v>
       </c>
       <c r="E8" s="11">
-        <v>70.16000366210938</v>
+        <v>70.51000213623047</v>
       </c>
       <c r="F8" s="20">
-        <v>0.8974445030180477</v>
+        <v>0.86365612643064</v>
       </c>
       <c r="G8" s="13">
         <v>1.255811942784209</v>
@@ -5631,16 +5631,16 @@
         <v>-0.5870526183679002</v>
       </c>
       <c r="J8" s="13">
-        <v>1.558174597985955</v>
+        <v>1.426430744770274</v>
       </c>
       <c r="K8" s="13">
         <v>4.037113416620117</v>
       </c>
       <c r="L8" s="13">
-        <v>0.01563980465027959</v>
+        <v>0.05745677158289661</v>
       </c>
       <c r="M8" s="13">
-        <v>-0.04799092386195003</v>
+        <v>-0.007668906845199941</v>
       </c>
       <c r="N8" s="13">
         <v>12.221939</v>
@@ -5655,10 +5655,10 @@
         <v>0.046</v>
       </c>
       <c r="R8" s="15">
-        <v>0.8659576199291157</v>
+        <v>0.8079487727238581</v>
       </c>
       <c r="S8" s="12">
-        <v>68.08093597350666</v>
+        <v>68.87073489813802</v>
       </c>
       <c r="T8" s="10" t="s">
         <v>136</v>
@@ -5669,58 +5669,58 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>58</v>
+        <v>137</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E9" s="11">
-        <v>377.8200073242188</v>
+        <v>931.239990234375</v>
       </c>
       <c r="F9" s="20">
-        <v>0.8818249596899992</v>
+        <v>0.8611243337134505</v>
       </c>
       <c r="G9" s="13">
-        <v>1.187286552445482</v>
+        <v>-0.1172294581697382</v>
       </c>
       <c r="H9" s="13">
-        <v>-0.1198805307813126</v>
+        <v>2.151002143997514</v>
       </c>
       <c r="I9" s="13">
-        <v>-0.3892490054509348</v>
+        <v>4.12785569855674</v>
       </c>
       <c r="J9" s="13">
-        <v>0.7371472278044641</v>
+        <v>1.29165159756436</v>
       </c>
       <c r="K9" s="13">
-        <v>3.994299457555074</v>
+        <v>-0.3486877085504021</v>
       </c>
       <c r="L9" s="13">
-        <v>0.9926924723957937</v>
+        <v>-2.427812056114018</v>
       </c>
       <c r="M9" s="13">
-        <v>-0.4225310733972489</v>
+        <v>-0.9338063448461471</v>
       </c>
       <c r="N9" s="13">
-        <v>9.904647000000001</v>
+        <v>13.84367</v>
       </c>
       <c r="O9" s="13">
-        <v>2.3224251</v>
+        <v>11.533936</v>
       </c>
       <c r="P9" s="15">
-        <v>0.26511</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.003</v>
+        <v>3.793</v>
       </c>
       <c r="R9" s="15">
-        <v>0.2718294193672723</v>
+        <v>1.03733299007094</v>
       </c>
       <c r="S9" s="12">
-        <v>63.94899117709577</v>
+        <v>39.17953272825716</v>
       </c>
       <c r="T9" s="10" t="s">
         <v>136</v>
@@ -5731,58 +5731,58 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>137</v>
+        <v>8</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E10" s="11">
-        <v>222.1999969482422</v>
+        <v>383.8900146484375</v>
       </c>
       <c r="F10" s="20">
-        <v>0.8487173035719388</v>
+        <v>0.8578744789909157</v>
       </c>
       <c r="G10" s="13">
-        <v>-0.6400146282615523</v>
+        <v>1.187286552445482</v>
       </c>
       <c r="H10" s="13">
-        <v>1.366445373608231</v>
+        <v>-0.1198805307813126</v>
       </c>
       <c r="I10" s="13">
-        <v>0.4239293519712278</v>
+        <v>-0.3892490054509348</v>
       </c>
       <c r="J10" s="13">
-        <v>2.227392860297685</v>
+        <v>0.6631308323587954</v>
       </c>
       <c r="K10" s="13">
-        <v>0.535548548847568</v>
+        <v>3.994299457555074</v>
       </c>
       <c r="L10" s="13">
-        <v>-0.432215872556926</v>
+        <v>0.9970090328741424</v>
       </c>
       <c r="M10" s="13">
-        <v>-0.04568737391274738</v>
+        <v>-0.4475880195732954</v>
       </c>
       <c r="N10" s="13">
-        <v>33.448517</v>
+        <v>9.904647000000001</v>
       </c>
       <c r="O10" s="13">
-        <v>31.089407</v>
+        <v>2.3224251</v>
       </c>
       <c r="P10" s="15">
-        <v>1.14818</v>
+        <v>0.26511</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.299</v>
+        <v>0.003</v>
       </c>
       <c r="R10" s="15">
-        <v>1.226428808465815</v>
+        <v>0.2943813556025821</v>
       </c>
       <c r="S10" s="12">
-        <v>57.00448767884139</v>
+        <v>68.93138565302499</v>
       </c>
       <c r="T10" s="10" t="s">
         <v>136</v>
@@ -5793,58 +5793,58 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>11</v>
+        <v>138</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>64</v>
+        <v>139</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="E11" s="11">
-        <v>347.6400146484375</v>
+        <v>246.7400054931641</v>
       </c>
       <c r="F11" s="20">
-        <v>0.8335946736879928</v>
+        <v>0.8313591679828858</v>
       </c>
       <c r="G11" s="13">
-        <v>-0.3285343560247656</v>
+        <v>0.445387850826149</v>
       </c>
       <c r="H11" s="13">
-        <v>1.459641297606501</v>
+        <v>0.5371012848843359</v>
       </c>
       <c r="I11" s="13">
-        <v>1.329512425464752</v>
+        <v>0.1720715631623876</v>
       </c>
       <c r="J11" s="13">
-        <v>0.1234071019879688</v>
+        <v>1.130507161632974</v>
       </c>
       <c r="K11" s="13">
-        <v>4.037113416620117</v>
+        <v>3.685807583381099</v>
       </c>
       <c r="L11" s="13">
-        <v>0.1382840507197841</v>
+        <v>-1.758822300025664</v>
       </c>
       <c r="M11" s="13">
-        <v>-0.04419720031320588</v>
+        <v>-0.3484215944704748</v>
       </c>
       <c r="N11" s="13">
-        <v>17.644756</v>
+        <v>20.963404</v>
       </c>
       <c r="O11" s="13">
-        <v>6.909384</v>
+        <v>4.913579</v>
       </c>
       <c r="P11" s="15">
-        <v>0.48676</v>
+        <v>0.19381</v>
       </c>
       <c r="Q11" s="15">
-        <v>0.242</v>
+        <v>0.108</v>
       </c>
       <c r="R11" s="15">
-        <v>0.03248472636154864</v>
+        <v>0.3674652365282667</v>
       </c>
       <c r="S11" s="12">
-        <v>51.27427440341948</v>
+        <v>61.59489832002181</v>
       </c>
       <c r="T11" s="10" t="s">
         <v>136</v>
@@ -5855,58 +5855,58 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="E12" s="11">
-        <v>61.40999984741211</v>
+        <v>349.2200012207031</v>
       </c>
       <c r="F12" s="20">
-        <v>0.8303882255887448</v>
+        <v>0.8250362077587839</v>
       </c>
       <c r="G12" s="13">
-        <v>0.5555932315613028</v>
+        <v>-0.3285343560247656</v>
       </c>
       <c r="H12" s="13">
-        <v>0.615262828357206</v>
+        <v>1.459641297606501</v>
       </c>
       <c r="I12" s="13">
-        <v>3.077929577016555</v>
+        <v>1.329512425464752</v>
       </c>
       <c r="J12" s="13">
-        <v>0.6897836443150713</v>
+        <v>0.07995121297483619</v>
       </c>
       <c r="K12" s="13">
-        <v>0.9345527958260584</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L12" s="13">
-        <v>0.1327018018753043</v>
+        <v>0.161483451001501</v>
       </c>
       <c r="M12" s="13">
-        <v>-0.03621379046581302</v>
+        <v>-0.005617990840357273</v>
       </c>
       <c r="N12" s="13">
-        <v>17.076704</v>
+        <v>17.644756</v>
       </c>
       <c r="O12" s="13">
-        <v>1.7959902</v>
+        <v>6.909384</v>
       </c>
       <c r="P12" s="15">
-        <v>0.10629</v>
+        <v>0.48676</v>
       </c>
       <c r="Q12" s="15">
-        <v>0.534</v>
+        <v>0.242</v>
       </c>
       <c r="R12" s="15">
-        <v>0.1100974115596502</v>
+        <v>0.04057265845847358</v>
       </c>
       <c r="S12" s="12">
-        <v>61.82698456128156</v>
+        <v>52.8329870820505</v>
       </c>
       <c r="T12" s="10" t="s">
         <v>136</v>
@@ -5917,58 +5917,58 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>91</v>
+        <v>4</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>139</v>
+        <v>52</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E13" s="11">
-        <v>914.1300048828125</v>
+        <v>60.66999816894531</v>
       </c>
       <c r="F13" s="20">
-        <v>0.8227437804748921</v>
+        <v>0.7691326543949388</v>
       </c>
       <c r="G13" s="13">
-        <v>-0.1172294581697382</v>
+        <v>0.5555932315613028</v>
       </c>
       <c r="H13" s="13">
-        <v>2.151002143997514</v>
+        <v>0.615262828357206</v>
       </c>
       <c r="I13" s="13">
-        <v>4.12785569855674</v>
+        <v>3.077929577016555</v>
       </c>
       <c r="J13" s="13">
-        <v>1.169969808953976</v>
+        <v>0.4361078354288994</v>
       </c>
       <c r="K13" s="13">
-        <v>-0.3486877085504021</v>
+        <v>0.9345527958260584</v>
       </c>
       <c r="L13" s="13">
-        <v>-2.422008617716169</v>
+        <v>0.1503275139176792</v>
       </c>
       <c r="M13" s="13">
-        <v>-0.9616091318375725</v>
+        <v>0.1361565689029777</v>
       </c>
       <c r="N13" s="13">
-        <v>13.84367</v>
+        <v>17.076704</v>
       </c>
       <c r="O13" s="13">
-        <v>11.533936</v>
+        <v>1.7959902</v>
       </c>
       <c r="P13" s="15">
-        <v>0.8826000000000001</v>
+        <v>0.10629</v>
       </c>
       <c r="Q13" s="15">
-        <v>3.793</v>
+        <v>0.534</v>
       </c>
       <c r="R13" s="15">
-        <v>1.004283947628566</v>
+        <v>0.07666450737259356</v>
       </c>
       <c r="S13" s="12">
-        <v>36.26124679880706</v>
+        <v>57.61667696751463</v>
       </c>
       <c r="T13" s="10" t="s">
         <v>136</v>
@@ -5979,58 +5979,58 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="D14" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E14" s="11">
-        <v>63.11000061035156</v>
+        <v>214.6999969482422</v>
       </c>
       <c r="F14" s="20">
-        <v>0.7417345846425372</v>
+        <v>0.7207501015337072</v>
       </c>
       <c r="G14" s="13">
-        <v>0.2210528163067884</v>
+        <v>-0.6400146282615523</v>
       </c>
       <c r="H14" s="13">
-        <v>-0.5344576345348465</v>
+        <v>1.366445373608231</v>
       </c>
       <c r="I14" s="13">
-        <v>2.11370107259597</v>
+        <v>0.4239293519712278</v>
       </c>
       <c r="J14" s="13">
-        <v>2.330621670522358</v>
+        <v>1.836324432712797</v>
       </c>
       <c r="K14" s="13">
-        <v>0.3679132074995579</v>
+        <v>0.535548548847568</v>
       </c>
       <c r="L14" s="13">
-        <v>-2.06572026997574</v>
+        <v>-0.4740818126237527</v>
       </c>
       <c r="M14" s="13">
-        <v>-0.5413084735602033</v>
+        <v>-0.1473713408971897</v>
       </c>
       <c r="N14" s="13">
-        <v>37.86598</v>
+        <v>33.448517</v>
       </c>
       <c r="O14" s="13">
-        <v>3.6796231</v>
+        <v>31.089407</v>
       </c>
       <c r="P14" s="15">
-        <v>0.10936</v>
+        <v>1.14818</v>
       </c>
       <c r="Q14" s="15">
-        <v>0.337</v>
+        <v>0.299</v>
       </c>
       <c r="R14" s="15">
-        <v>1.577365282101474</v>
+        <v>1.08176948747154</v>
       </c>
       <c r="S14" s="12">
-        <v>48.38639197874727</v>
+        <v>51.02214116011656</v>
       </c>
       <c r="T14" s="10" t="s">
         <v>136</v>
@@ -6041,58 +6041,58 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>140</v>
+        <v>18</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E15" s="11">
-        <v>235.9499969482422</v>
+        <v>235.3500061035156</v>
       </c>
       <c r="F15" s="20">
-        <v>0.7369781494044974</v>
+        <v>0.6618151676707162</v>
       </c>
       <c r="G15" s="13">
-        <v>0.445387850826149</v>
+        <v>0.1972144638373766</v>
       </c>
       <c r="H15" s="13">
-        <v>0.5371012848843359</v>
+        <v>0.0272457680026615</v>
       </c>
       <c r="I15" s="13">
-        <v>0.1720715631623876</v>
+        <v>-0.878827185566031</v>
       </c>
       <c r="J15" s="13">
-        <v>0.8444998961780219</v>
+        <v>0.9596041536135097</v>
       </c>
       <c r="K15" s="13">
-        <v>3.685807583381099</v>
+        <v>3.526205884589703</v>
       </c>
       <c r="L15" s="13">
-        <v>-1.780884631767303</v>
+        <v>0.6097669183954363</v>
       </c>
       <c r="M15" s="13">
-        <v>-0.4391103324380299</v>
+        <v>-0.4721500935297228</v>
       </c>
       <c r="N15" s="13">
-        <v>20.963404</v>
+        <v>40.090588</v>
       </c>
       <c r="O15" s="13">
-        <v>4.913579</v>
+        <v>1.7687485</v>
       </c>
       <c r="P15" s="15">
-        <v>0.19381</v>
+        <v>0.04575</v>
       </c>
       <c r="Q15" s="15">
-        <v>0.108</v>
+        <v>0.034</v>
       </c>
       <c r="R15" s="15">
-        <v>0.3343194829716822</v>
+        <v>0.3370639722245314</v>
       </c>
       <c r="S15" s="12">
-        <v>53.6771808177494</v>
+        <v>66.05219406942329</v>
       </c>
       <c r="T15" s="10" t="s">
         <v>136</v>
@@ -6103,58 +6103,58 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E16" s="11">
-        <v>507.9299926757812</v>
+        <v>156.6300048828125</v>
       </c>
       <c r="F16" s="20">
-        <v>0.6647884886059343</v>
+        <v>0.6461521903134528</v>
       </c>
       <c r="G16" s="13">
-        <v>-0.1075886523285822</v>
+        <v>0.4755572880593366</v>
       </c>
       <c r="H16" s="13">
-        <v>-0.8447423148789104</v>
+        <v>-0.5579052235604326</v>
       </c>
       <c r="I16" s="13">
-        <v>2.119917693224531</v>
+        <v>-0.05791369034948607</v>
       </c>
       <c r="J16" s="13">
-        <v>2.115454346998049</v>
+        <v>0.7514149812413122</v>
       </c>
       <c r="K16" s="13">
-        <v>1.69239307699997</v>
+        <v>3.44319157817136</v>
       </c>
       <c r="L16" s="13">
-        <v>-2.949498962581992</v>
+        <v>0.4303657702265942</v>
       </c>
       <c r="M16" s="13">
-        <v>-0.6679011062654987</v>
+        <v>-0.1102668337395311</v>
       </c>
       <c r="N16" s="13">
-        <v>33.41277</v>
+        <v>15.954309</v>
       </c>
       <c r="O16" s="13">
-        <v>-262.80716</v>
+        <v>3.911704</v>
       </c>
       <c r="P16" s="15">
-        <v>0</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q16" s="15">
-        <v>0.577</v>
+        <v>0.053</v>
       </c>
       <c r="R16" s="15">
-        <v>1.878742764702428</v>
+        <v>0.2857995173665979</v>
       </c>
       <c r="S16" s="12">
-        <v>41.92176235596323</v>
+        <v>52.35854975129516</v>
       </c>
       <c r="T16" s="10" t="s">
         <v>136</v>
@@ -6165,58 +6165,58 @@
         <v>13</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E17" s="11">
-        <v>47.36999893188477</v>
+        <v>124.4100036621094</v>
       </c>
       <c r="F17" s="20">
-        <v>0.6481137457849795</v>
+        <v>0.6440113224837559</v>
       </c>
       <c r="G17" s="13">
-        <v>0.9861002278279252</v>
+        <v>0.3844623079993796</v>
       </c>
       <c r="H17" s="13">
-        <v>0.5612515707924636</v>
+        <v>-0.1225159176090149</v>
       </c>
       <c r="I17" s="13">
-        <v>-0.2947421241753646</v>
+        <v>0.4303409832118458</v>
       </c>
       <c r="J17" s="13">
-        <v>1.738567162804421</v>
+        <v>0.1599978862524996</v>
       </c>
       <c r="K17" s="13">
-        <v>-0.5639893290676546</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L17" s="13">
-        <v>-0.5154522265252964</v>
+        <v>0.02035844693912237</v>
       </c>
       <c r="M17" s="13">
-        <v>-0.158432873687435</v>
+        <v>0.2212759106701755</v>
       </c>
       <c r="N17" s="13">
-        <v>9.699789000000001</v>
+        <v>14.45067</v>
       </c>
       <c r="O17" s="13">
-        <v>2.2914796</v>
+        <v>6.500466</v>
       </c>
       <c r="P17" s="15">
-        <v>0.26659</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q17" s="15">
-        <v>0.092</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R17" s="15">
-        <v>0.3120957736347147</v>
+        <v>0.2449715128807588</v>
       </c>
       <c r="S17" s="12">
-        <v>64.70245176621867</v>
+        <v>62.06776334832654</v>
       </c>
       <c r="T17" s="10" t="s">
         <v>136</v>
@@ -6227,58 +6227,58 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E18" s="11">
-        <v>155.3099975585938</v>
+        <v>47.22999954223633</v>
       </c>
       <c r="F18" s="20">
-        <v>0.6417892365552625</v>
+        <v>0.5855790213193544</v>
       </c>
       <c r="G18" s="13">
-        <v>0.4755572880593366</v>
+        <v>0.9861002278279252</v>
       </c>
       <c r="H18" s="13">
-        <v>-0.5579052235604326</v>
+        <v>0.5612515707924636</v>
       </c>
       <c r="I18" s="13">
-        <v>-0.05791369034948607</v>
+        <v>-0.2947421241753646</v>
       </c>
       <c r="J18" s="13">
-        <v>0.7919848434204225</v>
+        <v>1.513053585042006</v>
       </c>
       <c r="K18" s="13">
-        <v>3.44319157817136</v>
+        <v>-0.5639893290676546</v>
       </c>
       <c r="L18" s="13">
-        <v>0.4146312903387912</v>
+        <v>-0.5012981554450477</v>
       </c>
       <c r="M18" s="13">
-        <v>-0.3051398789727215</v>
+        <v>-0.1050565662088816</v>
       </c>
       <c r="N18" s="13">
-        <v>15.954309</v>
+        <v>9.699789000000001</v>
       </c>
       <c r="O18" s="13">
-        <v>3.911704</v>
+        <v>2.2914796</v>
       </c>
       <c r="P18" s="15">
-        <v>0.26408002</v>
+        <v>0.26659</v>
       </c>
       <c r="Q18" s="15">
-        <v>0.053</v>
+        <v>0.092</v>
       </c>
       <c r="R18" s="15">
-        <v>0.285755006502739</v>
+        <v>0.2633449527980081</v>
       </c>
       <c r="S18" s="12">
-        <v>49.77755513642406</v>
+        <v>63.849234543732</v>
       </c>
       <c r="T18" s="10" t="s">
         <v>136</v>
@@ -6289,58 +6289,58 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E19" s="11">
-        <v>232.8300018310547</v>
+        <v>254.7599945068359</v>
       </c>
       <c r="F19" s="20">
-        <v>0.6410855620214339</v>
+        <v>0.5809652377743185</v>
       </c>
       <c r="G19" s="13">
-        <v>0.1972144638373766</v>
+        <v>-0.02977335660029285</v>
       </c>
       <c r="H19" s="13">
-        <v>0.0272457680026615</v>
+        <v>0.160055113268548</v>
       </c>
       <c r="I19" s="13">
-        <v>-0.878827185566031</v>
+        <v>0.9707254877878508</v>
       </c>
       <c r="J19" s="13">
-        <v>0.9356240407770618</v>
+        <v>-0.01180503663604651</v>
       </c>
       <c r="K19" s="13">
-        <v>3.526205884589703</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L19" s="13">
-        <v>0.5488559694418522</v>
+        <v>-0.5235848713354175</v>
       </c>
       <c r="M19" s="13">
-        <v>-0.595661529293887</v>
+        <v>0.1768258542142923</v>
       </c>
       <c r="N19" s="13">
-        <v>40.090588</v>
+        <v>21.112629</v>
       </c>
       <c r="O19" s="13">
-        <v>1.7687485</v>
+        <v>5.1299944</v>
       </c>
       <c r="P19" s="15">
-        <v>0.04575</v>
+        <v>0.30558002</v>
       </c>
       <c r="Q19" s="15">
-        <v>0.034</v>
+        <v>0.196</v>
       </c>
       <c r="R19" s="15">
-        <v>0.2896311647804755</v>
+        <v>0.02026430765092324</v>
       </c>
       <c r="S19" s="12">
-        <v>63.69891901044474</v>
+        <v>50.09785874375961</v>
       </c>
       <c r="T19" s="10" t="s">
         <v>136</v>
@@ -6351,58 +6351,58 @@
         <v>16</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E20" s="11">
-        <v>121.7600021362305</v>
+        <v>1394.829956054688</v>
       </c>
       <c r="F20" s="20">
-        <v>0.6207711653919917</v>
+        <v>0.5545940163886861</v>
       </c>
       <c r="G20" s="13">
-        <v>0.3844623079993796</v>
+        <v>-0.3715766681671279</v>
       </c>
       <c r="H20" s="13">
-        <v>-0.1225159176090149</v>
+        <v>2.057050157474414</v>
       </c>
       <c r="I20" s="13">
-        <v>0.4303409832118458</v>
+        <v>4.09736352358056</v>
       </c>
       <c r="J20" s="13">
-        <v>0.0846708712803828</v>
+        <v>0.3296391575336684</v>
       </c>
       <c r="K20" s="13">
-        <v>4.037113416620117</v>
+        <v>0.1167279835627633</v>
       </c>
       <c r="L20" s="13">
-        <v>-0.007504507458442592</v>
+        <v>-2.899447602758569</v>
       </c>
       <c r="M20" s="13">
-        <v>0.234147468966735</v>
+        <v>-0.7039851252163897</v>
       </c>
       <c r="N20" s="13">
-        <v>14.45067</v>
+        <v>21.445498</v>
       </c>
       <c r="O20" s="13">
-        <v>6.500466</v>
+        <v>14.977796</v>
       </c>
       <c r="P20" s="15">
-        <v>0.46032003</v>
+        <v>0.9164</v>
       </c>
       <c r="Q20" s="15">
-        <v>0.07000000000000001</v>
+        <v>3.716</v>
       </c>
       <c r="R20" s="15">
-        <v>0.2016184736603308</v>
+        <v>0.5169934859189056</v>
       </c>
       <c r="S20" s="12">
-        <v>57.94718888596617</v>
+        <v>33.94073657914728</v>
       </c>
       <c r="T20" s="10" t="s">
         <v>136</v>
@@ -6413,58 +6413,58 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E21" s="11">
-        <v>254.0800018310547</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="F21" s="20">
-        <v>0.5950055868451747</v>
+        <v>0.5524416913165794</v>
       </c>
       <c r="G21" s="13">
-        <v>-0.02977335660029285</v>
+        <v>0.2210528163067884</v>
       </c>
       <c r="H21" s="13">
-        <v>0.160055113268548</v>
+        <v>-0.5344576345348465</v>
       </c>
       <c r="I21" s="13">
-        <v>0.9707254877878508</v>
+        <v>2.11370107259597</v>
       </c>
       <c r="J21" s="13">
-        <v>0.04440619398056514</v>
+        <v>1.781844120984375</v>
       </c>
       <c r="K21" s="13">
-        <v>4.037113416620117</v>
+        <v>0.3679132074995579</v>
       </c>
       <c r="L21" s="13">
-        <v>-0.5380224524188785</v>
+        <v>-2.177683288601284</v>
       </c>
       <c r="M21" s="13">
-        <v>0.1523662886002977</v>
+        <v>-0.7655815653980802</v>
       </c>
       <c r="N21" s="13">
-        <v>21.112629</v>
+        <v>37.86598</v>
       </c>
       <c r="O21" s="13">
-        <v>5.1299944</v>
+        <v>3.6796231</v>
       </c>
       <c r="P21" s="15">
-        <v>0.30558002</v>
+        <v>0.10936</v>
       </c>
       <c r="Q21" s="15">
-        <v>0.196</v>
+        <v>0.337</v>
       </c>
       <c r="R21" s="15">
-        <v>0.02245473573865064</v>
+        <v>1.27695109500519</v>
       </c>
       <c r="S21" s="12">
-        <v>49.33534011995932</v>
+        <v>41.75421824835702</v>
       </c>
       <c r="T21" s="10" t="s">
         <v>136</v>
@@ -6475,58 +6475,58 @@
         <v>18</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E22" s="11">
-        <v>1403.339965820312</v>
+        <v>239.6000061035156</v>
       </c>
       <c r="F22" s="20">
-        <v>0.558057235297111</v>
+        <v>0.5338367459240645</v>
       </c>
       <c r="G22" s="13">
-        <v>-0.3715766681671279</v>
+        <v>1.256899045882137</v>
       </c>
       <c r="H22" s="13">
-        <v>2.057050157474414</v>
+        <v>0.1687273867194284</v>
       </c>
       <c r="I22" s="13">
-        <v>4.09736352358056</v>
+        <v>-0.06592248185956601</v>
       </c>
       <c r="J22" s="13">
-        <v>0.3978093361686088</v>
+        <v>-0.03994471637095365</v>
       </c>
       <c r="K22" s="13">
-        <v>0.1167279835627633</v>
+        <v>1.954289824345583</v>
       </c>
       <c r="L22" s="13">
-        <v>-2.949498962581992</v>
+        <v>0.464064797365338</v>
       </c>
       <c r="M22" s="13">
-        <v>-0.8787945388745357</v>
+        <v>0.460194151550296</v>
       </c>
       <c r="N22" s="13">
-        <v>21.445498</v>
+        <v>4.590436</v>
       </c>
       <c r="O22" s="13">
-        <v>14.977796</v>
+        <v>1.838514</v>
       </c>
       <c r="P22" s="15">
-        <v>0.9164</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q22" s="15">
-        <v>3.716</v>
+        <v>0.118</v>
       </c>
       <c r="R22" s="15">
-        <v>0.5737451351614038</v>
+        <v>0.130895719724081</v>
       </c>
       <c r="S22" s="12">
-        <v>34.34738914248405</v>
+        <v>54.6251812956069</v>
       </c>
       <c r="T22" s="10" t="s">
         <v>136</v>
@@ -6537,58 +6537,58 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E23" s="11">
-        <v>222.0399932861328</v>
+        <v>473.3900146484375</v>
       </c>
       <c r="F23" s="20">
-        <v>0.5481076026540469</v>
+        <v>0.5201919778096951</v>
       </c>
       <c r="G23" s="13">
-        <v>0.4630268796884387</v>
+        <v>-0.1075886523285822</v>
       </c>
       <c r="H23" s="13">
-        <v>-0.3282907644621123</v>
+        <v>-0.8447423148789104</v>
       </c>
       <c r="I23" s="13">
-        <v>2.233294390227442</v>
+        <v>2.119917693224531</v>
       </c>
       <c r="J23" s="13">
-        <v>1.057651638229864</v>
+        <v>1.660670325400416</v>
       </c>
       <c r="K23" s="13">
-        <v>-0.144633187612409</v>
+        <v>1.69239307699997</v>
       </c>
       <c r="L23" s="13">
-        <v>0.7341297764532626</v>
+        <v>-2.899447602758569</v>
       </c>
       <c r="M23" s="13">
-        <v>-0.625343099266802</v>
+        <v>-0.8074559300949324</v>
       </c>
       <c r="N23" s="13">
-        <v>20.40231</v>
+        <v>33.41277</v>
       </c>
       <c r="O23" s="13">
-        <v>2.1898758</v>
+        <v>-262.80716</v>
       </c>
       <c r="P23" s="15">
-        <v>0.12231</v>
+        <v>0</v>
       </c>
       <c r="Q23" s="15">
-        <v>0.535</v>
+        <v>0.577</v>
       </c>
       <c r="R23" s="15">
-        <v>0.2223742950496221</v>
+        <v>1.463304262709574</v>
       </c>
       <c r="S23" s="12">
-        <v>71.31825715055166</v>
+        <v>36.27264636605871</v>
       </c>
       <c r="T23" s="10" t="s">
         <v>136</v>
@@ -6599,58 +6599,58 @@
         <v>20</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>12</v>
+        <v>143</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>66</v>
+        <v>144</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E24" s="11">
-        <v>236.1699981689453</v>
+        <v>219.3200073242188</v>
       </c>
       <c r="F24" s="20">
-        <v>0.54688789690373</v>
+        <v>0.5076858595158665</v>
       </c>
       <c r="G24" s="13">
-        <v>1.256899045882137</v>
+        <v>0.4630268796884387</v>
       </c>
       <c r="H24" s="13">
-        <v>0.1687273867194284</v>
+        <v>-0.3282907644621123</v>
       </c>
       <c r="I24" s="13">
-        <v>-0.06592248185956601</v>
+        <v>2.233294390227442</v>
       </c>
       <c r="J24" s="13">
-        <v>-0.009314915661564302</v>
+        <v>0.8301828045433609</v>
       </c>
       <c r="K24" s="13">
-        <v>1.954289824345583</v>
+        <v>-0.144633187612409</v>
       </c>
       <c r="L24" s="13">
-        <v>0.4602144262118926</v>
+        <v>0.741641987698424</v>
       </c>
       <c r="M24" s="13">
-        <v>0.5113595645009885</v>
+        <v>-0.2832409206035438</v>
       </c>
       <c r="N24" s="13">
-        <v>4.590436</v>
+        <v>20.40231</v>
       </c>
       <c r="O24" s="13">
-        <v>1.838514</v>
+        <v>2.1898758</v>
       </c>
       <c r="P24" s="15">
-        <v>0.46113998</v>
+        <v>0.12231</v>
       </c>
       <c r="Q24" s="15">
-        <v>0.118</v>
+        <v>0.535</v>
       </c>
       <c r="R24" s="15">
-        <v>0.09243564797535408</v>
+        <v>0.1866084403886643</v>
       </c>
       <c r="S24" s="12">
-        <v>50.0664847517501</v>
+        <v>65.50358996609432</v>
       </c>
       <c r="T24" s="10" t="s">
         <v>136</v>
@@ -6670,49 +6670,49 @@
         <v>41</v>
       </c>
       <c r="E25" s="11">
-        <v>184.0500030517578</v>
+        <v>377.510009765625</v>
       </c>
       <c r="F25" s="20">
-        <v>0.5300148814832472</v>
+        <v>0.5059029634097588</v>
       </c>
       <c r="G25" s="13">
-        <v>-2.114609254291167</v>
+        <v>0.05829011904393756</v>
       </c>
       <c r="H25" s="13">
-        <v>1.770921230679228</v>
+        <v>-0.2386394236856432</v>
       </c>
       <c r="I25" s="13">
-        <v>0.220221171989416</v>
+        <v>0.4382083912057649</v>
       </c>
       <c r="J25" s="13">
-        <v>2.050910296744923</v>
+        <v>1.375196713067072</v>
       </c>
       <c r="K25" s="13">
-        <v>0.4814553556330344</v>
+        <v>1.797366006406391</v>
       </c>
       <c r="L25" s="13">
-        <v>-0.6502105175938252</v>
+        <v>-1.794738392649662</v>
       </c>
       <c r="M25" s="13">
-        <v>-0.3595008436971591</v>
+        <v>-0.384830255986655</v>
       </c>
       <c r="N25" s="13">
-        <v>68.81625</v>
+        <v>35.48854</v>
       </c>
       <c r="O25" s="13">
-        <v>92.12393</v>
+        <v>5.341519</v>
       </c>
       <c r="P25" s="15">
-        <v>1.17442</v>
+        <v>0.15286</v>
       </c>
       <c r="Q25" s="15">
-        <v>0.256</v>
+        <v>0.204</v>
       </c>
       <c r="R25" s="15">
-        <v>1.311024666779198</v>
+        <v>0.6199365801650534</v>
       </c>
       <c r="S25" s="12">
-        <v>56.14718236618351</v>
+        <v>56.46539666828789</v>
       </c>
       <c r="T25" s="10" t="s">
         <v>136</v>
@@ -6723,58 +6723,58 @@
         <v>22</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>147</v>
+        <v>16</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E26" s="11">
-        <v>376.8800048828125</v>
+        <v>267.9299926757812</v>
       </c>
       <c r="F26" s="20">
-        <v>0.5230637675122519</v>
+        <v>0.496652601495944</v>
       </c>
       <c r="G26" s="13">
-        <v>0.05829011904393756</v>
+        <v>-0.7248874185708422</v>
       </c>
       <c r="H26" s="13">
-        <v>-0.2386394236856432</v>
+        <v>0.4430731040983454</v>
       </c>
       <c r="I26" s="13">
-        <v>0.4382083912057649</v>
+        <v>-0.4530813424943169</v>
       </c>
       <c r="J26" s="13">
-        <v>1.444707029718736</v>
+        <v>2.560089586553761</v>
       </c>
       <c r="K26" s="13">
-        <v>1.797366006406391</v>
+        <v>-0.2528195740414762</v>
       </c>
       <c r="L26" s="13">
-        <v>-1.796953766701602</v>
+        <v>-1.162892342933695</v>
       </c>
       <c r="M26" s="13">
-        <v>-0.4293223616102758</v>
+        <v>-0.8295776509092181</v>
       </c>
       <c r="N26" s="13">
-        <v>35.48854</v>
+        <v>51.89739</v>
       </c>
       <c r="O26" s="13">
-        <v>5.341519</v>
+        <v>14.800214</v>
       </c>
       <c r="P26" s="15">
-        <v>0.15286</v>
+        <v>0.32339</v>
       </c>
       <c r="Q26" s="15">
-        <v>0.204</v>
+        <v>0.094</v>
       </c>
       <c r="R26" s="15">
-        <v>0.6411775208348187</v>
+        <v>1.018761228235934</v>
       </c>
       <c r="S26" s="12">
-        <v>55.99241757454548</v>
+        <v>56.44961058354429</v>
       </c>
       <c r="T26" s="10" t="s">
         <v>136</v>
@@ -6785,58 +6785,58 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E27" s="11">
-        <v>142.3399963378906</v>
+        <v>1251.609985351562</v>
       </c>
       <c r="F27" s="20">
-        <v>0.4948522192547213</v>
+        <v>0.4927495854084328</v>
       </c>
       <c r="G27" s="13">
-        <v>0.4503326028677878</v>
+        <v>-1.067825127575939</v>
       </c>
       <c r="H27" s="13">
-        <v>-0.1381780449371671</v>
+        <v>1.801901173699206</v>
       </c>
       <c r="I27" s="13">
-        <v>0.7716117421870532</v>
+        <v>0.7243252315067988</v>
       </c>
       <c r="J27" s="13">
-        <v>1.225168296832862</v>
+        <v>0.7783881650179584</v>
       </c>
       <c r="K27" s="13">
-        <v>-0.05144293395568774</v>
+        <v>0.842433694510219</v>
       </c>
       <c r="L27" s="13">
-        <v>0.2882442862019671</v>
+        <v>0.2949594044253321</v>
       </c>
       <c r="M27" s="13">
-        <v>-0.2491541304691666</v>
+        <v>-0.351058246032309</v>
       </c>
       <c r="N27" s="13">
-        <v>17.76159</v>
+        <v>39.5861</v>
       </c>
       <c r="O27" s="13">
-        <v>2.4652097</v>
+        <v>31.03179</v>
       </c>
       <c r="P27" s="15">
-        <v>0.1418</v>
+        <v>1.02286</v>
       </c>
       <c r="Q27" s="15">
-        <v>0.355</v>
+        <v>0.477</v>
       </c>
       <c r="R27" s="15">
-        <v>0.2138771476263022</v>
+        <v>0.3889104460517532</v>
       </c>
       <c r="S27" s="12">
-        <v>71.29538722149405</v>
+        <v>67.7888449000562</v>
       </c>
       <c r="T27" s="10" t="s">
         <v>136</v>
@@ -6847,58 +6847,58 @@
         <v>24</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E28" s="11">
-        <v>154.1900024414062</v>
+        <v>98.41000366210938</v>
       </c>
       <c r="F28" s="20">
-        <v>0.4912680759628336</v>
+        <v>0.4878736341307687</v>
       </c>
       <c r="G28" s="13">
-        <v>0.5258568789706033</v>
+        <v>0.09120761566025611</v>
       </c>
       <c r="H28" s="13">
-        <v>0.4660864804691944</v>
+        <v>1.652287474348924</v>
       </c>
       <c r="I28" s="13">
-        <v>1.396975994830035</v>
+        <v>0.0273109313630392</v>
       </c>
       <c r="J28" s="13">
-        <v>0.8399506512951906</v>
+        <v>0.6058644870675111</v>
       </c>
       <c r="K28" s="13">
-        <v>-0.5056115264895936</v>
+        <v>0.06745497588219804</v>
       </c>
       <c r="L28" s="13">
-        <v>0.1106169185921604</v>
+        <v>0.5850117507712022</v>
       </c>
       <c r="M28" s="13">
-        <v>-0.1950803241910638</v>
+        <v>-0.257443424907479</v>
       </c>
       <c r="N28" s="13">
-        <v>11.529961</v>
+        <v>16.694096</v>
       </c>
       <c r="O28" s="13">
-        <v>2.443433</v>
+        <v>18.69391</v>
       </c>
       <c r="P28" s="15">
-        <v>0.22507</v>
+        <v>1.5956</v>
       </c>
       <c r="Q28" s="15">
-        <v>0.587</v>
+        <v>0.162</v>
       </c>
       <c r="R28" s="15">
-        <v>0.1824185236671019</v>
+        <v>0.07081353146505687</v>
       </c>
       <c r="S28" s="12">
-        <v>67.66312279253869</v>
+        <v>70.78043972117658</v>
       </c>
       <c r="T28" s="10" t="s">
         <v>136</v>
@@ -6909,58 +6909,58 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>16</v>
+        <v>151</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>73</v>
+        <v>152</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E29" s="11">
-        <v>271.760009765625</v>
+        <v>181.9100036621094</v>
       </c>
       <c r="F29" s="20">
-        <v>0.4876514246202027</v>
+        <v>0.480067059255698</v>
       </c>
       <c r="G29" s="13">
-        <v>-0.7248874185708422</v>
+        <v>-2.114609254291167</v>
       </c>
       <c r="H29" s="13">
-        <v>0.4430731040983454</v>
+        <v>1.770921230679228</v>
       </c>
       <c r="I29" s="13">
-        <v>-0.4530813424943169</v>
+        <v>0.220221171989416</v>
       </c>
       <c r="J29" s="13">
-        <v>2.592394613188554</v>
+        <v>1.869272379047665</v>
       </c>
       <c r="K29" s="13">
-        <v>-0.2528195740414762</v>
+        <v>0.4814553556330344</v>
       </c>
       <c r="L29" s="13">
-        <v>-1.163536009350817</v>
+        <v>-0.6318221844066476</v>
       </c>
       <c r="M29" s="13">
-        <v>-1.062753461923618</v>
+        <v>-0.3164976800671864</v>
       </c>
       <c r="N29" s="13">
-        <v>51.89739</v>
+        <v>68.81625</v>
       </c>
       <c r="O29" s="13">
-        <v>14.800214</v>
+        <v>92.12393</v>
       </c>
       <c r="P29" s="15">
-        <v>0.32339</v>
+        <v>1.17442</v>
       </c>
       <c r="Q29" s="15">
-        <v>0.094</v>
+        <v>0.256</v>
       </c>
       <c r="R29" s="15">
-        <v>1.05474082150804</v>
+        <v>1.207645634629969</v>
       </c>
       <c r="S29" s="12">
-        <v>58.88132724219482</v>
+        <v>53.42823458500122</v>
       </c>
       <c r="T29" s="10" t="s">
         <v>136</v>
@@ -6977,52 +6977,52 @@
         <v>154</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="E30" s="11">
-        <v>95.45999908447266</v>
+        <v>273.3999938964844</v>
       </c>
       <c r="F30" s="20">
-        <v>0.4627199685805627</v>
+        <v>0.4696258573732587</v>
       </c>
       <c r="G30" s="13">
-        <v>0.09120761566025611</v>
+        <v>-0.8805891848256409</v>
       </c>
       <c r="H30" s="13">
-        <v>1.652287474348924</v>
+        <v>0.03652855326022123</v>
       </c>
       <c r="I30" s="13">
-        <v>0.0273109313630392</v>
+        <v>2.246420289880714</v>
       </c>
       <c r="J30" s="13">
-        <v>0.4720630108032512</v>
+        <v>2.088338220942724</v>
       </c>
       <c r="K30" s="13">
-        <v>0.06745497588219804</v>
+        <v>-0.02573527777452323</v>
       </c>
       <c r="L30" s="13">
-        <v>0.6161377183359579</v>
+        <v>-2.529434428893377</v>
       </c>
       <c r="M30" s="13">
-        <v>-0.09345318396764679</v>
+        <v>-0.9250231760513088</v>
       </c>
       <c r="N30" s="13">
-        <v>16.694096</v>
+        <v>40.037346</v>
       </c>
       <c r="O30" s="13">
-        <v>18.69391</v>
+        <v>4.951591</v>
       </c>
       <c r="P30" s="15">
-        <v>1.5956</v>
+        <v>0.13497</v>
       </c>
       <c r="Q30" s="15">
-        <v>0.162</v>
+        <v>0.22</v>
       </c>
       <c r="R30" s="15">
-        <v>0.03230029322725958</v>
+        <v>0.9962031286086572</v>
       </c>
       <c r="S30" s="12">
-        <v>64.58742501238767</v>
+        <v>51.40677972950466</v>
       </c>
       <c r="T30" s="10" t="s">
         <v>136</v>
@@ -7039,52 +7039,52 @@
         <v>156</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E31" s="11">
-        <v>271.1199951171875</v>
+        <v>141.7299957275391</v>
       </c>
       <c r="F31" s="20">
-        <v>0.4471372258957333</v>
+        <v>0.4479174332382327</v>
       </c>
       <c r="G31" s="13">
-        <v>-0.8805891848256409</v>
+        <v>0.4503326028677878</v>
       </c>
       <c r="H31" s="13">
-        <v>0.03652855326022123</v>
+        <v>-0.1381780449371671</v>
       </c>
       <c r="I31" s="13">
-        <v>2.246420289880714</v>
+        <v>0.7716117421870532</v>
       </c>
       <c r="J31" s="13">
-        <v>2.096390508368464</v>
+        <v>1.037167410803707</v>
       </c>
       <c r="K31" s="13">
-        <v>-0.02573527777452323</v>
+        <v>-0.05144293395568774</v>
       </c>
       <c r="L31" s="13">
-        <v>-2.630324415505271</v>
+        <v>0.3030891679050353</v>
       </c>
       <c r="M31" s="13">
-        <v>-1.160659657407979</v>
+        <v>-0.1419692943432435</v>
       </c>
       <c r="N31" s="13">
-        <v>40.037346</v>
+        <v>17.76159</v>
       </c>
       <c r="O31" s="13">
-        <v>4.951591</v>
+        <v>2.4652097</v>
       </c>
       <c r="P31" s="15">
-        <v>0.13497</v>
+        <v>0.1418</v>
       </c>
       <c r="Q31" s="15">
-        <v>0.22</v>
+        <v>0.355</v>
       </c>
       <c r="R31" s="15">
-        <v>1.022227047855257</v>
+        <v>0.182328119510593</v>
       </c>
       <c r="S31" s="12">
-        <v>50.36741809631073</v>
+        <v>69.5620149784224</v>
       </c>
       <c r="T31" s="10" t="s">
         <v>136</v>
@@ -7101,52 +7101,52 @@
         <v>158</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E32" s="11">
-        <v>1208.739990234375</v>
+        <v>152.6199951171875</v>
       </c>
       <c r="F32" s="20">
-        <v>0.4457402747961864</v>
+        <v>0.4397657820486699</v>
       </c>
       <c r="G32" s="13">
-        <v>-1.067825127575939</v>
+        <v>0.5258568789706033</v>
       </c>
       <c r="H32" s="13">
-        <v>1.801901173699206</v>
+        <v>0.4660864804691944</v>
       </c>
       <c r="I32" s="13">
-        <v>0.7243252315067988</v>
+        <v>1.396975994830035</v>
       </c>
       <c r="J32" s="13">
-        <v>0.6080065705360135</v>
+        <v>0.6164882743621267</v>
       </c>
       <c r="K32" s="13">
-        <v>0.842433694510219</v>
+        <v>-0.5056115264895936</v>
       </c>
       <c r="L32" s="13">
-        <v>0.3305573712931109</v>
+        <v>0.1189063662009488</v>
       </c>
       <c r="M32" s="13">
-        <v>-0.3264421245289307</v>
+        <v>-0.007092170325712022</v>
       </c>
       <c r="N32" s="13">
-        <v>39.5861</v>
+        <v>11.529961</v>
       </c>
       <c r="O32" s="13">
-        <v>31.03179</v>
+        <v>2.443433</v>
       </c>
       <c r="P32" s="15">
-        <v>1.02286</v>
+        <v>0.22507</v>
       </c>
       <c r="Q32" s="15">
-        <v>0.477</v>
+        <v>0.587</v>
       </c>
       <c r="R32" s="15">
-        <v>0.339796252696557</v>
+        <v>0.1468088043547553</v>
       </c>
       <c r="S32" s="12">
-        <v>60.43546764048855</v>
+        <v>63.48273275206071</v>
       </c>
       <c r="T32" s="10" t="s">
         <v>136</v>
@@ -7163,52 +7163,52 @@
         <v>160</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E33" s="11">
-        <v>35.77999877929688</v>
+        <v>313.0299987792969</v>
       </c>
       <c r="F33" s="20">
-        <v>0.4384088602597463</v>
+        <v>0.4347748491125741</v>
       </c>
       <c r="G33" s="13">
-        <v>-0.01436423851863369</v>
+        <v>-0.6750434006171774</v>
       </c>
       <c r="H33" s="13">
-        <v>-0.8111350979836002</v>
+        <v>0.6516504181860266</v>
       </c>
       <c r="I33" s="13">
-        <v>3.797605429884786</v>
+        <v>-0.01179628325654914</v>
       </c>
       <c r="J33" s="13">
-        <v>0.08533625270185578</v>
+        <v>1.978765202718073</v>
       </c>
       <c r="K33" s="13">
-        <v>3.535310679487199</v>
+        <v>-0.3090550719377735</v>
       </c>
       <c r="L33" s="13">
-        <v>-2.949498962581992</v>
+        <v>-0.8454720719080344</v>
       </c>
       <c r="M33" s="13">
-        <v>-1.023159046401292</v>
+        <v>-0.6577050653606283</v>
       </c>
       <c r="N33" s="13">
-        <v>13.120689</v>
+        <v>48.545902</v>
       </c>
       <c r="O33" s="13">
-        <v>2.6814659</v>
+        <v>6.605916</v>
       </c>
       <c r="P33" s="15">
-        <v>0.21465999</v>
+        <v>0.14425</v>
       </c>
       <c r="Q33" s="15">
-        <v>0.9320000000000001</v>
+        <v>0.176</v>
       </c>
       <c r="R33" s="15">
-        <v>0.3111028794044097</v>
+        <v>0.8667183148779243</v>
       </c>
       <c r="S33" s="12">
-        <v>37.68367454999314</v>
+        <v>73.97198121602567</v>
       </c>
       <c r="T33" s="10" t="s">
         <v>136</v>
@@ -7219,58 +7219,58 @@
         <v>30</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E34" s="11">
-        <v>221.3000030517578</v>
+        <v>113.2699966430664</v>
       </c>
       <c r="F34" s="20">
-        <v>0.4243984586823153</v>
+        <v>0.4136609735249417</v>
       </c>
       <c r="G34" s="13">
-        <v>-1.1019019214601</v>
+        <v>0.3787913962730532</v>
       </c>
       <c r="H34" s="13">
-        <v>2.369306381861027</v>
+        <v>0.5071719458183616</v>
       </c>
       <c r="I34" s="13">
-        <v>2.390890545007346</v>
+        <v>0.5122250580763105</v>
       </c>
       <c r="J34" s="13">
-        <v>0.258180308540127</v>
+        <v>-0.04434842526500816</v>
       </c>
       <c r="K34" s="13">
-        <v>-0.2881676012905774</v>
+        <v>1.735774746805685</v>
       </c>
       <c r="L34" s="13">
-        <v>-0.1774039267954655</v>
+        <v>0.1490821355158805</v>
       </c>
       <c r="M34" s="13">
-        <v>-0.3458376981600805</v>
+        <v>0.1146891861136332</v>
       </c>
       <c r="N34" s="13">
-        <v>28.986094</v>
+        <v>14.368154</v>
       </c>
       <c r="O34" s="13">
-        <v>24.178003</v>
+        <v>3.572922</v>
       </c>
       <c r="P34" s="15">
-        <v>1.17211</v>
+        <v>0.30667</v>
       </c>
       <c r="Q34" s="15">
-        <v>1.059</v>
+        <v>0.377</v>
       </c>
       <c r="R34" s="15">
-        <v>0.1153307952322089</v>
+        <v>0.1883130193633105</v>
       </c>
       <c r="S34" s="12">
-        <v>43.97935058533494</v>
+        <v>39.7344302358994</v>
       </c>
       <c r="T34" s="10" t="s">
         <v>136</v>
@@ -7281,58 +7281,58 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>161</v>
+        <v>19</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>162</v>
+        <v>78</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>163</v>
+        <v>59</v>
       </c>
       <c r="E35" s="11">
-        <v>30.95</v>
+        <v>198.8600006103516</v>
       </c>
       <c r="F35" s="20">
-        <v>0.4215045175391142</v>
+        <v>0.4134649900637266</v>
       </c>
       <c r="G35" s="13">
-        <v>-0.01541387474592746</v>
+        <v>0.573799013559786</v>
       </c>
       <c r="H35" s="13">
-        <v>-1.00154153379357</v>
+        <v>-0.6557710512148275</v>
       </c>
       <c r="I35" s="13">
-        <v>-1.185161562431872</v>
+        <v>4.09736352358056</v>
       </c>
       <c r="J35" s="13">
-        <v>0.910656118902156</v>
+        <v>-0.4909207889676242</v>
       </c>
       <c r="K35" s="13">
-        <v>4.037113416620117</v>
+        <v>0.6560531871967765</v>
       </c>
       <c r="L35" s="13">
-        <v>0.4629239467103094</v>
+        <v>0.7017077289960002</v>
       </c>
       <c r="M35" s="13">
-        <v>-1.029800822801748</v>
+        <v>0.3976946743274433</v>
       </c>
       <c r="N35" s="13">
-        <v>497.26776</v>
+        <v>12.797688</v>
       </c>
       <c r="O35" s="13">
-        <v>2.3630948</v>
+        <v>1.1870677</v>
       </c>
       <c r="P35" s="15">
-        <v>-0.08785999999999999</v>
+        <v>0.09031</v>
       </c>
       <c r="Q35" s="15">
-        <v>-0.112</v>
+        <v>11.11</v>
       </c>
       <c r="R35" s="15">
-        <v>0.1308001461454147</v>
+        <v>-0.001450493509518536</v>
       </c>
       <c r="S35" s="12">
-        <v>75.22299401348903</v>
+        <v>46.89763529919124</v>
       </c>
       <c r="T35" s="10" t="s">
         <v>136</v>
@@ -7343,58 +7343,58 @@
         <v>32</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>78</v>
+        <v>162</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>59</v>
+        <v>163</v>
       </c>
       <c r="E36" s="11">
-        <v>194.3500061035156</v>
+        <v>30.95</v>
       </c>
       <c r="F36" s="20">
-        <v>0.4137428543891978</v>
+        <v>0.4053560321756641</v>
       </c>
       <c r="G36" s="13">
-        <v>0.573799013559786</v>
+        <v>-0.01541387474592746</v>
       </c>
       <c r="H36" s="13">
-        <v>-0.6557710512148275</v>
+        <v>-1.00154153379357</v>
       </c>
       <c r="I36" s="13">
-        <v>4.09736352358056</v>
+        <v>-1.185161562431872</v>
       </c>
       <c r="J36" s="13">
-        <v>-0.5431764848141137</v>
+        <v>0.8379074631625579</v>
       </c>
       <c r="K36" s="13">
-        <v>0.6560531871967765</v>
+        <v>4.037113416620117</v>
       </c>
       <c r="L36" s="13">
-        <v>0.6857711298223538</v>
+        <v>0.4788600725446244</v>
       </c>
       <c r="M36" s="13">
-        <v>0.6090792872004047</v>
+        <v>-0.9708015251971169</v>
       </c>
       <c r="N36" s="13">
-        <v>12.797688</v>
+        <v>497.26776</v>
       </c>
       <c r="O36" s="13">
-        <v>1.1870677</v>
+        <v>2.3630948</v>
       </c>
       <c r="P36" s="15">
-        <v>0.09031</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q36" s="15">
-        <v>11.11</v>
+        <v>-0.112</v>
       </c>
       <c r="R36" s="15">
-        <v>-0.03501068146755337</v>
+        <v>0.1308001461454147</v>
       </c>
       <c r="S36" s="12">
-        <v>38.08737904424933</v>
+        <v>75.22299401348897</v>
       </c>
       <c r="T36" s="10" t="s">
         <v>136</v>
@@ -7411,52 +7411,52 @@
         <v>165</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E37" s="11">
-        <v>177.0099945068359</v>
+        <v>35.09000015258789</v>
       </c>
       <c r="F37" s="20">
-        <v>0.404486204762235</v>
+        <v>0.4033055385453155</v>
       </c>
       <c r="G37" s="13">
-        <v>0.3069913706549089</v>
+        <v>-0.01436423851863369</v>
       </c>
       <c r="H37" s="13">
-        <v>-0.5480761301982536</v>
+        <v>-0.8111350979836002</v>
       </c>
       <c r="I37" s="13">
-        <v>1.025934986624751</v>
+        <v>3.797605429884786</v>
       </c>
       <c r="J37" s="13">
-        <v>1.088646310071552</v>
+        <v>-0.09915539792454391</v>
       </c>
       <c r="K37" s="13">
-        <v>0.09209147972248062</v>
+        <v>3.535310679487199</v>
       </c>
       <c r="L37" s="13">
-        <v>0.706020135818737</v>
+        <v>-2.899447602758569</v>
       </c>
       <c r="M37" s="13">
-        <v>-0.5709954815461327</v>
+        <v>-0.8076453978502462</v>
       </c>
       <c r="N37" s="13">
-        <v>21.7426</v>
+        <v>13.120689</v>
       </c>
       <c r="O37" s="13">
-        <v>2.6781864</v>
+        <v>2.6814659</v>
       </c>
       <c r="P37" s="15">
-        <v>0.12584</v>
+        <v>0.21465999</v>
       </c>
       <c r="Q37" s="15">
-        <v>0.441</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="R37" s="15">
-        <v>0.203713807215314</v>
+        <v>0.2355634022506312</v>
       </c>
       <c r="S37" s="12">
-        <v>74.92349295561721</v>
+        <v>36.27691637935801</v>
       </c>
       <c r="T37" s="10" t="s">
         <v>136</v>
@@ -7473,52 +7473,52 @@
         <v>167</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E38" s="11">
-        <v>49.91999816894531</v>
+        <v>252.0299987792969</v>
       </c>
       <c r="F38" s="20">
-        <v>0.3955166201400885</v>
+        <v>0.3997901154851364</v>
       </c>
       <c r="G38" s="13">
-        <v>0.3190129943001489</v>
+        <v>-0.05761153498665986</v>
       </c>
       <c r="H38" s="13">
-        <v>-0.04431119898918571</v>
+        <v>0.2709726849052398</v>
       </c>
       <c r="I38" s="13">
-        <v>1.24285337166309</v>
+        <v>-0.2889821613467594</v>
       </c>
       <c r="J38" s="13">
-        <v>0.7969238953376877</v>
+        <v>0.7847816592703691</v>
       </c>
       <c r="K38" s="13">
-        <v>-0.01502375436570473</v>
+        <v>1.410144435177601</v>
       </c>
       <c r="L38" s="13">
-        <v>0.04804998572963944</v>
+        <v>0.4073815718801216</v>
       </c>
       <c r="M38" s="13">
-        <v>-0.240732267289722</v>
+        <v>-0.4173993247832176</v>
       </c>
       <c r="N38" s="13">
-        <v>10.65342</v>
+        <v>24.797949</v>
       </c>
       <c r="O38" s="13">
-        <v>1.3292934</v>
+        <v>15.225441</v>
       </c>
       <c r="P38" s="15">
-        <v>0.11522</v>
+        <v>0.54960996</v>
       </c>
       <c r="Q38" s="15">
-        <v>0.642</v>
+        <v>0.067</v>
       </c>
       <c r="R38" s="15">
-        <v>0.1187412046852947</v>
+        <v>0.3257391458316929</v>
       </c>
       <c r="S38" s="12">
-        <v>59.96046600045739</v>
+        <v>69.13773281921134</v>
       </c>
       <c r="T38" s="10" t="s">
         <v>136</v>
@@ -7529,58 +7529,58 @@
         <v>35</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>168</v>
+        <v>7</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>169</v>
+        <v>56</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E39" s="11">
-        <v>427.3999938964844</v>
+        <v>217.2299957275391</v>
       </c>
       <c r="F39" s="20">
-        <v>0.3879338692574937</v>
+        <v>0.3981980186169776</v>
       </c>
       <c r="G39" s="13">
-        <v>0.2970607495888827</v>
+        <v>-1.1019019214601</v>
       </c>
       <c r="H39" s="13">
-        <v>-1.054613391281616</v>
+        <v>2.369306381861027</v>
       </c>
       <c r="I39" s="13">
-        <v>0.1591049640981598</v>
+        <v>2.390890545007346</v>
       </c>
       <c r="J39" s="13">
-        <v>1.733020161420015</v>
+        <v>0.1021911740426099</v>
       </c>
       <c r="K39" s="13">
-        <v>-0.1473110684646137</v>
+        <v>-0.2881676012905774</v>
       </c>
       <c r="L39" s="13">
-        <v>-0.4257336278185164</v>
+        <v>-0.1612523269981049</v>
       </c>
       <c r="M39" s="13">
-        <v>0.1325734748199665</v>
+        <v>-0.1004976444591342</v>
       </c>
       <c r="N39" s="13">
-        <v>40.81947</v>
+        <v>28.986094</v>
       </c>
       <c r="O39" s="13">
-        <v>2.6991706</v>
+        <v>24.178003</v>
       </c>
       <c r="P39" s="15">
-        <v>0.06893000000000001</v>
+        <v>1.17211</v>
       </c>
       <c r="Q39" s="15">
-        <v>0.262</v>
+        <v>1.059</v>
       </c>
       <c r="R39" s="15">
-        <v>1.159642837344081</v>
+        <v>0.09768855525624476</v>
       </c>
       <c r="S39" s="12">
-        <v>62.00128646866262</v>
+        <v>40.20329096761976</v>
       </c>
       <c r="T39" s="10" t="s">
         <v>136</v>
@@ -7591,58 +7591,58 @@
         <v>36</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E40" s="11">
-        <v>111.5699996948242</v>
+        <v>207.3099975585938</v>
       </c>
       <c r="F40" s="20">
-        <v>0.3847476415627792</v>
+        <v>0.3928099797264687</v>
       </c>
       <c r="G40" s="13">
-        <v>0.3787913962730532</v>
+        <v>0.6669465997956974</v>
       </c>
       <c r="H40" s="13">
-        <v>0.5071719458183616</v>
+        <v>1.145193734796624</v>
       </c>
       <c r="I40" s="13">
-        <v>0.5122250580763105</v>
+        <v>-0.5230891033109225</v>
       </c>
       <c r="J40" s="13">
-        <v>-0.05830769128455526</v>
+        <v>0.8846245156923344</v>
       </c>
       <c r="K40" s="13">
-        <v>1.735774746805685</v>
+        <v>0.2956104244900327</v>
       </c>
       <c r="L40" s="13">
-        <v>0.1382406635047936</v>
+        <v>-2.425661994802192</v>
       </c>
       <c r="M40" s="13">
-        <v>-0.1862491118317821</v>
+        <v>-0.1685422678937147</v>
       </c>
       <c r="N40" s="13">
-        <v>14.368154</v>
+        <v>17.283</v>
       </c>
       <c r="O40" s="13">
-        <v>3.572922</v>
+        <v>-73.57581999999999</v>
       </c>
       <c r="P40" s="15">
-        <v>0.30667</v>
+        <v>1.13581</v>
       </c>
       <c r="Q40" s="15">
-        <v>0.377</v>
+        <v>-0.006</v>
       </c>
       <c r="R40" s="15">
-        <v>0.1490216421018755</v>
+        <v>0.3329261183418044</v>
       </c>
       <c r="S40" s="12">
-        <v>34.99391983401442</v>
+        <v>65.29073634725839</v>
       </c>
       <c r="T40" s="10" t="s">
         <v>136</v>
@@ -7662,49 +7662,49 @@
         <v>63</v>
       </c>
       <c r="E41" s="11">
-        <v>297.3500061035156</v>
+        <v>444.1499938964844</v>
       </c>
       <c r="F41" s="20">
-        <v>0.3838247184468957</v>
+        <v>0.388873549411091</v>
       </c>
       <c r="G41" s="13">
-        <v>-0.6750434006171774</v>
+        <v>-0.8827962651810826</v>
       </c>
       <c r="H41" s="13">
-        <v>0.6516504181860266</v>
+        <v>-0.4361522536484728</v>
       </c>
       <c r="I41" s="13">
-        <v>-0.01179628325654914</v>
+        <v>4.09736352358056</v>
       </c>
       <c r="J41" s="13">
-        <v>1.790528600503205</v>
+        <v>0.9526175124499677</v>
       </c>
       <c r="K41" s="13">
-        <v>-0.3090550719377735</v>
+        <v>-0.5425662822500176</v>
       </c>
       <c r="L41" s="13">
-        <v>-0.8280026110745325</v>
+        <v>0.5214141186666083</v>
       </c>
       <c r="M41" s="13">
-        <v>-0.6017965360009805</v>
+        <v>-0.5517157701949907</v>
       </c>
       <c r="N41" s="13">
-        <v>48.545902</v>
+        <v>109.815186</v>
       </c>
       <c r="O41" s="13">
-        <v>6.605916</v>
+        <v>2.8040156</v>
       </c>
       <c r="P41" s="15">
-        <v>0.14425</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q41" s="15">
-        <v>0.176</v>
+        <v>1.134</v>
       </c>
       <c r="R41" s="15">
-        <v>0.777346088938947</v>
+        <v>0.3921451291396472</v>
       </c>
       <c r="S41" s="12">
-        <v>66.93181933307791</v>
+        <v>61.6806580967722</v>
       </c>
       <c r="T41" s="10" t="s">
         <v>136</v>
@@ -7721,52 +7721,52 @@
         <v>173</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E42" s="11">
-        <v>603.239990234375</v>
+        <v>125.9300003051758</v>
       </c>
       <c r="F42" s="20">
-        <v>0.3672650752951226</v>
+        <v>0.3823116820759173</v>
       </c>
       <c r="G42" s="13">
-        <v>-1.341725686078395</v>
+        <v>0.6111168829955569</v>
       </c>
       <c r="H42" s="13">
-        <v>2.889093849209865</v>
+        <v>-0.7016168425490857</v>
       </c>
       <c r="I42" s="13">
-        <v>-0.1842355355782666</v>
+        <v>-0.5658676683771782</v>
       </c>
       <c r="J42" s="13">
-        <v>0.5675987956162279</v>
+        <v>0.6711639588424445</v>
       </c>
       <c r="K42" s="13">
-        <v>-0.3219089000283558</v>
+        <v>1.855208232814011</v>
       </c>
       <c r="L42" s="13">
-        <v>1.024002403499752</v>
+        <v>0.5727012409895013</v>
       </c>
       <c r="M42" s="13">
-        <v>-0.3518309802246099</v>
+        <v>-0.214751815843703</v>
       </c>
       <c r="N42" s="13">
-        <v>32.40594</v>
+        <v>55.995327</v>
       </c>
       <c r="O42" s="13">
-        <v>92.11069500000001</v>
+        <v>2.2259169</v>
       </c>
       <c r="P42" s="15">
-        <v>2.41202</v>
+        <v>0.03931</v>
       </c>
       <c r="Q42" s="15">
-        <v>0.141</v>
+        <v>0.05</v>
       </c>
       <c r="R42" s="15">
-        <v>0.1638726102948753</v>
+        <v>0.3681188521920127</v>
       </c>
       <c r="S42" s="12">
-        <v>70.36768024122347</v>
+        <v>64.04309025211974</v>
       </c>
       <c r="T42" s="10" t="s">
         <v>136</v>
@@ -7783,52 +7783,52 @@
         <v>175</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="E43" s="11">
-        <v>73.12999725341797</v>
+        <v>616.3200073242188</v>
       </c>
       <c r="F43" s="20">
-        <v>0.3670164460944886</v>
+        <v>0.382138905087756</v>
       </c>
       <c r="G43" s="13">
-        <v>0.4281951431088404</v>
+        <v>-1.341725686078395</v>
       </c>
       <c r="H43" s="13">
-        <v>1.839920832819933</v>
+        <v>2.889093849209865</v>
       </c>
       <c r="I43" s="13">
-        <v>-0.6395167842697658</v>
+        <v>-0.1842355355782666</v>
       </c>
       <c r="J43" s="13">
-        <v>0.5657338531163074</v>
+        <v>0.636766994484204</v>
       </c>
       <c r="K43" s="13">
-        <v>-0.6807449342237767</v>
+        <v>-0.3219089000283558</v>
       </c>
       <c r="L43" s="13">
-        <v>0.3739159694915301</v>
+        <v>1.02987148365065</v>
       </c>
       <c r="M43" s="13">
-        <v>-0.6370007060855774</v>
+        <v>-0.4296906636847767</v>
       </c>
       <c r="N43" s="13">
-        <v>15.090527</v>
+        <v>32.40594</v>
       </c>
       <c r="O43" s="13">
-        <v>-44.856068</v>
+        <v>92.11069500000001</v>
       </c>
       <c r="P43" s="15">
-        <v>0</v>
+        <v>2.41202</v>
       </c>
       <c r="Q43" s="15">
-        <v>0.012</v>
+        <v>0.141</v>
       </c>
       <c r="R43" s="15">
-        <v>0.1705850852388084</v>
+        <v>0.1923652299531582</v>
       </c>
       <c r="S43" s="12">
-        <v>72.05984684714561</v>
+        <v>74.93240263420518</v>
       </c>
       <c r="T43" s="10" t="s">
         <v>136</v>
@@ -7845,52 +7845,52 @@
         <v>177</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E44" s="11">
-        <v>197.5099945068359</v>
+        <v>434.0299987792969</v>
       </c>
       <c r="F44" s="20">
-        <v>0.3661560894885361</v>
+        <v>0.3759398953811121</v>
       </c>
       <c r="G44" s="13">
-        <v>0.578054316350588</v>
+        <v>-0.2056696277886048</v>
       </c>
       <c r="H44" s="13">
-        <v>-0.04848410617494222</v>
+        <v>1.24177108368937</v>
       </c>
       <c r="I44" s="13">
-        <v>1.554104829957849</v>
+        <v>-0.109869796093493</v>
       </c>
       <c r="J44" s="13">
-        <v>0.3933033463599815</v>
+        <v>0.8001057291758285</v>
       </c>
       <c r="K44" s="13">
-        <v>-0.1724831484753372</v>
+        <v>0.02300215373560111</v>
       </c>
       <c r="L44" s="13">
-        <v>0.008771521503207765</v>
+        <v>-0.006444476167771388</v>
       </c>
       <c r="M44" s="13">
-        <v>0.2079246144561197</v>
+        <v>-0.2142659253605434</v>
       </c>
       <c r="N44" s="13">
-        <v>36.59619</v>
+        <v>25.768322</v>
       </c>
       <c r="O44" s="13">
-        <v>1.4223108</v>
+        <v>19.189177</v>
       </c>
       <c r="P44" s="15">
-        <v>0.034930002</v>
+        <v>0.91473</v>
       </c>
       <c r="Q44" s="15">
-        <v>0.525</v>
+        <v>0.095</v>
       </c>
       <c r="R44" s="15">
-        <v>0.07435304624468642</v>
+        <v>0.2589461930724164</v>
       </c>
       <c r="S44" s="12">
-        <v>58.19270011730175</v>
+        <v>63.69195932323474</v>
       </c>
       <c r="T44" s="10" t="s">
         <v>136</v>
@@ -8210,7 +8210,7 @@
         <v>238</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -8347,10 +8347,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BH21"/>
+  <dimension ref="A1:BI21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:60">
+    <row r="1" spans="1:61">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8531,8 +8531,11 @@
       <c r="BH1">
         <v>1403.339965820312</v>
       </c>
-    </row>
-    <row r="2" spans="1:60">
+      <c r="BI1">
+        <v>1394.829956054688</v>
+      </c>
+    </row>
+    <row r="2" spans="1:61">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -8713,8 +8716,11 @@
       <c r="BH2">
         <v>364.1000061035156</v>
       </c>
-    </row>
-    <row r="3" spans="1:60">
+      <c r="BI2">
+        <v>356.4500122070312</v>
+      </c>
+    </row>
+    <row r="3" spans="1:61">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -8895,8 +8901,11 @@
       <c r="BH3">
         <v>459.7799987792969</v>
       </c>
-    </row>
-    <row r="4" spans="1:60">
+      <c r="BI3">
+        <v>444.0599975585938</v>
+      </c>
+    </row>
+    <row r="4" spans="1:61">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -9077,8 +9086,11 @@
       <c r="BH4">
         <v>484.9200134277344</v>
       </c>
-    </row>
-    <row r="5" spans="1:60">
+      <c r="BI4">
+        <v>476.9200134277344</v>
+      </c>
+    </row>
+    <row r="5" spans="1:61">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -9259,8 +9271,11 @@
       <c r="BH5">
         <v>61.40999984741211</v>
       </c>
-    </row>
-    <row r="6" spans="1:60">
+      <c r="BI5">
+        <v>60.66999816894531</v>
+      </c>
+    </row>
+    <row r="6" spans="1:61">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -9441,8 +9456,11 @@
       <c r="BH6">
         <v>297.2900085449219</v>
       </c>
-    </row>
-    <row r="7" spans="1:60">
+      <c r="BI6">
+        <v>289.2000122070312</v>
+      </c>
+    </row>
+    <row r="7" spans="1:61">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -9623,8 +9641,11 @@
       <c r="BH7">
         <v>47.36999893188477</v>
       </c>
-    </row>
-    <row r="8" spans="1:60">
+      <c r="BI7">
+        <v>47.22999954223633</v>
+      </c>
+    </row>
+    <row r="8" spans="1:61">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -9805,8 +9826,11 @@
       <c r="BH8">
         <v>221.3000030517578</v>
       </c>
-    </row>
-    <row r="9" spans="1:60">
+      <c r="BI8">
+        <v>217.2299957275391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:61">
       <c r="A9" t="s">
         <v>8</v>
       </c>
@@ -9987,8 +10011,11 @@
       <c r="BH9">
         <v>377.8200073242188</v>
       </c>
-    </row>
-    <row r="10" spans="1:60">
+      <c r="BI9">
+        <v>383.8900146484375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:61">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -10169,8 +10196,11 @@
       <c r="BH10">
         <v>343.6499938964844</v>
       </c>
-    </row>
-    <row r="11" spans="1:60">
+      <c r="BI10">
+        <v>344.9100036621094</v>
+      </c>
+    </row>
+    <row r="11" spans="1:61">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -10351,8 +10381,11 @@
       <c r="BH11">
         <v>70.16000366210938</v>
       </c>
-    </row>
-    <row r="12" spans="1:60">
+      <c r="BI11">
+        <v>70.51000213623047</v>
+      </c>
+    </row>
+    <row r="12" spans="1:61">
       <c r="A12" t="s">
         <v>11</v>
       </c>
@@ -10533,8 +10566,11 @@
       <c r="BH12">
         <v>347.6400146484375</v>
       </c>
-    </row>
-    <row r="13" spans="1:60">
+      <c r="BI12">
+        <v>349.2200012207031</v>
+      </c>
+    </row>
+    <row r="13" spans="1:61">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -10715,8 +10751,11 @@
       <c r="BH13">
         <v>236.1699981689453</v>
       </c>
-    </row>
-    <row r="14" spans="1:60">
+      <c r="BI13">
+        <v>239.6000061035156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:61">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -10897,8 +10936,11 @@
       <c r="BH14">
         <v>155.3099975585938</v>
       </c>
-    </row>
-    <row r="15" spans="1:60">
+      <c r="BI14">
+        <v>156.6300048828125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:61">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -11079,8 +11121,11 @@
       <c r="BH15">
         <v>111.5699996948242</v>
       </c>
-    </row>
-    <row r="16" spans="1:60">
+      <c r="BI15">
+        <v>113.2699966430664</v>
+      </c>
+    </row>
+    <row r="16" spans="1:61">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -11261,8 +11306,11 @@
       <c r="BH16">
         <v>254.0800018310547</v>
       </c>
-    </row>
-    <row r="17" spans="1:60">
+      <c r="BI16">
+        <v>254.7599945068359</v>
+      </c>
+    </row>
+    <row r="17" spans="1:61">
       <c r="A17" t="s">
         <v>16</v>
       </c>
@@ -11443,8 +11491,11 @@
       <c r="BH17">
         <v>271.760009765625</v>
       </c>
-    </row>
-    <row r="18" spans="1:60">
+      <c r="BI17">
+        <v>267.9299926757812</v>
+      </c>
+    </row>
+    <row r="18" spans="1:61">
       <c r="A18" t="s">
         <v>17</v>
       </c>
@@ -11625,8 +11676,11 @@
       <c r="BH18">
         <v>121.7600021362305</v>
       </c>
-    </row>
-    <row r="19" spans="1:60">
+      <c r="BI18">
+        <v>124.4100036621094</v>
+      </c>
+    </row>
+    <row r="19" spans="1:61">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -11807,8 +11861,11 @@
       <c r="BH19">
         <v>232.8300018310547</v>
       </c>
-    </row>
-    <row r="20" spans="1:60">
+      <c r="BI19">
+        <v>235.3500061035156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -11989,8 +12046,11 @@
       <c r="BH20">
         <v>194.3500061035156</v>
       </c>
-    </row>
-    <row r="21" spans="1:60">
+      <c r="BI20">
+        <v>198.8600006103516</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -12170,6 +12230,9 @@
       </c>
       <c r="BH21">
         <v>63.11000061035156</v>
+      </c>
+      <c r="BI21">
+        <v>58.63000106811523</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="271">
   <si>
     <t>SNDK</t>
   </si>
@@ -388,6 +388,9 @@
     <t>2026-10-19</t>
   </si>
   <si>
+    <t>2026-10-21</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -454,22 +457,43 @@
     <t>Salesforce</t>
   </si>
   <si>
+    <t>HAS</t>
+  </si>
+  <si>
+    <t>Hasbro</t>
+  </si>
+  <si>
     <t>NTAP</t>
   </si>
   <si>
     <t>NetApp</t>
   </si>
   <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>Zebra Technologies</t>
+  </si>
+  <si>
     <t>CVX</t>
   </si>
   <si>
     <t>Chevron Corporation</t>
   </si>
   <si>
-    <t>ZBRA</t>
-  </si>
-  <si>
-    <t>Zebra Technologies</t>
+    <t>LLY</t>
+  </si>
+  <si>
+    <t>Lilly (Eli)</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Gartner</t>
+  </si>
+  <si>
+    <t>Dell Technologies</t>
   </si>
   <si>
     <t>EOG</t>
@@ -484,31 +508,67 @@
     <t>ConocoPhillips</t>
   </si>
   <si>
-    <t>Dell Technologies</t>
-  </si>
-  <si>
-    <t>LLY</t>
-  </si>
-  <si>
-    <t>Lilly (Eli)</t>
-  </si>
-  <si>
-    <t>HAS</t>
-  </si>
-  <si>
-    <t>Hasbro</t>
-  </si>
-  <si>
     <t>WSM</t>
   </si>
   <si>
     <t>Williams-Sonoma, Inc.</t>
   </si>
   <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Gartner</t>
+    <t>NWSA</t>
+  </si>
+  <si>
+    <t>News Corp (Class A)</t>
+  </si>
+  <si>
+    <t>SJM</t>
+  </si>
+  <si>
+    <t>J.M. Smucker Company (The)</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>Regeneron Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>BMY</t>
+  </si>
+  <si>
+    <t>Bristol Myers Squibb</t>
+  </si>
+  <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>Veeva Systems</t>
+  </si>
+  <si>
+    <t>WBD</t>
+  </si>
+  <si>
+    <t>nan</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>TWLO</t>
+  </si>
+  <si>
+    <t>Twilio</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
+  </si>
+  <si>
+    <t>EXPE</t>
+  </si>
+  <si>
+    <t>Expedia Group</t>
   </si>
   <si>
     <t>DVN</t>
@@ -517,57 +577,12 @@
     <t>Devon Energy</t>
   </si>
   <si>
-    <t>SJM</t>
-  </si>
-  <si>
-    <t>J.M. Smucker Company (The)</t>
-  </si>
-  <si>
-    <t>WBD</t>
-  </si>
-  <si>
-    <t>nan</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>NWSA</t>
-  </si>
-  <si>
-    <t>News Corp (Class A)</t>
-  </si>
-  <si>
-    <t>XOM</t>
-  </si>
-  <si>
-    <t>ExxonMobil</t>
-  </si>
-  <si>
     <t>MO</t>
   </si>
   <si>
     <t>Altria</t>
   </si>
   <si>
-    <t>FTNT</t>
-  </si>
-  <si>
-    <t>Fortinet</t>
-  </si>
-  <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>Veeva Systems</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>Mastercard</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -646,7 +661,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-10-21 00:42 UTC · данные на 2026-10-19 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-22 00:43 UTC · данные на 2026-10-21 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -730,7 +745,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-10-21 00:42 UTC</t>
+    <t>2026-10-22 00:43 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -745,7 +760,7 @@
     <t>Прошли фильтры</t>
   </si>
   <si>
-    <t>420</t>
+    <t>419</t>
   </si>
   <si>
     <t>Кандидат дня</t>
@@ -1277,9 +1292,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$34</c:f>
+              <c:f>Капитал!$A$5:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1369,16 +1384,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>2026-10-19</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2026-10-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$34</c:f>
+              <c:f>Капитал!$D$5:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1467,6 +1485,9 @@
                   <c:v>10320.820000000002</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>10374.140000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>10374.140000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1492,9 +1513,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$34</c:f>
+              <c:f>Капитал!$A$5:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1584,16 +1605,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>2026-10-19</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2026-10-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$34</c:f>
+              <c:f>Капитал!$F$5:$F$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1683,6 +1707,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>10064.36</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1822,9 +1849,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$34</c:f>
+              <c:f>Капитал!$A$5:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1914,16 +1941,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>2026-10-19</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2026-10-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$34</c:f>
+              <c:f>Капитал!$D$5:$D$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -2012,6 +2042,9 @@
                   <c:v>10320.820000000002</c:v>
                 </c:pt>
                 <c:pt idx="29">
+                  <c:v>10374.140000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>10374.140000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -2037,9 +2070,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$34</c:f>
+              <c:f>Капитал!$A$5:$A$35</c:f>
               <c:strCache>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -2129,16 +2162,19 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>2026-10-19</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2026-10-21</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$34</c:f>
+              <c:f>Капитал!$F$5:$F$35</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="30"/>
+                <c:ptCount val="31"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -2228,6 +2264,9 @@
                 </c:pt>
                 <c:pt idx="29">
                   <c:v>10064.36</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2722,12 +2761,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2735,13 +2774,13 @@
         <v>102</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2760,21 +2799,21 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>3.21462891367128</v>
+        <v>3.158439774689714</v>
       </c>
       <c r="D9" s="7">
         <v>2</v>
@@ -2788,7 +2827,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="9" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2817,7 +2856,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="10" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C16" s="11">
         <v>10000</v>
@@ -2825,7 +2864,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="10" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C17" s="12">
         <v>21</v>
@@ -2833,7 +2872,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="10" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C18" s="12">
         <v>0</v>
@@ -2841,23 +2880,23 @@
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="10" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C19" s="12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="10" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C21" s="13">
         <v>22</v>
@@ -2865,7 +2904,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="10" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="C22" s="14">
         <v>0.210302</v>
@@ -2873,7 +2912,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="10" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C23" s="14">
         <v>0</v>
@@ -2881,31 +2920,31 @@
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="10" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="10" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C25" s="15">
-        <v>0.1009294067007813</v>
+        <v>0.09930079145385329</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="10" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="C26" s="12">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="16" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C28" s="11">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2914,12 +2953,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="17" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="9" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -3114,7 +3153,7 @@
         <v>-0.11551777832687689</v>
       </c>
       <c r="L5" s="12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>43</v>
@@ -3167,7 +3206,7 @@
         <v>-0.23851334699505075</v>
       </c>
       <c r="L6" s="12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>43</v>
@@ -3220,7 +3259,7 @@
         <v>0.2031746616047501</v>
       </c>
       <c r="L7" s="12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>43</v>
@@ -3273,7 +3312,7 @@
         <v>0.24337509372837138</v>
       </c>
       <c r="L8" s="12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>43</v>
@@ -3326,7 +3365,7 @@
         <v>0.04272551403482912</v>
       </c>
       <c r="L9" s="12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>43</v>
@@ -3379,7 +3418,7 @@
         <v>0.15340792445550722</v>
       </c>
       <c r="L10" s="12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>43</v>
@@ -3432,7 +3471,7 @@
         <v>0.13862477289477573</v>
       </c>
       <c r="L11" s="12">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>43</v>
@@ -3485,7 +3524,7 @@
         <v>0.027180023803650654</v>
       </c>
       <c r="L12" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>43</v>
@@ -3538,7 +3577,7 @@
         <v>0.005893924930109997</v>
       </c>
       <c r="L13" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>43</v>
@@ -3591,7 +3630,7 @@
         <v>0.0025921578099839296</v>
       </c>
       <c r="L14" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>43</v>
@@ -3644,7 +3683,7 @@
         <v>0.019101186256372128</v>
       </c>
       <c r="L15" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>43</v>
@@ -3697,7 +3736,7 @@
         <v>0.009709630371900724</v>
       </c>
       <c r="L16" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M16" s="10" t="s">
         <v>43</v>
@@ -3750,7 +3789,7 @@
         <v>0.078916577376033</v>
       </c>
       <c r="L17" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>43</v>
@@ -3803,7 +3842,7 @@
         <v>-0.021625941570247907</v>
       </c>
       <c r="L18" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>43</v>
@@ -3856,7 +3895,7 @@
         <v>-0.08166955526859504</v>
       </c>
       <c r="L19" s="12">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M19" s="10" t="s">
         <v>43</v>
@@ -3909,7 +3948,7 @@
         <v>0.042561413568448565</v>
       </c>
       <c r="L20" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M20" s="10" t="s">
         <v>43</v>
@@ -3962,7 +4001,7 @@
         <v>-0.039130372238321116</v>
       </c>
       <c r="L21" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M21" s="10" t="s">
         <v>43</v>
@@ -4015,7 +4054,7 @@
         <v>0.08687390276757277</v>
       </c>
       <c r="L22" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M22" s="10" t="s">
         <v>43</v>
@@ -4068,7 +4107,7 @@
         <v>0.031349345455369874</v>
       </c>
       <c r="L23" s="12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M23" s="10" t="s">
         <v>43</v>
@@ -4121,7 +4160,7 @@
         <v>0.005639950174490104</v>
       </c>
       <c r="L24" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M24" s="10" t="s">
         <v>43</v>
@@ -4174,7 +4213,7 @@
         <v>-0.2334648801857212</v>
       </c>
       <c r="L25" s="12">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>43</v>
@@ -4765,7 +4804,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5414,6 +5453,25 @@
       <c r="F34" s="11">
         <v>10064.36</v>
       </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="B35" s="11">
+        <v>550.02</v>
+      </c>
+      <c r="C35" s="11">
+        <v>9824.120000000001</v>
+      </c>
+      <c r="D35" s="11">
+        <f>B35+C35</f>
+        <v>10374.140000000001</v>
+      </c>
+      <c r="E35" s="12">
+        <v>21</v>
+      </c>
+      <c r="F35" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5442,12 +5500,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5464,52 +5522,52 @@
         <v>25</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S4" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -5517,61 +5575,61 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="11">
-        <v>433.3099975585938</v>
+        <v>475.0400085449219</v>
       </c>
       <c r="F5" s="20">
-        <v>1.068864621436314</v>
+        <v>1.02162863331401</v>
       </c>
       <c r="G5" s="13">
-        <v>0.5441695646068145</v>
+        <v>0.5236085664662042</v>
       </c>
       <c r="H5" s="13">
-        <v>-0.679434895038627</v>
+        <v>-0.5744716818195363</v>
       </c>
       <c r="I5" s="13">
-        <v>2.801316555515531</v>
+        <v>2.413793147558647</v>
       </c>
       <c r="J5" s="13">
-        <v>2.483924394501515</v>
+        <v>2.424088622739075</v>
       </c>
       <c r="K5" s="13">
-        <v>0.7215948903827497</v>
+        <v>0.8962225452363762</v>
       </c>
       <c r="L5" s="13">
-        <v>-0.05365591510053497</v>
+        <v>-0.1466178998668669</v>
       </c>
       <c r="M5" s="13">
-        <v>-0.3632165353579779</v>
+        <v>-0.600762157159024</v>
       </c>
       <c r="N5" s="13">
-        <v>18.537308</v>
+        <v>16.55367</v>
       </c>
       <c r="O5" s="13">
-        <v>5.121617</v>
+        <v>7.0919743</v>
       </c>
       <c r="P5" s="15">
-        <v>0.27637</v>
+        <v>0.42099</v>
       </c>
       <c r="Q5" s="15">
-        <v>0.517</v>
+        <v>0.537</v>
       </c>
       <c r="R5" s="15">
-        <v>0.9314621920481505</v>
+        <v>1.169996231181436</v>
       </c>
       <c r="S5" s="12">
-        <v>59.68020039071128</v>
+        <v>71.9518870688083</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -5579,61 +5637,61 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>48</v>
       </c>
       <c r="E6" s="11">
-        <v>473.6900024414062</v>
+        <v>433.4200134277344</v>
       </c>
       <c r="F6" s="20">
-        <v>1.048932768185988</v>
+        <v>1.00742671778025</v>
       </c>
       <c r="G6" s="13">
-        <v>0.5230087163645327</v>
+        <v>0.5447519645801073</v>
       </c>
       <c r="H6" s="13">
-        <v>-0.5715412265413334</v>
+        <v>-0.6819902707968063</v>
       </c>
       <c r="I6" s="13">
-        <v>2.372422178988358</v>
+        <v>2.840883602905277</v>
       </c>
       <c r="J6" s="13">
-        <v>2.525977672841486</v>
+        <v>2.279666813644417</v>
       </c>
       <c r="K6" s="13">
-        <v>0.9013812132472169</v>
+        <v>0.7123554336706056</v>
       </c>
       <c r="L6" s="13">
-        <v>-0.1389921933404094</v>
+        <v>-0.06128510060541172</v>
       </c>
       <c r="M6" s="13">
-        <v>-0.6077992281692219</v>
+        <v>-0.3913017863085151</v>
       </c>
       <c r="N6" s="13">
-        <v>16.55367</v>
+        <v>18.537308</v>
       </c>
       <c r="O6" s="13">
-        <v>7.0919743</v>
+        <v>5.121617</v>
       </c>
       <c r="P6" s="15">
-        <v>0.42099</v>
+        <v>0.27637</v>
       </c>
       <c r="Q6" s="15">
-        <v>0.537</v>
+        <v>0.517</v>
       </c>
       <c r="R6" s="15">
-        <v>1.226787893360067</v>
+        <v>0.8730975486586645</v>
       </c>
       <c r="S6" s="12">
-        <v>71.56118683993174</v>
+        <v>59.72260038199791</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -5650,31 +5708,31 @@
         <v>48</v>
       </c>
       <c r="E7" s="11">
-        <v>290.5499877929688</v>
+        <v>291.0299987792969</v>
       </c>
       <c r="F7" s="20">
-        <v>0.9463111998231932</v>
+        <v>0.9012666888645469</v>
       </c>
       <c r="G7" s="13">
-        <v>0.3989619877707008</v>
+        <v>0.3995021602593209</v>
       </c>
       <c r="H7" s="13">
-        <v>-0.7867050759706654</v>
+        <v>-0.7892945836103283</v>
       </c>
       <c r="I7" s="13">
-        <v>2.342329077255244</v>
+        <v>2.38315886947137</v>
       </c>
       <c r="J7" s="13">
-        <v>2.298724304819996</v>
+        <v>2.129885985927741</v>
       </c>
       <c r="K7" s="13">
-        <v>0.8109331557567596</v>
+        <v>0.8037214983684114</v>
       </c>
       <c r="L7" s="13">
-        <v>0.3039882978604323</v>
+        <v>0.3002571177441445</v>
       </c>
       <c r="M7" s="13">
-        <v>-0.4878827694273382</v>
+        <v>-0.4512532024849496</v>
       </c>
       <c r="N7" s="13">
         <v>16.752573</v>
@@ -5689,13 +5747,13 @@
         <v>0.531</v>
       </c>
       <c r="R7" s="15">
-        <v>0.8890061268868747</v>
+        <v>0.8490321223410933</v>
       </c>
       <c r="S7" s="12">
-        <v>67.57679997012276</v>
+        <v>67.85634876364114</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5703,61 +5761,61 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C8" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="11">
+        <v>70.80999755859375</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0.8612283529725542</v>
+      </c>
+      <c r="G8" s="13">
+        <v>1.285944045024201</v>
+      </c>
+      <c r="H8" s="13">
+        <v>-1.369862149294123</v>
+      </c>
+      <c r="I8" s="13">
+        <v>-0.5769944704774098</v>
+      </c>
+      <c r="J8" s="13">
+        <v>1.431970504713593</v>
+      </c>
+      <c r="K8" s="13">
+        <v>4.020317717707746</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0.01426017586613477</v>
+      </c>
+      <c r="M8" s="13">
+        <v>-0.07811340359971064</v>
+      </c>
+      <c r="N8" s="13">
+        <v>12.932518</v>
+      </c>
+      <c r="O8" s="13">
+        <v>1.5142426</v>
+      </c>
+      <c r="P8" s="15">
+        <v>-0.20358999</v>
+      </c>
+      <c r="Q8" s="15">
+        <v>0.046</v>
+      </c>
+      <c r="R8" s="15">
+        <v>0.8091466188760659</v>
+      </c>
+      <c r="S8" s="12">
+        <v>65.82349156747074</v>
+      </c>
+      <c r="T8" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" s="11">
-        <v>904.9000244140625</v>
-      </c>
-      <c r="F8" s="20">
-        <v>0.8492286017547676</v>
-      </c>
-      <c r="G8" s="13">
-        <v>0.06853977380706891</v>
-      </c>
-      <c r="H8" s="13">
-        <v>2.151184763842294</v>
-      </c>
-      <c r="I8" s="13">
-        <v>4.142402510022424</v>
-      </c>
-      <c r="J8" s="13">
-        <v>1.050963916303663</v>
-      </c>
-      <c r="K8" s="13">
-        <v>-0.3221645951359624</v>
-      </c>
-      <c r="L8" s="13">
-        <v>-2.382804732910156</v>
-      </c>
-      <c r="M8" s="13">
-        <v>-0.6899938780961075</v>
-      </c>
-      <c r="N8" s="13">
-        <v>11.82349</v>
-      </c>
-      <c r="O8" s="13">
-        <v>7.183</v>
-      </c>
-      <c r="P8" s="15">
-        <v>0.8826000000000001</v>
-      </c>
-      <c r="Q8" s="15">
-        <v>3.793</v>
-      </c>
-      <c r="R8" s="15">
-        <v>1.018602167461715</v>
-      </c>
-      <c r="S8" s="12">
-        <v>38.36988445041676</v>
-      </c>
-      <c r="T8" s="10" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5765,61 +5823,61 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E9" s="11">
-        <v>62.72000122070312</v>
+        <v>896.0700073242188</v>
       </c>
       <c r="F9" s="20">
-        <v>0.8369879994701154</v>
+        <v>0.8263449305218465</v>
       </c>
       <c r="G9" s="13">
-        <v>0.5759095039645012</v>
+        <v>0.06941398245236211</v>
       </c>
       <c r="H9" s="13">
-        <v>0.6154825396339717</v>
+        <v>2.150861358222542</v>
       </c>
       <c r="I9" s="13">
-        <v>3.08973403891346</v>
+        <v>4.140310964546267</v>
       </c>
       <c r="J9" s="13">
-        <v>0.7134305934984712</v>
+        <v>0.9496485317648866</v>
       </c>
       <c r="K9" s="13">
-        <v>1.052312941084053</v>
+        <v>-0.3550952973640076</v>
       </c>
       <c r="L9" s="13">
-        <v>0.08681891142720961</v>
+        <v>-2.402425417913452</v>
       </c>
       <c r="M9" s="13">
-        <v>-0.2455273392692098</v>
+        <v>-0.5307012357598754</v>
       </c>
       <c r="N9" s="13">
-        <v>17.721592</v>
+        <v>11.82349</v>
       </c>
       <c r="O9" s="13">
-        <v>1.8638142</v>
+        <v>7.183</v>
       </c>
       <c r="P9" s="15">
-        <v>0.10629</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.534</v>
+        <v>3.793</v>
       </c>
       <c r="R9" s="15">
-        <v>0.1618728503298139</v>
+        <v>0.994634495377021</v>
       </c>
       <c r="S9" s="12">
-        <v>64.84910745728699</v>
+        <v>37.47218545377914</v>
       </c>
       <c r="T9" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5827,61 +5885,61 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>10</v>
+        <v>141</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>62</v>
+        <v>142</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E10" s="11">
-        <v>68.62999725341797</v>
+        <v>242.4299926757812</v>
       </c>
       <c r="F10" s="20">
-        <v>0.8273835372112954</v>
+        <v>0.8245631613952872</v>
       </c>
       <c r="G10" s="13">
-        <v>1.285384673837105</v>
+        <v>0.3943572019698282</v>
       </c>
       <c r="H10" s="13">
-        <v>-1.367964447767355</v>
+        <v>0.5369918921235662</v>
       </c>
       <c r="I10" s="13">
-        <v>-0.5711638776532628</v>
+        <v>0.189405644478103</v>
       </c>
       <c r="J10" s="13">
-        <v>1.285768844931802</v>
+        <v>0.9283294872900161</v>
       </c>
       <c r="K10" s="13">
-        <v>3.987025017975041</v>
+        <v>3.919815046540162</v>
       </c>
       <c r="L10" s="13">
-        <v>0.05470746140914914</v>
+        <v>-1.662638548773036</v>
       </c>
       <c r="M10" s="13">
-        <v>0.05686115009531262</v>
+        <v>-0.004984262403811876</v>
       </c>
       <c r="N10" s="13">
-        <v>12.932518</v>
+        <v>22.021957</v>
       </c>
       <c r="O10" s="13">
-        <v>1.5142426</v>
+        <v>5.1616917</v>
       </c>
       <c r="P10" s="15">
-        <v>-0.20358999</v>
+        <v>0.19381</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.046</v>
+        <v>0.108</v>
       </c>
       <c r="R10" s="15">
-        <v>0.791438130860143</v>
+        <v>0.3012842406429017</v>
       </c>
       <c r="S10" s="12">
-        <v>60.08412987606285</v>
+        <v>57.0718082607826</v>
       </c>
       <c r="T10" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5889,61 +5947,61 @@
         <v>7</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>140</v>
+        <v>4</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E11" s="11">
-        <v>242.4499969482422</v>
+        <v>62.91999816894531</v>
       </c>
       <c r="F11" s="20">
-        <v>0.8247685360204183</v>
+        <v>0.8097506512834178</v>
       </c>
       <c r="G11" s="13">
-        <v>0.3935940828125599</v>
+        <v>0.576507436874041</v>
       </c>
       <c r="H11" s="13">
-        <v>0.5373976351384561</v>
+        <v>0.6147487778468856</v>
       </c>
       <c r="I11" s="13">
-        <v>0.1867287852304891</v>
+        <v>3.130834419306667</v>
       </c>
       <c r="J11" s="13">
-        <v>0.9932717086479862</v>
+        <v>0.5721685710371798</v>
       </c>
       <c r="K11" s="13">
-        <v>3.857867411462899</v>
+        <v>1.050580120378011</v>
       </c>
       <c r="L11" s="13">
-        <v>-1.70983291359672</v>
+        <v>0.1661064945017811</v>
       </c>
       <c r="M11" s="13">
-        <v>-0.1133815773148118</v>
+        <v>-0.1643813645837533</v>
       </c>
       <c r="N11" s="13">
-        <v>22.021957</v>
+        <v>17.721592</v>
       </c>
       <c r="O11" s="13">
-        <v>5.1616917</v>
+        <v>1.8638142</v>
       </c>
       <c r="P11" s="15">
-        <v>0.19381</v>
+        <v>0.10629</v>
       </c>
       <c r="Q11" s="15">
-        <v>0.108</v>
+        <v>0.534</v>
       </c>
       <c r="R11" s="15">
-        <v>0.3072604477274865</v>
+        <v>0.1272976050367904</v>
       </c>
       <c r="S11" s="12">
-        <v>57.09170641911305</v>
+        <v>65.50669954529533</v>
       </c>
       <c r="T11" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -5951,61 +6009,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E12" s="11">
-        <v>344.1799926757812</v>
+        <v>243.1000061035156</v>
       </c>
       <c r="F12" s="20">
-        <v>0.8121011792481706</v>
+        <v>0.7245767452322718</v>
       </c>
       <c r="G12" s="13">
-        <v>-0.3611787401336813</v>
+        <v>0.1912118272149022</v>
       </c>
       <c r="H12" s="13">
-        <v>1.459707560722779</v>
+        <v>0.02798143859882</v>
       </c>
       <c r="I12" s="13">
-        <v>1.342478323993715</v>
+        <v>-0.8777690799810213</v>
       </c>
       <c r="J12" s="13">
-        <v>0.02459250433115811</v>
+        <v>1.10966009767503</v>
       </c>
       <c r="K12" s="13">
-        <v>3.987025017975041</v>
+        <v>3.750702703186459</v>
       </c>
       <c r="L12" s="13">
-        <v>0.3362339510994537</v>
+        <v>0.4954160794528933</v>
       </c>
       <c r="M12" s="13">
-        <v>0.04146899793621703</v>
+        <v>-0.4906103037022205</v>
       </c>
       <c r="N12" s="13">
-        <v>17.089312</v>
+        <v>41.323265</v>
       </c>
       <c r="O12" s="13">
-        <v>6.6918817</v>
+        <v>1.8231329</v>
       </c>
       <c r="P12" s="15">
-        <v>0.48676</v>
+        <v>0.04575</v>
       </c>
       <c r="Q12" s="15">
-        <v>0.242</v>
+        <v>0.034</v>
       </c>
       <c r="R12" s="15">
-        <v>0.02129960469555003</v>
+        <v>0.3073407372584185</v>
       </c>
       <c r="S12" s="12">
-        <v>48.14486338377436</v>
+        <v>70.59042043375403</v>
       </c>
       <c r="T12" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -6013,61 +6071,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E13" s="11">
-        <v>233.4799957275391</v>
+        <v>124.9599990844727</v>
       </c>
       <c r="F13" s="20">
-        <v>0.680719862117937</v>
+        <v>0.649106181081757</v>
       </c>
       <c r="G13" s="13">
-        <v>0.1904459751578014</v>
+        <v>0.3805332912349265</v>
       </c>
       <c r="H13" s="13">
-        <v>0.02761718478809213</v>
+        <v>-0.1243005063079742</v>
       </c>
       <c r="I13" s="13">
-        <v>-0.8737714308606213</v>
+        <v>0.4428140044701369</v>
       </c>
       <c r="J13" s="13">
-        <v>0.9361497908612391</v>
+        <v>0.1752802356386171</v>
       </c>
       <c r="K13" s="13">
-        <v>3.692508386112247</v>
+        <v>4.020317717707746</v>
       </c>
       <c r="L13" s="13">
-        <v>0.566574734100297</v>
+        <v>0.1296336842829748</v>
       </c>
       <c r="M13" s="13">
-        <v>-0.3567805941044893</v>
+        <v>0.1677081418529904</v>
       </c>
       <c r="N13" s="13">
-        <v>41.323265</v>
+        <v>15.125457</v>
       </c>
       <c r="O13" s="13">
-        <v>1.8231329</v>
+        <v>6.804011</v>
       </c>
       <c r="P13" s="15">
-        <v>0.04575</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q13" s="15">
-        <v>0.034</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R13" s="15">
-        <v>0.2734809664621232</v>
+        <v>0.2035057004795136</v>
       </c>
       <c r="S13" s="12">
-        <v>62.323377983839</v>
+        <v>61.94528186459848</v>
       </c>
       <c r="T13" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -6075,61 +6133,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E14" s="11">
-        <v>49.7599983215332</v>
+        <v>154</v>
       </c>
       <c r="F14" s="20">
-        <v>0.6770571836898372</v>
+        <v>0.6428742209527081</v>
       </c>
       <c r="G14" s="13">
-        <v>0.9851265426872245</v>
+        <v>0.511890850468534</v>
       </c>
       <c r="H14" s="13">
-        <v>0.5615743728567852</v>
+        <v>-0.5596396636832928</v>
       </c>
       <c r="I14" s="13">
-        <v>-0.2788109768673099</v>
+        <v>-0.04564568871787725</v>
       </c>
       <c r="J14" s="13">
-        <v>1.901612660840136</v>
+        <v>0.5431154927190269</v>
       </c>
       <c r="K14" s="13">
-        <v>-0.5452328105418753</v>
+        <v>3.66274158499913</v>
       </c>
       <c r="L14" s="13">
-        <v>-0.5630972623779869</v>
+        <v>0.4496473754582477</v>
       </c>
       <c r="M14" s="13">
-        <v>-0.4188302651069302</v>
+        <v>0.1924787798298476</v>
       </c>
       <c r="N14" s="13">
-        <v>10.391121</v>
+        <v>16.01869</v>
       </c>
       <c r="O14" s="13">
-        <v>2.4548</v>
+        <v>3.9274893</v>
       </c>
       <c r="P14" s="15">
-        <v>0.26659</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q14" s="15">
-        <v>0.092</v>
+        <v>0.053</v>
       </c>
       <c r="R14" s="15">
-        <v>0.4024362119954703</v>
+        <v>0.1858303496283789</v>
       </c>
       <c r="S14" s="12">
-        <v>71.3406647376314</v>
+        <v>47.39020386632503</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -6137,61 +6195,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>13</v>
+        <v>143</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E15" s="11">
-        <v>153.2899932861328</v>
+        <v>109.5199966430664</v>
       </c>
       <c r="F15" s="20">
-        <v>0.6571183915414717</v>
+        <v>0.6381121585794951</v>
       </c>
       <c r="G15" s="13">
-        <v>0.5113567112359665</v>
+        <v>0.02344107793329698</v>
       </c>
       <c r="H15" s="13">
-        <v>-0.5576762322925601</v>
+        <v>1.649714100513951</v>
       </c>
       <c r="I15" s="13">
-        <v>-0.04336176471899431</v>
+        <v>0.05989924891666139</v>
       </c>
       <c r="J15" s="13">
-        <v>0.623488020970478</v>
+        <v>1.028199998881743</v>
       </c>
       <c r="K15" s="13">
-        <v>3.606499497087579</v>
+        <v>0</v>
       </c>
       <c r="L15" s="13">
-        <v>0.421772615433035</v>
+        <v>0.01653032389633705</v>
       </c>
       <c r="M15" s="13">
-        <v>0.1688231786258961</v>
+        <v>-0.2759586818779912</v>
       </c>
       <c r="N15" s="13">
-        <v>16.01869</v>
+        <v>17.76259</v>
       </c>
       <c r="O15" s="13">
-        <v>3.9274893</v>
+        <v>19.783653</v>
       </c>
       <c r="P15" s="15">
-        <v>0.26408002</v>
+        <v>1.5956</v>
       </c>
       <c r="Q15" s="15">
-        <v>0.053</v>
+        <v>0.162</v>
       </c>
       <c r="R15" s="15">
-        <v>0.1977722609370798</v>
+        <v>0.2215380873826178</v>
       </c>
       <c r="S15" s="12">
-        <v>45.80134028818391</v>
+        <v>83.2708161314859</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -6199,61 +6257,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>142</v>
+        <v>6</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>143</v>
+        <v>55</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E16" s="11">
-        <v>207.3699951171875</v>
+        <v>49.90000152587891</v>
       </c>
       <c r="F16" s="20">
-        <v>0.6557072086255608</v>
+        <v>0.6305009494456815</v>
       </c>
       <c r="G16" s="13">
-        <v>-0.4971799866156371</v>
+        <v>0.9856664363574531</v>
       </c>
       <c r="H16" s="13">
-        <v>1.366831241464205</v>
+        <v>0.5611810516441377</v>
       </c>
       <c r="I16" s="13">
-        <v>0.4407360350915431</v>
+        <v>-0.2775772545641314</v>
       </c>
       <c r="J16" s="13">
-        <v>1.604886524267871</v>
+        <v>1.718404107915004</v>
       </c>
       <c r="K16" s="13">
-        <v>0</v>
+        <v>-0.5832267135659824</v>
       </c>
       <c r="L16" s="13">
-        <v>-0.5901040593890334</v>
+        <v>-0.5055497316261317</v>
       </c>
       <c r="M16" s="13">
-        <v>-0.5288946834892293</v>
+        <v>-0.301891184429057</v>
       </c>
       <c r="N16" s="13">
-        <v>28.74471</v>
+        <v>10.391121</v>
       </c>
       <c r="O16" s="13">
-        <v>26.717358</v>
+        <v>2.4548</v>
       </c>
       <c r="P16" s="15">
-        <v>1.14818</v>
+        <v>0.26659</v>
       </c>
       <c r="Q16" s="15">
-        <v>0.299</v>
+        <v>0.092</v>
       </c>
       <c r="R16" s="15">
-        <v>0.9521398096497777</v>
+        <v>0.3454140626518685</v>
       </c>
       <c r="S16" s="12">
-        <v>46.48682395700131</v>
+        <v>71.7100550294742</v>
       </c>
       <c r="T16" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -6270,31 +6328,31 @@
         <v>71</v>
       </c>
       <c r="E17" s="11">
-        <v>262.4500122070312</v>
+        <v>262.6300048828125</v>
       </c>
       <c r="F17" s="20">
-        <v>0.6324989517262135</v>
+        <v>0.6298910874720608</v>
       </c>
       <c r="G17" s="13">
-        <v>-0.0123811023701041</v>
+        <v>-0.01168000613350131</v>
       </c>
       <c r="H17" s="13">
-        <v>0.1602899161165935</v>
+        <v>0.1587373616637428</v>
       </c>
       <c r="I17" s="13">
-        <v>0.9841462557796273</v>
+        <v>0.9947603682216362</v>
       </c>
       <c r="J17" s="13">
-        <v>0.2689057250559135</v>
+        <v>0.2075467136386732</v>
       </c>
       <c r="K17" s="13">
-        <v>3.987025017975041</v>
+        <v>4.020317717707746</v>
       </c>
       <c r="L17" s="13">
-        <v>-0.5605532229249298</v>
+        <v>-0.5707446689505203</v>
       </c>
       <c r="M17" s="13">
-        <v>-0.1851873537758598</v>
+        <v>-0.0417248273971482</v>
       </c>
       <c r="N17" s="13">
         <v>20.11263</v>
@@ -6309,13 +6367,13 @@
         <v>0.196</v>
       </c>
       <c r="R17" s="15">
-        <v>0.05707271426374749</v>
+        <v>0.05089832753514423</v>
       </c>
       <c r="S17" s="12">
-        <v>57.26011610804441</v>
+        <v>57.4079998352241</v>
       </c>
       <c r="T17" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -6323,61 +6381,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>17</v>
+        <v>145</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>74</v>
+        <v>146</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E18" s="11">
-        <v>123.1500015258789</v>
+        <v>209.9700012207031</v>
       </c>
       <c r="F18" s="20">
-        <v>0.6235498536569333</v>
+        <v>0.6273819263740681</v>
       </c>
       <c r="G18" s="13">
-        <v>0.3799330293106025</v>
+        <v>-0.495979033109535</v>
       </c>
       <c r="H18" s="13">
-        <v>-0.1222581250201467</v>
+        <v>1.364720554774369</v>
       </c>
       <c r="I18" s="13">
-        <v>0.4435645954655572</v>
+        <v>0.4606403416133553</v>
       </c>
       <c r="J18" s="13">
-        <v>0.1069468725788219</v>
+        <v>1.532297718593555</v>
       </c>
       <c r="K18" s="13">
-        <v>3.987025017975041</v>
+        <v>0</v>
       </c>
       <c r="L18" s="13">
-        <v>0.06670932328451101</v>
+        <v>-0.6016458743516432</v>
       </c>
       <c r="M18" s="13">
-        <v>0.1979640688746289</v>
+        <v>-0.5829695609163286</v>
       </c>
       <c r="N18" s="13">
-        <v>15.125457</v>
+        <v>28.74471</v>
       </c>
       <c r="O18" s="13">
-        <v>6.804011</v>
+        <v>26.717358</v>
       </c>
       <c r="P18" s="15">
-        <v>0.46032003</v>
+        <v>1.14818</v>
       </c>
       <c r="Q18" s="15">
-        <v>0.07000000000000001</v>
+        <v>0.299</v>
       </c>
       <c r="R18" s="15">
-        <v>0.1482517624790574</v>
+        <v>0.8880391707310582</v>
       </c>
       <c r="S18" s="12">
-        <v>58.92537586639983</v>
+        <v>48.40504731936183</v>
       </c>
       <c r="T18" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -6394,31 +6452,31 @@
         <v>59</v>
       </c>
       <c r="E19" s="11">
-        <v>246.8500061035156</v>
+        <v>249.9100036621094</v>
       </c>
       <c r="F19" s="20">
-        <v>0.6086493409881607</v>
+        <v>0.6083345540359664</v>
       </c>
       <c r="G19" s="13">
-        <v>1.281517153205389</v>
+        <v>1.28199809939033</v>
       </c>
       <c r="H19" s="13">
-        <v>0.168914849402474</v>
+        <v>0.166463226470292</v>
       </c>
       <c r="I19" s="13">
-        <v>-0.05033333836322071</v>
+        <v>-0.04675451852533465</v>
       </c>
       <c r="J19" s="13">
-        <v>0.2390786798018182</v>
+        <v>0.2249011056711633</v>
       </c>
       <c r="K19" s="13">
-        <v>2.063888455225793</v>
+        <v>2.085116368478011</v>
       </c>
       <c r="L19" s="13">
-        <v>0.3930639551463718</v>
+        <v>0.3840764099940323</v>
       </c>
       <c r="M19" s="13">
-        <v>0.1626144433336734</v>
+        <v>0.1860918905580188</v>
       </c>
       <c r="N19" s="13">
         <v>4.9595838</v>
@@ -6433,13 +6491,13 @@
         <v>0.118</v>
       </c>
       <c r="R19" s="15">
-        <v>0.1581836142292201</v>
+        <v>0.1660909582305943</v>
       </c>
       <c r="S19" s="12">
-        <v>61.74215090255093</v>
+        <v>64.58109185521839</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -6447,61 +6505,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E20" s="11">
-        <v>224.3699951171875</v>
+        <v>384.0799865722656</v>
       </c>
       <c r="F20" s="20">
-        <v>0.5456880701765506</v>
+        <v>0.5554709544970838</v>
       </c>
       <c r="G20" s="13">
-        <v>0.4615159312950458</v>
+        <v>0.09653050747037273</v>
       </c>
       <c r="H20" s="13">
-        <v>-0.3280516239482582</v>
+        <v>-0.2394382368103288</v>
       </c>
       <c r="I20" s="13">
-        <v>2.247869721722085</v>
+        <v>0.4648264250834605</v>
       </c>
       <c r="J20" s="13">
-        <v>1.005282730852218</v>
+        <v>1.488921457540494</v>
       </c>
       <c r="K20" s="13">
-        <v>-0.1107491969527463</v>
+        <v>1.918841480549706</v>
       </c>
       <c r="L20" s="13">
-        <v>0.6659825451338081</v>
+        <v>-1.826430861230132</v>
       </c>
       <c r="M20" s="13">
-        <v>-0.474217226580117</v>
+        <v>-0.4678578090072709</v>
       </c>
       <c r="N20" s="13">
-        <v>21.225471</v>
+        <v>33.8231</v>
       </c>
       <c r="O20" s="13">
-        <v>2.324277</v>
+        <v>5.0908465</v>
       </c>
       <c r="P20" s="15">
-        <v>0.12231</v>
+        <v>0.15286</v>
       </c>
       <c r="Q20" s="15">
-        <v>0.535</v>
+        <v>0.204</v>
       </c>
       <c r="R20" s="15">
-        <v>0.2463907226556374</v>
+        <v>0.6228503382084478</v>
       </c>
       <c r="S20" s="12">
-        <v>69.57309166142892</v>
+        <v>59.67830289915142</v>
       </c>
       <c r="T20" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -6509,61 +6567,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>146</v>
+        <v>0</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>147</v>
+        <v>40</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E21" s="11">
-        <v>375.7699890136719</v>
+        <v>1365.380004882812</v>
       </c>
       <c r="F21" s="20">
-        <v>0.5416387454154545</v>
+        <v>0.5230213604171995</v>
       </c>
       <c r="G21" s="13">
-        <v>0.09577198155469299</v>
+        <v>-0.1705629317339571</v>
       </c>
       <c r="H21" s="13">
-        <v>-0.2383729102485588</v>
+        <v>2.05642902385236</v>
       </c>
       <c r="I21" s="13">
-        <v>0.4534907441692339</v>
+        <v>4.121304611935469</v>
       </c>
       <c r="J21" s="13">
-        <v>1.4291232606564</v>
+        <v>0.09428953912194542</v>
       </c>
       <c r="K21" s="13">
-        <v>1.90130391016626</v>
+        <v>0.138054455570112</v>
       </c>
       <c r="L21" s="13">
-        <v>-1.800946332903293</v>
+        <v>-2.909128081426966</v>
       </c>
       <c r="M21" s="13">
-        <v>-0.3955785935527245</v>
+        <v>-0.7217766049998995</v>
       </c>
       <c r="N21" s="13">
-        <v>33.8231</v>
+        <v>17.615238</v>
       </c>
       <c r="O21" s="13">
-        <v>5.0908465</v>
+        <v>12.302696</v>
       </c>
       <c r="P21" s="15">
-        <v>0.15286</v>
+        <v>0.9164</v>
       </c>
       <c r="Q21" s="15">
-        <v>0.204</v>
+        <v>3.716</v>
       </c>
       <c r="R21" s="15">
-        <v>0.5835229000469595</v>
+        <v>0.5112287016357737</v>
       </c>
       <c r="S21" s="12">
-        <v>54.14346100172344</v>
+        <v>35.87824519909739</v>
       </c>
       <c r="T21" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -6571,61 +6629,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E22" s="11">
-        <v>55.86999893188477</v>
+        <v>225.7100067138672</v>
       </c>
       <c r="F22" s="20">
-        <v>0.5363961483337187</v>
+        <v>0.5177893691072141</v>
       </c>
       <c r="G22" s="13">
-        <v>0.4649812608812564</v>
+        <v>0.4621184230168277</v>
       </c>
       <c r="H22" s="13">
-        <v>-0.5342291468581074</v>
+        <v>-0.3293171412879227</v>
       </c>
       <c r="I22" s="13">
-        <v>2.12558659158418</v>
+        <v>2.28906029817432</v>
       </c>
       <c r="J22" s="13">
-        <v>1.622749396879225</v>
+        <v>0.8830156341488813</v>
       </c>
       <c r="K22" s="13">
-        <v>0</v>
+        <v>-0.1388811939487032</v>
       </c>
       <c r="L22" s="13">
-        <v>-2.257297368274222</v>
+        <v>0.7113988323991762</v>
       </c>
       <c r="M22" s="13">
-        <v>-1.126712363167358</v>
+        <v>-0.4066263895243756</v>
       </c>
       <c r="N22" s="13">
-        <v>28.417526</v>
+        <v>21.225471</v>
       </c>
       <c r="O22" s="13">
-        <v>2.7614706</v>
+        <v>2.324277</v>
       </c>
       <c r="P22" s="15">
-        <v>0.10936</v>
+        <v>0.12231</v>
       </c>
       <c r="Q22" s="15">
-        <v>0.337</v>
+        <v>0.535</v>
       </c>
       <c r="R22" s="15">
-        <v>1.019963538282975</v>
+        <v>0.235429502550264</v>
       </c>
       <c r="S22" s="12">
-        <v>38.87597976166139</v>
+        <v>70.78961349727625</v>
       </c>
       <c r="T22" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -6633,61 +6691,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>40</v>
+        <v>152</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E23" s="11">
-        <v>1371.119995117188</v>
+        <v>1283.660034179688</v>
       </c>
       <c r="F23" s="20">
-        <v>0.5209864665562883</v>
+        <v>0.5145499782582459</v>
       </c>
       <c r="G23" s="13">
-        <v>-0.171636736355402</v>
+        <v>-1.324949930516061</v>
       </c>
       <c r="H23" s="13">
-        <v>2.057200793710924</v>
+        <v>1.800353218123673</v>
       </c>
       <c r="I23" s="13">
-        <v>4.125487702887782</v>
+        <v>0.7788800244637265</v>
       </c>
       <c r="J23" s="13">
-        <v>0.1451403183444528</v>
+        <v>0.9540406092115784</v>
       </c>
       <c r="K23" s="13">
-        <v>0.1600400794604018</v>
+        <v>0.9070048758528876</v>
       </c>
       <c r="L23" s="13">
-        <v>-2.925328346632834</v>
+        <v>0.2104780176683627</v>
       </c>
       <c r="M23" s="13">
-        <v>-0.9630877802859937</v>
+        <v>-0.2573125065118153</v>
       </c>
       <c r="N23" s="13">
-        <v>17.615238</v>
+        <v>42.196373</v>
       </c>
       <c r="O23" s="13">
-        <v>12.302696</v>
+        <v>33.078</v>
       </c>
       <c r="P23" s="15">
-        <v>0.9164</v>
+        <v>1.02286</v>
       </c>
       <c r="Q23" s="15">
-        <v>3.716</v>
+        <v>0.477</v>
       </c>
       <c r="R23" s="15">
-        <v>0.5017414358790608</v>
+        <v>0.4260064449852294</v>
       </c>
       <c r="S23" s="12">
-        <v>36.16247342554465</v>
+        <v>69.78480619826614</v>
       </c>
       <c r="T23" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -6695,61 +6753,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>149</v>
+        <v>80</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E24" s="11">
-        <v>157.6499938964844</v>
+        <v>56.09000015258789</v>
       </c>
       <c r="F24" s="20">
-        <v>0.4975487192938067</v>
+        <v>0.5036246660022281</v>
       </c>
       <c r="G24" s="13">
-        <v>0.5320320147799038</v>
+        <v>0.4656147266211902</v>
       </c>
       <c r="H24" s="13">
-        <v>0.4663062678807009</v>
+        <v>-0.5356868534061616</v>
       </c>
       <c r="I24" s="13">
-        <v>1.415088383842661</v>
+        <v>2.148918348349026</v>
       </c>
       <c r="J24" s="13">
-        <v>0.9013173779376299</v>
+        <v>1.475299439608947</v>
       </c>
       <c r="K24" s="13">
-        <v>-0.4847491401954959</v>
+        <v>0</v>
       </c>
       <c r="L24" s="13">
-        <v>0.01830060469612731</v>
+        <v>-2.283552980324228</v>
       </c>
       <c r="M24" s="13">
-        <v>-0.3457279681418917</v>
+        <v>-0.9422442007875107</v>
       </c>
       <c r="N24" s="13">
-        <v>12.296497</v>
+        <v>28.417526</v>
       </c>
       <c r="O24" s="13">
-        <v>2.6058776</v>
+        <v>2.7614706</v>
       </c>
       <c r="P24" s="15">
-        <v>0.22507</v>
+        <v>0.10936</v>
       </c>
       <c r="Q24" s="15">
-        <v>0.587</v>
+        <v>0.337</v>
       </c>
       <c r="R24" s="15">
-        <v>0.2379108466954338</v>
+        <v>0.960931424145665</v>
       </c>
       <c r="S24" s="12">
-        <v>70.41020221803387</v>
+        <v>39.32282125838386</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -6757,61 +6815,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>150</v>
+        <v>14</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>151</v>
+        <v>69</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E25" s="11">
-        <v>145.2400054931641</v>
+        <v>116.620002746582</v>
       </c>
       <c r="F25" s="20">
-        <v>0.4862474982136668</v>
+        <v>0.4945458028309485</v>
       </c>
       <c r="G25" s="13">
-        <v>0.4335221542047916</v>
+        <v>0.4010859088230096</v>
       </c>
       <c r="H25" s="13">
-        <v>-0.1379530307116736</v>
+        <v>0.5056475010694438</v>
       </c>
       <c r="I25" s="13">
-        <v>0.7881553330131479</v>
+        <v>0.5568966182992388</v>
       </c>
       <c r="J25" s="13">
-        <v>1.217276436166592</v>
+        <v>0.130831662432555</v>
       </c>
       <c r="K25" s="13">
-        <v>-0.01419728282182878</v>
+        <v>1.853580005765559</v>
       </c>
       <c r="L25" s="13">
-        <v>0.2209689074051197</v>
+        <v>0.08180836593875149</v>
       </c>
       <c r="M25" s="13">
-        <v>-0.3158366160788511</v>
+        <v>0.2396184482976642</v>
       </c>
       <c r="N25" s="13">
-        <v>19.405296</v>
+        <v>14.403822</v>
       </c>
       <c r="O25" s="13">
-        <v>2.693347</v>
+        <v>3.5817916</v>
       </c>
       <c r="P25" s="15">
-        <v>0.1418</v>
+        <v>0.30667</v>
       </c>
       <c r="Q25" s="15">
-        <v>0.355</v>
+        <v>0.377</v>
       </c>
       <c r="R25" s="15">
-        <v>0.2648803300653042</v>
+        <v>0.2120141474441133</v>
       </c>
       <c r="S25" s="12">
-        <v>71.27212118919752</v>
+        <v>48.95551659208853</v>
       </c>
       <c r="T25" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -6819,61 +6877,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>94</v>
+        <v>8</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>152</v>
+        <v>58</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E26" s="11">
-        <v>455.4400024414062</v>
+        <v>395.7300109863281</v>
       </c>
       <c r="F26" s="20">
-        <v>0.4841001002597541</v>
+        <v>0.4939209326976521</v>
       </c>
       <c r="G26" s="13">
-        <v>0.0686678124403054</v>
+        <v>1.194090308347607</v>
       </c>
       <c r="H26" s="13">
-        <v>-0.844293065729274</v>
+        <v>-0.1076216444283418</v>
       </c>
       <c r="I26" s="13">
-        <v>2.135516195906468</v>
+        <v>-0.619704699975514</v>
       </c>
       <c r="J26" s="13">
-        <v>1.426552670552126</v>
+        <v>0.8434070036761318</v>
       </c>
       <c r="K26" s="13">
-        <v>1.792544282754422</v>
+        <v>0.6930607367779014</v>
       </c>
       <c r="L26" s="13">
-        <v>-2.925328346632834</v>
+        <v>0.9515556674392436</v>
       </c>
       <c r="M26" s="13">
-        <v>-0.9284531168957757</v>
+        <v>-0.4388514907671672</v>
       </c>
       <c r="N26" s="13">
-        <v>26.262207</v>
+        <v>10.463068</v>
       </c>
       <c r="O26" s="13">
-        <v>-202.56053</v>
+        <v>2.7527773</v>
       </c>
       <c r="P26" s="15">
-        <v>0</v>
+        <v>0.27497</v>
       </c>
       <c r="Q26" s="15">
-        <v>0.577</v>
+        <v>-0.005</v>
       </c>
       <c r="R26" s="15">
-        <v>1.240521624339586</v>
+        <v>0.3228818714633928</v>
       </c>
       <c r="S26" s="12">
-        <v>34.26131585715846</v>
+        <v>72.79262372060083</v>
       </c>
       <c r="T26" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -6881,61 +6939,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>8</v>
+        <v>153</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E27" s="11">
-        <v>385.4500122070312</v>
+        <v>219.6399993896484</v>
       </c>
       <c r="F27" s="20">
-        <v>0.4831049683138238</v>
+        <v>0.4840448697426751</v>
       </c>
       <c r="G27" s="13">
-        <v>1.193560836150674</v>
+        <v>0.6433919468057578</v>
       </c>
       <c r="H27" s="13">
-        <v>-0.1054533128723899</v>
+        <v>1.143743903235913</v>
       </c>
       <c r="I27" s="13">
-        <v>-0.6121894045530525</v>
+        <v>-0.515542964509501</v>
       </c>
       <c r="J27" s="13">
-        <v>0.7649988771517408</v>
+        <v>1.192333747871116</v>
       </c>
       <c r="K27" s="13">
-        <v>0.7027284244031452</v>
+        <v>0.327596477986678</v>
       </c>
       <c r="L27" s="13">
-        <v>0.9948361359939333</v>
+        <v>-2.430834946904717</v>
       </c>
       <c r="M27" s="13">
-        <v>-0.3395219238993199</v>
+        <v>-0.1796501706826308</v>
       </c>
       <c r="N27" s="13">
-        <v>10.463068</v>
+        <v>18.566908</v>
       </c>
       <c r="O27" s="13">
-        <v>2.7527773</v>
+        <v>-79.04156999999999</v>
       </c>
       <c r="P27" s="15">
-        <v>0.27497</v>
+        <v>1.13581</v>
       </c>
       <c r="Q27" s="15">
-        <v>-0.005</v>
+        <v>-0.006</v>
       </c>
       <c r="R27" s="15">
-        <v>0.2912586679076508</v>
+        <v>0.3816443209603755</v>
       </c>
       <c r="S27" s="12">
-        <v>66.41204232327075</v>
+        <v>70.98672573735854</v>
       </c>
       <c r="T27" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -6943,61 +7001,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>153</v>
+        <v>94</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E28" s="11">
-        <v>1240.339965820312</v>
+        <v>461.5599975585938</v>
       </c>
       <c r="F28" s="20">
-        <v>0.4628719929352531</v>
+        <v>0.4766142720287261</v>
       </c>
       <c r="G28" s="13">
-        <v>-1.326724339929766</v>
+        <v>0.06909252259033988</v>
       </c>
       <c r="H28" s="13">
-        <v>1.802232776084169</v>
+        <v>-0.8471651400718279</v>
       </c>
       <c r="I28" s="13">
-        <v>0.74292081943507</v>
+        <v>2.180495006837846</v>
       </c>
       <c r="J28" s="13">
-        <v>0.7560855685284067</v>
+        <v>1.347488453957332</v>
       </c>
       <c r="K28" s="13">
-        <v>0.9119242383534664</v>
+        <v>1.807613227874116</v>
       </c>
       <c r="L28" s="13">
-        <v>0.2674723722014398</v>
+        <v>-2.909128081426966</v>
       </c>
       <c r="M28" s="13">
-        <v>-0.1658984185923451</v>
+        <v>-0.8117237369537856</v>
       </c>
       <c r="N28" s="13">
-        <v>42.196373</v>
+        <v>26.262207</v>
       </c>
       <c r="O28" s="13">
-        <v>33.078</v>
+        <v>-202.56053</v>
       </c>
       <c r="P28" s="15">
-        <v>1.02286</v>
+        <v>0</v>
       </c>
       <c r="Q28" s="15">
-        <v>0.477</v>
+        <v>0.577</v>
       </c>
       <c r="R28" s="15">
-        <v>0.3525986352829262</v>
+        <v>1.18008633485513</v>
       </c>
       <c r="S28" s="12">
-        <v>63.39515849937644</v>
+        <v>36.15911528627012</v>
       </c>
       <c r="T28" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -7005,61 +7063,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>69</v>
+        <v>157</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E29" s="11">
-        <v>113.25</v>
+        <v>157.9100036621094</v>
       </c>
       <c r="F29" s="20">
-        <v>0.4625881392270655</v>
+        <v>0.4699739682161381</v>
       </c>
       <c r="G29" s="13">
-        <v>0.4004173777660879</v>
+        <v>0.532634604807481</v>
       </c>
       <c r="H29" s="13">
-        <v>0.5073608672618347</v>
+        <v>0.4650914610299381</v>
       </c>
       <c r="I29" s="13">
-        <v>0.5299570191733038</v>
+        <v>1.460969155364312</v>
       </c>
       <c r="J29" s="13">
-        <v>-0.00665320209619541</v>
+        <v>0.7687422614954488</v>
       </c>
       <c r="K29" s="13">
-        <v>1.837490863470538</v>
+        <v>-0.5213701852923126</v>
       </c>
       <c r="L29" s="13">
-        <v>0.121278986988843</v>
+        <v>0.09407949636759708</v>
       </c>
       <c r="M29" s="13">
-        <v>0.3819986042876146</v>
+        <v>-0.2514354493255337</v>
       </c>
       <c r="N29" s="13">
-        <v>14.403822</v>
+        <v>12.296497</v>
       </c>
       <c r="O29" s="13">
-        <v>3.5817916</v>
+        <v>2.6058776</v>
       </c>
       <c r="P29" s="15">
-        <v>0.30667</v>
+        <v>0.22507</v>
       </c>
       <c r="Q29" s="15">
-        <v>0.377</v>
+        <v>0.587</v>
       </c>
       <c r="R29" s="15">
-        <v>0.1684894979319869</v>
+        <v>0.2093352903094625</v>
       </c>
       <c r="S29" s="12">
-        <v>39.90391328754555</v>
+        <v>70.70238647251864</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -7067,61 +7125,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>19</v>
+        <v>158</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E30" s="11">
-        <v>199.8300018310547</v>
+        <v>145.9499969482422</v>
       </c>
       <c r="F30" s="20">
-        <v>0.4493987895230812</v>
+        <v>0.4505846794304207</v>
       </c>
       <c r="G30" s="13">
-        <v>0.5875877985619562</v>
+        <v>0.4341489187690627</v>
       </c>
       <c r="H30" s="13">
-        <v>-0.6557807601431646</v>
+        <v>-0.1392720269078983</v>
       </c>
       <c r="I30" s="13">
-        <v>4.125487702887782</v>
+        <v>0.813110618840484</v>
       </c>
       <c r="J30" s="13">
-        <v>-0.3843571334821353</v>
+        <v>1.06837913061436</v>
       </c>
       <c r="K30" s="13">
-        <v>0.7188204100916313</v>
+        <v>-0.04013774514486335</v>
       </c>
       <c r="L30" s="13">
-        <v>0.6567157010139739</v>
+        <v>0.3039429883818122</v>
       </c>
       <c r="M30" s="13">
-        <v>0.3206860736107942</v>
+        <v>-0.2565431574578575</v>
       </c>
       <c r="N30" s="13">
-        <v>12.956969</v>
+        <v>19.405296</v>
       </c>
       <c r="O30" s="13">
-        <v>1.2018421</v>
+        <v>2.693347</v>
       </c>
       <c r="P30" s="15">
-        <v>0.09031</v>
+        <v>0.1418</v>
       </c>
       <c r="Q30" s="15">
-        <v>11.11</v>
+        <v>0.355</v>
       </c>
       <c r="R30" s="15">
-        <v>-0.02096900606374497</v>
+        <v>0.2307944811903566</v>
       </c>
       <c r="S30" s="12">
-        <v>48.54081307543591</v>
+        <v>72.0536215530567</v>
       </c>
       <c r="T30" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -7129,61 +7187,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>71</v>
       </c>
       <c r="E31" s="11">
-        <v>98.48999786376953</v>
+        <v>253.9900054931641</v>
       </c>
       <c r="F31" s="20">
-        <v>0.4433412161793428</v>
+        <v>0.4300392425764909</v>
       </c>
       <c r="G31" s="13">
-        <v>0.0225354241643628</v>
+        <v>-0.07251740337470877</v>
       </c>
       <c r="H31" s="13">
-        <v>1.652713180850361</v>
+        <v>0.2691688205067533</v>
       </c>
       <c r="I31" s="13">
-        <v>0.04480435604649428</v>
+        <v>-0.2744798645681174</v>
       </c>
       <c r="J31" s="13">
-        <v>0.5060626281731307</v>
+        <v>0.8237268852037558</v>
       </c>
       <c r="K31" s="13">
-        <v>0.1089896421038247</v>
+        <v>1.508545426037199</v>
       </c>
       <c r="L31" s="13">
-        <v>0.5789218549893805</v>
+        <v>0.4853703933249489</v>
       </c>
       <c r="M31" s="13">
-        <v>-0.3657820189338828</v>
+        <v>-0.3724048740677242</v>
       </c>
       <c r="N31" s="13">
-        <v>17.76259</v>
+        <v>25.657436</v>
       </c>
       <c r="O31" s="13">
-        <v>19.783653</v>
+        <v>13.762447</v>
       </c>
       <c r="P31" s="15">
-        <v>1.5956</v>
+        <v>0.54960996</v>
       </c>
       <c r="Q31" s="15">
-        <v>0.162</v>
+        <v>0.067</v>
       </c>
       <c r="R31" s="15">
-        <v>0.0488751020800815</v>
+        <v>0.2636387749660964</v>
       </c>
       <c r="S31" s="12">
-        <v>70.14537960650082</v>
+        <v>69.78394004918161</v>
       </c>
       <c r="T31" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -7200,31 +7258,31 @@
         <v>63</v>
       </c>
       <c r="E32" s="11">
-        <v>262.6600036621094</v>
+        <v>267.9299926757812</v>
       </c>
       <c r="F32" s="20">
-        <v>0.4328433196129662</v>
+        <v>0.4271248391187443</v>
       </c>
       <c r="G32" s="13">
-        <v>-0.7602416494768173</v>
+        <v>-0.7589860946385489</v>
       </c>
       <c r="H32" s="13">
-        <v>0.4433698793704594</v>
+        <v>0.4424895073656877</v>
       </c>
       <c r="I32" s="13">
-        <v>-0.4366025606922668</v>
+        <v>-0.4351884462710338</v>
       </c>
       <c r="J32" s="13">
-        <v>2.328592175920653</v>
+        <v>2.31704266595455</v>
       </c>
       <c r="K32" s="13">
-        <v>-0.2228382007139265</v>
+        <v>-0.2535143931347701</v>
       </c>
       <c r="L32" s="13">
-        <v>-1.166499541043542</v>
+        <v>-1.164355895919075</v>
       </c>
       <c r="M32" s="13">
-        <v>-0.7429900542395719</v>
+        <v>-0.7295857406596483</v>
       </c>
       <c r="N32" s="13">
         <v>48.981342</v>
@@ -7239,13 +7297,13 @@
         <v>0.094</v>
       </c>
       <c r="R32" s="15">
-        <v>0.9769682557237973</v>
+        <v>1.030080325422186</v>
       </c>
       <c r="S32" s="12">
-        <v>53.19063673702344</v>
+        <v>56.11755454828045</v>
       </c>
       <c r="T32" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -7253,61 +7311,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="E33" s="11">
-        <v>249.4299926757812</v>
+        <v>30.64999961853027</v>
       </c>
       <c r="F33" s="20">
-        <v>0.4223005926349582</v>
+        <v>0.4130430971399421</v>
       </c>
       <c r="G33" s="13">
-        <v>-0.07340653693232591</v>
+        <v>0.46909367085789</v>
       </c>
       <c r="H33" s="13">
-        <v>0.271230006609087</v>
+        <v>-0.286777552311737</v>
       </c>
       <c r="I33" s="13">
-        <v>-0.2734586853956155</v>
+        <v>-0.6746219453467055</v>
       </c>
       <c r="J33" s="13">
-        <v>0.8039252871922479</v>
+        <v>0.4981459381702493</v>
       </c>
       <c r="K33" s="13">
-        <v>1.50011406007055</v>
+        <v>2.267281006788543</v>
       </c>
       <c r="L33" s="13">
-        <v>0.4471124501759435</v>
+        <v>0.636629269149417</v>
       </c>
       <c r="M33" s="13">
-        <v>-0.3569397951476565</v>
+        <v>-0.2220302390574339</v>
       </c>
       <c r="N33" s="13">
-        <v>25.657436</v>
+        <v>29.155342</v>
       </c>
       <c r="O33" s="13">
-        <v>13.762447</v>
+        <v>1.9140799</v>
       </c>
       <c r="P33" s="15">
-        <v>0.54960996</v>
+        <v>0.07979</v>
       </c>
       <c r="Q33" s="15">
-        <v>0.067</v>
+        <v>0.108</v>
       </c>
       <c r="R33" s="15">
-        <v>0.2425490848742522</v>
+        <v>0.1640094143976365</v>
       </c>
       <c r="S33" s="12">
-        <v>66.18623105622979</v>
+        <v>65.39014877810916</v>
       </c>
       <c r="T33" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -7315,61 +7373,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E34" s="11">
-        <v>207.7200012207031</v>
+        <v>129.6699981689453</v>
       </c>
       <c r="F34" s="20">
-        <v>0.4163101752069729</v>
+        <v>0.4120682375207951</v>
       </c>
       <c r="G34" s="13">
-        <v>0.6430147073268255</v>
+        <v>0.5920488244253568</v>
       </c>
       <c r="H34" s="13">
-        <v>1.145619855113209</v>
+        <v>-0.7025044660757493</v>
       </c>
       <c r="I34" s="13">
-        <v>-0.5079374730280123</v>
+        <v>-0.5550326180845108</v>
       </c>
       <c r="J34" s="13">
-        <v>0.9438744163092876</v>
+        <v>0.7318360831615885</v>
       </c>
       <c r="K34" s="13">
-        <v>0.3453753629071055</v>
+        <v>1.980130517738296</v>
       </c>
       <c r="L34" s="13">
-        <v>-2.387480142305346</v>
+        <v>0.5802819476129887</v>
       </c>
       <c r="M34" s="13">
-        <v>-0.1662057691310767</v>
+        <v>-0.2322497303631193</v>
       </c>
       <c r="N34" s="13">
-        <v>18.566908</v>
+        <v>59.546726</v>
       </c>
       <c r="O34" s="13">
-        <v>-79.04156999999999</v>
+        <v>2.3670914</v>
       </c>
       <c r="P34" s="15">
-        <v>1.13581</v>
+        <v>0.03931</v>
       </c>
       <c r="Q34" s="15">
-        <v>-0.006</v>
+        <v>0.05</v>
       </c>
       <c r="R34" s="15">
-        <v>0.3295782301816179</v>
+        <v>0.3822648458555777</v>
       </c>
       <c r="S34" s="12">
-        <v>64.67059171275918</v>
+        <v>70.01585237497511</v>
       </c>
       <c r="T34" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -7377,61 +7435,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E35" s="11">
-        <v>50.91999816894531</v>
+        <v>807.47998046875</v>
       </c>
       <c r="F35" s="20">
-        <v>0.4122183903091031</v>
+        <v>0.4062222387188359</v>
       </c>
       <c r="G35" s="13">
-        <v>0.3322175042912772</v>
+        <v>0.179218298133199</v>
       </c>
       <c r="H35" s="13">
-        <v>-0.04409757845196494</v>
+        <v>0.1790552293207532</v>
       </c>
       <c r="I35" s="13">
-        <v>1.262324069011482</v>
+        <v>-0.2124000415459111</v>
       </c>
       <c r="J35" s="13">
-        <v>0.8389219093715332</v>
+        <v>0.5135085057101227</v>
       </c>
       <c r="K35" s="13">
-        <v>0.02353564913738036</v>
+        <v>1.628853536074061</v>
       </c>
       <c r="L35" s="13">
-        <v>0.0001138007126409557</v>
+        <v>0.1847500636301643</v>
       </c>
       <c r="M35" s="13">
-        <v>-0.2658154195358085</v>
+        <v>0.07442665822995792</v>
       </c>
       <c r="N35" s="13">
-        <v>11.052287</v>
+        <v>19.553413</v>
       </c>
       <c r="O35" s="13">
-        <v>1.3973281</v>
+        <v>2.5014632</v>
       </c>
       <c r="P35" s="15">
-        <v>0.11522</v>
+        <v>0.14043</v>
       </c>
       <c r="Q35" s="15">
-        <v>0.642</v>
+        <v>0.167</v>
       </c>
       <c r="R35" s="15">
-        <v>0.1485158805772946</v>
+        <v>0.08332036135921173</v>
       </c>
       <c r="S35" s="12">
-        <v>62.77150403782788</v>
+        <v>60.89548055596043</v>
       </c>
       <c r="T35" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -7439,61 +7497,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E36" s="11">
-        <v>127.0699996948242</v>
+        <v>61.68000030517578</v>
       </c>
       <c r="F36" s="20">
-        <v>0.4079908958393006</v>
+        <v>0.406167750078374</v>
       </c>
       <c r="G36" s="13">
-        <v>0.5912605751132745</v>
+        <v>0.5295268879890338</v>
       </c>
       <c r="H36" s="13">
-        <v>-0.7013641728016499</v>
+        <v>0.6581905543677987</v>
       </c>
       <c r="I36" s="13">
-        <v>-0.5499235937325816</v>
+        <v>0.2056474795724012</v>
       </c>
       <c r="J36" s="13">
-        <v>0.7206269909687593</v>
+        <v>0.1174093636176268</v>
       </c>
       <c r="K36" s="13">
-        <v>1.961232684454415</v>
+        <v>0.933676956851626</v>
       </c>
       <c r="L36" s="13">
-        <v>0.5746148042294403</v>
+        <v>0.427500077655151</v>
       </c>
       <c r="M36" s="13">
-        <v>-0.2154786042311333</v>
+        <v>0.150795312718347</v>
       </c>
       <c r="N36" s="13">
-        <v>59.546726</v>
+        <v>13.160793</v>
       </c>
       <c r="O36" s="13">
-        <v>2.3670914</v>
+        <v>5.4691076</v>
       </c>
       <c r="P36" s="15">
-        <v>0.03931</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q36" s="15">
-        <v>0.05</v>
+        <v>0.057</v>
       </c>
       <c r="R36" s="15">
-        <v>0.3489133417325303</v>
+        <v>0.0611596937824892</v>
       </c>
       <c r="S36" s="12">
-        <v>65.49761727591108</v>
+        <v>53.38371963056493</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -7501,61 +7559,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="E37" s="11">
-        <v>30.95</v>
+        <v>318.6700134277344</v>
       </c>
       <c r="F37" s="20">
-        <v>0.4070909176810039</v>
+        <v>0.4029015254655374</v>
       </c>
       <c r="G37" s="13">
-        <v>-0.04384905612784547</v>
+        <v>-0.899377246571977</v>
       </c>
       <c r="H37" s="13">
-        <v>-1.001192936831727</v>
+        <v>0.651197148783897</v>
       </c>
       <c r="I37" s="13">
-        <v>-1.180905936353672</v>
+        <v>0.01332868977496858</v>
       </c>
       <c r="J37" s="13">
-        <v>0.8841391759436558</v>
+        <v>1.958503723767202</v>
       </c>
       <c r="K37" s="13">
-        <v>3.987025017975041</v>
+        <v>-0.3131009570681217</v>
       </c>
       <c r="L37" s="13">
-        <v>0.4399228630770827</v>
+        <v>-0.789267314382883</v>
       </c>
       <c r="M37" s="13">
-        <v>-0.9601864426533376</v>
+        <v>-0.5419743294180019</v>
       </c>
       <c r="N37" s="13">
-        <v>497.26776</v>
+        <v>50.87869</v>
       </c>
       <c r="O37" s="13">
-        <v>2.3630948</v>
+        <v>6.758711</v>
       </c>
       <c r="P37" s="15">
-        <v>-0.08785999999999999</v>
+        <v>0.14425</v>
       </c>
       <c r="Q37" s="15">
-        <v>-0.112</v>
+        <v>0.176</v>
       </c>
       <c r="R37" s="15">
-        <v>0.1308001461454147</v>
+        <v>0.8992194181944175</v>
       </c>
       <c r="S37" s="12">
-        <v>75.22299401348863</v>
+        <v>74.4641926653278</v>
       </c>
       <c r="T37" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -7563,61 +7621,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="E38" s="11">
-        <v>30.05999946594238</v>
+        <v>30.95</v>
       </c>
       <c r="F38" s="20">
-        <v>0.4068103479828467</v>
+        <v>0.3845534632925743</v>
       </c>
       <c r="G38" s="13">
-        <v>0.4684682194641577</v>
+        <v>-0.04251914790126206</v>
       </c>
       <c r="H38" s="13">
-        <v>-0.2862553511202726</v>
+        <v>-1.001305748713663</v>
       </c>
       <c r="I38" s="13">
-        <v>-0.6772988045943193</v>
+        <v>-1.196106130416092</v>
       </c>
       <c r="J38" s="13">
-        <v>0.4641518973454954</v>
+        <v>0.7755489813393309</v>
       </c>
       <c r="K38" s="13">
-        <v>2.24201008991559</v>
+        <v>4.020317717707746</v>
       </c>
       <c r="L38" s="13">
-        <v>0.6359871673079411</v>
+        <v>0.4383322866492484</v>
       </c>
       <c r="M38" s="13">
-        <v>-0.1303650614252765</v>
+        <v>-0.8672039371885875</v>
       </c>
       <c r="N38" s="13">
-        <v>29.155342</v>
+        <v>497.26776</v>
       </c>
       <c r="O38" s="13">
-        <v>1.9140799</v>
+        <v>2.3630948</v>
       </c>
       <c r="P38" s="15">
-        <v>0.07979</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q38" s="15">
-        <v>0.108</v>
+        <v>-0.112</v>
       </c>
       <c r="R38" s="15">
-        <v>0.1613840842281253</v>
+        <v>0.1308001461454147</v>
       </c>
       <c r="S38" s="12">
-        <v>59.64022797132488</v>
+        <v>75.22299401348943</v>
       </c>
       <c r="T38" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -7625,61 +7683,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E39" s="11">
-        <v>217.0899963378906</v>
+        <v>258.6900024414062</v>
       </c>
       <c r="F39" s="20">
-        <v>0.4023705229044524</v>
+        <v>0.3844740031407636</v>
       </c>
       <c r="G39" s="13">
-        <v>-1.120223434191142</v>
+        <v>-0.8275724890736497</v>
       </c>
       <c r="H39" s="13">
-        <v>2.369495368780043</v>
+        <v>0.0352288459368772</v>
       </c>
       <c r="I39" s="13">
-        <v>2.411103571971912</v>
+        <v>2.268831712885381</v>
       </c>
       <c r="J39" s="13">
-        <v>0.1272069863684952</v>
+        <v>1.787546614415023</v>
       </c>
       <c r="K39" s="13">
-        <v>-0.2594613405566883</v>
+        <v>-0.01289817306104545</v>
       </c>
       <c r="L39" s="13">
-        <v>-0.1910369488379715</v>
+        <v>-2.821686239288451</v>
       </c>
       <c r="M39" s="13">
-        <v>-0.1472924157075974</v>
+        <v>-0.8062220583036548</v>
       </c>
       <c r="N39" s="13">
-        <v>27.070797</v>
+        <v>33.799446</v>
       </c>
       <c r="O39" s="13">
-        <v>22.580408</v>
+        <v>4.1801233</v>
       </c>
       <c r="P39" s="15">
-        <v>1.17211</v>
+        <v>0.13497</v>
       </c>
       <c r="Q39" s="15">
-        <v>1.059</v>
+        <v>0.22</v>
       </c>
       <c r="R39" s="15">
-        <v>0.07683966792622821</v>
+        <v>0.780385388906409</v>
       </c>
       <c r="S39" s="12">
-        <v>41.51496074041662</v>
+        <v>46.34510411785447</v>
       </c>
       <c r="T39" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -7687,61 +7745,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>170</v>
+        <v>7</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>171</v>
+        <v>56</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E40" s="11">
-        <v>178.2799987792969</v>
+        <v>216.4700012207031</v>
       </c>
       <c r="F40" s="20">
-        <v>0.3906082496600129</v>
+        <v>0.3799548487530597</v>
       </c>
       <c r="G40" s="13">
-        <v>0.2979887559507698</v>
+        <v>-1.118572244175211</v>
       </c>
       <c r="H40" s="13">
-        <v>-0.5478874135375696</v>
+        <v>2.368452570933654</v>
       </c>
       <c r="I40" s="13">
-        <v>1.04298669322405</v>
+        <v>2.409012026495755</v>
       </c>
       <c r="J40" s="13">
-        <v>1.022975320707297</v>
+        <v>0.01710198161974044</v>
       </c>
       <c r="K40" s="13">
-        <v>0.1345148607821132</v>
+        <v>-0.2909688047500197</v>
       </c>
       <c r="L40" s="13">
-        <v>0.6596617688397663</v>
+        <v>-0.09483324430199144</v>
       </c>
       <c r="M40" s="13">
-        <v>-0.5285061900493528</v>
+        <v>-0.03850130690203546</v>
       </c>
       <c r="N40" s="13">
-        <v>23.034748</v>
+        <v>27.070797</v>
       </c>
       <c r="O40" s="13">
-        <v>2.8373492</v>
+        <v>22.580408</v>
       </c>
       <c r="P40" s="15">
-        <v>0.12584</v>
+        <v>1.17211</v>
       </c>
       <c r="Q40" s="15">
-        <v>0.441</v>
+        <v>1.059</v>
       </c>
       <c r="R40" s="15">
-        <v>0.2232686343719432</v>
+        <v>0.08547520276846865</v>
       </c>
       <c r="S40" s="12">
-        <v>71.0891797097937</v>
+        <v>40.92991462248053</v>
       </c>
       <c r="T40" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -7749,61 +7807,61 @@
         <v>37</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E41" s="11">
-        <v>74.08999633789062</v>
+        <v>438.9400024414062</v>
       </c>
       <c r="F41" s="20">
-        <v>0.3848464658445815</v>
+        <v>0.37880748247031</v>
       </c>
       <c r="G41" s="13">
-        <v>0.394683678573625</v>
+        <v>-0.2936486380311477</v>
       </c>
       <c r="H41" s="13">
-        <v>1.8404582242832</v>
+        <v>1.240294774468037</v>
       </c>
       <c r="I41" s="13">
-        <v>-0.6237053563920132</v>
+        <v>-0.09299075107987806</v>
       </c>
       <c r="J41" s="13">
-        <v>0.5962065152350911</v>
+        <v>0.8508044676165736</v>
       </c>
       <c r="K41" s="13">
-        <v>-0.6662001512346341</v>
+        <v>0.03874351568119263</v>
       </c>
       <c r="L41" s="13">
-        <v>0.3384370839546824</v>
+        <v>-0.08994486193195664</v>
       </c>
       <c r="M41" s="13">
-        <v>-0.4690442250554238</v>
+        <v>-0.1497215242722425</v>
       </c>
       <c r="N41" s="13">
-        <v>15.812632</v>
+        <v>26.862732</v>
       </c>
       <c r="O41" s="13">
-        <v>-47.002502</v>
+        <v>20.004162</v>
       </c>
       <c r="P41" s="15">
-        <v>0</v>
+        <v>0.91473</v>
       </c>
       <c r="Q41" s="15">
-        <v>0.012</v>
+        <v>0.095</v>
       </c>
       <c r="R41" s="15">
-        <v>0.1824640782873521</v>
+        <v>0.2899124910217135</v>
       </c>
       <c r="S41" s="12">
-        <v>69.7395760152023</v>
+        <v>63.44882487513986</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -7811,61 +7869,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="E42" s="11">
-        <v>171.5</v>
+        <v>300.760009765625</v>
       </c>
       <c r="F42" s="20">
-        <v>0.3804505716401029</v>
+        <v>0.3705091648042955</v>
       </c>
       <c r="G42" s="13">
-        <v>-2.013855312600353</v>
+        <v>0.1338797210506113</v>
       </c>
       <c r="H42" s="13">
-        <v>1.771289817656464</v>
+        <v>1.210360910376113</v>
       </c>
       <c r="I42" s="13">
-        <v>0.2370235024582036</v>
+        <v>0.5961464855734491</v>
       </c>
       <c r="J42" s="13">
-        <v>1.496739159266282</v>
+        <v>0.4243333387476589</v>
       </c>
       <c r="K42" s="13">
-        <v>0.537924295110717</v>
+        <v>-0.09291441605726049</v>
       </c>
       <c r="L42" s="13">
-        <v>-0.8042964955743448</v>
+        <v>-0.7263962591710715</v>
       </c>
       <c r="M42" s="13">
-        <v>-0.3684883327674784</v>
+        <v>0.2571490581312542</v>
       </c>
       <c r="N42" s="13">
-        <v>59.763256</v>
+        <v>18.048096</v>
       </c>
       <c r="O42" s="13">
-        <v>80.00473</v>
+        <v>28.679903</v>
       </c>
       <c r="P42" s="15">
-        <v>1.17442</v>
+        <v>0.89489</v>
       </c>
       <c r="Q42" s="15">
-        <v>0.256</v>
+        <v>0.14</v>
       </c>
       <c r="R42" s="15">
-        <v>1.076271224795865</v>
+        <v>0.1023852173304152</v>
       </c>
       <c r="S42" s="12">
-        <v>43.42339151159739</v>
+        <v>64.85923565347476</v>
       </c>
       <c r="T42" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -7873,61 +7931,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E43" s="11">
-        <v>316.7999877929688</v>
+        <v>50.38000106811523</v>
       </c>
       <c r="F43" s="20">
-        <v>0.3785772201974371</v>
+        <v>0.3682805794938797</v>
       </c>
       <c r="G43" s="13">
-        <v>-0.9007822058619874</v>
+        <v>0.332787110620459</v>
       </c>
       <c r="H43" s="13">
-        <v>0.651886435809624</v>
+        <v>-0.04536551751463628</v>
       </c>
       <c r="I43" s="13">
-        <v>0.004518498513503999</v>
+        <v>1.313165623779629</v>
       </c>
       <c r="J43" s="13">
-        <v>1.902455600913674</v>
+        <v>0.6116953506650414</v>
       </c>
       <c r="K43" s="13">
-        <v>-0.2811022868274112</v>
+        <v>-0.001548351359454703</v>
       </c>
       <c r="L43" s="13">
-        <v>-0.8138627574075431</v>
+        <v>0.07092284876086068</v>
       </c>
       <c r="M43" s="13">
-        <v>-0.652603784233197</v>
+        <v>-0.04071692444316939</v>
       </c>
       <c r="N43" s="13">
-        <v>50.87869</v>
+        <v>11.052287</v>
       </c>
       <c r="O43" s="13">
-        <v>6.758711</v>
+        <v>1.3973281</v>
       </c>
       <c r="P43" s="15">
-        <v>0.14425</v>
+        <v>0.11522</v>
       </c>
       <c r="Q43" s="15">
-        <v>0.176</v>
+        <v>0.642</v>
       </c>
       <c r="R43" s="15">
-        <v>0.8763325909991941</v>
+        <v>0.1198889880817111</v>
       </c>
       <c r="S43" s="12">
-        <v>73.75412320103445</v>
+        <v>59.29111723421912</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -7935,61 +7993,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="E44" s="11">
-        <v>616.4000244140625</v>
+        <v>74.63999938964844</v>
       </c>
       <c r="F44" s="20">
-        <v>0.3755261429351075</v>
+        <v>0.3669804608455737</v>
       </c>
       <c r="G44" s="13">
-        <v>-1.459476025674528</v>
+        <v>0.3952758540064341</v>
       </c>
       <c r="H44" s="13">
-        <v>2.887446605031075</v>
+        <v>1.840190871076458</v>
       </c>
       <c r="I44" s="13">
-        <v>-0.1679026678302109</v>
+        <v>-0.6296873188110119</v>
       </c>
       <c r="J44" s="13">
-        <v>0.7108221445889372</v>
+        <v>0.5480694753898142</v>
       </c>
       <c r="K44" s="13">
-        <v>-0.2944197922247791</v>
+        <v>-0.706939770113322</v>
       </c>
       <c r="L44" s="13">
-        <v>1.00043656382305</v>
+        <v>0.3339116639530976</v>
       </c>
       <c r="M44" s="13">
-        <v>-0.5613978075564896</v>
+        <v>-0.4406721300906005</v>
       </c>
       <c r="N44" s="13">
-        <v>33.961494</v>
+        <v>15.812632</v>
       </c>
       <c r="O44" s="13">
-        <v>96.5322</v>
+        <v>-47.002502</v>
       </c>
       <c r="P44" s="15">
-        <v>2.41202</v>
+        <v>0</v>
       </c>
       <c r="Q44" s="15">
-        <v>0.141</v>
+        <v>0.012</v>
       </c>
       <c r="R44" s="15">
-        <v>0.1968823289665349</v>
+        <v>0.1905049843015705</v>
       </c>
       <c r="S44" s="12">
-        <v>74.2570461461538</v>
+        <v>71.41505017933778</v>
       </c>
       <c r="T44" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -8055,110 +8113,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B6" s="15">
         <v>0.18</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B7" s="15">
         <v>0.16</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B8" s="15">
         <v>0.1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B9" s="15">
         <v>0.3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B10" s="15">
         <v>0.12</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B11" s="15">
         <v>0.06</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B12" s="15">
         <v>0.08</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B13" s="15">
         <f>SUM(B6:B12)</f>
@@ -8167,22 +8225,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -8261,49 +8319,49 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="10" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="10" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="10" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>91</v>
@@ -8311,7 +8369,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="10" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>44</v>
@@ -8319,113 +8377,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="10" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="9" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="16" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="32" customHeight="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="32.25" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B23" s="26"/>
     </row>
-    <row r="24" spans="1:2" ht="32" customHeight="1">
+    <row r="24" spans="1:2" ht="32.25" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B24" s="26"/>
     </row>
-    <row r="25" spans="1:2" ht="32" customHeight="1">
+    <row r="25" spans="1:2" ht="32.25" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B25" s="26"/>
     </row>
-    <row r="26" spans="1:2" ht="32" customHeight="1">
+    <row r="26" spans="1:2" ht="32.25" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B26" s="26"/>
     </row>
-    <row r="27" spans="1:2" ht="32" customHeight="1">
+    <row r="27" spans="1:2" ht="32.25" customHeight="1">
       <c r="A27" s="26" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B27" s="26"/>
     </row>
@@ -8443,3892 +8501,3829 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BI21"/>
+  <dimension ref="A1:BH21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:61">
+    <row r="1" spans="1:60">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1">
-        <v>1278.22998046875</v>
+        <v>1015.890014648438</v>
       </c>
       <c r="C1">
-        <v>1096.099975585938</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="D1">
-        <v>1015.890014648438</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="E1">
-        <v>1279.9599609375</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="F1">
-        <v>1214.829956054688</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="G1">
-        <v>1288.030029296875</v>
+        <v>1350.5</v>
       </c>
       <c r="H1">
-        <v>1427.619995117188</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="I1">
-        <v>1350.5</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="J1">
-        <v>1258.579956054688</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="K1">
-        <v>1212.2099609375</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="L1">
-        <v>1237.920043945312</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="M1">
-        <v>1271.050048828125</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="N1">
-        <v>1344.2900390625</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="O1">
-        <v>1528.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="P1">
-        <v>1641.109985351562</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="Q1">
-        <v>1786.849975585938</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="R1">
-        <v>1625.780029296875</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="S1">
-        <v>1568.869995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="T1">
-        <v>1600.619995117188</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="U1">
-        <v>1596.079956054688</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="V1">
-        <v>1493.119995117188</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="W1">
-        <v>1480.77001953125</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="X1">
-        <v>1499.369995117188</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="Y1">
-        <v>1484.949951171875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="Z1">
-        <v>1484.97998046875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="AA1">
-        <v>1566.699951171875</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="AB1">
-        <v>1536.869995117188</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="AC1">
-        <v>1553.400024414062</v>
+        <v>1740</v>
       </c>
       <c r="AD1">
-        <v>1554.989990234375</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="AE1">
-        <v>1740</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="AF1">
-        <v>1737.989990234375</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="AG1">
-        <v>1764.170043945312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="AH1">
-        <v>1692.589965820312</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="AI1">
-        <v>1633.349975585938</v>
+        <v>1530.89501953125</v>
       </c>
       <c r="AJ1">
-        <v>1551.989990234375</v>
+        <v>1519.969970703125</v>
       </c>
       <c r="AK1">
-        <v>1530.89501953125</v>
+        <v>1614.390014648438</v>
       </c>
       <c r="AL1">
-        <v>1519.969970703125</v>
+        <v>1791.819946289062</v>
       </c>
       <c r="AM1">
-        <v>1614.390014648438</v>
+        <v>1766.640014648438</v>
       </c>
       <c r="AN1">
-        <v>1791.819946289062</v>
+        <v>1887.0400390625</v>
       </c>
       <c r="AO1">
-        <v>1766.640014648438</v>
+        <v>1816.569946289062</v>
       </c>
       <c r="AP1">
-        <v>1887.0400390625</v>
+        <v>1753.619995117188</v>
       </c>
       <c r="AQ1">
-        <v>1816.569946289062</v>
+        <v>1777.800048828125</v>
       </c>
       <c r="AR1">
-        <v>1753.619995117188</v>
+        <v>1712.890014648438</v>
       </c>
       <c r="AS1">
-        <v>1777.800048828125</v>
+        <v>1729.760009765625</v>
       </c>
       <c r="AT1">
-        <v>1712.890014648438</v>
+        <v>1739.890014648438</v>
       </c>
       <c r="AU1">
-        <v>1729.760009765625</v>
+        <v>1787.68994140625</v>
       </c>
       <c r="AV1">
-        <v>1739.890014648438</v>
+        <v>1719.989990234375</v>
       </c>
       <c r="AW1">
-        <v>1787.68994140625</v>
+        <v>1704.160034179688</v>
       </c>
       <c r="AX1">
-        <v>1719.989990234375</v>
+        <v>1660.4599609375</v>
       </c>
       <c r="AY1">
-        <v>1704.160034179688</v>
+        <v>1692.420043945312</v>
       </c>
       <c r="AZ1">
-        <v>1660.4599609375</v>
+        <v>1609.4599609375</v>
       </c>
       <c r="BA1">
-        <v>1692.420043945312</v>
+        <v>1581.819946289062</v>
       </c>
       <c r="BB1">
-        <v>1609.4599609375</v>
+        <v>1487.329956054688</v>
       </c>
       <c r="BC1">
-        <v>1581.819946289062</v>
+        <v>1482.329956054688</v>
       </c>
       <c r="BD1">
-        <v>1487.329956054688</v>
+        <v>1403.339965820312</v>
       </c>
       <c r="BE1">
-        <v>1482.329956054688</v>
+        <v>1394.829956054688</v>
       </c>
       <c r="BF1">
-        <v>1403.339965820312</v>
+        <v>1299.300048828125</v>
       </c>
       <c r="BG1">
-        <v>1394.829956054688</v>
+        <v>1371.119995117188</v>
       </c>
       <c r="BH1">
-        <v>1299.300048828125</v>
-      </c>
-      <c r="BI1">
-        <v>1371.119995117188</v>
-      </c>
-    </row>
-    <row r="2" spans="1:61">
+        <v>1365.380004882812</v>
+      </c>
+    </row>
+    <row r="2" spans="1:60">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>497.7602233886719</v>
+        <v>461.8917236328125</v>
       </c>
       <c r="C2">
-        <v>463.3612670898438</v>
+        <v>532.868896484375</v>
       </c>
       <c r="D2">
-        <v>461.8917236328125</v>
+        <v>544.6651611328125</v>
       </c>
       <c r="E2">
-        <v>532.868896484375</v>
+        <v>527.05078125</v>
       </c>
       <c r="F2">
-        <v>544.6651611328125</v>
+        <v>548.3839721679688</v>
       </c>
       <c r="G2">
-        <v>527.05078125</v>
+        <v>519.0033569335938</v>
       </c>
       <c r="H2">
-        <v>548.3839721679688</v>
+        <v>451.3750915527344</v>
       </c>
       <c r="I2">
-        <v>519.0033569335938</v>
+        <v>434.1606140136719</v>
       </c>
       <c r="J2">
-        <v>451.3750915527344</v>
+        <v>438.1993408203125</v>
       </c>
       <c r="K2">
-        <v>434.1606140136719</v>
+        <v>437.7894592285156</v>
       </c>
       <c r="L2">
-        <v>438.1993408203125</v>
+        <v>453.9542846679688</v>
       </c>
       <c r="M2">
-        <v>437.7894592285156</v>
+        <v>487.1336364746094</v>
       </c>
       <c r="N2">
-        <v>453.9542846679688</v>
+        <v>508.63671875</v>
       </c>
       <c r="O2">
-        <v>487.1336364746094</v>
+        <v>535.8380126953125</v>
       </c>
       <c r="P2">
-        <v>508.63671875</v>
+        <v>496.0007934570312</v>
       </c>
       <c r="Q2">
-        <v>535.8380126953125</v>
+        <v>461.9417114257812</v>
       </c>
       <c r="R2">
-        <v>496.0007934570312</v>
+        <v>468.8994750976562</v>
       </c>
       <c r="S2">
-        <v>461.9417114257812</v>
+        <v>459.2925720214844</v>
       </c>
       <c r="T2">
-        <v>468.8994750976562</v>
+        <v>435.2402954101562</v>
       </c>
       <c r="U2">
-        <v>459.2925720214844</v>
+        <v>450.6053466796875</v>
       </c>
       <c r="V2">
-        <v>435.2402954101562</v>
+        <v>468.7295227050781</v>
       </c>
       <c r="W2">
-        <v>450.6053466796875</v>
+        <v>461.8517456054688</v>
       </c>
       <c r="X2">
-        <v>468.7295227050781</v>
+        <v>459.3025817871094</v>
       </c>
       <c r="Y2">
-        <v>461.8517456054688</v>
+        <v>450.4053955078125</v>
       </c>
       <c r="Z2">
-        <v>459.3025817871094</v>
+        <v>450.2954406738281</v>
       </c>
       <c r="AA2">
-        <v>450.4053955078125</v>
+        <v>448.7559509277344</v>
       </c>
       <c r="AB2">
-        <v>450.2954406738281</v>
+        <v>441.4283142089844</v>
       </c>
       <c r="AC2">
-        <v>448.7559509277344</v>
+        <v>467.3099670410156</v>
       </c>
       <c r="AD2">
-        <v>441.4283142089844</v>
+        <v>477.2999877929688</v>
       </c>
       <c r="AE2">
-        <v>467.3099670410156</v>
+        <v>482.2799987792969</v>
       </c>
       <c r="AF2">
-        <v>477.2999877929688</v>
+        <v>460.9299926757812</v>
       </c>
       <c r="AG2">
-        <v>482.2799987792969</v>
+        <v>447.1799926757812</v>
       </c>
       <c r="AH2">
-        <v>460.9299926757812</v>
+        <v>426.9400024414062</v>
       </c>
       <c r="AI2">
-        <v>447.1799926757812</v>
+        <v>411.9599914550781</v>
       </c>
       <c r="AJ2">
-        <v>426.9400024414062</v>
+        <v>416.9700012207031</v>
       </c>
       <c r="AK2">
-        <v>411.9599914550781</v>
+        <v>423.8699951171875</v>
       </c>
       <c r="AL2">
-        <v>416.9700012207031</v>
+        <v>441.3599853515625</v>
       </c>
       <c r="AM2">
-        <v>423.8699951171875</v>
+        <v>448.1700134277344</v>
       </c>
       <c r="AN2">
-        <v>441.3599853515625</v>
+        <v>464.6000061035156</v>
       </c>
       <c r="AO2">
-        <v>448.1700134277344</v>
+        <v>473.6900024414062</v>
       </c>
       <c r="AP2">
-        <v>464.6000061035156</v>
+        <v>450.3099975585938</v>
       </c>
       <c r="AQ2">
-        <v>473.6900024414062</v>
+        <v>456.8099975585938</v>
       </c>
       <c r="AR2">
-        <v>450.3099975585938</v>
+        <v>453.2300109863281</v>
       </c>
       <c r="AS2">
-        <v>456.8099975585938</v>
+        <v>453.4800109863281</v>
       </c>
       <c r="AT2">
-        <v>453.2300109863281</v>
+        <v>454.4599914550781</v>
       </c>
       <c r="AU2">
-        <v>453.4800109863281</v>
+        <v>462.5599975585938</v>
       </c>
       <c r="AV2">
-        <v>454.4599914550781</v>
+        <v>415.2900085449219</v>
       </c>
       <c r="AW2">
-        <v>462.5599975585938</v>
+        <v>441.6400146484375</v>
       </c>
       <c r="AX2">
-        <v>415.2900085449219</v>
+        <v>411.0400085449219</v>
       </c>
       <c r="AY2">
-        <v>441.6400146484375</v>
+        <v>405.4200134277344</v>
       </c>
       <c r="AZ2">
-        <v>411.0400085449219</v>
+        <v>393.3099975585938</v>
       </c>
       <c r="BA2">
-        <v>405.4200134277344</v>
+        <v>397.2799987792969</v>
       </c>
       <c r="BB2">
-        <v>393.3099975585938</v>
+        <v>386.9400024414062</v>
       </c>
       <c r="BC2">
-        <v>397.2799987792969</v>
+        <v>380.7099914550781</v>
       </c>
       <c r="BD2">
-        <v>386.9400024414062</v>
+        <v>364.1000061035156</v>
       </c>
       <c r="BE2">
-        <v>380.7099914550781</v>
+        <v>356.4500122070312</v>
       </c>
       <c r="BF2">
-        <v>364.1000061035156</v>
+        <v>332</v>
       </c>
       <c r="BG2">
-        <v>356.4500122070312</v>
+        <v>352.2099914550781</v>
       </c>
       <c r="BH2">
-        <v>332</v>
-      </c>
-      <c r="BI2">
-        <v>352.2099914550781</v>
-      </c>
-    </row>
-    <row r="3" spans="1:61">
+        <v>364.3200073242188</v>
+      </c>
+    </row>
+    <row r="3" spans="1:60">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>303.756103515625</v>
+        <v>300.1600036621094</v>
       </c>
       <c r="C3">
-        <v>297.7294006347656</v>
+        <v>310.5099792480469</v>
       </c>
       <c r="D3">
-        <v>300.1600036621094</v>
+        <v>312.8999938964844</v>
       </c>
       <c r="E3">
-        <v>310.5099792480469</v>
+        <v>307.5400085449219</v>
       </c>
       <c r="F3">
-        <v>312.8999938964844</v>
+        <v>308.7300109863281</v>
       </c>
       <c r="G3">
-        <v>307.5400085449219</v>
+        <v>302.3900146484375</v>
       </c>
       <c r="H3">
-        <v>308.7300109863281</v>
+        <v>302.989990234375</v>
       </c>
       <c r="I3">
-        <v>302.3900146484375</v>
+        <v>298.3099975585938</v>
       </c>
       <c r="J3">
-        <v>302.989990234375</v>
+        <v>314.9500122070312</v>
       </c>
       <c r="K3">
-        <v>298.3099975585938</v>
+        <v>323.9200134277344</v>
       </c>
       <c r="L3">
-        <v>314.9500122070312</v>
+        <v>330.2099914550781</v>
       </c>
       <c r="M3">
-        <v>323.9200134277344</v>
+        <v>342.9200134277344</v>
       </c>
       <c r="N3">
-        <v>330.2099914550781</v>
+        <v>341.6700134277344</v>
       </c>
       <c r="O3">
-        <v>342.9200134277344</v>
+        <v>347.1900024414062</v>
       </c>
       <c r="P3">
-        <v>341.6700134277344</v>
+        <v>350.0499877929688</v>
       </c>
       <c r="Q3">
-        <v>347.1900024414062</v>
+        <v>346.260009765625</v>
       </c>
       <c r="R3">
-        <v>350.0499877929688</v>
+        <v>341.510009765625</v>
       </c>
       <c r="S3">
-        <v>346.260009765625</v>
+        <v>348.8599853515625</v>
       </c>
       <c r="T3">
-        <v>341.510009765625</v>
+        <v>346</v>
       </c>
       <c r="U3">
-        <v>348.8599853515625</v>
+        <v>340.4100036621094</v>
       </c>
       <c r="V3">
-        <v>346</v>
+        <v>348.0299987792969</v>
       </c>
       <c r="W3">
-        <v>340.4100036621094</v>
+        <v>346.5899963378906</v>
       </c>
       <c r="X3">
-        <v>348.0299987792969</v>
+        <v>352.3599853515625</v>
       </c>
       <c r="Y3">
-        <v>346.5899963378906</v>
+        <v>358.9200134277344</v>
       </c>
       <c r="Z3">
-        <v>352.3599853515625</v>
+        <v>361.989990234375</v>
       </c>
       <c r="AA3">
-        <v>358.9200134277344</v>
+        <v>366.0899963378906</v>
       </c>
       <c r="AB3">
-        <v>361.989990234375</v>
+        <v>370.6900024414062</v>
       </c>
       <c r="AC3">
-        <v>366.0899963378906</v>
+        <v>370.7200012207031</v>
       </c>
       <c r="AD3">
-        <v>370.6900024414062</v>
+        <v>382.8500061035156</v>
       </c>
       <c r="AE3">
-        <v>370.7200012207031</v>
+        <v>388.9500122070312</v>
       </c>
       <c r="AF3">
-        <v>382.8500061035156</v>
+        <v>385.4299926757812</v>
       </c>
       <c r="AG3">
-        <v>388.9500122070312</v>
+        <v>390.4200134277344</v>
       </c>
       <c r="AH3">
-        <v>385.4299926757812</v>
+        <v>382.9500122070312</v>
       </c>
       <c r="AI3">
-        <v>390.4200134277344</v>
+        <v>397.0400085449219</v>
       </c>
       <c r="AJ3">
-        <v>382.9500122070312</v>
+        <v>403.2799987792969</v>
       </c>
       <c r="AK3">
-        <v>397.0400085449219</v>
+        <v>412.5299987792969</v>
       </c>
       <c r="AL3">
-        <v>403.2799987792969</v>
+        <v>413.2799987792969</v>
       </c>
       <c r="AM3">
-        <v>412.5299987792969</v>
+        <v>393.2699890136719</v>
       </c>
       <c r="AN3">
-        <v>413.2799987792969</v>
+        <v>377.1400146484375</v>
       </c>
       <c r="AO3">
-        <v>393.2699890136719</v>
+        <v>375.8399963378906</v>
       </c>
       <c r="AP3">
-        <v>377.1400146484375</v>
+        <v>382.8599853515625</v>
       </c>
       <c r="AQ3">
-        <v>375.8399963378906</v>
+        <v>387.1799926757812</v>
       </c>
       <c r="AR3">
-        <v>382.8599853515625</v>
+        <v>389.5700073242188</v>
       </c>
       <c r="AS3">
-        <v>387.1799926757812</v>
+        <v>387.7200012207031</v>
       </c>
       <c r="AT3">
-        <v>389.5700073242188</v>
+        <v>387.6099853515625</v>
       </c>
       <c r="AU3">
-        <v>387.7200012207031</v>
+        <v>408.4599914550781</v>
       </c>
       <c r="AV3">
-        <v>387.6099853515625</v>
+        <v>406.2999877929688</v>
       </c>
       <c r="AW3">
-        <v>408.4599914550781</v>
+        <v>419.3299865722656</v>
       </c>
       <c r="AX3">
-        <v>406.2999877929688</v>
+        <v>419.2200012207031</v>
       </c>
       <c r="AY3">
-        <v>419.3299865722656</v>
+        <v>424.1000061035156</v>
       </c>
       <c r="AZ3">
-        <v>419.2200012207031</v>
+        <v>443.7999877929688</v>
       </c>
       <c r="BA3">
-        <v>424.1000061035156</v>
+        <v>433.75</v>
       </c>
       <c r="BB3">
-        <v>443.7999877929688</v>
+        <v>436</v>
       </c>
       <c r="BC3">
-        <v>433.75</v>
+        <v>456.4599914550781</v>
       </c>
       <c r="BD3">
-        <v>436</v>
+        <v>459.7799987792969</v>
       </c>
       <c r="BE3">
-        <v>456.4599914550781</v>
+        <v>444.0599975585938</v>
       </c>
       <c r="BF3">
-        <v>459.7799987792969</v>
+        <v>444.7099914550781</v>
       </c>
       <c r="BG3">
-        <v>444.0599975585938</v>
+        <v>433.3099975585938</v>
       </c>
       <c r="BH3">
-        <v>444.7099914550781</v>
-      </c>
-      <c r="BI3">
-        <v>433.3099975585938</v>
-      </c>
-    </row>
-    <row r="4" spans="1:61">
+        <v>433.4200134277344</v>
+      </c>
+    </row>
+    <row r="4" spans="1:60">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>311.4970703125</v>
+        <v>307.8769836425781</v>
       </c>
       <c r="C4">
-        <v>305.2142639160156</v>
+        <v>313.2223510742188</v>
       </c>
       <c r="D4">
-        <v>307.8769836425781</v>
+        <v>315.6058349609375</v>
       </c>
       <c r="E4">
-        <v>313.2223510742188</v>
+        <v>306.1915893554688</v>
       </c>
       <c r="F4">
-        <v>315.6058349609375</v>
+        <v>311.75634765625</v>
       </c>
       <c r="G4">
-        <v>306.1915893554688</v>
+        <v>296.9369506835938</v>
       </c>
       <c r="H4">
-        <v>311.75634765625</v>
+        <v>298.432861328125</v>
       </c>
       <c r="I4">
-        <v>296.9369506835938</v>
+        <v>297.3857421875</v>
       </c>
       <c r="J4">
-        <v>298.432861328125</v>
+        <v>319.4453125</v>
       </c>
       <c r="K4">
-        <v>297.3857421875</v>
+        <v>335.5013732910156</v>
       </c>
       <c r="L4">
-        <v>319.4453125</v>
+        <v>347.2990417480469</v>
       </c>
       <c r="M4">
-        <v>335.5013732910156</v>
+        <v>355.3968811035156</v>
       </c>
       <c r="N4">
-        <v>347.2990417480469</v>
+        <v>354.4494934082031</v>
       </c>
       <c r="O4">
-        <v>355.3968811035156</v>
+        <v>357.2019348144531</v>
       </c>
       <c r="P4">
-        <v>354.4494934082031</v>
+        <v>365.2099914550781</v>
       </c>
       <c r="Q4">
-        <v>357.2019348144531</v>
+        <v>360.75</v>
       </c>
       <c r="R4">
-        <v>365.2099914550781</v>
+        <v>358.2300109863281</v>
       </c>
       <c r="S4">
-        <v>360.75</v>
+        <v>360.7200012207031</v>
       </c>
       <c r="T4">
-        <v>358.2300109863281</v>
+        <v>362.5199890136719</v>
       </c>
       <c r="U4">
-        <v>360.7200012207031</v>
+        <v>354.8800048828125</v>
       </c>
       <c r="V4">
-        <v>362.5199890136719</v>
+        <v>362.2699890136719</v>
       </c>
       <c r="W4">
-        <v>354.8800048828125</v>
+        <v>363.5400085449219</v>
       </c>
       <c r="X4">
-        <v>362.2699890136719</v>
+        <v>368.8299865722656</v>
       </c>
       <c r="Y4">
-        <v>363.5400085449219</v>
+        <v>373.3200073242188</v>
       </c>
       <c r="Z4">
-        <v>368.8299865722656</v>
+        <v>383</v>
       </c>
       <c r="AA4">
-        <v>373.3200073242188</v>
+        <v>387</v>
       </c>
       <c r="AB4">
-        <v>383</v>
+        <v>387.7099914550781</v>
       </c>
       <c r="AC4">
-        <v>387</v>
+        <v>388.8999938964844</v>
       </c>
       <c r="AD4">
-        <v>387.7099914550781</v>
+        <v>397.7699890136719</v>
       </c>
       <c r="AE4">
-        <v>388.8999938964844</v>
+        <v>399.4400024414062</v>
       </c>
       <c r="AF4">
-        <v>397.7699890136719</v>
+        <v>392.4200134277344</v>
       </c>
       <c r="AG4">
-        <v>399.4400024414062</v>
+        <v>395.9299926757812</v>
       </c>
       <c r="AH4">
-        <v>392.4200134277344</v>
+        <v>396.4500122070312</v>
       </c>
       <c r="AI4">
-        <v>395.9299926757812</v>
+        <v>410.8399963378906</v>
       </c>
       <c r="AJ4">
-        <v>396.4500122070312</v>
+        <v>413.9200134277344</v>
       </c>
       <c r="AK4">
-        <v>410.8399963378906</v>
+        <v>421.9599914550781</v>
       </c>
       <c r="AL4">
-        <v>413.9200134277344</v>
+        <v>424.8900146484375</v>
       </c>
       <c r="AM4">
-        <v>421.9599914550781</v>
+        <v>402.3800048828125</v>
       </c>
       <c r="AN4">
-        <v>424.8900146484375</v>
+        <v>389.6799926757812</v>
       </c>
       <c r="AO4">
-        <v>402.3800048828125</v>
+        <v>388.3800048828125</v>
       </c>
       <c r="AP4">
-        <v>389.6799926757812</v>
+        <v>390.9500122070312</v>
       </c>
       <c r="AQ4">
-        <v>388.3800048828125</v>
+        <v>393.5199890136719</v>
       </c>
       <c r="AR4">
-        <v>390.9500122070312</v>
+        <v>389.4400024414062</v>
       </c>
       <c r="AS4">
-        <v>393.5199890136719</v>
+        <v>392.0299987792969</v>
       </c>
       <c r="AT4">
-        <v>389.4400024414062</v>
+        <v>395.4200134277344</v>
       </c>
       <c r="AU4">
-        <v>392.0299987792969</v>
+        <v>420.1499938964844</v>
       </c>
       <c r="AV4">
-        <v>395.4200134277344</v>
+        <v>422.3299865722656</v>
       </c>
       <c r="AW4">
-        <v>420.1499938964844</v>
+        <v>433.4700012207031</v>
       </c>
       <c r="AX4">
-        <v>422.3299865722656</v>
+        <v>432.3599853515625</v>
       </c>
       <c r="AY4">
-        <v>433.4700012207031</v>
+        <v>442.260009765625</v>
       </c>
       <c r="AZ4">
-        <v>432.3599853515625</v>
+        <v>463.3399963378906</v>
       </c>
       <c r="BA4">
-        <v>442.260009765625</v>
+        <v>455.0299987792969</v>
       </c>
       <c r="BB4">
-        <v>463.3399963378906</v>
+        <v>458.8099975585938</v>
       </c>
       <c r="BC4">
-        <v>455.0299987792969</v>
+        <v>476.9800109863281</v>
       </c>
       <c r="BD4">
-        <v>458.8099975585938</v>
+        <v>484.9200134277344</v>
       </c>
       <c r="BE4">
-        <v>476.9800109863281</v>
+        <v>476.9200134277344</v>
       </c>
       <c r="BF4">
-        <v>484.9200134277344</v>
+        <v>478.0700073242188</v>
       </c>
       <c r="BG4">
-        <v>476.9200134277344</v>
+        <v>473.6900024414062</v>
       </c>
       <c r="BH4">
-        <v>478.0700073242188</v>
-      </c>
-      <c r="BI4">
-        <v>473.6900024414062</v>
-      </c>
-    </row>
-    <row r="5" spans="1:61">
+        <v>475.0400085449219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:60">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>54.67909622192383</v>
+        <v>55.77407073974609</v>
       </c>
       <c r="C5">
-        <v>53.68366622924805</v>
+        <v>55.69443893432617</v>
       </c>
       <c r="D5">
-        <v>55.77407073974609</v>
+        <v>56.80932235717773</v>
       </c>
       <c r="E5">
-        <v>55.69443893432617</v>
+        <v>55.21663284301758</v>
       </c>
       <c r="F5">
-        <v>56.80932235717773</v>
+        <v>54.8383674621582</v>
       </c>
       <c r="G5">
-        <v>55.21663284301758</v>
+        <v>53.56421279907227</v>
       </c>
       <c r="H5">
-        <v>54.8383674621582</v>
+        <v>55.78402709960938</v>
       </c>
       <c r="I5">
-        <v>53.56421279907227</v>
+        <v>55.65462112426758</v>
       </c>
       <c r="J5">
-        <v>55.78402709960938</v>
+        <v>58.38210678100586</v>
       </c>
       <c r="K5">
-        <v>55.65462112426758</v>
+        <v>58.79023361206055</v>
       </c>
       <c r="L5">
-        <v>58.38210678100586</v>
+        <v>58.28256225585938</v>
       </c>
       <c r="M5">
-        <v>58.79023361206055</v>
+        <v>57.43644714355469</v>
       </c>
       <c r="N5">
-        <v>58.28256225585938</v>
+        <v>58.09342956542969</v>
       </c>
       <c r="O5">
-        <v>57.43644714355469</v>
+        <v>58.77032470703125</v>
       </c>
       <c r="P5">
-        <v>58.09342956542969</v>
+        <v>59.52685165405273</v>
       </c>
       <c r="Q5">
-        <v>58.77032470703125</v>
+        <v>59.81552886962891</v>
       </c>
       <c r="R5">
-        <v>59.52685165405273</v>
+        <v>61.23899841308594</v>
       </c>
       <c r="S5">
-        <v>59.81552886962891</v>
+        <v>61.02000045776367</v>
       </c>
       <c r="T5">
-        <v>61.23899841308594</v>
+        <v>59.8354377746582</v>
       </c>
       <c r="U5">
+        <v>58.1431999206543</v>
+      </c>
+      <c r="V5">
+        <v>58.35224151611328</v>
+      </c>
+      <c r="W5">
+        <v>58.89972686767578</v>
+      </c>
+      <c r="X5">
+        <v>58.83004760742188</v>
+      </c>
+      <c r="Y5">
+        <v>59.90511703491211</v>
+      </c>
+      <c r="Z5">
+        <v>60.67160034179688</v>
+      </c>
+      <c r="AA5">
+        <v>60.63178253173828</v>
+      </c>
+      <c r="AB5">
+        <v>60.33315277099609</v>
+      </c>
+      <c r="AC5">
+        <v>59.7657585144043</v>
+      </c>
+      <c r="AD5">
+        <v>60.37297058105469</v>
+      </c>
+      <c r="AE5">
         <v>61.02000045776367</v>
       </c>
-      <c r="V5">
-        <v>59.8354377746582</v>
-      </c>
-      <c r="W5">
-        <v>58.1431999206543</v>
-      </c>
-      <c r="X5">
-        <v>58.35224151611328</v>
-      </c>
-      <c r="Y5">
-        <v>58.89972686767578</v>
-      </c>
-      <c r="Z5">
-        <v>58.83004760742188</v>
-      </c>
-      <c r="AA5">
-        <v>59.90511703491211</v>
-      </c>
-      <c r="AB5">
-        <v>60.67160034179688</v>
-      </c>
-      <c r="AC5">
-        <v>60.63178253173828</v>
-      </c>
-      <c r="AD5">
-        <v>60.33315277099609</v>
-      </c>
-      <c r="AE5">
-        <v>59.7657585144043</v>
-      </c>
       <c r="AF5">
-        <v>60.37297058105469</v>
+        <v>61.15999984741211</v>
       </c>
       <c r="AG5">
-        <v>61.02000045776367</v>
+        <v>61.45999908447266</v>
       </c>
       <c r="AH5">
-        <v>61.15999984741211</v>
+        <v>61.77999877929688</v>
       </c>
       <c r="AI5">
-        <v>61.45999908447266</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="AJ5">
-        <v>61.77999877929688</v>
+        <v>59.36000061035156</v>
       </c>
       <c r="AK5">
-        <v>63.52000045776367</v>
+        <v>59.29000091552734</v>
       </c>
       <c r="AL5">
-        <v>59.36000061035156</v>
+        <v>58.84000015258789</v>
       </c>
       <c r="AM5">
-        <v>59.29000091552734</v>
+        <v>57.25</v>
       </c>
       <c r="AN5">
-        <v>58.84000015258789</v>
+        <v>56.31000137329102</v>
       </c>
       <c r="AO5">
-        <v>57.25</v>
+        <v>57.36000061035156</v>
       </c>
       <c r="AP5">
-        <v>56.31000137329102</v>
+        <v>58.04999923706055</v>
       </c>
       <c r="AQ5">
-        <v>57.36000061035156</v>
+        <v>56.86000061035156</v>
       </c>
       <c r="AR5">
-        <v>58.04999923706055</v>
+        <v>56.09999847412109</v>
       </c>
       <c r="AS5">
-        <v>56.86000061035156</v>
+        <v>54.93999862670898</v>
       </c>
       <c r="AT5">
-        <v>56.09999847412109</v>
+        <v>55.31999969482422</v>
       </c>
       <c r="AU5">
-        <v>54.93999862670898</v>
+        <v>57.84000015258789</v>
       </c>
       <c r="AV5">
-        <v>55.31999969482422</v>
+        <v>58.08000183105469</v>
       </c>
       <c r="AW5">
-        <v>57.84000015258789</v>
+        <v>58.31000137329102</v>
       </c>
       <c r="AX5">
-        <v>58.08000183105469</v>
+        <v>58.33000183105469</v>
       </c>
       <c r="AY5">
-        <v>58.31000137329102</v>
+        <v>58.20999908447266</v>
       </c>
       <c r="AZ5">
-        <v>58.33000183105469</v>
+        <v>60.27999877929688</v>
       </c>
       <c r="BA5">
-        <v>58.20999908447266</v>
+        <v>60.11000061035156</v>
       </c>
       <c r="BB5">
-        <v>60.27999877929688</v>
+        <v>61.13000106811523</v>
       </c>
       <c r="BC5">
-        <v>60.11000061035156</v>
+        <v>61.65000152587891</v>
       </c>
       <c r="BD5">
-        <v>61.13000106811523</v>
+        <v>61.40999984741211</v>
       </c>
       <c r="BE5">
-        <v>61.65000152587891</v>
+        <v>60.66999816894531</v>
       </c>
       <c r="BF5">
-        <v>61.40999984741211</v>
+        <v>62.38000106811523</v>
       </c>
       <c r="BG5">
-        <v>60.66999816894531</v>
+        <v>62.72000122070312</v>
       </c>
       <c r="BH5">
-        <v>62.38000106811523</v>
-      </c>
-      <c r="BI5">
-        <v>62.72000122070312</v>
-      </c>
-    </row>
-    <row r="6" spans="1:61">
+        <v>62.91999816894531</v>
+      </c>
+    </row>
+    <row r="6" spans="1:60">
       <c r="A6" t="s">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>206.7228088378906</v>
+        <v>205.7181396484375</v>
       </c>
       <c r="C6">
-        <v>204.7632141113281</v>
+        <v>209.4881286621094</v>
       </c>
       <c r="D6">
-        <v>205.7181396484375</v>
+        <v>210.5624237060547</v>
       </c>
       <c r="E6">
-        <v>209.4881286621094</v>
+        <v>205.1014099121094</v>
       </c>
       <c r="F6">
-        <v>210.5624237060547</v>
+        <v>204.8029937744141</v>
       </c>
       <c r="G6">
-        <v>205.1014099121094</v>
+        <v>201.4806365966797</v>
       </c>
       <c r="H6">
-        <v>204.8029937744141</v>
+        <v>204.4349517822266</v>
       </c>
       <c r="I6">
-        <v>201.4806365966797</v>
+        <v>202.8334503173828</v>
       </c>
       <c r="J6">
-        <v>204.4349517822266</v>
+        <v>214.3821563720703</v>
       </c>
       <c r="K6">
-        <v>202.8334503173828</v>
+        <v>223.1754760742188</v>
       </c>
       <c r="L6">
-        <v>214.3821563720703</v>
+        <v>224.3890380859375</v>
       </c>
       <c r="M6">
-        <v>223.1754760742188</v>
+        <v>231.3819274902344</v>
       </c>
       <c r="N6">
-        <v>224.3890380859375</v>
+        <v>232.3766479492188</v>
       </c>
       <c r="O6">
-        <v>231.3819274902344</v>
+        <v>239.2800140380859</v>
       </c>
       <c r="P6">
-        <v>232.3766479492188</v>
+        <v>243.4900054931641</v>
       </c>
       <c r="Q6">
-        <v>239.2800140380859</v>
+        <v>242.2899932861328</v>
       </c>
       <c r="R6">
-        <v>243.4900054931641</v>
+        <v>240</v>
       </c>
       <c r="S6">
-        <v>242.2899932861328</v>
+        <v>242.8699951171875</v>
       </c>
       <c r="T6">
-        <v>240</v>
+        <v>241.9600067138672</v>
       </c>
       <c r="U6">
-        <v>242.8699951171875</v>
+        <v>236.8999938964844</v>
       </c>
       <c r="V6">
-        <v>241.9600067138672</v>
+        <v>242.2299957275391</v>
       </c>
       <c r="W6">
-        <v>236.8999938964844</v>
+        <v>239.8099975585938</v>
       </c>
       <c r="X6">
-        <v>242.2299957275391</v>
+        <v>244.0099945068359</v>
       </c>
       <c r="Y6">
-        <v>239.8099975585938</v>
+        <v>246.5800018310547</v>
       </c>
       <c r="Z6">
-        <v>244.0099945068359</v>
+        <v>252.0200042724609</v>
       </c>
       <c r="AA6">
-        <v>246.5800018310547</v>
+        <v>256.0899963378906</v>
       </c>
       <c r="AB6">
-        <v>252.0200042724609</v>
+        <v>254.6600036621094</v>
       </c>
       <c r="AC6">
-        <v>256.0899963378906</v>
+        <v>255.0899963378906</v>
       </c>
       <c r="AD6">
-        <v>254.6600036621094</v>
+        <v>259.1400146484375</v>
       </c>
       <c r="AE6">
-        <v>255.0899963378906</v>
+        <v>260.7799987792969</v>
       </c>
       <c r="AF6">
-        <v>259.1400146484375</v>
+        <v>258.510009765625</v>
       </c>
       <c r="AG6">
-        <v>260.7799987792969</v>
+        <v>259.4700012207031</v>
       </c>
       <c r="AH6">
-        <v>258.510009765625</v>
+        <v>257.0599975585938</v>
       </c>
       <c r="AI6">
-        <v>259.4700012207031</v>
+        <v>264.9299926757812</v>
       </c>
       <c r="AJ6">
-        <v>257.0599975585938</v>
+        <v>264.6300048828125</v>
       </c>
       <c r="AK6">
-        <v>264.9299926757812</v>
+        <v>274.2099914550781</v>
       </c>
       <c r="AL6">
-        <v>264.6300048828125</v>
+        <v>273.1300048828125</v>
       </c>
       <c r="AM6">
-        <v>274.2099914550781</v>
+        <v>261.75</v>
       </c>
       <c r="AN6">
-        <v>273.1300048828125</v>
+        <v>256.7799987792969</v>
       </c>
       <c r="AO6">
-        <v>261.75</v>
+        <v>256.4800109863281</v>
       </c>
       <c r="AP6">
-        <v>256.7799987792969</v>
+        <v>255.8699951171875</v>
       </c>
       <c r="AQ6">
-        <v>256.4800109863281</v>
+        <v>255.75</v>
       </c>
       <c r="AR6">
-        <v>255.8699951171875</v>
+        <v>253.5500030517578</v>
       </c>
       <c r="AS6">
-        <v>255.75</v>
+        <v>252.25</v>
       </c>
       <c r="AT6">
-        <v>253.5500030517578</v>
+        <v>255.3099975585938</v>
       </c>
       <c r="AU6">
-        <v>252.25</v>
+        <v>264.2300109863281</v>
       </c>
       <c r="AV6">
-        <v>255.3099975585938</v>
+        <v>264.5799865722656</v>
       </c>
       <c r="AW6">
-        <v>264.2300109863281</v>
+        <v>269.7200012207031</v>
       </c>
       <c r="AX6">
-        <v>264.5799865722656</v>
+        <v>269.7900085449219</v>
       </c>
       <c r="AY6">
-        <v>269.7200012207031</v>
+        <v>271.6199951171875</v>
       </c>
       <c r="AZ6">
-        <v>269.7900085449219</v>
+        <v>281.6000061035156</v>
       </c>
       <c r="BA6">
-        <v>271.6199951171875</v>
+        <v>278.1799926757812</v>
       </c>
       <c r="BB6">
-        <v>281.6000061035156</v>
+        <v>281.4700012207031</v>
       </c>
       <c r="BC6">
-        <v>278.1799926757812</v>
+        <v>292.7300109863281</v>
       </c>
       <c r="BD6">
-        <v>281.4700012207031</v>
+        <v>297.2900085449219</v>
       </c>
       <c r="BE6">
-        <v>292.7300109863281</v>
+        <v>289.2000122070312</v>
       </c>
       <c r="BF6">
-        <v>297.2900085449219</v>
+        <v>293.1700134277344</v>
       </c>
       <c r="BG6">
-        <v>289.2000122070312</v>
+        <v>290.5499877929688</v>
       </c>
       <c r="BH6">
-        <v>293.1700134277344</v>
-      </c>
-      <c r="BI6">
-        <v>290.5499877929688</v>
-      </c>
-    </row>
-    <row r="7" spans="1:61">
+        <v>291.0299987792969</v>
+      </c>
+    </row>
+    <row r="7" spans="1:60">
       <c r="A7" t="s">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>34.7400016784668</v>
+        <v>36.70000076293945</v>
       </c>
       <c r="C7">
-        <v>34.93000030517578</v>
+        <v>36.33000183105469</v>
       </c>
       <c r="D7">
-        <v>36.70000076293945</v>
+        <v>37.31999969482422</v>
       </c>
       <c r="E7">
-        <v>36.33000183105469</v>
+        <v>36.86999893188477</v>
       </c>
       <c r="F7">
-        <v>37.31999969482422</v>
+        <v>35.79999923706055</v>
       </c>
       <c r="G7">
-        <v>36.86999893188477</v>
+        <v>34.65999984741211</v>
       </c>
       <c r="H7">
-        <v>35.79999923706055</v>
+        <v>36.52999877929688</v>
       </c>
       <c r="I7">
-        <v>34.65999984741211</v>
+        <v>37.63000106811523</v>
       </c>
       <c r="J7">
-        <v>36.52999877929688</v>
+        <v>41.02000045776367</v>
       </c>
       <c r="K7">
-        <v>37.63000106811523</v>
+        <v>40.61999893188477</v>
       </c>
       <c r="L7">
-        <v>41.02000045776367</v>
+        <v>39.97000122070312</v>
       </c>
       <c r="M7">
-        <v>40.61999893188477</v>
+        <v>40</v>
       </c>
       <c r="N7">
-        <v>39.97000122070312</v>
+        <v>40.47000122070312</v>
       </c>
       <c r="O7">
-        <v>40</v>
+        <v>41.58000183105469</v>
       </c>
       <c r="P7">
-        <v>40.47000122070312</v>
+        <v>42.36999893188477</v>
       </c>
       <c r="Q7">
-        <v>41.58000183105469</v>
+        <v>43.45000076293945</v>
       </c>
       <c r="R7">
-        <v>42.36999893188477</v>
+        <v>44.38999938964844</v>
       </c>
       <c r="S7">
-        <v>43.45000076293945</v>
+        <v>43.38999938964844</v>
       </c>
       <c r="T7">
-        <v>44.38999938964844</v>
+        <v>42.95999908447266</v>
       </c>
       <c r="U7">
-        <v>43.38999938964844</v>
+        <v>41.34999847412109</v>
       </c>
       <c r="V7">
-        <v>42.95999908447266</v>
+        <v>41.18999862670898</v>
       </c>
       <c r="W7">
-        <v>41.34999847412109</v>
+        <v>42.38000106811523</v>
       </c>
       <c r="X7">
-        <v>41.18999862670898</v>
+        <v>42.54000091552734</v>
       </c>
       <c r="Y7">
-        <v>42.38000106811523</v>
+        <v>43.15000152587891</v>
       </c>
       <c r="Z7">
-        <v>42.54000091552734</v>
+        <v>44.29999923706055</v>
       </c>
       <c r="AA7">
-        <v>43.15000152587891</v>
+        <v>44.70000076293945</v>
       </c>
       <c r="AB7">
-        <v>44.29999923706055</v>
+        <v>44.18000030517578</v>
       </c>
       <c r="AC7">
-        <v>44.70000076293945</v>
+        <v>42.77000045776367</v>
       </c>
       <c r="AD7">
-        <v>44.18000030517578</v>
+        <v>43.54999923706055</v>
       </c>
       <c r="AE7">
-        <v>42.77000045776367</v>
+        <v>44.84000015258789</v>
       </c>
       <c r="AF7">
-        <v>43.54999923706055</v>
+        <v>44.52999877929688</v>
       </c>
       <c r="AG7">
-        <v>44.84000015258789</v>
+        <v>44.72999954223633</v>
       </c>
       <c r="AH7">
-        <v>44.52999877929688</v>
+        <v>45.02999877929688</v>
       </c>
       <c r="AI7">
-        <v>44.72999954223633</v>
+        <v>47.40999984741211</v>
       </c>
       <c r="AJ7">
-        <v>45.02999877929688</v>
+        <v>44.79000091552734</v>
       </c>
       <c r="AK7">
-        <v>47.40999984741211</v>
+        <v>45.45999908447266</v>
       </c>
       <c r="AL7">
-        <v>44.79000091552734</v>
+        <v>44.86999893188477</v>
       </c>
       <c r="AM7">
-        <v>45.45999908447266</v>
+        <v>43.81000137329102</v>
       </c>
       <c r="AN7">
-        <v>44.86999893188477</v>
+        <v>42.29999923706055</v>
       </c>
       <c r="AO7">
+        <v>43.70000076293945</v>
+      </c>
+      <c r="AP7">
+        <v>43.68000030517578</v>
+      </c>
+      <c r="AQ7">
+        <v>42.7400016784668</v>
+      </c>
+      <c r="AR7">
+        <v>42.33000183105469</v>
+      </c>
+      <c r="AS7">
+        <v>42.18999862670898</v>
+      </c>
+      <c r="AT7">
+        <v>41.54000091552734</v>
+      </c>
+      <c r="AU7">
+        <v>43.34000015258789</v>
+      </c>
+      <c r="AV7">
+        <v>43.68000030517578</v>
+      </c>
+      <c r="AW7">
+        <v>43.84999847412109</v>
+      </c>
+      <c r="AX7">
+        <v>44.09999847412109</v>
+      </c>
+      <c r="AY7">
         <v>43.81000137329102</v>
       </c>
-      <c r="AP7">
-        <v>42.29999923706055</v>
-      </c>
-      <c r="AQ7">
-        <v>43.70000076293945</v>
-      </c>
-      <c r="AR7">
-        <v>43.68000030517578</v>
-      </c>
-      <c r="AS7">
-        <v>42.7400016784668</v>
-      </c>
-      <c r="AT7">
-        <v>42.33000183105469</v>
-      </c>
-      <c r="AU7">
-        <v>42.18999862670898</v>
-      </c>
-      <c r="AV7">
-        <v>41.54000091552734</v>
-      </c>
-      <c r="AW7">
-        <v>43.34000015258789</v>
-      </c>
-      <c r="AX7">
-        <v>43.68000030517578</v>
-      </c>
-      <c r="AY7">
-        <v>43.84999847412109</v>
-      </c>
       <c r="AZ7">
-        <v>44.09999847412109</v>
+        <v>45.47000122070312</v>
       </c>
       <c r="BA7">
-        <v>43.81000137329102</v>
+        <v>45.88000106811523</v>
       </c>
       <c r="BB7">
-        <v>45.47000122070312</v>
+        <v>46.84000015258789</v>
       </c>
       <c r="BC7">
-        <v>45.88000106811523</v>
+        <v>48.0099983215332</v>
       </c>
       <c r="BD7">
-        <v>46.84000015258789</v>
+        <v>47.36999893188477</v>
       </c>
       <c r="BE7">
-        <v>48.0099983215332</v>
+        <v>47.22999954223633</v>
       </c>
       <c r="BF7">
-        <v>47.36999893188477</v>
+        <v>49.15000152587891</v>
       </c>
       <c r="BG7">
-        <v>47.22999954223633</v>
+        <v>49.7599983215332</v>
       </c>
       <c r="BH7">
-        <v>49.15000152587891</v>
-      </c>
-      <c r="BI7">
-        <v>49.7599983215332</v>
-      </c>
-    </row>
-    <row r="8" spans="1:61">
+        <v>49.90000152587891</v>
+      </c>
+    </row>
+    <row r="8" spans="1:60">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>196.2903594970703</v>
+        <v>189.7976226806641</v>
       </c>
       <c r="C8">
-        <v>196.789794921875</v>
+        <v>194.8219909667969</v>
       </c>
       <c r="D8">
-        <v>189.7976226806641</v>
+        <v>200.5256195068359</v>
       </c>
       <c r="E8">
-        <v>194.8219909667969</v>
+        <v>206.4090423583984</v>
       </c>
       <c r="F8">
-        <v>200.5256195068359</v>
+        <v>211.7031097412109</v>
       </c>
       <c r="G8">
-        <v>206.4090423583984</v>
+        <v>218.9749755859375</v>
       </c>
       <c r="H8">
-        <v>211.7031097412109</v>
+        <v>218.7452392578125</v>
       </c>
       <c r="I8">
-        <v>218.9749755859375</v>
+        <v>223.7096862792969</v>
       </c>
       <c r="J8">
-        <v>218.7452392578125</v>
+        <v>217.3068389892578</v>
       </c>
       <c r="K8">
-        <v>223.7096862792969</v>
+        <v>217.2568969726562</v>
       </c>
       <c r="L8">
+        <v>223.8395233154297</v>
+      </c>
+      <c r="M8">
+        <v>225.0481872558594</v>
+      </c>
+      <c r="N8">
+        <v>224.9083404541016</v>
+      </c>
+      <c r="O8">
+        <v>224.7584991455078</v>
+      </c>
+      <c r="P8">
+        <v>219.4944000244141</v>
+      </c>
+      <c r="Q8">
+        <v>217.3168334960938</v>
+      </c>
+      <c r="R8">
+        <v>216.6076354980469</v>
+      </c>
+      <c r="S8">
+        <v>214.4800109863281</v>
+      </c>
+      <c r="T8">
+        <v>208.2469787597656</v>
+      </c>
+      <c r="U8">
+        <v>212.8118743896484</v>
+      </c>
+      <c r="V8">
+        <v>209.4256591796875</v>
+      </c>
+      <c r="W8">
+        <v>227.7251739501953</v>
+      </c>
+      <c r="X8">
         <v>217.3068389892578</v>
       </c>
-      <c r="M8">
-        <v>217.2568969726562</v>
-      </c>
-      <c r="N8">
-        <v>223.8395233154297</v>
-      </c>
-      <c r="O8">
-        <v>225.0481872558594</v>
-      </c>
-      <c r="P8">
-        <v>224.9083404541016</v>
-      </c>
-      <c r="Q8">
-        <v>224.7584991455078</v>
-      </c>
-      <c r="R8">
-        <v>219.4944000244141</v>
-      </c>
-      <c r="S8">
-        <v>217.3168334960938</v>
-      </c>
-      <c r="T8">
-        <v>216.6076354980469</v>
-      </c>
-      <c r="U8">
-        <v>214.4800109863281</v>
-      </c>
-      <c r="V8">
-        <v>208.2469787597656</v>
-      </c>
-      <c r="W8">
-        <v>212.8118743896484</v>
-      </c>
-      <c r="X8">
-        <v>209.4256591796875</v>
-      </c>
       <c r="Y8">
-        <v>227.7251739501953</v>
+        <v>220.5332336425781</v>
       </c>
       <c r="Z8">
-        <v>217.3068389892578</v>
+        <v>217.1969757080078</v>
       </c>
       <c r="AA8">
-        <v>220.5332336425781</v>
+        <v>224.1591796875</v>
       </c>
       <c r="AB8">
-        <v>217.1969757080078</v>
+        <v>228.1946563720703</v>
       </c>
       <c r="AC8">
-        <v>224.1591796875</v>
+        <v>230.1025238037109</v>
       </c>
       <c r="AD8">
-        <v>228.1946563720703</v>
+        <v>225.4776916503906</v>
       </c>
       <c r="AE8">
-        <v>230.1025238037109</v>
+        <v>223.4199981689453</v>
       </c>
       <c r="AF8">
-        <v>225.4776916503906</v>
+        <v>218.3600006103516</v>
       </c>
       <c r="AG8">
-        <v>223.4199981689453</v>
+        <v>218.2899932861328</v>
       </c>
       <c r="AH8">
-        <v>218.3600006103516</v>
+        <v>210.9600067138672</v>
       </c>
       <c r="AI8">
-        <v>218.2899932861328</v>
+        <v>212.1699981689453</v>
       </c>
       <c r="AJ8">
-        <v>210.9600067138672</v>
+        <v>213.8999938964844</v>
       </c>
       <c r="AK8">
-        <v>212.1699981689453</v>
+        <v>219.3399963378906</v>
       </c>
       <c r="AL8">
-        <v>213.8999938964844</v>
+        <v>222.2700042724609</v>
       </c>
       <c r="AM8">
-        <v>219.3399963378906</v>
+        <v>227.3800048828125</v>
       </c>
       <c r="AN8">
-        <v>222.2700042724609</v>
+        <v>228.8699951171875</v>
       </c>
       <c r="AO8">
-        <v>227.3800048828125</v>
+        <v>225.5099945068359</v>
       </c>
       <c r="AP8">
-        <v>228.8699951171875</v>
+        <v>224.5800018310547</v>
       </c>
       <c r="AQ8">
-        <v>225.5099945068359</v>
+        <v>225.0700073242188</v>
       </c>
       <c r="AR8">
-        <v>224.5800018310547</v>
+        <v>228.8600006103516</v>
       </c>
       <c r="AS8">
-        <v>225.0700073242188</v>
+        <v>227.2100067138672</v>
       </c>
       <c r="AT8">
-        <v>228.8600006103516</v>
+        <v>228.3800048828125</v>
       </c>
       <c r="AU8">
-        <v>227.2100067138672</v>
+        <v>230.8600006103516</v>
       </c>
       <c r="AV8">
-        <v>228.3800048828125</v>
+        <v>233.9499969482422</v>
       </c>
       <c r="AW8">
-        <v>230.8600006103516</v>
+        <v>238.8999938964844</v>
       </c>
       <c r="AX8">
-        <v>233.9499969482422</v>
+        <v>239.2400054931641</v>
       </c>
       <c r="AY8">
-        <v>238.8999938964844</v>
+        <v>237.4700012207031</v>
       </c>
       <c r="AZ8">
-        <v>239.2400054931641</v>
+        <v>230.4799957275391</v>
       </c>
       <c r="BA8">
-        <v>237.4700012207031</v>
+        <v>229.2799987792969</v>
       </c>
       <c r="BB8">
-        <v>230.4799957275391</v>
+        <v>226.3200073242188</v>
       </c>
       <c r="BC8">
-        <v>229.2799987792969</v>
+        <v>228.5200042724609</v>
       </c>
       <c r="BD8">
-        <v>226.3200073242188</v>
+        <v>221.3000030517578</v>
       </c>
       <c r="BE8">
-        <v>228.5200042724609</v>
+        <v>217.2299957275391</v>
       </c>
       <c r="BF8">
-        <v>221.3000030517578</v>
+        <v>214.1300048828125</v>
       </c>
       <c r="BG8">
-        <v>217.2299957275391</v>
+        <v>217.0899963378906</v>
       </c>
       <c r="BH8">
-        <v>214.1300048828125</v>
-      </c>
-      <c r="BI8">
-        <v>217.0899963378906</v>
-      </c>
-    </row>
-    <row r="9" spans="1:61">
+        <v>216.4700012207031</v>
+      </c>
+    </row>
+    <row r="9" spans="1:60">
       <c r="A9" t="s">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>389.0199584960938</v>
+        <v>387.6845092773438</v>
       </c>
       <c r="C9">
-        <v>395.8665161132812</v>
+        <v>374.7088623046875</v>
       </c>
       <c r="D9">
-        <v>387.6845092773438</v>
+        <v>373.0844116210938</v>
       </c>
       <c r="E9">
-        <v>374.7088623046875</v>
+        <v>372.5462646484375</v>
       </c>
       <c r="F9">
-        <v>373.0844116210938</v>
+        <v>375.8648986816406</v>
       </c>
       <c r="G9">
-        <v>372.5462646484375</v>
+        <v>381.1468811035156</v>
       </c>
       <c r="H9">
-        <v>375.8648986816406</v>
+        <v>384.6847534179688</v>
       </c>
       <c r="I9">
-        <v>381.1468811035156</v>
+        <v>383.0005187988281</v>
       </c>
       <c r="J9">
-        <v>384.6847534179688</v>
+        <v>374.3401184082031</v>
       </c>
       <c r="K9">
-        <v>383.0005187988281</v>
+        <v>374.3301391601562</v>
       </c>
       <c r="L9">
-        <v>374.3401184082031</v>
+        <v>368.8987426757812</v>
       </c>
       <c r="M9">
-        <v>374.3301391601562</v>
+        <v>368.7392883300781</v>
       </c>
       <c r="N9">
-        <v>368.8987426757812</v>
+        <v>369.0980224609375</v>
       </c>
       <c r="O9">
-        <v>368.7392883300781</v>
+        <v>363.2680053710938</v>
       </c>
       <c r="P9">
-        <v>369.0980224609375</v>
+        <v>366.6763305664062</v>
       </c>
       <c r="Q9">
-        <v>363.2680053710938</v>
+        <v>360.9857788085938</v>
       </c>
       <c r="R9">
-        <v>366.6763305664062</v>
+        <v>363.248046875</v>
       </c>
       <c r="S9">
-        <v>360.9857788085938</v>
+        <v>362.3411254882812</v>
       </c>
       <c r="T9">
-        <v>363.248046875</v>
+        <v>369.2873840332031</v>
       </c>
       <c r="U9">
-        <v>362.3411254882812</v>
+        <v>368.4004516601562</v>
       </c>
       <c r="V9">
-        <v>369.2873840332031</v>
+        <v>369.8853454589844</v>
       </c>
       <c r="W9">
-        <v>368.4004516601562</v>
+        <v>368.071533203125</v>
       </c>
       <c r="X9">
-        <v>369.8853454589844</v>
+        <v>368.6396179199219</v>
       </c>
       <c r="Y9">
-        <v>368.071533203125</v>
+        <v>364.6831359863281</v>
       </c>
       <c r="Z9">
-        <v>368.6396179199219</v>
+        <v>362.6799926757812</v>
       </c>
       <c r="AA9">
-        <v>364.6831359863281</v>
+        <v>364.9322814941406</v>
       </c>
       <c r="AB9">
-        <v>362.6799926757812</v>
+        <v>373.0644836425781</v>
       </c>
       <c r="AC9">
-        <v>364.9322814941406</v>
+        <v>368.0914916992188</v>
       </c>
       <c r="AD9">
-        <v>373.0644836425781</v>
+        <v>364.4140625</v>
       </c>
       <c r="AE9">
-        <v>368.0914916992188</v>
+        <v>365.6000061035156</v>
       </c>
       <c r="AF9">
-        <v>364.4140625</v>
+        <v>367.5599975585938</v>
       </c>
       <c r="AG9">
-        <v>365.6000061035156</v>
+        <v>375.2000122070312</v>
       </c>
       <c r="AH9">
-        <v>367.5599975585938</v>
+        <v>378.0499877929688</v>
       </c>
       <c r="AI9">
-        <v>375.2000122070312</v>
+        <v>377.9700012207031</v>
       </c>
       <c r="AJ9">
-        <v>378.0499877929688</v>
+        <v>378.9200134277344</v>
       </c>
       <c r="AK9">
-        <v>377.9700012207031</v>
+        <v>379.489990234375</v>
       </c>
       <c r="AL9">
-        <v>378.9200134277344</v>
+        <v>374.6199951171875</v>
       </c>
       <c r="AM9">
-        <v>379.489990234375</v>
+        <v>371.1300048828125</v>
       </c>
       <c r="AN9">
-        <v>374.6199951171875</v>
+        <v>362.010009765625</v>
       </c>
       <c r="AO9">
-        <v>371.1300048828125</v>
+        <v>360.3900146484375</v>
       </c>
       <c r="AP9">
-        <v>362.010009765625</v>
+        <v>362.3900146484375</v>
       </c>
       <c r="AQ9">
-        <v>360.3900146484375</v>
+        <v>363.0400085449219</v>
       </c>
       <c r="AR9">
-        <v>362.3900146484375</v>
+        <v>363.1600036621094</v>
       </c>
       <c r="AS9">
-        <v>363.0400085449219</v>
+        <v>363.2099914550781</v>
       </c>
       <c r="AT9">
-        <v>363.1600036621094</v>
+        <v>356.510009765625</v>
       </c>
       <c r="AU9">
-        <v>363.2099914550781</v>
+        <v>361.6400146484375</v>
       </c>
       <c r="AV9">
-        <v>356.510009765625</v>
+        <v>360.3800048828125</v>
       </c>
       <c r="AW9">
-        <v>361.6400146484375</v>
+        <v>360.7000122070312</v>
       </c>
       <c r="AX9">
-        <v>360.3800048828125</v>
+        <v>360.6400146484375</v>
       </c>
       <c r="AY9">
-        <v>360.7000122070312</v>
+        <v>360.6099853515625</v>
       </c>
       <c r="AZ9">
-        <v>360.6400146484375</v>
+        <v>370.2699890136719</v>
       </c>
       <c r="BA9">
-        <v>360.6099853515625</v>
+        <v>368.75</v>
       </c>
       <c r="BB9">
-        <v>370.2699890136719</v>
+        <v>371.6799926757812</v>
       </c>
       <c r="BC9">
-        <v>368.75</v>
+        <v>373.2799987792969</v>
       </c>
       <c r="BD9">
-        <v>371.6799926757812</v>
+        <v>377.8200073242188</v>
       </c>
       <c r="BE9">
-        <v>373.2799987792969</v>
+        <v>383.8900146484375</v>
       </c>
       <c r="BF9">
-        <v>377.8200073242188</v>
+        <v>389.5400085449219</v>
       </c>
       <c r="BG9">
-        <v>383.8900146484375</v>
+        <v>385.4500122070312</v>
       </c>
       <c r="BH9">
-        <v>389.5400085449219</v>
-      </c>
-      <c r="BI9">
-        <v>385.4500122070312</v>
-      </c>
-    </row>
-    <row r="10" spans="1:61">
+        <v>395.7300109863281</v>
+      </c>
+    </row>
+    <row r="10" spans="1:60">
       <c r="A10" t="s">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>326.3581237792969</v>
+        <v>335.5421752929688</v>
       </c>
       <c r="C10">
-        <v>332.3842163085938</v>
+        <v>333.4635009765625</v>
       </c>
       <c r="D10">
-        <v>335.5421752929688</v>
+        <v>356.4186096191406</v>
       </c>
       <c r="E10">
-        <v>333.4635009765625</v>
+        <v>372.2283325195312</v>
       </c>
       <c r="F10">
-        <v>356.4186096191406</v>
+        <v>375.1064758300781</v>
       </c>
       <c r="G10">
-        <v>372.2283325195312</v>
+        <v>359.8963623046875</v>
       </c>
       <c r="H10">
-        <v>375.1064758300781</v>
+        <v>356.3886108398438</v>
       </c>
       <c r="I10">
-        <v>359.8963623046875</v>
+        <v>353.2406616210938</v>
       </c>
       <c r="J10">
-        <v>356.3886108398438</v>
+        <v>355.609130859375</v>
       </c>
       <c r="K10">
-        <v>353.2406616210938</v>
+        <v>342.7774658203125</v>
       </c>
       <c r="L10">
-        <v>355.609130859375</v>
+        <v>342.1478576660156</v>
       </c>
       <c r="M10">
-        <v>342.7774658203125</v>
+        <v>343.7168579101562</v>
       </c>
       <c r="N10">
-        <v>342.1478576660156</v>
+        <v>343.3171081542969</v>
       </c>
       <c r="O10">
-        <v>343.7168579101562</v>
+        <v>341.2284851074219</v>
       </c>
       <c r="P10">
-        <v>343.3171081542969</v>
+        <v>341.0585632324219</v>
       </c>
       <c r="Q10">
-        <v>341.2284851074219</v>
+        <v>341.4783325195312</v>
       </c>
       <c r="R10">
-        <v>341.0585632324219</v>
+        <v>337.9805908203125</v>
       </c>
       <c r="S10">
-        <v>341.4783325195312</v>
+        <v>341.5282592773438</v>
       </c>
       <c r="T10">
-        <v>337.9805908203125</v>
+        <v>344.3664245605469</v>
       </c>
       <c r="U10">
-        <v>341.5282592773438</v>
+        <v>343.1172485351562</v>
       </c>
       <c r="V10">
-        <v>344.3664245605469</v>
+        <v>338.8800048828125</v>
       </c>
       <c r="W10">
-        <v>343.1172485351562</v>
+        <v>337.4908752441406</v>
       </c>
       <c r="X10">
-        <v>338.8800048828125</v>
+        <v>342.6575317382812</v>
       </c>
       <c r="Y10">
-        <v>337.4908752441406</v>
+        <v>335.1923828125</v>
       </c>
       <c r="Z10">
-        <v>342.6575317382812</v>
+        <v>331.8145751953125</v>
       </c>
       <c r="AA10">
-        <v>335.1923828125</v>
+        <v>333.5634460449219</v>
       </c>
       <c r="AB10">
-        <v>331.8145751953125</v>
+        <v>338.8599853515625</v>
       </c>
       <c r="AC10">
-        <v>333.5634460449219</v>
+        <v>335.3099975585938</v>
       </c>
       <c r="AD10">
-        <v>338.8599853515625</v>
+        <v>335.3800048828125</v>
       </c>
       <c r="AE10">
-        <v>335.3099975585938</v>
+        <v>328.3800048828125</v>
       </c>
       <c r="AF10">
-        <v>335.3800048828125</v>
+        <v>330.3900146484375</v>
       </c>
       <c r="AG10">
-        <v>328.3800048828125</v>
+        <v>335.4500122070312</v>
       </c>
       <c r="AH10">
-        <v>330.3900146484375</v>
+        <v>345.7099914550781</v>
       </c>
       <c r="AI10">
-        <v>335.4500122070312</v>
+        <v>341.4299926757812</v>
       </c>
       <c r="AJ10">
-        <v>345.7099914550781</v>
+        <v>339.3599853515625</v>
       </c>
       <c r="AK10">
-        <v>341.4299926757812</v>
+        <v>343.6799926757812</v>
       </c>
       <c r="AL10">
-        <v>339.3599853515625</v>
+        <v>344.4100036621094</v>
       </c>
       <c r="AM10">
-        <v>343.6799926757812</v>
+        <v>350.8699951171875</v>
       </c>
       <c r="AN10">
-        <v>344.4100036621094</v>
+        <v>347.4100036621094</v>
       </c>
       <c r="AO10">
-        <v>350.8699951171875</v>
+        <v>334.9800109863281</v>
       </c>
       <c r="AP10">
-        <v>347.4100036621094</v>
+        <v>339.010009765625</v>
       </c>
       <c r="AQ10">
-        <v>334.9800109863281</v>
+        <v>341.0799865722656</v>
       </c>
       <c r="AR10">
-        <v>339.010009765625</v>
+        <v>339.1600036621094</v>
       </c>
       <c r="AS10">
-        <v>341.0799865722656</v>
+        <v>337.3200073242188</v>
       </c>
       <c r="AT10">
-        <v>339.1600036621094</v>
+        <v>340.739990234375</v>
       </c>
       <c r="AU10">
-        <v>337.3200073242188</v>
+        <v>334.9299926757812</v>
       </c>
       <c r="AV10">
-        <v>340.739990234375</v>
+        <v>340.3500061035156</v>
       </c>
       <c r="AW10">
-        <v>334.9299926757812</v>
+        <v>343.8299865722656</v>
       </c>
       <c r="AX10">
-        <v>340.3500061035156</v>
+        <v>344.5899963378906</v>
       </c>
       <c r="AY10">
-        <v>343.8299865722656</v>
+        <v>347.3699951171875</v>
       </c>
       <c r="AZ10">
-        <v>344.5899963378906</v>
+        <v>344.8599853515625</v>
       </c>
       <c r="BA10">
-        <v>347.3699951171875</v>
+        <v>347.8599853515625</v>
       </c>
       <c r="BB10">
-        <v>344.8599853515625</v>
+        <v>348.9700012207031</v>
       </c>
       <c r="BC10">
-        <v>347.8599853515625</v>
+        <v>349.5199890136719</v>
       </c>
       <c r="BD10">
-        <v>348.9700012207031</v>
+        <v>343.6499938964844</v>
       </c>
       <c r="BE10">
-        <v>349.5199890136719</v>
+        <v>344.9100036621094</v>
       </c>
       <c r="BF10">
-        <v>343.6499938964844</v>
+        <v>336.9100036621094</v>
       </c>
       <c r="BG10">
-        <v>344.9100036621094</v>
+        <v>340.1600036621094</v>
       </c>
       <c r="BH10">
-        <v>336.9100036621094</v>
-      </c>
-      <c r="BI10">
-        <v>340.1600036621094</v>
-      </c>
-    </row>
-    <row r="11" spans="1:61">
+        <v>336.3999938964844</v>
+      </c>
+    </row>
+    <row r="11" spans="1:60">
       <c r="A11" t="s">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>64.08000183105469</v>
+        <v>61.81999969482422</v>
       </c>
       <c r="C11">
-        <v>63.90999984741211</v>
+        <v>60.84000015258789</v>
       </c>
       <c r="D11">
+        <v>62.22000122070312</v>
+      </c>
+      <c r="E11">
+        <v>63.7599983215332</v>
+      </c>
+      <c r="F11">
+        <v>64.06999969482422</v>
+      </c>
+      <c r="G11">
+        <v>66.98999786376953</v>
+      </c>
+      <c r="H11">
+        <v>64.19999694824219</v>
+      </c>
+      <c r="I11">
+        <v>65.76999664306641</v>
+      </c>
+      <c r="J11">
+        <v>66.56999969482422</v>
+      </c>
+      <c r="K11">
+        <v>64.87999725341797</v>
+      </c>
+      <c r="L11">
+        <v>67.06999969482422</v>
+      </c>
+      <c r="M11">
+        <v>66.04000091552734</v>
+      </c>
+      <c r="N11">
+        <v>67.47000122070312</v>
+      </c>
+      <c r="O11">
+        <v>64.41000366210938</v>
+      </c>
+      <c r="P11">
+        <v>65.22000122070312</v>
+      </c>
+      <c r="Q11">
+        <v>64.69999694824219</v>
+      </c>
+      <c r="R11">
+        <v>64.13999938964844</v>
+      </c>
+      <c r="S11">
+        <v>65.01999664306641</v>
+      </c>
+      <c r="T11">
+        <v>65.65000152587891</v>
+      </c>
+      <c r="U11">
+        <v>65</v>
+      </c>
+      <c r="V11">
+        <v>65.47000122070312</v>
+      </c>
+      <c r="W11">
+        <v>65.33000183105469</v>
+      </c>
+      <c r="X11">
+        <v>64.75</v>
+      </c>
+      <c r="Y11">
+        <v>64.33999633789062</v>
+      </c>
+      <c r="Z11">
+        <v>65.23000335693359</v>
+      </c>
+      <c r="AA11">
+        <v>67.33999633789062</v>
+      </c>
+      <c r="AB11">
+        <v>68.01999664306641</v>
+      </c>
+      <c r="AC11">
+        <v>67.04000091552734</v>
+      </c>
+      <c r="AD11">
+        <v>64.58000183105469</v>
+      </c>
+      <c r="AE11">
+        <v>64.05999755859375</v>
+      </c>
+      <c r="AF11">
+        <v>65.40000152587891</v>
+      </c>
+      <c r="AG11">
+        <v>66.41999816894531</v>
+      </c>
+      <c r="AH11">
+        <v>69.41000366210938</v>
+      </c>
+      <c r="AI11">
+        <v>67.66000366210938</v>
+      </c>
+      <c r="AJ11">
+        <v>66.01000213623047</v>
+      </c>
+      <c r="AK11">
+        <v>67.09999847412109</v>
+      </c>
+      <c r="AL11">
+        <v>65.11000061035156</v>
+      </c>
+      <c r="AM11">
+        <v>64.98999786376953</v>
+      </c>
+      <c r="AN11">
+        <v>63.29999923706055</v>
+      </c>
+      <c r="AO11">
+        <v>62.08000183105469</v>
+      </c>
+      <c r="AP11">
+        <v>61.91999816894531</v>
+      </c>
+      <c r="AQ11">
         <v>61.81999969482422</v>
       </c>
-      <c r="E11">
-        <v>60.84000015258789</v>
-      </c>
-      <c r="F11">
-        <v>62.22000122070312</v>
-      </c>
-      <c r="G11">
-        <v>63.7599983215332</v>
-      </c>
-      <c r="H11">
-        <v>64.06999969482422</v>
-      </c>
-      <c r="I11">
-        <v>66.98999786376953</v>
-      </c>
-      <c r="J11">
-        <v>64.19999694824219</v>
-      </c>
-      <c r="K11">
-        <v>65.76999664306641</v>
-      </c>
-      <c r="L11">
-        <v>66.56999969482422</v>
-      </c>
-      <c r="M11">
-        <v>64.87999725341797</v>
-      </c>
-      <c r="N11">
-        <v>67.06999969482422</v>
-      </c>
-      <c r="O11">
-        <v>66.04000091552734</v>
-      </c>
-      <c r="P11">
-        <v>67.47000122070312</v>
-      </c>
-      <c r="Q11">
-        <v>64.41000366210938</v>
-      </c>
-      <c r="R11">
-        <v>65.22000122070312</v>
-      </c>
-      <c r="S11">
-        <v>64.69999694824219</v>
-      </c>
-      <c r="T11">
-        <v>64.13999938964844</v>
-      </c>
-      <c r="U11">
-        <v>65.01999664306641</v>
-      </c>
-      <c r="V11">
-        <v>65.65000152587891</v>
-      </c>
-      <c r="W11">
-        <v>65</v>
-      </c>
-      <c r="X11">
-        <v>65.47000122070312</v>
-      </c>
-      <c r="Y11">
-        <v>65.33000183105469</v>
-      </c>
-      <c r="Z11">
-        <v>64.75</v>
-      </c>
-      <c r="AA11">
-        <v>64.33999633789062</v>
-      </c>
-      <c r="AB11">
-        <v>65.23000335693359</v>
-      </c>
-      <c r="AC11">
-        <v>67.33999633789062</v>
-      </c>
-      <c r="AD11">
-        <v>68.01999664306641</v>
-      </c>
-      <c r="AE11">
-        <v>67.04000091552734</v>
-      </c>
-      <c r="AF11">
-        <v>64.58000183105469</v>
-      </c>
-      <c r="AG11">
-        <v>64.05999755859375</v>
-      </c>
-      <c r="AH11">
-        <v>65.40000152587891</v>
-      </c>
-      <c r="AI11">
-        <v>66.41999816894531</v>
-      </c>
-      <c r="AJ11">
-        <v>69.41000366210938</v>
-      </c>
-      <c r="AK11">
-        <v>67.66000366210938</v>
-      </c>
-      <c r="AL11">
-        <v>66.01000213623047</v>
-      </c>
-      <c r="AM11">
-        <v>67.09999847412109</v>
-      </c>
-      <c r="AN11">
-        <v>65.11000061035156</v>
-      </c>
-      <c r="AO11">
+      <c r="AR11">
+        <v>62.52999877929688</v>
+      </c>
+      <c r="AS11">
+        <v>62.20999908447266</v>
+      </c>
+      <c r="AT11">
+        <v>62.11999893188477</v>
+      </c>
+      <c r="AU11">
+        <v>60.9900016784668</v>
+      </c>
+      <c r="AV11">
+        <v>62.9900016784668</v>
+      </c>
+      <c r="AW11">
+        <v>64.30000305175781</v>
+      </c>
+      <c r="AX11">
+        <v>64.61000061035156</v>
+      </c>
+      <c r="AY11">
         <v>64.98999786376953</v>
       </c>
-      <c r="AP11">
-        <v>63.29999923706055</v>
-      </c>
-      <c r="AQ11">
-        <v>62.08000183105469</v>
-      </c>
-      <c r="AR11">
-        <v>61.91999816894531</v>
-      </c>
-      <c r="AS11">
-        <v>61.81999969482422</v>
-      </c>
-      <c r="AT11">
-        <v>62.52999877929688</v>
-      </c>
-      <c r="AU11">
-        <v>62.20999908447266</v>
-      </c>
-      <c r="AV11">
-        <v>62.11999893188477</v>
-      </c>
-      <c r="AW11">
-        <v>60.9900016784668</v>
-      </c>
-      <c r="AX11">
-        <v>62.9900016784668</v>
-      </c>
-      <c r="AY11">
-        <v>64.30000305175781</v>
-      </c>
       <c r="AZ11">
-        <v>64.61000061035156</v>
+        <v>64.54000091552734</v>
       </c>
       <c r="BA11">
-        <v>64.98999786376953</v>
+        <v>65.36000061035156</v>
       </c>
       <c r="BB11">
-        <v>64.54000091552734</v>
+        <v>67.01999664306641</v>
       </c>
       <c r="BC11">
-        <v>65.36000061035156</v>
+        <v>68.86000061035156</v>
       </c>
       <c r="BD11">
-        <v>67.01999664306641</v>
+        <v>70.16000366210938</v>
       </c>
       <c r="BE11">
-        <v>68.86000061035156</v>
+        <v>70.51000213623047</v>
       </c>
       <c r="BF11">
-        <v>70.16000366210938</v>
+        <v>69.16000366210938</v>
       </c>
       <c r="BG11">
-        <v>70.51000213623047</v>
+        <v>68.62999725341797</v>
       </c>
       <c r="BH11">
-        <v>69.16000366210938</v>
-      </c>
-      <c r="BI11">
-        <v>68.62999725341797</v>
-      </c>
-    </row>
-    <row r="12" spans="1:61">
+        <v>70.80999755859375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:60">
       <c r="A12" t="s">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>326.3502197265625</v>
+        <v>336.4937133789062</v>
       </c>
       <c r="C12">
-        <v>333.4956359863281</v>
+        <v>333.4456787109375</v>
       </c>
       <c r="D12">
-        <v>336.4937133789062</v>
+        <v>355.9012451171875</v>
       </c>
       <c r="E12">
-        <v>333.4456787109375</v>
+        <v>373.2700805664062</v>
       </c>
       <c r="F12">
-        <v>355.9012451171875</v>
+        <v>377.4074096679688</v>
       </c>
       <c r="G12">
-        <v>373.2700805664062</v>
+        <v>362.1971740722656</v>
       </c>
       <c r="H12">
-        <v>377.4074096679688</v>
+        <v>357.5202026367188</v>
       </c>
       <c r="I12">
-        <v>362.1971740722656</v>
+        <v>354.0723876953125</v>
       </c>
       <c r="J12">
-        <v>357.5202026367188</v>
+        <v>357.2903442382812</v>
       </c>
       <c r="K12">
-        <v>354.0723876953125</v>
+        <v>343.5791320800781</v>
       </c>
       <c r="L12">
-        <v>357.2903442382812</v>
+        <v>343.3193359375</v>
       </c>
       <c r="M12">
-        <v>343.5791320800781</v>
+        <v>346.1375122070312</v>
       </c>
       <c r="N12">
-        <v>343.3193359375</v>
+        <v>345.6777954101562</v>
       </c>
       <c r="O12">
-        <v>346.1375122070312</v>
+        <v>343.7790222167969</v>
       </c>
       <c r="P12">
-        <v>345.6777954101562</v>
+        <v>343.9789123535156</v>
       </c>
       <c r="Q12">
-        <v>343.7790222167969</v>
+        <v>344.4985656738281</v>
       </c>
       <c r="R12">
-        <v>343.9789123535156</v>
+        <v>340.451171875</v>
       </c>
       <c r="S12">
-        <v>344.4985656738281</v>
+        <v>344.5985107421875</v>
       </c>
       <c r="T12">
-        <v>340.451171875</v>
+        <v>347.83642578125</v>
       </c>
       <c r="U12">
-        <v>344.5985107421875</v>
+        <v>346.7371215820312</v>
       </c>
       <c r="V12">
-        <v>347.83642578125</v>
+        <v>341.7803039550781</v>
       </c>
       <c r="W12">
-        <v>346.7371215820312</v>
+        <v>340.4311828613281</v>
       </c>
       <c r="X12">
-        <v>341.7803039550781</v>
+        <v>346.3673706054688</v>
       </c>
       <c r="Y12">
-        <v>340.4311828613281</v>
+        <v>339.1320190429688</v>
       </c>
       <c r="Z12">
-        <v>346.3673706054688</v>
+        <v>334.8047790527344</v>
       </c>
       <c r="AA12">
-        <v>339.1320190429688</v>
+        <v>336.9034423828125</v>
       </c>
       <c r="AB12">
-        <v>334.8047790527344</v>
+        <v>342.260009765625</v>
       </c>
       <c r="AC12">
-        <v>336.9034423828125</v>
+        <v>338.4599914550781</v>
       </c>
       <c r="AD12">
-        <v>342.260009765625</v>
+        <v>338.3599853515625</v>
       </c>
       <c r="AE12">
-        <v>338.4599914550781</v>
+        <v>330.6499938964844</v>
       </c>
       <c r="AF12">
-        <v>338.3599853515625</v>
+        <v>332.6000061035156</v>
       </c>
       <c r="AG12">
-        <v>330.6499938964844</v>
+        <v>338.5</v>
       </c>
       <c r="AH12">
-        <v>332.6000061035156</v>
+        <v>349.3900146484375</v>
       </c>
       <c r="AI12">
-        <v>338.5</v>
+        <v>344.9800109863281</v>
       </c>
       <c r="AJ12">
-        <v>349.3900146484375</v>
+        <v>342.8699951171875</v>
       </c>
       <c r="AK12">
-        <v>344.9800109863281</v>
+        <v>347.3299865722656</v>
       </c>
       <c r="AL12">
-        <v>342.8699951171875</v>
+        <v>349.5400085449219</v>
       </c>
       <c r="AM12">
-        <v>347.3299865722656</v>
+        <v>354.9700012207031</v>
       </c>
       <c r="AN12">
-        <v>349.5400085449219</v>
+        <v>351.1600036621094</v>
       </c>
       <c r="AO12">
-        <v>354.9700012207031</v>
+        <v>337.8299865722656</v>
       </c>
       <c r="AP12">
-        <v>351.1600036621094</v>
+        <v>342.3599853515625</v>
       </c>
       <c r="AQ12">
-        <v>337.8299865722656</v>
+        <v>343.9200134277344</v>
       </c>
       <c r="AR12">
-        <v>342.3599853515625</v>
+        <v>342.75</v>
       </c>
       <c r="AS12">
-        <v>343.9200134277344</v>
+        <v>340.9200134277344</v>
       </c>
       <c r="AT12">
-        <v>342.75</v>
+        <v>344.0799865722656</v>
       </c>
       <c r="AU12">
-        <v>340.9200134277344</v>
+        <v>338.239990234375</v>
       </c>
       <c r="AV12">
-        <v>344.0799865722656</v>
+        <v>343.5</v>
       </c>
       <c r="AW12">
-        <v>338.239990234375</v>
+        <v>346.4700012207031</v>
       </c>
       <c r="AX12">
-        <v>343.5</v>
+        <v>347.6799926757812</v>
       </c>
       <c r="AY12">
-        <v>346.4700012207031</v>
+        <v>350.5</v>
       </c>
       <c r="AZ12">
-        <v>347.6799926757812</v>
+        <v>348.2900085449219</v>
       </c>
       <c r="BA12">
-        <v>350.5</v>
+        <v>351.6600036621094</v>
       </c>
       <c r="BB12">
-        <v>348.2900085449219</v>
+        <v>352.7200012207031</v>
       </c>
       <c r="BC12">
-        <v>351.6600036621094</v>
+        <v>353.7799987792969</v>
       </c>
       <c r="BD12">
-        <v>352.7200012207031</v>
+        <v>347.6400146484375</v>
       </c>
       <c r="BE12">
-        <v>353.7799987792969</v>
+        <v>349.2200012207031</v>
       </c>
       <c r="BF12">
-        <v>347.6400146484375</v>
+        <v>340.5899963378906</v>
       </c>
       <c r="BG12">
-        <v>349.2200012207031</v>
+        <v>344.1799926757812</v>
       </c>
       <c r="BH12">
-        <v>340.5899963378906</v>
-      </c>
-      <c r="BI12">
-        <v>344.1799926757812</v>
-      </c>
-    </row>
-    <row r="13" spans="1:61">
+        <v>340.2799987792969</v>
+      </c>
+    </row>
+    <row r="13" spans="1:60">
       <c r="A13" t="s">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>260.1871337890625</v>
+        <v>273.2527770996094</v>
       </c>
       <c r="C13">
-        <v>271.2909240722656</v>
+        <v>264.2801208496094</v>
       </c>
       <c r="D13">
-        <v>273.2527770996094</v>
+        <v>262.9854736328125</v>
       </c>
       <c r="E13">
-        <v>264.2801208496094</v>
+        <v>261.5912780761719</v>
       </c>
       <c r="F13">
-        <v>262.9854736328125</v>
+        <v>261.4718017578125</v>
       </c>
       <c r="G13">
-        <v>261.5912780761719</v>
+        <v>263.4933776855469</v>
       </c>
       <c r="H13">
-        <v>261.4718017578125</v>
+        <v>273.9697570800781</v>
       </c>
       <c r="I13">
-        <v>263.4933776855469</v>
+        <v>265.8934020996094</v>
       </c>
       <c r="J13">
-        <v>273.9697570800781</v>
+        <v>268.5523376464844</v>
       </c>
       <c r="K13">
-        <v>265.8934020996094</v>
+        <v>261.1431579589844</v>
       </c>
       <c r="L13">
-        <v>268.5523376464844</v>
+        <v>254.7796325683594</v>
       </c>
       <c r="M13">
-        <v>261.1431579589844</v>
+        <v>259.4004211425781</v>
       </c>
       <c r="N13">
-        <v>254.7796325683594</v>
+        <v>260.3265686035156</v>
       </c>
       <c r="O13">
-        <v>259.4004211425781</v>
+        <v>257.0302734375</v>
       </c>
       <c r="P13">
-        <v>260.3265686035156</v>
+        <v>260.067626953125</v>
       </c>
       <c r="Q13">
-        <v>257.0302734375</v>
+        <v>258.6634826660156</v>
       </c>
       <c r="R13">
-        <v>260.067626953125</v>
+        <v>253.4850311279297</v>
       </c>
       <c r="S13">
-        <v>258.6634826660156</v>
+        <v>252.7779693603516</v>
       </c>
       <c r="T13">
-        <v>253.4850311279297</v>
+        <v>259.1116027832031</v>
       </c>
       <c r="U13">
-        <v>252.7779693603516</v>
+        <v>256.55224609375</v>
       </c>
       <c r="V13">
-        <v>259.1116027832031</v>
+        <v>260.7248840332031</v>
       </c>
       <c r="W13">
         <v>256.55224609375</v>
       </c>
       <c r="X13">
-        <v>260.7248840332031</v>
+        <v>259.4999694824219</v>
       </c>
       <c r="Y13">
-        <v>256.55224609375</v>
+        <v>257.7999877929688</v>
       </c>
       <c r="Z13">
-        <v>259.4999694824219</v>
+        <v>257.8699951171875</v>
       </c>
       <c r="AA13">
-        <v>257.7999877929688</v>
+        <v>259.3399963378906</v>
       </c>
       <c r="AB13">
-        <v>257.8699951171875</v>
+        <v>263.1099853515625</v>
       </c>
       <c r="AC13">
-        <v>259.3399963378906</v>
+        <v>259.5700073242188</v>
       </c>
       <c r="AD13">
-        <v>263.1099853515625</v>
+        <v>253.4600067138672</v>
       </c>
       <c r="AE13">
-        <v>259.5700073242188</v>
+        <v>253.5800018310547</v>
       </c>
       <c r="AF13">
-        <v>253.4600067138672</v>
+        <v>251.7899932861328</v>
       </c>
       <c r="AG13">
-        <v>253.5800018310547</v>
+        <v>253.7100067138672</v>
       </c>
       <c r="AH13">
-        <v>251.7899932861328</v>
+        <v>258.4800109863281</v>
       </c>
       <c r="AI13">
-        <v>253.7100067138672</v>
+        <v>257.2099914550781</v>
       </c>
       <c r="AJ13">
-        <v>258.4800109863281</v>
+        <v>254.8500061035156</v>
       </c>
       <c r="AK13">
-        <v>257.2099914550781</v>
+        <v>252.2100067138672</v>
       </c>
       <c r="AL13">
-        <v>254.8500061035156</v>
+        <v>249.8300018310547</v>
       </c>
       <c r="AM13">
-        <v>252.2100067138672</v>
+        <v>242.8600006103516</v>
       </c>
       <c r="AN13">
-        <v>249.8300018310547</v>
+        <v>229.5</v>
       </c>
       <c r="AO13">
-        <v>242.8600006103516</v>
+        <v>225.6600036621094</v>
       </c>
       <c r="AP13">
-        <v>229.5</v>
+        <v>227.1699981689453</v>
       </c>
       <c r="AQ13">
-        <v>225.6600036621094</v>
+        <v>227.6000061035156</v>
       </c>
       <c r="AR13">
-        <v>227.1699981689453</v>
+        <v>227.5500030517578</v>
       </c>
       <c r="AS13">
-        <v>227.6000061035156</v>
+        <v>225.4199981689453</v>
       </c>
       <c r="AT13">
-        <v>227.5500030517578</v>
+        <v>221.8600006103516</v>
       </c>
       <c r="AU13">
-        <v>225.4199981689453</v>
+        <v>224.4100036621094</v>
       </c>
       <c r="AV13">
-        <v>221.8600006103516</v>
+        <v>223.7400054931641</v>
       </c>
       <c r="AW13">
-        <v>224.4100036621094</v>
+        <v>224.7100067138672</v>
       </c>
       <c r="AX13">
-        <v>223.7400054931641</v>
+        <v>224.2700042724609</v>
       </c>
       <c r="AY13">
-        <v>224.7100067138672</v>
+        <v>223.9499969482422</v>
       </c>
       <c r="AZ13">
-        <v>224.2700042724609</v>
+        <v>230.6300048828125</v>
       </c>
       <c r="BA13">
-        <v>223.9499969482422</v>
+        <v>229.4299926757812</v>
       </c>
       <c r="BB13">
-        <v>230.6300048828125</v>
+        <v>232.6000061035156</v>
       </c>
       <c r="BC13">
-        <v>229.4299926757812</v>
+        <v>236.3999938964844</v>
       </c>
       <c r="BD13">
-        <v>232.6000061035156</v>
+        <v>236.1699981689453</v>
       </c>
       <c r="BE13">
-        <v>236.3999938964844</v>
+        <v>239.6000061035156</v>
       </c>
       <c r="BF13">
-        <v>236.1699981689453</v>
+        <v>247.8800048828125</v>
       </c>
       <c r="BG13">
-        <v>239.6000061035156</v>
+        <v>246.8500061035156</v>
       </c>
       <c r="BH13">
-        <v>247.8800048828125</v>
-      </c>
-      <c r="BI13">
-        <v>246.8500061035156</v>
-      </c>
-    </row>
-    <row r="14" spans="1:61">
+        <v>249.9100036621094</v>
+      </c>
+    </row>
+    <row r="14" spans="1:60">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>139.2710113525391</v>
+        <v>144.7886657714844</v>
       </c>
       <c r="C14">
-        <v>143.1016235351562</v>
+        <v>143.4092559814453</v>
       </c>
       <c r="D14">
-        <v>144.7886657714844</v>
+        <v>143.3894195556641</v>
       </c>
       <c r="E14">
-        <v>143.4092559814453</v>
+        <v>148.21240234375</v>
       </c>
       <c r="F14">
-        <v>143.3894195556641</v>
+        <v>146.9818420410156</v>
       </c>
       <c r="G14">
-        <v>148.21240234375</v>
+        <v>146.574951171875</v>
       </c>
       <c r="H14">
-        <v>146.9818420410156</v>
+        <v>145.9596862792969</v>
       </c>
       <c r="I14">
-        <v>146.574951171875</v>
+        <v>148.5597229003906</v>
       </c>
       <c r="J14">
-        <v>145.9596862792969</v>
+        <v>150.862060546875</v>
       </c>
       <c r="K14">
-        <v>148.5597229003906</v>
+        <v>151.1299896240234</v>
       </c>
       <c r="L14">
-        <v>150.862060546875</v>
+        <v>154</v>
       </c>
       <c r="M14">
-        <v>151.1299896240234</v>
+        <v>155.5099945068359</v>
       </c>
       <c r="N14">
+        <v>154.4799957275391</v>
+      </c>
+      <c r="O14">
+        <v>151.0099945068359</v>
+      </c>
+      <c r="P14">
+        <v>152.4799957275391</v>
+      </c>
+      <c r="Q14">
+        <v>159</v>
+      </c>
+      <c r="R14">
+        <v>158.25</v>
+      </c>
+      <c r="S14">
+        <v>165.4400024414062</v>
+      </c>
+      <c r="T14">
+        <v>169.8899993896484</v>
+      </c>
+      <c r="U14">
+        <v>163.4700012207031</v>
+      </c>
+      <c r="V14">
+        <v>164.0399932861328</v>
+      </c>
+      <c r="W14">
+        <v>165.9299926757812</v>
+      </c>
+      <c r="X14">
+        <v>163.1799926757812</v>
+      </c>
+      <c r="Y14">
+        <v>160.8800048828125</v>
+      </c>
+      <c r="Z14">
+        <v>163.75</v>
+      </c>
+      <c r="AA14">
+        <v>163.3600006103516</v>
+      </c>
+      <c r="AB14">
+        <v>164.0099945068359</v>
+      </c>
+      <c r="AC14">
+        <v>164.4400024414062</v>
+      </c>
+      <c r="AD14">
+        <v>162.7100067138672</v>
+      </c>
+      <c r="AE14">
+        <v>157.5200042724609</v>
+      </c>
+      <c r="AF14">
+        <v>155.7299957275391</v>
+      </c>
+      <c r="AG14">
+        <v>155.8300018310547</v>
+      </c>
+      <c r="AH14">
+        <v>158.6999969482422</v>
+      </c>
+      <c r="AI14">
+        <v>154.3999938964844</v>
+      </c>
+      <c r="AJ14">
+        <v>154.6799926757812</v>
+      </c>
+      <c r="AK14">
+        <v>159.8300018310547</v>
+      </c>
+      <c r="AL14">
+        <v>158.1900024414062</v>
+      </c>
+      <c r="AM14">
+        <v>157.7100067138672</v>
+      </c>
+      <c r="AN14">
+        <v>159.0200042724609</v>
+      </c>
+      <c r="AO14">
+        <v>156.2599945068359</v>
+      </c>
+      <c r="AP14">
+        <v>156.1499938964844</v>
+      </c>
+      <c r="AQ14">
+        <v>157.4499969482422</v>
+      </c>
+      <c r="AR14">
+        <v>158.4299926757812</v>
+      </c>
+      <c r="AS14">
+        <v>156.4299926757812</v>
+      </c>
+      <c r="AT14">
+        <v>156.6900024414062</v>
+      </c>
+      <c r="AU14">
+        <v>156.6999969482422</v>
+      </c>
+      <c r="AV14">
+        <v>156</v>
+      </c>
+      <c r="AW14">
+        <v>152.9900054931641</v>
+      </c>
+      <c r="AX14">
+        <v>154.3300018310547</v>
+      </c>
+      <c r="AY14">
+        <v>150.9199981689453</v>
+      </c>
+      <c r="AZ14">
+        <v>154.7599945068359</v>
+      </c>
+      <c r="BA14">
+        <v>153.6399993896484</v>
+      </c>
+      <c r="BB14">
+        <v>153.6199951171875</v>
+      </c>
+      <c r="BC14">
+        <v>151.9900054931641</v>
+      </c>
+      <c r="BD14">
+        <v>155.3099975585938</v>
+      </c>
+      <c r="BE14">
+        <v>156.6300048828125</v>
+      </c>
+      <c r="BF14">
+        <v>154.2599945068359</v>
+      </c>
+      <c r="BG14">
+        <v>153.2899932861328</v>
+      </c>
+      <c r="BH14">
         <v>154</v>
       </c>
-      <c r="O14">
-        <v>155.5099945068359</v>
-      </c>
-      <c r="P14">
-        <v>154.4799957275391</v>
-      </c>
-      <c r="Q14">
-        <v>151.0099945068359</v>
-      </c>
-      <c r="R14">
-        <v>152.4799957275391</v>
-      </c>
-      <c r="S14">
-        <v>159</v>
-      </c>
-      <c r="T14">
-        <v>158.25</v>
-      </c>
-      <c r="U14">
-        <v>165.4400024414062</v>
-      </c>
-      <c r="V14">
-        <v>169.8899993896484</v>
-      </c>
-      <c r="W14">
-        <v>163.4700012207031</v>
-      </c>
-      <c r="X14">
-        <v>164.0399932861328</v>
-      </c>
-      <c r="Y14">
-        <v>165.9299926757812</v>
-      </c>
-      <c r="Z14">
-        <v>163.1799926757812</v>
-      </c>
-      <c r="AA14">
-        <v>160.8800048828125</v>
-      </c>
-      <c r="AB14">
-        <v>163.75</v>
-      </c>
-      <c r="AC14">
-        <v>163.3600006103516</v>
-      </c>
-      <c r="AD14">
-        <v>164.0099945068359</v>
-      </c>
-      <c r="AE14">
-        <v>164.4400024414062</v>
-      </c>
-      <c r="AF14">
-        <v>162.7100067138672</v>
-      </c>
-      <c r="AG14">
-        <v>157.5200042724609</v>
-      </c>
-      <c r="AH14">
-        <v>155.7299957275391</v>
-      </c>
-      <c r="AI14">
-        <v>155.8300018310547</v>
-      </c>
-      <c r="AJ14">
-        <v>158.6999969482422</v>
-      </c>
-      <c r="AK14">
-        <v>154.3999938964844</v>
-      </c>
-      <c r="AL14">
-        <v>154.6799926757812</v>
-      </c>
-      <c r="AM14">
-        <v>159.8300018310547</v>
-      </c>
-      <c r="AN14">
-        <v>158.1900024414062</v>
-      </c>
-      <c r="AO14">
-        <v>157.7100067138672</v>
-      </c>
-      <c r="AP14">
-        <v>159.0200042724609</v>
-      </c>
-      <c r="AQ14">
-        <v>156.2599945068359</v>
-      </c>
-      <c r="AR14">
-        <v>156.1499938964844</v>
-      </c>
-      <c r="AS14">
-        <v>157.4499969482422</v>
-      </c>
-      <c r="AT14">
-        <v>158.4299926757812</v>
-      </c>
-      <c r="AU14">
-        <v>156.4299926757812</v>
-      </c>
-      <c r="AV14">
-        <v>156.6900024414062</v>
-      </c>
-      <c r="AW14">
-        <v>156.6999969482422</v>
-      </c>
-      <c r="AX14">
-        <v>156</v>
-      </c>
-      <c r="AY14">
-        <v>152.9900054931641</v>
-      </c>
-      <c r="AZ14">
-        <v>154.3300018310547</v>
-      </c>
-      <c r="BA14">
-        <v>150.9199981689453</v>
-      </c>
-      <c r="BB14">
-        <v>154.7599945068359</v>
-      </c>
-      <c r="BC14">
-        <v>153.6399993896484</v>
-      </c>
-      <c r="BD14">
-        <v>153.6199951171875</v>
-      </c>
-      <c r="BE14">
-        <v>151.9900054931641</v>
-      </c>
-      <c r="BF14">
-        <v>155.3099975585938</v>
-      </c>
-      <c r="BG14">
-        <v>156.6300048828125</v>
-      </c>
-      <c r="BH14">
-        <v>154.2599945068359</v>
-      </c>
-      <c r="BI14">
-        <v>153.2899932861328</v>
-      </c>
-    </row>
-    <row r="15" spans="1:61">
+    </row>
+    <row r="15" spans="1:60">
       <c r="A15" t="s">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>118.870002746582</v>
+        <v>127.0999984741211</v>
       </c>
       <c r="C15">
-        <v>129.9299926757812</v>
+        <v>122.9899978637695</v>
       </c>
       <c r="D15">
-        <v>127.0999984741211</v>
+        <v>119.5199966430664</v>
       </c>
       <c r="E15">
-        <v>122.9899978637695</v>
+        <v>118.4300003051758</v>
       </c>
       <c r="F15">
-        <v>119.5199966430664</v>
+        <v>120.5999984741211</v>
       </c>
       <c r="G15">
-        <v>118.4300003051758</v>
+        <v>119.8000030517578</v>
       </c>
       <c r="H15">
-        <v>120.5999984741211</v>
+        <v>118.379997253418</v>
       </c>
       <c r="I15">
-        <v>119.8000030517578</v>
+        <v>120.5599975585938</v>
       </c>
       <c r="J15">
-        <v>118.379997253418</v>
+        <v>121.5500030517578</v>
       </c>
       <c r="K15">
-        <v>120.5599975585938</v>
+        <v>121.0699996948242</v>
       </c>
       <c r="L15">
-        <v>121.5500030517578</v>
+        <v>120.7699966430664</v>
       </c>
       <c r="M15">
-        <v>121.0699996948242</v>
+        <v>120.5199966430664</v>
       </c>
       <c r="N15">
-        <v>120.7699966430664</v>
+        <v>120.1600036621094</v>
       </c>
       <c r="O15">
-        <v>120.5199966430664</v>
+        <v>123.5</v>
       </c>
       <c r="P15">
-        <v>120.1600036621094</v>
+        <v>123.4700012207031</v>
       </c>
       <c r="Q15">
-        <v>123.5</v>
+        <v>128.4700012207031</v>
       </c>
       <c r="R15">
-        <v>123.4700012207031</v>
+        <v>127.2200012207031</v>
       </c>
       <c r="S15">
-        <v>128.4700012207031</v>
+        <v>127.8099975585938</v>
       </c>
       <c r="T15">
-        <v>127.2200012207031</v>
+        <v>127.9800033569336</v>
       </c>
       <c r="U15">
-        <v>127.8099975585938</v>
+        <v>129.7200012207031</v>
       </c>
       <c r="V15">
-        <v>127.9800033569336</v>
+        <v>128.1199951171875</v>
       </c>
       <c r="W15">
-        <v>129.7200012207031</v>
+        <v>127.7399978637695</v>
       </c>
       <c r="X15">
-        <v>128.1199951171875</v>
+        <v>124.370002746582</v>
       </c>
       <c r="Y15">
-        <v>127.7399978637695</v>
+        <v>123.2200012207031</v>
       </c>
       <c r="Z15">
-        <v>124.370002746582</v>
+        <v>125.0100021362305</v>
       </c>
       <c r="AA15">
-        <v>123.2200012207031</v>
+        <v>128.8300018310547</v>
       </c>
       <c r="AB15">
-        <v>125.0100021362305</v>
+        <v>128</v>
       </c>
       <c r="AC15">
-        <v>128.8300018310547</v>
+        <v>126.75</v>
       </c>
       <c r="AD15">
-        <v>128</v>
+        <v>124.4000015258789</v>
       </c>
       <c r="AE15">
-        <v>126.75</v>
+        <v>126.0100021362305</v>
       </c>
       <c r="AF15">
-        <v>124.4000015258789</v>
+        <v>123.2799987792969</v>
       </c>
       <c r="AG15">
-        <v>126.0100021362305</v>
+        <v>121.4700012207031</v>
       </c>
       <c r="AH15">
-        <v>123.2799987792969</v>
+        <v>122.1900024414062</v>
       </c>
       <c r="AI15">
-        <v>121.4700012207031</v>
+        <v>121.7399978637695</v>
       </c>
       <c r="AJ15">
-        <v>122.1900024414062</v>
+        <v>124.75</v>
       </c>
       <c r="AK15">
-        <v>121.7399978637695</v>
+        <v>127.620002746582</v>
       </c>
       <c r="AL15">
-        <v>124.75</v>
+        <v>125.3099975585938</v>
       </c>
       <c r="AM15">
-        <v>127.620002746582</v>
+        <v>124.6500015258789</v>
       </c>
       <c r="AN15">
-        <v>125.3099975585938</v>
+        <v>126.9300003051758</v>
       </c>
       <c r="AO15">
-        <v>124.6500015258789</v>
+        <v>124.6399993896484</v>
       </c>
       <c r="AP15">
-        <v>126.9300003051758</v>
+        <v>124.4400024414062</v>
       </c>
       <c r="AQ15">
-        <v>124.6399993896484</v>
+        <v>123.8899993896484</v>
       </c>
       <c r="AR15">
-        <v>124.4400024414062</v>
+        <v>124.8199996948242</v>
       </c>
       <c r="AS15">
-        <v>123.8899993896484</v>
+        <v>123.1999969482422</v>
       </c>
       <c r="AT15">
-        <v>124.8199996948242</v>
+        <v>121.3499984741211</v>
       </c>
       <c r="AU15">
-        <v>123.1999969482422</v>
+        <v>117.1399993896484</v>
       </c>
       <c r="AV15">
-        <v>121.3499984741211</v>
+        <v>115.3000030517578</v>
       </c>
       <c r="AW15">
-        <v>117.1399993896484</v>
+        <v>114.129997253418</v>
       </c>
       <c r="AX15">
-        <v>115.3000030517578</v>
+        <v>112.7300033569336</v>
       </c>
       <c r="AY15">
-        <v>114.129997253418</v>
+        <v>113.4400024414062</v>
       </c>
       <c r="AZ15">
-        <v>112.7300033569336</v>
+        <v>112.75</v>
       </c>
       <c r="BA15">
-        <v>113.4400024414062</v>
+        <v>112.7900009155273</v>
       </c>
       <c r="BB15">
-        <v>112.75</v>
+        <v>111.3600006103516</v>
       </c>
       <c r="BC15">
-        <v>112.7900009155273</v>
+        <v>108.620002746582</v>
       </c>
       <c r="BD15">
-        <v>111.3600006103516</v>
+        <v>111.5699996948242</v>
       </c>
       <c r="BE15">
-        <v>108.620002746582</v>
+        <v>113.2699966430664</v>
       </c>
       <c r="BF15">
-        <v>111.5699996948242</v>
+        <v>113.0699996948242</v>
       </c>
       <c r="BG15">
-        <v>113.2699966430664</v>
+        <v>113.25</v>
       </c>
       <c r="BH15">
-        <v>113.0699996948242</v>
-      </c>
-      <c r="BI15">
-        <v>113.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:61">
+        <v>116.620002746582</v>
+      </c>
+    </row>
+    <row r="16" spans="1:60">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>231.3899993896484</v>
+        <v>226.6499938964844</v>
       </c>
       <c r="C16">
-        <v>230.8600006103516</v>
+        <v>235.5</v>
       </c>
       <c r="D16">
-        <v>226.6499938964844</v>
+        <v>271.5799865722656</v>
       </c>
       <c r="E16">
-        <v>235.5</v>
+        <v>284.0199890136719</v>
       </c>
       <c r="F16">
-        <v>271.5799865722656</v>
+        <v>277.4200134277344</v>
       </c>
       <c r="G16">
-        <v>284.0199890136719</v>
+        <v>272.6499938964844</v>
       </c>
       <c r="H16">
-        <v>277.4200134277344</v>
+        <v>272.260009765625</v>
       </c>
       <c r="I16">
-        <v>272.6499938964844</v>
+        <v>274.4800109863281</v>
       </c>
       <c r="J16">
-        <v>272.260009765625</v>
+        <v>278.0899963378906</v>
       </c>
       <c r="K16">
-        <v>274.4800109863281</v>
+        <v>272.2699890136719</v>
       </c>
       <c r="L16">
-        <v>278.0899963378906</v>
+        <v>267.2799987792969</v>
       </c>
       <c r="M16">
-        <v>272.2699890136719</v>
+        <v>265.1300048828125</v>
       </c>
       <c r="N16">
-        <v>267.2799987792969</v>
+        <v>262.6499938964844</v>
       </c>
       <c r="O16">
-        <v>265.1300048828125</v>
+        <v>261.3099975585938</v>
       </c>
       <c r="P16">
-        <v>262.6499938964844</v>
+        <v>259.4500122070312</v>
       </c>
       <c r="Q16">
-        <v>261.3099975585938</v>
+        <v>265.8399963378906</v>
       </c>
       <c r="R16">
-        <v>259.4500122070312</v>
+        <v>260.1099853515625</v>
       </c>
       <c r="S16">
-        <v>265.8399963378906</v>
+        <v>258.6300048828125</v>
       </c>
       <c r="T16">
-        <v>260.1099853515625</v>
+        <v>262.0700073242188</v>
       </c>
       <c r="U16">
-        <v>258.6300048828125</v>
+        <v>261.0599975585938</v>
       </c>
       <c r="V16">
-        <v>262.0700073242188</v>
+        <v>260.2799987792969</v>
       </c>
       <c r="W16">
-        <v>261.0599975585938</v>
+        <v>256.260009765625</v>
       </c>
       <c r="X16">
-        <v>260.2799987792969</v>
+        <v>266.4299926757812</v>
       </c>
       <c r="Y16">
-        <v>256.260009765625</v>
+        <v>259.7699890136719</v>
       </c>
       <c r="Z16">
-        <v>266.4299926757812</v>
+        <v>254.9199981689453</v>
       </c>
       <c r="AA16">
-        <v>259.7699890136719</v>
+        <v>254.9799957275391</v>
       </c>
       <c r="AB16">
-        <v>254.9199981689453</v>
+        <v>258.8999938964844</v>
       </c>
       <c r="AC16">
+        <v>258.510009765625</v>
+      </c>
+      <c r="AD16">
+        <v>256.9700012207031</v>
+      </c>
+      <c r="AE16">
+        <v>252.3999938964844</v>
+      </c>
+      <c r="AF16">
+        <v>251.8899993896484</v>
+      </c>
+      <c r="AG16">
+        <v>256.7799987792969</v>
+      </c>
+      <c r="AH16">
+        <v>253.5399932861328</v>
+      </c>
+      <c r="AI16">
+        <v>248.4199981689453</v>
+      </c>
+      <c r="AJ16">
+        <v>245.9600067138672</v>
+      </c>
+      <c r="AK16">
+        <v>251.1900024414062</v>
+      </c>
+      <c r="AL16">
+        <v>253.7100067138672</v>
+      </c>
+      <c r="AM16">
+        <v>258.4500122070312</v>
+      </c>
+      <c r="AN16">
         <v>254.9799957275391</v>
       </c>
-      <c r="AD16">
-        <v>258.8999938964844</v>
-      </c>
-      <c r="AE16">
-        <v>258.510009765625</v>
-      </c>
-      <c r="AF16">
-        <v>256.9700012207031</v>
-      </c>
-      <c r="AG16">
-        <v>252.3999938964844</v>
-      </c>
-      <c r="AH16">
-        <v>251.8899993896484</v>
-      </c>
-      <c r="AI16">
-        <v>256.7799987792969</v>
-      </c>
-      <c r="AJ16">
-        <v>253.5399932861328</v>
-      </c>
-      <c r="AK16">
-        <v>248.4199981689453</v>
-      </c>
-      <c r="AL16">
-        <v>245.9600067138672</v>
-      </c>
-      <c r="AM16">
-        <v>251.1900024414062</v>
-      </c>
-      <c r="AN16">
-        <v>253.7100067138672</v>
-      </c>
       <c r="AO16">
-        <v>258.4500122070312</v>
+        <v>249.2700042724609</v>
       </c>
       <c r="AP16">
-        <v>254.9799957275391</v>
+        <v>249.3800048828125</v>
       </c>
       <c r="AQ16">
-        <v>249.2700042724609</v>
+        <v>249.6699981689453</v>
       </c>
       <c r="AR16">
-        <v>249.3800048828125</v>
+        <v>246.1499938964844</v>
       </c>
       <c r="AS16">
-        <v>249.6699981689453</v>
+        <v>246.6699981689453</v>
       </c>
       <c r="AT16">
-        <v>246.1499938964844</v>
+        <v>249.1499938964844</v>
       </c>
       <c r="AU16">
-        <v>246.6699981689453</v>
+        <v>248.2299957275391</v>
       </c>
       <c r="AV16">
-        <v>249.1499938964844</v>
+        <v>251.5200042724609</v>
       </c>
       <c r="AW16">
-        <v>248.2299957275391</v>
+        <v>251.3999938964844</v>
       </c>
       <c r="AX16">
-        <v>251.5200042724609</v>
+        <v>256.2900085449219</v>
       </c>
       <c r="AY16">
-        <v>251.3999938964844</v>
+        <v>259.9200134277344</v>
       </c>
       <c r="AZ16">
-        <v>256.2900085449219</v>
+        <v>254.0599975585938</v>
       </c>
       <c r="BA16">
-        <v>259.9200134277344</v>
+        <v>262.4299926757812</v>
       </c>
       <c r="BB16">
-        <v>254.0599975585938</v>
+        <v>259.5299987792969</v>
       </c>
       <c r="BC16">
-        <v>262.4299926757812</v>
+        <v>258.5799865722656</v>
       </c>
       <c r="BD16">
-        <v>259.5299987792969</v>
+        <v>254.0800018310547</v>
       </c>
       <c r="BE16">
-        <v>258.5799865722656</v>
+        <v>254.7599945068359</v>
       </c>
       <c r="BF16">
-        <v>254.0800018310547</v>
+        <v>250</v>
       </c>
       <c r="BG16">
-        <v>254.7599945068359</v>
+        <v>262.4500122070312</v>
       </c>
       <c r="BH16">
-        <v>250</v>
-      </c>
-      <c r="BI16">
-        <v>262.4500122070312</v>
-      </c>
-    </row>
-    <row r="17" spans="1:61">
+        <v>262.6300048828125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:60">
       <c r="A17" t="s">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>189.4700012207031</v>
+        <v>194.8200073242188</v>
       </c>
       <c r="C17">
-        <v>192.9799957275391</v>
+        <v>205.0899963378906</v>
       </c>
       <c r="D17">
-        <v>194.8200073242188</v>
+        <v>205.1000061035156</v>
       </c>
       <c r="E17">
-        <v>205.0899963378906</v>
+        <v>198.1600036621094</v>
       </c>
       <c r="F17">
-        <v>205.1000061035156</v>
+        <v>203.0099945068359</v>
       </c>
       <c r="G17">
-        <v>198.1600036621094</v>
+        <v>199.8699951171875</v>
       </c>
       <c r="H17">
-        <v>203.0099945068359</v>
+        <v>193.7200012207031</v>
       </c>
       <c r="I17">
-        <v>199.8699951171875</v>
+        <v>187.9600067138672</v>
       </c>
       <c r="J17">
-        <v>193.7200012207031</v>
+        <v>191.7899932861328</v>
       </c>
       <c r="K17">
-        <v>187.9600067138672</v>
+        <v>192.8399963378906</v>
       </c>
       <c r="L17">
-        <v>191.7899932861328</v>
+        <v>192.9100036621094</v>
       </c>
       <c r="M17">
-        <v>192.8399963378906</v>
+        <v>192.6399993896484</v>
       </c>
       <c r="N17">
-        <v>192.9100036621094</v>
+        <v>190.8899993896484</v>
       </c>
       <c r="O17">
-        <v>192.6399993896484</v>
+        <v>193.1399993896484</v>
       </c>
       <c r="P17">
-        <v>190.8899993896484</v>
+        <v>188.2899932861328</v>
       </c>
       <c r="Q17">
-        <v>193.1399993896484</v>
+        <v>205</v>
       </c>
       <c r="R17">
-        <v>188.2899932861328</v>
+        <v>213.2400054931641</v>
       </c>
       <c r="S17">
+        <v>219.3999938964844</v>
+      </c>
+      <c r="T17">
+        <v>223.2200012207031</v>
+      </c>
+      <c r="U17">
+        <v>224.9900054931641</v>
+      </c>
+      <c r="V17">
+        <v>224.8399963378906</v>
+      </c>
+      <c r="W17">
+        <v>227.6900024414062</v>
+      </c>
+      <c r="X17">
+        <v>215.5899963378906</v>
+      </c>
+      <c r="Y17">
+        <v>213.6300048828125</v>
+      </c>
+      <c r="Z17">
+        <v>207.1300048828125</v>
+      </c>
+      <c r="AA17">
+        <v>213.25</v>
+      </c>
+      <c r="AB17">
+        <v>221.6600036621094</v>
+      </c>
+      <c r="AC17">
+        <v>218.2200012207031</v>
+      </c>
+      <c r="AD17">
+        <v>211.0599975585938</v>
+      </c>
+      <c r="AE17">
         <v>205</v>
       </c>
-      <c r="T17">
-        <v>213.2400054931641</v>
-      </c>
-      <c r="U17">
-        <v>219.3999938964844</v>
-      </c>
-      <c r="V17">
-        <v>223.2200012207031</v>
-      </c>
-      <c r="W17">
-        <v>224.9900054931641</v>
-      </c>
-      <c r="X17">
-        <v>224.8399963378906</v>
-      </c>
-      <c r="Y17">
-        <v>227.6900024414062</v>
-      </c>
-      <c r="Z17">
-        <v>215.5899963378906</v>
-      </c>
-      <c r="AA17">
-        <v>213.6300048828125</v>
-      </c>
-      <c r="AB17">
-        <v>207.1300048828125</v>
-      </c>
-      <c r="AC17">
-        <v>213.25</v>
-      </c>
-      <c r="AD17">
-        <v>221.6600036621094</v>
-      </c>
-      <c r="AE17">
-        <v>218.2200012207031</v>
-      </c>
       <c r="AF17">
-        <v>211.0599975585938</v>
+        <v>201.2700042724609</v>
       </c>
       <c r="AG17">
-        <v>205</v>
+        <v>206.4499969482422</v>
       </c>
       <c r="AH17">
-        <v>201.2700042724609</v>
+        <v>208.2100067138672</v>
       </c>
       <c r="AI17">
-        <v>206.4499969482422</v>
+        <v>222.2899932861328</v>
       </c>
       <c r="AJ17">
-        <v>208.2100067138672</v>
+        <v>228.9299926757812</v>
       </c>
       <c r="AK17">
-        <v>222.2899932861328</v>
+        <v>245.1799926757812</v>
       </c>
       <c r="AL17">
-        <v>228.9299926757812</v>
+        <v>239.6199951171875</v>
       </c>
       <c r="AM17">
-        <v>245.1799926757812</v>
+        <v>238.8200073242188</v>
       </c>
       <c r="AN17">
-        <v>239.6199951171875</v>
+        <v>247.4600067138672</v>
       </c>
       <c r="AO17">
-        <v>238.8200073242188</v>
+        <v>255.3800048828125</v>
       </c>
       <c r="AP17">
-        <v>247.4600067138672</v>
+        <v>273.8999938964844</v>
       </c>
       <c r="AQ17">
-        <v>255.3800048828125</v>
+        <v>270</v>
       </c>
       <c r="AR17">
-        <v>273.8999938964844</v>
+        <v>271.8999938964844</v>
       </c>
       <c r="AS17">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AT17">
-        <v>271.8999938964844</v>
+        <v>273.6799926757812</v>
       </c>
       <c r="AU17">
-        <v>272</v>
+        <v>265.7200012207031</v>
       </c>
       <c r="AV17">
-        <v>273.6799926757812</v>
+        <v>273.0400085449219</v>
       </c>
       <c r="AW17">
-        <v>265.7200012207031</v>
+        <v>293.6900024414062</v>
       </c>
       <c r="AX17">
-        <v>273.0400085449219</v>
+        <v>273.5400085449219</v>
       </c>
       <c r="AY17">
-        <v>293.6900024414062</v>
+        <v>267.760009765625</v>
       </c>
       <c r="AZ17">
-        <v>273.5400085449219</v>
+        <v>264.5700073242188</v>
       </c>
       <c r="BA17">
-        <v>267.760009765625</v>
+        <v>278.1700134277344</v>
       </c>
       <c r="BB17">
-        <v>264.5700073242188</v>
+        <v>276.6700134277344</v>
       </c>
       <c r="BC17">
-        <v>278.1700134277344</v>
+        <v>271.1799926757812</v>
       </c>
       <c r="BD17">
-        <v>276.6700134277344</v>
+        <v>271.760009765625</v>
       </c>
       <c r="BE17">
-        <v>271.1799926757812</v>
+        <v>267.9299926757812</v>
       </c>
       <c r="BF17">
-        <v>271.760009765625</v>
+        <v>262.5400085449219</v>
       </c>
       <c r="BG17">
+        <v>262.6600036621094</v>
+      </c>
+      <c r="BH17">
         <v>267.9299926757812</v>
       </c>
-      <c r="BH17">
-        <v>262.5400085449219</v>
-      </c>
-      <c r="BI17">
-        <v>262.6600036621094</v>
-      </c>
-    </row>
-    <row r="18" spans="1:61">
+    </row>
+    <row r="18" spans="1:60">
       <c r="A18" t="s">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>125.5400009155273</v>
+        <v>128.9499969482422</v>
       </c>
       <c r="C18">
-        <v>126.7600021362305</v>
+        <v>128.5700073242188</v>
       </c>
       <c r="D18">
-        <v>128.9499969482422</v>
+        <v>127.2099990844727</v>
       </c>
       <c r="E18">
-        <v>128.5700073242188</v>
+        <v>129.3500061035156</v>
       </c>
       <c r="F18">
-        <v>127.2099990844727</v>
+        <v>130.7100067138672</v>
       </c>
       <c r="G18">
-        <v>129.3500061035156</v>
+        <v>128.7599945068359</v>
       </c>
       <c r="H18">
-        <v>130.7100067138672</v>
+        <v>129.6799926757812</v>
       </c>
       <c r="I18">
-        <v>128.7599945068359</v>
+        <v>130.8999938964844</v>
       </c>
       <c r="J18">
-        <v>129.6799926757812</v>
+        <v>129.3699951171875</v>
       </c>
       <c r="K18">
-        <v>130.8999938964844</v>
+        <v>128.0599975585938</v>
       </c>
       <c r="L18">
-        <v>129.3699951171875</v>
+        <v>128.6100006103516</v>
       </c>
       <c r="M18">
-        <v>128.0599975585938</v>
+        <v>129.5299987792969</v>
       </c>
       <c r="N18">
-        <v>128.6100006103516</v>
+        <v>129.3899993896484</v>
       </c>
       <c r="O18">
-        <v>129.5299987792969</v>
+        <v>129.5399932861328</v>
       </c>
       <c r="P18">
-        <v>129.3899993896484</v>
+        <v>130.4799957275391</v>
       </c>
       <c r="Q18">
-        <v>129.5399932861328</v>
+        <v>131.8399963378906</v>
       </c>
       <c r="R18">
-        <v>130.4799957275391</v>
+        <v>128.4499969482422</v>
       </c>
       <c r="S18">
-        <v>131.8399963378906</v>
+        <v>131.4799957275391</v>
       </c>
       <c r="T18">
-        <v>128.4499969482422</v>
+        <v>136.75</v>
       </c>
       <c r="U18">
-        <v>131.4799957275391</v>
+        <v>134.4799957275391</v>
       </c>
       <c r="V18">
-        <v>136.75</v>
+        <v>132.1799926757812</v>
       </c>
       <c r="W18">
-        <v>134.4799957275391</v>
+        <v>127</v>
       </c>
       <c r="X18">
-        <v>132.1799926757812</v>
+        <v>128.2599945068359</v>
       </c>
       <c r="Y18">
-        <v>127</v>
+        <v>126.5899963378906</v>
       </c>
       <c r="Z18">
-        <v>128.2599945068359</v>
+        <v>131.7100067138672</v>
       </c>
       <c r="AA18">
-        <v>126.5899963378906</v>
+        <v>131.9100036621094</v>
       </c>
       <c r="AB18">
-        <v>131.7100067138672</v>
+        <v>131.0399932861328</v>
       </c>
       <c r="AC18">
-        <v>131.9100036621094</v>
+        <v>131.4199981689453</v>
       </c>
       <c r="AD18">
-        <v>131.0399932861328</v>
+        <v>124.0400009155273</v>
       </c>
       <c r="AE18">
-        <v>131.4199981689453</v>
+        <v>118.3899993896484</v>
       </c>
       <c r="AF18">
-        <v>124.0400009155273</v>
+        <v>118.6600036621094</v>
       </c>
       <c r="AG18">
-        <v>118.3899993896484</v>
+        <v>118.1699981689453</v>
       </c>
       <c r="AH18">
-        <v>118.6600036621094</v>
+        <v>119.1699981689453</v>
       </c>
       <c r="AI18">
-        <v>118.1699981689453</v>
+        <v>112.7900009155273</v>
       </c>
       <c r="AJ18">
-        <v>119.1699981689453</v>
+        <v>112.4000015258789</v>
       </c>
       <c r="AK18">
-        <v>112.7900009155273</v>
+        <v>114.4000015258789</v>
       </c>
       <c r="AL18">
-        <v>112.4000015258789</v>
+        <v>111.9599990844727</v>
       </c>
       <c r="AM18">
-        <v>114.4000015258789</v>
+        <v>112.3300018310547</v>
       </c>
       <c r="AN18">
-        <v>111.9599990844727</v>
+        <v>115.0400009155273</v>
       </c>
       <c r="AO18">
-        <v>112.3300018310547</v>
+        <v>113.1600036621094</v>
       </c>
       <c r="AP18">
-        <v>115.0400009155273</v>
+        <v>113.5</v>
       </c>
       <c r="AQ18">
-        <v>113.1600036621094</v>
+        <v>114.0699996948242</v>
       </c>
       <c r="AR18">
-        <v>113.5</v>
+        <v>116.0199966430664</v>
       </c>
       <c r="AS18">
-        <v>114.0699996948242</v>
+        <v>113.3000030517578</v>
       </c>
       <c r="AT18">
-        <v>116.0199966430664</v>
+        <v>114.0199966430664</v>
       </c>
       <c r="AU18">
-        <v>113.3000030517578</v>
+        <v>114.4300003051758</v>
       </c>
       <c r="AV18">
-        <v>114.0199966430664</v>
+        <v>112.1600036621094</v>
       </c>
       <c r="AW18">
-        <v>114.4300003051758</v>
+        <v>113.1900024414062</v>
       </c>
       <c r="AX18">
-        <v>112.1600036621094</v>
+        <v>116.1900024414062</v>
       </c>
       <c r="AY18">
-        <v>113.1900024414062</v>
+        <v>116.3000030517578</v>
       </c>
       <c r="AZ18">
-        <v>116.1900024414062</v>
+        <v>118.620002746582</v>
       </c>
       <c r="BA18">
-        <v>116.3000030517578</v>
+        <v>118.6399993896484</v>
       </c>
       <c r="BB18">
-        <v>118.620002746582</v>
+        <v>117.6100006103516</v>
       </c>
       <c r="BC18">
-        <v>118.6399993896484</v>
+        <v>116.2799987792969</v>
       </c>
       <c r="BD18">
-        <v>117.6100006103516</v>
+        <v>121.7600021362305</v>
       </c>
       <c r="BE18">
-        <v>116.2799987792969</v>
+        <v>124.4100036621094</v>
       </c>
       <c r="BF18">
-        <v>121.7600021362305</v>
+        <v>124.1800003051758</v>
       </c>
       <c r="BG18">
-        <v>124.4100036621094</v>
+        <v>123.1500015258789</v>
       </c>
       <c r="BH18">
-        <v>124.1800003051758</v>
-      </c>
-      <c r="BI18">
-        <v>123.1500015258789</v>
-      </c>
-    </row>
-    <row r="19" spans="1:61">
+        <v>124.9599990844727</v>
+      </c>
+    </row>
+    <row r="19" spans="1:60">
       <c r="A19" t="s">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>200.1399993896484</v>
+        <v>209.2299957275391</v>
       </c>
       <c r="C19">
-        <v>205.6100006103516</v>
+        <v>207.9299926757812</v>
       </c>
       <c r="D19">
-        <v>209.2299957275391</v>
+        <v>202.9499969482422</v>
       </c>
       <c r="E19">
-        <v>207.9299926757812</v>
+        <v>201.8200073242188</v>
       </c>
       <c r="F19">
-        <v>202.9499969482422</v>
+        <v>208.4499969482422</v>
       </c>
       <c r="G19">
-        <v>201.8200073242188</v>
+        <v>206.6300048828125</v>
       </c>
       <c r="H19">
-        <v>208.4499969482422</v>
+        <v>206.2799987792969</v>
       </c>
       <c r="I19">
-        <v>206.6300048828125</v>
+        <v>207.9400024414062</v>
       </c>
       <c r="J19">
-        <v>206.2799987792969</v>
+        <v>207.1300048828125</v>
       </c>
       <c r="K19">
-        <v>207.9400024414062</v>
+        <v>203.8899993896484</v>
       </c>
       <c r="L19">
-        <v>207.1300048828125</v>
+        <v>208.8699951171875</v>
       </c>
       <c r="M19">
-        <v>203.8899993896484</v>
+        <v>210.6499938964844</v>
       </c>
       <c r="N19">
-        <v>208.8699951171875</v>
+        <v>209.8300018310547</v>
       </c>
       <c r="O19">
-        <v>210.6499938964844</v>
+        <v>209.1499938964844</v>
       </c>
       <c r="P19">
-        <v>209.8300018310547</v>
+        <v>212.5500030517578</v>
       </c>
       <c r="Q19">
-        <v>209.1499938964844</v>
+        <v>221.5599975585938</v>
       </c>
       <c r="R19">
-        <v>212.5500030517578</v>
+        <v>214.3500061035156</v>
       </c>
       <c r="S19">
-        <v>221.5599975585938</v>
+        <v>216.7799987792969</v>
       </c>
       <c r="T19">
-        <v>214.3500061035156</v>
+        <v>218.1199951171875</v>
       </c>
       <c r="U19">
-        <v>216.7799987792969</v>
+        <v>220.7700042724609</v>
       </c>
       <c r="V19">
-        <v>218.1199951171875</v>
+        <v>221.0700073242188</v>
       </c>
       <c r="W19">
-        <v>220.7700042724609</v>
+        <v>221.5</v>
       </c>
       <c r="X19">
-        <v>221.0700073242188</v>
+        <v>218.5</v>
       </c>
       <c r="Y19">
-        <v>221.5</v>
+        <v>216.6499938964844</v>
       </c>
       <c r="Z19">
-        <v>218.5</v>
+        <v>216.0399932861328</v>
       </c>
       <c r="AA19">
-        <v>216.6499938964844</v>
+        <v>222.6699981689453</v>
       </c>
       <c r="AB19">
-        <v>216.0399932861328</v>
+        <v>224.5099945068359</v>
       </c>
       <c r="AC19">
-        <v>222.6699981689453</v>
+        <v>220.8300018310547</v>
       </c>
       <c r="AD19">
-        <v>224.5099945068359</v>
+        <v>212.5</v>
       </c>
       <c r="AE19">
-        <v>220.8300018310547</v>
+        <v>210.7299957275391</v>
       </c>
       <c r="AF19">
-        <v>212.5</v>
+        <v>215.4299926757812</v>
       </c>
       <c r="AG19">
-        <v>210.7299957275391</v>
+        <v>217.1499938964844</v>
       </c>
       <c r="AH19">
-        <v>215.4299926757812</v>
+        <v>217.3600006103516</v>
       </c>
       <c r="AI19">
-        <v>217.1499938964844</v>
+        <v>216.1699981689453</v>
       </c>
       <c r="AJ19">
-        <v>217.3600006103516</v>
+        <v>216.0099945068359</v>
       </c>
       <c r="AK19">
-        <v>216.1699981689453</v>
+        <v>219.0500030517578</v>
       </c>
       <c r="AL19">
-        <v>216.0099945068359</v>
+        <v>215.5</v>
       </c>
       <c r="AM19">
-        <v>219.0500030517578</v>
+        <v>219.0700073242188</v>
       </c>
       <c r="AN19">
-        <v>215.5</v>
+        <v>225.3600006103516</v>
       </c>
       <c r="AO19">
-        <v>219.0700073242188</v>
+        <v>227.5299987792969</v>
       </c>
       <c r="AP19">
-        <v>225.3600006103516</v>
+        <v>226.3600006103516</v>
       </c>
       <c r="AQ19">
-        <v>227.5299987792969</v>
+        <v>227.6000061035156</v>
       </c>
       <c r="AR19">
-        <v>226.3600006103516</v>
+        <v>228.6900024414062</v>
       </c>
       <c r="AS19">
-        <v>227.6000061035156</v>
+        <v>227.0700073242188</v>
       </c>
       <c r="AT19">
-        <v>228.6900024414062</v>
+        <v>225.8800048828125</v>
       </c>
       <c r="AU19">
-        <v>227.0700073242188</v>
+        <v>222.8200073242188</v>
       </c>
       <c r="AV19">
-        <v>225.8800048828125</v>
+        <v>219.8800048828125</v>
       </c>
       <c r="AW19">
-        <v>222.8200073242188</v>
+        <v>223.5899963378906</v>
       </c>
       <c r="AX19">
-        <v>219.8800048828125</v>
+        <v>222.8899993896484</v>
       </c>
       <c r="AY19">
-        <v>223.5899963378906</v>
+        <v>222.1499938964844</v>
       </c>
       <c r="AZ19">
-        <v>222.8899993896484</v>
+        <v>218.4299926757812</v>
       </c>
       <c r="BA19">
-        <v>222.1499938964844</v>
+        <v>225.7100067138672</v>
       </c>
       <c r="BB19">
-        <v>218.4299926757812</v>
+        <v>229.4100036621094</v>
       </c>
       <c r="BC19">
-        <v>225.7100067138672</v>
+        <v>228.8999938964844</v>
       </c>
       <c r="BD19">
-        <v>229.4100036621094</v>
+        <v>232.8300018310547</v>
       </c>
       <c r="BE19">
-        <v>228.8999938964844</v>
+        <v>235.3500061035156</v>
       </c>
       <c r="BF19">
-        <v>232.8300018310547</v>
+        <v>232.6499938964844</v>
       </c>
       <c r="BG19">
-        <v>235.3500061035156</v>
+        <v>233.4799957275391</v>
       </c>
       <c r="BH19">
-        <v>232.6499938964844</v>
-      </c>
-      <c r="BI19">
-        <v>233.4799957275391</v>
-      </c>
-    </row>
-    <row r="20" spans="1:61">
+        <v>243.1000061035156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:60">
       <c r="A20" t="s">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>206.3214111328125</v>
+        <v>207.9755706787109</v>
       </c>
       <c r="C20">
-        <v>211.6625518798828</v>
+        <v>209.4005279541016</v>
       </c>
       <c r="D20">
-        <v>207.9755706787109</v>
+        <v>208.2745056152344</v>
       </c>
       <c r="E20">
-        <v>209.4005279541016</v>
+        <v>216.9139862060547</v>
       </c>
       <c r="F20">
-        <v>208.2745056152344</v>
+        <v>221.1291198730469</v>
       </c>
       <c r="G20">
-        <v>216.9139862060547</v>
+        <v>220.85009765625</v>
       </c>
       <c r="H20">
-        <v>221.1291198730469</v>
+        <v>219.225830078125</v>
       </c>
       <c r="I20">
-        <v>220.85009765625</v>
+        <v>216.9937133789062</v>
       </c>
       <c r="J20">
-        <v>219.225830078125</v>
+        <v>218.199462890625</v>
       </c>
       <c r="K20">
-        <v>216.9937133789062</v>
+        <v>218.3788146972656</v>
       </c>
       <c r="L20">
-        <v>218.199462890625</v>
+        <v>221.6572570800781</v>
       </c>
       <c r="M20">
-        <v>218.3788146972656</v>
+        <v>223.0423583984375</v>
       </c>
       <c r="N20">
-        <v>221.6572570800781</v>
+        <v>226.5399932861328</v>
       </c>
       <c r="O20">
-        <v>223.0423583984375</v>
+        <v>221.4499969482422</v>
       </c>
       <c r="P20">
-        <v>226.5399932861328</v>
+        <v>221.4700012207031</v>
       </c>
       <c r="Q20">
-        <v>221.4499969482422</v>
+        <v>220.7299957275391</v>
       </c>
       <c r="R20">
-        <v>221.4700012207031</v>
+        <v>212.4799957275391</v>
       </c>
       <c r="S20">
-        <v>220.7299957275391</v>
+        <v>217.9100036621094</v>
       </c>
       <c r="T20">
-        <v>212.4799957275391</v>
+        <v>216.2700042724609</v>
       </c>
       <c r="U20">
-        <v>217.9100036621094</v>
+        <v>216.2400054931641</v>
       </c>
       <c r="V20">
-        <v>216.2700042724609</v>
+        <v>217.2100067138672</v>
       </c>
       <c r="W20">
-        <v>216.2400054931641</v>
+        <v>216.6699981689453</v>
       </c>
       <c r="X20">
-        <v>217.2100067138672</v>
+        <v>215.6699981689453</v>
       </c>
       <c r="Y20">
-        <v>216.6699981689453</v>
+        <v>214.5099945068359</v>
       </c>
       <c r="Z20">
-        <v>215.6699981689453</v>
+        <v>211.3399963378906</v>
       </c>
       <c r="AA20">
-        <v>214.5099945068359</v>
+        <v>216.6000061035156</v>
       </c>
       <c r="AB20">
-        <v>211.3399963378906</v>
+        <v>220.5</v>
       </c>
       <c r="AC20">
-        <v>216.6000061035156</v>
+        <v>219.6000061035156</v>
       </c>
       <c r="AD20">
-        <v>220.5</v>
+        <v>213.9600067138672</v>
       </c>
       <c r="AE20">
-        <v>219.6000061035156</v>
+        <v>210.8600006103516</v>
       </c>
       <c r="AF20">
-        <v>213.9600067138672</v>
+        <v>207.1100006103516</v>
       </c>
       <c r="AG20">
-        <v>210.8600006103516</v>
+        <v>208.3000030517578</v>
       </c>
       <c r="AH20">
-        <v>207.1100006103516</v>
+        <v>206.6799926757812</v>
       </c>
       <c r="AI20">
-        <v>208.3000030517578</v>
+        <v>206.8500061035156</v>
       </c>
       <c r="AJ20">
-        <v>206.6799926757812</v>
+        <v>203.1900024414062</v>
       </c>
       <c r="AK20">
-        <v>206.8500061035156</v>
+        <v>202.0399932861328</v>
       </c>
       <c r="AL20">
-        <v>203.1900024414062</v>
+        <v>202.4299926757812</v>
       </c>
       <c r="AM20">
-        <v>202.0399932861328</v>
+        <v>204.9199981689453</v>
       </c>
       <c r="AN20">
-        <v>202.4299926757812</v>
+        <v>200.5500030517578</v>
       </c>
       <c r="AO20">
-        <v>204.9199981689453</v>
+        <v>196.1000061035156</v>
       </c>
       <c r="AP20">
-        <v>200.5500030517578</v>
+        <v>196.6100006103516</v>
       </c>
       <c r="AQ20">
-        <v>196.1000061035156</v>
+        <v>200.1999969482422</v>
       </c>
       <c r="AR20">
-        <v>196.6100006103516</v>
+        <v>196.4600067138672</v>
       </c>
       <c r="AS20">
-        <v>200.1999969482422</v>
+        <v>196.4600067138672</v>
       </c>
       <c r="AT20">
-        <v>196.4600067138672</v>
+        <v>193.0700073242188</v>
       </c>
       <c r="AU20">
-        <v>196.4600067138672</v>
+        <v>194.4799957275391</v>
       </c>
       <c r="AV20">
-        <v>193.0700073242188</v>
+        <v>194.7200012207031</v>
       </c>
       <c r="AW20">
-        <v>194.4799957275391</v>
+        <v>195.1399993896484</v>
       </c>
       <c r="AX20">
-        <v>194.7200012207031</v>
+        <v>195.8200073242188</v>
       </c>
       <c r="AY20">
-        <v>195.1399993896484</v>
+        <v>195.9100036621094</v>
       </c>
       <c r="AZ20">
-        <v>195.8200073242188</v>
+        <v>199.3999938964844</v>
       </c>
       <c r="BA20">
-        <v>195.9100036621094</v>
+        <v>199.2599945068359</v>
       </c>
       <c r="BB20">
-        <v>199.3999938964844</v>
+        <v>201.1399993896484</v>
       </c>
       <c r="BC20">
-        <v>199.2599945068359</v>
+        <v>198.0700073242188</v>
       </c>
       <c r="BD20">
-        <v>201.1399993896484</v>
+        <v>194.3500061035156</v>
       </c>
       <c r="BE20">
-        <v>198.0700073242188</v>
+        <v>198.8600006103516</v>
       </c>
       <c r="BF20">
-        <v>194.3500061035156</v>
+        <v>201.7400054931641</v>
       </c>
       <c r="BG20">
-        <v>198.8600006103516</v>
+        <v>199.8300018310547</v>
       </c>
       <c r="BH20">
-        <v>201.7400054931641</v>
-      </c>
-      <c r="BI20">
-        <v>199.8300018310547</v>
-      </c>
-    </row>
-    <row r="21" spans="1:61">
+        <v>201.5599975585938</v>
+      </c>
+    </row>
+    <row r="21" spans="1:60">
       <c r="A21" t="s">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>48.06841659545898</v>
+        <v>44.32787704467773</v>
       </c>
       <c r="C21">
-        <v>45.47497940063477</v>
+        <v>47.02106857299805</v>
       </c>
       <c r="D21">
-        <v>44.32787704467773</v>
+        <v>47.77915191650391</v>
       </c>
       <c r="E21">
-        <v>47.02106857299805</v>
+        <v>50.11325073242188</v>
       </c>
       <c r="F21">
-        <v>47.77915191650391</v>
+        <v>52.2578239440918</v>
       </c>
       <c r="G21">
-        <v>50.11325073242188</v>
+        <v>53.08573150634766</v>
       </c>
       <c r="H21">
-        <v>52.2578239440918</v>
+        <v>52.29772186279297</v>
       </c>
       <c r="I21">
         <v>53.08573150634766</v>
       </c>
       <c r="J21">
+        <v>54.54204559326172</v>
+      </c>
+      <c r="K21">
+        <v>54.24280166625977</v>
+      </c>
+      <c r="L21">
+        <v>58.64167785644531</v>
+      </c>
+      <c r="M21">
+        <v>59.6690788269043</v>
+      </c>
+      <c r="N21">
+        <v>58.5618782043457</v>
+      </c>
+      <c r="O21">
+        <v>57.46465301513672</v>
+      </c>
+      <c r="P21">
+        <v>55.54949569702148</v>
+      </c>
+      <c r="Q21">
+        <v>52.99595642089844</v>
+      </c>
+      <c r="R21">
+        <v>52.75656127929688</v>
+      </c>
+      <c r="S21">
+        <v>53.31515121459961</v>
+      </c>
+      <c r="T21">
         <v>52.29772186279297</v>
       </c>
-      <c r="K21">
-        <v>53.08573150634766</v>
-      </c>
-      <c r="L21">
-        <v>54.54204559326172</v>
-      </c>
-      <c r="M21">
-        <v>54.24280166625977</v>
-      </c>
-      <c r="N21">
-        <v>58.64167785644531</v>
-      </c>
-      <c r="O21">
-        <v>59.6690788269043</v>
-      </c>
-      <c r="P21">
-        <v>58.5618782043457</v>
-      </c>
-      <c r="Q21">
-        <v>57.46465301513672</v>
-      </c>
-      <c r="R21">
-        <v>55.54949569702148</v>
-      </c>
-      <c r="S21">
-        <v>52.99595642089844</v>
-      </c>
-      <c r="T21">
-        <v>52.75656127929688</v>
-      </c>
       <c r="U21">
-        <v>53.31515121459961</v>
+        <v>53.30517196655273</v>
       </c>
       <c r="V21">
-        <v>52.29772186279297</v>
+        <v>55.09065628051758</v>
       </c>
       <c r="W21">
-        <v>53.30517196655273</v>
+        <v>54.27272796630859</v>
       </c>
       <c r="X21">
-        <v>55.09065628051758</v>
+        <v>52.17802429199219</v>
       </c>
       <c r="Y21">
-        <v>54.27272796630859</v>
+        <v>52.10820388793945</v>
       </c>
       <c r="Z21">
-        <v>52.17802429199219</v>
+        <v>50.74165725708008</v>
       </c>
       <c r="AA21">
-        <v>52.10820388793945</v>
+        <v>51.69923782348633</v>
       </c>
       <c r="AB21">
-        <v>50.74165725708008</v>
+        <v>54.30265045166016</v>
       </c>
       <c r="AC21">
-        <v>51.69923782348633</v>
+        <v>51.86880493164062</v>
       </c>
       <c r="AD21">
-        <v>54.30265045166016</v>
+        <v>55.88863754272461</v>
       </c>
       <c r="AE21">
-        <v>51.86880493164062</v>
+        <v>58.75139999389648</v>
       </c>
       <c r="AF21">
-        <v>55.88863754272461</v>
+        <v>55.08068466186523</v>
       </c>
       <c r="AG21">
-        <v>58.75139999389648</v>
+        <v>61.933349609375</v>
       </c>
       <c r="AH21">
-        <v>55.08068466186523</v>
+        <v>55.27020263671875</v>
       </c>
       <c r="AI21">
-        <v>61.933349609375</v>
+        <v>55.73901748657227</v>
       </c>
       <c r="AJ21">
-        <v>55.27020263671875</v>
+        <v>56.5369987487793</v>
       </c>
       <c r="AK21">
-        <v>55.73901748657227</v>
+        <v>61.04000091552734</v>
       </c>
       <c r="AL21">
-        <v>56.5369987487793</v>
+        <v>60.7599983215332</v>
       </c>
       <c r="AM21">
-        <v>61.04000091552734</v>
+        <v>61.75</v>
       </c>
       <c r="AN21">
-        <v>60.7599983215332</v>
+        <v>61.02999877929688</v>
       </c>
       <c r="AO21">
-        <v>61.75</v>
+        <v>62.33000183105469</v>
       </c>
       <c r="AP21">
-        <v>61.02999877929688</v>
+        <v>63.52000045776367</v>
       </c>
       <c r="AQ21">
-        <v>62.33000183105469</v>
+        <v>62.93999862670898</v>
       </c>
       <c r="AR21">
-        <v>63.52000045776367</v>
+        <v>62.63000106811523</v>
       </c>
       <c r="AS21">
-        <v>62.93999862670898</v>
+        <v>61.4900016784668</v>
       </c>
       <c r="AT21">
-        <v>62.63000106811523</v>
+        <v>63.88999938964844</v>
       </c>
       <c r="AU21">
-        <v>61.4900016784668</v>
+        <v>64.58000183105469</v>
       </c>
       <c r="AV21">
-        <v>63.88999938964844</v>
+        <v>69.33000183105469</v>
       </c>
       <c r="AW21">
-        <v>64.58000183105469</v>
+        <v>68.36000061035156</v>
       </c>
       <c r="AX21">
-        <v>69.33000183105469</v>
+        <v>70.48000335693359</v>
       </c>
       <c r="AY21">
-        <v>68.36000061035156</v>
+        <v>72.08999633789062</v>
       </c>
       <c r="AZ21">
-        <v>70.48000335693359</v>
+        <v>71</v>
       </c>
       <c r="BA21">
-        <v>72.08999633789062</v>
+        <v>73.45999908447266</v>
       </c>
       <c r="BB21">
-        <v>71</v>
+        <v>70.33000183105469</v>
       </c>
       <c r="BC21">
-        <v>73.45999908447266</v>
+        <v>68.80999755859375</v>
       </c>
       <c r="BD21">
-        <v>70.33000183105469</v>
+        <v>63.11000061035156</v>
       </c>
       <c r="BE21">
-        <v>68.80999755859375</v>
+        <v>58.63000106811523</v>
       </c>
       <c r="BF21">
-        <v>63.11000061035156</v>
+        <v>55.13000106811523</v>
       </c>
       <c r="BG21">
-        <v>58.63000106811523</v>
+        <v>55.86999893188477</v>
       </c>
       <c r="BH21">
-        <v>55.13000106811523</v>
-      </c>
-      <c r="BI21">
-        <v>55.86999893188477</v>
+        <v>56.09000015258789</v>
       </c>
     </row>
   </sheetData>

--- a/Portfolio.xlsx
+++ b/Portfolio.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="271">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="273">
   <si>
     <t>SNDK</t>
   </si>
@@ -391,6 +391,9 @@
     <t>2026-10-21</t>
   </si>
   <si>
+    <t>2026-10-22</t>
+  </si>
+  <si>
     <t>Скрин дня</t>
   </si>
   <si>
@@ -475,6 +478,15 @@
     <t>Zebra Technologies</t>
   </si>
   <si>
+    <t>Dell Technologies</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Gartner</t>
+  </si>
+  <si>
     <t>CVX</t>
   </si>
   <si>
@@ -487,61 +499,85 @@
     <t>Lilly (Eli)</t>
   </si>
   <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Gartner</t>
-  </si>
-  <si>
-    <t>Dell Technologies</t>
-  </si>
-  <si>
     <t>EOG</t>
   </si>
   <si>
     <t>EOG Resources</t>
   </si>
   <si>
+    <t>VEEV</t>
+  </si>
+  <si>
+    <t>Veeva Systems</t>
+  </si>
+  <si>
+    <t>TWLO</t>
+  </si>
+  <si>
+    <t>Twilio</t>
+  </si>
+  <si>
+    <t>WSM</t>
+  </si>
+  <si>
+    <t>Williams-Sonoma, Inc.</t>
+  </si>
+  <si>
     <t>COP</t>
   </si>
   <si>
     <t>ConocoPhillips</t>
   </si>
   <si>
-    <t>WSM</t>
-  </si>
-  <si>
-    <t>Williams-Sonoma, Inc.</t>
-  </si>
-  <si>
     <t>NWSA</t>
   </si>
   <si>
     <t>News Corp (Class A)</t>
   </si>
   <si>
+    <t>VRSN</t>
+  </si>
+  <si>
+    <t>Verisign</t>
+  </si>
+  <si>
+    <t>REGN</t>
+  </si>
+  <si>
+    <t>Regeneron Pharmaceuticals</t>
+  </si>
+  <si>
     <t>SJM</t>
   </si>
   <si>
     <t>J.M. Smucker Company (The)</t>
   </si>
   <si>
-    <t>REGN</t>
-  </si>
-  <si>
-    <t>Regeneron Pharmaceuticals</t>
-  </si>
-  <si>
     <t>BMY</t>
   </si>
   <si>
     <t>Bristol Myers Squibb</t>
   </si>
   <si>
-    <t>VEEV</t>
-  </si>
-  <si>
-    <t>Veeva Systems</t>
+    <t>SWK</t>
+  </si>
+  <si>
+    <t>Stanley Black &amp; Decker</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
+  </si>
+  <si>
+    <t>AMGN</t>
+  </si>
+  <si>
+    <t>Amgen</t>
   </si>
   <si>
     <t>WBD</t>
@@ -553,36 +589,6 @@
     <t>Unknown</t>
   </si>
   <si>
-    <t>TWLO</t>
-  </si>
-  <si>
-    <t>Twilio</t>
-  </si>
-  <si>
-    <t>AMGN</t>
-  </si>
-  <si>
-    <t>Amgen</t>
-  </si>
-  <si>
-    <t>EXPE</t>
-  </si>
-  <si>
-    <t>Expedia Group</t>
-  </si>
-  <si>
-    <t>DVN</t>
-  </si>
-  <si>
-    <t>Devon Energy</t>
-  </si>
-  <si>
-    <t>MO</t>
-  </si>
-  <si>
-    <t>Altria</t>
-  </si>
-  <si>
     <t>Факторы и самообучение</t>
   </si>
   <si>
@@ -661,7 +667,7 @@
     <t>Бумажный портфель S&amp;P 500</t>
   </si>
   <si>
-    <t>Обновлено 2026-10-22 00:43 UTC · данные на 2026-10-21 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
+    <t>Обновлено 2026-10-23 00:43 UTC · данные на 2026-10-22 · стратегия «ladder-momentum-value» · все сделки виртуальные</t>
   </si>
   <si>
     <t>Доходность</t>
@@ -745,7 +751,7 @@
     <t>Время запуска (UTC)</t>
   </si>
   <si>
-    <t>2026-10-22 00:43 UTC</t>
+    <t>2026-10-23 00:43 UTC</t>
   </si>
   <si>
     <t>Дата данных</t>
@@ -1292,9 +1298,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$35</c:f>
+              <c:f>Капитал!$A$5:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1387,16 +1393,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>2026-10-21</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026-10-22</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$35</c:f>
+              <c:f>Капитал!$D$5:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -1488,6 +1497,9 @@
                   <c:v>10374.140000000001</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>10374.140000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>10374.140000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -1513,9 +1525,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$35</c:f>
+              <c:f>Капитал!$A$5:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1608,16 +1620,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>2026-10-21</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026-10-22</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$35</c:f>
+              <c:f>Капитал!$F$5:$F$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -1709,6 +1724,9 @@
                   <c:v>10064.36</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -1849,9 +1867,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$35</c:f>
+              <c:f>Капитал!$A$5:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -1944,16 +1962,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>2026-10-21</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026-10-22</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$D$5:$D$35</c:f>
+              <c:f>Капитал!$D$5:$D$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>10000.0</c:v>
                 </c:pt>
@@ -2045,6 +2066,9 @@
                   <c:v>10374.140000000001</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>10374.140000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>10374.140000000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -2070,9 +2094,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Капитал!$A$5:$A$35</c:f>
+              <c:f>Капитал!$A$5:$A$36</c:f>
               <c:strCache>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>2026-08-24</c:v>
                 </c:pt>
@@ -2165,16 +2189,19 @@
                 </c:pt>
                 <c:pt idx="30">
                   <c:v>2026-10-21</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2026-10-22</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Капитал!$F$5:$F$35</c:f>
+              <c:f>Капитал!$F$5:$F$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="31"/>
+                <c:ptCount val="32"/>
                 <c:pt idx="0">
                   <c:v>10000</c:v>
                 </c:pt>
@@ -2266,6 +2293,9 @@
                   <c:v>10064.36</c:v>
                 </c:pt>
                 <c:pt idx="30">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="31">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2761,12 +2791,12 @@
   <sheetData>
     <row r="2" spans="2:8">
       <c r="B2" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5" spans="2:8">
@@ -2774,13 +2804,13 @@
         <v>102</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" spans="2:8">
@@ -2799,21 +2829,21 @@
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="7">
-        <v>3.158439774689714</v>
+        <v>3.105097671378445</v>
       </c>
       <c r="D9" s="7">
         <v>2</v>
@@ -2827,7 +2857,7 @@
     </row>
     <row r="12" spans="2:8">
       <c r="B12" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="2:8">
@@ -2856,7 +2886,7 @@
     </row>
     <row r="16" spans="2:8">
       <c r="B16" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C16" s="11">
         <v>10000</v>
@@ -2864,7 +2894,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="B17" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C17" s="12">
         <v>21</v>
@@ -2872,7 +2902,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="B18" s="10" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C18" s="12">
         <v>0</v>
@@ -2880,7 +2910,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="B19" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C19" s="12">
         <v>2</v>
@@ -2888,15 +2918,15 @@
     </row>
     <row r="20" spans="1:3">
       <c r="B20" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="B21" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C21" s="13">
         <v>22</v>
@@ -2904,7 +2934,7 @@
     </row>
     <row r="22" spans="1:3">
       <c r="B22" s="10" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C22" s="14">
         <v>0.210302</v>
@@ -2912,7 +2942,7 @@
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="10" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C23" s="14">
         <v>0</v>
@@ -2920,31 +2950,31 @@
     </row>
     <row r="24" spans="1:3">
       <c r="B24" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="B25" s="10" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C25" s="15">
-        <v>0.09930079145385329</v>
+        <v>0.09774838832025239</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="B26" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C26" s="12">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="B28" s="16" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C28" s="11">
         <f>C13+IFERROR(SUM('Позиции'!I5:I200),0)</f>
@@ -2953,12 +2983,12 @@
     </row>
     <row r="29" spans="1:3">
       <c r="B29" s="17" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" spans="1:3">
       <c r="B31" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="30" customHeight="1">
@@ -3153,7 +3183,7 @@
         <v>-0.11551777832687689</v>
       </c>
       <c r="L5" s="12">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M5" s="10" t="s">
         <v>43</v>
@@ -3206,7 +3236,7 @@
         <v>-0.23851334699505075</v>
       </c>
       <c r="L6" s="12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M6" s="10" t="s">
         <v>43</v>
@@ -3259,7 +3289,7 @@
         <v>0.2031746616047501</v>
       </c>
       <c r="L7" s="12">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>43</v>
@@ -3312,7 +3342,7 @@
         <v>0.24337509372837138</v>
       </c>
       <c r="L8" s="12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>43</v>
@@ -3365,7 +3395,7 @@
         <v>0.04272551403482912</v>
       </c>
       <c r="L9" s="12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>43</v>
@@ -3418,7 +3448,7 @@
         <v>0.15340792445550722</v>
       </c>
       <c r="L10" s="12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M10" s="10" t="s">
         <v>43</v>
@@ -3471,7 +3501,7 @@
         <v>0.13862477289477573</v>
       </c>
       <c r="L11" s="12">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M11" s="10" t="s">
         <v>43</v>
@@ -3524,7 +3554,7 @@
         <v>0.027180023803650654</v>
       </c>
       <c r="L12" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>43</v>
@@ -3577,7 +3607,7 @@
         <v>0.005893924930109997</v>
       </c>
       <c r="L13" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>43</v>
@@ -3630,7 +3660,7 @@
         <v>0.0025921578099839296</v>
       </c>
       <c r="L14" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>43</v>
@@ -3683,7 +3713,7 @@
         <v>0.019101186256372128</v>
       </c>
       <c r="L15" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M15" s="10" t="s">
         <v>43</v>
@@ -3736,7 +3766,7 @@
         <v>0.009709630371900724</v>
       </c>
       <c r="L16" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M16" s="10" t="s">
         <v>43</v>
@@ -3789,7 +3819,7 @@
         <v>0.078916577376033</v>
       </c>
       <c r="L17" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>43</v>
@@ -3842,7 +3872,7 @@
         <v>-0.021625941570247907</v>
       </c>
       <c r="L18" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="10" t="s">
         <v>43</v>
@@ -3895,7 +3925,7 @@
         <v>-0.08166955526859504</v>
       </c>
       <c r="L19" s="12">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M19" s="10" t="s">
         <v>43</v>
@@ -3948,7 +3978,7 @@
         <v>0.042561413568448565</v>
       </c>
       <c r="L20" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M20" s="10" t="s">
         <v>43</v>
@@ -4001,7 +4031,7 @@
         <v>-0.039130372238321116</v>
       </c>
       <c r="L21" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M21" s="10" t="s">
         <v>43</v>
@@ -4054,7 +4084,7 @@
         <v>0.08687390276757277</v>
       </c>
       <c r="L22" s="12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M22" s="10" t="s">
         <v>43</v>
@@ -4107,7 +4137,7 @@
         <v>0.031349345455369874</v>
       </c>
       <c r="L23" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M23" s="10" t="s">
         <v>43</v>
@@ -4160,7 +4190,7 @@
         <v>0.005639950174490104</v>
       </c>
       <c r="L24" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M24" s="10" t="s">
         <v>43</v>
@@ -4213,7 +4243,7 @@
         <v>-0.2334648801857212</v>
       </c>
       <c r="L25" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>43</v>
@@ -4804,7 +4834,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5472,6 +5502,25 @@
         <v>21</v>
       </c>
       <c r="F35" s="11"/>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" s="11">
+        <v>550.02</v>
+      </c>
+      <c r="C36" s="11">
+        <v>9824.120000000001</v>
+      </c>
+      <c r="D36" s="11">
+        <f>B36+C36</f>
+        <v>10374.140000000001</v>
+      </c>
+      <c r="E36" s="12">
+        <v>21</v>
+      </c>
+      <c r="F36" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5500,12 +5549,12 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5522,52 +5571,52 @@
         <v>25</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F4" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I4" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J4" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K4" s="18" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L4" s="18" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M4" s="18" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N4" s="18" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P4" s="18" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Q4" s="18" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="R4" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="S4" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="T4" s="18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -5584,13 +5633,13 @@
         <v>48</v>
       </c>
       <c r="E5" s="11">
-        <v>475.0400085449219</v>
+        <v>467.9800109863281</v>
       </c>
       <c r="F5" s="20">
-        <v>1.02162863331401</v>
+        <v>1.011097959524074</v>
       </c>
       <c r="G5" s="13">
-        <v>0.5236085664662042</v>
+        <v>0.523608566466204</v>
       </c>
       <c r="H5" s="13">
         <v>-0.5744716818195363</v>
@@ -5599,16 +5648,16 @@
         <v>2.413793147558647</v>
       </c>
       <c r="J5" s="13">
-        <v>2.424088622739075</v>
+        <v>2.392148072639907</v>
       </c>
       <c r="K5" s="13">
-        <v>0.8962225452363762</v>
+        <v>0.8839823193387985</v>
       </c>
       <c r="L5" s="13">
-        <v>-0.1466178998668669</v>
+        <v>-0.1689095599462649</v>
       </c>
       <c r="M5" s="13">
-        <v>-0.600762157159024</v>
+        <v>-0.5775394327554261</v>
       </c>
       <c r="N5" s="13">
         <v>16.55367</v>
@@ -5623,13 +5672,13 @@
         <v>0.537</v>
       </c>
       <c r="R5" s="15">
-        <v>1.169996231181436</v>
+        <v>1.121188572354957</v>
       </c>
       <c r="S5" s="12">
-        <v>71.9518870688083</v>
+        <v>66.78460618245569</v>
       </c>
       <c r="T5" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -5646,13 +5695,13 @@
         <v>48</v>
       </c>
       <c r="E6" s="11">
-        <v>433.4200134277344</v>
+        <v>436.75</v>
       </c>
       <c r="F6" s="20">
-        <v>1.00742671778025</v>
+        <v>0.9891034579667707</v>
       </c>
       <c r="G6" s="13">
-        <v>0.5447519645801073</v>
+        <v>0.5447519645801074</v>
       </c>
       <c r="H6" s="13">
         <v>-0.6819902707968063</v>
@@ -5661,16 +5710,16 @@
         <v>2.840883602905277</v>
       </c>
       <c r="J6" s="13">
-        <v>2.279666813644417</v>
+        <v>2.271180198266574</v>
       </c>
       <c r="K6" s="13">
-        <v>0.7123554336706056</v>
+        <v>0.7010730251159257</v>
       </c>
       <c r="L6" s="13">
-        <v>-0.06128510060541172</v>
+        <v>-0.06534561176728722</v>
       </c>
       <c r="M6" s="13">
-        <v>-0.3913017863085151</v>
+        <v>-0.5685487301066682</v>
       </c>
       <c r="N6" s="13">
         <v>18.537308</v>
@@ -5685,13 +5734,13 @@
         <v>0.517</v>
       </c>
       <c r="R6" s="15">
-        <v>0.8730975486586645</v>
+        <v>0.8796763049267113</v>
       </c>
       <c r="S6" s="12">
-        <v>59.72260038199791</v>
+        <v>61.05748351729646</v>
       </c>
       <c r="T6" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -5708,10 +5757,10 @@
         <v>48</v>
       </c>
       <c r="E7" s="11">
-        <v>291.0299987792969</v>
+        <v>290.0700073242188</v>
       </c>
       <c r="F7" s="20">
-        <v>0.9012666888645469</v>
+        <v>0.8788400978163681</v>
       </c>
       <c r="G7" s="13">
         <v>0.3995021602593209</v>
@@ -5723,16 +5772,16 @@
         <v>2.38315886947137</v>
       </c>
       <c r="J7" s="13">
-        <v>2.129885985927741</v>
+        <v>2.084042430851917</v>
       </c>
       <c r="K7" s="13">
-        <v>0.8037214983684114</v>
+        <v>0.7919631373686495</v>
       </c>
       <c r="L7" s="13">
-        <v>0.3002571177441445</v>
+        <v>0.2764291552714828</v>
       </c>
       <c r="M7" s="13">
-        <v>-0.4512532024849496</v>
+        <v>-0.5241637456987043</v>
       </c>
       <c r="N7" s="13">
         <v>16.752573</v>
@@ -5747,13 +5796,13 @@
         <v>0.531</v>
       </c>
       <c r="R7" s="15">
-        <v>0.8490321223410933</v>
+        <v>0.8283639129392286</v>
       </c>
       <c r="S7" s="12">
-        <v>67.85634876364114</v>
+        <v>66.61925565753572</v>
       </c>
       <c r="T7" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
@@ -5761,61 +5810,61 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>10</v>
+        <v>91</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>62</v>
+        <v>141</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E8" s="11">
-        <v>70.80999755859375</v>
+        <v>913.6699829101562</v>
       </c>
       <c r="F8" s="20">
-        <v>0.8612283529725542</v>
+        <v>0.8358154946073425</v>
       </c>
       <c r="G8" s="13">
-        <v>1.285944045024201</v>
+        <v>0.0694139824523624</v>
       </c>
       <c r="H8" s="13">
-        <v>-1.369862149294123</v>
+        <v>2.150861358222542</v>
       </c>
       <c r="I8" s="13">
-        <v>-0.5769944704774098</v>
+        <v>4.140310964546267</v>
       </c>
       <c r="J8" s="13">
-        <v>1.431970504713593</v>
+        <v>0.9566221675422946</v>
       </c>
       <c r="K8" s="13">
-        <v>4.020317717707746</v>
+        <v>-0.3608170441224193</v>
       </c>
       <c r="L8" s="13">
-        <v>0.01426017586613477</v>
+        <v>-2.279066390893142</v>
       </c>
       <c r="M8" s="13">
-        <v>-0.07811340359971064</v>
+        <v>-0.5224069689840729</v>
       </c>
       <c r="N8" s="13">
-        <v>12.932518</v>
+        <v>11.82349</v>
       </c>
       <c r="O8" s="13">
-        <v>1.5142426</v>
+        <v>7.183</v>
       </c>
       <c r="P8" s="15">
-        <v>-0.20358999</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="Q8" s="15">
-        <v>0.046</v>
+        <v>3.793</v>
       </c>
       <c r="R8" s="15">
-        <v>0.8091466188760659</v>
+        <v>0.8748549043458309</v>
       </c>
       <c r="S8" s="12">
-        <v>65.82349156747074</v>
+        <v>40.46216665004615</v>
       </c>
       <c r="T8" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
@@ -5823,61 +5872,61 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="C9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="11">
+        <v>70.23999786376953</v>
+      </c>
+      <c r="F9" s="20">
+        <v>0.8251195971612808</v>
+      </c>
+      <c r="G9" s="13">
+        <v>1.285944045024201</v>
+      </c>
+      <c r="H9" s="13">
+        <v>-1.369862149294123</v>
+      </c>
+      <c r="I9" s="13">
+        <v>-0.5769944704774098</v>
+      </c>
+      <c r="J9" s="13">
+        <v>1.339006904433675</v>
+      </c>
+      <c r="K9" s="13">
+        <v>3.931815695950569</v>
+      </c>
+      <c r="L9" s="13">
+        <v>-0.02127116678775619</v>
+      </c>
+      <c r="M9" s="13">
+        <v>-0.02145781056475105</v>
+      </c>
+      <c r="N9" s="13">
+        <v>12.932518</v>
+      </c>
+      <c r="O9" s="13">
+        <v>1.5142426</v>
+      </c>
+      <c r="P9" s="15">
+        <v>-0.20358999</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>0.046</v>
+      </c>
+      <c r="R9" s="15">
+        <v>0.8042639946866648</v>
+      </c>
+      <c r="S9" s="12">
+        <v>63.26216589474755</v>
+      </c>
+      <c r="T9" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" s="11">
-        <v>896.0700073242188</v>
-      </c>
-      <c r="F9" s="20">
-        <v>0.8263449305218465</v>
-      </c>
-      <c r="G9" s="13">
-        <v>0.06941398245236211</v>
-      </c>
-      <c r="H9" s="13">
-        <v>2.150861358222542</v>
-      </c>
-      <c r="I9" s="13">
-        <v>4.140310964546267</v>
-      </c>
-      <c r="J9" s="13">
-        <v>0.9496485317648866</v>
-      </c>
-      <c r="K9" s="13">
-        <v>-0.3550952973640076</v>
-      </c>
-      <c r="L9" s="13">
-        <v>-2.402425417913452</v>
-      </c>
-      <c r="M9" s="13">
-        <v>-0.5307012357598754</v>
-      </c>
-      <c r="N9" s="13">
-        <v>11.82349</v>
-      </c>
-      <c r="O9" s="13">
-        <v>7.183</v>
-      </c>
-      <c r="P9" s="15">
-        <v>0.8826000000000001</v>
-      </c>
-      <c r="Q9" s="15">
-        <v>3.793</v>
-      </c>
-      <c r="R9" s="15">
-        <v>0.994634495377021</v>
-      </c>
-      <c r="S9" s="12">
-        <v>37.47218545377914</v>
-      </c>
-      <c r="T9" s="10" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
@@ -5885,19 +5934,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D10" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E10" s="11">
-        <v>242.4299926757812</v>
+        <v>241.7799987792969</v>
       </c>
       <c r="F10" s="20">
-        <v>0.8245631613952872</v>
+        <v>0.8064852210694181</v>
       </c>
       <c r="G10" s="13">
         <v>0.3943572019698282</v>
@@ -5909,16 +5958,16 @@
         <v>0.189405644478103</v>
       </c>
       <c r="J10" s="13">
-        <v>0.9283294872900161</v>
+        <v>0.8774312330102085</v>
       </c>
       <c r="K10" s="13">
-        <v>3.919815046540162</v>
+        <v>3.891824046559374</v>
       </c>
       <c r="L10" s="13">
-        <v>-1.662638548773036</v>
+        <v>-1.663791296142042</v>
       </c>
       <c r="M10" s="13">
-        <v>-0.004984262403811876</v>
+        <v>0.002760997570037553</v>
       </c>
       <c r="N10" s="13">
         <v>22.021957</v>
@@ -5933,13 +5982,13 @@
         <v>0.108</v>
       </c>
       <c r="R10" s="15">
-        <v>0.3012842406429017</v>
+        <v>0.2794018985826556</v>
       </c>
       <c r="S10" s="12">
-        <v>57.0718082607826</v>
+        <v>56.38415714974611</v>
       </c>
       <c r="T10" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
@@ -5956,13 +6005,13 @@
         <v>48</v>
       </c>
       <c r="E11" s="11">
-        <v>62.91999816894531</v>
+        <v>62.70000076293945</v>
       </c>
       <c r="F11" s="20">
-        <v>0.8097506512834178</v>
+        <v>0.7830053173330669</v>
       </c>
       <c r="G11" s="13">
-        <v>0.576507436874041</v>
+        <v>0.5765074368740414</v>
       </c>
       <c r="H11" s="13">
         <v>0.6147487778468856</v>
@@ -5971,16 +6020,16 @@
         <v>3.130834419306667</v>
       </c>
       <c r="J11" s="13">
-        <v>0.5721685710371798</v>
+        <v>0.4892301713641671</v>
       </c>
       <c r="K11" s="13">
-        <v>1.050580120378011</v>
+        <v>1.037535800908618</v>
       </c>
       <c r="L11" s="13">
-        <v>0.1661064945017811</v>
+        <v>0.1525679972570398</v>
       </c>
       <c r="M11" s="13">
-        <v>-0.1643813645837533</v>
+        <v>-0.1579586880516975</v>
       </c>
       <c r="N11" s="13">
         <v>17.721592</v>
@@ -5995,13 +6044,13 @@
         <v>0.534</v>
       </c>
       <c r="R11" s="15">
-        <v>0.1272976050367904</v>
+        <v>0.1091787068620307</v>
       </c>
       <c r="S11" s="12">
-        <v>65.50669954529533</v>
+        <v>64.0864479130996</v>
       </c>
       <c r="T11" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
@@ -6009,61 +6058,61 @@
         <v>8</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>18</v>
+        <v>144</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>76</v>
+        <v>145</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E12" s="11">
-        <v>243.1000061035156</v>
+        <v>114</v>
       </c>
       <c r="F12" s="20">
-        <v>0.7245767452322718</v>
+        <v>0.7044216088914989</v>
       </c>
       <c r="G12" s="13">
-        <v>0.1912118272149022</v>
+        <v>0.02344107793329732</v>
       </c>
       <c r="H12" s="13">
-        <v>0.02798143859882</v>
+        <v>1.649714100513951</v>
       </c>
       <c r="I12" s="13">
-        <v>-0.8777690799810213</v>
+        <v>0.05989924891666139</v>
       </c>
       <c r="J12" s="13">
-        <v>1.10966009767503</v>
+        <v>1.194645549235432</v>
       </c>
       <c r="K12" s="13">
-        <v>3.750702703186459</v>
+        <v>0</v>
       </c>
       <c r="L12" s="13">
-        <v>0.4954160794528933</v>
+        <v>0.07887143532089654</v>
       </c>
       <c r="M12" s="13">
-        <v>-0.4906103037022205</v>
+        <v>-0.2174813758406997</v>
       </c>
       <c r="N12" s="13">
-        <v>41.323265</v>
+        <v>17.76259</v>
       </c>
       <c r="O12" s="13">
-        <v>1.8231329</v>
+        <v>19.783653</v>
       </c>
       <c r="P12" s="15">
-        <v>0.04575</v>
+        <v>1.5956</v>
       </c>
       <c r="Q12" s="15">
-        <v>0.034</v>
+        <v>0.162</v>
       </c>
       <c r="R12" s="15">
-        <v>0.3073407372584185</v>
+        <v>0.2779611475113717</v>
       </c>
       <c r="S12" s="12">
-        <v>70.59042043375403</v>
+        <v>85.96903566373963</v>
       </c>
       <c r="T12" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
@@ -6071,61 +6120,61 @@
         <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E13" s="11">
-        <v>124.9599990844727</v>
+        <v>240.9799957275391</v>
       </c>
       <c r="F13" s="20">
-        <v>0.649106181081757</v>
+        <v>0.6866944184977725</v>
       </c>
       <c r="G13" s="13">
-        <v>0.3805332912349265</v>
+        <v>0.1912118272149021</v>
       </c>
       <c r="H13" s="13">
-        <v>-0.1243005063079742</v>
+        <v>0.02798143859882</v>
       </c>
       <c r="I13" s="13">
-        <v>0.4428140044701369</v>
+        <v>-0.8777690799810213</v>
       </c>
       <c r="J13" s="13">
-        <v>0.1752802356386171</v>
+        <v>0.9599761098776876</v>
       </c>
       <c r="K13" s="13">
-        <v>4.020317717707746</v>
+        <v>3.723592658663028</v>
       </c>
       <c r="L13" s="13">
-        <v>0.1296336842829748</v>
+        <v>0.4891881065874262</v>
       </c>
       <c r="M13" s="13">
-        <v>0.1677081418529904</v>
+        <v>-0.3574883872091777</v>
       </c>
       <c r="N13" s="13">
-        <v>15.125457</v>
+        <v>41.323265</v>
       </c>
       <c r="O13" s="13">
-        <v>6.804011</v>
+        <v>1.8231329</v>
       </c>
       <c r="P13" s="15">
-        <v>0.46032003</v>
+        <v>0.04575</v>
       </c>
       <c r="Q13" s="15">
-        <v>0.07000000000000001</v>
+        <v>0.034</v>
       </c>
       <c r="R13" s="15">
-        <v>0.2035057004795136</v>
+        <v>0.2678486159916791</v>
       </c>
       <c r="S13" s="12">
-        <v>61.94528186459848</v>
+        <v>67.09640674871019</v>
       </c>
       <c r="T13" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
@@ -6133,61 +6182,61 @@
         <v>10</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>13</v>
+        <v>146</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>67</v>
+        <v>147</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="E14" s="11">
-        <v>154</v>
+        <v>217.2100067138672</v>
       </c>
       <c r="F14" s="20">
-        <v>0.6428742209527081</v>
+        <v>0.6836153223156402</v>
       </c>
       <c r="G14" s="13">
-        <v>0.511890850468534</v>
+        <v>-0.4959790331095348</v>
       </c>
       <c r="H14" s="13">
-        <v>-0.5596396636832928</v>
+        <v>1.364720554774369</v>
       </c>
       <c r="I14" s="13">
-        <v>-0.04564568871787725</v>
+        <v>0.4606403416133553</v>
       </c>
       <c r="J14" s="13">
-        <v>0.5431154927190269</v>
+        <v>1.750425946070536</v>
       </c>
       <c r="K14" s="13">
-        <v>3.66274158499913</v>
+        <v>0</v>
       </c>
       <c r="L14" s="13">
-        <v>0.4496473754582477</v>
+        <v>-0.6480078553252493</v>
       </c>
       <c r="M14" s="13">
-        <v>0.1924787798298476</v>
+        <v>-0.74761157286751</v>
       </c>
       <c r="N14" s="13">
-        <v>16.01869</v>
+        <v>28.74471</v>
       </c>
       <c r="O14" s="13">
-        <v>3.9274893</v>
+        <v>26.717358</v>
       </c>
       <c r="P14" s="15">
-        <v>0.26408002</v>
+        <v>1.14818</v>
       </c>
       <c r="Q14" s="15">
-        <v>0.053</v>
+        <v>0.299</v>
       </c>
       <c r="R14" s="15">
-        <v>0.1858303496283789</v>
+        <v>0.9668634648158858</v>
       </c>
       <c r="S14" s="12">
-        <v>47.39020386632503</v>
+        <v>53.41291864722999</v>
       </c>
       <c r="T14" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -6195,61 +6244,61 @@
         <v>11</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>144</v>
+        <v>74</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E15" s="11">
-        <v>109.5199966430664</v>
+        <v>125.4800033569336</v>
       </c>
       <c r="F15" s="20">
-        <v>0.6381121585794951</v>
+        <v>0.6499503881386183</v>
       </c>
       <c r="G15" s="13">
-        <v>0.02344107793329698</v>
+        <v>0.3805332912349265</v>
       </c>
       <c r="H15" s="13">
-        <v>1.649714100513951</v>
+        <v>-0.1243005063079742</v>
       </c>
       <c r="I15" s="13">
-        <v>0.05989924891666139</v>
+        <v>0.4428140044701369</v>
       </c>
       <c r="J15" s="13">
-        <v>1.028199998881743</v>
+        <v>0.2316057358888467</v>
       </c>
       <c r="K15" s="13">
-        <v>0</v>
+        <v>3.931815695950569</v>
       </c>
       <c r="L15" s="13">
-        <v>0.01653032389633705</v>
+        <v>0.1012123101691432</v>
       </c>
       <c r="M15" s="13">
-        <v>-0.2759586818779912</v>
+        <v>0.1211091673465344</v>
       </c>
       <c r="N15" s="13">
-        <v>17.76259</v>
+        <v>15.125457</v>
       </c>
       <c r="O15" s="13">
-        <v>19.783653</v>
+        <v>6.804011</v>
       </c>
       <c r="P15" s="15">
-        <v>1.5956</v>
+        <v>0.46032003</v>
       </c>
       <c r="Q15" s="15">
-        <v>0.162</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R15" s="15">
-        <v>0.2215380873826178</v>
+        <v>0.230558025446578</v>
       </c>
       <c r="S15" s="12">
-        <v>83.2708161314859</v>
+        <v>62.7916777067352</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
@@ -6257,61 +6306,61 @@
         <v>12</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>48</v>
+        <v>68</v>
       </c>
       <c r="E16" s="11">
-        <v>49.90000152587891</v>
+        <v>152.3800048828125</v>
       </c>
       <c r="F16" s="20">
-        <v>0.6305009494456815</v>
+        <v>0.6270278235762253</v>
       </c>
       <c r="G16" s="13">
-        <v>0.9856664363574531</v>
+        <v>0.5118908504685342</v>
       </c>
       <c r="H16" s="13">
-        <v>0.5611810516441377</v>
+        <v>-0.5596396636832928</v>
       </c>
       <c r="I16" s="13">
-        <v>-0.2775772545641314</v>
+        <v>-0.04564568871787725</v>
       </c>
       <c r="J16" s="13">
-        <v>1.718404107915004</v>
+        <v>0.46797250427813</v>
       </c>
       <c r="K16" s="13">
-        <v>-0.5832267135659824</v>
+        <v>3.63608975556258</v>
       </c>
       <c r="L16" s="13">
-        <v>-0.5055497316261317</v>
+        <v>0.4470609576285982</v>
       </c>
       <c r="M16" s="13">
-        <v>-0.301891184429057</v>
+        <v>0.3181025768042407</v>
       </c>
       <c r="N16" s="13">
-        <v>10.391121</v>
+        <v>16.01869</v>
       </c>
       <c r="O16" s="13">
-        <v>2.4548</v>
+        <v>3.9274893</v>
       </c>
       <c r="P16" s="15">
-        <v>0.26659</v>
+        <v>0.26408002</v>
       </c>
       <c r="Q16" s="15">
-        <v>0.092</v>
+        <v>0.053</v>
       </c>
       <c r="R16" s="15">
-        <v>0.3454140626518685</v>
+        <v>0.1868325729421156</v>
       </c>
       <c r="S16" s="12">
-        <v>71.7100550294742</v>
+        <v>44.20590185336943</v>
       </c>
       <c r="T16" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.25">
@@ -6328,13 +6377,13 @@
         <v>71</v>
       </c>
       <c r="E17" s="11">
-        <v>262.6300048828125</v>
+        <v>262.3699951171875</v>
       </c>
       <c r="F17" s="20">
-        <v>0.6298910874720608</v>
+        <v>0.6167940435948067</v>
       </c>
       <c r="G17" s="13">
-        <v>-0.01168000613350131</v>
+        <v>-0.01168000613350126</v>
       </c>
       <c r="H17" s="13">
         <v>0.1587373616637428</v>
@@ -6343,16 +6392,16 @@
         <v>0.9947603682216362</v>
       </c>
       <c r="J17" s="13">
-        <v>0.2075467136386732</v>
+        <v>0.1993535059997246</v>
       </c>
       <c r="K17" s="13">
-        <v>4.020317717707746</v>
+        <v>3.931815695950569</v>
       </c>
       <c r="L17" s="13">
-        <v>-0.5707446689505203</v>
+        <v>-0.6046355280340494</v>
       </c>
       <c r="M17" s="13">
-        <v>-0.0417248273971482</v>
+        <v>-0.01654217026835393</v>
       </c>
       <c r="N17" s="13">
         <v>20.11263</v>
@@ -6367,13 +6416,13 @@
         <v>0.196</v>
       </c>
       <c r="R17" s="15">
-        <v>0.05089832753514423</v>
+        <v>0.02745141952569274</v>
       </c>
       <c r="S17" s="12">
-        <v>57.4079998352241</v>
+        <v>57.10063970368801</v>
       </c>
       <c r="T17" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.25">
@@ -6381,61 +6430,61 @@
         <v>14</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>145</v>
+        <v>12</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>146</v>
+        <v>66</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E18" s="11">
-        <v>209.9700012207031</v>
+        <v>251.0399932861328</v>
       </c>
       <c r="F18" s="20">
-        <v>0.6273819263740681</v>
+        <v>0.6022131656799165</v>
       </c>
       <c r="G18" s="13">
-        <v>-0.495979033109535</v>
+        <v>1.28199809939033</v>
       </c>
       <c r="H18" s="13">
-        <v>1.364720554774369</v>
+        <v>0.166463226470292</v>
       </c>
       <c r="I18" s="13">
-        <v>0.4606403416133553</v>
+        <v>-0.04675451852533465</v>
       </c>
       <c r="J18" s="13">
-        <v>1.532297718593555</v>
+        <v>0.2055598727431361</v>
       </c>
       <c r="K18" s="13">
-        <v>0</v>
+        <v>2.066682848341634</v>
       </c>
       <c r="L18" s="13">
-        <v>-0.6016458743516432</v>
+        <v>0.4502052544113339</v>
       </c>
       <c r="M18" s="13">
-        <v>-0.5829695609163286</v>
+        <v>0.1601578064790866</v>
       </c>
       <c r="N18" s="13">
-        <v>28.74471</v>
+        <v>4.9595838</v>
       </c>
       <c r="O18" s="13">
-        <v>26.717358</v>
+        <v>1.9863613</v>
       </c>
       <c r="P18" s="15">
-        <v>1.14818</v>
+        <v>0.46113998</v>
       </c>
       <c r="Q18" s="15">
-        <v>0.299</v>
+        <v>0.118</v>
       </c>
       <c r="R18" s="15">
-        <v>0.8880391707310582</v>
+        <v>0.1832871420378381</v>
       </c>
       <c r="S18" s="12">
-        <v>48.40504731936183</v>
+        <v>65.59635432994509</v>
       </c>
       <c r="T18" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.25">
@@ -6443,61 +6492,61 @@
         <v>15</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>66</v>
+        <v>149</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="E19" s="11">
-        <v>249.9100036621094</v>
+        <v>391</v>
       </c>
       <c r="F19" s="20">
-        <v>0.6083345540359664</v>
+        <v>0.5882840402344938</v>
       </c>
       <c r="G19" s="13">
-        <v>1.28199809939033</v>
+        <v>0.09653050747037281</v>
       </c>
       <c r="H19" s="13">
-        <v>0.166463226470292</v>
+        <v>-0.2394382368103288</v>
       </c>
       <c r="I19" s="13">
-        <v>-0.04675451852533465</v>
+        <v>0.4648264250834605</v>
       </c>
       <c r="J19" s="13">
-        <v>0.2249011056711633</v>
+        <v>1.62420610771538</v>
       </c>
       <c r="K19" s="13">
-        <v>2.085116368478011</v>
+        <v>1.901274134738851</v>
       </c>
       <c r="L19" s="13">
-        <v>0.3840764099940323</v>
+        <v>-1.756784885035037</v>
       </c>
       <c r="M19" s="13">
-        <v>0.1860918905580188</v>
+        <v>-0.5908951388755119</v>
       </c>
       <c r="N19" s="13">
-        <v>4.9595838</v>
+        <v>33.8231</v>
       </c>
       <c r="O19" s="13">
-        <v>1.9863613</v>
+        <v>5.0908465</v>
       </c>
       <c r="P19" s="15">
-        <v>0.46113998</v>
+        <v>0.15286</v>
       </c>
       <c r="Q19" s="15">
-        <v>0.118</v>
+        <v>0.204</v>
       </c>
       <c r="R19" s="15">
-        <v>0.1660909582305943</v>
+        <v>0.6919082201359228</v>
       </c>
       <c r="S19" s="12">
-        <v>64.58109185521839</v>
+        <v>63.61651388805629</v>
       </c>
       <c r="T19" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.25">
@@ -6505,61 +6554,61 @@
         <v>16</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>147</v>
+        <v>6</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>148</v>
+        <v>55</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E20" s="11">
-        <v>384.0799865722656</v>
+        <v>49.63000106811523</v>
       </c>
       <c r="F20" s="20">
-        <v>0.5554709544970838</v>
+        <v>0.5795359972710922</v>
       </c>
       <c r="G20" s="13">
-        <v>0.09653050747037273</v>
+        <v>0.9856664363574528</v>
       </c>
       <c r="H20" s="13">
-        <v>-0.2394382368103288</v>
+        <v>0.5611810516441377</v>
       </c>
       <c r="I20" s="13">
-        <v>0.4648264250834605</v>
+        <v>-0.2775772545641314</v>
       </c>
       <c r="J20" s="13">
-        <v>1.488921457540494</v>
+        <v>1.556526341142537</v>
       </c>
       <c r="K20" s="13">
-        <v>1.918841480549706</v>
+        <v>-0.5877600573248727</v>
       </c>
       <c r="L20" s="13">
-        <v>-1.826430861230132</v>
+        <v>-0.5442861157015785</v>
       </c>
       <c r="M20" s="13">
-        <v>-0.4678578090072709</v>
+        <v>-0.2960591575197488</v>
       </c>
       <c r="N20" s="13">
-        <v>33.8231</v>
+        <v>10.391121</v>
       </c>
       <c r="O20" s="13">
-        <v>5.0908465</v>
+        <v>2.4548</v>
       </c>
       <c r="P20" s="15">
-        <v>0.15286</v>
+        <v>0.26659</v>
       </c>
       <c r="Q20" s="15">
-        <v>0.204</v>
+        <v>0.092</v>
       </c>
       <c r="R20" s="15">
-        <v>0.6228503382084478</v>
+        <v>0.3131716082079086</v>
       </c>
       <c r="S20" s="12">
-        <v>59.67830289915142</v>
+        <v>69.84050142781759</v>
       </c>
       <c r="T20" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.25">
@@ -6567,61 +6616,61 @@
         <v>17</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="D21" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E21" s="11">
-        <v>1365.380004882812</v>
+        <v>58.16999816894531</v>
       </c>
       <c r="F21" s="20">
-        <v>0.5230213604171995</v>
+        <v>0.5472921735931936</v>
       </c>
       <c r="G21" s="13">
-        <v>-0.1705629317339571</v>
+        <v>0.46561472662119</v>
       </c>
       <c r="H21" s="13">
-        <v>2.05642902385236</v>
+        <v>-0.5356868534061616</v>
       </c>
       <c r="I21" s="13">
-        <v>4.121304611935469</v>
+        <v>2.148918348349026</v>
       </c>
       <c r="J21" s="13">
-        <v>0.09428953912194542</v>
+        <v>1.636209173647995</v>
       </c>
       <c r="K21" s="13">
-        <v>0.138054455570112</v>
+        <v>0</v>
       </c>
       <c r="L21" s="13">
-        <v>-2.909128081426966</v>
+        <v>-2.274741306166336</v>
       </c>
       <c r="M21" s="13">
-        <v>-0.7217766049998995</v>
+        <v>-1.071921875551738</v>
       </c>
       <c r="N21" s="13">
-        <v>17.615238</v>
+        <v>28.417526</v>
       </c>
       <c r="O21" s="13">
-        <v>12.302696</v>
+        <v>2.7614706</v>
       </c>
       <c r="P21" s="15">
-        <v>0.9164</v>
+        <v>0.10936</v>
       </c>
       <c r="Q21" s="15">
-        <v>3.716</v>
+        <v>0.337</v>
       </c>
       <c r="R21" s="15">
-        <v>0.5112287016357737</v>
+        <v>1.05148186377932</v>
       </c>
       <c r="S21" s="12">
-        <v>35.87824519909739</v>
+        <v>43.52631340126121</v>
       </c>
       <c r="T21" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.25">
@@ -6629,61 +6678,61 @@
         <v>18</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>150</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E22" s="11">
-        <v>225.7100067138672</v>
+        <v>485.8800048828125</v>
       </c>
       <c r="F22" s="20">
-        <v>0.5177893691072141</v>
+        <v>0.5353138039940292</v>
       </c>
       <c r="G22" s="13">
-        <v>0.4621184230168277</v>
+        <v>0.0690925225903401</v>
       </c>
       <c r="H22" s="13">
-        <v>-0.3293171412879227</v>
+        <v>-0.8471651400718279</v>
       </c>
       <c r="I22" s="13">
-        <v>2.28906029817432</v>
+        <v>2.180495006837846</v>
       </c>
       <c r="J22" s="13">
-        <v>0.8830156341488813</v>
+        <v>1.609819693900383</v>
       </c>
       <c r="K22" s="13">
-        <v>-0.1388811939487032</v>
+        <v>1.790625302431187</v>
       </c>
       <c r="L22" s="13">
-        <v>0.7113988323991762</v>
+        <v>-2.919797836906683</v>
       </c>
       <c r="M22" s="13">
-        <v>-0.4066263895243756</v>
+        <v>-1.028237532399759</v>
       </c>
       <c r="N22" s="13">
-        <v>21.225471</v>
+        <v>26.262207</v>
       </c>
       <c r="O22" s="13">
-        <v>2.324277</v>
+        <v>-202.56053</v>
       </c>
       <c r="P22" s="15">
-        <v>0.12231</v>
+        <v>0</v>
       </c>
       <c r="Q22" s="15">
-        <v>0.535</v>
+        <v>0.577</v>
       </c>
       <c r="R22" s="15">
-        <v>0.235429502550264</v>
+        <v>1.270473140611956</v>
       </c>
       <c r="S22" s="12">
-        <v>70.78961349727625</v>
+        <v>42.58988061739579</v>
       </c>
       <c r="T22" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.25">
@@ -6691,61 +6740,61 @@
         <v>19</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>152</v>
+        <v>40</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E23" s="11">
-        <v>1283.660034179688</v>
+        <v>1378.219970703125</v>
       </c>
       <c r="F23" s="20">
-        <v>0.5145499782582459</v>
+        <v>0.5218886727047179</v>
       </c>
       <c r="G23" s="13">
-        <v>-1.324949930516061</v>
+        <v>-0.1705629317339568</v>
       </c>
       <c r="H23" s="13">
-        <v>1.800353218123673</v>
+        <v>2.05642902385236</v>
       </c>
       <c r="I23" s="13">
-        <v>0.7788800244637265</v>
+        <v>4.121304611935469</v>
       </c>
       <c r="J23" s="13">
-        <v>0.9540406092115784</v>
+        <v>0.06239903230129684</v>
       </c>
       <c r="K23" s="13">
-        <v>0.9070048758528876</v>
+        <v>0.1297637480988044</v>
       </c>
       <c r="L23" s="13">
-        <v>0.2104780176683627</v>
+        <v>-2.919797836906683</v>
       </c>
       <c r="M23" s="13">
-        <v>-0.2573125065118153</v>
+        <v>-0.5959074230117385</v>
       </c>
       <c r="N23" s="13">
-        <v>42.196373</v>
+        <v>17.615238</v>
       </c>
       <c r="O23" s="13">
-        <v>33.078</v>
+        <v>12.302696</v>
       </c>
       <c r="P23" s="15">
-        <v>1.02286</v>
+        <v>0.9164</v>
       </c>
       <c r="Q23" s="15">
-        <v>0.477</v>
+        <v>3.716</v>
       </c>
       <c r="R23" s="15">
-        <v>0.4260064449852294</v>
+        <v>0.4076827605717146</v>
       </c>
       <c r="S23" s="12">
-        <v>69.78480619826614</v>
+        <v>37.06977729100647</v>
       </c>
       <c r="T23" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.25">
@@ -6753,61 +6802,61 @@
         <v>20</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>80</v>
+        <v>152</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>41</v>
       </c>
       <c r="E24" s="11">
-        <v>56.09000015258789</v>
+        <v>219.5700073242188</v>
       </c>
       <c r="F24" s="20">
-        <v>0.5036246660022281</v>
+        <v>0.5043589484152842</v>
       </c>
       <c r="G24" s="13">
-        <v>0.4656147266211902</v>
+        <v>0.6433919468057576</v>
       </c>
       <c r="H24" s="13">
-        <v>-0.5356868534061616</v>
+        <v>1.143743903235913</v>
       </c>
       <c r="I24" s="13">
-        <v>2.148918348349026</v>
+        <v>-0.515542964509501</v>
       </c>
       <c r="J24" s="13">
-        <v>1.475299439608947</v>
+        <v>1.248599197229785</v>
       </c>
       <c r="K24" s="13">
-        <v>0</v>
+        <v>0.3183183909088029</v>
       </c>
       <c r="L24" s="13">
-        <v>-2.283552980324228</v>
+        <v>-2.421626951607285</v>
       </c>
       <c r="M24" s="13">
-        <v>-0.9422442007875107</v>
+        <v>-0.1297084882262861</v>
       </c>
       <c r="N24" s="13">
-        <v>28.417526</v>
+        <v>18.566908</v>
       </c>
       <c r="O24" s="13">
-        <v>2.7614706</v>
+        <v>-79.04156999999999</v>
       </c>
       <c r="P24" s="15">
-        <v>0.10936</v>
+        <v>1.13581</v>
       </c>
       <c r="Q24" s="15">
-        <v>0.337</v>
+        <v>-0.006</v>
       </c>
       <c r="R24" s="15">
-        <v>0.960931424145665</v>
+        <v>0.3977338623901778</v>
       </c>
       <c r="S24" s="12">
-        <v>39.32282125838386</v>
+        <v>70.90656554925714</v>
       </c>
       <c r="T24" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.25">
@@ -6815,61 +6864,61 @@
         <v>21</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>14</v>
+        <v>153</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>69</v>
+        <v>154</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="E25" s="11">
-        <v>116.620002746582</v>
+        <v>226.7799987792969</v>
       </c>
       <c r="F25" s="20">
-        <v>0.4945458028309485</v>
+        <v>0.4978283348246706</v>
       </c>
       <c r="G25" s="13">
-        <v>0.4010859088230096</v>
+        <v>0.4621184230168276</v>
       </c>
       <c r="H25" s="13">
-        <v>0.5056475010694438</v>
+        <v>-0.3293171412879227</v>
       </c>
       <c r="I25" s="13">
-        <v>0.5568966182992388</v>
+        <v>2.28906029817432</v>
       </c>
       <c r="J25" s="13">
-        <v>0.130831662432555</v>
+        <v>0.8478012322456284</v>
       </c>
       <c r="K25" s="13">
-        <v>1.853580005765559</v>
+        <v>-0.14572926295293</v>
       </c>
       <c r="L25" s="13">
-        <v>0.08180836593875149</v>
+        <v>0.6972269686744224</v>
       </c>
       <c r="M25" s="13">
-        <v>0.2396184482976642</v>
+        <v>-0.5031843096190629</v>
       </c>
       <c r="N25" s="13">
-        <v>14.403822</v>
+        <v>21.225471</v>
       </c>
       <c r="O25" s="13">
-        <v>3.5817916</v>
+        <v>2.324277</v>
       </c>
       <c r="P25" s="15">
-        <v>0.30667</v>
+        <v>0.12231</v>
       </c>
       <c r="Q25" s="15">
-        <v>0.377</v>
+        <v>0.535</v>
       </c>
       <c r="R25" s="15">
-        <v>0.2120141474441133</v>
+        <v>0.2390210083918021</v>
       </c>
       <c r="S25" s="12">
-        <v>48.95551659208853</v>
+        <v>71.76051579429918</v>
       </c>
       <c r="T25" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.25">
@@ -6877,61 +6926,61 @@
         <v>22</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E26" s="11">
-        <v>395.7300109863281</v>
+        <v>113.4400024414062</v>
       </c>
       <c r="F26" s="20">
-        <v>0.4939209326976521</v>
+        <v>0.4810818728010601</v>
       </c>
       <c r="G26" s="13">
-        <v>1.194090308347607</v>
+        <v>0.4010859088230099</v>
       </c>
       <c r="H26" s="13">
-        <v>-0.1076216444283418</v>
+        <v>0.5056475010694438</v>
       </c>
       <c r="I26" s="13">
-        <v>-0.619704699975514</v>
+        <v>0.5568966182992388</v>
       </c>
       <c r="J26" s="13">
-        <v>0.8434070036761318</v>
+        <v>-0.06797367280416818</v>
       </c>
       <c r="K26" s="13">
-        <v>0.6930607367779014</v>
+        <v>1.836352625986905</v>
       </c>
       <c r="L26" s="13">
-        <v>0.9515556674392436</v>
+        <v>0.4430308698622381</v>
       </c>
       <c r="M26" s="13">
-        <v>-0.4388514907671672</v>
+        <v>0.571763521787137</v>
       </c>
       <c r="N26" s="13">
-        <v>10.463068</v>
+        <v>14.403822</v>
       </c>
       <c r="O26" s="13">
-        <v>2.7527773</v>
+        <v>3.5817916</v>
       </c>
       <c r="P26" s="15">
-        <v>0.27497</v>
+        <v>0.30667</v>
       </c>
       <c r="Q26" s="15">
-        <v>-0.005</v>
+        <v>0.377</v>
       </c>
       <c r="R26" s="15">
-        <v>0.3228818714633928</v>
+        <v>0.1726277129047891</v>
       </c>
       <c r="S26" s="12">
-        <v>72.79262372060083</v>
+        <v>42.45705215094931</v>
       </c>
       <c r="T26" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.25">
@@ -6939,61 +6988,61 @@
         <v>23</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>153</v>
+        <v>8</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="E27" s="11">
-        <v>219.6399993896484</v>
+        <v>398.9500122070312</v>
       </c>
       <c r="F27" s="20">
-        <v>0.4840448697426751</v>
+        <v>0.4787931786902542</v>
       </c>
       <c r="G27" s="13">
-        <v>0.6433919468057578</v>
+        <v>1.194090308347607</v>
       </c>
       <c r="H27" s="13">
-        <v>1.143743903235913</v>
+        <v>-0.1076216444283418</v>
       </c>
       <c r="I27" s="13">
-        <v>-0.515542964509501</v>
+        <v>-0.619704699975514</v>
       </c>
       <c r="J27" s="13">
-        <v>1.192333747871116</v>
+        <v>0.8207331541988571</v>
       </c>
       <c r="K27" s="13">
-        <v>0.327596477986678</v>
+        <v>0.6818788399196983</v>
       </c>
       <c r="L27" s="13">
-        <v>-2.430834946904717</v>
+        <v>0.939899286515928</v>
       </c>
       <c r="M27" s="13">
-        <v>-0.1796501706826308</v>
+        <v>-0.5174063493400691</v>
       </c>
       <c r="N27" s="13">
-        <v>18.566908</v>
+        <v>10.463068</v>
       </c>
       <c r="O27" s="13">
-        <v>-79.04156999999999</v>
+        <v>2.7527773</v>
       </c>
       <c r="P27" s="15">
-        <v>1.13581</v>
+        <v>0.27497</v>
       </c>
       <c r="Q27" s="15">
-        <v>-0.006</v>
+        <v>-0.005</v>
       </c>
       <c r="R27" s="15">
-        <v>0.3816443209603755</v>
+        <v>0.3324966322663134</v>
       </c>
       <c r="S27" s="12">
-        <v>70.98672573735854</v>
+        <v>74.43108652756132</v>
       </c>
       <c r="T27" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.25">
@@ -7001,61 +7050,61 @@
         <v>24</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E28" s="11">
-        <v>461.5599975585938</v>
+        <v>1270.75</v>
       </c>
       <c r="F28" s="20">
-        <v>0.4766142720287261</v>
+        <v>0.4763799839278788</v>
       </c>
       <c r="G28" s="13">
-        <v>0.06909252259033988</v>
+        <v>-1.324949930516061</v>
       </c>
       <c r="H28" s="13">
-        <v>-0.8471651400718279</v>
+        <v>1.800353218123673</v>
       </c>
       <c r="I28" s="13">
-        <v>2.180495006837846</v>
+        <v>0.7788800244637265</v>
       </c>
       <c r="J28" s="13">
-        <v>1.347488453957332</v>
+        <v>0.8009486981193906</v>
       </c>
       <c r="K28" s="13">
-        <v>1.807613227874116</v>
+        <v>0.8947084816543374</v>
       </c>
       <c r="L28" s="13">
-        <v>-2.909128081426966</v>
+        <v>0.1885201824442533</v>
       </c>
       <c r="M28" s="13">
-        <v>-0.8117237369537856</v>
+        <v>-0.1254298013297925</v>
       </c>
       <c r="N28" s="13">
-        <v>26.262207</v>
+        <v>42.196373</v>
       </c>
       <c r="O28" s="13">
-        <v>-202.56053</v>
+        <v>33.078</v>
       </c>
       <c r="P28" s="15">
-        <v>0</v>
+        <v>1.02286</v>
       </c>
       <c r="Q28" s="15">
-        <v>0.577</v>
+        <v>0.477</v>
       </c>
       <c r="R28" s="15">
-        <v>1.18008633485513</v>
+        <v>0.3833850154454974</v>
       </c>
       <c r="S28" s="12">
-        <v>36.15911528627012</v>
+        <v>66.0826981353012</v>
       </c>
       <c r="T28" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.25">
@@ -7063,61 +7112,61 @@
         <v>25</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>156</v>
+        <v>16</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E29" s="11">
-        <v>157.9100036621094</v>
+        <v>282.8599853515625</v>
       </c>
       <c r="F29" s="20">
-        <v>0.4699739682161381</v>
+        <v>0.4502698703908647</v>
       </c>
       <c r="G29" s="13">
-        <v>0.532634604807481</v>
+        <v>-0.7589860946385489</v>
       </c>
       <c r="H29" s="13">
-        <v>0.4650914610299381</v>
+        <v>0.4424895073656877</v>
       </c>
       <c r="I29" s="13">
-        <v>1.460969155364312</v>
+        <v>-0.4351884462710338</v>
       </c>
       <c r="J29" s="13">
-        <v>0.7687422614954488</v>
+        <v>2.455626246014417</v>
       </c>
       <c r="K29" s="13">
-        <v>-0.5213701852923126</v>
+        <v>-0.2597653044128692</v>
       </c>
       <c r="L29" s="13">
-        <v>0.09407949636759708</v>
+        <v>-1.263564454366132</v>
       </c>
       <c r="M29" s="13">
-        <v>-0.2514354493255337</v>
+        <v>-0.8761784892302009</v>
       </c>
       <c r="N29" s="13">
-        <v>12.296497</v>
+        <v>48.981342</v>
       </c>
       <c r="O29" s="13">
-        <v>2.6058776</v>
+        <v>13.968609</v>
       </c>
       <c r="P29" s="15">
-        <v>0.22507</v>
+        <v>0.32339</v>
       </c>
       <c r="Q29" s="15">
-        <v>0.587</v>
+        <v>0.094</v>
       </c>
       <c r="R29" s="15">
-        <v>0.2093352903094625</v>
+        <v>1.167509466295498</v>
       </c>
       <c r="S29" s="12">
-        <v>70.70238647251864</v>
+        <v>63.14787196170919</v>
       </c>
       <c r="T29" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
@@ -7125,61 +7174,61 @@
         <v>26</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="C30" s="10" t="s">
         <v>158</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>159</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>48</v>
       </c>
       <c r="E30" s="11">
-        <v>145.9499969482422</v>
+        <v>157.8800048828125</v>
       </c>
       <c r="F30" s="20">
-        <v>0.4505846794304207</v>
+        <v>0.4430066032227193</v>
       </c>
       <c r="G30" s="13">
-        <v>0.4341489187690627</v>
+        <v>0.532634604807481</v>
       </c>
       <c r="H30" s="13">
-        <v>-0.1392720269078983</v>
+        <v>0.4650914610299381</v>
       </c>
       <c r="I30" s="13">
-        <v>0.813110618840484</v>
+        <v>1.460969155364312</v>
       </c>
       <c r="J30" s="13">
-        <v>1.06837913061436</v>
+        <v>0.704709474122455</v>
       </c>
       <c r="K30" s="13">
-        <v>-0.04013774514486335</v>
+        <v>-0.5262257577252025</v>
       </c>
       <c r="L30" s="13">
-        <v>0.3039429883818122</v>
+        <v>0.0640646801621951</v>
       </c>
       <c r="M30" s="13">
-        <v>-0.2565431574578575</v>
+        <v>-0.3186100882911571</v>
       </c>
       <c r="N30" s="13">
-        <v>19.405296</v>
+        <v>12.296497</v>
       </c>
       <c r="O30" s="13">
-        <v>2.693347</v>
+        <v>2.6058776</v>
       </c>
       <c r="P30" s="15">
-        <v>0.1418</v>
+        <v>0.22507</v>
       </c>
       <c r="Q30" s="15">
-        <v>0.355</v>
+        <v>0.587</v>
       </c>
       <c r="R30" s="15">
-        <v>0.2307944811903566</v>
+        <v>0.2038332508425347</v>
       </c>
       <c r="S30" s="12">
-        <v>72.0536215530567</v>
+        <v>70.61574693499867</v>
       </c>
       <c r="T30" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.25">
@@ -7187,61 +7236,61 @@
         <v>27</v>
       </c>
       <c r="B31" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="C31" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>161</v>
-      </c>
       <c r="D31" s="10" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E31" s="11">
-        <v>253.9900054931641</v>
+        <v>320.5499877929688</v>
       </c>
       <c r="F31" s="20">
-        <v>0.4300392425764909</v>
+        <v>0.4349986783586624</v>
       </c>
       <c r="G31" s="13">
-        <v>-0.07251740337470877</v>
+        <v>-0.8993772465719768</v>
       </c>
       <c r="H31" s="13">
-        <v>0.2691688205067533</v>
+        <v>0.651197148783897</v>
       </c>
       <c r="I31" s="13">
-        <v>-0.2744798645681174</v>
+        <v>0.01332868977496858</v>
       </c>
       <c r="J31" s="13">
-        <v>0.8237268852037558</v>
+        <v>2.095620071363446</v>
       </c>
       <c r="K31" s="13">
-        <v>1.508545426037199</v>
+        <v>-0.3190414645776892</v>
       </c>
       <c r="L31" s="13">
-        <v>0.4853703933249489</v>
+        <v>-0.8027897752232616</v>
       </c>
       <c r="M31" s="13">
-        <v>-0.3724048740677242</v>
+        <v>-0.6358936148452202</v>
       </c>
       <c r="N31" s="13">
-        <v>25.657436</v>
+        <v>50.87869</v>
       </c>
       <c r="O31" s="13">
-        <v>13.762447</v>
+        <v>6.758711</v>
       </c>
       <c r="P31" s="15">
-        <v>0.54960996</v>
+        <v>0.14425</v>
       </c>
       <c r="Q31" s="15">
-        <v>0.067</v>
+        <v>0.176</v>
       </c>
       <c r="R31" s="15">
-        <v>0.2636387749660964</v>
+        <v>0.9571986212121579</v>
       </c>
       <c r="S31" s="12">
-        <v>69.78394004918161</v>
+        <v>75.19086792219936</v>
       </c>
       <c r="T31" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.25">
@@ -7249,61 +7298,61 @@
         <v>28</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E32" s="11">
-        <v>267.9299926757812</v>
+        <v>266.6799926757812</v>
       </c>
       <c r="F32" s="20">
-        <v>0.4271248391187443</v>
+        <v>0.424853750564247</v>
       </c>
       <c r="G32" s="13">
-        <v>-0.7589860946385489</v>
+        <v>-0.8275724890736493</v>
       </c>
       <c r="H32" s="13">
-        <v>0.4424895073656877</v>
+        <v>0.0352288459368772</v>
       </c>
       <c r="I32" s="13">
-        <v>-0.4351884462710338</v>
+        <v>2.268831712885381</v>
       </c>
       <c r="J32" s="13">
-        <v>2.31704266595455</v>
+        <v>1.943948016599911</v>
       </c>
       <c r="K32" s="13">
-        <v>-0.2535143931347701</v>
+        <v>-0.02040252431873931</v>
       </c>
       <c r="L32" s="13">
-        <v>-1.164355895919075</v>
+        <v>-2.874413577223597</v>
       </c>
       <c r="M32" s="13">
-        <v>-0.7295857406596483</v>
+        <v>-0.8371784433655454</v>
       </c>
       <c r="N32" s="13">
-        <v>48.981342</v>
+        <v>33.799446</v>
       </c>
       <c r="O32" s="13">
-        <v>13.968609</v>
+        <v>4.1801233</v>
       </c>
       <c r="P32" s="15">
-        <v>0.32339</v>
+        <v>0.13497</v>
       </c>
       <c r="Q32" s="15">
-        <v>0.094</v>
+        <v>0.22</v>
       </c>
       <c r="R32" s="15">
-        <v>1.030080325422186</v>
+        <v>0.7725490068805021</v>
       </c>
       <c r="S32" s="12">
-        <v>56.11755454828045</v>
+        <v>49.78519614231631</v>
       </c>
       <c r="T32" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.25">
@@ -7311,61 +7360,61 @@
         <v>29</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="E33" s="11">
-        <v>30.64999961853027</v>
+        <v>253.3200073242188</v>
       </c>
       <c r="F33" s="20">
-        <v>0.4130430971399421</v>
+        <v>0.4216416497855828</v>
       </c>
       <c r="G33" s="13">
-        <v>0.46909367085789</v>
+        <v>-0.07251740337470869</v>
       </c>
       <c r="H33" s="13">
-        <v>-0.286777552311737</v>
+        <v>0.2691688205067533</v>
       </c>
       <c r="I33" s="13">
-        <v>-0.6746219453467055</v>
+        <v>-0.2744798645681174</v>
       </c>
       <c r="J33" s="13">
-        <v>0.4981459381702493</v>
+        <v>0.8086051031093371</v>
       </c>
       <c r="K33" s="13">
-        <v>2.267281006788543</v>
+        <v>1.493115431889662</v>
       </c>
       <c r="L33" s="13">
-        <v>0.636629269149417</v>
+        <v>0.4563455262427917</v>
       </c>
       <c r="M33" s="13">
-        <v>-0.2220302390574339</v>
+        <v>-0.3757544595670813</v>
       </c>
       <c r="N33" s="13">
-        <v>29.155342</v>
+        <v>25.657436</v>
       </c>
       <c r="O33" s="13">
-        <v>1.9140799</v>
+        <v>13.762447</v>
       </c>
       <c r="P33" s="15">
-        <v>0.07979</v>
+        <v>0.54960996</v>
       </c>
       <c r="Q33" s="15">
-        <v>0.108</v>
+        <v>0.067</v>
       </c>
       <c r="R33" s="15">
-        <v>0.1640094143976365</v>
+        <v>0.2921820308833247</v>
       </c>
       <c r="S33" s="12">
-        <v>65.39014877810916</v>
+        <v>68.62854770400355</v>
       </c>
       <c r="T33" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.25">
@@ -7373,61 +7422,61 @@
         <v>30</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="E34" s="11">
-        <v>129.6699981689453</v>
+        <v>145.6699981689453</v>
       </c>
       <c r="F34" s="20">
-        <v>0.4120682375207951</v>
+        <v>0.411812791962536</v>
       </c>
       <c r="G34" s="13">
-        <v>0.5920488244253568</v>
+        <v>0.4341489187690629</v>
       </c>
       <c r="H34" s="13">
-        <v>-0.7025044660757493</v>
+        <v>-0.1392720269078983</v>
       </c>
       <c r="I34" s="13">
-        <v>-0.5550326180845108</v>
+        <v>0.813110618840484</v>
       </c>
       <c r="J34" s="13">
-        <v>0.7318360831615885</v>
+        <v>0.9602072768267518</v>
       </c>
       <c r="K34" s="13">
-        <v>1.980130517738296</v>
+        <v>-0.04750019753694272</v>
       </c>
       <c r="L34" s="13">
-        <v>0.5802819476129887</v>
+        <v>0.2850770803122317</v>
       </c>
       <c r="M34" s="13">
-        <v>-0.2322497303631193</v>
+        <v>-0.310354189462579</v>
       </c>
       <c r="N34" s="13">
-        <v>59.546726</v>
+        <v>19.405296</v>
       </c>
       <c r="O34" s="13">
-        <v>2.3670914</v>
+        <v>2.693347</v>
       </c>
       <c r="P34" s="15">
-        <v>0.03931</v>
+        <v>0.1418</v>
       </c>
       <c r="Q34" s="15">
-        <v>0.05</v>
+        <v>0.355</v>
       </c>
       <c r="R34" s="15">
-        <v>0.3822648458555777</v>
+        <v>0.2049868729962385</v>
       </c>
       <c r="S34" s="12">
-        <v>70.01585237497511</v>
+        <v>71.23065860116138</v>
       </c>
       <c r="T34" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.25">
@@ -7435,61 +7484,61 @@
         <v>31</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>166</v>
+        <v>7</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>167</v>
+        <v>56</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E35" s="11">
-        <v>807.47998046875</v>
+        <v>221.9700012207031</v>
       </c>
       <c r="F35" s="20">
-        <v>0.4062222387188359</v>
+        <v>0.4050290247635221</v>
       </c>
       <c r="G35" s="13">
-        <v>0.179218298133199</v>
+        <v>-1.118572244175211</v>
       </c>
       <c r="H35" s="13">
-        <v>0.1790552293207532</v>
+        <v>2.368452570933654</v>
       </c>
       <c r="I35" s="13">
-        <v>-0.2124000415459111</v>
+        <v>2.409012026495755</v>
       </c>
       <c r="J35" s="13">
-        <v>0.5135085057101227</v>
+        <v>0.1658578416070467</v>
       </c>
       <c r="K35" s="13">
-        <v>1.628853536074061</v>
+        <v>-0.2970246050878989</v>
       </c>
       <c r="L35" s="13">
-        <v>0.1847500636301643</v>
+        <v>-0.1494186283381317</v>
       </c>
       <c r="M35" s="13">
-        <v>0.07442665822995792</v>
+        <v>-0.2328858431897306</v>
       </c>
       <c r="N35" s="13">
-        <v>19.553413</v>
+        <v>27.070797</v>
       </c>
       <c r="O35" s="13">
-        <v>2.5014632</v>
+        <v>22.580408</v>
       </c>
       <c r="P35" s="15">
-        <v>0.14043</v>
+        <v>1.17211</v>
       </c>
       <c r="Q35" s="15">
-        <v>0.167</v>
+        <v>1.059</v>
       </c>
       <c r="R35" s="15">
-        <v>0.08332036135921173</v>
+        <v>0.09865366642058349</v>
       </c>
       <c r="S35" s="12">
-        <v>60.89548055596043</v>
+        <v>47.9389392809458</v>
       </c>
       <c r="T35" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.25">
@@ -7497,61 +7546,61 @@
         <v>32</v>
       </c>
       <c r="B36" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>169</v>
-      </c>
       <c r="D36" s="10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E36" s="11">
-        <v>61.68000030517578</v>
+        <v>30.43000030517578</v>
       </c>
       <c r="F36" s="20">
-        <v>0.406167750078374</v>
+        <v>0.4035090389804945</v>
       </c>
       <c r="G36" s="13">
-        <v>0.5295268879890338</v>
+        <v>0.4690936708578898</v>
       </c>
       <c r="H36" s="13">
-        <v>0.6581905543677987</v>
+        <v>-0.286777552311737</v>
       </c>
       <c r="I36" s="13">
-        <v>0.2056474795724012</v>
+        <v>-0.6746219453467055</v>
       </c>
       <c r="J36" s="13">
-        <v>0.1174093636176268</v>
+        <v>0.4360570749005494</v>
       </c>
       <c r="K36" s="13">
-        <v>0.933676956851626</v>
+        <v>2.247898537988369</v>
       </c>
       <c r="L36" s="13">
-        <v>0.427500077655151</v>
+        <v>0.6582980837752084</v>
       </c>
       <c r="M36" s="13">
-        <v>0.150795312718347</v>
+        <v>-0.09555063655823476</v>
       </c>
       <c r="N36" s="13">
-        <v>13.160793</v>
+        <v>29.155342</v>
       </c>
       <c r="O36" s="13">
-        <v>5.4691076</v>
+        <v>1.9140799</v>
       </c>
       <c r="P36" s="15">
-        <v>0.46598998</v>
+        <v>0.07979</v>
       </c>
       <c r="Q36" s="15">
-        <v>0.057</v>
+        <v>0.108</v>
       </c>
       <c r="R36" s="15">
-        <v>0.0611596937824892</v>
+        <v>0.1456807152445467</v>
       </c>
       <c r="S36" s="12">
-        <v>53.38371963056493</v>
+        <v>61.85165552440265</v>
       </c>
       <c r="T36" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.25">
@@ -7559,61 +7608,61 @@
         <v>33</v>
       </c>
       <c r="B37" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="C37" s="10" t="s">
-        <v>171</v>
-      </c>
       <c r="D37" s="10" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="E37" s="11">
-        <v>318.6700134277344</v>
+        <v>307.25</v>
       </c>
       <c r="F37" s="20">
-        <v>0.4029015254655374</v>
+        <v>0.4017401063858326</v>
       </c>
       <c r="G37" s="13">
-        <v>-0.899377246571977</v>
+        <v>-0.8004035395390546</v>
       </c>
       <c r="H37" s="13">
-        <v>0.651197148783897</v>
+        <v>2.306990125187904</v>
       </c>
       <c r="I37" s="13">
-        <v>0.01332868977496858</v>
+        <v>-0.45040199689134</v>
       </c>
       <c r="J37" s="13">
-        <v>1.958503723767202</v>
+        <v>0.5472285672427454</v>
       </c>
       <c r="K37" s="13">
-        <v>-0.3131009570681217</v>
+        <v>0</v>
       </c>
       <c r="L37" s="13">
-        <v>-0.789267314382883</v>
+        <v>0.6307773954751774</v>
       </c>
       <c r="M37" s="13">
-        <v>-0.5419743294180019</v>
+        <v>-0.3561187938212808</v>
       </c>
       <c r="N37" s="13">
-        <v>50.87869</v>
+        <v>32.720238</v>
       </c>
       <c r="O37" s="13">
-        <v>6.758711</v>
+        <v>-12.124925</v>
       </c>
       <c r="P37" s="15">
-        <v>0.14425</v>
+        <v>0</v>
       </c>
       <c r="Q37" s="15">
-        <v>0.176</v>
+        <v>0.06</v>
       </c>
       <c r="R37" s="15">
-        <v>0.8992194181944175</v>
+        <v>0.1450605742153557</v>
       </c>
       <c r="S37" s="12">
-        <v>74.4641926653278</v>
+        <v>64.46289853434483</v>
       </c>
       <c r="T37" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
@@ -7621,61 +7670,61 @@
         <v>34</v>
       </c>
       <c r="B38" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>173</v>
-      </c>
       <c r="D38" s="10" t="s">
-        <v>174</v>
+        <v>63</v>
       </c>
       <c r="E38" s="11">
-        <v>30.95</v>
+        <v>805.6699829101562</v>
       </c>
       <c r="F38" s="20">
-        <v>0.3845534632925743</v>
+        <v>0.3972747082684681</v>
       </c>
       <c r="G38" s="13">
-        <v>-0.04251914790126206</v>
+        <v>0.1792182981331988</v>
       </c>
       <c r="H38" s="13">
-        <v>-1.001305748713663</v>
+        <v>0.1790552293207532</v>
       </c>
       <c r="I38" s="13">
-        <v>-1.196106130416092</v>
+        <v>-0.2124000415459111</v>
       </c>
       <c r="J38" s="13">
-        <v>0.7755489813393309</v>
+        <v>0.466812161071092</v>
       </c>
       <c r="K38" s="13">
-        <v>4.020317717707746</v>
+        <v>1.612796821936727</v>
       </c>
       <c r="L38" s="13">
-        <v>0.4383322866492484</v>
+        <v>0.2226856654280896</v>
       </c>
       <c r="M38" s="13">
-        <v>-0.8672039371885875</v>
+        <v>0.1333271898542832</v>
       </c>
       <c r="N38" s="13">
-        <v>497.26776</v>
+        <v>19.553413</v>
       </c>
       <c r="O38" s="13">
-        <v>2.3630948</v>
+        <v>2.5014632</v>
       </c>
       <c r="P38" s="15">
-        <v>-0.08785999999999999</v>
+        <v>0.14043</v>
       </c>
       <c r="Q38" s="15">
-        <v>-0.112</v>
+        <v>0.167</v>
       </c>
       <c r="R38" s="15">
-        <v>0.1308001461454147</v>
+        <v>0.08202128287435206</v>
       </c>
       <c r="S38" s="12">
-        <v>75.22299401348943</v>
+        <v>60.20072270842176</v>
       </c>
       <c r="T38" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
@@ -7683,61 +7732,61 @@
         <v>35</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="E39" s="11">
-        <v>258.6900024414062</v>
+        <v>127.8099975585938</v>
       </c>
       <c r="F39" s="20">
-        <v>0.3844740031407636</v>
+        <v>0.3939424901600002</v>
       </c>
       <c r="G39" s="13">
-        <v>-0.8275724890736497</v>
+        <v>0.5920488244253564</v>
       </c>
       <c r="H39" s="13">
-        <v>0.0352288459368772</v>
+        <v>-0.7025044660757493</v>
       </c>
       <c r="I39" s="13">
-        <v>2.268831712885381</v>
+        <v>-0.5550326180845108</v>
       </c>
       <c r="J39" s="13">
-        <v>1.787546614415023</v>
+        <v>0.6211313295249795</v>
       </c>
       <c r="K39" s="13">
-        <v>-0.01289817306104545</v>
+        <v>1.962243899479808</v>
       </c>
       <c r="L39" s="13">
-        <v>-2.821686239288451</v>
+        <v>0.5495666436726864</v>
       </c>
       <c r="M39" s="13">
-        <v>-0.8062220583036548</v>
+        <v>0.006187659107187604</v>
       </c>
       <c r="N39" s="13">
-        <v>33.799446</v>
+        <v>59.546726</v>
       </c>
       <c r="O39" s="13">
-        <v>4.1801233</v>
+        <v>2.3670914</v>
       </c>
       <c r="P39" s="15">
-        <v>0.13497</v>
+        <v>0.03931</v>
       </c>
       <c r="Q39" s="15">
-        <v>0.22</v>
+        <v>0.05</v>
       </c>
       <c r="R39" s="15">
-        <v>0.780385388906409</v>
+        <v>0.3731945803104679</v>
       </c>
       <c r="S39" s="12">
-        <v>46.34510411785447</v>
+        <v>63.59936702566596</v>
       </c>
       <c r="T39" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.25">
@@ -7745,61 +7794,61 @@
         <v>36</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>56</v>
+        <v>176</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="E40" s="11">
-        <v>216.4700012207031</v>
+        <v>61.11999893188477</v>
       </c>
       <c r="F40" s="20">
-        <v>0.3799548487530597</v>
+        <v>0.3890458647001643</v>
       </c>
       <c r="G40" s="13">
-        <v>-1.118572244175211</v>
+        <v>0.529526887989034</v>
       </c>
       <c r="H40" s="13">
-        <v>2.368452570933654</v>
+        <v>0.6581905543677987</v>
       </c>
       <c r="I40" s="13">
-        <v>2.409012026495755</v>
+        <v>0.2056474795724012</v>
       </c>
       <c r="J40" s="13">
-        <v>0.01710198161974044</v>
+        <v>0.02350158364643677</v>
       </c>
       <c r="K40" s="13">
-        <v>-0.2909688047500197</v>
+        <v>0.9212416200138283</v>
       </c>
       <c r="L40" s="13">
-        <v>-0.09483324430199144</v>
+        <v>0.4071376501063325</v>
       </c>
       <c r="M40" s="13">
-        <v>-0.03850130690203546</v>
+        <v>0.3228507463009981</v>
       </c>
       <c r="N40" s="13">
-        <v>27.070797</v>
+        <v>13.160793</v>
       </c>
       <c r="O40" s="13">
-        <v>22.580408</v>
+        <v>5.4691076</v>
       </c>
       <c r="P40" s="15">
-        <v>1.17211</v>
+        <v>0.46598998</v>
       </c>
       <c r="Q40" s="15">
-        <v>1.059</v>
+        <v>0.057</v>
       </c>
       <c r="R40" s="15">
-        <v>0.08547520276846865</v>
+        <v>0.06207630607170778</v>
       </c>
       <c r="S40" s="12">
-        <v>40.92991462248053</v>
+        <v>51.28856535971509</v>
       </c>
       <c r="T40" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.25">
@@ -7813,55 +7862,55 @@
         <v>178</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="E41" s="11">
-        <v>438.9400024414062</v>
+        <v>95.44000244140625</v>
       </c>
       <c r="F41" s="20">
-        <v>0.37880748247031</v>
+        <v>0.3746262646496876</v>
       </c>
       <c r="G41" s="13">
-        <v>-0.2936486380311477</v>
+        <v>0.793747741530719</v>
       </c>
       <c r="H41" s="13">
-        <v>1.240294774468037</v>
+        <v>-0.7099927280282885</v>
       </c>
       <c r="I41" s="13">
-        <v>-0.09299075107987806</v>
+        <v>0.4928036167144187</v>
       </c>
       <c r="J41" s="13">
-        <v>0.8508044676165736</v>
+        <v>0.4988008418876442</v>
       </c>
       <c r="K41" s="13">
-        <v>0.03874351568119263</v>
+        <v>1.040923010060893</v>
       </c>
       <c r="L41" s="13">
-        <v>-0.08994486193195664</v>
+        <v>0.3760030182815661</v>
       </c>
       <c r="M41" s="13">
-        <v>-0.1497215242722425</v>
+        <v>-0.01301311104065023</v>
       </c>
       <c r="N41" s="13">
-        <v>26.862732</v>
+        <v>22.611246</v>
       </c>
       <c r="O41" s="13">
-        <v>20.004162</v>
+        <v>1.5588707</v>
       </c>
       <c r="P41" s="15">
-        <v>0.91473</v>
+        <v>0.06886</v>
       </c>
       <c r="Q41" s="15">
-        <v>0.095</v>
+        <v>0.004</v>
       </c>
       <c r="R41" s="15">
-        <v>0.2899124910217135</v>
+        <v>0.2853321644676972</v>
       </c>
       <c r="S41" s="12">
-        <v>63.44882487513986</v>
+        <v>62.18066227679093</v>
       </c>
       <c r="T41" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.25">
@@ -7869,61 +7918,61 @@
         <v>38</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E42" s="11">
-        <v>300.760009765625</v>
+        <v>457.4700012207031</v>
       </c>
       <c r="F42" s="20">
-        <v>0.3705091648042955</v>
+        <v>0.3717979929434415</v>
       </c>
       <c r="G42" s="13">
-        <v>0.1338797210506113</v>
+        <v>-0.9763436709728449</v>
       </c>
       <c r="H42" s="13">
-        <v>1.210360910376113</v>
+        <v>-0.4362001812103688</v>
       </c>
       <c r="I42" s="13">
-        <v>0.5961464855734491</v>
+        <v>4.121304611935469</v>
       </c>
       <c r="J42" s="13">
-        <v>0.4243333387476589</v>
+        <v>0.948752938487695</v>
       </c>
       <c r="K42" s="13">
-        <v>-0.09291441605726049</v>
+        <v>-0.5651786629763699</v>
       </c>
       <c r="L42" s="13">
-        <v>-0.7263962591710715</v>
+        <v>0.4947018286554709</v>
       </c>
       <c r="M42" s="13">
-        <v>0.2571490581312542</v>
+        <v>-0.5160641273725854</v>
       </c>
       <c r="N42" s="13">
-        <v>18.048096</v>
+        <v>110.620255</v>
       </c>
       <c r="O42" s="13">
-        <v>28.679903</v>
+        <v>2.824572</v>
       </c>
       <c r="P42" s="15">
-        <v>0.89489</v>
+        <v>0.019199999</v>
       </c>
       <c r="Q42" s="15">
-        <v>0.14</v>
+        <v>1.134</v>
       </c>
       <c r="R42" s="15">
-        <v>0.1023852173304152</v>
+        <v>0.3681141053306372</v>
       </c>
       <c r="S42" s="12">
-        <v>64.85923565347476</v>
+        <v>65.95058568747177</v>
       </c>
       <c r="T42" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.25">
@@ -7931,61 +7980,61 @@
         <v>39</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E43" s="11">
-        <v>50.38000106811523</v>
+        <v>438.3399963378906</v>
       </c>
       <c r="F43" s="20">
-        <v>0.3682805794938797</v>
+        <v>0.3633035230947784</v>
       </c>
       <c r="G43" s="13">
-        <v>0.332787110620459</v>
+        <v>-0.2936486380311477</v>
       </c>
       <c r="H43" s="13">
-        <v>-0.04536551751463628</v>
+        <v>1.240294774468037</v>
       </c>
       <c r="I43" s="13">
-        <v>1.313165623779629</v>
+        <v>-0.09299075107987806</v>
       </c>
       <c r="J43" s="13">
-        <v>0.6116953506650414</v>
+        <v>0.7918672438406782</v>
       </c>
       <c r="K43" s="13">
-        <v>-0.001548351359454703</v>
+        <v>0.03097014782410461</v>
       </c>
       <c r="L43" s="13">
-        <v>0.07092284876086068</v>
+        <v>-0.04962722158903411</v>
       </c>
       <c r="M43" s="13">
-        <v>-0.04071692444316939</v>
+        <v>-0.1410846057783387</v>
       </c>
       <c r="N43" s="13">
-        <v>11.052287</v>
+        <v>26.862732</v>
       </c>
       <c r="O43" s="13">
-        <v>1.3973281</v>
+        <v>20.004162</v>
       </c>
       <c r="P43" s="15">
-        <v>0.11522</v>
+        <v>0.91473</v>
       </c>
       <c r="Q43" s="15">
-        <v>0.642</v>
+        <v>0.095</v>
       </c>
       <c r="R43" s="15">
-        <v>0.1198889880817111</v>
+        <v>0.2842019253473491</v>
       </c>
       <c r="S43" s="12">
-        <v>59.29111723421912</v>
+        <v>63.0143778168794</v>
       </c>
       <c r="T43" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.25">
@@ -7993,61 +8042,61 @@
         <v>40</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="E44" s="11">
-        <v>74.63999938964844</v>
+        <v>30.95</v>
       </c>
       <c r="F44" s="20">
-        <v>0.3669804608455737</v>
+        <v>0.3561300991626699</v>
       </c>
       <c r="G44" s="13">
-        <v>0.3952758540064341</v>
+        <v>-0.04251914790126206</v>
       </c>
       <c r="H44" s="13">
-        <v>1.840190871076458</v>
+        <v>-1.001305748713663</v>
       </c>
       <c r="I44" s="13">
-        <v>-0.6296873188110119</v>
+        <v>-1.196106130416092</v>
       </c>
       <c r="J44" s="13">
-        <v>0.5480694753898142</v>
+        <v>0.7438542462290948</v>
       </c>
       <c r="K44" s="13">
-        <v>-0.706939770113322</v>
+        <v>3.931815695950569</v>
       </c>
       <c r="L44" s="13">
-        <v>0.3339116639530976</v>
+        <v>0.4075599743738321</v>
       </c>
       <c r="M44" s="13">
-        <v>-0.4406721300906005</v>
+        <v>-0.9478084653066794</v>
       </c>
       <c r="N44" s="13">
-        <v>15.812632</v>
+        <v>497.26776</v>
       </c>
       <c r="O44" s="13">
-        <v>-47.002502</v>
+        <v>2.3630948</v>
       </c>
       <c r="P44" s="15">
-        <v>0</v>
+        <v>-0.08785999999999999</v>
       </c>
       <c r="Q44" s="15">
-        <v>0.012</v>
+        <v>-0.112</v>
       </c>
       <c r="R44" s="15">
-        <v>0.1905049843015705</v>
+        <v>0.1308001461454147</v>
       </c>
       <c r="S44" s="12">
-        <v>71.41505017933778</v>
+        <v>75.22299401348975</v>
       </c>
       <c r="T44" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -8113,110 +8162,110 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B6" s="15">
         <v>0.18</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B7" s="15">
         <v>0.16</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B8" s="15">
         <v>0.1</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B9" s="15">
         <v>0.3</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B10" s="15">
         <v>0.12</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B11" s="15">
         <v>0.06</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B12" s="15">
         <v>0.08</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B13" s="15">
         <f>SUM(B6:B12)</f>
@@ -8225,22 +8274,22 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
@@ -8319,49 +8368,49 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="10" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>91</v>
@@ -8369,7 +8418,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>44</v>
@@ -8377,113 +8426,113 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="10" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="10" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="10" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="10" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="30" customHeight="1">
       <c r="A17" s="16" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="30" customHeight="1">
       <c r="A18" s="16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="30" customHeight="1">
       <c r="A19" s="16" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="30" customHeight="1">
       <c r="A20" s="16" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="32.25" customHeight="1">
       <c r="A23" s="26" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B23" s="26"/>
     </row>
     <row r="24" spans="1:2" ht="32.25" customHeight="1">
       <c r="A24" s="26" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B24" s="26"/>
     </row>
     <row r="25" spans="1:2" ht="32.25" customHeight="1">
       <c r="A25" s="26" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B25" s="26"/>
     </row>
     <row r="26" spans="1:2" ht="32.25" customHeight="1">
       <c r="A26" s="26" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B26" s="26"/>
     </row>
     <row r="27" spans="1:2" ht="32.25" customHeight="1">
       <c r="A27" s="26" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B27" s="26"/>
     </row>
@@ -8509,181 +8558,181 @@
         <v>0</v>
       </c>
       <c r="B1">
-        <v>1015.890014648438</v>
+        <v>1279.9599609375</v>
       </c>
       <c r="C1">
-        <v>1279.9599609375</v>
+        <v>1214.829956054688</v>
       </c>
       <c r="D1">
-        <v>1214.829956054688</v>
+        <v>1288.030029296875</v>
       </c>
       <c r="E1">
-        <v>1288.030029296875</v>
+        <v>1427.619995117188</v>
       </c>
       <c r="F1">
-        <v>1427.619995117188</v>
+        <v>1350.5</v>
       </c>
       <c r="G1">
-        <v>1350.5</v>
+        <v>1258.579956054688</v>
       </c>
       <c r="H1">
-        <v>1258.579956054688</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="I1">
-        <v>1212.2099609375</v>
+        <v>1237.920043945312</v>
       </c>
       <c r="J1">
-        <v>1237.920043945312</v>
+        <v>1271.050048828125</v>
       </c>
       <c r="K1">
-        <v>1271.050048828125</v>
+        <v>1344.2900390625</v>
       </c>
       <c r="L1">
-        <v>1344.2900390625</v>
+        <v>1528.109985351562</v>
       </c>
       <c r="M1">
-        <v>1528.109985351562</v>
+        <v>1641.109985351562</v>
       </c>
       <c r="N1">
-        <v>1641.109985351562</v>
+        <v>1786.849975585938</v>
       </c>
       <c r="O1">
-        <v>1786.849975585938</v>
+        <v>1625.780029296875</v>
       </c>
       <c r="P1">
-        <v>1625.780029296875</v>
+        <v>1568.869995117188</v>
       </c>
       <c r="Q1">
-        <v>1568.869995117188</v>
+        <v>1600.619995117188</v>
       </c>
       <c r="R1">
-        <v>1600.619995117188</v>
+        <v>1596.079956054688</v>
       </c>
       <c r="S1">
-        <v>1596.079956054688</v>
+        <v>1493.119995117188</v>
       </c>
       <c r="T1">
-        <v>1493.119995117188</v>
+        <v>1480.77001953125</v>
       </c>
       <c r="U1">
-        <v>1480.77001953125</v>
+        <v>1499.369995117188</v>
       </c>
       <c r="V1">
-        <v>1499.369995117188</v>
+        <v>1484.949951171875</v>
       </c>
       <c r="W1">
-        <v>1484.949951171875</v>
+        <v>1484.97998046875</v>
       </c>
       <c r="X1">
-        <v>1484.97998046875</v>
+        <v>1566.699951171875</v>
       </c>
       <c r="Y1">
-        <v>1566.699951171875</v>
+        <v>1536.869995117188</v>
       </c>
       <c r="Z1">
-        <v>1536.869995117188</v>
+        <v>1553.400024414062</v>
       </c>
       <c r="AA1">
-        <v>1553.400024414062</v>
+        <v>1554.989990234375</v>
       </c>
       <c r="AB1">
-        <v>1554.989990234375</v>
+        <v>1740</v>
       </c>
       <c r="AC1">
-        <v>1740</v>
+        <v>1737.989990234375</v>
       </c>
       <c r="AD1">
-        <v>1737.989990234375</v>
+        <v>1764.170043945312</v>
       </c>
       <c r="AE1">
-        <v>1764.170043945312</v>
+        <v>1692.589965820312</v>
       </c>
       <c r="AF1">
-        <v>1692.589965820312</v>
+        <v>1633.349975585938</v>
       </c>
       <c r="AG1">
-        <v>1633.349975585938</v>
+        <v>1551.989990234375</v>
       </c>
       <c r="AH1">
-        <v>1551.989990234375</v>
+        <v>1530.89501953125</v>
       </c>
       <c r="AI1">
-        <v>1530.89501953125</v>
+        <v>1519.969970703125</v>
       </c>
       <c r="AJ1">
-        <v>1519.969970703125</v>
+        <v>1614.390014648438</v>
       </c>
       <c r="AK1">
-        <v>1614.390014648438</v>
+        <v>1791.819946289062</v>
       </c>
       <c r="AL1">
-        <v>1791.819946289062</v>
+        <v>1766.640014648438</v>
       </c>
       <c r="AM1">
-        <v>1766.640014648438</v>
+        <v>1887.0400390625</v>
       </c>
       <c r="AN1">
-        <v>1887.0400390625</v>
+        <v>1816.569946289062</v>
       </c>
       <c r="AO1">
-        <v>1816.569946289062</v>
+        <v>1753.619995117188</v>
       </c>
       <c r="AP1">
-        <v>1753.619995117188</v>
+        <v>1777.800048828125</v>
       </c>
       <c r="AQ1">
-        <v>1777.800048828125</v>
+        <v>1712.89001464843